--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="288">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -655,6 +655,12 @@
     <t>['24', '30', '59']</t>
   </si>
   <si>
+    <t>['17', '71']</t>
+  </si>
+  <si>
+    <t>['90+1']</t>
+  </si>
+  <si>
     <t>['16', '45+2']</t>
   </si>
   <si>
@@ -866,6 +872,12 @@
   </si>
   <si>
     <t>['27', '64']</t>
+  </si>
+  <si>
+    <t>['46']</t>
+  </si>
+  <si>
+    <t>['77']</t>
   </si>
 </sst>
 </file>
@@ -1227,7 +1239,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP181"/>
+  <dimension ref="A1:BP187"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1483,7 +1495,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q2">
         <v>2.4</v>
@@ -1561,7 +1573,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ2">
         <v>0.91</v>
@@ -1770,7 +1782,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ3">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1895,7 +1907,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q4">
         <v>3.6</v>
@@ -1973,10 +1985,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AQ4">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2179,7 +2191,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ5">
         <v>1</v>
@@ -2385,10 +2397,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ6">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2719,7 +2731,7 @@
         <v>90</v>
       </c>
       <c r="P8" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q8">
         <v>3.1</v>
@@ -3131,7 +3143,7 @@
         <v>94</v>
       </c>
       <c r="P10" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q10">
         <v>2.6</v>
@@ -3749,7 +3761,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q13">
         <v>3.1</v>
@@ -3830,7 +3842,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ13">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4033,7 +4045,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ14">
         <v>0.44</v>
@@ -4239,7 +4251,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ15">
         <v>0.6</v>
@@ -4367,7 +4379,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q16">
         <v>2.63</v>
@@ -4448,7 +4460,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ16">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4573,7 +4585,7 @@
         <v>99</v>
       </c>
       <c r="P17" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -5066,7 +5078,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ19">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5475,7 +5487,7 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ21">
         <v>1.7</v>
@@ -5603,7 +5615,7 @@
         <v>103</v>
       </c>
       <c r="P22" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -5887,10 +5899,10 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AQ23">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR23">
         <v>2.13</v>
@@ -6015,7 +6027,7 @@
         <v>105</v>
       </c>
       <c r="P24" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q24">
         <v>2.62</v>
@@ -6096,7 +6108,7 @@
         <v>1</v>
       </c>
       <c r="AQ24">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR24">
         <v>1.39</v>
@@ -6427,7 +6439,7 @@
         <v>106</v>
       </c>
       <c r="P26" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q26">
         <v>2.83</v>
@@ -6505,7 +6517,7 @@
         <v>1</v>
       </c>
       <c r="AP26">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ26">
         <v>0.91</v>
@@ -6711,7 +6723,7 @@
         <v>3</v>
       </c>
       <c r="AP27">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ27">
         <v>1.2</v>
@@ -6839,7 +6851,7 @@
         <v>108</v>
       </c>
       <c r="P28" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q28">
         <v>2.6</v>
@@ -6920,7 +6932,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ28">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR28">
         <v>1.92</v>
@@ -7126,7 +7138,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ29">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR29">
         <v>1.48</v>
@@ -7535,7 +7547,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ31">
         <v>1.2</v>
@@ -7741,10 +7753,10 @@
         <v>3</v>
       </c>
       <c r="AP32">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ32">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR32">
         <v>0.82</v>
@@ -8153,7 +8165,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ34">
         <v>0.91</v>
@@ -8281,7 +8293,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q35">
         <v>3.3</v>
@@ -8487,7 +8499,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q36">
         <v>3.1</v>
@@ -8568,7 +8580,7 @@
         <v>2</v>
       </c>
       <c r="AQ36">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR36">
         <v>1.66</v>
@@ -8693,7 +8705,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q37">
         <v>3.4</v>
@@ -8771,7 +8783,7 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ37">
         <v>0.44</v>
@@ -8899,7 +8911,7 @@
         <v>90</v>
       </c>
       <c r="P38" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q38">
         <v>3.2</v>
@@ -8980,7 +8992,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ38">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR38">
         <v>1.59</v>
@@ -9105,7 +9117,7 @@
         <v>90</v>
       </c>
       <c r="P39" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q39">
         <v>3.4</v>
@@ -9389,7 +9401,7 @@
         <v>3</v>
       </c>
       <c r="AP40">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ40">
         <v>1.7</v>
@@ -9517,7 +9529,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q41">
         <v>2.5</v>
@@ -9598,7 +9610,7 @@
         <v>2</v>
       </c>
       <c r="AQ41">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR41">
         <v>1.73</v>
@@ -9723,7 +9735,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q42">
         <v>3.25</v>
@@ -9801,7 +9813,7 @@
         <v>1</v>
       </c>
       <c r="AP42">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AQ42">
         <v>0.91</v>
@@ -9929,7 +9941,7 @@
         <v>90</v>
       </c>
       <c r="P43" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q43">
         <v>2.75</v>
@@ -10010,7 +10022,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ43">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR43">
         <v>0.8</v>
@@ -10216,7 +10228,7 @@
         <v>1</v>
       </c>
       <c r="AQ44">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR44">
         <v>1.25</v>
@@ -10419,7 +10431,7 @@
         <v>3</v>
       </c>
       <c r="AP45">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ45">
         <v>1.3</v>
@@ -11246,7 +11258,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ49">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR49">
         <v>1.53</v>
@@ -11655,7 +11667,7 @@
         <v>1.33</v>
       </c>
       <c r="AP51">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ51">
         <v>1.2</v>
@@ -11989,7 +12001,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -12067,7 +12079,7 @@
         <v>2</v>
       </c>
       <c r="AP53">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AQ53">
         <v>0.8</v>
@@ -12195,7 +12207,7 @@
         <v>129</v>
       </c>
       <c r="P54" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q54">
         <v>2.55</v>
@@ -12273,7 +12285,7 @@
         <v>1</v>
       </c>
       <c r="AP54">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ54">
         <v>1</v>
@@ -12401,7 +12413,7 @@
         <v>130</v>
       </c>
       <c r="P55" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q55">
         <v>2.55</v>
@@ -12482,7 +12494,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ55">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR55">
         <v>1.98</v>
@@ -12688,7 +12700,7 @@
         <v>2.8</v>
       </c>
       <c r="AQ56">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR56">
         <v>1.76</v>
@@ -12813,7 +12825,7 @@
         <v>132</v>
       </c>
       <c r="P57" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -13019,7 +13031,7 @@
         <v>133</v>
       </c>
       <c r="P58" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -13225,7 +13237,7 @@
         <v>134</v>
       </c>
       <c r="P59" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q59">
         <v>2.62</v>
@@ -13303,10 +13315,10 @@
         <v>1.67</v>
       </c>
       <c r="AP59">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ59">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR59">
         <v>1.53</v>
@@ -13431,7 +13443,7 @@
         <v>135</v>
       </c>
       <c r="P60" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q60">
         <v>2.88</v>
@@ -13509,10 +13521,10 @@
         <v>1</v>
       </c>
       <c r="AP60">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ60">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR60">
         <v>1.51</v>
@@ -13715,7 +13727,7 @@
         <v>1.5</v>
       </c>
       <c r="AP61">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ61">
         <v>1.3</v>
@@ -13843,7 +13855,7 @@
         <v>137</v>
       </c>
       <c r="P62" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q62">
         <v>3.6</v>
@@ -14049,7 +14061,7 @@
         <v>138</v>
       </c>
       <c r="P63" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q63">
         <v>3.75</v>
@@ -14130,7 +14142,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ63">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR63">
         <v>1.33</v>
@@ -14542,7 +14554,7 @@
         <v>2</v>
       </c>
       <c r="AQ65">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR65">
         <v>1.6</v>
@@ -14951,7 +14963,7 @@
         <v>0.25</v>
       </c>
       <c r="AP67">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AQ67">
         <v>0.91</v>
@@ -15079,7 +15091,7 @@
         <v>143</v>
       </c>
       <c r="P68" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15285,7 +15297,7 @@
         <v>144</v>
       </c>
       <c r="P69" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15366,7 +15378,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ69">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR69">
         <v>1.23</v>
@@ -15491,7 +15503,7 @@
         <v>145</v>
       </c>
       <c r="P70" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q70">
         <v>3.75</v>
@@ -15775,7 +15787,7 @@
         <v>2</v>
       </c>
       <c r="AP71">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ71">
         <v>1.5</v>
@@ -15903,7 +15915,7 @@
         <v>147</v>
       </c>
       <c r="P72" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16109,7 +16121,7 @@
         <v>90</v>
       </c>
       <c r="P73" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q73">
         <v>4.33</v>
@@ -16190,7 +16202,7 @@
         <v>0.36</v>
       </c>
       <c r="AQ73">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR73">
         <v>1</v>
@@ -16315,7 +16327,7 @@
         <v>90</v>
       </c>
       <c r="P74" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q74">
         <v>2.4</v>
@@ -16521,7 +16533,7 @@
         <v>148</v>
       </c>
       <c r="P75" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q75">
         <v>3.5</v>
@@ -16727,7 +16739,7 @@
         <v>149</v>
       </c>
       <c r="P76" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q76">
         <v>2.88</v>
@@ -17011,10 +17023,10 @@
         <v>2</v>
       </c>
       <c r="AP77">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ77">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR77">
         <v>1.29</v>
@@ -17217,7 +17229,7 @@
         <v>1</v>
       </c>
       <c r="AP78">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ78">
         <v>1.3</v>
@@ -17345,7 +17357,7 @@
         <v>151</v>
       </c>
       <c r="P79" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17423,10 +17435,10 @@
         <v>0.25</v>
       </c>
       <c r="AP79">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ79">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR79">
         <v>1.66</v>
@@ -17551,7 +17563,7 @@
         <v>152</v>
       </c>
       <c r="P80" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q80">
         <v>2.05</v>
@@ -17632,7 +17644,7 @@
         <v>2.8</v>
       </c>
       <c r="AQ80">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR80">
         <v>2.09</v>
@@ -17757,7 +17769,7 @@
         <v>90</v>
       </c>
       <c r="P81" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q81">
         <v>4.33</v>
@@ -18041,7 +18053,7 @@
         <v>1.33</v>
       </c>
       <c r="AP82">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ82">
         <v>0.8</v>
@@ -18247,7 +18259,7 @@
         <v>0.8</v>
       </c>
       <c r="AP83">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AQ83">
         <v>1</v>
@@ -18456,7 +18468,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ84">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR84">
         <v>1.51</v>
@@ -18581,7 +18593,7 @@
         <v>90</v>
       </c>
       <c r="P85" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q85">
         <v>3.1</v>
@@ -18659,7 +18671,7 @@
         <v>0</v>
       </c>
       <c r="AP85">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ85">
         <v>0.6</v>
@@ -18787,7 +18799,7 @@
         <v>156</v>
       </c>
       <c r="P86" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -19071,10 +19083,10 @@
         <v>1</v>
       </c>
       <c r="AP87">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ87">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR87">
         <v>1.28</v>
@@ -19611,7 +19623,7 @@
         <v>90</v>
       </c>
       <c r="P90" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q90">
         <v>2.38</v>
@@ -20023,7 +20035,7 @@
         <v>160</v>
       </c>
       <c r="P92" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20310,7 +20322,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ93">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR93">
         <v>1.43</v>
@@ -20513,10 +20525,10 @@
         <v>1.2</v>
       </c>
       <c r="AP94">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ94">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR94">
         <v>1.21</v>
@@ -20641,7 +20653,7 @@
         <v>162</v>
       </c>
       <c r="P95" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q95">
         <v>1.9</v>
@@ -20847,7 +20859,7 @@
         <v>163</v>
       </c>
       <c r="P96" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q96">
         <v>2.75</v>
@@ -20925,10 +20937,10 @@
         <v>1.2</v>
       </c>
       <c r="AP96">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ96">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR96">
         <v>1.65</v>
@@ -21131,7 +21143,7 @@
         <v>2.4</v>
       </c>
       <c r="AP97">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ97">
         <v>1.7</v>
@@ -21259,7 +21271,7 @@
         <v>90</v>
       </c>
       <c r="P98" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q98">
         <v>4.75</v>
@@ -21546,7 +21558,7 @@
         <v>2</v>
       </c>
       <c r="AQ99">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR99">
         <v>1.8</v>
@@ -21749,7 +21761,7 @@
         <v>0.6</v>
       </c>
       <c r="AP100">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AQ100">
         <v>0.6</v>
@@ -22164,7 +22176,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ102">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR102">
         <v>1.45</v>
@@ -22289,7 +22301,7 @@
         <v>166</v>
       </c>
       <c r="P103" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q103">
         <v>4.2</v>
@@ -22367,7 +22379,7 @@
         <v>1.33</v>
       </c>
       <c r="AP103">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ103">
         <v>1.2</v>
@@ -22495,7 +22507,7 @@
         <v>167</v>
       </c>
       <c r="P104" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q104">
         <v>2.25</v>
@@ -22576,7 +22588,7 @@
         <v>2</v>
       </c>
       <c r="AQ104">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR104">
         <v>1.78</v>
@@ -23319,7 +23331,7 @@
         <v>90</v>
       </c>
       <c r="P108" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q108">
         <v>4.5</v>
@@ -23400,7 +23412,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ108">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR108">
         <v>1.07</v>
@@ -23603,10 +23615,10 @@
         <v>1.4</v>
       </c>
       <c r="AP109">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ109">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR109">
         <v>1.6</v>
@@ -23812,7 +23824,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ110">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR110">
         <v>1.85</v>
@@ -24015,7 +24027,7 @@
         <v>0.8</v>
       </c>
       <c r="AP111">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ111">
         <v>1.2</v>
@@ -24143,7 +24155,7 @@
         <v>173</v>
       </c>
       <c r="P112" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q112">
         <v>3.5</v>
@@ -24555,7 +24567,7 @@
         <v>90</v>
       </c>
       <c r="P114" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q114">
         <v>2.85</v>
@@ -24839,7 +24851,7 @@
         <v>2.17</v>
       </c>
       <c r="AP115">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ115">
         <v>1.7</v>
@@ -24967,7 +24979,7 @@
         <v>175</v>
       </c>
       <c r="P116" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q116">
         <v>2.4</v>
@@ -25379,7 +25391,7 @@
         <v>90</v>
       </c>
       <c r="P118" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q118">
         <v>4</v>
@@ -25460,7 +25472,7 @@
         <v>0.36</v>
       </c>
       <c r="AQ118">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR118">
         <v>0.99</v>
@@ -25869,10 +25881,10 @@
         <v>1.5</v>
       </c>
       <c r="AP120">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ120">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR120">
         <v>1.24</v>
@@ -25997,7 +26009,7 @@
         <v>178</v>
       </c>
       <c r="P121" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q121">
         <v>2.88</v>
@@ -26078,7 +26090,7 @@
         <v>1</v>
       </c>
       <c r="AQ121">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR121">
         <v>1.35</v>
@@ -26487,7 +26499,7 @@
         <v>1</v>
       </c>
       <c r="AP123">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ123">
         <v>1</v>
@@ -26696,7 +26708,7 @@
         <v>2</v>
       </c>
       <c r="AQ124">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR124">
         <v>1.79</v>
@@ -26899,7 +26911,7 @@
         <v>1.14</v>
       </c>
       <c r="AP125">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ125">
         <v>1.2</v>
@@ -27105,10 +27117,10 @@
         <v>0.17</v>
       </c>
       <c r="AP126">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AQ126">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR126">
         <v>1.58</v>
@@ -28675,7 +28687,7 @@
         <v>90</v>
       </c>
       <c r="P134" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q134">
         <v>3.2</v>
@@ -28753,7 +28765,7 @@
         <v>0.43</v>
       </c>
       <c r="AP134">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ134">
         <v>0.6</v>
@@ -28881,7 +28893,7 @@
         <v>90</v>
       </c>
       <c r="P135" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q135">
         <v>5</v>
@@ -29371,7 +29383,7 @@
         <v>1.29</v>
       </c>
       <c r="AP137">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ137">
         <v>1.5</v>
@@ -29577,10 +29589,10 @@
         <v>0.14</v>
       </c>
       <c r="AP138">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ138">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR138">
         <v>1.44</v>
@@ -29786,7 +29798,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ139">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR139">
         <v>1.46</v>
@@ -29911,7 +29923,7 @@
         <v>188</v>
       </c>
       <c r="P140" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q140">
         <v>2.95</v>
@@ -29989,10 +30001,10 @@
         <v>1.13</v>
       </c>
       <c r="AP140">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ140">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR140">
         <v>1.24</v>
@@ -30117,7 +30129,7 @@
         <v>189</v>
       </c>
       <c r="P141" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q141">
         <v>2.8</v>
@@ -30195,10 +30207,10 @@
         <v>1.38</v>
       </c>
       <c r="AP141">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ141">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR141">
         <v>1.72</v>
@@ -30816,7 +30828,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ144">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR144">
         <v>1.43</v>
@@ -30941,7 +30953,7 @@
         <v>192</v>
       </c>
       <c r="P145" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q145">
         <v>2.75</v>
@@ -31019,7 +31031,7 @@
         <v>0.57</v>
       </c>
       <c r="AP145">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AQ145">
         <v>0.44</v>
@@ -31147,7 +31159,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q146">
         <v>3.75</v>
@@ -31225,7 +31237,7 @@
         <v>1</v>
       </c>
       <c r="AP146">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ146">
         <v>0.8</v>
@@ -31353,7 +31365,7 @@
         <v>129</v>
       </c>
       <c r="P147" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q147">
         <v>3.75</v>
@@ -31434,7 +31446,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ147">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR147">
         <v>1.16</v>
@@ -31559,7 +31571,7 @@
         <v>90</v>
       </c>
       <c r="P148" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q148">
         <v>2.4</v>
@@ -31765,7 +31777,7 @@
         <v>90</v>
       </c>
       <c r="P149" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q149">
         <v>3.1</v>
@@ -31843,7 +31855,7 @@
         <v>0.88</v>
       </c>
       <c r="AP149">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ149">
         <v>0.91</v>
@@ -32177,7 +32189,7 @@
         <v>194</v>
       </c>
       <c r="P151" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q151">
         <v>1.62</v>
@@ -32258,7 +32270,7 @@
         <v>2</v>
       </c>
       <c r="AQ151">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR151">
         <v>1.79</v>
@@ -32589,7 +32601,7 @@
         <v>95</v>
       </c>
       <c r="P153" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q153">
         <v>2.63</v>
@@ -33285,7 +33297,7 @@
         <v>1</v>
       </c>
       <c r="AP156">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ156">
         <v>1.2</v>
@@ -33413,7 +33425,7 @@
         <v>197</v>
       </c>
       <c r="P157" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q157">
         <v>2.7</v>
@@ -33619,7 +33631,7 @@
         <v>96</v>
       </c>
       <c r="P158" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q158">
         <v>2.55</v>
@@ -33825,7 +33837,7 @@
         <v>198</v>
       </c>
       <c r="P159" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q159">
         <v>3.3</v>
@@ -34031,7 +34043,7 @@
         <v>90</v>
       </c>
       <c r="P160" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q160">
         <v>2.75</v>
@@ -34521,10 +34533,10 @@
         <v>0.13</v>
       </c>
       <c r="AP162">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ162">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR162">
         <v>1.68</v>
@@ -34730,7 +34742,7 @@
         <v>2.8</v>
       </c>
       <c r="AQ163">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR163">
         <v>1.75</v>
@@ -34936,7 +34948,7 @@
         <v>2</v>
       </c>
       <c r="AQ164">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR164">
         <v>1.64</v>
@@ -35139,10 +35151,10 @@
         <v>1.38</v>
       </c>
       <c r="AP165">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ165">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR165">
         <v>1.13</v>
@@ -35345,7 +35357,7 @@
         <v>0.89</v>
       </c>
       <c r="AP166">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ166">
         <v>0.8</v>
@@ -35473,7 +35485,7 @@
         <v>109</v>
       </c>
       <c r="P167" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q167">
         <v>3.35</v>
@@ -35885,7 +35897,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q169">
         <v>2.8</v>
@@ -35963,10 +35975,10 @@
         <v>1.56</v>
       </c>
       <c r="AP169">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ169">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR169">
         <v>1.32</v>
@@ -36091,7 +36103,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q170">
         <v>3</v>
@@ -36375,7 +36387,7 @@
         <v>1</v>
       </c>
       <c r="AP171">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AQ171">
         <v>1.2</v>
@@ -36503,7 +36515,7 @@
         <v>90</v>
       </c>
       <c r="P172" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q172">
         <v>2.63</v>
@@ -36584,7 +36596,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ172">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR172">
         <v>1.73</v>
@@ -36709,7 +36721,7 @@
         <v>207</v>
       </c>
       <c r="P173" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q173">
         <v>2.3</v>
@@ -36790,7 +36802,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ173">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR173">
         <v>1.78</v>
@@ -36993,7 +37005,7 @@
         <v>0.9</v>
       </c>
       <c r="AP174">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ174">
         <v>0.91</v>
@@ -37739,7 +37751,7 @@
         <v>90</v>
       </c>
       <c r="P178" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q178">
         <v>3.25</v>
@@ -38151,7 +38163,7 @@
         <v>212</v>
       </c>
       <c r="P180" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q180">
         <v>2.2</v>
@@ -38357,7 +38369,7 @@
         <v>90</v>
       </c>
       <c r="P181" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q181">
         <v>3.25</v>
@@ -38514,6 +38526,1242 @@
       </c>
       <c r="BP181">
         <v>1.14</v>
+      </c>
+    </row>
+    <row r="182" spans="1:68">
+      <c r="A182" s="1">
+        <v>181</v>
+      </c>
+      <c r="B182">
+        <v>7469049</v>
+      </c>
+      <c r="C182" t="s">
+        <v>68</v>
+      </c>
+      <c r="D182" t="s">
+        <v>69</v>
+      </c>
+      <c r="E182" s="2">
+        <v>45688.66666666666</v>
+      </c>
+      <c r="F182">
+        <v>21</v>
+      </c>
+      <c r="G182" t="s">
+        <v>72</v>
+      </c>
+      <c r="H182" t="s">
+        <v>77</v>
+      </c>
+      <c r="I182">
+        <v>0</v>
+      </c>
+      <c r="J182">
+        <v>0</v>
+      </c>
+      <c r="K182">
+        <v>0</v>
+      </c>
+      <c r="L182">
+        <v>0</v>
+      </c>
+      <c r="M182">
+        <v>1</v>
+      </c>
+      <c r="N182">
+        <v>1</v>
+      </c>
+      <c r="O182" t="s">
+        <v>90</v>
+      </c>
+      <c r="P182" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q182">
+        <v>1.95</v>
+      </c>
+      <c r="R182">
+        <v>2.3</v>
+      </c>
+      <c r="S182">
+        <v>7.5</v>
+      </c>
+      <c r="T182">
+        <v>1.36</v>
+      </c>
+      <c r="U182">
+        <v>3</v>
+      </c>
+      <c r="V182">
+        <v>2.75</v>
+      </c>
+      <c r="W182">
+        <v>1.4</v>
+      </c>
+      <c r="X182">
+        <v>8</v>
+      </c>
+      <c r="Y182">
+        <v>1.08</v>
+      </c>
+      <c r="Z182">
+        <v>1.35</v>
+      </c>
+      <c r="AA182">
+        <v>4.6</v>
+      </c>
+      <c r="AB182">
+        <v>8.1</v>
+      </c>
+      <c r="AC182">
+        <v>1.04</v>
+      </c>
+      <c r="AD182">
+        <v>10</v>
+      </c>
+      <c r="AE182">
+        <v>1.25</v>
+      </c>
+      <c r="AF182">
+        <v>3.85</v>
+      </c>
+      <c r="AG182">
+        <v>1.76</v>
+      </c>
+      <c r="AH182">
+        <v>1.95</v>
+      </c>
+      <c r="AI182">
+        <v>2.1</v>
+      </c>
+      <c r="AJ182">
+        <v>1.67</v>
+      </c>
+      <c r="AK182">
+        <v>1.07</v>
+      </c>
+      <c r="AL182">
+        <v>1.18</v>
+      </c>
+      <c r="AM182">
+        <v>3.1</v>
+      </c>
+      <c r="AN182">
+        <v>2.4</v>
+      </c>
+      <c r="AO182">
+        <v>1.22</v>
+      </c>
+      <c r="AP182">
+        <v>2.18</v>
+      </c>
+      <c r="AQ182">
+        <v>1.4</v>
+      </c>
+      <c r="AR182">
+        <v>1.62</v>
+      </c>
+      <c r="AS182">
+        <v>1.11</v>
+      </c>
+      <c r="AT182">
+        <v>2.73</v>
+      </c>
+      <c r="AU182">
+        <v>4</v>
+      </c>
+      <c r="AV182">
+        <v>4</v>
+      </c>
+      <c r="AW182">
+        <v>9</v>
+      </c>
+      <c r="AX182">
+        <v>6</v>
+      </c>
+      <c r="AY182">
+        <v>13</v>
+      </c>
+      <c r="AZ182">
+        <v>10</v>
+      </c>
+      <c r="BA182">
+        <v>6</v>
+      </c>
+      <c r="BB182">
+        <v>6</v>
+      </c>
+      <c r="BC182">
+        <v>12</v>
+      </c>
+      <c r="BD182">
+        <v>1.29</v>
+      </c>
+      <c r="BE182">
+        <v>7.5</v>
+      </c>
+      <c r="BF182">
+        <v>3.95</v>
+      </c>
+      <c r="BG182">
+        <v>1.43</v>
+      </c>
+      <c r="BH182">
+        <v>2.55</v>
+      </c>
+      <c r="BI182">
+        <v>1.72</v>
+      </c>
+      <c r="BJ182">
+        <v>1.98</v>
+      </c>
+      <c r="BK182">
+        <v>2.15</v>
+      </c>
+      <c r="BL182">
+        <v>1.61</v>
+      </c>
+      <c r="BM182">
+        <v>2.7</v>
+      </c>
+      <c r="BN182">
+        <v>1.38</v>
+      </c>
+      <c r="BO182">
+        <v>3.55</v>
+      </c>
+      <c r="BP182">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="183" spans="1:68">
+      <c r="A183" s="1">
+        <v>182</v>
+      </c>
+      <c r="B183">
+        <v>7469047</v>
+      </c>
+      <c r="C183" t="s">
+        <v>68</v>
+      </c>
+      <c r="D183" t="s">
+        <v>69</v>
+      </c>
+      <c r="E183" s="2">
+        <v>45688.66666666666</v>
+      </c>
+      <c r="F183">
+        <v>21</v>
+      </c>
+      <c r="G183" t="s">
+        <v>74</v>
+      </c>
+      <c r="H183" t="s">
+        <v>81</v>
+      </c>
+      <c r="I183">
+        <v>1</v>
+      </c>
+      <c r="J183">
+        <v>1</v>
+      </c>
+      <c r="K183">
+        <v>2</v>
+      </c>
+      <c r="L183">
+        <v>2</v>
+      </c>
+      <c r="M183">
+        <v>1</v>
+      </c>
+      <c r="N183">
+        <v>3</v>
+      </c>
+      <c r="O183" t="s">
+        <v>213</v>
+      </c>
+      <c r="P183" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q183">
+        <v>2.95</v>
+      </c>
+      <c r="R183">
+        <v>2.05</v>
+      </c>
+      <c r="S183">
+        <v>3.35</v>
+      </c>
+      <c r="T183">
+        <v>1.38</v>
+      </c>
+      <c r="U183">
+        <v>2.8</v>
+      </c>
+      <c r="V183">
+        <v>2.65</v>
+      </c>
+      <c r="W183">
+        <v>1.42</v>
+      </c>
+      <c r="X183">
+        <v>7.6</v>
+      </c>
+      <c r="Y183">
+        <v>1.05</v>
+      </c>
+      <c r="Z183">
+        <v>2.59</v>
+      </c>
+      <c r="AA183">
+        <v>3.38</v>
+      </c>
+      <c r="AB183">
+        <v>2.69</v>
+      </c>
+      <c r="AC183">
+        <v>1.05</v>
+      </c>
+      <c r="AD183">
+        <v>9</v>
+      </c>
+      <c r="AE183">
+        <v>1.28</v>
+      </c>
+      <c r="AF183">
+        <v>3.55</v>
+      </c>
+      <c r="AG183">
+        <v>1.86</v>
+      </c>
+      <c r="AH183">
+        <v>1.94</v>
+      </c>
+      <c r="AI183">
+        <v>1.62</v>
+      </c>
+      <c r="AJ183">
+        <v>2.1</v>
+      </c>
+      <c r="AK183">
+        <v>1.4</v>
+      </c>
+      <c r="AL183">
+        <v>1.25</v>
+      </c>
+      <c r="AM183">
+        <v>1.55</v>
+      </c>
+      <c r="AN183">
+        <v>2</v>
+      </c>
+      <c r="AO183">
+        <v>1</v>
+      </c>
+      <c r="AP183">
+        <v>2.09</v>
+      </c>
+      <c r="AQ183">
+        <v>0.91</v>
+      </c>
+      <c r="AR183">
+        <v>1.2</v>
+      </c>
+      <c r="AS183">
+        <v>1.37</v>
+      </c>
+      <c r="AT183">
+        <v>2.57</v>
+      </c>
+      <c r="AU183">
+        <v>7</v>
+      </c>
+      <c r="AV183">
+        <v>8</v>
+      </c>
+      <c r="AW183">
+        <v>8</v>
+      </c>
+      <c r="AX183">
+        <v>7</v>
+      </c>
+      <c r="AY183">
+        <v>15</v>
+      </c>
+      <c r="AZ183">
+        <v>15</v>
+      </c>
+      <c r="BA183">
+        <v>3</v>
+      </c>
+      <c r="BB183">
+        <v>9</v>
+      </c>
+      <c r="BC183">
+        <v>12</v>
+      </c>
+      <c r="BD183">
+        <v>1.96</v>
+      </c>
+      <c r="BE183">
+        <v>6.4</v>
+      </c>
+      <c r="BF183">
+        <v>2.05</v>
+      </c>
+      <c r="BG183">
+        <v>1.42</v>
+      </c>
+      <c r="BH183">
+        <v>2.65</v>
+      </c>
+      <c r="BI183">
+        <v>1.7</v>
+      </c>
+      <c r="BJ183">
+        <v>2.02</v>
+      </c>
+      <c r="BK183">
+        <v>2.1</v>
+      </c>
+      <c r="BL183">
+        <v>1.64</v>
+      </c>
+      <c r="BM183">
+        <v>2.7</v>
+      </c>
+      <c r="BN183">
+        <v>1.4</v>
+      </c>
+      <c r="BO183">
+        <v>3.55</v>
+      </c>
+      <c r="BP183">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="184" spans="1:68">
+      <c r="A184" s="1">
+        <v>183</v>
+      </c>
+      <c r="B184">
+        <v>7469048</v>
+      </c>
+      <c r="C184" t="s">
+        <v>68</v>
+      </c>
+      <c r="D184" t="s">
+        <v>69</v>
+      </c>
+      <c r="E184" s="2">
+        <v>45688.66666666666</v>
+      </c>
+      <c r="F184">
+        <v>21</v>
+      </c>
+      <c r="G184" t="s">
+        <v>73</v>
+      </c>
+      <c r="H184" t="s">
+        <v>84</v>
+      </c>
+      <c r="I184">
+        <v>1</v>
+      </c>
+      <c r="J184">
+        <v>0</v>
+      </c>
+      <c r="K184">
+        <v>1</v>
+      </c>
+      <c r="L184">
+        <v>1</v>
+      </c>
+      <c r="M184">
+        <v>0</v>
+      </c>
+      <c r="N184">
+        <v>1</v>
+      </c>
+      <c r="O184" t="s">
+        <v>176</v>
+      </c>
+      <c r="P184" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q184">
+        <v>3.25</v>
+      </c>
+      <c r="R184">
+        <v>2</v>
+      </c>
+      <c r="S184">
+        <v>3.5</v>
+      </c>
+      <c r="T184">
+        <v>1.5</v>
+      </c>
+      <c r="U184">
+        <v>2.5</v>
+      </c>
+      <c r="V184">
+        <v>3.4</v>
+      </c>
+      <c r="W184">
+        <v>1.3</v>
+      </c>
+      <c r="X184">
+        <v>10</v>
+      </c>
+      <c r="Y184">
+        <v>1.06</v>
+      </c>
+      <c r="Z184">
+        <v>2.12</v>
+      </c>
+      <c r="AA184">
+        <v>3.4</v>
+      </c>
+      <c r="AB184">
+        <v>3.13</v>
+      </c>
+      <c r="AC184">
+        <v>1.06</v>
+      </c>
+      <c r="AD184">
+        <v>8.5</v>
+      </c>
+      <c r="AE184">
+        <v>1.38</v>
+      </c>
+      <c r="AF184">
+        <v>2.95</v>
+      </c>
+      <c r="AG184">
+        <v>2</v>
+      </c>
+      <c r="AH184">
+        <v>1.72</v>
+      </c>
+      <c r="AI184">
+        <v>1.91</v>
+      </c>
+      <c r="AJ184">
+        <v>1.8</v>
+      </c>
+      <c r="AK184">
+        <v>1.33</v>
+      </c>
+      <c r="AL184">
+        <v>1.29</v>
+      </c>
+      <c r="AM184">
+        <v>1.66</v>
+      </c>
+      <c r="AN184">
+        <v>2</v>
+      </c>
+      <c r="AO184">
+        <v>1.4</v>
+      </c>
+      <c r="AP184">
+        <v>2.09</v>
+      </c>
+      <c r="AQ184">
+        <v>1.27</v>
+      </c>
+      <c r="AR184">
+        <v>1.62</v>
+      </c>
+      <c r="AS184">
+        <v>1.3</v>
+      </c>
+      <c r="AT184">
+        <v>2.92</v>
+      </c>
+      <c r="AU184">
+        <v>4</v>
+      </c>
+      <c r="AV184">
+        <v>5</v>
+      </c>
+      <c r="AW184">
+        <v>8</v>
+      </c>
+      <c r="AX184">
+        <v>9</v>
+      </c>
+      <c r="AY184">
+        <v>12</v>
+      </c>
+      <c r="AZ184">
+        <v>14</v>
+      </c>
+      <c r="BA184">
+        <v>6</v>
+      </c>
+      <c r="BB184">
+        <v>4</v>
+      </c>
+      <c r="BC184">
+        <v>10</v>
+      </c>
+      <c r="BD184">
+        <v>1.98</v>
+      </c>
+      <c r="BE184">
+        <v>6.4</v>
+      </c>
+      <c r="BF184">
+        <v>2</v>
+      </c>
+      <c r="BG184">
+        <v>1.47</v>
+      </c>
+      <c r="BH184">
+        <v>2.48</v>
+      </c>
+      <c r="BI184">
+        <v>1.79</v>
+      </c>
+      <c r="BJ184">
+        <v>1.9</v>
+      </c>
+      <c r="BK184">
+        <v>2.28</v>
+      </c>
+      <c r="BL184">
+        <v>1.54</v>
+      </c>
+      <c r="BM184">
+        <v>2.95</v>
+      </c>
+      <c r="BN184">
+        <v>1.33</v>
+      </c>
+      <c r="BO184">
+        <v>4</v>
+      </c>
+      <c r="BP184">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="185" spans="1:68">
+      <c r="A185" s="1">
+        <v>184</v>
+      </c>
+      <c r="B185">
+        <v>7469051</v>
+      </c>
+      <c r="C185" t="s">
+        <v>68</v>
+      </c>
+      <c r="D185" t="s">
+        <v>69</v>
+      </c>
+      <c r="E185" s="2">
+        <v>45688.66666666666</v>
+      </c>
+      <c r="F185">
+        <v>21</v>
+      </c>
+      <c r="G185" t="s">
+        <v>82</v>
+      </c>
+      <c r="H185" t="s">
+        <v>80</v>
+      </c>
+      <c r="I185">
+        <v>0</v>
+      </c>
+      <c r="J185">
+        <v>0</v>
+      </c>
+      <c r="K185">
+        <v>0</v>
+      </c>
+      <c r="L185">
+        <v>1</v>
+      </c>
+      <c r="M185">
+        <v>1</v>
+      </c>
+      <c r="N185">
+        <v>2</v>
+      </c>
+      <c r="O185" t="s">
+        <v>214</v>
+      </c>
+      <c r="P185" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q185">
+        <v>2.6</v>
+      </c>
+      <c r="R185">
+        <v>2.05</v>
+      </c>
+      <c r="S185">
+        <v>4</v>
+      </c>
+      <c r="T185">
+        <v>1.42</v>
+      </c>
+      <c r="U185">
+        <v>2.65</v>
+      </c>
+      <c r="V185">
+        <v>2.88</v>
+      </c>
+      <c r="W185">
+        <v>1.36</v>
+      </c>
+      <c r="X185">
+        <v>7.4</v>
+      </c>
+      <c r="Y185">
+        <v>1.06</v>
+      </c>
+      <c r="Z185">
+        <v>2.06</v>
+      </c>
+      <c r="AA185">
+        <v>3.48</v>
+      </c>
+      <c r="AB185">
+        <v>3.56</v>
+      </c>
+      <c r="AC185">
+        <v>1.07</v>
+      </c>
+      <c r="AD185">
+        <v>8</v>
+      </c>
+      <c r="AE185">
+        <v>1.35</v>
+      </c>
+      <c r="AF185">
+        <v>3.1</v>
+      </c>
+      <c r="AG185">
+        <v>2.07</v>
+      </c>
+      <c r="AH185">
+        <v>1.75</v>
+      </c>
+      <c r="AI185">
+        <v>1.83</v>
+      </c>
+      <c r="AJ185">
+        <v>1.85</v>
+      </c>
+      <c r="AK185">
+        <v>1.25</v>
+      </c>
+      <c r="AL185">
+        <v>1.28</v>
+      </c>
+      <c r="AM185">
+        <v>1.73</v>
+      </c>
+      <c r="AN185">
+        <v>2</v>
+      </c>
+      <c r="AO185">
+        <v>1.5</v>
+      </c>
+      <c r="AP185">
+        <v>1.9</v>
+      </c>
+      <c r="AQ185">
+        <v>1.45</v>
+      </c>
+      <c r="AR185">
+        <v>1.51</v>
+      </c>
+      <c r="AS185">
+        <v>1.08</v>
+      </c>
+      <c r="AT185">
+        <v>2.59</v>
+      </c>
+      <c r="AU185">
+        <v>9</v>
+      </c>
+      <c r="AV185">
+        <v>6</v>
+      </c>
+      <c r="AW185">
+        <v>13</v>
+      </c>
+      <c r="AX185">
+        <v>4</v>
+      </c>
+      <c r="AY185">
+        <v>22</v>
+      </c>
+      <c r="AZ185">
+        <v>10</v>
+      </c>
+      <c r="BA185">
+        <v>8</v>
+      </c>
+      <c r="BB185">
+        <v>4</v>
+      </c>
+      <c r="BC185">
+        <v>12</v>
+      </c>
+      <c r="BD185">
+        <v>1.72</v>
+      </c>
+      <c r="BE185">
+        <v>6.1</v>
+      </c>
+      <c r="BF185">
+        <v>2.4</v>
+      </c>
+      <c r="BG185">
+        <v>1.46</v>
+      </c>
+      <c r="BH185">
+        <v>2.5</v>
+      </c>
+      <c r="BI185">
+        <v>1.76</v>
+      </c>
+      <c r="BJ185">
+        <v>1.94</v>
+      </c>
+      <c r="BK185">
+        <v>2.2</v>
+      </c>
+      <c r="BL185">
+        <v>1.58</v>
+      </c>
+      <c r="BM185">
+        <v>2.9</v>
+      </c>
+      <c r="BN185">
+        <v>1.35</v>
+      </c>
+      <c r="BO185">
+        <v>3.8</v>
+      </c>
+      <c r="BP185">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="186" spans="1:68">
+      <c r="A186" s="1">
+        <v>185</v>
+      </c>
+      <c r="B186">
+        <v>7469053</v>
+      </c>
+      <c r="C186" t="s">
+        <v>68</v>
+      </c>
+      <c r="D186" t="s">
+        <v>69</v>
+      </c>
+      <c r="E186" s="2">
+        <v>45688.66666666666</v>
+      </c>
+      <c r="F186">
+        <v>21</v>
+      </c>
+      <c r="G186" t="s">
+        <v>83</v>
+      </c>
+      <c r="H186" t="s">
+        <v>78</v>
+      </c>
+      <c r="I186">
+        <v>1</v>
+      </c>
+      <c r="J186">
+        <v>0</v>
+      </c>
+      <c r="K186">
+        <v>1</v>
+      </c>
+      <c r="L186">
+        <v>1</v>
+      </c>
+      <c r="M186">
+        <v>1</v>
+      </c>
+      <c r="N186">
+        <v>2</v>
+      </c>
+      <c r="O186" t="s">
+        <v>123</v>
+      </c>
+      <c r="P186" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q186">
+        <v>3.25</v>
+      </c>
+      <c r="R186">
+        <v>1.91</v>
+      </c>
+      <c r="S186">
+        <v>3.45</v>
+      </c>
+      <c r="T186">
+        <v>1.53</v>
+      </c>
+      <c r="U186">
+        <v>2.38</v>
+      </c>
+      <c r="V186">
+        <v>3.4</v>
+      </c>
+      <c r="W186">
+        <v>1.28</v>
+      </c>
+      <c r="X186">
+        <v>11</v>
+      </c>
+      <c r="Y186">
+        <v>1.01</v>
+      </c>
+      <c r="Z186">
+        <v>2.74</v>
+      </c>
+      <c r="AA186">
+        <v>2.98</v>
+      </c>
+      <c r="AB186">
+        <v>2.84</v>
+      </c>
+      <c r="AC186">
+        <v>1.1</v>
+      </c>
+      <c r="AD186">
+        <v>6.5</v>
+      </c>
+      <c r="AE186">
+        <v>1.48</v>
+      </c>
+      <c r="AF186">
+        <v>2.6</v>
+      </c>
+      <c r="AG186">
+        <v>2.48</v>
+      </c>
+      <c r="AH186">
+        <v>1.54</v>
+      </c>
+      <c r="AI186">
+        <v>1.95</v>
+      </c>
+      <c r="AJ186">
+        <v>1.73</v>
+      </c>
+      <c r="AK186">
+        <v>1.4</v>
+      </c>
+      <c r="AL186">
+        <v>1.3</v>
+      </c>
+      <c r="AM186">
+        <v>1.48</v>
+      </c>
+      <c r="AN186">
+        <v>1.8</v>
+      </c>
+      <c r="AO186">
+        <v>1.33</v>
+      </c>
+      <c r="AP186">
+        <v>1.73</v>
+      </c>
+      <c r="AQ186">
+        <v>1.3</v>
+      </c>
+      <c r="AR186">
+        <v>1.69</v>
+      </c>
+      <c r="AS186">
+        <v>1.28</v>
+      </c>
+      <c r="AT186">
+        <v>2.97</v>
+      </c>
+      <c r="AU186">
+        <v>6</v>
+      </c>
+      <c r="AV186">
+        <v>3</v>
+      </c>
+      <c r="AW186">
+        <v>17</v>
+      </c>
+      <c r="AX186">
+        <v>3</v>
+      </c>
+      <c r="AY186">
+        <v>23</v>
+      </c>
+      <c r="AZ186">
+        <v>6</v>
+      </c>
+      <c r="BA186">
+        <v>4</v>
+      </c>
+      <c r="BB186">
+        <v>3</v>
+      </c>
+      <c r="BC186">
+        <v>7</v>
+      </c>
+      <c r="BD186">
+        <v>1.95</v>
+      </c>
+      <c r="BE186">
+        <v>6.25</v>
+      </c>
+      <c r="BF186">
+        <v>2.07</v>
+      </c>
+      <c r="BG186">
+        <v>1.53</v>
+      </c>
+      <c r="BH186">
+        <v>2.3</v>
+      </c>
+      <c r="BI186">
+        <v>1.91</v>
+      </c>
+      <c r="BJ186">
+        <v>1.78</v>
+      </c>
+      <c r="BK186">
+        <v>2.43</v>
+      </c>
+      <c r="BL186">
+        <v>1.48</v>
+      </c>
+      <c r="BM186">
+        <v>3.15</v>
+      </c>
+      <c r="BN186">
+        <v>1.29</v>
+      </c>
+      <c r="BO186">
+        <v>4.3</v>
+      </c>
+      <c r="BP186">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="187" spans="1:68">
+      <c r="A187" s="1">
+        <v>186</v>
+      </c>
+      <c r="B187">
+        <v>7469054</v>
+      </c>
+      <c r="C187" t="s">
+        <v>68</v>
+      </c>
+      <c r="D187" t="s">
+        <v>69</v>
+      </c>
+      <c r="E187" s="2">
+        <v>45688.66666666666</v>
+      </c>
+      <c r="F187">
+        <v>21</v>
+      </c>
+      <c r="G187" t="s">
+        <v>70</v>
+      </c>
+      <c r="H187" t="s">
+        <v>71</v>
+      </c>
+      <c r="I187">
+        <v>0</v>
+      </c>
+      <c r="J187">
+        <v>0</v>
+      </c>
+      <c r="K187">
+        <v>0</v>
+      </c>
+      <c r="L187">
+        <v>0</v>
+      </c>
+      <c r="M187">
+        <v>1</v>
+      </c>
+      <c r="N187">
+        <v>1</v>
+      </c>
+      <c r="O187" t="s">
+        <v>90</v>
+      </c>
+      <c r="P187" t="s">
+        <v>287</v>
+      </c>
+      <c r="Q187">
+        <v>2.55</v>
+      </c>
+      <c r="R187">
+        <v>1.95</v>
+      </c>
+      <c r="S187">
+        <v>4.75</v>
+      </c>
+      <c r="T187">
+        <v>1.5</v>
+      </c>
+      <c r="U187">
+        <v>2.4</v>
+      </c>
+      <c r="V187">
+        <v>3.3</v>
+      </c>
+      <c r="W187">
+        <v>1.28</v>
+      </c>
+      <c r="X187">
+        <v>9.4</v>
+      </c>
+      <c r="Y187">
+        <v>1.02</v>
+      </c>
+      <c r="Z187">
+        <v>1.83</v>
+      </c>
+      <c r="AA187">
+        <v>3.38</v>
+      </c>
+      <c r="AB187">
+        <v>4.7</v>
+      </c>
+      <c r="AC187">
+        <v>1.09</v>
+      </c>
+      <c r="AD187">
+        <v>7</v>
+      </c>
+      <c r="AE187">
+        <v>1.48</v>
+      </c>
+      <c r="AF187">
+        <v>2.65</v>
+      </c>
+      <c r="AG187">
+        <v>2.34</v>
+      </c>
+      <c r="AH187">
+        <v>1.6</v>
+      </c>
+      <c r="AI187">
+        <v>2.05</v>
+      </c>
+      <c r="AJ187">
+        <v>1.67</v>
+      </c>
+      <c r="AK187">
+        <v>1.2</v>
+      </c>
+      <c r="AL187">
+        <v>1.3</v>
+      </c>
+      <c r="AM187">
+        <v>1.83</v>
+      </c>
+      <c r="AN187">
+        <v>1.1</v>
+      </c>
+      <c r="AO187">
+        <v>0.4</v>
+      </c>
+      <c r="AP187">
+        <v>1</v>
+      </c>
+      <c r="AQ187">
+        <v>0.64</v>
+      </c>
+      <c r="AR187">
+        <v>1.32</v>
+      </c>
+      <c r="AS187">
+        <v>1</v>
+      </c>
+      <c r="AT187">
+        <v>2.32</v>
+      </c>
+      <c r="AU187">
+        <v>3</v>
+      </c>
+      <c r="AV187">
+        <v>7</v>
+      </c>
+      <c r="AW187">
+        <v>16</v>
+      </c>
+      <c r="AX187">
+        <v>2</v>
+      </c>
+      <c r="AY187">
+        <v>19</v>
+      </c>
+      <c r="AZ187">
+        <v>9</v>
+      </c>
+      <c r="BA187">
+        <v>7</v>
+      </c>
+      <c r="BB187">
+        <v>2</v>
+      </c>
+      <c r="BC187">
+        <v>9</v>
+      </c>
+      <c r="BD187">
+        <v>1.61</v>
+      </c>
+      <c r="BE187">
+        <v>6.25</v>
+      </c>
+      <c r="BF187">
+        <v>2.63</v>
+      </c>
+      <c r="BG187">
+        <v>1.5</v>
+      </c>
+      <c r="BH187">
+        <v>2.4</v>
+      </c>
+      <c r="BI187">
+        <v>1.84</v>
+      </c>
+      <c r="BJ187">
+        <v>1.84</v>
+      </c>
+      <c r="BK187">
+        <v>2.33</v>
+      </c>
+      <c r="BL187">
+        <v>1.52</v>
+      </c>
+      <c r="BM187">
+        <v>3.05</v>
+      </c>
+      <c r="BN187">
+        <v>1.3</v>
+      </c>
+      <c r="BO187">
+        <v>4.1</v>
+      </c>
+      <c r="BP187">
+        <v>1.19</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1202" uniqueCount="291">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -661,6 +661,12 @@
     <t>['90+1']</t>
   </si>
   <si>
+    <t>['66']</t>
+  </si>
+  <si>
+    <t>['48', '51', '70']</t>
+  </si>
+  <si>
     <t>['16', '45+2']</t>
   </si>
   <si>
@@ -878,6 +884,9 @@
   </si>
   <si>
     <t>['77']</t>
+  </si>
+  <si>
+    <t>['24', '57']</t>
   </si>
 </sst>
 </file>
@@ -1239,7 +1248,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP187"/>
+  <dimension ref="A1:BP190"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1495,7 +1504,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q2">
         <v>2.4</v>
@@ -1907,7 +1916,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q4">
         <v>3.6</v>
@@ -2603,7 +2612,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ7">
         <v>0.91</v>
@@ -2731,7 +2740,7 @@
         <v>90</v>
       </c>
       <c r="P8" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q8">
         <v>3.1</v>
@@ -2812,7 +2821,7 @@
         <v>1</v>
       </c>
       <c r="AQ8">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3018,7 +3027,7 @@
         <v>0.36</v>
       </c>
       <c r="AQ9">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3143,7 +3152,7 @@
         <v>94</v>
       </c>
       <c r="P10" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q10">
         <v>2.6</v>
@@ -3427,7 +3436,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ11">
         <v>1.3</v>
@@ -3761,7 +3770,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q13">
         <v>3.1</v>
@@ -4048,7 +4057,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ14">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4379,7 +4388,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q16">
         <v>2.63</v>
@@ -4585,7 +4594,7 @@
         <v>99</v>
       </c>
       <c r="P17" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -5075,7 +5084,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ19">
         <v>0.64</v>
@@ -5490,7 +5499,7 @@
         <v>1</v>
       </c>
       <c r="AQ21">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR21">
         <v>1.81</v>
@@ -5615,7 +5624,7 @@
         <v>103</v>
       </c>
       <c r="P22" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -5693,7 +5702,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ22">
         <v>1</v>
@@ -6027,7 +6036,7 @@
         <v>105</v>
       </c>
       <c r="P24" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q24">
         <v>2.62</v>
@@ -6439,7 +6448,7 @@
         <v>106</v>
       </c>
       <c r="P26" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q26">
         <v>2.83</v>
@@ -6726,7 +6735,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ27">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR27">
         <v>1.55</v>
@@ -6851,7 +6860,7 @@
         <v>108</v>
       </c>
       <c r="P28" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q28">
         <v>2.6</v>
@@ -8293,7 +8302,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q35">
         <v>3.3</v>
@@ -8499,7 +8508,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q36">
         <v>3.1</v>
@@ -8705,7 +8714,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q37">
         <v>3.4</v>
@@ -8786,7 +8795,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ37">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR37">
         <v>1.13</v>
@@ -8911,7 +8920,7 @@
         <v>90</v>
       </c>
       <c r="P38" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q38">
         <v>3.2</v>
@@ -8989,7 +8998,7 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ38">
         <v>0.91</v>
@@ -9117,7 +9126,7 @@
         <v>90</v>
       </c>
       <c r="P39" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q39">
         <v>3.4</v>
@@ -9404,7 +9413,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ40">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR40">
         <v>1.41</v>
@@ -9529,7 +9538,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q41">
         <v>2.5</v>
@@ -9607,7 +9616,7 @@
         <v>2</v>
       </c>
       <c r="AP41">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ41">
         <v>1.27</v>
@@ -9735,7 +9744,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q42">
         <v>3.25</v>
@@ -9941,7 +9950,7 @@
         <v>90</v>
       </c>
       <c r="P43" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q43">
         <v>2.75</v>
@@ -10019,7 +10028,7 @@
         <v>0.5</v>
       </c>
       <c r="AP43">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ43">
         <v>1.45</v>
@@ -10640,7 +10649,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ46">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR46">
         <v>1.88</v>
@@ -11670,7 +11679,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ51">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR51">
         <v>1.48</v>
@@ -12001,7 +12010,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -12207,7 +12216,7 @@
         <v>129</v>
       </c>
       <c r="P54" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q54">
         <v>2.55</v>
@@ -12413,7 +12422,7 @@
         <v>130</v>
       </c>
       <c r="P55" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q55">
         <v>2.55</v>
@@ -12825,7 +12834,7 @@
         <v>132</v>
       </c>
       <c r="P57" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -13031,7 +13040,7 @@
         <v>133</v>
       </c>
       <c r="P58" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -13237,7 +13246,7 @@
         <v>134</v>
       </c>
       <c r="P59" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q59">
         <v>2.62</v>
@@ -13443,7 +13452,7 @@
         <v>135</v>
       </c>
       <c r="P60" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q60">
         <v>2.88</v>
@@ -13855,7 +13864,7 @@
         <v>137</v>
       </c>
       <c r="P62" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q62">
         <v>3.6</v>
@@ -13933,10 +13942,10 @@
         <v>2</v>
       </c>
       <c r="AP62">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ62">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR62">
         <v>1.16</v>
@@ -14061,7 +14070,7 @@
         <v>138</v>
       </c>
       <c r="P63" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q63">
         <v>3.75</v>
@@ -14139,7 +14148,7 @@
         <v>3</v>
       </c>
       <c r="AP63">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ63">
         <v>1.3</v>
@@ -14345,10 +14354,10 @@
         <v>0</v>
       </c>
       <c r="AP64">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ64">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR64">
         <v>1.73</v>
@@ -15091,7 +15100,7 @@
         <v>143</v>
       </c>
       <c r="P68" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15297,7 +15306,7 @@
         <v>144</v>
       </c>
       <c r="P69" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15503,7 +15512,7 @@
         <v>145</v>
       </c>
       <c r="P70" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q70">
         <v>3.75</v>
@@ -15584,7 +15593,7 @@
         <v>1</v>
       </c>
       <c r="AQ70">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR70">
         <v>1.55</v>
@@ -15915,7 +15924,7 @@
         <v>147</v>
       </c>
       <c r="P72" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16121,7 +16130,7 @@
         <v>90</v>
       </c>
       <c r="P73" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q73">
         <v>4.33</v>
@@ -16327,7 +16336,7 @@
         <v>90</v>
       </c>
       <c r="P74" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q74">
         <v>2.4</v>
@@ -16405,7 +16414,7 @@
         <v>0.5</v>
       </c>
       <c r="AP74">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ74">
         <v>0.91</v>
@@ -16533,7 +16542,7 @@
         <v>148</v>
       </c>
       <c r="P75" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q75">
         <v>3.5</v>
@@ -16611,10 +16620,10 @@
         <v>0</v>
       </c>
       <c r="AP75">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ75">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR75">
         <v>1.25</v>
@@ -16739,7 +16748,7 @@
         <v>149</v>
       </c>
       <c r="P76" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q76">
         <v>2.88</v>
@@ -17357,7 +17366,7 @@
         <v>151</v>
       </c>
       <c r="P79" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17563,7 +17572,7 @@
         <v>152</v>
       </c>
       <c r="P80" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q80">
         <v>2.05</v>
@@ -17769,7 +17778,7 @@
         <v>90</v>
       </c>
       <c r="P81" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q81">
         <v>4.33</v>
@@ -17847,10 +17856,10 @@
         <v>2.25</v>
       </c>
       <c r="AP81">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ81">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR81">
         <v>1.22</v>
@@ -18593,7 +18602,7 @@
         <v>90</v>
       </c>
       <c r="P85" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q85">
         <v>3.1</v>
@@ -18799,7 +18808,7 @@
         <v>156</v>
       </c>
       <c r="P86" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -18880,7 +18889,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ86">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR86">
         <v>1.88</v>
@@ -19623,7 +19632,7 @@
         <v>90</v>
       </c>
       <c r="P90" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q90">
         <v>2.38</v>
@@ -19907,7 +19916,7 @@
         <v>1</v>
       </c>
       <c r="AP91">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ91">
         <v>0.91</v>
@@ -20035,7 +20044,7 @@
         <v>160</v>
       </c>
       <c r="P92" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20319,7 +20328,7 @@
         <v>1.5</v>
       </c>
       <c r="AP93">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ93">
         <v>1.3</v>
@@ -20653,7 +20662,7 @@
         <v>162</v>
       </c>
       <c r="P95" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q95">
         <v>1.9</v>
@@ -20859,7 +20868,7 @@
         <v>163</v>
       </c>
       <c r="P96" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q96">
         <v>2.75</v>
@@ -21146,7 +21155,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ97">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR97">
         <v>1.69</v>
@@ -21271,7 +21280,7 @@
         <v>90</v>
       </c>
       <c r="P98" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q98">
         <v>4.75</v>
@@ -21352,7 +21361,7 @@
         <v>0.36</v>
       </c>
       <c r="AQ98">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR98">
         <v>1.06</v>
@@ -21555,7 +21564,7 @@
         <v>0.2</v>
       </c>
       <c r="AP99">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ99">
         <v>0.64</v>
@@ -22173,7 +22182,7 @@
         <v>1.17</v>
       </c>
       <c r="AP102">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ102">
         <v>1.45</v>
@@ -22301,7 +22310,7 @@
         <v>166</v>
       </c>
       <c r="P103" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q103">
         <v>4.2</v>
@@ -22382,7 +22391,7 @@
         <v>1</v>
       </c>
       <c r="AQ103">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR103">
         <v>1.26</v>
@@ -22507,7 +22516,7 @@
         <v>167</v>
       </c>
       <c r="P104" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q104">
         <v>2.25</v>
@@ -23203,7 +23212,7 @@
         <v>0.6</v>
       </c>
       <c r="AP107">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ107">
         <v>0.7</v>
@@ -23331,7 +23340,7 @@
         <v>90</v>
       </c>
       <c r="P108" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q108">
         <v>4.5</v>
@@ -24155,7 +24164,7 @@
         <v>173</v>
       </c>
       <c r="P112" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q112">
         <v>3.5</v>
@@ -24567,7 +24576,7 @@
         <v>90</v>
       </c>
       <c r="P114" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q114">
         <v>2.85</v>
@@ -24645,7 +24654,7 @@
         <v>0.67</v>
       </c>
       <c r="AP114">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ114">
         <v>0.91</v>
@@ -24854,7 +24863,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ115">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR115">
         <v>1.51</v>
@@ -24979,7 +24988,7 @@
         <v>175</v>
       </c>
       <c r="P116" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q116">
         <v>2.4</v>
@@ -25266,7 +25275,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ117">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR117">
         <v>1.7</v>
@@ -25391,7 +25400,7 @@
         <v>90</v>
       </c>
       <c r="P118" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q118">
         <v>4</v>
@@ -25675,7 +25684,7 @@
         <v>0.5</v>
       </c>
       <c r="AP119">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ119">
         <v>0.7</v>
@@ -26009,7 +26018,7 @@
         <v>178</v>
       </c>
       <c r="P121" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q121">
         <v>2.88</v>
@@ -26293,7 +26302,7 @@
         <v>0.5</v>
       </c>
       <c r="AP122">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ122">
         <v>0.6</v>
@@ -26914,7 +26923,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ125">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR125">
         <v>1.66</v>
@@ -28353,7 +28362,7 @@
         <v>1</v>
       </c>
       <c r="AP132">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ132">
         <v>0.8</v>
@@ -28562,7 +28571,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ133">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR133">
         <v>1.34</v>
@@ -28687,7 +28696,7 @@
         <v>90</v>
       </c>
       <c r="P134" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q134">
         <v>3.2</v>
@@ -28893,7 +28902,7 @@
         <v>90</v>
       </c>
       <c r="P135" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q135">
         <v>5</v>
@@ -28974,7 +28983,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ135">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR135">
         <v>1.14</v>
@@ -29795,7 +29804,7 @@
         <v>1.33</v>
       </c>
       <c r="AP139">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ139">
         <v>1.4</v>
@@ -29923,7 +29932,7 @@
         <v>188</v>
       </c>
       <c r="P140" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q140">
         <v>2.95</v>
@@ -30129,7 +30138,7 @@
         <v>189</v>
       </c>
       <c r="P141" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q141">
         <v>2.8</v>
@@ -30416,7 +30425,7 @@
         <v>2.8</v>
       </c>
       <c r="AQ142">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR142">
         <v>1.78</v>
@@ -30619,7 +30628,7 @@
         <v>0.57</v>
       </c>
       <c r="AP143">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ143">
         <v>0.7</v>
@@ -30953,7 +30962,7 @@
         <v>192</v>
       </c>
       <c r="P145" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q145">
         <v>2.75</v>
@@ -31034,7 +31043,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ145">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR145">
         <v>1.62</v>
@@ -31159,7 +31168,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q146">
         <v>3.75</v>
@@ -31365,7 +31374,7 @@
         <v>129</v>
       </c>
       <c r="P147" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q147">
         <v>3.75</v>
@@ -31571,7 +31580,7 @@
         <v>90</v>
       </c>
       <c r="P148" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q148">
         <v>2.4</v>
@@ -31777,7 +31786,7 @@
         <v>90</v>
       </c>
       <c r="P149" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q149">
         <v>3.1</v>
@@ -32189,7 +32198,7 @@
         <v>194</v>
       </c>
       <c r="P151" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q151">
         <v>1.62</v>
@@ -32601,7 +32610,7 @@
         <v>95</v>
       </c>
       <c r="P153" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q153">
         <v>2.63</v>
@@ -32679,7 +32688,7 @@
         <v>1</v>
       </c>
       <c r="AP153">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ153">
         <v>1.2</v>
@@ -32888,7 +32897,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ154">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR154">
         <v>1.27</v>
@@ -33425,7 +33434,7 @@
         <v>197</v>
       </c>
       <c r="P157" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q157">
         <v>2.7</v>
@@ -33631,7 +33640,7 @@
         <v>96</v>
       </c>
       <c r="P158" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q158">
         <v>2.55</v>
@@ -33837,7 +33846,7 @@
         <v>198</v>
       </c>
       <c r="P159" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q159">
         <v>3.3</v>
@@ -34043,7 +34052,7 @@
         <v>90</v>
       </c>
       <c r="P160" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q160">
         <v>2.75</v>
@@ -34945,7 +34954,7 @@
         <v>1.11</v>
       </c>
       <c r="AP164">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ164">
         <v>0.91</v>
@@ -35485,7 +35494,7 @@
         <v>109</v>
       </c>
       <c r="P167" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q167">
         <v>3.35</v>
@@ -35563,7 +35572,7 @@
         <v>0.67</v>
       </c>
       <c r="AP167">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ167">
         <v>0.91</v>
@@ -35772,7 +35781,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ168">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR168">
         <v>1.22</v>
@@ -35897,7 +35906,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q169">
         <v>2.8</v>
@@ -36103,7 +36112,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q170">
         <v>3</v>
@@ -36184,7 +36193,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ170">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR170">
         <v>1.64</v>
@@ -36390,7 +36399,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ171">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR171">
         <v>1.68</v>
@@ -36515,7 +36524,7 @@
         <v>90</v>
       </c>
       <c r="P172" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q172">
         <v>2.63</v>
@@ -36593,7 +36602,7 @@
         <v>1.22</v>
       </c>
       <c r="AP172">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ172">
         <v>1.27</v>
@@ -36721,7 +36730,7 @@
         <v>207</v>
       </c>
       <c r="P173" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q173">
         <v>2.3</v>
@@ -37751,7 +37760,7 @@
         <v>90</v>
       </c>
       <c r="P178" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q178">
         <v>3.25</v>
@@ -38163,7 +38172,7 @@
         <v>212</v>
       </c>
       <c r="P180" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q180">
         <v>2.2</v>
@@ -38369,7 +38378,7 @@
         <v>90</v>
       </c>
       <c r="P181" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q181">
         <v>3.25</v>
@@ -39193,7 +39202,7 @@
         <v>214</v>
       </c>
       <c r="P185" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q185">
         <v>2.6</v>
@@ -39605,7 +39614,7 @@
         <v>90</v>
       </c>
       <c r="P187" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q187">
         <v>2.55</v>
@@ -39762,6 +39771,624 @@
       </c>
       <c r="BP187">
         <v>1.19</v>
+      </c>
+    </row>
+    <row r="188" spans="1:68">
+      <c r="A188" s="1">
+        <v>187</v>
+      </c>
+      <c r="B188">
+        <v>7469050</v>
+      </c>
+      <c r="C188" t="s">
+        <v>68</v>
+      </c>
+      <c r="D188" t="s">
+        <v>69</v>
+      </c>
+      <c r="E188" s="2">
+        <v>45689.41666666666</v>
+      </c>
+      <c r="F188">
+        <v>21</v>
+      </c>
+      <c r="G188" t="s">
+        <v>87</v>
+      </c>
+      <c r="H188" t="s">
+        <v>86</v>
+      </c>
+      <c r="I188">
+        <v>0</v>
+      </c>
+      <c r="J188">
+        <v>1</v>
+      </c>
+      <c r="K188">
+        <v>1</v>
+      </c>
+      <c r="L188">
+        <v>1</v>
+      </c>
+      <c r="M188">
+        <v>2</v>
+      </c>
+      <c r="N188">
+        <v>3</v>
+      </c>
+      <c r="O188" t="s">
+        <v>215</v>
+      </c>
+      <c r="P188" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q188">
+        <v>4.5</v>
+      </c>
+      <c r="R188">
+        <v>2.25</v>
+      </c>
+      <c r="S188">
+        <v>2.2</v>
+      </c>
+      <c r="T188">
+        <v>1.33</v>
+      </c>
+      <c r="U188">
+        <v>3</v>
+      </c>
+      <c r="V188">
+        <v>2.45</v>
+      </c>
+      <c r="W188">
+        <v>1.48</v>
+      </c>
+      <c r="X188">
+        <v>6.1</v>
+      </c>
+      <c r="Y188">
+        <v>1.09</v>
+      </c>
+      <c r="Z188">
+        <v>4.8</v>
+      </c>
+      <c r="AA188">
+        <v>3.55</v>
+      </c>
+      <c r="AB188">
+        <v>1.73</v>
+      </c>
+      <c r="AC188">
+        <v>1.05</v>
+      </c>
+      <c r="AD188">
+        <v>9.5</v>
+      </c>
+      <c r="AE188">
+        <v>1.25</v>
+      </c>
+      <c r="AF188">
+        <v>3.75</v>
+      </c>
+      <c r="AG188">
+        <v>1.7</v>
+      </c>
+      <c r="AH188">
+        <v>1.95</v>
+      </c>
+      <c r="AI188">
+        <v>1.67</v>
+      </c>
+      <c r="AJ188">
+        <v>2.05</v>
+      </c>
+      <c r="AK188">
+        <v>2.05</v>
+      </c>
+      <c r="AL188">
+        <v>1.22</v>
+      </c>
+      <c r="AM188">
+        <v>1.2</v>
+      </c>
+      <c r="AN188">
+        <v>1.22</v>
+      </c>
+      <c r="AO188">
+        <v>1.2</v>
+      </c>
+      <c r="AP188">
+        <v>1.1</v>
+      </c>
+      <c r="AQ188">
+        <v>1.36</v>
+      </c>
+      <c r="AR188">
+        <v>1.26</v>
+      </c>
+      <c r="AS188">
+        <v>1.49</v>
+      </c>
+      <c r="AT188">
+        <v>2.75</v>
+      </c>
+      <c r="AU188">
+        <v>2</v>
+      </c>
+      <c r="AV188">
+        <v>6</v>
+      </c>
+      <c r="AW188">
+        <v>4</v>
+      </c>
+      <c r="AX188">
+        <v>10</v>
+      </c>
+      <c r="AY188">
+        <v>6</v>
+      </c>
+      <c r="AZ188">
+        <v>16</v>
+      </c>
+      <c r="BA188">
+        <v>2</v>
+      </c>
+      <c r="BB188">
+        <v>3</v>
+      </c>
+      <c r="BC188">
+        <v>5</v>
+      </c>
+      <c r="BD188">
+        <v>2.7</v>
+      </c>
+      <c r="BE188">
+        <v>7</v>
+      </c>
+      <c r="BF188">
+        <v>1.53</v>
+      </c>
+      <c r="BG188">
+        <v>1.29</v>
+      </c>
+      <c r="BH188">
+        <v>3.2</v>
+      </c>
+      <c r="BI188">
+        <v>1.49</v>
+      </c>
+      <c r="BJ188">
+        <v>2.4</v>
+      </c>
+      <c r="BK188">
+        <v>1.82</v>
+      </c>
+      <c r="BL188">
+        <v>1.86</v>
+      </c>
+      <c r="BM188">
+        <v>2.3</v>
+      </c>
+      <c r="BN188">
+        <v>1.54</v>
+      </c>
+      <c r="BO188">
+        <v>2.9</v>
+      </c>
+      <c r="BP188">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="189" spans="1:68">
+      <c r="A189" s="1">
+        <v>188</v>
+      </c>
+      <c r="B189">
+        <v>7469052</v>
+      </c>
+      <c r="C189" t="s">
+        <v>68</v>
+      </c>
+      <c r="D189" t="s">
+        <v>69</v>
+      </c>
+      <c r="E189" s="2">
+        <v>45689.41666666666</v>
+      </c>
+      <c r="F189">
+        <v>21</v>
+      </c>
+      <c r="G189" t="s">
+        <v>79</v>
+      </c>
+      <c r="H189" t="s">
+        <v>76</v>
+      </c>
+      <c r="I189">
+        <v>0</v>
+      </c>
+      <c r="J189">
+        <v>0</v>
+      </c>
+      <c r="K189">
+        <v>0</v>
+      </c>
+      <c r="L189">
+        <v>3</v>
+      </c>
+      <c r="M189">
+        <v>0</v>
+      </c>
+      <c r="N189">
+        <v>3</v>
+      </c>
+      <c r="O189" t="s">
+        <v>216</v>
+      </c>
+      <c r="P189" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q189">
+        <v>2.6</v>
+      </c>
+      <c r="R189">
+        <v>2.1</v>
+      </c>
+      <c r="S189">
+        <v>3.85</v>
+      </c>
+      <c r="T189">
+        <v>1.38</v>
+      </c>
+      <c r="U189">
+        <v>2.8</v>
+      </c>
+      <c r="V189">
+        <v>2.7</v>
+      </c>
+      <c r="W189">
+        <v>1.4</v>
+      </c>
+      <c r="X189">
+        <v>6.7</v>
+      </c>
+      <c r="Y189">
+        <v>1.07</v>
+      </c>
+      <c r="Z189">
+        <v>1.91</v>
+      </c>
+      <c r="AA189">
+        <v>3.47</v>
+      </c>
+      <c r="AB189">
+        <v>3.88</v>
+      </c>
+      <c r="AC189">
+        <v>1.05</v>
+      </c>
+      <c r="AD189">
+        <v>9</v>
+      </c>
+      <c r="AE189">
+        <v>1.3</v>
+      </c>
+      <c r="AF189">
+        <v>3.4</v>
+      </c>
+      <c r="AG189">
+        <v>1.84</v>
+      </c>
+      <c r="AH189">
+        <v>1.86</v>
+      </c>
+      <c r="AI189">
+        <v>1.73</v>
+      </c>
+      <c r="AJ189">
+        <v>1.95</v>
+      </c>
+      <c r="AK189">
+        <v>1.28</v>
+      </c>
+      <c r="AL189">
+        <v>1.25</v>
+      </c>
+      <c r="AM189">
+        <v>1.77</v>
+      </c>
+      <c r="AN189">
+        <v>1.22</v>
+      </c>
+      <c r="AO189">
+        <v>0.44</v>
+      </c>
+      <c r="AP189">
+        <v>1.4</v>
+      </c>
+      <c r="AQ189">
+        <v>0.4</v>
+      </c>
+      <c r="AR189">
+        <v>1.73</v>
+      </c>
+      <c r="AS189">
+        <v>1.27</v>
+      </c>
+      <c r="AT189">
+        <v>3</v>
+      </c>
+      <c r="AU189">
+        <v>7</v>
+      </c>
+      <c r="AV189">
+        <v>6</v>
+      </c>
+      <c r="AW189">
+        <v>9</v>
+      </c>
+      <c r="AX189">
+        <v>5</v>
+      </c>
+      <c r="AY189">
+        <v>16</v>
+      </c>
+      <c r="AZ189">
+        <v>11</v>
+      </c>
+      <c r="BA189">
+        <v>3</v>
+      </c>
+      <c r="BB189">
+        <v>3</v>
+      </c>
+      <c r="BC189">
+        <v>6</v>
+      </c>
+      <c r="BD189">
+        <v>1.77</v>
+      </c>
+      <c r="BE189">
+        <v>6.4</v>
+      </c>
+      <c r="BF189">
+        <v>2.25</v>
+      </c>
+      <c r="BG189">
+        <v>1.4</v>
+      </c>
+      <c r="BH189">
+        <v>2.7</v>
+      </c>
+      <c r="BI189">
+        <v>1.67</v>
+      </c>
+      <c r="BJ189">
+        <v>2.07</v>
+      </c>
+      <c r="BK189">
+        <v>2.05</v>
+      </c>
+      <c r="BL189">
+        <v>1.68</v>
+      </c>
+      <c r="BM189">
+        <v>2.65</v>
+      </c>
+      <c r="BN189">
+        <v>1.42</v>
+      </c>
+      <c r="BO189">
+        <v>3.45</v>
+      </c>
+      <c r="BP189">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="190" spans="1:68">
+      <c r="A190" s="1">
+        <v>189</v>
+      </c>
+      <c r="B190">
+        <v>7469046</v>
+      </c>
+      <c r="C190" t="s">
+        <v>68</v>
+      </c>
+      <c r="D190" t="s">
+        <v>69</v>
+      </c>
+      <c r="E190" s="2">
+        <v>45689.66666666666</v>
+      </c>
+      <c r="F190">
+        <v>21</v>
+      </c>
+      <c r="G190" t="s">
+        <v>75</v>
+      </c>
+      <c r="H190" t="s">
+        <v>85</v>
+      </c>
+      <c r="I190">
+        <v>0</v>
+      </c>
+      <c r="J190">
+        <v>1</v>
+      </c>
+      <c r="K190">
+        <v>1</v>
+      </c>
+      <c r="L190">
+        <v>0</v>
+      </c>
+      <c r="M190">
+        <v>1</v>
+      </c>
+      <c r="N190">
+        <v>1</v>
+      </c>
+      <c r="O190" t="s">
+        <v>90</v>
+      </c>
+      <c r="P190" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q190">
+        <v>3.3</v>
+      </c>
+      <c r="R190">
+        <v>2</v>
+      </c>
+      <c r="S190">
+        <v>3.2</v>
+      </c>
+      <c r="T190">
+        <v>1.42</v>
+      </c>
+      <c r="U190">
+        <v>2.65</v>
+      </c>
+      <c r="V190">
+        <v>2.9</v>
+      </c>
+      <c r="W190">
+        <v>1.36</v>
+      </c>
+      <c r="X190">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Y190">
+        <v>1.03</v>
+      </c>
+      <c r="Z190">
+        <v>2.67</v>
+      </c>
+      <c r="AA190">
+        <v>3.11</v>
+      </c>
+      <c r="AB190">
+        <v>2.67</v>
+      </c>
+      <c r="AC190">
+        <v>1.07</v>
+      </c>
+      <c r="AD190">
+        <v>8</v>
+      </c>
+      <c r="AE190">
+        <v>1.35</v>
+      </c>
+      <c r="AF190">
+        <v>3.1</v>
+      </c>
+      <c r="AG190">
+        <v>1.95</v>
+      </c>
+      <c r="AH190">
+        <v>1.7</v>
+      </c>
+      <c r="AI190">
+        <v>1.77</v>
+      </c>
+      <c r="AJ190">
+        <v>1.91</v>
+      </c>
+      <c r="AK190">
+        <v>1.48</v>
+      </c>
+      <c r="AL190">
+        <v>1.28</v>
+      </c>
+      <c r="AM190">
+        <v>1.44</v>
+      </c>
+      <c r="AN190">
+        <v>2</v>
+      </c>
+      <c r="AO190">
+        <v>1.7</v>
+      </c>
+      <c r="AP190">
+        <v>1.82</v>
+      </c>
+      <c r="AQ190">
+        <v>1.82</v>
+      </c>
+      <c r="AR190">
+        <v>1.63</v>
+      </c>
+      <c r="AS190">
+        <v>1.43</v>
+      </c>
+      <c r="AT190">
+        <v>3.06</v>
+      </c>
+      <c r="AU190">
+        <v>3</v>
+      </c>
+      <c r="AV190">
+        <v>3</v>
+      </c>
+      <c r="AW190">
+        <v>4</v>
+      </c>
+      <c r="AX190">
+        <v>9</v>
+      </c>
+      <c r="AY190">
+        <v>7</v>
+      </c>
+      <c r="AZ190">
+        <v>12</v>
+      </c>
+      <c r="BA190">
+        <v>4</v>
+      </c>
+      <c r="BB190">
+        <v>3</v>
+      </c>
+      <c r="BC190">
+        <v>7</v>
+      </c>
+      <c r="BD190">
+        <v>2.05</v>
+      </c>
+      <c r="BE190">
+        <v>6.4</v>
+      </c>
+      <c r="BF190">
+        <v>1.97</v>
+      </c>
+      <c r="BG190">
+        <v>1.36</v>
+      </c>
+      <c r="BH190">
+        <v>2.8</v>
+      </c>
+      <c r="BI190">
+        <v>1.63</v>
+      </c>
+      <c r="BJ190">
+        <v>2.12</v>
+      </c>
+      <c r="BK190">
+        <v>1.98</v>
+      </c>
+      <c r="BL190">
+        <v>1.72</v>
+      </c>
+      <c r="BM190">
+        <v>2.55</v>
+      </c>
+      <c r="BN190">
+        <v>1.45</v>
+      </c>
+      <c r="BO190">
+        <v>3.3</v>
+      </c>
+      <c r="BP190">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1202" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="295">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -667,6 +667,9 @@
     <t>['48', '51', '70']</t>
   </si>
   <si>
+    <t>['28', '49', '75']</t>
+  </si>
+  <si>
     <t>['16', '45+2']</t>
   </si>
   <si>
@@ -887,6 +890,15 @@
   </si>
   <si>
     <t>['24', '57']</t>
+  </si>
+  <si>
+    <t>['86']</t>
+  </si>
+  <si>
+    <t>['15', '88']</t>
+  </si>
+  <si>
+    <t>['12', '27']</t>
   </si>
 </sst>
 </file>
@@ -1248,7 +1260,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP190"/>
+  <dimension ref="A1:BP195"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1504,7 +1516,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q2">
         <v>2.4</v>
@@ -1585,7 +1597,7 @@
         <v>1</v>
       </c>
       <c r="AQ2">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1916,7 +1928,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q4">
         <v>3.6</v>
@@ -1997,7 +2009,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ4">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2406,7 +2418,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ6">
         <v>1.45</v>
@@ -2615,7 +2627,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ7">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2740,7 +2752,7 @@
         <v>90</v>
       </c>
       <c r="P8" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q8">
         <v>3.1</v>
@@ -3024,7 +3036,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AQ9">
         <v>1.36</v>
@@ -3152,7 +3164,7 @@
         <v>94</v>
       </c>
       <c r="P10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q10">
         <v>2.6</v>
@@ -3233,7 +3245,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ10">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3642,7 +3654,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ12">
         <v>1.5</v>
@@ -3770,7 +3782,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q13">
         <v>3.1</v>
@@ -3848,7 +3860,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ13">
         <v>1.3</v>
@@ -4388,7 +4400,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q16">
         <v>2.63</v>
@@ -4594,7 +4606,7 @@
         <v>99</v>
       </c>
       <c r="P17" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -4672,7 +4684,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ17">
         <v>1.2</v>
@@ -5293,7 +5305,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ20">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR20">
         <v>0.67</v>
@@ -5624,7 +5636,7 @@
         <v>103</v>
       </c>
       <c r="P22" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -6036,7 +6048,7 @@
         <v>105</v>
       </c>
       <c r="P24" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q24">
         <v>2.62</v>
@@ -6117,7 +6129,7 @@
         <v>1</v>
       </c>
       <c r="AQ24">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR24">
         <v>1.39</v>
@@ -6320,10 +6332,10 @@
         <v>1</v>
       </c>
       <c r="AP25">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AQ25">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR25">
         <v>0.67</v>
@@ -6448,7 +6460,7 @@
         <v>106</v>
       </c>
       <c r="P26" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q26">
         <v>2.83</v>
@@ -6526,10 +6538,10 @@
         <v>1</v>
       </c>
       <c r="AP26">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ26">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR26">
         <v>1.19</v>
@@ -6860,7 +6872,7 @@
         <v>108</v>
       </c>
       <c r="P28" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q28">
         <v>2.6</v>
@@ -7144,7 +7156,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ29">
         <v>0.64</v>
@@ -8177,7 +8189,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ34">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR34">
         <v>1.55</v>
@@ -8302,7 +8314,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q35">
         <v>3.3</v>
@@ -8380,7 +8392,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ35">
         <v>1.5</v>
@@ -8508,7 +8520,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q36">
         <v>3.1</v>
@@ -8586,7 +8598,7 @@
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ36">
         <v>1.3</v>
@@ -8714,7 +8726,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q37">
         <v>3.4</v>
@@ -8792,7 +8804,7 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ37">
         <v>0.4</v>
@@ -8920,7 +8932,7 @@
         <v>90</v>
       </c>
       <c r="P38" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q38">
         <v>3.2</v>
@@ -9126,7 +9138,7 @@
         <v>90</v>
       </c>
       <c r="P39" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q39">
         <v>3.4</v>
@@ -9204,7 +9216,7 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AQ39">
         <v>0.7</v>
@@ -9538,7 +9550,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q41">
         <v>2.5</v>
@@ -9619,7 +9631,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ41">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR41">
         <v>1.73</v>
@@ -9744,7 +9756,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q42">
         <v>3.25</v>
@@ -9825,7 +9837,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ42">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR42">
         <v>1.75</v>
@@ -9950,7 +9962,7 @@
         <v>90</v>
       </c>
       <c r="P43" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q43">
         <v>2.75</v>
@@ -11061,7 +11073,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ48">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR48">
         <v>1.82</v>
@@ -11470,7 +11482,7 @@
         <v>3</v>
       </c>
       <c r="AP50">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ50">
         <v>1.5</v>
@@ -12010,7 +12022,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -12091,7 +12103,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ53">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR53">
         <v>1.76</v>
@@ -12216,7 +12228,7 @@
         <v>129</v>
       </c>
       <c r="P54" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q54">
         <v>2.55</v>
@@ -12422,7 +12434,7 @@
         <v>130</v>
       </c>
       <c r="P55" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q55">
         <v>2.55</v>
@@ -12500,7 +12512,7 @@
         <v>1.33</v>
       </c>
       <c r="AP55">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ55">
         <v>1.45</v>
@@ -12834,7 +12846,7 @@
         <v>132</v>
       </c>
       <c r="P57" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -12912,10 +12924,10 @@
         <v>0.67</v>
       </c>
       <c r="AP57">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ57">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR57">
         <v>1.54</v>
@@ -13040,7 +13052,7 @@
         <v>133</v>
       </c>
       <c r="P58" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -13118,7 +13130,7 @@
         <v>1.5</v>
       </c>
       <c r="AP58">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AQ58">
         <v>1.2</v>
@@ -13246,7 +13258,7 @@
         <v>134</v>
       </c>
       <c r="P59" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q59">
         <v>2.62</v>
@@ -13327,7 +13339,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ59">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR59">
         <v>1.53</v>
@@ -13452,7 +13464,7 @@
         <v>135</v>
       </c>
       <c r="P60" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q60">
         <v>2.88</v>
@@ -13736,7 +13748,7 @@
         <v>1.5</v>
       </c>
       <c r="AP61">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ61">
         <v>1.3</v>
@@ -13864,7 +13876,7 @@
         <v>137</v>
       </c>
       <c r="P62" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q62">
         <v>3.6</v>
@@ -14070,7 +14082,7 @@
         <v>138</v>
       </c>
       <c r="P63" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q63">
         <v>3.75</v>
@@ -14560,7 +14572,7 @@
         <v>1.75</v>
       </c>
       <c r="AP65">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ65">
         <v>1.45</v>
@@ -14975,7 +14987,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ67">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR67">
         <v>1.61</v>
@@ -15100,7 +15112,7 @@
         <v>143</v>
       </c>
       <c r="P68" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15178,7 +15190,7 @@
         <v>1</v>
       </c>
       <c r="AP68">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ68">
         <v>0.7</v>
@@ -15306,7 +15318,7 @@
         <v>144</v>
       </c>
       <c r="P69" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15512,7 +15524,7 @@
         <v>145</v>
       </c>
       <c r="P70" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q70">
         <v>3.75</v>
@@ -15924,7 +15936,7 @@
         <v>147</v>
       </c>
       <c r="P72" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16130,7 +16142,7 @@
         <v>90</v>
       </c>
       <c r="P73" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q73">
         <v>4.33</v>
@@ -16208,7 +16220,7 @@
         <v>0.75</v>
       </c>
       <c r="AP73">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AQ73">
         <v>0.91</v>
@@ -16336,7 +16348,7 @@
         <v>90</v>
       </c>
       <c r="P74" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q74">
         <v>2.4</v>
@@ -16417,7 +16429,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ74">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR74">
         <v>1.85</v>
@@ -16542,7 +16554,7 @@
         <v>148</v>
       </c>
       <c r="P75" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q75">
         <v>3.5</v>
@@ -16748,7 +16760,7 @@
         <v>149</v>
       </c>
       <c r="P76" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q76">
         <v>2.88</v>
@@ -16826,7 +16838,7 @@
         <v>1.33</v>
       </c>
       <c r="AP76">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ76">
         <v>1.2</v>
@@ -17032,7 +17044,7 @@
         <v>2</v>
       </c>
       <c r="AP77">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ77">
         <v>1.3</v>
@@ -17366,7 +17378,7 @@
         <v>151</v>
       </c>
       <c r="P79" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17572,7 +17584,7 @@
         <v>152</v>
       </c>
       <c r="P80" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q80">
         <v>2.05</v>
@@ -17653,7 +17665,7 @@
         <v>2.8</v>
       </c>
       <c r="AQ80">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR80">
         <v>2.09</v>
@@ -17778,7 +17790,7 @@
         <v>90</v>
       </c>
       <c r="P81" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q81">
         <v>4.33</v>
@@ -18065,7 +18077,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ82">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR82">
         <v>1.57</v>
@@ -18602,7 +18614,7 @@
         <v>90</v>
       </c>
       <c r="P85" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q85">
         <v>3.1</v>
@@ -18808,7 +18820,7 @@
         <v>156</v>
       </c>
       <c r="P86" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -18886,7 +18898,7 @@
         <v>1.4</v>
       </c>
       <c r="AP86">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ86">
         <v>1.36</v>
@@ -19504,7 +19516,7 @@
         <v>0.75</v>
       </c>
       <c r="AP89">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ89">
         <v>0.7</v>
@@ -19632,7 +19644,7 @@
         <v>90</v>
       </c>
       <c r="P90" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q90">
         <v>2.38</v>
@@ -19713,7 +19725,7 @@
         <v>1</v>
       </c>
       <c r="AQ90">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR90">
         <v>1.42</v>
@@ -19919,7 +19931,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ91">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR91">
         <v>1.25</v>
@@ -20044,7 +20056,7 @@
         <v>160</v>
       </c>
       <c r="P92" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20122,7 +20134,7 @@
         <v>1</v>
       </c>
       <c r="AP92">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ92">
         <v>1.3</v>
@@ -20534,10 +20546,10 @@
         <v>1.2</v>
       </c>
       <c r="AP94">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ94">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR94">
         <v>1.21</v>
@@ -20662,7 +20674,7 @@
         <v>162</v>
       </c>
       <c r="P95" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q95">
         <v>1.9</v>
@@ -20868,7 +20880,7 @@
         <v>163</v>
       </c>
       <c r="P96" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q96">
         <v>2.75</v>
@@ -21280,7 +21292,7 @@
         <v>90</v>
       </c>
       <c r="P98" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q98">
         <v>4.75</v>
@@ -21358,7 +21370,7 @@
         <v>0.25</v>
       </c>
       <c r="AP98">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AQ98">
         <v>0.4</v>
@@ -21976,7 +21988,7 @@
         <v>0.67</v>
       </c>
       <c r="AP101">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AQ101">
         <v>1</v>
@@ -22310,7 +22322,7 @@
         <v>166</v>
       </c>
       <c r="P103" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q103">
         <v>4.2</v>
@@ -22516,7 +22528,7 @@
         <v>167</v>
       </c>
       <c r="P104" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q104">
         <v>2.25</v>
@@ -22594,7 +22606,7 @@
         <v>1.17</v>
       </c>
       <c r="AP104">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ104">
         <v>0.91</v>
@@ -22803,7 +22815,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ105">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR105">
         <v>1.41</v>
@@ -23009,7 +23021,7 @@
         <v>1</v>
       </c>
       <c r="AQ106">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR106">
         <v>1.41</v>
@@ -23340,7 +23352,7 @@
         <v>90</v>
       </c>
       <c r="P108" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q108">
         <v>4.5</v>
@@ -23830,10 +23842,10 @@
         <v>1.17</v>
       </c>
       <c r="AP110">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ110">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR110">
         <v>1.85</v>
@@ -24036,7 +24048,7 @@
         <v>0.8</v>
       </c>
       <c r="AP111">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ111">
         <v>1.2</v>
@@ -24164,7 +24176,7 @@
         <v>173</v>
       </c>
       <c r="P112" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q112">
         <v>3.5</v>
@@ -24242,10 +24254,10 @@
         <v>1</v>
       </c>
       <c r="AP112">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ112">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR112">
         <v>1.26</v>
@@ -24576,7 +24588,7 @@
         <v>90</v>
       </c>
       <c r="P114" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q114">
         <v>2.85</v>
@@ -24657,7 +24669,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ114">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR114">
         <v>1.28</v>
@@ -24988,7 +25000,7 @@
         <v>175</v>
       </c>
       <c r="P116" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q116">
         <v>2.4</v>
@@ -25400,7 +25412,7 @@
         <v>90</v>
       </c>
       <c r="P118" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q118">
         <v>4</v>
@@ -25478,7 +25490,7 @@
         <v>1.14</v>
       </c>
       <c r="AP118">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AQ118">
         <v>1.45</v>
@@ -26018,7 +26030,7 @@
         <v>178</v>
       </c>
       <c r="P121" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q121">
         <v>2.88</v>
@@ -26714,10 +26726,10 @@
         <v>1</v>
       </c>
       <c r="AP124">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ124">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR124">
         <v>1.79</v>
@@ -27335,7 +27347,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ127">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR127">
         <v>1.21</v>
@@ -27541,7 +27553,7 @@
         <v>2.8</v>
       </c>
       <c r="AQ128">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR128">
         <v>1.83</v>
@@ -27744,7 +27756,7 @@
         <v>1</v>
       </c>
       <c r="AP129">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AQ129">
         <v>1.5</v>
@@ -27950,10 +27962,10 @@
         <v>0.71</v>
       </c>
       <c r="AP130">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ130">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR130">
         <v>1.89</v>
@@ -28365,7 +28377,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ132">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR132">
         <v>1.26</v>
@@ -28568,7 +28580,7 @@
         <v>0.67</v>
       </c>
       <c r="AP133">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ133">
         <v>0.4</v>
@@ -28696,7 +28708,7 @@
         <v>90</v>
       </c>
       <c r="P134" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q134">
         <v>3.2</v>
@@ -28774,7 +28786,7 @@
         <v>0.43</v>
       </c>
       <c r="AP134">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ134">
         <v>0.6</v>
@@ -28902,7 +28914,7 @@
         <v>90</v>
       </c>
       <c r="P135" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q135">
         <v>5</v>
@@ -29932,7 +29944,7 @@
         <v>188</v>
       </c>
       <c r="P140" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q140">
         <v>2.95</v>
@@ -30138,7 +30150,7 @@
         <v>189</v>
       </c>
       <c r="P141" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q141">
         <v>2.8</v>
@@ -30962,7 +30974,7 @@
         <v>192</v>
       </c>
       <c r="P145" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q145">
         <v>2.75</v>
@@ -31168,7 +31180,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q146">
         <v>3.75</v>
@@ -31246,10 +31258,10 @@
         <v>1</v>
       </c>
       <c r="AP146">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ146">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR146">
         <v>1.08</v>
@@ -31374,7 +31386,7 @@
         <v>129</v>
       </c>
       <c r="P147" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q147">
         <v>3.75</v>
@@ -31455,7 +31467,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ147">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR147">
         <v>1.16</v>
@@ -31580,7 +31592,7 @@
         <v>90</v>
       </c>
       <c r="P148" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q148">
         <v>2.4</v>
@@ -31658,7 +31670,7 @@
         <v>0.88</v>
       </c>
       <c r="AP148">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ148">
         <v>1</v>
@@ -31786,7 +31798,7 @@
         <v>90</v>
       </c>
       <c r="P149" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q149">
         <v>3.1</v>
@@ -31867,7 +31879,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ149">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR149">
         <v>1.68</v>
@@ -32198,7 +32210,7 @@
         <v>194</v>
       </c>
       <c r="P151" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q151">
         <v>1.62</v>
@@ -32276,7 +32288,7 @@
         <v>1.14</v>
       </c>
       <c r="AP151">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ151">
         <v>1.4</v>
@@ -32485,7 +32497,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ152">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR152">
         <v>1.6</v>
@@ -32610,7 +32622,7 @@
         <v>95</v>
       </c>
       <c r="P153" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q153">
         <v>2.63</v>
@@ -32894,7 +32906,7 @@
         <v>1.13</v>
       </c>
       <c r="AP154">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ154">
         <v>1.36</v>
@@ -33100,7 +33112,7 @@
         <v>1.25</v>
       </c>
       <c r="AP155">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AQ155">
         <v>1.3</v>
@@ -33434,7 +33446,7 @@
         <v>197</v>
       </c>
       <c r="P157" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q157">
         <v>2.7</v>
@@ -33512,10 +33524,10 @@
         <v>1.11</v>
       </c>
       <c r="AP157">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ157">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR157">
         <v>1.86</v>
@@ -33640,7 +33652,7 @@
         <v>96</v>
       </c>
       <c r="P158" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q158">
         <v>2.55</v>
@@ -33718,7 +33730,7 @@
         <v>1.11</v>
       </c>
       <c r="AP158">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ158">
         <v>1</v>
@@ -33846,7 +33858,7 @@
         <v>198</v>
       </c>
       <c r="P159" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q159">
         <v>3.3</v>
@@ -34052,7 +34064,7 @@
         <v>90</v>
       </c>
       <c r="P160" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q160">
         <v>2.75</v>
@@ -34336,7 +34348,7 @@
         <v>0.75</v>
       </c>
       <c r="AP161">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ161">
         <v>0.6</v>
@@ -35160,7 +35172,7 @@
         <v>1.38</v>
       </c>
       <c r="AP165">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ165">
         <v>1.4</v>
@@ -35369,7 +35381,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ166">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR166">
         <v>1.68</v>
@@ -35494,7 +35506,7 @@
         <v>109</v>
       </c>
       <c r="P167" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q167">
         <v>3.35</v>
@@ -35575,7 +35587,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ167">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR167">
         <v>1.14</v>
@@ -35906,7 +35918,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q169">
         <v>2.8</v>
@@ -36112,7 +36124,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q170">
         <v>3</v>
@@ -36524,7 +36536,7 @@
         <v>90</v>
       </c>
       <c r="P172" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q172">
         <v>2.63</v>
@@ -36605,7 +36617,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ172">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR172">
         <v>1.73</v>
@@ -36730,7 +36742,7 @@
         <v>207</v>
       </c>
       <c r="P173" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q173">
         <v>2.3</v>
@@ -36808,7 +36820,7 @@
         <v>0.11</v>
       </c>
       <c r="AP173">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ173">
         <v>0.64</v>
@@ -37017,7 +37029,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ174">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR174">
         <v>1.67</v>
@@ -37220,7 +37232,7 @@
         <v>0.67</v>
       </c>
       <c r="AP175">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AQ175">
         <v>0.6</v>
@@ -37426,10 +37438,10 @@
         <v>1</v>
       </c>
       <c r="AP176">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ176">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR176">
         <v>1.28</v>
@@ -37760,7 +37772,7 @@
         <v>90</v>
       </c>
       <c r="P178" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q178">
         <v>3.25</v>
@@ -38044,7 +38056,7 @@
         <v>1.1</v>
       </c>
       <c r="AP179">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ179">
         <v>1</v>
@@ -38172,7 +38184,7 @@
         <v>212</v>
       </c>
       <c r="P180" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q180">
         <v>2.2</v>
@@ -38378,7 +38390,7 @@
         <v>90</v>
       </c>
       <c r="P181" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q181">
         <v>3.25</v>
@@ -38868,7 +38880,7 @@
         <v>1</v>
       </c>
       <c r="AP183">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ183">
         <v>0.91</v>
@@ -39077,7 +39089,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ184">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR184">
         <v>1.62</v>
@@ -39202,7 +39214,7 @@
         <v>214</v>
       </c>
       <c r="P185" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q185">
         <v>2.6</v>
@@ -39614,7 +39626,7 @@
         <v>90</v>
       </c>
       <c r="P187" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q187">
         <v>2.55</v>
@@ -39820,7 +39832,7 @@
         <v>215</v>
       </c>
       <c r="P188" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q188">
         <v>4.5</v>
@@ -40232,7 +40244,7 @@
         <v>90</v>
       </c>
       <c r="P190" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q190">
         <v>3.3</v>
@@ -40389,6 +40401,1036 @@
       </c>
       <c r="BP190">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="191" spans="1:68">
+      <c r="A191" s="1">
+        <v>190</v>
+      </c>
+      <c r="B191">
+        <v>7469063</v>
+      </c>
+      <c r="C191" t="s">
+        <v>68</v>
+      </c>
+      <c r="D191" t="s">
+        <v>69</v>
+      </c>
+      <c r="E191" s="2">
+        <v>45695.66666666666</v>
+      </c>
+      <c r="F191">
+        <v>22</v>
+      </c>
+      <c r="G191" t="s">
+        <v>80</v>
+      </c>
+      <c r="H191" t="s">
+        <v>84</v>
+      </c>
+      <c r="I191">
+        <v>0</v>
+      </c>
+      <c r="J191">
+        <v>0</v>
+      </c>
+      <c r="K191">
+        <v>0</v>
+      </c>
+      <c r="L191">
+        <v>0</v>
+      </c>
+      <c r="M191">
+        <v>1</v>
+      </c>
+      <c r="N191">
+        <v>1</v>
+      </c>
+      <c r="O191" t="s">
+        <v>90</v>
+      </c>
+      <c r="P191" t="s">
+        <v>292</v>
+      </c>
+      <c r="Q191">
+        <v>2.75</v>
+      </c>
+      <c r="R191">
+        <v>2</v>
+      </c>
+      <c r="S191">
+        <v>3.95</v>
+      </c>
+      <c r="T191">
+        <v>1.45</v>
+      </c>
+      <c r="U191">
+        <v>2.55</v>
+      </c>
+      <c r="V191">
+        <v>3.1</v>
+      </c>
+      <c r="W191">
+        <v>1.33</v>
+      </c>
+      <c r="X191">
+        <v>8.5</v>
+      </c>
+      <c r="Y191">
+        <v>1.04</v>
+      </c>
+      <c r="Z191">
+        <v>2.19</v>
+      </c>
+      <c r="AA191">
+        <v>3.23</v>
+      </c>
+      <c r="AB191">
+        <v>3.28</v>
+      </c>
+      <c r="AC191">
+        <v>1.07</v>
+      </c>
+      <c r="AD191">
+        <v>8</v>
+      </c>
+      <c r="AE191">
+        <v>1.38</v>
+      </c>
+      <c r="AF191">
+        <v>2.95</v>
+      </c>
+      <c r="AG191">
+        <v>2.1</v>
+      </c>
+      <c r="AH191">
+        <v>1.61</v>
+      </c>
+      <c r="AI191">
+        <v>1.85</v>
+      </c>
+      <c r="AJ191">
+        <v>1.8</v>
+      </c>
+      <c r="AK191">
+        <v>1.3</v>
+      </c>
+      <c r="AL191">
+        <v>1.28</v>
+      </c>
+      <c r="AM191">
+        <v>1.7</v>
+      </c>
+      <c r="AN191">
+        <v>1.8</v>
+      </c>
+      <c r="AO191">
+        <v>1.27</v>
+      </c>
+      <c r="AP191">
+        <v>1.64</v>
+      </c>
+      <c r="AQ191">
+        <v>1.42</v>
+      </c>
+      <c r="AR191">
+        <v>1.28</v>
+      </c>
+      <c r="AS191">
+        <v>1.33</v>
+      </c>
+      <c r="AT191">
+        <v>2.61</v>
+      </c>
+      <c r="AU191">
+        <v>3</v>
+      </c>
+      <c r="AV191">
+        <v>4</v>
+      </c>
+      <c r="AW191">
+        <v>6</v>
+      </c>
+      <c r="AX191">
+        <v>4</v>
+      </c>
+      <c r="AY191">
+        <v>9</v>
+      </c>
+      <c r="AZ191">
+        <v>8</v>
+      </c>
+      <c r="BA191">
+        <v>5</v>
+      </c>
+      <c r="BB191">
+        <v>2</v>
+      </c>
+      <c r="BC191">
+        <v>7</v>
+      </c>
+      <c r="BD191">
+        <v>1.73</v>
+      </c>
+      <c r="BE191">
+        <v>6.25</v>
+      </c>
+      <c r="BF191">
+        <v>2.4</v>
+      </c>
+      <c r="BG191">
+        <v>1.5</v>
+      </c>
+      <c r="BH191">
+        <v>2.38</v>
+      </c>
+      <c r="BI191">
+        <v>1.86</v>
+      </c>
+      <c r="BJ191">
+        <v>1.82</v>
+      </c>
+      <c r="BK191">
+        <v>2.4</v>
+      </c>
+      <c r="BL191">
+        <v>1.49</v>
+      </c>
+      <c r="BM191">
+        <v>3.15</v>
+      </c>
+      <c r="BN191">
+        <v>1.3</v>
+      </c>
+      <c r="BO191">
+        <v>4.3</v>
+      </c>
+      <c r="BP191">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="192" spans="1:68">
+      <c r="A192" s="1">
+        <v>191</v>
+      </c>
+      <c r="B192">
+        <v>7469059</v>
+      </c>
+      <c r="C192" t="s">
+        <v>68</v>
+      </c>
+      <c r="D192" t="s">
+        <v>69</v>
+      </c>
+      <c r="E192" s="2">
+        <v>45695.66666666666</v>
+      </c>
+      <c r="F192">
+        <v>22</v>
+      </c>
+      <c r="G192" t="s">
+        <v>81</v>
+      </c>
+      <c r="H192" t="s">
+        <v>83</v>
+      </c>
+      <c r="I192">
+        <v>0</v>
+      </c>
+      <c r="J192">
+        <v>1</v>
+      </c>
+      <c r="K192">
+        <v>1</v>
+      </c>
+      <c r="L192">
+        <v>0</v>
+      </c>
+      <c r="M192">
+        <v>2</v>
+      </c>
+      <c r="N192">
+        <v>2</v>
+      </c>
+      <c r="O192" t="s">
+        <v>90</v>
+      </c>
+      <c r="P192" t="s">
+        <v>293</v>
+      </c>
+      <c r="Q192">
+        <v>3.25</v>
+      </c>
+      <c r="R192">
+        <v>2.05</v>
+      </c>
+      <c r="S192">
+        <v>3.1</v>
+      </c>
+      <c r="T192">
+        <v>1.4</v>
+      </c>
+      <c r="U192">
+        <v>2.75</v>
+      </c>
+      <c r="V192">
+        <v>2.8</v>
+      </c>
+      <c r="W192">
+        <v>1.38</v>
+      </c>
+      <c r="X192">
+        <v>7.7</v>
+      </c>
+      <c r="Y192">
+        <v>1.05</v>
+      </c>
+      <c r="Z192">
+        <v>2.73</v>
+      </c>
+      <c r="AA192">
+        <v>3.15</v>
+      </c>
+      <c r="AB192">
+        <v>2.59</v>
+      </c>
+      <c r="AC192">
+        <v>1.06</v>
+      </c>
+      <c r="AD192">
+        <v>8.5</v>
+      </c>
+      <c r="AE192">
+        <v>1.33</v>
+      </c>
+      <c r="AF192">
+        <v>3.25</v>
+      </c>
+      <c r="AG192">
+        <v>2</v>
+      </c>
+      <c r="AH192">
+        <v>1.75</v>
+      </c>
+      <c r="AI192">
+        <v>1.7</v>
+      </c>
+      <c r="AJ192">
+        <v>2</v>
+      </c>
+      <c r="AK192">
+        <v>1.48</v>
+      </c>
+      <c r="AL192">
+        <v>1.28</v>
+      </c>
+      <c r="AM192">
+        <v>1.45</v>
+      </c>
+      <c r="AN192">
+        <v>1.3</v>
+      </c>
+      <c r="AO192">
+        <v>0.8</v>
+      </c>
+      <c r="AP192">
+        <v>1.18</v>
+      </c>
+      <c r="AQ192">
+        <v>1</v>
+      </c>
+      <c r="AR192">
+        <v>1.84</v>
+      </c>
+      <c r="AS192">
+        <v>1.4</v>
+      </c>
+      <c r="AT192">
+        <v>3.24</v>
+      </c>
+      <c r="AU192">
+        <v>3</v>
+      </c>
+      <c r="AV192">
+        <v>7</v>
+      </c>
+      <c r="AW192">
+        <v>4</v>
+      </c>
+      <c r="AX192">
+        <v>8</v>
+      </c>
+      <c r="AY192">
+        <v>7</v>
+      </c>
+      <c r="AZ192">
+        <v>15</v>
+      </c>
+      <c r="BA192">
+        <v>9</v>
+      </c>
+      <c r="BB192">
+        <v>2</v>
+      </c>
+      <c r="BC192">
+        <v>11</v>
+      </c>
+      <c r="BD192">
+        <v>2</v>
+      </c>
+      <c r="BE192">
+        <v>6.4</v>
+      </c>
+      <c r="BF192">
+        <v>1.98</v>
+      </c>
+      <c r="BG192">
+        <v>1.33</v>
+      </c>
+      <c r="BH192">
+        <v>2.95</v>
+      </c>
+      <c r="BI192">
+        <v>1.58</v>
+      </c>
+      <c r="BJ192">
+        <v>2.2</v>
+      </c>
+      <c r="BK192">
+        <v>1.9</v>
+      </c>
+      <c r="BL192">
+        <v>1.9</v>
+      </c>
+      <c r="BM192">
+        <v>2.45</v>
+      </c>
+      <c r="BN192">
+        <v>1.48</v>
+      </c>
+      <c r="BO192">
+        <v>3.15</v>
+      </c>
+      <c r="BP192">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="193" spans="1:68">
+      <c r="A193" s="1">
+        <v>192</v>
+      </c>
+      <c r="B193">
+        <v>7469062</v>
+      </c>
+      <c r="C193" t="s">
+        <v>68</v>
+      </c>
+      <c r="D193" t="s">
+        <v>69</v>
+      </c>
+      <c r="E193" s="2">
+        <v>45695.66666666666</v>
+      </c>
+      <c r="F193">
+        <v>22</v>
+      </c>
+      <c r="G193" t="s">
+        <v>74</v>
+      </c>
+      <c r="H193" t="s">
+        <v>87</v>
+      </c>
+      <c r="I193">
+        <v>0</v>
+      </c>
+      <c r="J193">
+        <v>0</v>
+      </c>
+      <c r="K193">
+        <v>0</v>
+      </c>
+      <c r="L193">
+        <v>0</v>
+      </c>
+      <c r="M193">
+        <v>0</v>
+      </c>
+      <c r="N193">
+        <v>0</v>
+      </c>
+      <c r="O193" t="s">
+        <v>90</v>
+      </c>
+      <c r="P193" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q193">
+        <v>2.75</v>
+      </c>
+      <c r="R193">
+        <v>2.05</v>
+      </c>
+      <c r="S193">
+        <v>3.75</v>
+      </c>
+      <c r="T193">
+        <v>1.4</v>
+      </c>
+      <c r="U193">
+        <v>2.7</v>
+      </c>
+      <c r="V193">
+        <v>2.8</v>
+      </c>
+      <c r="W193">
+        <v>1.38</v>
+      </c>
+      <c r="X193">
+        <v>8</v>
+      </c>
+      <c r="Y193">
+        <v>1.05</v>
+      </c>
+      <c r="Z193">
+        <v>2.06</v>
+      </c>
+      <c r="AA193">
+        <v>3.33</v>
+      </c>
+      <c r="AB193">
+        <v>3.53</v>
+      </c>
+      <c r="AC193">
+        <v>1.06</v>
+      </c>
+      <c r="AD193">
+        <v>8.5</v>
+      </c>
+      <c r="AE193">
+        <v>1.33</v>
+      </c>
+      <c r="AF193">
+        <v>3.2</v>
+      </c>
+      <c r="AG193">
+        <v>1.98</v>
+      </c>
+      <c r="AH193">
+        <v>1.77</v>
+      </c>
+      <c r="AI193">
+        <v>1.75</v>
+      </c>
+      <c r="AJ193">
+        <v>1.93</v>
+      </c>
+      <c r="AK193">
+        <v>1.33</v>
+      </c>
+      <c r="AL193">
+        <v>1.25</v>
+      </c>
+      <c r="AM193">
+        <v>1.65</v>
+      </c>
+      <c r="AN193">
+        <v>2.09</v>
+      </c>
+      <c r="AO193">
+        <v>1</v>
+      </c>
+      <c r="AP193">
+        <v>2</v>
+      </c>
+      <c r="AQ193">
+        <v>1</v>
+      </c>
+      <c r="AR193">
+        <v>1.24</v>
+      </c>
+      <c r="AS193">
+        <v>1.26</v>
+      </c>
+      <c r="AT193">
+        <v>2.5</v>
+      </c>
+      <c r="AU193">
+        <v>3</v>
+      </c>
+      <c r="AV193">
+        <v>2</v>
+      </c>
+      <c r="AW193">
+        <v>7</v>
+      </c>
+      <c r="AX193">
+        <v>10</v>
+      </c>
+      <c r="AY193">
+        <v>10</v>
+      </c>
+      <c r="AZ193">
+        <v>12</v>
+      </c>
+      <c r="BA193">
+        <v>4</v>
+      </c>
+      <c r="BB193">
+        <v>4</v>
+      </c>
+      <c r="BC193">
+        <v>8</v>
+      </c>
+      <c r="BD193">
+        <v>1.75</v>
+      </c>
+      <c r="BE193">
+        <v>6.5</v>
+      </c>
+      <c r="BF193">
+        <v>2.3</v>
+      </c>
+      <c r="BG193">
+        <v>1.33</v>
+      </c>
+      <c r="BH193">
+        <v>2.95</v>
+      </c>
+      <c r="BI193">
+        <v>1.57</v>
+      </c>
+      <c r="BJ193">
+        <v>2.23</v>
+      </c>
+      <c r="BK193">
+        <v>1.82</v>
+      </c>
+      <c r="BL193">
+        <v>1.98</v>
+      </c>
+      <c r="BM193">
+        <v>2.4</v>
+      </c>
+      <c r="BN193">
+        <v>1.49</v>
+      </c>
+      <c r="BO193">
+        <v>3.15</v>
+      </c>
+      <c r="BP193">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="194" spans="1:68">
+      <c r="A194" s="1">
+        <v>193</v>
+      </c>
+      <c r="B194">
+        <v>7469058</v>
+      </c>
+      <c r="C194" t="s">
+        <v>68</v>
+      </c>
+      <c r="D194" t="s">
+        <v>69</v>
+      </c>
+      <c r="E194" s="2">
+        <v>45695.66666666666</v>
+      </c>
+      <c r="F194">
+        <v>22</v>
+      </c>
+      <c r="G194" t="s">
+        <v>85</v>
+      </c>
+      <c r="H194" t="s">
+        <v>82</v>
+      </c>
+      <c r="I194">
+        <v>1</v>
+      </c>
+      <c r="J194">
+        <v>1</v>
+      </c>
+      <c r="K194">
+        <v>2</v>
+      </c>
+      <c r="L194">
+        <v>3</v>
+      </c>
+      <c r="M194">
+        <v>1</v>
+      </c>
+      <c r="N194">
+        <v>4</v>
+      </c>
+      <c r="O194" t="s">
+        <v>217</v>
+      </c>
+      <c r="P194" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q194">
+        <v>2.22</v>
+      </c>
+      <c r="R194">
+        <v>2.29</v>
+      </c>
+      <c r="S194">
+        <v>5</v>
+      </c>
+      <c r="T194">
+        <v>1.36</v>
+      </c>
+      <c r="U194">
+        <v>2.9</v>
+      </c>
+      <c r="V194">
+        <v>2.6</v>
+      </c>
+      <c r="W194">
+        <v>1.44</v>
+      </c>
+      <c r="X194">
+        <v>6.1</v>
+      </c>
+      <c r="Y194">
+        <v>1.1</v>
+      </c>
+      <c r="Z194">
+        <v>1.7</v>
+      </c>
+      <c r="AA194">
+        <v>3.76</v>
+      </c>
+      <c r="AB194">
+        <v>4.6</v>
+      </c>
+      <c r="AC194">
+        <v>1.05</v>
+      </c>
+      <c r="AD194">
+        <v>9.5</v>
+      </c>
+      <c r="AE194">
+        <v>1.27</v>
+      </c>
+      <c r="AF194">
+        <v>3.45</v>
+      </c>
+      <c r="AG194">
+        <v>1.83</v>
+      </c>
+      <c r="AH194">
+        <v>1.91</v>
+      </c>
+      <c r="AI194">
+        <v>1.79</v>
+      </c>
+      <c r="AJ194">
+        <v>1.93</v>
+      </c>
+      <c r="AK194">
+        <v>1.19</v>
+      </c>
+      <c r="AL194">
+        <v>1.24</v>
+      </c>
+      <c r="AM194">
+        <v>2.05</v>
+      </c>
+      <c r="AN194">
+        <v>2</v>
+      </c>
+      <c r="AO194">
+        <v>0.91</v>
+      </c>
+      <c r="AP194">
+        <v>2.09</v>
+      </c>
+      <c r="AQ194">
+        <v>0.83</v>
+      </c>
+      <c r="AR194">
+        <v>1.83</v>
+      </c>
+      <c r="AS194">
+        <v>1.43</v>
+      </c>
+      <c r="AT194">
+        <v>3.26</v>
+      </c>
+      <c r="AU194">
+        <v>7</v>
+      </c>
+      <c r="AV194">
+        <v>6</v>
+      </c>
+      <c r="AW194">
+        <v>3</v>
+      </c>
+      <c r="AX194">
+        <v>5</v>
+      </c>
+      <c r="AY194">
+        <v>10</v>
+      </c>
+      <c r="AZ194">
+        <v>11</v>
+      </c>
+      <c r="BA194">
+        <v>4</v>
+      </c>
+      <c r="BB194">
+        <v>6</v>
+      </c>
+      <c r="BC194">
+        <v>10</v>
+      </c>
+      <c r="BD194">
+        <v>1.58</v>
+      </c>
+      <c r="BE194">
+        <v>6.4</v>
+      </c>
+      <c r="BF194">
+        <v>2.65</v>
+      </c>
+      <c r="BG194">
+        <v>1.42</v>
+      </c>
+      <c r="BH194">
+        <v>2.65</v>
+      </c>
+      <c r="BI194">
+        <v>1.68</v>
+      </c>
+      <c r="BJ194">
+        <v>2.05</v>
+      </c>
+      <c r="BK194">
+        <v>1.9</v>
+      </c>
+      <c r="BL194">
+        <v>1.9</v>
+      </c>
+      <c r="BM194">
+        <v>2.65</v>
+      </c>
+      <c r="BN194">
+        <v>1.41</v>
+      </c>
+      <c r="BO194">
+        <v>3.55</v>
+      </c>
+      <c r="BP194">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="195" spans="1:68">
+      <c r="A195" s="1">
+        <v>194</v>
+      </c>
+      <c r="B195">
+        <v>7469055</v>
+      </c>
+      <c r="C195" t="s">
+        <v>68</v>
+      </c>
+      <c r="D195" t="s">
+        <v>69</v>
+      </c>
+      <c r="E195" s="2">
+        <v>45695.66666666666</v>
+      </c>
+      <c r="F195">
+        <v>22</v>
+      </c>
+      <c r="G195" t="s">
+        <v>77</v>
+      </c>
+      <c r="H195" t="s">
+        <v>79</v>
+      </c>
+      <c r="I195">
+        <v>0</v>
+      </c>
+      <c r="J195">
+        <v>2</v>
+      </c>
+      <c r="K195">
+        <v>2</v>
+      </c>
+      <c r="L195">
+        <v>1</v>
+      </c>
+      <c r="M195">
+        <v>2</v>
+      </c>
+      <c r="N195">
+        <v>3</v>
+      </c>
+      <c r="O195" t="s">
+        <v>214</v>
+      </c>
+      <c r="P195" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q195">
+        <v>4.75</v>
+      </c>
+      <c r="R195">
+        <v>2.1</v>
+      </c>
+      <c r="S195">
+        <v>2.3</v>
+      </c>
+      <c r="T195">
+        <v>1.4</v>
+      </c>
+      <c r="U195">
+        <v>2.75</v>
+      </c>
+      <c r="V195">
+        <v>2.8</v>
+      </c>
+      <c r="W195">
+        <v>1.38</v>
+      </c>
+      <c r="X195">
+        <v>7.6</v>
+      </c>
+      <c r="Y195">
+        <v>1.05</v>
+      </c>
+      <c r="Z195">
+        <v>4.33</v>
+      </c>
+      <c r="AA195">
+        <v>3.53</v>
+      </c>
+      <c r="AB195">
+        <v>1.79</v>
+      </c>
+      <c r="AC195">
+        <v>1.06</v>
+      </c>
+      <c r="AD195">
+        <v>8.5</v>
+      </c>
+      <c r="AE195">
+        <v>1.33</v>
+      </c>
+      <c r="AF195">
+        <v>3.2</v>
+      </c>
+      <c r="AG195">
+        <v>1.98</v>
+      </c>
+      <c r="AH195">
+        <v>1.77</v>
+      </c>
+      <c r="AI195">
+        <v>1.83</v>
+      </c>
+      <c r="AJ195">
+        <v>1.83</v>
+      </c>
+      <c r="AK195">
+        <v>2</v>
+      </c>
+      <c r="AL195">
+        <v>1.25</v>
+      </c>
+      <c r="AM195">
+        <v>1.18</v>
+      </c>
+      <c r="AN195">
+        <v>0.36</v>
+      </c>
+      <c r="AO195">
+        <v>0.91</v>
+      </c>
+      <c r="AP195">
+        <v>0.33</v>
+      </c>
+      <c r="AQ195">
+        <v>1.08</v>
+      </c>
+      <c r="AR195">
+        <v>1.02</v>
+      </c>
+      <c r="AS195">
+        <v>1.27</v>
+      </c>
+      <c r="AT195">
+        <v>2.29</v>
+      </c>
+      <c r="AU195">
+        <v>4</v>
+      </c>
+      <c r="AV195">
+        <v>9</v>
+      </c>
+      <c r="AW195">
+        <v>2</v>
+      </c>
+      <c r="AX195">
+        <v>10</v>
+      </c>
+      <c r="AY195">
+        <v>6</v>
+      </c>
+      <c r="AZ195">
+        <v>19</v>
+      </c>
+      <c r="BA195">
+        <v>1</v>
+      </c>
+      <c r="BB195">
+        <v>5</v>
+      </c>
+      <c r="BC195">
+        <v>6</v>
+      </c>
+      <c r="BD195">
+        <v>2.8</v>
+      </c>
+      <c r="BE195">
+        <v>6.75</v>
+      </c>
+      <c r="BF195">
+        <v>1.5</v>
+      </c>
+      <c r="BG195">
+        <v>1.28</v>
+      </c>
+      <c r="BH195">
+        <v>3.3</v>
+      </c>
+      <c r="BI195">
+        <v>1.49</v>
+      </c>
+      <c r="BJ195">
+        <v>2.4</v>
+      </c>
+      <c r="BK195">
+        <v>1.92</v>
+      </c>
+      <c r="BL195">
+        <v>1.88</v>
+      </c>
+      <c r="BM195">
+        <v>2.23</v>
+      </c>
+      <c r="BN195">
+        <v>1.57</v>
+      </c>
+      <c r="BO195">
+        <v>2.9</v>
+      </c>
+      <c r="BP195">
+        <v>1.35</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1244" uniqueCount="298">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -670,6 +670,9 @@
     <t>['28', '49', '75']</t>
   </si>
   <si>
+    <t>['9', '83', '86']</t>
+  </si>
+  <si>
     <t>['16', '45+2']</t>
   </si>
   <si>
@@ -899,6 +902,12 @@
   </si>
   <si>
     <t>['12', '27']</t>
+  </si>
+  <si>
+    <t>['14', '42', '56']</t>
+  </si>
+  <si>
+    <t>['7']</t>
   </si>
 </sst>
 </file>
@@ -1260,7 +1269,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP195"/>
+  <dimension ref="A1:BP197"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1516,7 +1525,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q2">
         <v>2.4</v>
@@ -1800,7 +1809,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ3">
         <v>0.91</v>
@@ -1928,7 +1937,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q4">
         <v>3.6</v>
@@ -2752,7 +2761,7 @@
         <v>90</v>
       </c>
       <c r="P8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q8">
         <v>3.1</v>
@@ -3164,7 +3173,7 @@
         <v>94</v>
       </c>
       <c r="P10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q10">
         <v>2.6</v>
@@ -3657,7 +3666,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ12">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3782,7 +3791,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q13">
         <v>3.1</v>
@@ -4275,7 +4284,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ15">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4400,7 +4409,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q16">
         <v>2.63</v>
@@ -4606,7 +4615,7 @@
         <v>99</v>
       </c>
       <c r="P17" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -4890,7 +4899,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ18">
         <v>0.7</v>
@@ -5302,7 +5311,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ20">
         <v>1.08</v>
@@ -5636,7 +5645,7 @@
         <v>103</v>
       </c>
       <c r="P22" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -6048,7 +6057,7 @@
         <v>105</v>
       </c>
       <c r="P24" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q24">
         <v>2.62</v>
@@ -6460,7 +6469,7 @@
         <v>106</v>
       </c>
       <c r="P26" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q26">
         <v>2.83</v>
@@ -6872,7 +6881,7 @@
         <v>108</v>
       </c>
       <c r="P28" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q28">
         <v>2.6</v>
@@ -7362,7 +7371,7 @@
         <v>1.5</v>
       </c>
       <c r="AP30">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ30">
         <v>1</v>
@@ -7983,7 +7992,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ33">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR33">
         <v>2.15</v>
@@ -8314,7 +8323,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q35">
         <v>3.3</v>
@@ -8395,7 +8404,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ35">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR35">
         <v>1.69</v>
@@ -8520,7 +8529,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q36">
         <v>3.1</v>
@@ -8726,7 +8735,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q37">
         <v>3.4</v>
@@ -8932,7 +8941,7 @@
         <v>90</v>
       </c>
       <c r="P38" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q38">
         <v>3.2</v>
@@ -9138,7 +9147,7 @@
         <v>90</v>
       </c>
       <c r="P39" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q39">
         <v>3.4</v>
@@ -9550,7 +9559,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q41">
         <v>2.5</v>
@@ -9756,7 +9765,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q42">
         <v>3.25</v>
@@ -9962,7 +9971,7 @@
         <v>90</v>
       </c>
       <c r="P43" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q43">
         <v>2.75</v>
@@ -10867,7 +10876,7 @@
         <v>1</v>
       </c>
       <c r="AQ47">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR47">
         <v>1.49</v>
@@ -11485,7 +11494,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ50">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR50">
         <v>1.61</v>
@@ -11894,7 +11903,7 @@
         <v>1.5</v>
       </c>
       <c r="AP52">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ52">
         <v>0.7</v>
@@ -12022,7 +12031,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -12228,7 +12237,7 @@
         <v>129</v>
       </c>
       <c r="P54" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q54">
         <v>2.55</v>
@@ -12434,7 +12443,7 @@
         <v>130</v>
       </c>
       <c r="P55" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q55">
         <v>2.55</v>
@@ -12718,7 +12727,7 @@
         <v>0.33</v>
       </c>
       <c r="AP56">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ56">
         <v>0.64</v>
@@ -12846,7 +12855,7 @@
         <v>132</v>
       </c>
       <c r="P57" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -13052,7 +13061,7 @@
         <v>133</v>
       </c>
       <c r="P58" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -13258,7 +13267,7 @@
         <v>134</v>
       </c>
       <c r="P59" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q59">
         <v>2.62</v>
@@ -13464,7 +13473,7 @@
         <v>135</v>
       </c>
       <c r="P60" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q60">
         <v>2.88</v>
@@ -13876,7 +13885,7 @@
         <v>137</v>
       </c>
       <c r="P62" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q62">
         <v>3.6</v>
@@ -14082,7 +14091,7 @@
         <v>138</v>
       </c>
       <c r="P63" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q63">
         <v>3.75</v>
@@ -15112,7 +15121,7 @@
         <v>143</v>
       </c>
       <c r="P68" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15318,7 +15327,7 @@
         <v>144</v>
       </c>
       <c r="P69" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15396,7 +15405,7 @@
         <v>1</v>
       </c>
       <c r="AP69">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ69">
         <v>1.4</v>
@@ -15524,7 +15533,7 @@
         <v>145</v>
       </c>
       <c r="P70" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q70">
         <v>3.75</v>
@@ -15811,7 +15820,7 @@
         <v>1</v>
       </c>
       <c r="AQ71">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR71">
         <v>1.24</v>
@@ -15936,7 +15945,7 @@
         <v>147</v>
       </c>
       <c r="P72" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16017,7 +16026,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ72">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR72">
         <v>1.72</v>
@@ -16142,7 +16151,7 @@
         <v>90</v>
       </c>
       <c r="P73" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q73">
         <v>4.33</v>
@@ -16348,7 +16357,7 @@
         <v>90</v>
       </c>
       <c r="P74" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q74">
         <v>2.4</v>
@@ -16554,7 +16563,7 @@
         <v>148</v>
       </c>
       <c r="P75" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q75">
         <v>3.5</v>
@@ -16760,7 +16769,7 @@
         <v>149</v>
       </c>
       <c r="P76" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q76">
         <v>2.88</v>
@@ -17378,7 +17387,7 @@
         <v>151</v>
       </c>
       <c r="P79" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17584,7 +17593,7 @@
         <v>152</v>
       </c>
       <c r="P80" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q80">
         <v>2.05</v>
@@ -17662,7 +17671,7 @@
         <v>1.5</v>
       </c>
       <c r="AP80">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ80">
         <v>1.42</v>
@@ -17790,7 +17799,7 @@
         <v>90</v>
       </c>
       <c r="P81" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q81">
         <v>4.33</v>
@@ -18614,7 +18623,7 @@
         <v>90</v>
       </c>
       <c r="P85" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q85">
         <v>3.1</v>
@@ -18695,7 +18704,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ85">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR85">
         <v>1.48</v>
@@ -18820,7 +18829,7 @@
         <v>156</v>
       </c>
       <c r="P86" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -19313,7 +19322,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ88">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR88">
         <v>1.77</v>
@@ -19644,7 +19653,7 @@
         <v>90</v>
       </c>
       <c r="P90" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q90">
         <v>2.38</v>
@@ -20056,7 +20065,7 @@
         <v>160</v>
       </c>
       <c r="P92" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20674,7 +20683,7 @@
         <v>162</v>
       </c>
       <c r="P95" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q95">
         <v>1.9</v>
@@ -20752,7 +20761,7 @@
         <v>1</v>
       </c>
       <c r="AP95">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ95">
         <v>1.2</v>
@@ -20880,7 +20889,7 @@
         <v>163</v>
       </c>
       <c r="P96" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q96">
         <v>2.75</v>
@@ -21292,7 +21301,7 @@
         <v>90</v>
       </c>
       <c r="P98" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q98">
         <v>4.75</v>
@@ -21785,7 +21794,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ100">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR100">
         <v>1.57</v>
@@ -22322,7 +22331,7 @@
         <v>166</v>
       </c>
       <c r="P103" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q103">
         <v>4.2</v>
@@ -22528,7 +22537,7 @@
         <v>167</v>
       </c>
       <c r="P104" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q104">
         <v>2.25</v>
@@ -23352,7 +23361,7 @@
         <v>90</v>
       </c>
       <c r="P108" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q108">
         <v>4.5</v>
@@ -23430,7 +23439,7 @@
         <v>1.2</v>
       </c>
       <c r="AP108">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ108">
         <v>1.3</v>
@@ -24176,7 +24185,7 @@
         <v>173</v>
       </c>
       <c r="P112" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q112">
         <v>3.5</v>
@@ -24460,7 +24469,7 @@
         <v>1.4</v>
       </c>
       <c r="AP113">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ113">
         <v>1.3</v>
@@ -24588,7 +24597,7 @@
         <v>90</v>
       </c>
       <c r="P114" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q114">
         <v>2.85</v>
@@ -25000,7 +25009,7 @@
         <v>175</v>
       </c>
       <c r="P116" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q116">
         <v>2.4</v>
@@ -25078,10 +25087,10 @@
         <v>1.2</v>
       </c>
       <c r="AP116">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ116">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR116">
         <v>1.94</v>
@@ -25412,7 +25421,7 @@
         <v>90</v>
       </c>
       <c r="P118" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q118">
         <v>4</v>
@@ -26030,7 +26039,7 @@
         <v>178</v>
       </c>
       <c r="P121" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q121">
         <v>2.88</v>
@@ -26317,7 +26326,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ122">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR122">
         <v>1.78</v>
@@ -27344,7 +27353,7 @@
         <v>1</v>
       </c>
       <c r="AP127">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ127">
         <v>1</v>
@@ -27550,7 +27559,7 @@
         <v>1</v>
       </c>
       <c r="AP128">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ128">
         <v>1.08</v>
@@ -27759,7 +27768,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ129">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR129">
         <v>0.99</v>
@@ -28708,7 +28717,7 @@
         <v>90</v>
       </c>
       <c r="P134" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q134">
         <v>3.2</v>
@@ -28789,7 +28798,7 @@
         <v>2</v>
       </c>
       <c r="AQ134">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR134">
         <v>1.08</v>
@@ -28914,7 +28923,7 @@
         <v>90</v>
       </c>
       <c r="P135" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q135">
         <v>5</v>
@@ -28992,7 +29001,7 @@
         <v>2</v>
       </c>
       <c r="AP135">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ135">
         <v>1.82</v>
@@ -29407,7 +29416,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ137">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR137">
         <v>1.66</v>
@@ -29944,7 +29953,7 @@
         <v>188</v>
       </c>
       <c r="P140" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q140">
         <v>2.95</v>
@@ -30150,7 +30159,7 @@
         <v>189</v>
       </c>
       <c r="P141" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q141">
         <v>2.8</v>
@@ -30434,7 +30443,7 @@
         <v>2.13</v>
       </c>
       <c r="AP142">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ142">
         <v>1.82</v>
@@ -30974,7 +30983,7 @@
         <v>192</v>
       </c>
       <c r="P145" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q145">
         <v>2.75</v>
@@ -31180,7 +31189,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q146">
         <v>3.75</v>
@@ -31386,7 +31395,7 @@
         <v>129</v>
       </c>
       <c r="P147" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q147">
         <v>3.75</v>
@@ -31464,7 +31473,7 @@
         <v>1</v>
       </c>
       <c r="AP147">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ147">
         <v>1.42</v>
@@ -31592,7 +31601,7 @@
         <v>90</v>
       </c>
       <c r="P148" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q148">
         <v>2.4</v>
@@ -31798,7 +31807,7 @@
         <v>90</v>
       </c>
       <c r="P149" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q149">
         <v>3.1</v>
@@ -32210,7 +32219,7 @@
         <v>194</v>
       </c>
       <c r="P151" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q151">
         <v>1.62</v>
@@ -32622,7 +32631,7 @@
         <v>95</v>
       </c>
       <c r="P153" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q153">
         <v>2.63</v>
@@ -33446,7 +33455,7 @@
         <v>197</v>
       </c>
       <c r="P157" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q157">
         <v>2.7</v>
@@ -33652,7 +33661,7 @@
         <v>96</v>
       </c>
       <c r="P158" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q158">
         <v>2.55</v>
@@ -33858,7 +33867,7 @@
         <v>198</v>
       </c>
       <c r="P159" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q159">
         <v>3.3</v>
@@ -33939,7 +33948,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ159">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR159">
         <v>1.45</v>
@@ -34064,7 +34073,7 @@
         <v>90</v>
       </c>
       <c r="P160" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q160">
         <v>2.75</v>
@@ -34351,7 +34360,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ161">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR161">
         <v>1.88</v>
@@ -34760,7 +34769,7 @@
         <v>1.38</v>
       </c>
       <c r="AP163">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ163">
         <v>1.3</v>
@@ -35506,7 +35515,7 @@
         <v>109</v>
       </c>
       <c r="P167" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q167">
         <v>3.35</v>
@@ -35790,7 +35799,7 @@
         <v>0.5</v>
       </c>
       <c r="AP168">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ168">
         <v>0.4</v>
@@ -35918,7 +35927,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q169">
         <v>2.8</v>
@@ -36124,7 +36133,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q170">
         <v>3</v>
@@ -36536,7 +36545,7 @@
         <v>90</v>
       </c>
       <c r="P172" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q172">
         <v>2.63</v>
@@ -36742,7 +36751,7 @@
         <v>207</v>
       </c>
       <c r="P173" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q173">
         <v>2.3</v>
@@ -37235,7 +37244,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ175">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR175">
         <v>0.95</v>
@@ -37772,7 +37781,7 @@
         <v>90</v>
       </c>
       <c r="P178" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q178">
         <v>3.25</v>
@@ -37853,7 +37862,7 @@
         <v>1</v>
       </c>
       <c r="AQ178">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR178">
         <v>1.34</v>
@@ -38184,7 +38193,7 @@
         <v>212</v>
       </c>
       <c r="P180" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q180">
         <v>2.2</v>
@@ -38262,7 +38271,7 @@
         <v>1.44</v>
       </c>
       <c r="AP180">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ180">
         <v>1.3</v>
@@ -38390,7 +38399,7 @@
         <v>90</v>
       </c>
       <c r="P181" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q181">
         <v>3.25</v>
@@ -39214,7 +39223,7 @@
         <v>214</v>
       </c>
       <c r="P185" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q185">
         <v>2.6</v>
@@ -39626,7 +39635,7 @@
         <v>90</v>
       </c>
       <c r="P187" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q187">
         <v>2.55</v>
@@ -39832,7 +39841,7 @@
         <v>215</v>
       </c>
       <c r="P188" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q188">
         <v>4.5</v>
@@ -40244,7 +40253,7 @@
         <v>90</v>
       </c>
       <c r="P190" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q190">
         <v>3.3</v>
@@ -40450,7 +40459,7 @@
         <v>90</v>
       </c>
       <c r="P191" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q191">
         <v>2.75</v>
@@ -40656,7 +40665,7 @@
         <v>90</v>
       </c>
       <c r="P192" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q192">
         <v>3.25</v>
@@ -41274,7 +41283,7 @@
         <v>214</v>
       </c>
       <c r="P195" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q195">
         <v>4.75</v>
@@ -41431,6 +41440,418 @@
       </c>
       <c r="BP195">
         <v>1.35</v>
+      </c>
+    </row>
+    <row r="196" spans="1:68">
+      <c r="A196" s="1">
+        <v>195</v>
+      </c>
+      <c r="B196">
+        <v>7469060</v>
+      </c>
+      <c r="C196" t="s">
+        <v>68</v>
+      </c>
+      <c r="D196" t="s">
+        <v>69</v>
+      </c>
+      <c r="E196" s="2">
+        <v>45696.41666666666</v>
+      </c>
+      <c r="F196">
+        <v>22</v>
+      </c>
+      <c r="G196" t="s">
+        <v>71</v>
+      </c>
+      <c r="H196" t="s">
+        <v>75</v>
+      </c>
+      <c r="I196">
+        <v>0</v>
+      </c>
+      <c r="J196">
+        <v>2</v>
+      </c>
+      <c r="K196">
+        <v>2</v>
+      </c>
+      <c r="L196">
+        <v>0</v>
+      </c>
+      <c r="M196">
+        <v>3</v>
+      </c>
+      <c r="N196">
+        <v>3</v>
+      </c>
+      <c r="O196" t="s">
+        <v>90</v>
+      </c>
+      <c r="P196" t="s">
+        <v>296</v>
+      </c>
+      <c r="Q196">
+        <v>3.65</v>
+      </c>
+      <c r="R196">
+        <v>1.97</v>
+      </c>
+      <c r="S196">
+        <v>3.35</v>
+      </c>
+      <c r="T196">
+        <v>1.54</v>
+      </c>
+      <c r="U196">
+        <v>2.35</v>
+      </c>
+      <c r="V196">
+        <v>3.35</v>
+      </c>
+      <c r="W196">
+        <v>1.28</v>
+      </c>
+      <c r="X196">
+        <v>10.75</v>
+      </c>
+      <c r="Y196">
+        <v>1.01</v>
+      </c>
+      <c r="Z196">
+        <v>3.35</v>
+      </c>
+      <c r="AA196">
+        <v>3.06</v>
+      </c>
+      <c r="AB196">
+        <v>2.25</v>
+      </c>
+      <c r="AC196">
+        <v>1.09</v>
+      </c>
+      <c r="AD196">
+        <v>7</v>
+      </c>
+      <c r="AE196">
+        <v>1.45</v>
+      </c>
+      <c r="AF196">
+        <v>2.5</v>
+      </c>
+      <c r="AG196">
+        <v>2.3</v>
+      </c>
+      <c r="AH196">
+        <v>1.5</v>
+      </c>
+      <c r="AI196">
+        <v>1.99</v>
+      </c>
+      <c r="AJ196">
+        <v>1.74</v>
+      </c>
+      <c r="AK196">
+        <v>1.47</v>
+      </c>
+      <c r="AL196">
+        <v>1.34</v>
+      </c>
+      <c r="AM196">
+        <v>1.4</v>
+      </c>
+      <c r="AN196">
+        <v>1.7</v>
+      </c>
+      <c r="AO196">
+        <v>1.5</v>
+      </c>
+      <c r="AP196">
+        <v>1.55</v>
+      </c>
+      <c r="AQ196">
+        <v>1.64</v>
+      </c>
+      <c r="AR196">
+        <v>1.27</v>
+      </c>
+      <c r="AS196">
+        <v>1.36</v>
+      </c>
+      <c r="AT196">
+        <v>2.63</v>
+      </c>
+      <c r="AU196">
+        <v>0</v>
+      </c>
+      <c r="AV196">
+        <v>4</v>
+      </c>
+      <c r="AW196">
+        <v>9</v>
+      </c>
+      <c r="AX196">
+        <v>8</v>
+      </c>
+      <c r="AY196">
+        <v>9</v>
+      </c>
+      <c r="AZ196">
+        <v>12</v>
+      </c>
+      <c r="BA196">
+        <v>4</v>
+      </c>
+      <c r="BB196">
+        <v>5</v>
+      </c>
+      <c r="BC196">
+        <v>9</v>
+      </c>
+      <c r="BD196">
+        <v>2.02</v>
+      </c>
+      <c r="BE196">
+        <v>6.25</v>
+      </c>
+      <c r="BF196">
+        <v>1.98</v>
+      </c>
+      <c r="BG196">
+        <v>1.43</v>
+      </c>
+      <c r="BH196">
+        <v>2.55</v>
+      </c>
+      <c r="BI196">
+        <v>1.73</v>
+      </c>
+      <c r="BJ196">
+        <v>1.98</v>
+      </c>
+      <c r="BK196">
+        <v>2.17</v>
+      </c>
+      <c r="BL196">
+        <v>1.6</v>
+      </c>
+      <c r="BM196">
+        <v>2.8</v>
+      </c>
+      <c r="BN196">
+        <v>1.37</v>
+      </c>
+      <c r="BO196">
+        <v>3.65</v>
+      </c>
+      <c r="BP196">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="197" spans="1:68">
+      <c r="A197" s="1">
+        <v>196</v>
+      </c>
+      <c r="B197">
+        <v>7469056</v>
+      </c>
+      <c r="C197" t="s">
+        <v>68</v>
+      </c>
+      <c r="D197" t="s">
+        <v>69</v>
+      </c>
+      <c r="E197" s="2">
+        <v>45696.41666666666</v>
+      </c>
+      <c r="F197">
+        <v>22</v>
+      </c>
+      <c r="G197" t="s">
+        <v>86</v>
+      </c>
+      <c r="H197" t="s">
+        <v>73</v>
+      </c>
+      <c r="I197">
+        <v>1</v>
+      </c>
+      <c r="J197">
+        <v>1</v>
+      </c>
+      <c r="K197">
+        <v>2</v>
+      </c>
+      <c r="L197">
+        <v>3</v>
+      </c>
+      <c r="M197">
+        <v>1</v>
+      </c>
+      <c r="N197">
+        <v>4</v>
+      </c>
+      <c r="O197" t="s">
+        <v>218</v>
+      </c>
+      <c r="P197" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q197">
+        <v>1.94</v>
+      </c>
+      <c r="R197">
+        <v>2.41</v>
+      </c>
+      <c r="S197">
+        <v>6.6</v>
+      </c>
+      <c r="T197">
+        <v>1.35</v>
+      </c>
+      <c r="U197">
+        <v>3</v>
+      </c>
+      <c r="V197">
+        <v>2.55</v>
+      </c>
+      <c r="W197">
+        <v>1.45</v>
+      </c>
+      <c r="X197">
+        <v>6.1</v>
+      </c>
+      <c r="Y197">
+        <v>1.1</v>
+      </c>
+      <c r="Z197">
+        <v>1.47</v>
+      </c>
+      <c r="AA197">
+        <v>4.33</v>
+      </c>
+      <c r="AB197">
+        <v>6.3</v>
+      </c>
+      <c r="AC197">
+        <v>1.05</v>
+      </c>
+      <c r="AD197">
+        <v>9.5</v>
+      </c>
+      <c r="AE197">
+        <v>1.26</v>
+      </c>
+      <c r="AF197">
+        <v>3.5</v>
+      </c>
+      <c r="AG197">
+        <v>1.8</v>
+      </c>
+      <c r="AH197">
+        <v>1.94</v>
+      </c>
+      <c r="AI197">
+        <v>1.96</v>
+      </c>
+      <c r="AJ197">
+        <v>1.76</v>
+      </c>
+      <c r="AK197">
+        <v>1.11</v>
+      </c>
+      <c r="AL197">
+        <v>1.19</v>
+      </c>
+      <c r="AM197">
+        <v>2.55</v>
+      </c>
+      <c r="AN197">
+        <v>2.8</v>
+      </c>
+      <c r="AO197">
+        <v>0.6</v>
+      </c>
+      <c r="AP197">
+        <v>2.82</v>
+      </c>
+      <c r="AQ197">
+        <v>0.55</v>
+      </c>
+      <c r="AR197">
+        <v>1.67</v>
+      </c>
+      <c r="AS197">
+        <v>1.27</v>
+      </c>
+      <c r="AT197">
+        <v>2.94</v>
+      </c>
+      <c r="AU197">
+        <v>9</v>
+      </c>
+      <c r="AV197">
+        <v>3</v>
+      </c>
+      <c r="AW197">
+        <v>16</v>
+      </c>
+      <c r="AX197">
+        <v>1</v>
+      </c>
+      <c r="AY197">
+        <v>25</v>
+      </c>
+      <c r="AZ197">
+        <v>4</v>
+      </c>
+      <c r="BA197">
+        <v>9</v>
+      </c>
+      <c r="BB197">
+        <v>1</v>
+      </c>
+      <c r="BC197">
+        <v>10</v>
+      </c>
+      <c r="BD197">
+        <v>1.38</v>
+      </c>
+      <c r="BE197">
+        <v>7</v>
+      </c>
+      <c r="BF197">
+        <v>3.4</v>
+      </c>
+      <c r="BG197">
+        <v>1.3</v>
+      </c>
+      <c r="BH197">
+        <v>3.05</v>
+      </c>
+      <c r="BI197">
+        <v>1.54</v>
+      </c>
+      <c r="BJ197">
+        <v>2.3</v>
+      </c>
+      <c r="BK197">
+        <v>1.95</v>
+      </c>
+      <c r="BL197">
+        <v>1.85</v>
+      </c>
+      <c r="BM197">
+        <v>2.33</v>
+      </c>
+      <c r="BN197">
+        <v>1.52</v>
+      </c>
+      <c r="BO197">
+        <v>3</v>
+      </c>
+      <c r="BP197">
+        <v>1.32</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1244" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1250" uniqueCount="299">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -673,6 +673,9 @@
     <t>['9', '83', '86']</t>
   </si>
   <si>
+    <t>['4', '18', '69']</t>
+  </si>
+  <si>
     <t>['16', '45+2']</t>
   </si>
   <si>
@@ -1269,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP197"/>
+  <dimension ref="A1:BP198"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1525,7 +1528,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q2">
         <v>2.4</v>
@@ -1937,7 +1940,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q4">
         <v>3.6</v>
@@ -2761,7 +2764,7 @@
         <v>90</v>
       </c>
       <c r="P8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q8">
         <v>3.1</v>
@@ -3173,7 +3176,7 @@
         <v>94</v>
       </c>
       <c r="P10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q10">
         <v>2.6</v>
@@ -3251,7 +3254,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ10">
         <v>1</v>
@@ -3460,7 +3463,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ11">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3791,7 +3794,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q13">
         <v>3.1</v>
@@ -4409,7 +4412,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q16">
         <v>2.63</v>
@@ -4615,7 +4618,7 @@
         <v>99</v>
       </c>
       <c r="P17" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -5645,7 +5648,7 @@
         <v>103</v>
       </c>
       <c r="P22" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -6057,7 +6060,7 @@
         <v>105</v>
       </c>
       <c r="P24" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q24">
         <v>2.62</v>
@@ -6469,7 +6472,7 @@
         <v>106</v>
       </c>
       <c r="P26" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q26">
         <v>2.83</v>
@@ -6881,7 +6884,7 @@
         <v>108</v>
       </c>
       <c r="P28" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q28">
         <v>2.6</v>
@@ -6959,7 +6962,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ28">
         <v>1.45</v>
@@ -8323,7 +8326,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q35">
         <v>3.3</v>
@@ -8529,7 +8532,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q36">
         <v>3.1</v>
@@ -8735,7 +8738,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q37">
         <v>3.4</v>
@@ -8941,7 +8944,7 @@
         <v>90</v>
       </c>
       <c r="P38" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q38">
         <v>3.2</v>
@@ -9147,7 +9150,7 @@
         <v>90</v>
       </c>
       <c r="P39" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q39">
         <v>3.4</v>
@@ -9559,7 +9562,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q41">
         <v>2.5</v>
@@ -9765,7 +9768,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q42">
         <v>3.25</v>
@@ -9971,7 +9974,7 @@
         <v>90</v>
       </c>
       <c r="P43" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q43">
         <v>2.75</v>
@@ -10464,7 +10467,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ45">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR45">
         <v>1.53</v>
@@ -10667,7 +10670,7 @@
         <v>1.5</v>
       </c>
       <c r="AP46">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ46">
         <v>1.36</v>
@@ -11285,7 +11288,7 @@
         <v>1.5</v>
       </c>
       <c r="AP49">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ49">
         <v>1.4</v>
@@ -12031,7 +12034,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -12237,7 +12240,7 @@
         <v>129</v>
       </c>
       <c r="P54" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q54">
         <v>2.55</v>
@@ -12443,7 +12446,7 @@
         <v>130</v>
       </c>
       <c r="P55" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q55">
         <v>2.55</v>
@@ -12855,7 +12858,7 @@
         <v>132</v>
       </c>
       <c r="P57" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -13061,7 +13064,7 @@
         <v>133</v>
       </c>
       <c r="P58" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -13267,7 +13270,7 @@
         <v>134</v>
       </c>
       <c r="P59" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q59">
         <v>2.62</v>
@@ -13473,7 +13476,7 @@
         <v>135</v>
       </c>
       <c r="P60" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q60">
         <v>2.88</v>
@@ -13760,7 +13763,7 @@
         <v>2</v>
       </c>
       <c r="AQ61">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR61">
         <v>1.29</v>
@@ -13885,7 +13888,7 @@
         <v>137</v>
       </c>
       <c r="P62" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q62">
         <v>3.6</v>
@@ -14091,7 +14094,7 @@
         <v>138</v>
       </c>
       <c r="P63" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q63">
         <v>3.75</v>
@@ -15121,7 +15124,7 @@
         <v>143</v>
       </c>
       <c r="P68" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15327,7 +15330,7 @@
         <v>144</v>
       </c>
       <c r="P69" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15533,7 +15536,7 @@
         <v>145</v>
       </c>
       <c r="P70" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q70">
         <v>3.75</v>
@@ -15945,7 +15948,7 @@
         <v>147</v>
       </c>
       <c r="P72" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16023,7 +16026,7 @@
         <v>0</v>
       </c>
       <c r="AP72">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ72">
         <v>0.55</v>
@@ -16151,7 +16154,7 @@
         <v>90</v>
       </c>
       <c r="P73" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q73">
         <v>4.33</v>
@@ -16357,7 +16360,7 @@
         <v>90</v>
       </c>
       <c r="P74" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q74">
         <v>2.4</v>
@@ -16563,7 +16566,7 @@
         <v>148</v>
       </c>
       <c r="P75" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q75">
         <v>3.5</v>
@@ -16769,7 +16772,7 @@
         <v>149</v>
       </c>
       <c r="P76" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q76">
         <v>2.88</v>
@@ -17262,7 +17265,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ78">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR78">
         <v>1.7</v>
@@ -17387,7 +17390,7 @@
         <v>151</v>
       </c>
       <c r="P79" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17593,7 +17596,7 @@
         <v>152</v>
       </c>
       <c r="P80" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q80">
         <v>2.05</v>
@@ -17799,7 +17802,7 @@
         <v>90</v>
       </c>
       <c r="P81" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q81">
         <v>4.33</v>
@@ -18623,7 +18626,7 @@
         <v>90</v>
       </c>
       <c r="P85" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q85">
         <v>3.1</v>
@@ -18829,7 +18832,7 @@
         <v>156</v>
       </c>
       <c r="P86" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -19319,7 +19322,7 @@
         <v>1.5</v>
       </c>
       <c r="AP88">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ88">
         <v>1.64</v>
@@ -19653,7 +19656,7 @@
         <v>90</v>
       </c>
       <c r="P90" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q90">
         <v>2.38</v>
@@ -20065,7 +20068,7 @@
         <v>160</v>
       </c>
       <c r="P92" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20146,7 +20149,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ92">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR92">
         <v>1.2</v>
@@ -20683,7 +20686,7 @@
         <v>162</v>
       </c>
       <c r="P95" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q95">
         <v>1.9</v>
@@ -20889,7 +20892,7 @@
         <v>163</v>
       </c>
       <c r="P96" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q96">
         <v>2.75</v>
@@ -21301,7 +21304,7 @@
         <v>90</v>
       </c>
       <c r="P98" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q98">
         <v>4.75</v>
@@ -22331,7 +22334,7 @@
         <v>166</v>
       </c>
       <c r="P103" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q103">
         <v>4.2</v>
@@ -22537,7 +22540,7 @@
         <v>167</v>
       </c>
       <c r="P104" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q104">
         <v>2.25</v>
@@ -23361,7 +23364,7 @@
         <v>90</v>
       </c>
       <c r="P108" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q108">
         <v>4.5</v>
@@ -24185,7 +24188,7 @@
         <v>173</v>
       </c>
       <c r="P112" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q112">
         <v>3.5</v>
@@ -24472,7 +24475,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ113">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR113">
         <v>1.1</v>
@@ -24597,7 +24600,7 @@
         <v>90</v>
       </c>
       <c r="P114" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q114">
         <v>2.85</v>
@@ -25009,7 +25012,7 @@
         <v>175</v>
       </c>
       <c r="P116" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q116">
         <v>2.4</v>
@@ -25293,7 +25296,7 @@
         <v>0.8</v>
       </c>
       <c r="AP117">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ117">
         <v>0.4</v>
@@ -25421,7 +25424,7 @@
         <v>90</v>
       </c>
       <c r="P118" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q118">
         <v>4</v>
@@ -26039,7 +26042,7 @@
         <v>178</v>
       </c>
       <c r="P121" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q121">
         <v>2.88</v>
@@ -28180,7 +28183,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ131">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR131">
         <v>1.33</v>
@@ -28717,7 +28720,7 @@
         <v>90</v>
       </c>
       <c r="P134" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q134">
         <v>3.2</v>
@@ -28923,7 +28926,7 @@
         <v>90</v>
       </c>
       <c r="P135" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q135">
         <v>5</v>
@@ -29207,7 +29210,7 @@
         <v>1.17</v>
       </c>
       <c r="AP136">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ136">
         <v>1.2</v>
@@ -29953,7 +29956,7 @@
         <v>188</v>
       </c>
       <c r="P140" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q140">
         <v>2.95</v>
@@ -30159,7 +30162,7 @@
         <v>189</v>
       </c>
       <c r="P141" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q141">
         <v>2.8</v>
@@ -30983,7 +30986,7 @@
         <v>192</v>
       </c>
       <c r="P145" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q145">
         <v>2.75</v>
@@ -31189,7 +31192,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q146">
         <v>3.75</v>
@@ -31395,7 +31398,7 @@
         <v>129</v>
       </c>
       <c r="P147" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q147">
         <v>3.75</v>
@@ -31601,7 +31604,7 @@
         <v>90</v>
       </c>
       <c r="P148" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q148">
         <v>2.4</v>
@@ -31807,7 +31810,7 @@
         <v>90</v>
       </c>
       <c r="P149" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q149">
         <v>3.1</v>
@@ -32094,7 +32097,7 @@
         <v>1</v>
       </c>
       <c r="AQ150">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR150">
         <v>1.35</v>
@@ -32219,7 +32222,7 @@
         <v>194</v>
       </c>
       <c r="P151" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q151">
         <v>1.62</v>
@@ -32503,7 +32506,7 @@
         <v>0.63</v>
       </c>
       <c r="AP152">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ152">
         <v>0.83</v>
@@ -32631,7 +32634,7 @@
         <v>95</v>
       </c>
       <c r="P153" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q153">
         <v>2.63</v>
@@ -33124,7 +33127,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ155">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR155">
         <v>1</v>
@@ -33455,7 +33458,7 @@
         <v>197</v>
       </c>
       <c r="P157" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q157">
         <v>2.7</v>
@@ -33661,7 +33664,7 @@
         <v>96</v>
       </c>
       <c r="P158" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q158">
         <v>2.55</v>
@@ -33867,7 +33870,7 @@
         <v>198</v>
       </c>
       <c r="P159" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q159">
         <v>3.3</v>
@@ -34073,7 +34076,7 @@
         <v>90</v>
       </c>
       <c r="P160" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q160">
         <v>2.75</v>
@@ -35515,7 +35518,7 @@
         <v>109</v>
       </c>
       <c r="P167" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q167">
         <v>3.35</v>
@@ -35927,7 +35930,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q169">
         <v>2.8</v>
@@ -36133,7 +36136,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q170">
         <v>3</v>
@@ -36211,7 +36214,7 @@
         <v>1.89</v>
       </c>
       <c r="AP170">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ170">
         <v>1.82</v>
@@ -36545,7 +36548,7 @@
         <v>90</v>
       </c>
       <c r="P172" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q172">
         <v>2.63</v>
@@ -36751,7 +36754,7 @@
         <v>207</v>
       </c>
       <c r="P173" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q173">
         <v>2.3</v>
@@ -37653,7 +37656,7 @@
         <v>0.78</v>
       </c>
       <c r="AP177">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ177">
         <v>0.7</v>
@@ -37781,7 +37784,7 @@
         <v>90</v>
       </c>
       <c r="P178" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q178">
         <v>3.25</v>
@@ -38193,7 +38196,7 @@
         <v>212</v>
       </c>
       <c r="P180" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q180">
         <v>2.2</v>
@@ -38274,7 +38277,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ180">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR180">
         <v>1.65</v>
@@ -38399,7 +38402,7 @@
         <v>90</v>
       </c>
       <c r="P181" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q181">
         <v>3.25</v>
@@ -39223,7 +39226,7 @@
         <v>214</v>
       </c>
       <c r="P185" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q185">
         <v>2.6</v>
@@ -39635,7 +39638,7 @@
         <v>90</v>
       </c>
       <c r="P187" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q187">
         <v>2.55</v>
@@ -39841,7 +39844,7 @@
         <v>215</v>
       </c>
       <c r="P188" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q188">
         <v>4.5</v>
@@ -40253,7 +40256,7 @@
         <v>90</v>
       </c>
       <c r="P190" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q190">
         <v>3.3</v>
@@ -40459,7 +40462,7 @@
         <v>90</v>
       </c>
       <c r="P191" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q191">
         <v>2.75</v>
@@ -40665,7 +40668,7 @@
         <v>90</v>
       </c>
       <c r="P192" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q192">
         <v>3.25</v>
@@ -41283,7 +41286,7 @@
         <v>214</v>
       </c>
       <c r="P195" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q195">
         <v>4.75</v>
@@ -41489,7 +41492,7 @@
         <v>90</v>
       </c>
       <c r="P196" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q196">
         <v>3.65</v>
@@ -41695,7 +41698,7 @@
         <v>218</v>
       </c>
       <c r="P197" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q197">
         <v>1.94</v>
@@ -41851,6 +41854,212 @@
         <v>3</v>
       </c>
       <c r="BP197">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="198" spans="1:68">
+      <c r="A198" s="1">
+        <v>197</v>
+      </c>
+      <c r="B198">
+        <v>7469057</v>
+      </c>
+      <c r="C198" t="s">
+        <v>68</v>
+      </c>
+      <c r="D198" t="s">
+        <v>69</v>
+      </c>
+      <c r="E198" s="2">
+        <v>45696.66666666666</v>
+      </c>
+      <c r="F198">
+        <v>22</v>
+      </c>
+      <c r="G198" t="s">
+        <v>78</v>
+      </c>
+      <c r="H198" t="s">
+        <v>70</v>
+      </c>
+      <c r="I198">
+        <v>2</v>
+      </c>
+      <c r="J198">
+        <v>0</v>
+      </c>
+      <c r="K198">
+        <v>2</v>
+      </c>
+      <c r="L198">
+        <v>3</v>
+      </c>
+      <c r="M198">
+        <v>1</v>
+      </c>
+      <c r="N198">
+        <v>4</v>
+      </c>
+      <c r="O198" t="s">
+        <v>219</v>
+      </c>
+      <c r="P198" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q198">
+        <v>2.29</v>
+      </c>
+      <c r="R198">
+        <v>2.16</v>
+      </c>
+      <c r="S198">
+        <v>5.4</v>
+      </c>
+      <c r="T198">
+        <v>1.43</v>
+      </c>
+      <c r="U198">
+        <v>2.65</v>
+      </c>
+      <c r="V198">
+        <v>2.9</v>
+      </c>
+      <c r="W198">
+        <v>1.36</v>
+      </c>
+      <c r="X198">
+        <v>8.1</v>
+      </c>
+      <c r="Y198">
+        <v>1.04</v>
+      </c>
+      <c r="Z198">
+        <v>1.62</v>
+      </c>
+      <c r="AA198">
+        <v>3.79</v>
+      </c>
+      <c r="AB198">
+        <v>5.3</v>
+      </c>
+      <c r="AC198">
+        <v>1.07</v>
+      </c>
+      <c r="AD198">
+        <v>8</v>
+      </c>
+      <c r="AE198">
+        <v>1.35</v>
+      </c>
+      <c r="AF198">
+        <v>2.9</v>
+      </c>
+      <c r="AG198">
+        <v>1.98</v>
+      </c>
+      <c r="AH198">
+        <v>1.77</v>
+      </c>
+      <c r="AI198">
+        <v>1.98</v>
+      </c>
+      <c r="AJ198">
+        <v>1.75</v>
+      </c>
+      <c r="AK198">
+        <v>1.18</v>
+      </c>
+      <c r="AL198">
+        <v>1.26</v>
+      </c>
+      <c r="AM198">
+        <v>2.02</v>
+      </c>
+      <c r="AN198">
+        <v>2.27</v>
+      </c>
+      <c r="AO198">
+        <v>1.3</v>
+      </c>
+      <c r="AP198">
+        <v>2.33</v>
+      </c>
+      <c r="AQ198">
+        <v>1.18</v>
+      </c>
+      <c r="AR198">
+        <v>1.7</v>
+      </c>
+      <c r="AS198">
+        <v>1.35</v>
+      </c>
+      <c r="AT198">
+        <v>3.05</v>
+      </c>
+      <c r="AU198">
+        <v>8</v>
+      </c>
+      <c r="AV198">
+        <v>6</v>
+      </c>
+      <c r="AW198">
+        <v>12</v>
+      </c>
+      <c r="AX198">
+        <v>7</v>
+      </c>
+      <c r="AY198">
+        <v>20</v>
+      </c>
+      <c r="AZ198">
+        <v>13</v>
+      </c>
+      <c r="BA198">
+        <v>6</v>
+      </c>
+      <c r="BB198">
+        <v>3</v>
+      </c>
+      <c r="BC198">
+        <v>9</v>
+      </c>
+      <c r="BD198">
+        <v>1.46</v>
+      </c>
+      <c r="BE198">
+        <v>7</v>
+      </c>
+      <c r="BF198">
+        <v>3.05</v>
+      </c>
+      <c r="BG198">
+        <v>1.29</v>
+      </c>
+      <c r="BH198">
+        <v>3.35</v>
+      </c>
+      <c r="BI198">
+        <v>1.53</v>
+      </c>
+      <c r="BJ198">
+        <v>2.41</v>
+      </c>
+      <c r="BK198">
+        <v>1.87</v>
+      </c>
+      <c r="BL198">
+        <v>1.87</v>
+      </c>
+      <c r="BM198">
+        <v>2.38</v>
+      </c>
+      <c r="BN198">
+        <v>1.54</v>
+      </c>
+      <c r="BO198">
+        <v>3.2</v>
+      </c>
+      <c r="BP198">
         <v>1.32</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
@@ -670,7 +670,7 @@
     <t>['28', '49', '75']</t>
   </si>
   <si>
-    <t>['9', '83', '86']</t>
+    <t>['9', '83', '85']</t>
   </si>
   <si>
     <t>['4', '18', '69']</t>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1250" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1256" uniqueCount="300">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -912,6 +912,9 @@
   <si>
     <t>['7']</t>
   </si>
+  <si>
+    <t>['45', '56']</t>
+  </si>
 </sst>
 </file>
 
@@ -1272,7 +1275,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP198"/>
+  <dimension ref="A1:BP199"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2842,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ8">
         <v>1.82</v>
@@ -4699,7 +4702,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ17">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -6138,7 +6141,7 @@
         <v>3</v>
       </c>
       <c r="AP24">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ24">
         <v>1.42</v>
@@ -7583,7 +7586,7 @@
         <v>1</v>
       </c>
       <c r="AQ31">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR31">
         <v>1.38</v>
@@ -10258,7 +10261,7 @@
         <v>0.5</v>
       </c>
       <c r="AP44">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ44">
         <v>0.64</v>
@@ -10876,7 +10879,7 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ47">
         <v>0.55</v>
@@ -13145,7 +13148,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ58">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR58">
         <v>1</v>
@@ -15614,7 +15617,7 @@
         <v>1</v>
       </c>
       <c r="AP70">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ70">
         <v>1.36</v>
@@ -16853,7 +16856,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ76">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR76">
         <v>1.45</v>
@@ -19734,7 +19737,7 @@
         <v>0.2</v>
       </c>
       <c r="AP90">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ90">
         <v>1.08</v>
@@ -20767,7 +20770,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ95">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR95">
         <v>2.11</v>
@@ -23030,7 +23033,7 @@
         <v>1.25</v>
       </c>
       <c r="AP106">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ106">
         <v>1</v>
@@ -24063,7 +24066,7 @@
         <v>2</v>
       </c>
       <c r="AQ111">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR111">
         <v>1.14</v>
@@ -26120,7 +26123,7 @@
         <v>1.14</v>
       </c>
       <c r="AP121">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ121">
         <v>0.91</v>
@@ -29213,7 +29216,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ136">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR136">
         <v>1.62</v>
@@ -32094,7 +32097,7 @@
         <v>1</v>
       </c>
       <c r="AP150">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ150">
         <v>1.18</v>
@@ -32715,7 +32718,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ153">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR153">
         <v>1.78</v>
@@ -33333,7 +33336,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ156">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR156">
         <v>1.52</v>
@@ -34154,7 +34157,7 @@
         <v>0.5</v>
       </c>
       <c r="AP160">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ160">
         <v>0.7</v>
@@ -37862,7 +37865,7 @@
         <v>1.33</v>
       </c>
       <c r="AP178">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ178">
         <v>1.64</v>
@@ -38483,7 +38486,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ181">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR181">
         <v>1.42</v>
@@ -42061,6 +42064,212 @@
       </c>
       <c r="BP198">
         <v>1.32</v>
+      </c>
+    </row>
+    <row r="199" spans="1:68">
+      <c r="A199" s="1">
+        <v>198</v>
+      </c>
+      <c r="B199">
+        <v>7469061</v>
+      </c>
+      <c r="C199" t="s">
+        <v>68</v>
+      </c>
+      <c r="D199" t="s">
+        <v>69</v>
+      </c>
+      <c r="E199" s="2">
+        <v>45698.69791666666</v>
+      </c>
+      <c r="F199">
+        <v>22</v>
+      </c>
+      <c r="G199" t="s">
+        <v>76</v>
+      </c>
+      <c r="H199" t="s">
+        <v>72</v>
+      </c>
+      <c r="I199">
+        <v>0</v>
+      </c>
+      <c r="J199">
+        <v>1</v>
+      </c>
+      <c r="K199">
+        <v>1</v>
+      </c>
+      <c r="L199">
+        <v>0</v>
+      </c>
+      <c r="M199">
+        <v>2</v>
+      </c>
+      <c r="N199">
+        <v>2</v>
+      </c>
+      <c r="O199" t="s">
+        <v>90</v>
+      </c>
+      <c r="P199" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q199">
+        <v>3.75</v>
+      </c>
+      <c r="R199">
+        <v>2.08</v>
+      </c>
+      <c r="S199">
+        <v>3</v>
+      </c>
+      <c r="T199">
+        <v>1.46</v>
+      </c>
+      <c r="U199">
+        <v>2.55</v>
+      </c>
+      <c r="V199">
+        <v>2.95</v>
+      </c>
+      <c r="W199">
+        <v>1.35</v>
+      </c>
+      <c r="X199">
+        <v>8.5</v>
+      </c>
+      <c r="Y199">
+        <v>1.07</v>
+      </c>
+      <c r="Z199">
+        <v>2.91</v>
+      </c>
+      <c r="AA199">
+        <v>3.45</v>
+      </c>
+      <c r="AB199">
+        <v>2.29</v>
+      </c>
+      <c r="AC199">
+        <v>1.06</v>
+      </c>
+      <c r="AD199">
+        <v>8.5</v>
+      </c>
+      <c r="AE199">
+        <v>1.35</v>
+      </c>
+      <c r="AF199">
+        <v>2.9</v>
+      </c>
+      <c r="AG199">
+        <v>2</v>
+      </c>
+      <c r="AH199">
+        <v>1.75</v>
+      </c>
+      <c r="AI199">
+        <v>1.83</v>
+      </c>
+      <c r="AJ199">
+        <v>1.88</v>
+      </c>
+      <c r="AK199">
+        <v>1.58</v>
+      </c>
+      <c r="AL199">
+        <v>1.3</v>
+      </c>
+      <c r="AM199">
+        <v>1.37</v>
+      </c>
+      <c r="AN199">
+        <v>1</v>
+      </c>
+      <c r="AO199">
+        <v>1.2</v>
+      </c>
+      <c r="AP199">
+        <v>0.92</v>
+      </c>
+      <c r="AQ199">
+        <v>1.36</v>
+      </c>
+      <c r="AR199">
+        <v>1.34</v>
+      </c>
+      <c r="AS199">
+        <v>1.31</v>
+      </c>
+      <c r="AT199">
+        <v>2.65</v>
+      </c>
+      <c r="AU199">
+        <v>0</v>
+      </c>
+      <c r="AV199">
+        <v>9</v>
+      </c>
+      <c r="AW199">
+        <v>5</v>
+      </c>
+      <c r="AX199">
+        <v>12</v>
+      </c>
+      <c r="AY199">
+        <v>5</v>
+      </c>
+      <c r="AZ199">
+        <v>21</v>
+      </c>
+      <c r="BA199">
+        <v>0</v>
+      </c>
+      <c r="BB199">
+        <v>3</v>
+      </c>
+      <c r="BC199">
+        <v>3</v>
+      </c>
+      <c r="BD199">
+        <v>2.12</v>
+      </c>
+      <c r="BE199">
+        <v>6.1</v>
+      </c>
+      <c r="BF199">
+        <v>1.9</v>
+      </c>
+      <c r="BG199">
+        <v>1.46</v>
+      </c>
+      <c r="BH199">
+        <v>2.5</v>
+      </c>
+      <c r="BI199">
+        <v>1.76</v>
+      </c>
+      <c r="BJ199">
+        <v>1.94</v>
+      </c>
+      <c r="BK199">
+        <v>2.23</v>
+      </c>
+      <c r="BL199">
+        <v>1.57</v>
+      </c>
+      <c r="BM199">
+        <v>2.9</v>
+      </c>
+      <c r="BN199">
+        <v>1.35</v>
+      </c>
+      <c r="BO199">
+        <v>3.9</v>
+      </c>
+      <c r="BP199">
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1256" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1292" uniqueCount="303">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -676,6 +676,15 @@
     <t>['4', '18', '69']</t>
   </si>
   <si>
+    <t>['70']</t>
+  </si>
+  <si>
+    <t>['46']</t>
+  </si>
+  <si>
+    <t>['5', '38', '87']</t>
+  </si>
+  <si>
     <t>['16', '45+2']</t>
   </si>
   <si>
@@ -743,9 +752,6 @@
   </si>
   <si>
     <t>['76']</t>
-  </si>
-  <si>
-    <t>['70']</t>
   </si>
   <si>
     <t>['10', '82']</t>
@@ -889,9 +895,6 @@
     <t>['27', '64']</t>
   </si>
   <si>
-    <t>['46']</t>
-  </si>
-  <si>
     <t>['77']</t>
   </si>
   <si>
@@ -914,6 +917,12 @@
   </si>
   <si>
     <t>['45', '56']</t>
+  </si>
+  <si>
+    <t>['9', '18', '31', '65']</t>
+  </si>
+  <si>
+    <t>['10', '45+3', '66', '69', '79']</t>
   </si>
 </sst>
 </file>
@@ -1275,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP199"/>
+  <dimension ref="A1:BP205"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1531,7 +1540,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q2">
         <v>2.4</v>
@@ -1815,10 +1824,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ3">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1943,7 +1952,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q4">
         <v>3.6</v>
@@ -2227,7 +2236,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ5">
         <v>1</v>
@@ -2436,7 +2445,7 @@
         <v>2</v>
       </c>
       <c r="AQ6">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2767,7 +2776,7 @@
         <v>90</v>
       </c>
       <c r="P8" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q8">
         <v>3.1</v>
@@ -3054,7 +3063,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ9">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3179,7 +3188,7 @@
         <v>94</v>
       </c>
       <c r="P10" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q10">
         <v>2.6</v>
@@ -3463,7 +3472,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ11">
         <v>1.18</v>
@@ -3797,7 +3806,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q13">
         <v>3.1</v>
@@ -4081,7 +4090,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ14">
         <v>0.4</v>
@@ -4415,7 +4424,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q16">
         <v>2.63</v>
@@ -4496,7 +4505,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ16">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4621,7 +4630,7 @@
         <v>99</v>
       </c>
       <c r="P17" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -4908,7 +4917,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ18">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5111,7 +5120,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ19">
         <v>0.64</v>
@@ -5317,7 +5326,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ20">
         <v>1.08</v>
@@ -5651,7 +5660,7 @@
         <v>103</v>
       </c>
       <c r="P22" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -5938,7 +5947,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ23">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR23">
         <v>2.13</v>
@@ -6063,7 +6072,7 @@
         <v>105</v>
       </c>
       <c r="P24" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q24">
         <v>2.62</v>
@@ -6475,7 +6484,7 @@
         <v>106</v>
       </c>
       <c r="P26" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q26">
         <v>2.83</v>
@@ -6759,10 +6768,10 @@
         <v>3</v>
       </c>
       <c r="AP27">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ27">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR27">
         <v>1.55</v>
@@ -6887,7 +6896,7 @@
         <v>108</v>
       </c>
       <c r="P28" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q28">
         <v>2.6</v>
@@ -6968,7 +6977,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ28">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR28">
         <v>1.92</v>
@@ -7789,10 +7798,10 @@
         <v>3</v>
       </c>
       <c r="AP32">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ32">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR32">
         <v>0.82</v>
@@ -8329,7 +8338,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q35">
         <v>3.3</v>
@@ -8535,7 +8544,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q36">
         <v>3.1</v>
@@ -8741,7 +8750,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q37">
         <v>3.4</v>
@@ -8947,7 +8956,7 @@
         <v>90</v>
       </c>
       <c r="P38" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q38">
         <v>3.2</v>
@@ -9025,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ38">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR38">
         <v>1.59</v>
@@ -9153,7 +9162,7 @@
         <v>90</v>
       </c>
       <c r="P39" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q39">
         <v>3.4</v>
@@ -9234,7 +9243,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ39">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR39">
         <v>0.8</v>
@@ -9565,7 +9574,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q41">
         <v>2.5</v>
@@ -9771,7 +9780,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q42">
         <v>3.25</v>
@@ -9977,7 +9986,7 @@
         <v>90</v>
       </c>
       <c r="P43" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q43">
         <v>2.75</v>
@@ -10055,10 +10064,10 @@
         <v>0.5</v>
       </c>
       <c r="AP43">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ43">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR43">
         <v>0.8</v>
@@ -10467,7 +10476,7 @@
         <v>3</v>
       </c>
       <c r="AP45">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ45">
         <v>1.18</v>
@@ -10676,7 +10685,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ46">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR46">
         <v>1.88</v>
@@ -11294,7 +11303,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ49">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR49">
         <v>1.53</v>
@@ -11703,10 +11712,10 @@
         <v>1.33</v>
       </c>
       <c r="AP51">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ51">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR51">
         <v>1.48</v>
@@ -11909,10 +11918,10 @@
         <v>1.5</v>
       </c>
       <c r="AP52">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ52">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR52">
         <v>1.34</v>
@@ -12037,7 +12046,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -12243,7 +12252,7 @@
         <v>129</v>
       </c>
       <c r="P54" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q54">
         <v>2.55</v>
@@ -12449,7 +12458,7 @@
         <v>130</v>
       </c>
       <c r="P55" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q55">
         <v>2.55</v>
@@ -12530,7 +12539,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ55">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR55">
         <v>1.98</v>
@@ -12861,7 +12870,7 @@
         <v>132</v>
       </c>
       <c r="P57" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -13067,7 +13076,7 @@
         <v>133</v>
       </c>
       <c r="P58" t="s">
-        <v>243</v>
+        <v>220</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -13273,7 +13282,7 @@
         <v>134</v>
       </c>
       <c r="P59" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q59">
         <v>2.62</v>
@@ -13479,7 +13488,7 @@
         <v>135</v>
       </c>
       <c r="P60" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q60">
         <v>2.88</v>
@@ -13557,10 +13566,10 @@
         <v>1</v>
       </c>
       <c r="AP60">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ60">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR60">
         <v>1.51</v>
@@ -13891,7 +13900,7 @@
         <v>137</v>
       </c>
       <c r="P62" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q62">
         <v>3.6</v>
@@ -13969,7 +13978,7 @@
         <v>2</v>
       </c>
       <c r="AP62">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ62">
         <v>1.82</v>
@@ -14097,7 +14106,7 @@
         <v>138</v>
       </c>
       <c r="P63" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q63">
         <v>3.75</v>
@@ -14175,7 +14184,7 @@
         <v>3</v>
       </c>
       <c r="AP63">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ63">
         <v>1.3</v>
@@ -14590,7 +14599,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ65">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR65">
         <v>1.6</v>
@@ -15127,7 +15136,7 @@
         <v>143</v>
       </c>
       <c r="P68" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15208,7 +15217,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ68">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR68">
         <v>1.95</v>
@@ -15333,7 +15342,7 @@
         <v>144</v>
       </c>
       <c r="P69" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15411,10 +15420,10 @@
         <v>1</v>
       </c>
       <c r="AP69">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ69">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR69">
         <v>1.23</v>
@@ -15539,7 +15548,7 @@
         <v>145</v>
       </c>
       <c r="P70" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q70">
         <v>3.75</v>
@@ -15620,7 +15629,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ70">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR70">
         <v>1.55</v>
@@ -15951,7 +15960,7 @@
         <v>147</v>
       </c>
       <c r="P72" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16157,7 +16166,7 @@
         <v>90</v>
       </c>
       <c r="P73" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q73">
         <v>4.33</v>
@@ -16238,7 +16247,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ73">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR73">
         <v>1</v>
@@ -16363,7 +16372,7 @@
         <v>90</v>
       </c>
       <c r="P74" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q74">
         <v>2.4</v>
@@ -16569,7 +16578,7 @@
         <v>148</v>
       </c>
       <c r="P75" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q75">
         <v>3.5</v>
@@ -16647,7 +16656,7 @@
         <v>0</v>
       </c>
       <c r="AP75">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ75">
         <v>0.4</v>
@@ -16775,7 +16784,7 @@
         <v>149</v>
       </c>
       <c r="P76" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q76">
         <v>2.88</v>
@@ -17393,7 +17402,7 @@
         <v>151</v>
       </c>
       <c r="P79" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17471,7 +17480,7 @@
         <v>0.25</v>
       </c>
       <c r="AP79">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ79">
         <v>0.64</v>
@@ -17599,7 +17608,7 @@
         <v>152</v>
       </c>
       <c r="P80" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q80">
         <v>2.05</v>
@@ -17805,7 +17814,7 @@
         <v>90</v>
       </c>
       <c r="P81" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q81">
         <v>4.33</v>
@@ -17883,7 +17892,7 @@
         <v>2.25</v>
       </c>
       <c r="AP81">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ81">
         <v>1.82</v>
@@ -18089,7 +18098,7 @@
         <v>1.33</v>
       </c>
       <c r="AP82">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ82">
         <v>1</v>
@@ -18504,7 +18513,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ84">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR84">
         <v>1.51</v>
@@ -18629,7 +18638,7 @@
         <v>90</v>
       </c>
       <c r="P85" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q85">
         <v>3.1</v>
@@ -18707,7 +18716,7 @@
         <v>0</v>
       </c>
       <c r="AP85">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ85">
         <v>0.55</v>
@@ -18835,7 +18844,7 @@
         <v>156</v>
       </c>
       <c r="P86" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -18916,7 +18925,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ86">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR86">
         <v>1.88</v>
@@ -19122,7 +19131,7 @@
         <v>1</v>
       </c>
       <c r="AQ87">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR87">
         <v>1.28</v>
@@ -19534,7 +19543,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ89">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR89">
         <v>1.72</v>
@@ -19659,7 +19668,7 @@
         <v>90</v>
       </c>
       <c r="P90" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q90">
         <v>2.38</v>
@@ -19943,7 +19952,7 @@
         <v>1</v>
       </c>
       <c r="AP91">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ91">
         <v>0.83</v>
@@ -20071,7 +20080,7 @@
         <v>160</v>
       </c>
       <c r="P92" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20355,7 +20364,7 @@
         <v>1.5</v>
       </c>
       <c r="AP93">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ93">
         <v>1.3</v>
@@ -20689,7 +20698,7 @@
         <v>162</v>
       </c>
       <c r="P95" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q95">
         <v>1.9</v>
@@ -20895,7 +20904,7 @@
         <v>163</v>
       </c>
       <c r="P96" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q96">
         <v>2.75</v>
@@ -20976,7 +20985,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ96">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR96">
         <v>1.65</v>
@@ -21179,7 +21188,7 @@
         <v>2.4</v>
       </c>
       <c r="AP97">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ97">
         <v>1.82</v>
@@ -21307,7 +21316,7 @@
         <v>90</v>
       </c>
       <c r="P98" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q98">
         <v>4.75</v>
@@ -22209,10 +22218,10 @@
         <v>1.17</v>
       </c>
       <c r="AP102">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ102">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR102">
         <v>1.45</v>
@@ -22337,7 +22346,7 @@
         <v>166</v>
       </c>
       <c r="P103" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q103">
         <v>4.2</v>
@@ -22418,7 +22427,7 @@
         <v>1</v>
       </c>
       <c r="AQ103">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR103">
         <v>1.26</v>
@@ -22543,7 +22552,7 @@
         <v>167</v>
       </c>
       <c r="P104" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q104">
         <v>2.25</v>
@@ -22624,7 +22633,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ104">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR104">
         <v>1.78</v>
@@ -23242,7 +23251,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ107">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR107">
         <v>1.74</v>
@@ -23367,7 +23376,7 @@
         <v>90</v>
       </c>
       <c r="P108" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q108">
         <v>4.5</v>
@@ -23445,7 +23454,7 @@
         <v>1.2</v>
       </c>
       <c r="AP108">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ108">
         <v>1.3</v>
@@ -23651,10 +23660,10 @@
         <v>1.4</v>
       </c>
       <c r="AP109">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ109">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR109">
         <v>1.6</v>
@@ -24191,7 +24200,7 @@
         <v>173</v>
       </c>
       <c r="P112" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q112">
         <v>3.5</v>
@@ -24475,7 +24484,7 @@
         <v>1.4</v>
       </c>
       <c r="AP113">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ113">
         <v>1.18</v>
@@ -24603,7 +24612,7 @@
         <v>90</v>
       </c>
       <c r="P114" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q114">
         <v>2.85</v>
@@ -24681,7 +24690,7 @@
         <v>0.67</v>
       </c>
       <c r="AP114">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ114">
         <v>1.08</v>
@@ -24887,7 +24896,7 @@
         <v>2.17</v>
       </c>
       <c r="AP115">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ115">
         <v>1.82</v>
@@ -25015,7 +25024,7 @@
         <v>175</v>
       </c>
       <c r="P116" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q116">
         <v>2.4</v>
@@ -25427,7 +25436,7 @@
         <v>90</v>
       </c>
       <c r="P118" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q118">
         <v>4</v>
@@ -25508,7 +25517,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ118">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR118">
         <v>0.99</v>
@@ -25711,10 +25720,10 @@
         <v>0.5</v>
       </c>
       <c r="AP119">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ119">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR119">
         <v>1.46</v>
@@ -26045,7 +26054,7 @@
         <v>178</v>
       </c>
       <c r="P121" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q121">
         <v>2.88</v>
@@ -26126,7 +26135,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ121">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR121">
         <v>1.35</v>
@@ -26535,7 +26544,7 @@
         <v>1</v>
       </c>
       <c r="AP123">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ123">
         <v>1</v>
@@ -26950,7 +26959,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ125">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR125">
         <v>1.66</v>
@@ -27359,7 +27368,7 @@
         <v>1</v>
       </c>
       <c r="AP127">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ127">
         <v>1</v>
@@ -28389,7 +28398,7 @@
         <v>1</v>
       </c>
       <c r="AP132">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ132">
         <v>1</v>
@@ -28723,7 +28732,7 @@
         <v>90</v>
       </c>
       <c r="P134" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q134">
         <v>3.2</v>
@@ -28929,7 +28938,7 @@
         <v>90</v>
       </c>
       <c r="P135" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q135">
         <v>5</v>
@@ -29007,7 +29016,7 @@
         <v>2</v>
       </c>
       <c r="AP135">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ135">
         <v>1.82</v>
@@ -29625,7 +29634,7 @@
         <v>0.14</v>
       </c>
       <c r="AP138">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ138">
         <v>0.64</v>
@@ -29831,10 +29840,10 @@
         <v>1.33</v>
       </c>
       <c r="AP139">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ139">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR139">
         <v>1.46</v>
@@ -29959,7 +29968,7 @@
         <v>188</v>
       </c>
       <c r="P140" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q140">
         <v>2.95</v>
@@ -30040,7 +30049,7 @@
         <v>1</v>
       </c>
       <c r="AQ140">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR140">
         <v>1.24</v>
@@ -30165,7 +30174,7 @@
         <v>189</v>
       </c>
       <c r="P141" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q141">
         <v>2.8</v>
@@ -30243,10 +30252,10 @@
         <v>1.38</v>
       </c>
       <c r="AP141">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ141">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR141">
         <v>1.72</v>
@@ -30655,10 +30664,10 @@
         <v>0.57</v>
       </c>
       <c r="AP143">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ143">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR143">
         <v>1.16</v>
@@ -30989,7 +30998,7 @@
         <v>192</v>
       </c>
       <c r="P145" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q145">
         <v>2.75</v>
@@ -31195,7 +31204,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q146">
         <v>3.75</v>
@@ -31401,7 +31410,7 @@
         <v>129</v>
       </c>
       <c r="P147" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q147">
         <v>3.75</v>
@@ -31479,7 +31488,7 @@
         <v>1</v>
       </c>
       <c r="AP147">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ147">
         <v>1.42</v>
@@ -31607,7 +31616,7 @@
         <v>90</v>
       </c>
       <c r="P148" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q148">
         <v>2.4</v>
@@ -31813,7 +31822,7 @@
         <v>90</v>
       </c>
       <c r="P149" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q149">
         <v>3.1</v>
@@ -31891,7 +31900,7 @@
         <v>0.88</v>
       </c>
       <c r="AP149">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ149">
         <v>1.08</v>
@@ -32225,7 +32234,7 @@
         <v>194</v>
       </c>
       <c r="P151" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q151">
         <v>1.62</v>
@@ -32306,7 +32315,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ151">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR151">
         <v>1.79</v>
@@ -32637,7 +32646,7 @@
         <v>95</v>
       </c>
       <c r="P153" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q153">
         <v>2.63</v>
@@ -32924,7 +32933,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ154">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR154">
         <v>1.27</v>
@@ -33333,7 +33342,7 @@
         <v>1</v>
       </c>
       <c r="AP156">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ156">
         <v>1.36</v>
@@ -33461,7 +33470,7 @@
         <v>197</v>
       </c>
       <c r="P157" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q157">
         <v>2.7</v>
@@ -33667,7 +33676,7 @@
         <v>96</v>
       </c>
       <c r="P158" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q158">
         <v>2.55</v>
@@ -33873,7 +33882,7 @@
         <v>198</v>
       </c>
       <c r="P159" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q159">
         <v>3.3</v>
@@ -34079,7 +34088,7 @@
         <v>90</v>
       </c>
       <c r="P160" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q160">
         <v>2.75</v>
@@ -34160,7 +34169,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ160">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR160">
         <v>1.38</v>
@@ -34984,7 +34993,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ164">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR164">
         <v>1.64</v>
@@ -35190,7 +35199,7 @@
         <v>2</v>
       </c>
       <c r="AQ165">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR165">
         <v>1.13</v>
@@ -35393,7 +35402,7 @@
         <v>0.89</v>
       </c>
       <c r="AP166">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ166">
         <v>1</v>
@@ -35521,7 +35530,7 @@
         <v>109</v>
       </c>
       <c r="P167" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q167">
         <v>3.35</v>
@@ -35599,7 +35608,7 @@
         <v>0.67</v>
       </c>
       <c r="AP167">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ167">
         <v>0.83</v>
@@ -35805,7 +35814,7 @@
         <v>0.5</v>
       </c>
       <c r="AP168">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ168">
         <v>0.4</v>
@@ -35933,7 +35942,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q169">
         <v>2.8</v>
@@ -36014,7 +36023,7 @@
         <v>1</v>
       </c>
       <c r="AQ169">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR169">
         <v>1.32</v>
@@ -36139,7 +36148,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q170">
         <v>3</v>
@@ -36426,7 +36435,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ171">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR171">
         <v>1.68</v>
@@ -36551,7 +36560,7 @@
         <v>90</v>
       </c>
       <c r="P172" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q172">
         <v>2.63</v>
@@ -36629,7 +36638,7 @@
         <v>1.22</v>
       </c>
       <c r="AP172">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ172">
         <v>1.42</v>
@@ -36757,7 +36766,7 @@
         <v>207</v>
       </c>
       <c r="P173" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q173">
         <v>2.3</v>
@@ -37662,7 +37671,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ177">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR177">
         <v>1.6</v>
@@ -37787,7 +37796,7 @@
         <v>90</v>
       </c>
       <c r="P178" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q178">
         <v>3.25</v>
@@ -38199,7 +38208,7 @@
         <v>212</v>
       </c>
       <c r="P180" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q180">
         <v>2.2</v>
@@ -38405,7 +38414,7 @@
         <v>90</v>
       </c>
       <c r="P181" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q181">
         <v>3.25</v>
@@ -38692,7 +38701,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ182">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR182">
         <v>1.62</v>
@@ -38898,7 +38907,7 @@
         <v>2</v>
       </c>
       <c r="AQ183">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR183">
         <v>1.2</v>
@@ -39101,7 +39110,7 @@
         <v>1.4</v>
       </c>
       <c r="AP184">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ184">
         <v>1.42</v>
@@ -39229,7 +39238,7 @@
         <v>214</v>
       </c>
       <c r="P185" t="s">
-        <v>291</v>
+        <v>221</v>
       </c>
       <c r="Q185">
         <v>2.6</v>
@@ -39307,10 +39316,10 @@
         <v>1.5</v>
       </c>
       <c r="AP185">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ185">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR185">
         <v>1.51</v>
@@ -39641,7 +39650,7 @@
         <v>90</v>
       </c>
       <c r="P187" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q187">
         <v>2.55</v>
@@ -39847,7 +39856,7 @@
         <v>215</v>
       </c>
       <c r="P188" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q188">
         <v>4.5</v>
@@ -39925,10 +39934,10 @@
         <v>1.2</v>
       </c>
       <c r="AP188">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ188">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR188">
         <v>1.26</v>
@@ -40131,7 +40140,7 @@
         <v>0.44</v>
       </c>
       <c r="AP189">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ189">
         <v>0.4</v>
@@ -40259,7 +40268,7 @@
         <v>90</v>
       </c>
       <c r="P190" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q190">
         <v>3.3</v>
@@ -40465,7 +40474,7 @@
         <v>90</v>
       </c>
       <c r="P191" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q191">
         <v>2.75</v>
@@ -40671,7 +40680,7 @@
         <v>90</v>
       </c>
       <c r="P192" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q192">
         <v>3.25</v>
@@ -41289,7 +41298,7 @@
         <v>214</v>
       </c>
       <c r="P195" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q195">
         <v>4.75</v>
@@ -41495,7 +41504,7 @@
         <v>90</v>
       </c>
       <c r="P196" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q196">
         <v>3.65</v>
@@ -41573,7 +41582,7 @@
         <v>1.5</v>
       </c>
       <c r="AP196">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ196">
         <v>1.64</v>
@@ -41701,7 +41710,7 @@
         <v>218</v>
       </c>
       <c r="P197" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q197">
         <v>1.94</v>
@@ -42113,7 +42122,7 @@
         <v>90</v>
       </c>
       <c r="P199" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q199">
         <v>3.75</v>
@@ -42270,6 +42279,1242 @@
       </c>
       <c r="BP199">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="200" spans="1:68">
+      <c r="A200" s="1">
+        <v>199</v>
+      </c>
+      <c r="B200">
+        <v>7469072</v>
+      </c>
+      <c r="C200" t="s">
+        <v>68</v>
+      </c>
+      <c r="D200" t="s">
+        <v>69</v>
+      </c>
+      <c r="E200" s="2">
+        <v>45702.66666666666</v>
+      </c>
+      <c r="F200">
+        <v>23</v>
+      </c>
+      <c r="G200" t="s">
+        <v>70</v>
+      </c>
+      <c r="H200" t="s">
+        <v>83</v>
+      </c>
+      <c r="I200">
+        <v>0</v>
+      </c>
+      <c r="J200">
+        <v>1</v>
+      </c>
+      <c r="K200">
+        <v>1</v>
+      </c>
+      <c r="L200">
+        <v>1</v>
+      </c>
+      <c r="M200">
+        <v>1</v>
+      </c>
+      <c r="N200">
+        <v>2</v>
+      </c>
+      <c r="O200" t="s">
+        <v>220</v>
+      </c>
+      <c r="P200" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q200">
+        <v>3.55</v>
+      </c>
+      <c r="R200">
+        <v>1.93</v>
+      </c>
+      <c r="S200">
+        <v>3.1</v>
+      </c>
+      <c r="T200">
+        <v>1.48</v>
+      </c>
+      <c r="U200">
+        <v>2.45</v>
+      </c>
+      <c r="V200">
+        <v>3.2</v>
+      </c>
+      <c r="W200">
+        <v>1.3</v>
+      </c>
+      <c r="X200">
+        <v>10.25</v>
+      </c>
+      <c r="Y200">
+        <v>1.02</v>
+      </c>
+      <c r="Z200">
+        <v>2.71</v>
+      </c>
+      <c r="AA200">
+        <v>3.02</v>
+      </c>
+      <c r="AB200">
+        <v>2.71</v>
+      </c>
+      <c r="AC200">
+        <v>1.09</v>
+      </c>
+      <c r="AD200">
+        <v>7</v>
+      </c>
+      <c r="AE200">
+        <v>1.44</v>
+      </c>
+      <c r="AF200">
+        <v>2.75</v>
+      </c>
+      <c r="AG200">
+        <v>2.2</v>
+      </c>
+      <c r="AH200">
+        <v>1.55</v>
+      </c>
+      <c r="AI200">
+        <v>1.9</v>
+      </c>
+      <c r="AJ200">
+        <v>1.77</v>
+      </c>
+      <c r="AK200">
+        <v>1.5</v>
+      </c>
+      <c r="AL200">
+        <v>1.3</v>
+      </c>
+      <c r="AM200">
+        <v>1.38</v>
+      </c>
+      <c r="AN200">
+        <v>1</v>
+      </c>
+      <c r="AO200">
+        <v>1</v>
+      </c>
+      <c r="AP200">
+        <v>1</v>
+      </c>
+      <c r="AQ200">
+        <v>1</v>
+      </c>
+      <c r="AR200">
+        <v>1.39</v>
+      </c>
+      <c r="AS200">
+        <v>1.43</v>
+      </c>
+      <c r="AT200">
+        <v>2.82</v>
+      </c>
+      <c r="AU200">
+        <v>4</v>
+      </c>
+      <c r="AV200">
+        <v>5</v>
+      </c>
+      <c r="AW200">
+        <v>10</v>
+      </c>
+      <c r="AX200">
+        <v>7</v>
+      </c>
+      <c r="AY200">
+        <v>14</v>
+      </c>
+      <c r="AZ200">
+        <v>12</v>
+      </c>
+      <c r="BA200">
+        <v>7</v>
+      </c>
+      <c r="BB200">
+        <v>3</v>
+      </c>
+      <c r="BC200">
+        <v>10</v>
+      </c>
+      <c r="BD200">
+        <v>2.08</v>
+      </c>
+      <c r="BE200">
+        <v>6.25</v>
+      </c>
+      <c r="BF200">
+        <v>1.93</v>
+      </c>
+      <c r="BG200">
+        <v>1.5</v>
+      </c>
+      <c r="BH200">
+        <v>2.38</v>
+      </c>
+      <c r="BI200">
+        <v>1.84</v>
+      </c>
+      <c r="BJ200">
+        <v>1.84</v>
+      </c>
+      <c r="BK200">
+        <v>2.35</v>
+      </c>
+      <c r="BL200">
+        <v>1.5</v>
+      </c>
+      <c r="BM200">
+        <v>3.05</v>
+      </c>
+      <c r="BN200">
+        <v>1.3</v>
+      </c>
+      <c r="BO200">
+        <v>4.1</v>
+      </c>
+      <c r="BP200">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="201" spans="1:68">
+      <c r="A201" s="1">
+        <v>200</v>
+      </c>
+      <c r="B201">
+        <v>7469070</v>
+      </c>
+      <c r="C201" t="s">
+        <v>68</v>
+      </c>
+      <c r="D201" t="s">
+        <v>69</v>
+      </c>
+      <c r="E201" s="2">
+        <v>45702.66666666666</v>
+      </c>
+      <c r="F201">
+        <v>23</v>
+      </c>
+      <c r="G201" t="s">
+        <v>79</v>
+      </c>
+      <c r="H201" t="s">
+        <v>86</v>
+      </c>
+      <c r="I201">
+        <v>0</v>
+      </c>
+      <c r="J201">
+        <v>0</v>
+      </c>
+      <c r="K201">
+        <v>0</v>
+      </c>
+      <c r="L201">
+        <v>0</v>
+      </c>
+      <c r="M201">
+        <v>1</v>
+      </c>
+      <c r="N201">
+        <v>1</v>
+      </c>
+      <c r="O201" t="s">
+        <v>90</v>
+      </c>
+      <c r="P201" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q201">
+        <v>4.4</v>
+      </c>
+      <c r="R201">
+        <v>2.14</v>
+      </c>
+      <c r="S201">
+        <v>2.55</v>
+      </c>
+      <c r="T201">
+        <v>1.43</v>
+      </c>
+      <c r="U201">
+        <v>2.65</v>
+      </c>
+      <c r="V201">
+        <v>2.85</v>
+      </c>
+      <c r="W201">
+        <v>1.37</v>
+      </c>
+      <c r="X201">
+        <v>8.4</v>
+      </c>
+      <c r="Y201">
+        <v>1.04</v>
+      </c>
+      <c r="Z201">
+        <v>3.68</v>
+      </c>
+      <c r="AA201">
+        <v>2.98</v>
+      </c>
+      <c r="AB201">
+        <v>2.16</v>
+      </c>
+      <c r="AC201">
+        <v>1.07</v>
+      </c>
+      <c r="AD201">
+        <v>8</v>
+      </c>
+      <c r="AE201">
+        <v>1.33</v>
+      </c>
+      <c r="AF201">
+        <v>3.05</v>
+      </c>
+      <c r="AG201">
+        <v>1.95</v>
+      </c>
+      <c r="AH201">
+        <v>1.79</v>
+      </c>
+      <c r="AI201">
+        <v>1.8</v>
+      </c>
+      <c r="AJ201">
+        <v>1.91</v>
+      </c>
+      <c r="AK201">
+        <v>1.71</v>
+      </c>
+      <c r="AL201">
+        <v>1.32</v>
+      </c>
+      <c r="AM201">
+        <v>1.25</v>
+      </c>
+      <c r="AN201">
+        <v>1.4</v>
+      </c>
+      <c r="AO201">
+        <v>1.36</v>
+      </c>
+      <c r="AP201">
+        <v>1.27</v>
+      </c>
+      <c r="AQ201">
+        <v>1.5</v>
+      </c>
+      <c r="AR201">
+        <v>1.74</v>
+      </c>
+      <c r="AS201">
+        <v>1.53</v>
+      </c>
+      <c r="AT201">
+        <v>3.27</v>
+      </c>
+      <c r="AU201">
+        <v>7</v>
+      </c>
+      <c r="AV201">
+        <v>6</v>
+      </c>
+      <c r="AW201">
+        <v>7</v>
+      </c>
+      <c r="AX201">
+        <v>6</v>
+      </c>
+      <c r="AY201">
+        <v>14</v>
+      </c>
+      <c r="AZ201">
+        <v>12</v>
+      </c>
+      <c r="BA201">
+        <v>4</v>
+      </c>
+      <c r="BB201">
+        <v>4</v>
+      </c>
+      <c r="BC201">
+        <v>8</v>
+      </c>
+      <c r="BD201">
+        <v>2.43</v>
+      </c>
+      <c r="BE201">
+        <v>6.4</v>
+      </c>
+      <c r="BF201">
+        <v>1.68</v>
+      </c>
+      <c r="BG201">
+        <v>1.43</v>
+      </c>
+      <c r="BH201">
+        <v>2.6</v>
+      </c>
+      <c r="BI201">
+        <v>1.72</v>
+      </c>
+      <c r="BJ201">
+        <v>1.98</v>
+      </c>
+      <c r="BK201">
+        <v>2.12</v>
+      </c>
+      <c r="BL201">
+        <v>1.63</v>
+      </c>
+      <c r="BM201">
+        <v>2.75</v>
+      </c>
+      <c r="BN201">
+        <v>1.38</v>
+      </c>
+      <c r="BO201">
+        <v>3.65</v>
+      </c>
+      <c r="BP201">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="202" spans="1:68">
+      <c r="A202" s="1">
+        <v>201</v>
+      </c>
+      <c r="B202">
+        <v>7469068</v>
+      </c>
+      <c r="C202" t="s">
+        <v>68</v>
+      </c>
+      <c r="D202" t="s">
+        <v>69</v>
+      </c>
+      <c r="E202" s="2">
+        <v>45702.66666666666</v>
+      </c>
+      <c r="F202">
+        <v>23</v>
+      </c>
+      <c r="G202" t="s">
+        <v>87</v>
+      </c>
+      <c r="H202" t="s">
+        <v>77</v>
+      </c>
+      <c r="I202">
+        <v>0</v>
+      </c>
+      <c r="J202">
+        <v>0</v>
+      </c>
+      <c r="K202">
+        <v>0</v>
+      </c>
+      <c r="L202">
+        <v>1</v>
+      </c>
+      <c r="M202">
+        <v>0</v>
+      </c>
+      <c r="N202">
+        <v>1</v>
+      </c>
+      <c r="O202" t="s">
+        <v>221</v>
+      </c>
+      <c r="P202" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q202">
+        <v>2.24</v>
+      </c>
+      <c r="R202">
+        <v>2.26</v>
+      </c>
+      <c r="S202">
+        <v>5</v>
+      </c>
+      <c r="T202">
+        <v>1.38</v>
+      </c>
+      <c r="U202">
+        <v>2.85</v>
+      </c>
+      <c r="V202">
+        <v>2.65</v>
+      </c>
+      <c r="W202">
+        <v>1.42</v>
+      </c>
+      <c r="X202">
+        <v>6.3</v>
+      </c>
+      <c r="Y202">
+        <v>1.09</v>
+      </c>
+      <c r="Z202">
+        <v>1.64</v>
+      </c>
+      <c r="AA202">
+        <v>3.83</v>
+      </c>
+      <c r="AB202">
+        <v>5</v>
+      </c>
+      <c r="AC202">
+        <v>1.05</v>
+      </c>
+      <c r="AD202">
+        <v>9.5</v>
+      </c>
+      <c r="AE202">
+        <v>1.28</v>
+      </c>
+      <c r="AF202">
+        <v>3.3</v>
+      </c>
+      <c r="AG202">
+        <v>1.85</v>
+      </c>
+      <c r="AH202">
+        <v>1.89</v>
+      </c>
+      <c r="AI202">
+        <v>1.83</v>
+      </c>
+      <c r="AJ202">
+        <v>1.88</v>
+      </c>
+      <c r="AK202">
+        <v>1.19</v>
+      </c>
+      <c r="AL202">
+        <v>1.24</v>
+      </c>
+      <c r="AM202">
+        <v>2.04</v>
+      </c>
+      <c r="AN202">
+        <v>1.1</v>
+      </c>
+      <c r="AO202">
+        <v>1.4</v>
+      </c>
+      <c r="AP202">
+        <v>1.27</v>
+      </c>
+      <c r="AQ202">
+        <v>1.27</v>
+      </c>
+      <c r="AR202">
+        <v>1.2</v>
+      </c>
+      <c r="AS202">
+        <v>1.11</v>
+      </c>
+      <c r="AT202">
+        <v>2.31</v>
+      </c>
+      <c r="AU202">
+        <v>10</v>
+      </c>
+      <c r="AV202">
+        <v>3</v>
+      </c>
+      <c r="AW202">
+        <v>7</v>
+      </c>
+      <c r="AX202">
+        <v>7</v>
+      </c>
+      <c r="AY202">
+        <v>17</v>
+      </c>
+      <c r="AZ202">
+        <v>10</v>
+      </c>
+      <c r="BA202">
+        <v>3</v>
+      </c>
+      <c r="BB202">
+        <v>4</v>
+      </c>
+      <c r="BC202">
+        <v>7</v>
+      </c>
+      <c r="BD202">
+        <v>1.52</v>
+      </c>
+      <c r="BE202">
+        <v>6.75</v>
+      </c>
+      <c r="BF202">
+        <v>2.8</v>
+      </c>
+      <c r="BG202">
+        <v>1.46</v>
+      </c>
+      <c r="BH202">
+        <v>2.5</v>
+      </c>
+      <c r="BI202">
+        <v>1.75</v>
+      </c>
+      <c r="BJ202">
+        <v>1.95</v>
+      </c>
+      <c r="BK202">
+        <v>2.18</v>
+      </c>
+      <c r="BL202">
+        <v>1.58</v>
+      </c>
+      <c r="BM202">
+        <v>2.8</v>
+      </c>
+      <c r="BN202">
+        <v>1.36</v>
+      </c>
+      <c r="BO202">
+        <v>3.8</v>
+      </c>
+      <c r="BP202">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="203" spans="1:68">
+      <c r="A203" s="1">
+        <v>202</v>
+      </c>
+      <c r="B203">
+        <v>7469069</v>
+      </c>
+      <c r="C203" t="s">
+        <v>68</v>
+      </c>
+      <c r="D203" t="s">
+        <v>69</v>
+      </c>
+      <c r="E203" s="2">
+        <v>45702.66666666666</v>
+      </c>
+      <c r="F203">
+        <v>23</v>
+      </c>
+      <c r="G203" t="s">
+        <v>71</v>
+      </c>
+      <c r="H203" t="s">
+        <v>80</v>
+      </c>
+      <c r="I203">
+        <v>2</v>
+      </c>
+      <c r="J203">
+        <v>0</v>
+      </c>
+      <c r="K203">
+        <v>2</v>
+      </c>
+      <c r="L203">
+        <v>3</v>
+      </c>
+      <c r="M203">
+        <v>0</v>
+      </c>
+      <c r="N203">
+        <v>3</v>
+      </c>
+      <c r="O203" t="s">
+        <v>222</v>
+      </c>
+      <c r="P203" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q203">
+        <v>3.45</v>
+      </c>
+      <c r="R203">
+        <v>1.9</v>
+      </c>
+      <c r="S203">
+        <v>3.8</v>
+      </c>
+      <c r="T203">
+        <v>1.6</v>
+      </c>
+      <c r="U203">
+        <v>2.22</v>
+      </c>
+      <c r="V203">
+        <v>3.65</v>
+      </c>
+      <c r="W203">
+        <v>1.24</v>
+      </c>
+      <c r="X203">
+        <v>11.5</v>
+      </c>
+      <c r="Y203">
+        <v>1.01</v>
+      </c>
+      <c r="Z203">
+        <v>2.81</v>
+      </c>
+      <c r="AA203">
+        <v>2.84</v>
+      </c>
+      <c r="AB203">
+        <v>2.76</v>
+      </c>
+      <c r="AC203">
+        <v>1.12</v>
+      </c>
+      <c r="AD203">
+        <v>6</v>
+      </c>
+      <c r="AE203">
+        <v>1.48</v>
+      </c>
+      <c r="AF203">
+        <v>2.37</v>
+      </c>
+      <c r="AG203">
+        <v>2.56</v>
+      </c>
+      <c r="AH203">
+        <v>1.45</v>
+      </c>
+      <c r="AI203">
+        <v>2.12</v>
+      </c>
+      <c r="AJ203">
+        <v>1.66</v>
+      </c>
+      <c r="AK203">
+        <v>1.38</v>
+      </c>
+      <c r="AL203">
+        <v>1.38</v>
+      </c>
+      <c r="AM203">
+        <v>1.45</v>
+      </c>
+      <c r="AN203">
+        <v>1.55</v>
+      </c>
+      <c r="AO203">
+        <v>1.45</v>
+      </c>
+      <c r="AP203">
+        <v>1.67</v>
+      </c>
+      <c r="AQ203">
+        <v>1.33</v>
+      </c>
+      <c r="AR203">
+        <v>1.24</v>
+      </c>
+      <c r="AS203">
+        <v>1.1</v>
+      </c>
+      <c r="AT203">
+        <v>2.34</v>
+      </c>
+      <c r="AU203">
+        <v>6</v>
+      </c>
+      <c r="AV203">
+        <v>3</v>
+      </c>
+      <c r="AW203">
+        <v>5</v>
+      </c>
+      <c r="AX203">
+        <v>10</v>
+      </c>
+      <c r="AY203">
+        <v>11</v>
+      </c>
+      <c r="AZ203">
+        <v>13</v>
+      </c>
+      <c r="BA203">
+        <v>4</v>
+      </c>
+      <c r="BB203">
+        <v>5</v>
+      </c>
+      <c r="BC203">
+        <v>9</v>
+      </c>
+      <c r="BD203">
+        <v>1.97</v>
+      </c>
+      <c r="BE203">
+        <v>6.1</v>
+      </c>
+      <c r="BF203">
+        <v>2.07</v>
+      </c>
+      <c r="BG203">
+        <v>1.55</v>
+      </c>
+      <c r="BH203">
+        <v>2.28</v>
+      </c>
+      <c r="BI203">
+        <v>1.93</v>
+      </c>
+      <c r="BJ203">
+        <v>1.77</v>
+      </c>
+      <c r="BK203">
+        <v>2.48</v>
+      </c>
+      <c r="BL203">
+        <v>1.47</v>
+      </c>
+      <c r="BM203">
+        <v>3.3</v>
+      </c>
+      <c r="BN203">
+        <v>1.28</v>
+      </c>
+      <c r="BO203">
+        <v>4.4</v>
+      </c>
+      <c r="BP203">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="204" spans="1:68">
+      <c r="A204" s="1">
+        <v>203</v>
+      </c>
+      <c r="B204">
+        <v>7469065</v>
+      </c>
+      <c r="C204" t="s">
+        <v>68</v>
+      </c>
+      <c r="D204" t="s">
+        <v>69</v>
+      </c>
+      <c r="E204" s="2">
+        <v>45702.66666666666</v>
+      </c>
+      <c r="F204">
+        <v>23</v>
+      </c>
+      <c r="G204" t="s">
+        <v>73</v>
+      </c>
+      <c r="H204" t="s">
+        <v>74</v>
+      </c>
+      <c r="I204">
+        <v>1</v>
+      </c>
+      <c r="J204">
+        <v>3</v>
+      </c>
+      <c r="K204">
+        <v>4</v>
+      </c>
+      <c r="L204">
+        <v>1</v>
+      </c>
+      <c r="M204">
+        <v>4</v>
+      </c>
+      <c r="N204">
+        <v>5</v>
+      </c>
+      <c r="O204" t="s">
+        <v>160</v>
+      </c>
+      <c r="P204" t="s">
+        <v>301</v>
+      </c>
+      <c r="Q204">
+        <v>3</v>
+      </c>
+      <c r="R204">
+        <v>2.03</v>
+      </c>
+      <c r="S204">
+        <v>3.95</v>
+      </c>
+      <c r="T204">
+        <v>1.5</v>
+      </c>
+      <c r="U204">
+        <v>2.45</v>
+      </c>
+      <c r="V204">
+        <v>3.15</v>
+      </c>
+      <c r="W204">
+        <v>1.32</v>
+      </c>
+      <c r="X204">
+        <v>9.4</v>
+      </c>
+      <c r="Y204">
+        <v>1.02</v>
+      </c>
+      <c r="Z204">
+        <v>2.38</v>
+      </c>
+      <c r="AA204">
+        <v>2.79</v>
+      </c>
+      <c r="AB204">
+        <v>3.45</v>
+      </c>
+      <c r="AC204">
+        <v>1.1</v>
+      </c>
+      <c r="AD204">
+        <v>6.5</v>
+      </c>
+      <c r="AE204">
+        <v>1.4</v>
+      </c>
+      <c r="AF204">
+        <v>2.7</v>
+      </c>
+      <c r="AG204">
+        <v>2.15</v>
+      </c>
+      <c r="AH204">
+        <v>1.57</v>
+      </c>
+      <c r="AI204">
+        <v>1.89</v>
+      </c>
+      <c r="AJ204">
+        <v>1.83</v>
+      </c>
+      <c r="AK204">
+        <v>1.31</v>
+      </c>
+      <c r="AL204">
+        <v>1.36</v>
+      </c>
+      <c r="AM204">
+        <v>1.55</v>
+      </c>
+      <c r="AN204">
+        <v>2.09</v>
+      </c>
+      <c r="AO204">
+        <v>0.7</v>
+      </c>
+      <c r="AP204">
+        <v>1.92</v>
+      </c>
+      <c r="AQ204">
+        <v>0.91</v>
+      </c>
+      <c r="AR204">
+        <v>1.59</v>
+      </c>
+      <c r="AS204">
+        <v>1.41</v>
+      </c>
+      <c r="AT204">
+        <v>3</v>
+      </c>
+      <c r="AU204">
+        <v>9</v>
+      </c>
+      <c r="AV204">
+        <v>7</v>
+      </c>
+      <c r="AW204">
+        <v>7</v>
+      </c>
+      <c r="AX204">
+        <v>5</v>
+      </c>
+      <c r="AY204">
+        <v>16</v>
+      </c>
+      <c r="AZ204">
+        <v>12</v>
+      </c>
+      <c r="BA204">
+        <v>8</v>
+      </c>
+      <c r="BB204">
+        <v>5</v>
+      </c>
+      <c r="BC204">
+        <v>13</v>
+      </c>
+      <c r="BD204">
+        <v>1.76</v>
+      </c>
+      <c r="BE204">
+        <v>6.1</v>
+      </c>
+      <c r="BF204">
+        <v>2.32</v>
+      </c>
+      <c r="BG204">
+        <v>1.52</v>
+      </c>
+      <c r="BH204">
+        <v>2.33</v>
+      </c>
+      <c r="BI204">
+        <v>1.88</v>
+      </c>
+      <c r="BJ204">
+        <v>1.82</v>
+      </c>
+      <c r="BK204">
+        <v>2.4</v>
+      </c>
+      <c r="BL204">
+        <v>1.5</v>
+      </c>
+      <c r="BM204">
+        <v>3.15</v>
+      </c>
+      <c r="BN204">
+        <v>1.3</v>
+      </c>
+      <c r="BO204">
+        <v>4.3</v>
+      </c>
+      <c r="BP204">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="205" spans="1:68">
+      <c r="A205" s="1">
+        <v>204</v>
+      </c>
+      <c r="B205">
+        <v>7469064</v>
+      </c>
+      <c r="C205" t="s">
+        <v>68</v>
+      </c>
+      <c r="D205" t="s">
+        <v>69</v>
+      </c>
+      <c r="E205" s="2">
+        <v>45702.66666666666</v>
+      </c>
+      <c r="F205">
+        <v>23</v>
+      </c>
+      <c r="G205" t="s">
+        <v>82</v>
+      </c>
+      <c r="H205" t="s">
+        <v>81</v>
+      </c>
+      <c r="I205">
+        <v>0</v>
+      </c>
+      <c r="J205">
+        <v>2</v>
+      </c>
+      <c r="K205">
+        <v>2</v>
+      </c>
+      <c r="L205">
+        <v>0</v>
+      </c>
+      <c r="M205">
+        <v>5</v>
+      </c>
+      <c r="N205">
+        <v>5</v>
+      </c>
+      <c r="O205" t="s">
+        <v>90</v>
+      </c>
+      <c r="P205" t="s">
+        <v>302</v>
+      </c>
+      <c r="Q205">
+        <v>2.75</v>
+      </c>
+      <c r="R205">
+        <v>2.32</v>
+      </c>
+      <c r="S205">
+        <v>3.5</v>
+      </c>
+      <c r="T205">
+        <v>1.32</v>
+      </c>
+      <c r="U205">
+        <v>3.1</v>
+      </c>
+      <c r="V205">
+        <v>2.39</v>
+      </c>
+      <c r="W205">
+        <v>1.52</v>
+      </c>
+      <c r="X205">
+        <v>5.35</v>
+      </c>
+      <c r="Y205">
+        <v>1.12</v>
+      </c>
+      <c r="Z205">
+        <v>2.45</v>
+      </c>
+      <c r="AA205">
+        <v>3.01</v>
+      </c>
+      <c r="AB205">
+        <v>3.05</v>
+      </c>
+      <c r="AC205">
+        <v>1.05</v>
+      </c>
+      <c r="AD205">
+        <v>9.5</v>
+      </c>
+      <c r="AE205">
+        <v>1.21</v>
+      </c>
+      <c r="AF205">
+        <v>4.1</v>
+      </c>
+      <c r="AG205">
+        <v>1.82</v>
+      </c>
+      <c r="AH205">
+        <v>1.92</v>
+      </c>
+      <c r="AI205">
+        <v>1.54</v>
+      </c>
+      <c r="AJ205">
+        <v>2.33</v>
+      </c>
+      <c r="AK205">
+        <v>1.35</v>
+      </c>
+      <c r="AL205">
+        <v>1.3</v>
+      </c>
+      <c r="AM205">
+        <v>1.59</v>
+      </c>
+      <c r="AN205">
+        <v>1.9</v>
+      </c>
+      <c r="AO205">
+        <v>0.91</v>
+      </c>
+      <c r="AP205">
+        <v>1.73</v>
+      </c>
+      <c r="AQ205">
+        <v>1.08</v>
+      </c>
+      <c r="AR205">
+        <v>1.62</v>
+      </c>
+      <c r="AS205">
+        <v>1.42</v>
+      </c>
+      <c r="AT205">
+        <v>3.04</v>
+      </c>
+      <c r="AU205">
+        <v>5</v>
+      </c>
+      <c r="AV205">
+        <v>10</v>
+      </c>
+      <c r="AW205">
+        <v>10</v>
+      </c>
+      <c r="AX205">
+        <v>6</v>
+      </c>
+      <c r="AY205">
+        <v>15</v>
+      </c>
+      <c r="AZ205">
+        <v>16</v>
+      </c>
+      <c r="BA205">
+        <v>5</v>
+      </c>
+      <c r="BB205">
+        <v>3</v>
+      </c>
+      <c r="BC205">
+        <v>8</v>
+      </c>
+      <c r="BD205">
+        <v>1.84</v>
+      </c>
+      <c r="BE205">
+        <v>6.4</v>
+      </c>
+      <c r="BF205">
+        <v>2.17</v>
+      </c>
+      <c r="BG205">
+        <v>1.34</v>
+      </c>
+      <c r="BH205">
+        <v>2.9</v>
+      </c>
+      <c r="BI205">
+        <v>1.58</v>
+      </c>
+      <c r="BJ205">
+        <v>2.18</v>
+      </c>
+      <c r="BK205">
+        <v>1.97</v>
+      </c>
+      <c r="BL205">
+        <v>1.74</v>
+      </c>
+      <c r="BM205">
+        <v>2.48</v>
+      </c>
+      <c r="BN205">
+        <v>1.47</v>
+      </c>
+      <c r="BO205">
+        <v>3.2</v>
+      </c>
+      <c r="BP205">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1292" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1304" uniqueCount="304">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -919,10 +919,13 @@
     <t>['45', '56']</t>
   </si>
   <si>
-    <t>['9', '18', '31', '65']</t>
+    <t>['9', '19', '31', '65']</t>
   </si>
   <si>
     <t>['10', '45+3', '66', '69', '79']</t>
+  </si>
+  <si>
+    <t>['28', '87', '90+3']</t>
   </si>
 </sst>
 </file>
@@ -1284,7 +1287,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP205"/>
+  <dimension ref="A1:BP207"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2030,7 +2033,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ4">
         <v>1.42</v>
@@ -2648,7 +2651,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ7">
         <v>1.08</v>
@@ -2857,7 +2860,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ8">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3887,7 +3890,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ13">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -5535,7 +5538,7 @@
         <v>1</v>
       </c>
       <c r="AQ21">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR21">
         <v>1.81</v>
@@ -5738,7 +5741,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ22">
         <v>1</v>
@@ -5944,7 +5947,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ23">
         <v>1.08</v>
@@ -8625,7 +8628,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ36">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR36">
         <v>1.66</v>
@@ -9449,7 +9452,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ40">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR40">
         <v>1.41</v>
@@ -9652,7 +9655,7 @@
         <v>2</v>
       </c>
       <c r="AP41">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ41">
         <v>1.42</v>
@@ -9858,7 +9861,7 @@
         <v>1</v>
       </c>
       <c r="AP42">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ42">
         <v>0.83</v>
@@ -12124,7 +12127,7 @@
         <v>2</v>
       </c>
       <c r="AP53">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ53">
         <v>1</v>
@@ -13981,7 +13984,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ62">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR62">
         <v>1.16</v>
@@ -14187,7 +14190,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ63">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR63">
         <v>1.33</v>
@@ -14390,7 +14393,7 @@
         <v>0</v>
       </c>
       <c r="AP64">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ64">
         <v>0.4</v>
@@ -15008,7 +15011,7 @@
         <v>0.25</v>
       </c>
       <c r="AP67">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ67">
         <v>1.08</v>
@@ -16450,7 +16453,7 @@
         <v>0.5</v>
       </c>
       <c r="AP74">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ74">
         <v>0.83</v>
@@ -17071,7 +17074,7 @@
         <v>2</v>
       </c>
       <c r="AQ77">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR77">
         <v>1.29</v>
@@ -17895,7 +17898,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ81">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR81">
         <v>1.22</v>
@@ -18304,7 +18307,7 @@
         <v>0.8</v>
       </c>
       <c r="AP83">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ83">
         <v>1</v>
@@ -20367,7 +20370,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ93">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR93">
         <v>1.43</v>
@@ -21191,7 +21194,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ97">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR97">
         <v>1.69</v>
@@ -21600,7 +21603,7 @@
         <v>0.2</v>
       </c>
       <c r="AP99">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ99">
         <v>0.64</v>
@@ -21806,7 +21809,7 @@
         <v>0.6</v>
       </c>
       <c r="AP100">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ100">
         <v>0.55</v>
@@ -23248,7 +23251,7 @@
         <v>0.6</v>
       </c>
       <c r="AP107">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ107">
         <v>0.91</v>
@@ -23457,7 +23460,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ108">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR108">
         <v>1.07</v>
@@ -24899,7 +24902,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ115">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR115">
         <v>1.51</v>
@@ -25929,7 +25932,7 @@
         <v>1</v>
       </c>
       <c r="AQ120">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR120">
         <v>1.24</v>
@@ -26338,7 +26341,7 @@
         <v>0.5</v>
       </c>
       <c r="AP122">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ122">
         <v>0.55</v>
@@ -27162,7 +27165,7 @@
         <v>0.17</v>
       </c>
       <c r="AP126">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ126">
         <v>0.64</v>
@@ -29019,7 +29022,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ135">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR135">
         <v>1.14</v>
@@ -30461,7 +30464,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ142">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR142">
         <v>1.78</v>
@@ -30873,7 +30876,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ144">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR144">
         <v>1.43</v>
@@ -31076,7 +31079,7 @@
         <v>0.57</v>
       </c>
       <c r="AP145">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ145">
         <v>0.4</v>
@@ -32724,7 +32727,7 @@
         <v>1</v>
       </c>
       <c r="AP153">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ153">
         <v>1.36</v>
@@ -34787,7 +34790,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ163">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR163">
         <v>1.75</v>
@@ -34990,7 +34993,7 @@
         <v>1.11</v>
       </c>
       <c r="AP164">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ164">
         <v>1.08</v>
@@ -36229,7 +36232,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ170">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR170">
         <v>1.64</v>
@@ -36432,7 +36435,7 @@
         <v>1</v>
       </c>
       <c r="AP171">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ171">
         <v>1.5</v>
@@ -38698,7 +38701,7 @@
         <v>1.22</v>
       </c>
       <c r="AP182">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ182">
         <v>1.27</v>
@@ -39525,7 +39528,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ186">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR186">
         <v>1.69</v>
@@ -40346,10 +40349,10 @@
         <v>1.7</v>
       </c>
       <c r="AP190">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ190">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR190">
         <v>1.63</v>
@@ -43515,6 +43518,418 @@
       </c>
       <c r="BP205">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="206" spans="1:68">
+      <c r="A206" s="1">
+        <v>205</v>
+      </c>
+      <c r="B206">
+        <v>7469067</v>
+      </c>
+      <c r="C206" t="s">
+        <v>68</v>
+      </c>
+      <c r="D206" t="s">
+        <v>69</v>
+      </c>
+      <c r="E206" s="2">
+        <v>45703.41666666666</v>
+      </c>
+      <c r="F206">
+        <v>23</v>
+      </c>
+      <c r="G206" t="s">
+        <v>72</v>
+      </c>
+      <c r="H206" t="s">
+        <v>85</v>
+      </c>
+      <c r="I206">
+        <v>0</v>
+      </c>
+      <c r="J206">
+        <v>0</v>
+      </c>
+      <c r="K206">
+        <v>0</v>
+      </c>
+      <c r="L206">
+        <v>1</v>
+      </c>
+      <c r="M206">
+        <v>0</v>
+      </c>
+      <c r="N206">
+        <v>1</v>
+      </c>
+      <c r="O206" t="s">
+        <v>140</v>
+      </c>
+      <c r="P206" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q206">
+        <v>3.5</v>
+      </c>
+      <c r="R206">
+        <v>1.98</v>
+      </c>
+      <c r="S206">
+        <v>3</v>
+      </c>
+      <c r="T206">
+        <v>1.46</v>
+      </c>
+      <c r="U206">
+        <v>2.5</v>
+      </c>
+      <c r="V206">
+        <v>3</v>
+      </c>
+      <c r="W206">
+        <v>1.33</v>
+      </c>
+      <c r="X206">
+        <v>8.25</v>
+      </c>
+      <c r="Y206">
+        <v>1.06</v>
+      </c>
+      <c r="Z206">
+        <v>2.89</v>
+      </c>
+      <c r="AA206">
+        <v>3.19</v>
+      </c>
+      <c r="AB206">
+        <v>2.44</v>
+      </c>
+      <c r="AC206">
+        <v>1.08</v>
+      </c>
+      <c r="AD206">
+        <v>7.5</v>
+      </c>
+      <c r="AE206">
+        <v>1.4</v>
+      </c>
+      <c r="AF206">
+        <v>2.9</v>
+      </c>
+      <c r="AG206">
+        <v>2.05</v>
+      </c>
+      <c r="AH206">
+        <v>1.61</v>
+      </c>
+      <c r="AI206">
+        <v>1.88</v>
+      </c>
+      <c r="AJ206">
+        <v>1.8</v>
+      </c>
+      <c r="AK206">
+        <v>1.53</v>
+      </c>
+      <c r="AL206">
+        <v>1.34</v>
+      </c>
+      <c r="AM206">
+        <v>1.38</v>
+      </c>
+      <c r="AN206">
+        <v>2.18</v>
+      </c>
+      <c r="AO206">
+        <v>1.82</v>
+      </c>
+      <c r="AP206">
+        <v>2.25</v>
+      </c>
+      <c r="AQ206">
+        <v>1.67</v>
+      </c>
+      <c r="AR206">
+        <v>1.62</v>
+      </c>
+      <c r="AS206">
+        <v>1.43</v>
+      </c>
+      <c r="AT206">
+        <v>3.05</v>
+      </c>
+      <c r="AU206">
+        <v>2</v>
+      </c>
+      <c r="AV206">
+        <v>3</v>
+      </c>
+      <c r="AW206">
+        <v>4</v>
+      </c>
+      <c r="AX206">
+        <v>7</v>
+      </c>
+      <c r="AY206">
+        <v>6</v>
+      </c>
+      <c r="AZ206">
+        <v>10</v>
+      </c>
+      <c r="BA206">
+        <v>5</v>
+      </c>
+      <c r="BB206">
+        <v>3</v>
+      </c>
+      <c r="BC206">
+        <v>8</v>
+      </c>
+      <c r="BD206">
+        <v>2.1</v>
+      </c>
+      <c r="BE206">
+        <v>6.25</v>
+      </c>
+      <c r="BF206">
+        <v>1.9</v>
+      </c>
+      <c r="BG206">
+        <v>1.45</v>
+      </c>
+      <c r="BH206">
+        <v>2.55</v>
+      </c>
+      <c r="BI206">
+        <v>1.75</v>
+      </c>
+      <c r="BJ206">
+        <v>1.95</v>
+      </c>
+      <c r="BK206">
+        <v>2.2</v>
+      </c>
+      <c r="BL206">
+        <v>1.58</v>
+      </c>
+      <c r="BM206">
+        <v>2.9</v>
+      </c>
+      <c r="BN206">
+        <v>1.35</v>
+      </c>
+      <c r="BO206">
+        <v>3.9</v>
+      </c>
+      <c r="BP206">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="207" spans="1:68">
+      <c r="A207" s="1">
+        <v>206</v>
+      </c>
+      <c r="B207">
+        <v>7469071</v>
+      </c>
+      <c r="C207" t="s">
+        <v>68</v>
+      </c>
+      <c r="D207" t="s">
+        <v>69</v>
+      </c>
+      <c r="E207" s="2">
+        <v>45703.66666666666</v>
+      </c>
+      <c r="F207">
+        <v>23</v>
+      </c>
+      <c r="G207" t="s">
+        <v>75</v>
+      </c>
+      <c r="H207" t="s">
+        <v>78</v>
+      </c>
+      <c r="I207">
+        <v>0</v>
+      </c>
+      <c r="J207">
+        <v>1</v>
+      </c>
+      <c r="K207">
+        <v>1</v>
+      </c>
+      <c r="L207">
+        <v>0</v>
+      </c>
+      <c r="M207">
+        <v>3</v>
+      </c>
+      <c r="N207">
+        <v>3</v>
+      </c>
+      <c r="O207" t="s">
+        <v>90</v>
+      </c>
+      <c r="P207" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q207">
+        <v>3.8</v>
+      </c>
+      <c r="R207">
+        <v>2.09</v>
+      </c>
+      <c r="S207">
+        <v>2.95</v>
+      </c>
+      <c r="T207">
+        <v>1.45</v>
+      </c>
+      <c r="U207">
+        <v>2.6</v>
+      </c>
+      <c r="V207">
+        <v>2.95</v>
+      </c>
+      <c r="W207">
+        <v>1.35</v>
+      </c>
+      <c r="X207">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="Y207">
+        <v>1.02</v>
+      </c>
+      <c r="Z207">
+        <v>2.92</v>
+      </c>
+      <c r="AA207">
+        <v>3.07</v>
+      </c>
+      <c r="AB207">
+        <v>2.49</v>
+      </c>
+      <c r="AC207">
+        <v>1.07</v>
+      </c>
+      <c r="AD207">
+        <v>8</v>
+      </c>
+      <c r="AE207">
+        <v>1.35</v>
+      </c>
+      <c r="AF207">
+        <v>2.95</v>
+      </c>
+      <c r="AG207">
+        <v>2</v>
+      </c>
+      <c r="AH207">
+        <v>1.65</v>
+      </c>
+      <c r="AI207">
+        <v>1.81</v>
+      </c>
+      <c r="AJ207">
+        <v>1.9</v>
+      </c>
+      <c r="AK207">
+        <v>1.58</v>
+      </c>
+      <c r="AL207">
+        <v>1.32</v>
+      </c>
+      <c r="AM207">
+        <v>1.34</v>
+      </c>
+      <c r="AN207">
+        <v>1.82</v>
+      </c>
+      <c r="AO207">
+        <v>1.3</v>
+      </c>
+      <c r="AP207">
+        <v>1.67</v>
+      </c>
+      <c r="AQ207">
+        <v>1.45</v>
+      </c>
+      <c r="AR207">
+        <v>1.58</v>
+      </c>
+      <c r="AS207">
+        <v>1.24</v>
+      </c>
+      <c r="AT207">
+        <v>2.82</v>
+      </c>
+      <c r="AU207">
+        <v>7</v>
+      </c>
+      <c r="AV207">
+        <v>6</v>
+      </c>
+      <c r="AW207">
+        <v>7</v>
+      </c>
+      <c r="AX207">
+        <v>8</v>
+      </c>
+      <c r="AY207">
+        <v>14</v>
+      </c>
+      <c r="AZ207">
+        <v>14</v>
+      </c>
+      <c r="BA207">
+        <v>9</v>
+      </c>
+      <c r="BB207">
+        <v>2</v>
+      </c>
+      <c r="BC207">
+        <v>11</v>
+      </c>
+      <c r="BD207">
+        <v>2.17</v>
+      </c>
+      <c r="BE207">
+        <v>6.25</v>
+      </c>
+      <c r="BF207">
+        <v>1.84</v>
+      </c>
+      <c r="BG207">
+        <v>1.43</v>
+      </c>
+      <c r="BH207">
+        <v>2.6</v>
+      </c>
+      <c r="BI207">
+        <v>1.72</v>
+      </c>
+      <c r="BJ207">
+        <v>1.98</v>
+      </c>
+      <c r="BK207">
+        <v>2.15</v>
+      </c>
+      <c r="BL207">
+        <v>1.63</v>
+      </c>
+      <c r="BM207">
+        <v>2.8</v>
+      </c>
+      <c r="BN207">
+        <v>1.38</v>
+      </c>
+      <c r="BO207">
+        <v>3.65</v>
+      </c>
+      <c r="BP207">
+        <v>1.23</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1304" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1310" uniqueCount="304">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1287,7 +1287,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP207"/>
+  <dimension ref="A1:BP208"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -4096,7 +4096,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ14">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4505,7 +4505,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ16">
         <v>1.27</v>
@@ -8007,7 +8007,7 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ33">
         <v>0.55</v>
@@ -8834,7 +8834,7 @@
         <v>2</v>
       </c>
       <c r="AQ37">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR37">
         <v>1.13</v>
@@ -11097,7 +11097,7 @@
         <v>0.33</v>
       </c>
       <c r="AP48">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ48">
         <v>1.08</v>
@@ -14396,7 +14396,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ64">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR64">
         <v>1.73</v>
@@ -14805,7 +14805,7 @@
         <v>1</v>
       </c>
       <c r="AP66">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ66">
         <v>1</v>
@@ -16662,7 +16662,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ75">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR75">
         <v>1.25</v>
@@ -18513,7 +18513,7 @@
         <v>1.4</v>
       </c>
       <c r="AP84">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ84">
         <v>1.33</v>
@@ -21400,7 +21400,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ98">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR98">
         <v>1.06</v>
@@ -22839,7 +22839,7 @@
         <v>0.83</v>
       </c>
       <c r="AP105">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ105">
         <v>0.83</v>
@@ -25314,7 +25314,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ117">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR117">
         <v>1.7</v>
@@ -28195,7 +28195,7 @@
         <v>1.17</v>
       </c>
       <c r="AP131">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ131">
         <v>1.18</v>
@@ -28610,7 +28610,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ133">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR133">
         <v>1.34</v>
@@ -30873,7 +30873,7 @@
         <v>1.43</v>
       </c>
       <c r="AP144">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ144">
         <v>1.45</v>
@@ -31082,7 +31082,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ145">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR145">
         <v>1.62</v>
@@ -33963,7 +33963,7 @@
         <v>1.13</v>
       </c>
       <c r="AP159">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ159">
         <v>1.64</v>
@@ -35820,7 +35820,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ168">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR168">
         <v>1.22</v>
@@ -38495,7 +38495,7 @@
         <v>1</v>
       </c>
       <c r="AP181">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ181">
         <v>1.36</v>
@@ -40146,7 +40146,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ189">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR189">
         <v>1.73</v>
@@ -43929,6 +43929,212 @@
         <v>3.65</v>
       </c>
       <c r="BP207">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="208" spans="1:68">
+      <c r="A208" s="1">
+        <v>207</v>
+      </c>
+      <c r="B208">
+        <v>7469066</v>
+      </c>
+      <c r="C208" t="s">
+        <v>68</v>
+      </c>
+      <c r="D208" t="s">
+        <v>69</v>
+      </c>
+      <c r="E208" s="2">
+        <v>45705.69791666666</v>
+      </c>
+      <c r="F208">
+        <v>23</v>
+      </c>
+      <c r="G208" t="s">
+        <v>84</v>
+      </c>
+      <c r="H208" t="s">
+        <v>76</v>
+      </c>
+      <c r="I208">
+        <v>1</v>
+      </c>
+      <c r="J208">
+        <v>0</v>
+      </c>
+      <c r="K208">
+        <v>1</v>
+      </c>
+      <c r="L208">
+        <v>1</v>
+      </c>
+      <c r="M208">
+        <v>0</v>
+      </c>
+      <c r="N208">
+        <v>1</v>
+      </c>
+      <c r="O208" t="s">
+        <v>194</v>
+      </c>
+      <c r="P208" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q208">
+        <v>3.1</v>
+      </c>
+      <c r="R208">
+        <v>2.1</v>
+      </c>
+      <c r="S208">
+        <v>3.6</v>
+      </c>
+      <c r="T208">
+        <v>1.44</v>
+      </c>
+      <c r="U208">
+        <v>2.63</v>
+      </c>
+      <c r="V208">
+        <v>3.25</v>
+      </c>
+      <c r="W208">
+        <v>1.33</v>
+      </c>
+      <c r="X208">
+        <v>9</v>
+      </c>
+      <c r="Y208">
+        <v>1.07</v>
+      </c>
+      <c r="Z208">
+        <v>2.37</v>
+      </c>
+      <c r="AA208">
+        <v>3.19</v>
+      </c>
+      <c r="AB208">
+        <v>2.99</v>
+      </c>
+      <c r="AC208">
+        <v>1.02</v>
+      </c>
+      <c r="AD208">
+        <v>9.65</v>
+      </c>
+      <c r="AE208">
+        <v>1.29</v>
+      </c>
+      <c r="AF208">
+        <v>3.12</v>
+      </c>
+      <c r="AG208">
+        <v>1.95</v>
+      </c>
+      <c r="AH208">
+        <v>1.7</v>
+      </c>
+      <c r="AI208">
+        <v>1.8</v>
+      </c>
+      <c r="AJ208">
+        <v>1.91</v>
+      </c>
+      <c r="AK208">
+        <v>1.36</v>
+      </c>
+      <c r="AL208">
+        <v>1.31</v>
+      </c>
+      <c r="AM208">
+        <v>1.55</v>
+      </c>
+      <c r="AN208">
+        <v>1.9</v>
+      </c>
+      <c r="AO208">
+        <v>0.4</v>
+      </c>
+      <c r="AP208">
+        <v>2</v>
+      </c>
+      <c r="AQ208">
+        <v>0.36</v>
+      </c>
+      <c r="AR208">
+        <v>1.37</v>
+      </c>
+      <c r="AS208">
+        <v>1.29</v>
+      </c>
+      <c r="AT208">
+        <v>2.66</v>
+      </c>
+      <c r="AU208">
+        <v>7</v>
+      </c>
+      <c r="AV208">
+        <v>2</v>
+      </c>
+      <c r="AW208">
+        <v>6</v>
+      </c>
+      <c r="AX208">
+        <v>5</v>
+      </c>
+      <c r="AY208">
+        <v>13</v>
+      </c>
+      <c r="AZ208">
+        <v>7</v>
+      </c>
+      <c r="BA208">
+        <v>7</v>
+      </c>
+      <c r="BB208">
+        <v>9</v>
+      </c>
+      <c r="BC208">
+        <v>16</v>
+      </c>
+      <c r="BD208">
+        <v>1.8</v>
+      </c>
+      <c r="BE208">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="BF208">
+        <v>2.44</v>
+      </c>
+      <c r="BG208">
+        <v>1.28</v>
+      </c>
+      <c r="BH208">
+        <v>3.08</v>
+      </c>
+      <c r="BI208">
+        <v>1.54</v>
+      </c>
+      <c r="BJ208">
+        <v>2.25</v>
+      </c>
+      <c r="BK208">
+        <v>1.95</v>
+      </c>
+      <c r="BL208">
+        <v>1.76</v>
+      </c>
+      <c r="BM208">
+        <v>2.54</v>
+      </c>
+      <c r="BN208">
+        <v>1.43</v>
+      </c>
+      <c r="BO208">
+        <v>3.42</v>
+      </c>
+      <c r="BP208">
         <v>1.23</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1310" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1346" uniqueCount="308">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -685,6 +685,21 @@
     <t>['5', '38', '87']</t>
   </si>
   <si>
+    <t>['68']</t>
+  </si>
+  <si>
+    <t>['81']</t>
+  </si>
+  <si>
+    <t>['29', '31', '51']</t>
+  </si>
+  <si>
+    <t>['33']</t>
+  </si>
+  <si>
+    <t>['17', '90+7']</t>
+  </si>
+  <si>
     <t>['16', '45+2']</t>
   </si>
   <si>
@@ -710,9 +725,6 @@
   </si>
   <si>
     <t>['52']</t>
-  </si>
-  <si>
-    <t>['68']</t>
   </si>
   <si>
     <t>['5']</t>
@@ -820,9 +832,6 @@
     <t>['69', '90+1', '90+5']</t>
   </si>
   <si>
-    <t>['81']</t>
-  </si>
-  <si>
     <t>['10', '37', '48']</t>
   </si>
   <si>
@@ -926,6 +935,9 @@
   </si>
   <si>
     <t>['28', '87', '90+3']</t>
+  </si>
+  <si>
+    <t>['48']</t>
   </si>
 </sst>
 </file>
@@ -1287,7 +1299,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP208"/>
+  <dimension ref="A1:BP214"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1543,7 +1555,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="Q2">
         <v>2.4</v>
@@ -1955,7 +1967,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="Q4">
         <v>3.6</v>
@@ -2033,10 +2045,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ4">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2242,7 +2254,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ5">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2445,7 +2457,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ6">
         <v>1.33</v>
@@ -2654,7 +2666,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ7">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2779,7 +2791,7 @@
         <v>90</v>
       </c>
       <c r="P8" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="Q8">
         <v>3.1</v>
@@ -3063,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="AQ9">
         <v>1.5</v>
@@ -3191,7 +3203,7 @@
         <v>94</v>
       </c>
       <c r="P10" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="Q10">
         <v>2.6</v>
@@ -3478,7 +3490,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ11">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3684,7 +3696,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ12">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3809,7 +3821,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="Q13">
         <v>3.1</v>
@@ -3887,7 +3899,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ13">
         <v>1.45</v>
@@ -4299,10 +4311,10 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ15">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4427,7 +4439,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="Q16">
         <v>2.63</v>
@@ -4633,7 +4645,7 @@
         <v>99</v>
       </c>
       <c r="P17" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -4711,7 +4723,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ17">
         <v>1.36</v>
@@ -5332,7 +5344,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ20">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR20">
         <v>0.67</v>
@@ -5663,7 +5675,7 @@
         <v>103</v>
       </c>
       <c r="P22" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -5744,7 +5756,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ22">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR22">
         <v>1.64</v>
@@ -5947,7 +5959,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ23">
         <v>1.08</v>
@@ -6075,7 +6087,7 @@
         <v>105</v>
       </c>
       <c r="P24" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="Q24">
         <v>2.62</v>
@@ -6156,7 +6168,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ24">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR24">
         <v>1.39</v>
@@ -6359,7 +6371,7 @@
         <v>1</v>
       </c>
       <c r="AP25">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="AQ25">
         <v>1</v>
@@ -6487,7 +6499,7 @@
         <v>106</v>
       </c>
       <c r="P26" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="Q26">
         <v>2.83</v>
@@ -6565,7 +6577,7 @@
         <v>1</v>
       </c>
       <c r="AP26">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ26">
         <v>0.83</v>
@@ -6899,7 +6911,7 @@
         <v>108</v>
       </c>
       <c r="P28" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="Q28">
         <v>2.6</v>
@@ -7392,7 +7404,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ30">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR30">
         <v>1.49</v>
@@ -8010,7 +8022,7 @@
         <v>2</v>
       </c>
       <c r="AQ33">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR33">
         <v>2.15</v>
@@ -8213,10 +8225,10 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ34">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR34">
         <v>1.55</v>
@@ -8341,7 +8353,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="Q35">
         <v>3.3</v>
@@ -8419,10 +8431,10 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ35">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AR35">
         <v>1.69</v>
@@ -8547,7 +8559,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q36">
         <v>3.1</v>
@@ -8625,7 +8637,7 @@
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ36">
         <v>1.45</v>
@@ -8753,7 +8765,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="Q37">
         <v>3.4</v>
@@ -8831,7 +8843,7 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ37">
         <v>0.36</v>
@@ -8959,7 +8971,7 @@
         <v>90</v>
       </c>
       <c r="P38" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="Q38">
         <v>3.2</v>
@@ -9165,7 +9177,7 @@
         <v>90</v>
       </c>
       <c r="P39" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="Q39">
         <v>3.4</v>
@@ -9243,7 +9255,7 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="AQ39">
         <v>0.91</v>
@@ -9449,7 +9461,7 @@
         <v>3</v>
       </c>
       <c r="AP40">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ40">
         <v>1.67</v>
@@ -9577,7 +9589,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="Q41">
         <v>2.5</v>
@@ -9658,7 +9670,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ41">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR41">
         <v>1.73</v>
@@ -9783,7 +9795,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="Q42">
         <v>3.25</v>
@@ -9861,7 +9873,7 @@
         <v>1</v>
       </c>
       <c r="AP42">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ42">
         <v>0.83</v>
@@ -9989,7 +10001,7 @@
         <v>90</v>
       </c>
       <c r="P43" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="Q43">
         <v>2.75</v>
@@ -10482,7 +10494,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ45">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR45">
         <v>1.53</v>
@@ -10894,7 +10906,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ47">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR47">
         <v>1.49</v>
@@ -11100,7 +11112,7 @@
         <v>2</v>
       </c>
       <c r="AQ48">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR48">
         <v>1.82</v>
@@ -11509,10 +11521,10 @@
         <v>3</v>
       </c>
       <c r="AP50">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ50">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AR50">
         <v>1.61</v>
@@ -12049,7 +12061,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -12127,7 +12139,7 @@
         <v>2</v>
       </c>
       <c r="AP53">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ53">
         <v>1</v>
@@ -12255,7 +12267,7 @@
         <v>129</v>
       </c>
       <c r="P54" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="Q54">
         <v>2.55</v>
@@ -12336,7 +12348,7 @@
         <v>1</v>
       </c>
       <c r="AQ54">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR54">
         <v>1.19</v>
@@ -12461,7 +12473,7 @@
         <v>130</v>
       </c>
       <c r="P55" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="Q55">
         <v>2.55</v>
@@ -12539,7 +12551,7 @@
         <v>1.33</v>
       </c>
       <c r="AP55">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ55">
         <v>1.33</v>
@@ -12873,7 +12885,7 @@
         <v>132</v>
       </c>
       <c r="P57" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -13157,7 +13169,7 @@
         <v>1.5</v>
       </c>
       <c r="AP58">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="AQ58">
         <v>1.36</v>
@@ -13285,7 +13297,7 @@
         <v>134</v>
       </c>
       <c r="P59" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="Q59">
         <v>2.62</v>
@@ -13363,10 +13375,10 @@
         <v>1.67</v>
       </c>
       <c r="AP59">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ59">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR59">
         <v>1.53</v>
@@ -13491,7 +13503,7 @@
         <v>135</v>
       </c>
       <c r="P60" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="Q60">
         <v>2.88</v>
@@ -13775,10 +13787,10 @@
         <v>1.5</v>
       </c>
       <c r="AP61">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ61">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR61">
         <v>1.29</v>
@@ -13903,7 +13915,7 @@
         <v>137</v>
       </c>
       <c r="P62" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="Q62">
         <v>3.6</v>
@@ -14109,7 +14121,7 @@
         <v>138</v>
       </c>
       <c r="P63" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="Q63">
         <v>3.75</v>
@@ -14599,7 +14611,7 @@
         <v>1.75</v>
       </c>
       <c r="AP65">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ65">
         <v>1.33</v>
@@ -14808,7 +14820,7 @@
         <v>2</v>
       </c>
       <c r="AQ66">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR66">
         <v>1.59</v>
@@ -15011,10 +15023,10 @@
         <v>0.25</v>
       </c>
       <c r="AP67">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ67">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR67">
         <v>1.61</v>
@@ -15139,7 +15151,7 @@
         <v>143</v>
       </c>
       <c r="P68" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15217,7 +15229,7 @@
         <v>1</v>
       </c>
       <c r="AP68">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ68">
         <v>0.91</v>
@@ -15345,7 +15357,7 @@
         <v>144</v>
       </c>
       <c r="P69" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15551,7 +15563,7 @@
         <v>145</v>
       </c>
       <c r="P70" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="Q70">
         <v>3.75</v>
@@ -15838,7 +15850,7 @@
         <v>1</v>
       </c>
       <c r="AQ71">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AR71">
         <v>1.24</v>
@@ -15963,7 +15975,7 @@
         <v>147</v>
       </c>
       <c r="P72" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16044,7 +16056,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ72">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR72">
         <v>1.72</v>
@@ -16169,7 +16181,7 @@
         <v>90</v>
       </c>
       <c r="P73" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="Q73">
         <v>4.33</v>
@@ -16247,7 +16259,7 @@
         <v>0.75</v>
       </c>
       <c r="AP73">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="AQ73">
         <v>1.08</v>
@@ -16375,7 +16387,7 @@
         <v>90</v>
       </c>
       <c r="P74" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="Q74">
         <v>2.4</v>
@@ -16581,7 +16593,7 @@
         <v>148</v>
       </c>
       <c r="P75" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="Q75">
         <v>3.5</v>
@@ -16787,7 +16799,7 @@
         <v>149</v>
       </c>
       <c r="P76" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Q76">
         <v>2.88</v>
@@ -17071,7 +17083,7 @@
         <v>2</v>
       </c>
       <c r="AP77">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ77">
         <v>1.45</v>
@@ -17277,10 +17289,10 @@
         <v>1</v>
       </c>
       <c r="AP78">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ78">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR78">
         <v>1.7</v>
@@ -17405,7 +17417,7 @@
         <v>151</v>
       </c>
       <c r="P79" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17611,7 +17623,7 @@
         <v>152</v>
       </c>
       <c r="P80" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="Q80">
         <v>2.05</v>
@@ -17692,7 +17704,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ80">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR80">
         <v>2.09</v>
@@ -17817,7 +17829,7 @@
         <v>90</v>
       </c>
       <c r="P81" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="Q81">
         <v>4.33</v>
@@ -18307,10 +18319,10 @@
         <v>0.8</v>
       </c>
       <c r="AP83">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ83">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR83">
         <v>1.6</v>
@@ -18641,7 +18653,7 @@
         <v>90</v>
       </c>
       <c r="P85" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="Q85">
         <v>3.1</v>
@@ -18722,7 +18734,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ85">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR85">
         <v>1.48</v>
@@ -18847,7 +18859,7 @@
         <v>156</v>
       </c>
       <c r="P86" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -18925,7 +18937,7 @@
         <v>1.4</v>
       </c>
       <c r="AP86">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ86">
         <v>1.5</v>
@@ -19340,7 +19352,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ88">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AR88">
         <v>1.77</v>
@@ -19543,7 +19555,7 @@
         <v>0.75</v>
       </c>
       <c r="AP89">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ89">
         <v>0.91</v>
@@ -19671,7 +19683,7 @@
         <v>90</v>
       </c>
       <c r="P90" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="Q90">
         <v>2.38</v>
@@ -19752,7 +19764,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ90">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR90">
         <v>1.42</v>
@@ -20083,7 +20095,7 @@
         <v>160</v>
       </c>
       <c r="P92" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20164,7 +20176,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ92">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR92">
         <v>1.2</v>
@@ -20573,10 +20585,10 @@
         <v>1.2</v>
       </c>
       <c r="AP94">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ94">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR94">
         <v>1.21</v>
@@ -20701,7 +20713,7 @@
         <v>162</v>
       </c>
       <c r="P95" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="Q95">
         <v>1.9</v>
@@ -20907,7 +20919,7 @@
         <v>163</v>
       </c>
       <c r="P96" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="Q96">
         <v>2.75</v>
@@ -20985,7 +20997,7 @@
         <v>1.2</v>
       </c>
       <c r="AP96">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ96">
         <v>1.08</v>
@@ -21319,7 +21331,7 @@
         <v>90</v>
       </c>
       <c r="P98" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="Q98">
         <v>4.75</v>
@@ -21397,7 +21409,7 @@
         <v>0.25</v>
       </c>
       <c r="AP98">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="AQ98">
         <v>0.36</v>
@@ -21809,10 +21821,10 @@
         <v>0.6</v>
       </c>
       <c r="AP100">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ100">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR100">
         <v>1.57</v>
@@ -22015,10 +22027,10 @@
         <v>0.67</v>
       </c>
       <c r="AP101">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="AQ101">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR101">
         <v>1.04</v>
@@ -22349,7 +22361,7 @@
         <v>166</v>
       </c>
       <c r="P103" t="s">
-        <v>268</v>
+        <v>224</v>
       </c>
       <c r="Q103">
         <v>4.2</v>
@@ -22555,7 +22567,7 @@
         <v>167</v>
       </c>
       <c r="P104" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q104">
         <v>2.25</v>
@@ -22633,7 +22645,7 @@
         <v>1.17</v>
       </c>
       <c r="AP104">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ104">
         <v>1.08</v>
@@ -23379,7 +23391,7 @@
         <v>90</v>
       </c>
       <c r="P108" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="Q108">
         <v>4.5</v>
@@ -23869,10 +23881,10 @@
         <v>1.17</v>
       </c>
       <c r="AP110">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ110">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR110">
         <v>1.85</v>
@@ -24075,7 +24087,7 @@
         <v>0.8</v>
       </c>
       <c r="AP111">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ111">
         <v>1.36</v>
@@ -24203,7 +24215,7 @@
         <v>173</v>
       </c>
       <c r="P112" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q112">
         <v>3.5</v>
@@ -24490,7 +24502,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ113">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR113">
         <v>1.1</v>
@@ -24615,7 +24627,7 @@
         <v>90</v>
       </c>
       <c r="P114" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q114">
         <v>2.85</v>
@@ -24696,7 +24708,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ114">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR114">
         <v>1.28</v>
@@ -25027,7 +25039,7 @@
         <v>175</v>
       </c>
       <c r="P116" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q116">
         <v>2.4</v>
@@ -25108,7 +25120,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ116">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AR116">
         <v>1.94</v>
@@ -25439,7 +25451,7 @@
         <v>90</v>
       </c>
       <c r="P118" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q118">
         <v>4</v>
@@ -25517,7 +25529,7 @@
         <v>1.14</v>
       </c>
       <c r="AP118">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="AQ118">
         <v>1.33</v>
@@ -26057,7 +26069,7 @@
         <v>178</v>
       </c>
       <c r="P121" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q121">
         <v>2.88</v>
@@ -26344,7 +26356,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ122">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR122">
         <v>1.78</v>
@@ -26550,7 +26562,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ123">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR123">
         <v>1.44</v>
@@ -26753,10 +26765,10 @@
         <v>1</v>
       </c>
       <c r="AP124">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ124">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR124">
         <v>1.79</v>
@@ -26959,7 +26971,7 @@
         <v>1.14</v>
       </c>
       <c r="AP125">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ125">
         <v>1.5</v>
@@ -27165,7 +27177,7 @@
         <v>0.17</v>
       </c>
       <c r="AP126">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ126">
         <v>0.64</v>
@@ -27580,7 +27592,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ128">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR128">
         <v>1.83</v>
@@ -27783,10 +27795,10 @@
         <v>1</v>
       </c>
       <c r="AP129">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="AQ129">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AR129">
         <v>0.99</v>
@@ -27989,7 +28001,7 @@
         <v>0.71</v>
       </c>
       <c r="AP130">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ130">
         <v>0.83</v>
@@ -28198,7 +28210,7 @@
         <v>2</v>
       </c>
       <c r="AQ131">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR131">
         <v>1.33</v>
@@ -28735,7 +28747,7 @@
         <v>90</v>
       </c>
       <c r="P134" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q134">
         <v>3.2</v>
@@ -28813,10 +28825,10 @@
         <v>0.43</v>
       </c>
       <c r="AP134">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ134">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR134">
         <v>1.08</v>
@@ -28941,7 +28953,7 @@
         <v>90</v>
       </c>
       <c r="P135" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q135">
         <v>5</v>
@@ -29431,10 +29443,10 @@
         <v>1.29</v>
       </c>
       <c r="AP137">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ137">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AR137">
         <v>1.66</v>
@@ -29971,7 +29983,7 @@
         <v>188</v>
       </c>
       <c r="P140" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q140">
         <v>2.95</v>
@@ -30177,7 +30189,7 @@
         <v>189</v>
       </c>
       <c r="P141" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q141">
         <v>2.8</v>
@@ -31001,7 +31013,7 @@
         <v>192</v>
       </c>
       <c r="P145" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q145">
         <v>2.75</v>
@@ -31079,7 +31091,7 @@
         <v>0.57</v>
       </c>
       <c r="AP145">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ145">
         <v>0.36</v>
@@ -31207,7 +31219,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q146">
         <v>3.75</v>
@@ -31285,7 +31297,7 @@
         <v>1</v>
       </c>
       <c r="AP146">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ146">
         <v>1</v>
@@ -31413,7 +31425,7 @@
         <v>129</v>
       </c>
       <c r="P147" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q147">
         <v>3.75</v>
@@ -31494,7 +31506,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ147">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR147">
         <v>1.16</v>
@@ -31619,7 +31631,7 @@
         <v>90</v>
       </c>
       <c r="P148" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q148">
         <v>2.4</v>
@@ -31697,10 +31709,10 @@
         <v>0.88</v>
       </c>
       <c r="AP148">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ148">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR148">
         <v>1.89</v>
@@ -31825,7 +31837,7 @@
         <v>90</v>
       </c>
       <c r="P149" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q149">
         <v>3.1</v>
@@ -31906,7 +31918,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ149">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR149">
         <v>1.68</v>
@@ -32112,7 +32124,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ150">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR150">
         <v>1.35</v>
@@ -32237,7 +32249,7 @@
         <v>194</v>
       </c>
       <c r="P151" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q151">
         <v>1.62</v>
@@ -32315,7 +32327,7 @@
         <v>1.14</v>
       </c>
       <c r="AP151">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ151">
         <v>1.27</v>
@@ -32649,7 +32661,7 @@
         <v>95</v>
       </c>
       <c r="P153" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q153">
         <v>2.63</v>
@@ -33139,10 +33151,10 @@
         <v>1.25</v>
       </c>
       <c r="AP155">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="AQ155">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR155">
         <v>1</v>
@@ -33473,7 +33485,7 @@
         <v>197</v>
       </c>
       <c r="P157" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q157">
         <v>2.7</v>
@@ -33551,10 +33563,10 @@
         <v>1.11</v>
       </c>
       <c r="AP157">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ157">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR157">
         <v>1.86</v>
@@ -33679,7 +33691,7 @@
         <v>96</v>
       </c>
       <c r="P158" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q158">
         <v>2.55</v>
@@ -33760,7 +33772,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ158">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR158">
         <v>1.25</v>
@@ -33885,7 +33897,7 @@
         <v>198</v>
       </c>
       <c r="P159" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q159">
         <v>3.3</v>
@@ -33966,7 +33978,7 @@
         <v>2</v>
       </c>
       <c r="AQ159">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AR159">
         <v>1.45</v>
@@ -34091,7 +34103,7 @@
         <v>90</v>
       </c>
       <c r="P160" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="Q160">
         <v>2.75</v>
@@ -34375,10 +34387,10 @@
         <v>0.75</v>
       </c>
       <c r="AP161">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ161">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR161">
         <v>1.88</v>
@@ -34581,7 +34593,7 @@
         <v>0.13</v>
       </c>
       <c r="AP162">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ162">
         <v>0.64</v>
@@ -35199,7 +35211,7 @@
         <v>1.38</v>
       </c>
       <c r="AP165">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ165">
         <v>1.27</v>
@@ -35533,7 +35545,7 @@
         <v>109</v>
       </c>
       <c r="P167" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q167">
         <v>3.35</v>
@@ -35945,7 +35957,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q169">
         <v>2.8</v>
@@ -36151,7 +36163,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q170">
         <v>3</v>
@@ -36435,7 +36447,7 @@
         <v>1</v>
       </c>
       <c r="AP171">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ171">
         <v>1.5</v>
@@ -36563,7 +36575,7 @@
         <v>90</v>
       </c>
       <c r="P172" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="Q172">
         <v>2.63</v>
@@ -36644,7 +36656,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ172">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR172">
         <v>1.73</v>
@@ -36769,7 +36781,7 @@
         <v>207</v>
       </c>
       <c r="P173" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q173">
         <v>2.3</v>
@@ -36847,7 +36859,7 @@
         <v>0.11</v>
       </c>
       <c r="AP173">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ173">
         <v>0.64</v>
@@ -37053,7 +37065,7 @@
         <v>0.9</v>
       </c>
       <c r="AP174">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ174">
         <v>0.83</v>
@@ -37259,10 +37271,10 @@
         <v>0.67</v>
       </c>
       <c r="AP175">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="AQ175">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR175">
         <v>0.95</v>
@@ -37468,7 +37480,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ176">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR176">
         <v>1.28</v>
@@ -37799,7 +37811,7 @@
         <v>90</v>
       </c>
       <c r="P178" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="Q178">
         <v>3.25</v>
@@ -37880,7 +37892,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ178">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AR178">
         <v>1.34</v>
@@ -38083,10 +38095,10 @@
         <v>1.1</v>
       </c>
       <c r="AP179">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ179">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR179">
         <v>1.86</v>
@@ -38211,7 +38223,7 @@
         <v>212</v>
       </c>
       <c r="P180" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q180">
         <v>2.2</v>
@@ -38292,7 +38304,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ180">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR180">
         <v>1.65</v>
@@ -38417,7 +38429,7 @@
         <v>90</v>
       </c>
       <c r="P181" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q181">
         <v>3.25</v>
@@ -38701,7 +38713,7 @@
         <v>1.22</v>
       </c>
       <c r="AP182">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ182">
         <v>1.27</v>
@@ -38907,7 +38919,7 @@
         <v>1</v>
       </c>
       <c r="AP183">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ183">
         <v>1.08</v>
@@ -39116,7 +39128,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ184">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR184">
         <v>1.62</v>
@@ -39525,7 +39537,7 @@
         <v>1.33</v>
       </c>
       <c r="AP186">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ186">
         <v>1.45</v>
@@ -39653,7 +39665,7 @@
         <v>90</v>
       </c>
       <c r="P187" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q187">
         <v>2.55</v>
@@ -39859,7 +39871,7 @@
         <v>215</v>
       </c>
       <c r="P188" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q188">
         <v>4.5</v>
@@ -40271,7 +40283,7 @@
         <v>90</v>
       </c>
       <c r="P190" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="Q190">
         <v>3.3</v>
@@ -40477,7 +40489,7 @@
         <v>90</v>
       </c>
       <c r="P191" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q191">
         <v>2.75</v>
@@ -40558,7 +40570,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ191">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR191">
         <v>1.28</v>
@@ -40683,7 +40695,7 @@
         <v>90</v>
       </c>
       <c r="P192" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q192">
         <v>3.25</v>
@@ -40761,7 +40773,7 @@
         <v>0.8</v>
       </c>
       <c r="AP192">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ192">
         <v>1</v>
@@ -40967,10 +40979,10 @@
         <v>1</v>
       </c>
       <c r="AP193">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ193">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR193">
         <v>1.24</v>
@@ -41173,7 +41185,7 @@
         <v>0.91</v>
       </c>
       <c r="AP194">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ194">
         <v>0.83</v>
@@ -41301,7 +41313,7 @@
         <v>214</v>
       </c>
       <c r="P195" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q195">
         <v>4.75</v>
@@ -41379,10 +41391,10 @@
         <v>0.91</v>
       </c>
       <c r="AP195">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="AQ195">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR195">
         <v>1.02</v>
@@ -41507,7 +41519,7 @@
         <v>90</v>
       </c>
       <c r="P196" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q196">
         <v>3.65</v>
@@ -41588,7 +41600,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ196">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AR196">
         <v>1.27</v>
@@ -41713,7 +41725,7 @@
         <v>218</v>
       </c>
       <c r="P197" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q197">
         <v>1.94</v>
@@ -41794,7 +41806,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ197">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR197">
         <v>1.67</v>
@@ -42000,7 +42012,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ198">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR198">
         <v>1.7</v>
@@ -42125,7 +42137,7 @@
         <v>90</v>
       </c>
       <c r="P199" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q199">
         <v>3.75</v>
@@ -43155,7 +43167,7 @@
         <v>160</v>
       </c>
       <c r="P204" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q204">
         <v>3</v>
@@ -43361,7 +43373,7 @@
         <v>90</v>
       </c>
       <c r="P205" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q205">
         <v>2.75</v>
@@ -43645,7 +43657,7 @@
         <v>1.82</v>
       </c>
       <c r="AP206">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ206">
         <v>1.67</v>
@@ -43773,7 +43785,7 @@
         <v>90</v>
       </c>
       <c r="P207" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q207">
         <v>3.8</v>
@@ -44136,6 +44148,1242 @@
       </c>
       <c r="BP208">
         <v>1.23</v>
+      </c>
+    </row>
+    <row r="209" spans="1:68">
+      <c r="A209" s="1">
+        <v>208</v>
+      </c>
+      <c r="B209">
+        <v>7469078</v>
+      </c>
+      <c r="C209" t="s">
+        <v>68</v>
+      </c>
+      <c r="D209" t="s">
+        <v>69</v>
+      </c>
+      <c r="E209" s="2">
+        <v>45709.66666666666</v>
+      </c>
+      <c r="F209">
+        <v>24</v>
+      </c>
+      <c r="G209" t="s">
+        <v>81</v>
+      </c>
+      <c r="H209" t="s">
+        <v>73</v>
+      </c>
+      <c r="I209">
+        <v>1</v>
+      </c>
+      <c r="J209">
+        <v>0</v>
+      </c>
+      <c r="K209">
+        <v>1</v>
+      </c>
+      <c r="L209">
+        <v>1</v>
+      </c>
+      <c r="M209">
+        <v>1</v>
+      </c>
+      <c r="N209">
+        <v>2</v>
+      </c>
+      <c r="O209" t="s">
+        <v>104</v>
+      </c>
+      <c r="P209" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q209">
+        <v>2.29</v>
+      </c>
+      <c r="R209">
+        <v>2.26</v>
+      </c>
+      <c r="S209">
+        <v>4.9</v>
+      </c>
+      <c r="T209">
+        <v>1.38</v>
+      </c>
+      <c r="U209">
+        <v>2.85</v>
+      </c>
+      <c r="V209">
+        <v>2.65</v>
+      </c>
+      <c r="W209">
+        <v>1.43</v>
+      </c>
+      <c r="X209">
+        <v>6.3</v>
+      </c>
+      <c r="Y209">
+        <v>1.09</v>
+      </c>
+      <c r="Z209">
+        <v>1.63</v>
+      </c>
+      <c r="AA209">
+        <v>3.9</v>
+      </c>
+      <c r="AB209">
+        <v>5</v>
+      </c>
+      <c r="AC209">
+        <v>1.05</v>
+      </c>
+      <c r="AD209">
+        <v>9.5</v>
+      </c>
+      <c r="AE209">
+        <v>1.28</v>
+      </c>
+      <c r="AF209">
+        <v>3.4</v>
+      </c>
+      <c r="AG209">
+        <v>1.82</v>
+      </c>
+      <c r="AH209">
+        <v>1.92</v>
+      </c>
+      <c r="AI209">
+        <v>1.78</v>
+      </c>
+      <c r="AJ209">
+        <v>1.93</v>
+      </c>
+      <c r="AK209">
+        <v>1.2</v>
+      </c>
+      <c r="AL209">
+        <v>1.25</v>
+      </c>
+      <c r="AM209">
+        <v>1.97</v>
+      </c>
+      <c r="AN209">
+        <v>1.18</v>
+      </c>
+      <c r="AO209">
+        <v>0.55</v>
+      </c>
+      <c r="AP209">
+        <v>1.17</v>
+      </c>
+      <c r="AQ209">
+        <v>0.58</v>
+      </c>
+      <c r="AR209">
+        <v>1.77</v>
+      </c>
+      <c r="AS209">
+        <v>1.2</v>
+      </c>
+      <c r="AT209">
+        <v>2.97</v>
+      </c>
+      <c r="AU209">
+        <v>2</v>
+      </c>
+      <c r="AV209">
+        <v>3</v>
+      </c>
+      <c r="AW209">
+        <v>15</v>
+      </c>
+      <c r="AX209">
+        <v>2</v>
+      </c>
+      <c r="AY209">
+        <v>18</v>
+      </c>
+      <c r="AZ209">
+        <v>5</v>
+      </c>
+      <c r="BA209">
+        <v>13</v>
+      </c>
+      <c r="BB209">
+        <v>3</v>
+      </c>
+      <c r="BC209">
+        <v>16</v>
+      </c>
+      <c r="BD209">
+        <v>1.58</v>
+      </c>
+      <c r="BE209">
+        <v>6.5</v>
+      </c>
+      <c r="BF209">
+        <v>2.65</v>
+      </c>
+      <c r="BG209">
+        <v>1.38</v>
+      </c>
+      <c r="BH209">
+        <v>2.7</v>
+      </c>
+      <c r="BI209">
+        <v>1.67</v>
+      </c>
+      <c r="BJ209">
+        <v>2.07</v>
+      </c>
+      <c r="BK209">
+        <v>2.07</v>
+      </c>
+      <c r="BL209">
+        <v>1.67</v>
+      </c>
+      <c r="BM209">
+        <v>2.65</v>
+      </c>
+      <c r="BN209">
+        <v>1.41</v>
+      </c>
+      <c r="BO209">
+        <v>3.55</v>
+      </c>
+      <c r="BP209">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="210" spans="1:68">
+      <c r="A210" s="1">
+        <v>209</v>
+      </c>
+      <c r="B210">
+        <v>7469081</v>
+      </c>
+      <c r="C210" t="s">
+        <v>68</v>
+      </c>
+      <c r="D210" t="s">
+        <v>69</v>
+      </c>
+      <c r="E210" s="2">
+        <v>45709.66666666666</v>
+      </c>
+      <c r="F210">
+        <v>24</v>
+      </c>
+      <c r="G210" t="s">
+        <v>83</v>
+      </c>
+      <c r="H210" t="s">
+        <v>87</v>
+      </c>
+      <c r="I210">
+        <v>0</v>
+      </c>
+      <c r="J210">
+        <v>0</v>
+      </c>
+      <c r="K210">
+        <v>0</v>
+      </c>
+      <c r="L210">
+        <v>1</v>
+      </c>
+      <c r="M210">
+        <v>0</v>
+      </c>
+      <c r="N210">
+        <v>1</v>
+      </c>
+      <c r="O210" t="s">
+        <v>223</v>
+      </c>
+      <c r="P210" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q210">
+        <v>2.31</v>
+      </c>
+      <c r="R210">
+        <v>2.16</v>
+      </c>
+      <c r="S210">
+        <v>5.2</v>
+      </c>
+      <c r="T210">
+        <v>1.43</v>
+      </c>
+      <c r="U210">
+        <v>2.65</v>
+      </c>
+      <c r="V210">
+        <v>2.9</v>
+      </c>
+      <c r="W210">
+        <v>1.36</v>
+      </c>
+      <c r="X210">
+        <v>8.1</v>
+      </c>
+      <c r="Y210">
+        <v>1.02</v>
+      </c>
+      <c r="Z210">
+        <v>1.67</v>
+      </c>
+      <c r="AA210">
+        <v>3.65</v>
+      </c>
+      <c r="AB210">
+        <v>5</v>
+      </c>
+      <c r="AC210">
+        <v>1.07</v>
+      </c>
+      <c r="AD210">
+        <v>8</v>
+      </c>
+      <c r="AE210">
+        <v>1.35</v>
+      </c>
+      <c r="AF210">
+        <v>2.9</v>
+      </c>
+      <c r="AG210">
+        <v>2</v>
+      </c>
+      <c r="AH210">
+        <v>1.67</v>
+      </c>
+      <c r="AI210">
+        <v>1.97</v>
+      </c>
+      <c r="AJ210">
+        <v>1.75</v>
+      </c>
+      <c r="AK210">
+        <v>1.18</v>
+      </c>
+      <c r="AL210">
+        <v>1.26</v>
+      </c>
+      <c r="AM210">
+        <v>2</v>
+      </c>
+      <c r="AN210">
+        <v>1.73</v>
+      </c>
+      <c r="AO210">
+        <v>1</v>
+      </c>
+      <c r="AP210">
+        <v>1.83</v>
+      </c>
+      <c r="AQ210">
+        <v>0.92</v>
+      </c>
+      <c r="AR210">
+        <v>1.74</v>
+      </c>
+      <c r="AS210">
+        <v>1.24</v>
+      </c>
+      <c r="AT210">
+        <v>2.98</v>
+      </c>
+      <c r="AU210">
+        <v>9</v>
+      </c>
+      <c r="AV210">
+        <v>0</v>
+      </c>
+      <c r="AW210">
+        <v>7</v>
+      </c>
+      <c r="AX210">
+        <v>5</v>
+      </c>
+      <c r="AY210">
+        <v>16</v>
+      </c>
+      <c r="AZ210">
+        <v>5</v>
+      </c>
+      <c r="BA210">
+        <v>1</v>
+      </c>
+      <c r="BB210">
+        <v>2</v>
+      </c>
+      <c r="BC210">
+        <v>3</v>
+      </c>
+      <c r="BD210">
+        <v>1.52</v>
+      </c>
+      <c r="BE210">
+        <v>6.75</v>
+      </c>
+      <c r="BF210">
+        <v>2.8</v>
+      </c>
+      <c r="BG210">
+        <v>1.33</v>
+      </c>
+      <c r="BH210">
+        <v>2.95</v>
+      </c>
+      <c r="BI210">
+        <v>1.57</v>
+      </c>
+      <c r="BJ210">
+        <v>2.23</v>
+      </c>
+      <c r="BK210">
+        <v>1.92</v>
+      </c>
+      <c r="BL210">
+        <v>1.77</v>
+      </c>
+      <c r="BM210">
+        <v>2.4</v>
+      </c>
+      <c r="BN210">
+        <v>1.49</v>
+      </c>
+      <c r="BO210">
+        <v>3.15</v>
+      </c>
+      <c r="BP210">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="211" spans="1:68">
+      <c r="A211" s="1">
+        <v>210</v>
+      </c>
+      <c r="B211">
+        <v>7469075</v>
+      </c>
+      <c r="C211" t="s">
+        <v>68</v>
+      </c>
+      <c r="D211" t="s">
+        <v>69</v>
+      </c>
+      <c r="E211" s="2">
+        <v>45709.66666666666</v>
+      </c>
+      <c r="F211">
+        <v>24</v>
+      </c>
+      <c r="G211" t="s">
+        <v>85</v>
+      </c>
+      <c r="H211" t="s">
+        <v>79</v>
+      </c>
+      <c r="I211">
+        <v>0</v>
+      </c>
+      <c r="J211">
+        <v>0</v>
+      </c>
+      <c r="K211">
+        <v>0</v>
+      </c>
+      <c r="L211">
+        <v>1</v>
+      </c>
+      <c r="M211">
+        <v>0</v>
+      </c>
+      <c r="N211">
+        <v>1</v>
+      </c>
+      <c r="O211" t="s">
+        <v>224</v>
+      </c>
+      <c r="P211" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q211">
+        <v>2.28</v>
+      </c>
+      <c r="R211">
+        <v>2.19</v>
+      </c>
+      <c r="S211">
+        <v>5.2</v>
+      </c>
+      <c r="T211">
+        <v>1.42</v>
+      </c>
+      <c r="U211">
+        <v>2.7</v>
+      </c>
+      <c r="V211">
+        <v>2.85</v>
+      </c>
+      <c r="W211">
+        <v>1.37</v>
+      </c>
+      <c r="X211">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="Y211">
+        <v>1.01</v>
+      </c>
+      <c r="Z211">
+        <v>1.78</v>
+      </c>
+      <c r="AA211">
+        <v>3.52</v>
+      </c>
+      <c r="AB211">
+        <v>4.4</v>
+      </c>
+      <c r="AC211">
+        <v>1.07</v>
+      </c>
+      <c r="AD211">
+        <v>8</v>
+      </c>
+      <c r="AE211">
+        <v>1.33</v>
+      </c>
+      <c r="AF211">
+        <v>3</v>
+      </c>
+      <c r="AG211">
+        <v>1.95</v>
+      </c>
+      <c r="AH211">
+        <v>1.7</v>
+      </c>
+      <c r="AI211">
+        <v>1.94</v>
+      </c>
+      <c r="AJ211">
+        <v>1.78</v>
+      </c>
+      <c r="AK211">
+        <v>1.18</v>
+      </c>
+      <c r="AL211">
+        <v>1.25</v>
+      </c>
+      <c r="AM211">
+        <v>2.03</v>
+      </c>
+      <c r="AN211">
+        <v>2.09</v>
+      </c>
+      <c r="AO211">
+        <v>1.08</v>
+      </c>
+      <c r="AP211">
+        <v>2.17</v>
+      </c>
+      <c r="AQ211">
+        <v>1</v>
+      </c>
+      <c r="AR211">
+        <v>1.79</v>
+      </c>
+      <c r="AS211">
+        <v>1.34</v>
+      </c>
+      <c r="AT211">
+        <v>3.13</v>
+      </c>
+      <c r="AU211">
+        <v>2</v>
+      </c>
+      <c r="AV211">
+        <v>3</v>
+      </c>
+      <c r="AW211">
+        <v>8</v>
+      </c>
+      <c r="AX211">
+        <v>9</v>
+      </c>
+      <c r="AY211">
+        <v>10</v>
+      </c>
+      <c r="AZ211">
+        <v>12</v>
+      </c>
+      <c r="BA211">
+        <v>3</v>
+      </c>
+      <c r="BB211">
+        <v>5</v>
+      </c>
+      <c r="BC211">
+        <v>8</v>
+      </c>
+      <c r="BD211">
+        <v>1.53</v>
+      </c>
+      <c r="BE211">
+        <v>6.25</v>
+      </c>
+      <c r="BF211">
+        <v>2.8</v>
+      </c>
+      <c r="BG211">
+        <v>1.44</v>
+      </c>
+      <c r="BH211">
+        <v>2.55</v>
+      </c>
+      <c r="BI211">
+        <v>1.74</v>
+      </c>
+      <c r="BJ211">
+        <v>1.98</v>
+      </c>
+      <c r="BK211">
+        <v>2.18</v>
+      </c>
+      <c r="BL211">
+        <v>1.58</v>
+      </c>
+      <c r="BM211">
+        <v>2.8</v>
+      </c>
+      <c r="BN211">
+        <v>1.38</v>
+      </c>
+      <c r="BO211">
+        <v>3.65</v>
+      </c>
+      <c r="BP211">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="212" spans="1:68">
+      <c r="A212" s="1">
+        <v>211</v>
+      </c>
+      <c r="B212">
+        <v>7469080</v>
+      </c>
+      <c r="C212" t="s">
+        <v>68</v>
+      </c>
+      <c r="D212" t="s">
+        <v>69</v>
+      </c>
+      <c r="E212" s="2">
+        <v>45709.66666666666</v>
+      </c>
+      <c r="F212">
+        <v>24</v>
+      </c>
+      <c r="G212" t="s">
+        <v>72</v>
+      </c>
+      <c r="H212" t="s">
+        <v>70</v>
+      </c>
+      <c r="I212">
+        <v>2</v>
+      </c>
+      <c r="J212">
+        <v>0</v>
+      </c>
+      <c r="K212">
+        <v>2</v>
+      </c>
+      <c r="L212">
+        <v>3</v>
+      </c>
+      <c r="M212">
+        <v>0</v>
+      </c>
+      <c r="N212">
+        <v>3</v>
+      </c>
+      <c r="O212" t="s">
+        <v>225</v>
+      </c>
+      <c r="P212" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q212">
+        <v>2.65</v>
+      </c>
+      <c r="R212">
+        <v>2.04</v>
+      </c>
+      <c r="S212">
+        <v>4.6</v>
+      </c>
+      <c r="T212">
+        <v>1.5</v>
+      </c>
+      <c r="U212">
+        <v>2.45</v>
+      </c>
+      <c r="V212">
+        <v>3.2</v>
+      </c>
+      <c r="W212">
+        <v>1.31</v>
+      </c>
+      <c r="X212">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="Y212">
+        <v>1.01</v>
+      </c>
+      <c r="Z212">
+        <v>2.2</v>
+      </c>
+      <c r="AA212">
+        <v>3.15</v>
+      </c>
+      <c r="AB212">
+        <v>3.35</v>
+      </c>
+      <c r="AC212">
+        <v>1.09</v>
+      </c>
+      <c r="AD212">
+        <v>7</v>
+      </c>
+      <c r="AE212">
+        <v>1.41</v>
+      </c>
+      <c r="AF212">
+        <v>2.65</v>
+      </c>
+      <c r="AG212">
+        <v>2.15</v>
+      </c>
+      <c r="AH212">
+        <v>1.57</v>
+      </c>
+      <c r="AI212">
+        <v>1.98</v>
+      </c>
+      <c r="AJ212">
+        <v>1.75</v>
+      </c>
+      <c r="AK212">
+        <v>1.25</v>
+      </c>
+      <c r="AL212">
+        <v>1.32</v>
+      </c>
+      <c r="AM212">
+        <v>1.72</v>
+      </c>
+      <c r="AN212">
+        <v>2.25</v>
+      </c>
+      <c r="AO212">
+        <v>1.18</v>
+      </c>
+      <c r="AP212">
+        <v>2.31</v>
+      </c>
+      <c r="AQ212">
+        <v>1.08</v>
+      </c>
+      <c r="AR212">
+        <v>1.56</v>
+      </c>
+      <c r="AS212">
+        <v>1.37</v>
+      </c>
+      <c r="AT212">
+        <v>2.93</v>
+      </c>
+      <c r="AU212">
+        <v>10</v>
+      </c>
+      <c r="AV212">
+        <v>5</v>
+      </c>
+      <c r="AW212">
+        <v>6</v>
+      </c>
+      <c r="AX212">
+        <v>2</v>
+      </c>
+      <c r="AY212">
+        <v>16</v>
+      </c>
+      <c r="AZ212">
+        <v>7</v>
+      </c>
+      <c r="BA212">
+        <v>9</v>
+      </c>
+      <c r="BB212">
+        <v>4</v>
+      </c>
+      <c r="BC212">
+        <v>13</v>
+      </c>
+      <c r="BD212">
+        <v>1.68</v>
+      </c>
+      <c r="BE212">
+        <v>6.25</v>
+      </c>
+      <c r="BF212">
+        <v>2.48</v>
+      </c>
+      <c r="BG212">
+        <v>1.52</v>
+      </c>
+      <c r="BH212">
+        <v>2.33</v>
+      </c>
+      <c r="BI212">
+        <v>1.88</v>
+      </c>
+      <c r="BJ212">
+        <v>1.82</v>
+      </c>
+      <c r="BK212">
+        <v>2.38</v>
+      </c>
+      <c r="BL212">
+        <v>1.5</v>
+      </c>
+      <c r="BM212">
+        <v>3.15</v>
+      </c>
+      <c r="BN212">
+        <v>1.3</v>
+      </c>
+      <c r="BO212">
+        <v>4.1</v>
+      </c>
+      <c r="BP212">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="213" spans="1:68">
+      <c r="A213" s="1">
+        <v>212</v>
+      </c>
+      <c r="B213">
+        <v>7469077</v>
+      </c>
+      <c r="C213" t="s">
+        <v>68</v>
+      </c>
+      <c r="D213" t="s">
+        <v>69</v>
+      </c>
+      <c r="E213" s="2">
+        <v>45709.66666666666</v>
+      </c>
+      <c r="F213">
+        <v>24</v>
+      </c>
+      <c r="G213" t="s">
+        <v>74</v>
+      </c>
+      <c r="H213" t="s">
+        <v>75</v>
+      </c>
+      <c r="I213">
+        <v>1</v>
+      </c>
+      <c r="J213">
+        <v>0</v>
+      </c>
+      <c r="K213">
+        <v>1</v>
+      </c>
+      <c r="L213">
+        <v>1</v>
+      </c>
+      <c r="M213">
+        <v>1</v>
+      </c>
+      <c r="N213">
+        <v>2</v>
+      </c>
+      <c r="O213" t="s">
+        <v>226</v>
+      </c>
+      <c r="P213" t="s">
+        <v>307</v>
+      </c>
+      <c r="Q213">
+        <v>3.75</v>
+      </c>
+      <c r="R213">
+        <v>2.09</v>
+      </c>
+      <c r="S213">
+        <v>3</v>
+      </c>
+      <c r="T213">
+        <v>1.45</v>
+      </c>
+      <c r="U213">
+        <v>2.6</v>
+      </c>
+      <c r="V213">
+        <v>2.95</v>
+      </c>
+      <c r="W213">
+        <v>1.35</v>
+      </c>
+      <c r="X213">
+        <v>8.1</v>
+      </c>
+      <c r="Y213">
+        <v>1.02</v>
+      </c>
+      <c r="Z213">
+        <v>2.98</v>
+      </c>
+      <c r="AA213">
+        <v>3.15</v>
+      </c>
+      <c r="AB213">
+        <v>2.4</v>
+      </c>
+      <c r="AC213">
+        <v>1.07</v>
+      </c>
+      <c r="AD213">
+        <v>8</v>
+      </c>
+      <c r="AE213">
+        <v>1.34</v>
+      </c>
+      <c r="AF213">
+        <v>2.95</v>
+      </c>
+      <c r="AG213">
+        <v>1.95</v>
+      </c>
+      <c r="AH213">
+        <v>1.7</v>
+      </c>
+      <c r="AI213">
+        <v>1.8</v>
+      </c>
+      <c r="AJ213">
+        <v>1.92</v>
+      </c>
+      <c r="AK213">
+        <v>1.56</v>
+      </c>
+      <c r="AL213">
+        <v>1.32</v>
+      </c>
+      <c r="AM213">
+        <v>1.35</v>
+      </c>
+      <c r="AN213">
+        <v>2</v>
+      </c>
+      <c r="AO213">
+        <v>1.64</v>
+      </c>
+      <c r="AP213">
+        <v>1.92</v>
+      </c>
+      <c r="AQ213">
+        <v>1.58</v>
+      </c>
+      <c r="AR213">
+        <v>1.24</v>
+      </c>
+      <c r="AS213">
+        <v>1.35</v>
+      </c>
+      <c r="AT213">
+        <v>2.59</v>
+      </c>
+      <c r="AU213">
+        <v>7</v>
+      </c>
+      <c r="AV213">
+        <v>12</v>
+      </c>
+      <c r="AW213">
+        <v>3</v>
+      </c>
+      <c r="AX213">
+        <v>15</v>
+      </c>
+      <c r="AY213">
+        <v>10</v>
+      </c>
+      <c r="AZ213">
+        <v>27</v>
+      </c>
+      <c r="BA213">
+        <v>1</v>
+      </c>
+      <c r="BB213">
+        <v>6</v>
+      </c>
+      <c r="BC213">
+        <v>7</v>
+      </c>
+      <c r="BD213">
+        <v>2.18</v>
+      </c>
+      <c r="BE213">
+        <v>6.25</v>
+      </c>
+      <c r="BF213">
+        <v>1.83</v>
+      </c>
+      <c r="BG213">
+        <v>1.47</v>
+      </c>
+      <c r="BH213">
+        <v>2.48</v>
+      </c>
+      <c r="BI213">
+        <v>1.78</v>
+      </c>
+      <c r="BJ213">
+        <v>1.91</v>
+      </c>
+      <c r="BK213">
+        <v>2.23</v>
+      </c>
+      <c r="BL213">
+        <v>1.56</v>
+      </c>
+      <c r="BM213">
+        <v>2.9</v>
+      </c>
+      <c r="BN213">
+        <v>1.35</v>
+      </c>
+      <c r="BO213">
+        <v>3.9</v>
+      </c>
+      <c r="BP213">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="214" spans="1:68">
+      <c r="A214" s="1">
+        <v>213</v>
+      </c>
+      <c r="B214">
+        <v>7469079</v>
+      </c>
+      <c r="C214" t="s">
+        <v>68</v>
+      </c>
+      <c r="D214" t="s">
+        <v>69</v>
+      </c>
+      <c r="E214" s="2">
+        <v>45709.66666666666</v>
+      </c>
+      <c r="F214">
+        <v>24</v>
+      </c>
+      <c r="G214" t="s">
+        <v>77</v>
+      </c>
+      <c r="H214" t="s">
+        <v>84</v>
+      </c>
+      <c r="I214">
+        <v>1</v>
+      </c>
+      <c r="J214">
+        <v>0</v>
+      </c>
+      <c r="K214">
+        <v>1</v>
+      </c>
+      <c r="L214">
+        <v>2</v>
+      </c>
+      <c r="M214">
+        <v>0</v>
+      </c>
+      <c r="N214">
+        <v>2</v>
+      </c>
+      <c r="O214" t="s">
+        <v>227</v>
+      </c>
+      <c r="P214" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q214">
+        <v>3.7</v>
+      </c>
+      <c r="R214">
+        <v>2.05</v>
+      </c>
+      <c r="S214">
+        <v>2.75</v>
+      </c>
+      <c r="T214">
+        <v>1.41</v>
+      </c>
+      <c r="U214">
+        <v>2.65</v>
+      </c>
+      <c r="V214">
+        <v>2.85</v>
+      </c>
+      <c r="W214">
+        <v>1.37</v>
+      </c>
+      <c r="X214">
+        <v>7.5</v>
+      </c>
+      <c r="Y214">
+        <v>1.08</v>
+      </c>
+      <c r="Z214">
+        <v>3.58</v>
+      </c>
+      <c r="AA214">
+        <v>3.41</v>
+      </c>
+      <c r="AB214">
+        <v>2.01</v>
+      </c>
+      <c r="AC214">
+        <v>1.06</v>
+      </c>
+      <c r="AD214">
+        <v>8.5</v>
+      </c>
+      <c r="AE214">
+        <v>1.34</v>
+      </c>
+      <c r="AF214">
+        <v>2.95</v>
+      </c>
+      <c r="AG214">
+        <v>1.95</v>
+      </c>
+      <c r="AH214">
+        <v>1.7</v>
+      </c>
+      <c r="AI214">
+        <v>1.83</v>
+      </c>
+      <c r="AJ214">
+        <v>1.85</v>
+      </c>
+      <c r="AK214">
+        <v>1.63</v>
+      </c>
+      <c r="AL214">
+        <v>1.32</v>
+      </c>
+      <c r="AM214">
+        <v>1.33</v>
+      </c>
+      <c r="AN214">
+        <v>0.33</v>
+      </c>
+      <c r="AO214">
+        <v>1.42</v>
+      </c>
+      <c r="AP214">
+        <v>0.54</v>
+      </c>
+      <c r="AQ214">
+        <v>1.31</v>
+      </c>
+      <c r="AR214">
+        <v>1.01</v>
+      </c>
+      <c r="AS214">
+        <v>1.29</v>
+      </c>
+      <c r="AT214">
+        <v>2.3</v>
+      </c>
+      <c r="AU214">
+        <v>5</v>
+      </c>
+      <c r="AV214">
+        <v>4</v>
+      </c>
+      <c r="AW214">
+        <v>8</v>
+      </c>
+      <c r="AX214">
+        <v>9</v>
+      </c>
+      <c r="AY214">
+        <v>13</v>
+      </c>
+      <c r="AZ214">
+        <v>13</v>
+      </c>
+      <c r="BA214">
+        <v>2</v>
+      </c>
+      <c r="BB214">
+        <v>1</v>
+      </c>
+      <c r="BC214">
+        <v>3</v>
+      </c>
+      <c r="BD214">
+        <v>2.25</v>
+      </c>
+      <c r="BE214">
+        <v>6.25</v>
+      </c>
+      <c r="BF214">
+        <v>1.79</v>
+      </c>
+      <c r="BG214">
+        <v>1.45</v>
+      </c>
+      <c r="BH214">
+        <v>2.55</v>
+      </c>
+      <c r="BI214">
+        <v>1.74</v>
+      </c>
+      <c r="BJ214">
+        <v>1.96</v>
+      </c>
+      <c r="BK214">
+        <v>2.18</v>
+      </c>
+      <c r="BL214">
+        <v>1.58</v>
+      </c>
+      <c r="BM214">
+        <v>2.8</v>
+      </c>
+      <c r="BN214">
+        <v>1.37</v>
+      </c>
+      <c r="BO214">
+        <v>3.8</v>
+      </c>
+      <c r="BP214">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1346" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="311">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -700,6 +700,9 @@
     <t>['17', '90+7']</t>
   </si>
   <si>
+    <t>['10', '59']</t>
+  </si>
+  <si>
     <t>['16', '45+2']</t>
   </si>
   <si>
@@ -938,6 +941,12 @@
   </si>
   <si>
     <t>['48']</t>
+  </si>
+  <si>
+    <t>['7', '71']</t>
+  </si>
+  <si>
+    <t>['87']</t>
   </si>
 </sst>
 </file>
@@ -1299,7 +1308,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP214"/>
+  <dimension ref="A1:BP217"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1555,7 +1564,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q2">
         <v>2.4</v>
@@ -1636,7 +1645,7 @@
         <v>1</v>
       </c>
       <c r="AQ2">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1967,7 +1976,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q4">
         <v>3.6</v>
@@ -2460,7 +2469,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ6">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2791,7 +2800,7 @@
         <v>90</v>
       </c>
       <c r="P8" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q8">
         <v>3.1</v>
@@ -3203,7 +3212,7 @@
         <v>94</v>
       </c>
       <c r="P10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q10">
         <v>2.6</v>
@@ -3281,7 +3290,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AQ10">
         <v>1</v>
@@ -3821,7 +3830,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q13">
         <v>3.1</v>
@@ -4439,7 +4448,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q16">
         <v>2.63</v>
@@ -4645,7 +4654,7 @@
         <v>99</v>
       </c>
       <c r="P17" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -4929,7 +4938,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2.82</v>
+        <v>2.58</v>
       </c>
       <c r="AQ18">
         <v>0.91</v>
@@ -5138,7 +5147,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ19">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5675,7 +5684,7 @@
         <v>103</v>
       </c>
       <c r="P22" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -6087,7 +6096,7 @@
         <v>105</v>
       </c>
       <c r="P24" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q24">
         <v>2.62</v>
@@ -6580,7 +6589,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ26">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR26">
         <v>1.19</v>
@@ -6911,7 +6920,7 @@
         <v>108</v>
       </c>
       <c r="P28" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q28">
         <v>2.6</v>
@@ -6989,10 +6998,10 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AQ28">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR28">
         <v>1.92</v>
@@ -7198,7 +7207,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ29">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR29">
         <v>1.48</v>
@@ -7401,7 +7410,7 @@
         <v>1.5</v>
       </c>
       <c r="AP30">
-        <v>2.82</v>
+        <v>2.58</v>
       </c>
       <c r="AQ30">
         <v>0.92</v>
@@ -8353,7 +8362,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q35">
         <v>3.3</v>
@@ -8559,7 +8568,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q36">
         <v>3.1</v>
@@ -8765,7 +8774,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q37">
         <v>3.4</v>
@@ -8971,7 +8980,7 @@
         <v>90</v>
       </c>
       <c r="P38" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q38">
         <v>3.2</v>
@@ -9177,7 +9186,7 @@
         <v>90</v>
       </c>
       <c r="P39" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q39">
         <v>3.4</v>
@@ -9589,7 +9598,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q41">
         <v>2.5</v>
@@ -9795,7 +9804,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q42">
         <v>3.25</v>
@@ -9876,7 +9885,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ42">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR42">
         <v>1.75</v>
@@ -10001,7 +10010,7 @@
         <v>90</v>
       </c>
       <c r="P43" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q43">
         <v>2.75</v>
@@ -10082,7 +10091,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ43">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR43">
         <v>0.8</v>
@@ -10288,7 +10297,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ44">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR44">
         <v>1.25</v>
@@ -10697,7 +10706,7 @@
         <v>1.5</v>
       </c>
       <c r="AP46">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AQ46">
         <v>1.5</v>
@@ -11315,7 +11324,7 @@
         <v>1.5</v>
       </c>
       <c r="AP49">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AQ49">
         <v>1.27</v>
@@ -12061,7 +12070,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -12267,7 +12276,7 @@
         <v>129</v>
       </c>
       <c r="P54" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q54">
         <v>2.55</v>
@@ -12473,7 +12482,7 @@
         <v>130</v>
       </c>
       <c r="P55" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q55">
         <v>2.55</v>
@@ -12554,7 +12563,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ55">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR55">
         <v>1.98</v>
@@ -12757,10 +12766,10 @@
         <v>0.33</v>
       </c>
       <c r="AP56">
-        <v>2.82</v>
+        <v>2.58</v>
       </c>
       <c r="AQ56">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR56">
         <v>1.76</v>
@@ -12885,7 +12894,7 @@
         <v>132</v>
       </c>
       <c r="P57" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -12966,7 +12975,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ57">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR57">
         <v>1.54</v>
@@ -13297,7 +13306,7 @@
         <v>134</v>
       </c>
       <c r="P59" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q59">
         <v>2.62</v>
@@ -13503,7 +13512,7 @@
         <v>135</v>
       </c>
       <c r="P60" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q60">
         <v>2.88</v>
@@ -13915,7 +13924,7 @@
         <v>137</v>
       </c>
       <c r="P62" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q62">
         <v>3.6</v>
@@ -14121,7 +14130,7 @@
         <v>138</v>
       </c>
       <c r="P63" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q63">
         <v>3.75</v>
@@ -14614,7 +14623,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ65">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR65">
         <v>1.6</v>
@@ -15151,7 +15160,7 @@
         <v>143</v>
       </c>
       <c r="P68" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15357,7 +15366,7 @@
         <v>144</v>
       </c>
       <c r="P69" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15563,7 +15572,7 @@
         <v>145</v>
       </c>
       <c r="P70" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q70">
         <v>3.75</v>
@@ -15975,7 +15984,7 @@
         <v>147</v>
       </c>
       <c r="P72" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16053,7 +16062,7 @@
         <v>0</v>
       </c>
       <c r="AP72">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AQ72">
         <v>0.58</v>
@@ -16181,7 +16190,7 @@
         <v>90</v>
       </c>
       <c r="P73" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q73">
         <v>4.33</v>
@@ -16387,7 +16396,7 @@
         <v>90</v>
       </c>
       <c r="P74" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q74">
         <v>2.4</v>
@@ -16468,7 +16477,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ74">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR74">
         <v>1.85</v>
@@ -16593,7 +16602,7 @@
         <v>148</v>
       </c>
       <c r="P75" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q75">
         <v>3.5</v>
@@ -16799,7 +16808,7 @@
         <v>149</v>
       </c>
       <c r="P76" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q76">
         <v>2.88</v>
@@ -17417,7 +17426,7 @@
         <v>151</v>
       </c>
       <c r="P79" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17498,7 +17507,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ79">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR79">
         <v>1.66</v>
@@ -17623,7 +17632,7 @@
         <v>152</v>
       </c>
       <c r="P80" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q80">
         <v>2.05</v>
@@ -17701,7 +17710,7 @@
         <v>1.5</v>
       </c>
       <c r="AP80">
-        <v>2.82</v>
+        <v>2.58</v>
       </c>
       <c r="AQ80">
         <v>1.31</v>
@@ -17829,7 +17838,7 @@
         <v>90</v>
       </c>
       <c r="P81" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q81">
         <v>4.33</v>
@@ -18528,7 +18537,7 @@
         <v>2</v>
       </c>
       <c r="AQ84">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR84">
         <v>1.51</v>
@@ -18653,7 +18662,7 @@
         <v>90</v>
       </c>
       <c r="P85" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q85">
         <v>3.1</v>
@@ -18859,7 +18868,7 @@
         <v>156</v>
       </c>
       <c r="P86" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -19349,7 +19358,7 @@
         <v>1.5</v>
       </c>
       <c r="AP88">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AQ88">
         <v>1.58</v>
@@ -19683,7 +19692,7 @@
         <v>90</v>
       </c>
       <c r="P90" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q90">
         <v>2.38</v>
@@ -19970,7 +19979,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ91">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR91">
         <v>1.25</v>
@@ -20095,7 +20104,7 @@
         <v>160</v>
       </c>
       <c r="P92" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20713,7 +20722,7 @@
         <v>162</v>
       </c>
       <c r="P95" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q95">
         <v>1.9</v>
@@ -20791,7 +20800,7 @@
         <v>1</v>
       </c>
       <c r="AP95">
-        <v>2.82</v>
+        <v>2.58</v>
       </c>
       <c r="AQ95">
         <v>1.36</v>
@@ -20919,7 +20928,7 @@
         <v>163</v>
       </c>
       <c r="P96" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q96">
         <v>2.75</v>
@@ -21331,7 +21340,7 @@
         <v>90</v>
       </c>
       <c r="P98" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q98">
         <v>4.75</v>
@@ -21618,7 +21627,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ99">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR99">
         <v>1.8</v>
@@ -22236,7 +22245,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ102">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR102">
         <v>1.45</v>
@@ -22567,7 +22576,7 @@
         <v>167</v>
       </c>
       <c r="P104" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q104">
         <v>2.25</v>
@@ -22854,7 +22863,7 @@
         <v>2</v>
       </c>
       <c r="AQ105">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR105">
         <v>1.41</v>
@@ -23391,7 +23400,7 @@
         <v>90</v>
       </c>
       <c r="P108" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q108">
         <v>4.5</v>
@@ -24215,7 +24224,7 @@
         <v>173</v>
       </c>
       <c r="P112" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q112">
         <v>3.5</v>
@@ -24627,7 +24636,7 @@
         <v>90</v>
       </c>
       <c r="P114" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q114">
         <v>2.85</v>
@@ -25039,7 +25048,7 @@
         <v>175</v>
       </c>
       <c r="P116" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q116">
         <v>2.4</v>
@@ -25117,7 +25126,7 @@
         <v>1.2</v>
       </c>
       <c r="AP116">
-        <v>2.82</v>
+        <v>2.58</v>
       </c>
       <c r="AQ116">
         <v>1.58</v>
@@ -25323,7 +25332,7 @@
         <v>0.8</v>
       </c>
       <c r="AP117">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AQ117">
         <v>0.36</v>
@@ -25451,7 +25460,7 @@
         <v>90</v>
       </c>
       <c r="P118" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q118">
         <v>4</v>
@@ -25532,7 +25541,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ118">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR118">
         <v>0.99</v>
@@ -26069,7 +26078,7 @@
         <v>178</v>
       </c>
       <c r="P121" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q121">
         <v>2.88</v>
@@ -27180,7 +27189,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ126">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR126">
         <v>1.58</v>
@@ -27589,7 +27598,7 @@
         <v>1</v>
       </c>
       <c r="AP128">
-        <v>2.82</v>
+        <v>2.58</v>
       </c>
       <c r="AQ128">
         <v>1</v>
@@ -28004,7 +28013,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ130">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR130">
         <v>1.89</v>
@@ -28747,7 +28756,7 @@
         <v>90</v>
       </c>
       <c r="P134" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q134">
         <v>3.2</v>
@@ -28953,7 +28962,7 @@
         <v>90</v>
       </c>
       <c r="P135" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q135">
         <v>5</v>
@@ -29237,7 +29246,7 @@
         <v>1.17</v>
       </c>
       <c r="AP136">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AQ136">
         <v>1.36</v>
@@ -29652,7 +29661,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ138">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR138">
         <v>1.44</v>
@@ -29983,7 +29992,7 @@
         <v>188</v>
       </c>
       <c r="P140" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q140">
         <v>2.95</v>
@@ -30189,7 +30198,7 @@
         <v>189</v>
       </c>
       <c r="P141" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q141">
         <v>2.8</v>
@@ -30270,7 +30279,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ141">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR141">
         <v>1.72</v>
@@ -30473,7 +30482,7 @@
         <v>2.13</v>
       </c>
       <c r="AP142">
-        <v>2.82</v>
+        <v>2.58</v>
       </c>
       <c r="AQ142">
         <v>1.67</v>
@@ -31013,7 +31022,7 @@
         <v>192</v>
       </c>
       <c r="P145" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q145">
         <v>2.75</v>
@@ -31219,7 +31228,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q146">
         <v>3.75</v>
@@ -31425,7 +31434,7 @@
         <v>129</v>
       </c>
       <c r="P147" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q147">
         <v>3.75</v>
@@ -31631,7 +31640,7 @@
         <v>90</v>
       </c>
       <c r="P148" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q148">
         <v>2.4</v>
@@ -31837,7 +31846,7 @@
         <v>90</v>
       </c>
       <c r="P149" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q149">
         <v>3.1</v>
@@ -32249,7 +32258,7 @@
         <v>194</v>
       </c>
       <c r="P151" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q151">
         <v>1.62</v>
@@ -32533,10 +32542,10 @@
         <v>0.63</v>
       </c>
       <c r="AP152">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AQ152">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR152">
         <v>1.6</v>
@@ -32661,7 +32670,7 @@
         <v>95</v>
       </c>
       <c r="P153" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q153">
         <v>2.63</v>
@@ -33485,7 +33494,7 @@
         <v>197</v>
       </c>
       <c r="P157" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q157">
         <v>2.7</v>
@@ -33691,7 +33700,7 @@
         <v>96</v>
       </c>
       <c r="P158" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q158">
         <v>2.55</v>
@@ -33897,7 +33906,7 @@
         <v>198</v>
       </c>
       <c r="P159" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q159">
         <v>3.3</v>
@@ -34103,7 +34112,7 @@
         <v>90</v>
       </c>
       <c r="P160" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q160">
         <v>2.75</v>
@@ -34596,7 +34605,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ162">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR162">
         <v>1.68</v>
@@ -34799,7 +34808,7 @@
         <v>1.38</v>
       </c>
       <c r="AP163">
-        <v>2.82</v>
+        <v>2.58</v>
       </c>
       <c r="AQ163">
         <v>1.45</v>
@@ -35545,7 +35554,7 @@
         <v>109</v>
       </c>
       <c r="P167" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q167">
         <v>3.35</v>
@@ -35626,7 +35635,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ167">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR167">
         <v>1.14</v>
@@ -35957,7 +35966,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q169">
         <v>2.8</v>
@@ -36038,7 +36047,7 @@
         <v>1</v>
       </c>
       <c r="AQ169">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR169">
         <v>1.32</v>
@@ -36163,7 +36172,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q170">
         <v>3</v>
@@ -36241,7 +36250,7 @@
         <v>1.89</v>
       </c>
       <c r="AP170">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AQ170">
         <v>1.67</v>
@@ -36575,7 +36584,7 @@
         <v>90</v>
       </c>
       <c r="P172" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q172">
         <v>2.63</v>
@@ -36781,7 +36790,7 @@
         <v>207</v>
       </c>
       <c r="P173" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q173">
         <v>2.3</v>
@@ -36862,7 +36871,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ173">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR173">
         <v>1.78</v>
@@ -37068,7 +37077,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ174">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR174">
         <v>1.67</v>
@@ -37683,7 +37692,7 @@
         <v>0.78</v>
       </c>
       <c r="AP177">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AQ177">
         <v>0.91</v>
@@ -37811,7 +37820,7 @@
         <v>90</v>
       </c>
       <c r="P178" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q178">
         <v>3.25</v>
@@ -38223,7 +38232,7 @@
         <v>212</v>
       </c>
       <c r="P180" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q180">
         <v>2.2</v>
@@ -38301,7 +38310,7 @@
         <v>1.44</v>
       </c>
       <c r="AP180">
-        <v>2.82</v>
+        <v>2.58</v>
       </c>
       <c r="AQ180">
         <v>1.08</v>
@@ -38429,7 +38438,7 @@
         <v>90</v>
       </c>
       <c r="P181" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q181">
         <v>3.25</v>
@@ -39334,7 +39343,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ185">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR185">
         <v>1.51</v>
@@ -39665,7 +39674,7 @@
         <v>90</v>
       </c>
       <c r="P187" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q187">
         <v>2.55</v>
@@ -39746,7 +39755,7 @@
         <v>1</v>
       </c>
       <c r="AQ187">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR187">
         <v>1.32</v>
@@ -39871,7 +39880,7 @@
         <v>215</v>
       </c>
       <c r="P188" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q188">
         <v>4.5</v>
@@ -40283,7 +40292,7 @@
         <v>90</v>
       </c>
       <c r="P190" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q190">
         <v>3.3</v>
@@ -40489,7 +40498,7 @@
         <v>90</v>
       </c>
       <c r="P191" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q191">
         <v>2.75</v>
@@ -40695,7 +40704,7 @@
         <v>90</v>
       </c>
       <c r="P192" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q192">
         <v>3.25</v>
@@ -41188,7 +41197,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ194">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR194">
         <v>1.83</v>
@@ -41313,7 +41322,7 @@
         <v>214</v>
       </c>
       <c r="P195" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q195">
         <v>4.75</v>
@@ -41519,7 +41528,7 @@
         <v>90</v>
       </c>
       <c r="P196" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q196">
         <v>3.65</v>
@@ -41725,7 +41734,7 @@
         <v>218</v>
       </c>
       <c r="P197" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q197">
         <v>1.94</v>
@@ -41803,7 +41812,7 @@
         <v>0.6</v>
       </c>
       <c r="AP197">
-        <v>2.82</v>
+        <v>2.58</v>
       </c>
       <c r="AQ197">
         <v>0.58</v>
@@ -42009,7 +42018,7 @@
         <v>1.3</v>
       </c>
       <c r="AP198">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AQ198">
         <v>1.08</v>
@@ -42137,7 +42146,7 @@
         <v>90</v>
       </c>
       <c r="P199" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q199">
         <v>3.75</v>
@@ -43042,7 +43051,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ203">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR203">
         <v>1.24</v>
@@ -43167,7 +43176,7 @@
         <v>160</v>
       </c>
       <c r="P204" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q204">
         <v>3</v>
@@ -43373,7 +43382,7 @@
         <v>90</v>
       </c>
       <c r="P205" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q205">
         <v>2.75</v>
@@ -43785,7 +43794,7 @@
         <v>90</v>
       </c>
       <c r="P207" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q207">
         <v>3.8</v>
@@ -45021,7 +45030,7 @@
         <v>226</v>
       </c>
       <c r="P213" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q213">
         <v>3.75</v>
@@ -45384,6 +45393,624 @@
       </c>
       <c r="BP214">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="215" spans="1:68">
+      <c r="A215" s="1">
+        <v>214</v>
+      </c>
+      <c r="B215">
+        <v>7469076</v>
+      </c>
+      <c r="C215" t="s">
+        <v>68</v>
+      </c>
+      <c r="D215" t="s">
+        <v>69</v>
+      </c>
+      <c r="E215" s="2">
+        <v>45710.41666666666</v>
+      </c>
+      <c r="F215">
+        <v>24</v>
+      </c>
+      <c r="G215" t="s">
+        <v>76</v>
+      </c>
+      <c r="H215" t="s">
+        <v>82</v>
+      </c>
+      <c r="I215">
+        <v>1</v>
+      </c>
+      <c r="J215">
+        <v>1</v>
+      </c>
+      <c r="K215">
+        <v>2</v>
+      </c>
+      <c r="L215">
+        <v>2</v>
+      </c>
+      <c r="M215">
+        <v>2</v>
+      </c>
+      <c r="N215">
+        <v>4</v>
+      </c>
+      <c r="O215" t="s">
+        <v>228</v>
+      </c>
+      <c r="P215" t="s">
+        <v>309</v>
+      </c>
+      <c r="Q215">
+        <v>2.95</v>
+      </c>
+      <c r="R215">
+        <v>2.05</v>
+      </c>
+      <c r="S215">
+        <v>3.4</v>
+      </c>
+      <c r="T215">
+        <v>1.4</v>
+      </c>
+      <c r="U215">
+        <v>2.7</v>
+      </c>
+      <c r="V215">
+        <v>2.75</v>
+      </c>
+      <c r="W215">
+        <v>1.39</v>
+      </c>
+      <c r="X215">
+        <v>7</v>
+      </c>
+      <c r="Y215">
+        <v>1.08</v>
+      </c>
+      <c r="Z215">
+        <v>2.71</v>
+      </c>
+      <c r="AA215">
+        <v>3.26</v>
+      </c>
+      <c r="AB215">
+        <v>2.54</v>
+      </c>
+      <c r="AC215">
+        <v>1.06</v>
+      </c>
+      <c r="AD215">
+        <v>8.5</v>
+      </c>
+      <c r="AE215">
+        <v>1.33</v>
+      </c>
+      <c r="AF215">
+        <v>3.25</v>
+      </c>
+      <c r="AG215">
+        <v>1.95</v>
+      </c>
+      <c r="AH215">
+        <v>1.79</v>
+      </c>
+      <c r="AI215">
+        <v>1.72</v>
+      </c>
+      <c r="AJ215">
+        <v>1.98</v>
+      </c>
+      <c r="AK215">
+        <v>1.39</v>
+      </c>
+      <c r="AL215">
+        <v>1.32</v>
+      </c>
+      <c r="AM215">
+        <v>1.53</v>
+      </c>
+      <c r="AN215">
+        <v>0.92</v>
+      </c>
+      <c r="AO215">
+        <v>0.83</v>
+      </c>
+      <c r="AP215">
+        <v>0.92</v>
+      </c>
+      <c r="AQ215">
+        <v>0.85</v>
+      </c>
+      <c r="AR215">
+        <v>1.26</v>
+      </c>
+      <c r="AS215">
+        <v>1.43</v>
+      </c>
+      <c r="AT215">
+        <v>2.69</v>
+      </c>
+      <c r="AU215">
+        <v>5</v>
+      </c>
+      <c r="AV215">
+        <v>4</v>
+      </c>
+      <c r="AW215">
+        <v>6</v>
+      </c>
+      <c r="AX215">
+        <v>7</v>
+      </c>
+      <c r="AY215">
+        <v>11</v>
+      </c>
+      <c r="AZ215">
+        <v>11</v>
+      </c>
+      <c r="BA215">
+        <v>5</v>
+      </c>
+      <c r="BB215">
+        <v>2</v>
+      </c>
+      <c r="BC215">
+        <v>7</v>
+      </c>
+      <c r="BD215">
+        <v>1.9</v>
+      </c>
+      <c r="BE215">
+        <v>6.4</v>
+      </c>
+      <c r="BF215">
+        <v>2.07</v>
+      </c>
+      <c r="BG215">
+        <v>1.27</v>
+      </c>
+      <c r="BH215">
+        <v>3.3</v>
+      </c>
+      <c r="BI215">
+        <v>1.47</v>
+      </c>
+      <c r="BJ215">
+        <v>2.48</v>
+      </c>
+      <c r="BK215">
+        <v>1.76</v>
+      </c>
+      <c r="BL215">
+        <v>1.94</v>
+      </c>
+      <c r="BM215">
+        <v>2.17</v>
+      </c>
+      <c r="BN215">
+        <v>1.6</v>
+      </c>
+      <c r="BO215">
+        <v>2.7</v>
+      </c>
+      <c r="BP215">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="216" spans="1:68">
+      <c r="A216" s="1">
+        <v>215</v>
+      </c>
+      <c r="B216">
+        <v>7469073</v>
+      </c>
+      <c r="C216" t="s">
+        <v>68</v>
+      </c>
+      <c r="D216" t="s">
+        <v>69</v>
+      </c>
+      <c r="E216" s="2">
+        <v>45710.41666666666</v>
+      </c>
+      <c r="F216">
+        <v>24</v>
+      </c>
+      <c r="G216" t="s">
+        <v>86</v>
+      </c>
+      <c r="H216" t="s">
+        <v>80</v>
+      </c>
+      <c r="I216">
+        <v>0</v>
+      </c>
+      <c r="J216">
+        <v>0</v>
+      </c>
+      <c r="K216">
+        <v>0</v>
+      </c>
+      <c r="L216">
+        <v>0</v>
+      </c>
+      <c r="M216">
+        <v>1</v>
+      </c>
+      <c r="N216">
+        <v>1</v>
+      </c>
+      <c r="O216" t="s">
+        <v>90</v>
+      </c>
+      <c r="P216" t="s">
+        <v>310</v>
+      </c>
+      <c r="Q216">
+        <v>1.96</v>
+      </c>
+      <c r="R216">
+        <v>2.38</v>
+      </c>
+      <c r="S216">
+        <v>6.6</v>
+      </c>
+      <c r="T216">
+        <v>1.36</v>
+      </c>
+      <c r="U216">
+        <v>2.95</v>
+      </c>
+      <c r="V216">
+        <v>2.6</v>
+      </c>
+      <c r="W216">
+        <v>1.44</v>
+      </c>
+      <c r="X216">
+        <v>6.3</v>
+      </c>
+      <c r="Y216">
+        <v>1.09</v>
+      </c>
+      <c r="Z216">
+        <v>1.46</v>
+      </c>
+      <c r="AA216">
+        <v>4.3</v>
+      </c>
+      <c r="AB216">
+        <v>6.6</v>
+      </c>
+      <c r="AC216">
+        <v>1.01</v>
+      </c>
+      <c r="AD216">
+        <v>11.9</v>
+      </c>
+      <c r="AE216">
+        <v>1.28</v>
+      </c>
+      <c r="AF216">
+        <v>3.58</v>
+      </c>
+      <c r="AG216">
+        <v>1.85</v>
+      </c>
+      <c r="AH216">
+        <v>1.89</v>
+      </c>
+      <c r="AI216">
+        <v>1.98</v>
+      </c>
+      <c r="AJ216">
+        <v>1.74</v>
+      </c>
+      <c r="AK216">
+        <v>1.12</v>
+      </c>
+      <c r="AL216">
+        <v>1.19</v>
+      </c>
+      <c r="AM216">
+        <v>2.5</v>
+      </c>
+      <c r="AN216">
+        <v>2.82</v>
+      </c>
+      <c r="AO216">
+        <v>1.33</v>
+      </c>
+      <c r="AP216">
+        <v>2.58</v>
+      </c>
+      <c r="AQ216">
+        <v>1.46</v>
+      </c>
+      <c r="AR216">
+        <v>1.78</v>
+      </c>
+      <c r="AS216">
+        <v>1.12</v>
+      </c>
+      <c r="AT216">
+        <v>2.9</v>
+      </c>
+      <c r="AU216">
+        <v>7</v>
+      </c>
+      <c r="AV216">
+        <v>4</v>
+      </c>
+      <c r="AW216">
+        <v>12</v>
+      </c>
+      <c r="AX216">
+        <v>4</v>
+      </c>
+      <c r="AY216">
+        <v>19</v>
+      </c>
+      <c r="AZ216">
+        <v>8</v>
+      </c>
+      <c r="BA216">
+        <v>4</v>
+      </c>
+      <c r="BB216">
+        <v>3</v>
+      </c>
+      <c r="BC216">
+        <v>7</v>
+      </c>
+      <c r="BD216">
+        <v>1.38</v>
+      </c>
+      <c r="BE216">
+        <v>7</v>
+      </c>
+      <c r="BF216">
+        <v>3.45</v>
+      </c>
+      <c r="BG216">
+        <v>1.26</v>
+      </c>
+      <c r="BH216">
+        <v>3.4</v>
+      </c>
+      <c r="BI216">
+        <v>1.47</v>
+      </c>
+      <c r="BJ216">
+        <v>2.48</v>
+      </c>
+      <c r="BK216">
+        <v>1.74</v>
+      </c>
+      <c r="BL216">
+        <v>1.96</v>
+      </c>
+      <c r="BM216">
+        <v>2.15</v>
+      </c>
+      <c r="BN216">
+        <v>1.61</v>
+      </c>
+      <c r="BO216">
+        <v>2.7</v>
+      </c>
+      <c r="BP216">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="217" spans="1:68">
+      <c r="A217" s="1">
+        <v>216</v>
+      </c>
+      <c r="B217">
+        <v>7469074</v>
+      </c>
+      <c r="C217" t="s">
+        <v>68</v>
+      </c>
+      <c r="D217" t="s">
+        <v>69</v>
+      </c>
+      <c r="E217" s="2">
+        <v>45710.66666666666</v>
+      </c>
+      <c r="F217">
+        <v>24</v>
+      </c>
+      <c r="G217" t="s">
+        <v>78</v>
+      </c>
+      <c r="H217" t="s">
+        <v>71</v>
+      </c>
+      <c r="I217">
+        <v>0</v>
+      </c>
+      <c r="J217">
+        <v>0</v>
+      </c>
+      <c r="K217">
+        <v>0</v>
+      </c>
+      <c r="L217">
+        <v>0</v>
+      </c>
+      <c r="M217">
+        <v>1</v>
+      </c>
+      <c r="N217">
+        <v>1</v>
+      </c>
+      <c r="O217" t="s">
+        <v>90</v>
+      </c>
+      <c r="P217" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q217">
+        <v>2.06</v>
+      </c>
+      <c r="R217">
+        <v>2.23</v>
+      </c>
+      <c r="S217">
+        <v>6.8</v>
+      </c>
+      <c r="T217">
+        <v>1.43</v>
+      </c>
+      <c r="U217">
+        <v>2.65</v>
+      </c>
+      <c r="V217">
+        <v>2.95</v>
+      </c>
+      <c r="W217">
+        <v>1.35</v>
+      </c>
+      <c r="X217">
+        <v>7.6</v>
+      </c>
+      <c r="Y217">
+        <v>1.03</v>
+      </c>
+      <c r="Z217">
+        <v>1.51</v>
+      </c>
+      <c r="AA217">
+        <v>3.94</v>
+      </c>
+      <c r="AB217">
+        <v>6.6</v>
+      </c>
+      <c r="AC217">
+        <v>1.06</v>
+      </c>
+      <c r="AD217">
+        <v>8.5</v>
+      </c>
+      <c r="AE217">
+        <v>1.36</v>
+      </c>
+      <c r="AF217">
+        <v>2.85</v>
+      </c>
+      <c r="AG217">
+        <v>2.05</v>
+      </c>
+      <c r="AH217">
+        <v>1.65</v>
+      </c>
+      <c r="AI217">
+        <v>2.19</v>
+      </c>
+      <c r="AJ217">
+        <v>1.61</v>
+      </c>
+      <c r="AK217">
+        <v>1.12</v>
+      </c>
+      <c r="AL217">
+        <v>1.22</v>
+      </c>
+      <c r="AM217">
+        <v>2.38</v>
+      </c>
+      <c r="AN217">
+        <v>2.33</v>
+      </c>
+      <c r="AO217">
+        <v>0.64</v>
+      </c>
+      <c r="AP217">
+        <v>2.15</v>
+      </c>
+      <c r="AQ217">
+        <v>0.83</v>
+      </c>
+      <c r="AR217">
+        <v>1.74</v>
+      </c>
+      <c r="AS217">
+        <v>1.03</v>
+      </c>
+      <c r="AT217">
+        <v>2.77</v>
+      </c>
+      <c r="AU217">
+        <v>4</v>
+      </c>
+      <c r="AV217">
+        <v>3</v>
+      </c>
+      <c r="AW217">
+        <v>13</v>
+      </c>
+      <c r="AX217">
+        <v>4</v>
+      </c>
+      <c r="AY217">
+        <v>17</v>
+      </c>
+      <c r="AZ217">
+        <v>7</v>
+      </c>
+      <c r="BA217">
+        <v>4</v>
+      </c>
+      <c r="BB217">
+        <v>2</v>
+      </c>
+      <c r="BC217">
+        <v>6</v>
+      </c>
+      <c r="BD217">
+        <v>1.41</v>
+      </c>
+      <c r="BE217">
+        <v>6.75</v>
+      </c>
+      <c r="BF217">
+        <v>3.3</v>
+      </c>
+      <c r="BG217">
+        <v>1.52</v>
+      </c>
+      <c r="BH217">
+        <v>2.33</v>
+      </c>
+      <c r="BI217">
+        <v>1.86</v>
+      </c>
+      <c r="BJ217">
+        <v>1.82</v>
+      </c>
+      <c r="BK217">
+        <v>2.33</v>
+      </c>
+      <c r="BL217">
+        <v>1.5</v>
+      </c>
+      <c r="BM217">
+        <v>3.05</v>
+      </c>
+      <c r="BN217">
+        <v>1.3</v>
+      </c>
+      <c r="BO217">
+        <v>4.1</v>
+      </c>
+      <c r="BP217">
+        <v>1.19</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1394" uniqueCount="314">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -703,6 +703,12 @@
     <t>['10', '59']</t>
   </si>
   <si>
+    <t>['19', '61']</t>
+  </si>
+  <si>
+    <t>['12', '53']</t>
+  </si>
+  <si>
     <t>['16', '45+2']</t>
   </si>
   <si>
@@ -947,6 +953,9 @@
   </si>
   <si>
     <t>['87']</t>
+  </si>
+  <si>
+    <t>['10', '57', '62']</t>
   </si>
 </sst>
 </file>
@@ -1308,7 +1317,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP217"/>
+  <dimension ref="A1:BP222"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1564,7 +1573,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q2">
         <v>2.4</v>
@@ -1642,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ2">
         <v>0.85</v>
@@ -1976,7 +1985,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q4">
         <v>3.6</v>
@@ -2800,7 +2809,7 @@
         <v>90</v>
       </c>
       <c r="P8" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q8">
         <v>3.1</v>
@@ -2881,7 +2890,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ8">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3212,7 +3221,7 @@
         <v>94</v>
       </c>
       <c r="P10" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q10">
         <v>2.6</v>
@@ -3293,7 +3302,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ10">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3496,7 +3505,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ11">
         <v>1.08</v>
@@ -3702,7 +3711,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ12">
         <v>1.58</v>
@@ -3830,7 +3839,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q13">
         <v>3.1</v>
@@ -4114,10 +4123,10 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ14">
-        <v>0.36</v>
+        <v>0.58</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4448,7 +4457,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q16">
         <v>2.63</v>
@@ -4526,10 +4535,10 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ16">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4654,7 +4663,7 @@
         <v>99</v>
       </c>
       <c r="P17" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -4941,7 +4950,7 @@
         <v>2.58</v>
       </c>
       <c r="AQ18">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5556,10 +5565,10 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ21">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR21">
         <v>1.81</v>
@@ -5684,7 +5693,7 @@
         <v>103</v>
       </c>
       <c r="P22" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -6096,7 +6105,7 @@
         <v>105</v>
       </c>
       <c r="P24" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q24">
         <v>2.62</v>
@@ -6383,7 +6392,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ25">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR25">
         <v>0.67</v>
@@ -6920,7 +6929,7 @@
         <v>108</v>
       </c>
       <c r="P28" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q28">
         <v>2.6</v>
@@ -7204,7 +7213,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ29">
         <v>0.83</v>
@@ -7616,7 +7625,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ31">
         <v>1.36</v>
@@ -7822,10 +7831,10 @@
         <v>3</v>
       </c>
       <c r="AP32">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ32">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR32">
         <v>0.82</v>
@@ -8028,7 +8037,7 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ33">
         <v>0.58</v>
@@ -8362,7 +8371,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q35">
         <v>3.3</v>
@@ -8568,7 +8577,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q36">
         <v>3.1</v>
@@ -8774,7 +8783,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q37">
         <v>3.4</v>
@@ -8855,7 +8864,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ37">
-        <v>0.36</v>
+        <v>0.58</v>
       </c>
       <c r="AR37">
         <v>1.13</v>
@@ -8980,7 +8989,7 @@
         <v>90</v>
       </c>
       <c r="P38" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q38">
         <v>3.2</v>
@@ -9058,7 +9067,7 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ38">
         <v>1.08</v>
@@ -9186,7 +9195,7 @@
         <v>90</v>
       </c>
       <c r="P39" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q39">
         <v>3.4</v>
@@ -9267,7 +9276,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ39">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR39">
         <v>0.8</v>
@@ -9473,7 +9482,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ40">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR40">
         <v>1.41</v>
@@ -9598,7 +9607,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q41">
         <v>2.5</v>
@@ -9804,7 +9813,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q42">
         <v>3.25</v>
@@ -10010,7 +10019,7 @@
         <v>90</v>
       </c>
       <c r="P43" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q43">
         <v>2.75</v>
@@ -11118,7 +11127,7 @@
         <v>0.33</v>
       </c>
       <c r="AP48">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ48">
         <v>1</v>
@@ -11327,7 +11336,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ49">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR49">
         <v>1.53</v>
@@ -11736,7 +11745,7 @@
         <v>1.33</v>
       </c>
       <c r="AP51">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ51">
         <v>1.5</v>
@@ -11945,7 +11954,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ52">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR52">
         <v>1.34</v>
@@ -12070,7 +12079,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -12151,7 +12160,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ53">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR53">
         <v>1.76</v>
@@ -12276,7 +12285,7 @@
         <v>129</v>
       </c>
       <c r="P54" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q54">
         <v>2.55</v>
@@ -12354,7 +12363,7 @@
         <v>1</v>
       </c>
       <c r="AP54">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ54">
         <v>0.92</v>
@@ -12482,7 +12491,7 @@
         <v>130</v>
       </c>
       <c r="P55" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q55">
         <v>2.55</v>
@@ -12894,7 +12903,7 @@
         <v>132</v>
       </c>
       <c r="P57" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -12972,7 +12981,7 @@
         <v>0.67</v>
       </c>
       <c r="AP57">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ57">
         <v>0.85</v>
@@ -13306,7 +13315,7 @@
         <v>134</v>
       </c>
       <c r="P59" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q59">
         <v>2.62</v>
@@ -13512,7 +13521,7 @@
         <v>135</v>
       </c>
       <c r="P60" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q60">
         <v>2.88</v>
@@ -13924,7 +13933,7 @@
         <v>137</v>
       </c>
       <c r="P62" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q62">
         <v>3.6</v>
@@ -14005,7 +14014,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ62">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR62">
         <v>1.16</v>
@@ -14130,7 +14139,7 @@
         <v>138</v>
       </c>
       <c r="P63" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q63">
         <v>3.75</v>
@@ -14208,7 +14217,7 @@
         <v>3</v>
       </c>
       <c r="AP63">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ63">
         <v>1.45</v>
@@ -14417,7 +14426,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ64">
-        <v>0.36</v>
+        <v>0.58</v>
       </c>
       <c r="AR64">
         <v>1.73</v>
@@ -14826,7 +14835,7 @@
         <v>1</v>
       </c>
       <c r="AP66">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ66">
         <v>0.92</v>
@@ -15160,7 +15169,7 @@
         <v>143</v>
       </c>
       <c r="P68" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15241,7 +15250,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ68">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR68">
         <v>1.95</v>
@@ -15366,7 +15375,7 @@
         <v>144</v>
       </c>
       <c r="P69" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15447,7 +15456,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ69">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR69">
         <v>1.23</v>
@@ -15572,7 +15581,7 @@
         <v>145</v>
       </c>
       <c r="P70" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q70">
         <v>3.75</v>
@@ -15856,7 +15865,7 @@
         <v>2</v>
       </c>
       <c r="AP71">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ71">
         <v>1.58</v>
@@ -15984,7 +15993,7 @@
         <v>147</v>
       </c>
       <c r="P72" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16190,7 +16199,7 @@
         <v>90</v>
       </c>
       <c r="P73" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q73">
         <v>4.33</v>
@@ -16396,7 +16405,7 @@
         <v>90</v>
       </c>
       <c r="P74" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q74">
         <v>2.4</v>
@@ -16602,7 +16611,7 @@
         <v>148</v>
       </c>
       <c r="P75" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q75">
         <v>3.5</v>
@@ -16683,7 +16692,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ75">
-        <v>0.36</v>
+        <v>0.58</v>
       </c>
       <c r="AR75">
         <v>1.25</v>
@@ -16808,7 +16817,7 @@
         <v>149</v>
       </c>
       <c r="P76" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q76">
         <v>2.88</v>
@@ -16886,7 +16895,7 @@
         <v>1.33</v>
       </c>
       <c r="AP76">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ76">
         <v>1.36</v>
@@ -17426,7 +17435,7 @@
         <v>151</v>
       </c>
       <c r="P79" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17632,7 +17641,7 @@
         <v>152</v>
       </c>
       <c r="P80" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q80">
         <v>2.05</v>
@@ -17838,7 +17847,7 @@
         <v>90</v>
       </c>
       <c r="P81" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q81">
         <v>4.33</v>
@@ -17916,10 +17925,10 @@
         <v>2.25</v>
       </c>
       <c r="AP81">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ81">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR81">
         <v>1.22</v>
@@ -18122,10 +18131,10 @@
         <v>1.33</v>
       </c>
       <c r="AP82">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ82">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR82">
         <v>1.57</v>
@@ -18534,7 +18543,7 @@
         <v>1.4</v>
       </c>
       <c r="AP84">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ84">
         <v>1.46</v>
@@ -18662,7 +18671,7 @@
         <v>90</v>
       </c>
       <c r="P85" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q85">
         <v>3.1</v>
@@ -18740,7 +18749,7 @@
         <v>0</v>
       </c>
       <c r="AP85">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ85">
         <v>0.58</v>
@@ -18868,7 +18877,7 @@
         <v>156</v>
       </c>
       <c r="P86" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -19152,10 +19161,10 @@
         <v>1</v>
       </c>
       <c r="AP87">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ87">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR87">
         <v>1.28</v>
@@ -19567,7 +19576,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ89">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR89">
         <v>1.72</v>
@@ -19692,7 +19701,7 @@
         <v>90</v>
       </c>
       <c r="P90" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q90">
         <v>2.38</v>
@@ -19976,7 +19985,7 @@
         <v>1</v>
       </c>
       <c r="AP91">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ91">
         <v>0.85</v>
@@ -20104,7 +20113,7 @@
         <v>160</v>
       </c>
       <c r="P92" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20182,7 +20191,7 @@
         <v>1</v>
       </c>
       <c r="AP92">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ92">
         <v>1.08</v>
@@ -20722,7 +20731,7 @@
         <v>162</v>
       </c>
       <c r="P95" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q95">
         <v>1.9</v>
@@ -20928,7 +20937,7 @@
         <v>163</v>
       </c>
       <c r="P96" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q96">
         <v>2.75</v>
@@ -21215,7 +21224,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ97">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR97">
         <v>1.69</v>
@@ -21340,7 +21349,7 @@
         <v>90</v>
       </c>
       <c r="P98" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q98">
         <v>4.75</v>
@@ -21421,7 +21430,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ98">
-        <v>0.36</v>
+        <v>0.58</v>
       </c>
       <c r="AR98">
         <v>1.06</v>
@@ -22242,7 +22251,7 @@
         <v>1.17</v>
       </c>
       <c r="AP102">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ102">
         <v>1.46</v>
@@ -22448,7 +22457,7 @@
         <v>1.33</v>
       </c>
       <c r="AP103">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ103">
         <v>1.5</v>
@@ -22576,7 +22585,7 @@
         <v>167</v>
       </c>
       <c r="P104" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q104">
         <v>2.25</v>
@@ -22860,7 +22869,7 @@
         <v>0.83</v>
       </c>
       <c r="AP105">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ105">
         <v>0.85</v>
@@ -23069,7 +23078,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ106">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR106">
         <v>1.41</v>
@@ -23275,7 +23284,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ107">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR107">
         <v>1.74</v>
@@ -23400,7 +23409,7 @@
         <v>90</v>
       </c>
       <c r="P108" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q108">
         <v>4.5</v>
@@ -23687,7 +23696,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ109">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR109">
         <v>1.6</v>
@@ -24224,7 +24233,7 @@
         <v>173</v>
       </c>
       <c r="P112" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q112">
         <v>3.5</v>
@@ -24302,10 +24311,10 @@
         <v>1</v>
       </c>
       <c r="AP112">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ112">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR112">
         <v>1.26</v>
@@ -24636,7 +24645,7 @@
         <v>90</v>
       </c>
       <c r="P114" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q114">
         <v>2.85</v>
@@ -24920,10 +24929,10 @@
         <v>2.17</v>
       </c>
       <c r="AP115">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ115">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR115">
         <v>1.51</v>
@@ -25048,7 +25057,7 @@
         <v>175</v>
       </c>
       <c r="P116" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q116">
         <v>2.4</v>
@@ -25335,7 +25344,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ117">
-        <v>0.36</v>
+        <v>0.58</v>
       </c>
       <c r="AR117">
         <v>1.7</v>
@@ -25460,7 +25469,7 @@
         <v>90</v>
       </c>
       <c r="P118" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q118">
         <v>4</v>
@@ -25744,10 +25753,10 @@
         <v>0.5</v>
       </c>
       <c r="AP119">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ119">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR119">
         <v>1.46</v>
@@ -25950,7 +25959,7 @@
         <v>1.5</v>
       </c>
       <c r="AP120">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ120">
         <v>1.45</v>
@@ -26078,7 +26087,7 @@
         <v>178</v>
       </c>
       <c r="P121" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q121">
         <v>2.88</v>
@@ -26568,7 +26577,7 @@
         <v>1</v>
       </c>
       <c r="AP123">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ123">
         <v>0.92</v>
@@ -27395,7 +27404,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ127">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR127">
         <v>1.21</v>
@@ -28216,7 +28225,7 @@
         <v>1.17</v>
       </c>
       <c r="AP131">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ131">
         <v>1.08</v>
@@ -28425,7 +28434,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ132">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR132">
         <v>1.26</v>
@@ -28628,10 +28637,10 @@
         <v>0.67</v>
       </c>
       <c r="AP133">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ133">
-        <v>0.36</v>
+        <v>0.58</v>
       </c>
       <c r="AR133">
         <v>1.34</v>
@@ -28756,7 +28765,7 @@
         <v>90</v>
       </c>
       <c r="P134" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q134">
         <v>3.2</v>
@@ -28962,7 +28971,7 @@
         <v>90</v>
       </c>
       <c r="P135" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q135">
         <v>5</v>
@@ -29043,7 +29052,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ135">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR135">
         <v>1.14</v>
@@ -29658,7 +29667,7 @@
         <v>0.14</v>
       </c>
       <c r="AP138">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ138">
         <v>0.83</v>
@@ -29864,10 +29873,10 @@
         <v>1.33</v>
       </c>
       <c r="AP139">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ139">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR139">
         <v>1.46</v>
@@ -29992,7 +30001,7 @@
         <v>188</v>
       </c>
       <c r="P140" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q140">
         <v>2.95</v>
@@ -30070,7 +30079,7 @@
         <v>1.13</v>
       </c>
       <c r="AP140">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ140">
         <v>1.08</v>
@@ -30198,7 +30207,7 @@
         <v>189</v>
       </c>
       <c r="P141" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q141">
         <v>2.8</v>
@@ -30485,7 +30494,7 @@
         <v>2.58</v>
       </c>
       <c r="AQ142">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR142">
         <v>1.78</v>
@@ -30691,7 +30700,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ143">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR143">
         <v>1.16</v>
@@ -30894,7 +30903,7 @@
         <v>1.43</v>
       </c>
       <c r="AP144">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ144">
         <v>1.45</v>
@@ -31022,7 +31031,7 @@
         <v>192</v>
       </c>
       <c r="P145" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q145">
         <v>2.75</v>
@@ -31103,7 +31112,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ145">
-        <v>0.36</v>
+        <v>0.58</v>
       </c>
       <c r="AR145">
         <v>1.62</v>
@@ -31228,7 +31237,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q146">
         <v>3.75</v>
@@ -31309,7 +31318,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ146">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR146">
         <v>1.08</v>
@@ -31434,7 +31443,7 @@
         <v>129</v>
       </c>
       <c r="P147" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q147">
         <v>3.75</v>
@@ -31640,7 +31649,7 @@
         <v>90</v>
       </c>
       <c r="P148" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q148">
         <v>2.4</v>
@@ -31846,7 +31855,7 @@
         <v>90</v>
       </c>
       <c r="P149" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q149">
         <v>3.1</v>
@@ -32258,7 +32267,7 @@
         <v>194</v>
       </c>
       <c r="P151" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q151">
         <v>1.62</v>
@@ -32339,7 +32348,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ151">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR151">
         <v>1.79</v>
@@ -32670,7 +32679,7 @@
         <v>95</v>
       </c>
       <c r="P153" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q153">
         <v>2.63</v>
@@ -32954,7 +32963,7 @@
         <v>1.13</v>
       </c>
       <c r="AP154">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ154">
         <v>1.5</v>
@@ -33366,7 +33375,7 @@
         <v>1</v>
       </c>
       <c r="AP156">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ156">
         <v>1.36</v>
@@ -33494,7 +33503,7 @@
         <v>197</v>
       </c>
       <c r="P157" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q157">
         <v>2.7</v>
@@ -33700,7 +33709,7 @@
         <v>96</v>
       </c>
       <c r="P158" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q158">
         <v>2.55</v>
@@ -33778,7 +33787,7 @@
         <v>1.11</v>
       </c>
       <c r="AP158">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ158">
         <v>0.92</v>
@@ -33906,7 +33915,7 @@
         <v>198</v>
       </c>
       <c r="P159" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q159">
         <v>3.3</v>
@@ -33984,7 +33993,7 @@
         <v>1.13</v>
       </c>
       <c r="AP159">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ159">
         <v>1.58</v>
@@ -34112,7 +34121,7 @@
         <v>90</v>
       </c>
       <c r="P160" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q160">
         <v>2.75</v>
@@ -34193,7 +34202,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ160">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR160">
         <v>1.38</v>
@@ -35223,7 +35232,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ165">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR165">
         <v>1.13</v>
@@ -35429,7 +35438,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ166">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR166">
         <v>1.68</v>
@@ -35554,7 +35563,7 @@
         <v>109</v>
       </c>
       <c r="P167" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q167">
         <v>3.35</v>
@@ -35841,7 +35850,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ168">
-        <v>0.36</v>
+        <v>0.58</v>
       </c>
       <c r="AR168">
         <v>1.22</v>
@@ -35966,7 +35975,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q169">
         <v>2.8</v>
@@ -36044,7 +36053,7 @@
         <v>1.56</v>
       </c>
       <c r="AP169">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ169">
         <v>1.46</v>
@@ -36172,7 +36181,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q170">
         <v>3</v>
@@ -36253,7 +36262,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ170">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR170">
         <v>1.64</v>
@@ -36584,7 +36593,7 @@
         <v>90</v>
       </c>
       <c r="P172" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q172">
         <v>2.63</v>
@@ -36662,7 +36671,7 @@
         <v>1.22</v>
       </c>
       <c r="AP172">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ172">
         <v>1.31</v>
@@ -36790,7 +36799,7 @@
         <v>207</v>
       </c>
       <c r="P173" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q173">
         <v>2.3</v>
@@ -37486,7 +37495,7 @@
         <v>1</v>
       </c>
       <c r="AP176">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ176">
         <v>1</v>
@@ -37695,7 +37704,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ177">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR177">
         <v>1.6</v>
@@ -37820,7 +37829,7 @@
         <v>90</v>
       </c>
       <c r="P178" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q178">
         <v>3.25</v>
@@ -38232,7 +38241,7 @@
         <v>212</v>
       </c>
       <c r="P180" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q180">
         <v>2.2</v>
@@ -38438,7 +38447,7 @@
         <v>90</v>
       </c>
       <c r="P181" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q181">
         <v>3.25</v>
@@ -38516,7 +38525,7 @@
         <v>1</v>
       </c>
       <c r="AP181">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ181">
         <v>1.36</v>
@@ -38725,7 +38734,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ182">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR182">
         <v>1.62</v>
@@ -39340,7 +39349,7 @@
         <v>1.5</v>
       </c>
       <c r="AP185">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ185">
         <v>1.46</v>
@@ -39674,7 +39683,7 @@
         <v>90</v>
       </c>
       <c r="P187" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q187">
         <v>2.55</v>
@@ -39752,7 +39761,7 @@
         <v>0.4</v>
       </c>
       <c r="AP187">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ187">
         <v>0.83</v>
@@ -39880,7 +39889,7 @@
         <v>215</v>
       </c>
       <c r="P188" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q188">
         <v>4.5</v>
@@ -40164,10 +40173,10 @@
         <v>0.44</v>
       </c>
       <c r="AP189">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ189">
-        <v>0.36</v>
+        <v>0.58</v>
       </c>
       <c r="AR189">
         <v>1.73</v>
@@ -40292,7 +40301,7 @@
         <v>90</v>
       </c>
       <c r="P190" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q190">
         <v>3.3</v>
@@ -40373,7 +40382,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ190">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR190">
         <v>1.63</v>
@@ -40498,7 +40507,7 @@
         <v>90</v>
       </c>
       <c r="P191" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q191">
         <v>2.75</v>
@@ -40576,7 +40585,7 @@
         <v>1.27</v>
       </c>
       <c r="AP191">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ191">
         <v>1.31</v>
@@ -40704,7 +40713,7 @@
         <v>90</v>
       </c>
       <c r="P192" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q192">
         <v>3.25</v>
@@ -40785,7 +40794,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ192">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR192">
         <v>1.84</v>
@@ -41322,7 +41331,7 @@
         <v>214</v>
       </c>
       <c r="P195" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q195">
         <v>4.75</v>
@@ -41528,7 +41537,7 @@
         <v>90</v>
       </c>
       <c r="P196" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q196">
         <v>3.65</v>
@@ -41734,7 +41743,7 @@
         <v>218</v>
       </c>
       <c r="P197" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q197">
         <v>1.94</v>
@@ -42146,7 +42155,7 @@
         <v>90</v>
       </c>
       <c r="P199" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q199">
         <v>3.75</v>
@@ -42430,10 +42439,10 @@
         <v>1</v>
       </c>
       <c r="AP200">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ200">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR200">
         <v>1.39</v>
@@ -42636,7 +42645,7 @@
         <v>1.36</v>
       </c>
       <c r="AP201">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ201">
         <v>1.5</v>
@@ -42845,7 +42854,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ202">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR202">
         <v>1.2</v>
@@ -43176,7 +43185,7 @@
         <v>160</v>
       </c>
       <c r="P204" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q204">
         <v>3</v>
@@ -43257,7 +43266,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ204">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR204">
         <v>1.59</v>
@@ -43382,7 +43391,7 @@
         <v>90</v>
       </c>
       <c r="P205" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q205">
         <v>2.75</v>
@@ -43460,7 +43469,7 @@
         <v>0.91</v>
       </c>
       <c r="AP205">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ205">
         <v>1.08</v>
@@ -43669,7 +43678,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ206">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR206">
         <v>1.62</v>
@@ -43794,7 +43803,7 @@
         <v>90</v>
       </c>
       <c r="P207" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q207">
         <v>3.8</v>
@@ -44078,10 +44087,10 @@
         <v>0.4</v>
       </c>
       <c r="AP208">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ208">
-        <v>0.36</v>
+        <v>0.58</v>
       </c>
       <c r="AR208">
         <v>1.37</v>
@@ -45030,7 +45039,7 @@
         <v>226</v>
       </c>
       <c r="P213" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q213">
         <v>3.75</v>
@@ -45442,7 +45451,7 @@
         <v>228</v>
       </c>
       <c r="P215" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q215">
         <v>2.95</v>
@@ -45648,7 +45657,7 @@
         <v>90</v>
       </c>
       <c r="P216" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q216">
         <v>1.96</v>
@@ -46011,6 +46020,1036 @@
       </c>
       <c r="BP217">
         <v>1.19</v>
+      </c>
+    </row>
+    <row r="218" spans="1:68">
+      <c r="A218" s="1">
+        <v>217</v>
+      </c>
+      <c r="B218">
+        <v>7469083</v>
+      </c>
+      <c r="C218" t="s">
+        <v>68</v>
+      </c>
+      <c r="D218" t="s">
+        <v>69</v>
+      </c>
+      <c r="E218" s="2">
+        <v>45716.66666666666</v>
+      </c>
+      <c r="F218">
+        <v>25</v>
+      </c>
+      <c r="G218" t="s">
+        <v>82</v>
+      </c>
+      <c r="H218" t="s">
+        <v>74</v>
+      </c>
+      <c r="I218">
+        <v>0</v>
+      </c>
+      <c r="J218">
+        <v>0</v>
+      </c>
+      <c r="K218">
+        <v>0</v>
+      </c>
+      <c r="L218">
+        <v>1</v>
+      </c>
+      <c r="M218">
+        <v>0</v>
+      </c>
+      <c r="N218">
+        <v>1</v>
+      </c>
+      <c r="O218" t="s">
+        <v>199</v>
+      </c>
+      <c r="P218" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q218">
+        <v>2.42</v>
+      </c>
+      <c r="R218">
+        <v>2.25</v>
+      </c>
+      <c r="S218">
+        <v>4.4</v>
+      </c>
+      <c r="T218">
+        <v>1.37</v>
+      </c>
+      <c r="U218">
+        <v>2.9</v>
+      </c>
+      <c r="V218">
+        <v>2.6</v>
+      </c>
+      <c r="W218">
+        <v>1.44</v>
+      </c>
+      <c r="X218">
+        <v>6.1</v>
+      </c>
+      <c r="Y218">
+        <v>1.1</v>
+      </c>
+      <c r="Z218">
+        <v>1.92</v>
+      </c>
+      <c r="AA218">
+        <v>3.57</v>
+      </c>
+      <c r="AB218">
+        <v>3.71</v>
+      </c>
+      <c r="AC218">
+        <v>1.05</v>
+      </c>
+      <c r="AD218">
+        <v>9.5</v>
+      </c>
+      <c r="AE218">
+        <v>1.26</v>
+      </c>
+      <c r="AF218">
+        <v>3.5</v>
+      </c>
+      <c r="AG218">
+        <v>1.83</v>
+      </c>
+      <c r="AH218">
+        <v>1.91</v>
+      </c>
+      <c r="AI218">
+        <v>1.71</v>
+      </c>
+      <c r="AJ218">
+        <v>2.02</v>
+      </c>
+      <c r="AK218">
+        <v>1.25</v>
+      </c>
+      <c r="AL218">
+        <v>1.26</v>
+      </c>
+      <c r="AM218">
+        <v>1.84</v>
+      </c>
+      <c r="AN218">
+        <v>1.73</v>
+      </c>
+      <c r="AO218">
+        <v>0.91</v>
+      </c>
+      <c r="AP218">
+        <v>1.83</v>
+      </c>
+      <c r="AQ218">
+        <v>0.83</v>
+      </c>
+      <c r="AR218">
+        <v>1.63</v>
+      </c>
+      <c r="AS218">
+        <v>1.42</v>
+      </c>
+      <c r="AT218">
+        <v>3.05</v>
+      </c>
+      <c r="AU218">
+        <v>6</v>
+      </c>
+      <c r="AV218">
+        <v>0</v>
+      </c>
+      <c r="AW218">
+        <v>16</v>
+      </c>
+      <c r="AX218">
+        <v>8</v>
+      </c>
+      <c r="AY218">
+        <v>22</v>
+      </c>
+      <c r="AZ218">
+        <v>8</v>
+      </c>
+      <c r="BA218">
+        <v>15</v>
+      </c>
+      <c r="BB218">
+        <v>4</v>
+      </c>
+      <c r="BC218">
+        <v>19</v>
+      </c>
+      <c r="BD218">
+        <v>1.66</v>
+      </c>
+      <c r="BE218">
+        <v>6.5</v>
+      </c>
+      <c r="BF218">
+        <v>2.48</v>
+      </c>
+      <c r="BG218">
+        <v>1.36</v>
+      </c>
+      <c r="BH218">
+        <v>2.8</v>
+      </c>
+      <c r="BI218">
+        <v>1.63</v>
+      </c>
+      <c r="BJ218">
+        <v>2.15</v>
+      </c>
+      <c r="BK218">
+        <v>1.98</v>
+      </c>
+      <c r="BL218">
+        <v>1.72</v>
+      </c>
+      <c r="BM218">
+        <v>2.55</v>
+      </c>
+      <c r="BN218">
+        <v>1.45</v>
+      </c>
+      <c r="BO218">
+        <v>3.3</v>
+      </c>
+      <c r="BP218">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="219" spans="1:68">
+      <c r="A219" s="1">
+        <v>218</v>
+      </c>
+      <c r="B219">
+        <v>7469084</v>
+      </c>
+      <c r="C219" t="s">
+        <v>68</v>
+      </c>
+      <c r="D219" t="s">
+        <v>69</v>
+      </c>
+      <c r="E219" s="2">
+        <v>45716.66666666666</v>
+      </c>
+      <c r="F219">
+        <v>25</v>
+      </c>
+      <c r="G219" t="s">
+        <v>84</v>
+      </c>
+      <c r="H219" t="s">
+        <v>85</v>
+      </c>
+      <c r="I219">
+        <v>1</v>
+      </c>
+      <c r="J219">
+        <v>1</v>
+      </c>
+      <c r="K219">
+        <v>2</v>
+      </c>
+      <c r="L219">
+        <v>2</v>
+      </c>
+      <c r="M219">
+        <v>3</v>
+      </c>
+      <c r="N219">
+        <v>5</v>
+      </c>
+      <c r="O219" t="s">
+        <v>229</v>
+      </c>
+      <c r="P219" t="s">
+        <v>313</v>
+      </c>
+      <c r="Q219">
+        <v>4.3</v>
+      </c>
+      <c r="R219">
+        <v>2.13</v>
+      </c>
+      <c r="S219">
+        <v>2.6</v>
+      </c>
+      <c r="T219">
+        <v>1.43</v>
+      </c>
+      <c r="U219">
+        <v>2.65</v>
+      </c>
+      <c r="V219">
+        <v>2.85</v>
+      </c>
+      <c r="W219">
+        <v>1.37</v>
+      </c>
+      <c r="X219">
+        <v>7</v>
+      </c>
+      <c r="Y219">
+        <v>1.04</v>
+      </c>
+      <c r="Z219">
+        <v>3.76</v>
+      </c>
+      <c r="AA219">
+        <v>3.32</v>
+      </c>
+      <c r="AB219">
+        <v>1.99</v>
+      </c>
+      <c r="AC219">
+        <v>1.02</v>
+      </c>
+      <c r="AD219">
+        <v>8.1</v>
+      </c>
+      <c r="AE219">
+        <v>1.33</v>
+      </c>
+      <c r="AF219">
+        <v>3</v>
+      </c>
+      <c r="AG219">
+        <v>2</v>
+      </c>
+      <c r="AH219">
+        <v>1.67</v>
+      </c>
+      <c r="AI219">
+        <v>1.82</v>
+      </c>
+      <c r="AJ219">
+        <v>1.89</v>
+      </c>
+      <c r="AK219">
+        <v>1.73</v>
+      </c>
+      <c r="AL219">
+        <v>1.29</v>
+      </c>
+      <c r="AM219">
+        <v>1.27</v>
+      </c>
+      <c r="AN219">
+        <v>2</v>
+      </c>
+      <c r="AO219">
+        <v>1.67</v>
+      </c>
+      <c r="AP219">
+        <v>1.83</v>
+      </c>
+      <c r="AQ219">
+        <v>1.77</v>
+      </c>
+      <c r="AR219">
+        <v>1.4</v>
+      </c>
+      <c r="AS219">
+        <v>1.4</v>
+      </c>
+      <c r="AT219">
+        <v>2.8</v>
+      </c>
+      <c r="AU219">
+        <v>4</v>
+      </c>
+      <c r="AV219">
+        <v>7</v>
+      </c>
+      <c r="AW219">
+        <v>2</v>
+      </c>
+      <c r="AX219">
+        <v>8</v>
+      </c>
+      <c r="AY219">
+        <v>6</v>
+      </c>
+      <c r="AZ219">
+        <v>15</v>
+      </c>
+      <c r="BA219">
+        <v>1</v>
+      </c>
+      <c r="BB219">
+        <v>5</v>
+      </c>
+      <c r="BC219">
+        <v>6</v>
+      </c>
+      <c r="BD219">
+        <v>2.48</v>
+      </c>
+      <c r="BE219">
+        <v>6.4</v>
+      </c>
+      <c r="BF219">
+        <v>1.67</v>
+      </c>
+      <c r="BG219">
+        <v>1.42</v>
+      </c>
+      <c r="BH219">
+        <v>2.65</v>
+      </c>
+      <c r="BI219">
+        <v>1.73</v>
+      </c>
+      <c r="BJ219">
+        <v>1.98</v>
+      </c>
+      <c r="BK219">
+        <v>2.17</v>
+      </c>
+      <c r="BL219">
+        <v>1.6</v>
+      </c>
+      <c r="BM219">
+        <v>2.8</v>
+      </c>
+      <c r="BN219">
+        <v>1.38</v>
+      </c>
+      <c r="BO219">
+        <v>3.65</v>
+      </c>
+      <c r="BP219">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="220" spans="1:68">
+      <c r="A220" s="1">
+        <v>219</v>
+      </c>
+      <c r="B220">
+        <v>7469087</v>
+      </c>
+      <c r="C220" t="s">
+        <v>68</v>
+      </c>
+      <c r="D220" t="s">
+        <v>69</v>
+      </c>
+      <c r="E220" s="2">
+        <v>45716.66666666666</v>
+      </c>
+      <c r="F220">
+        <v>25</v>
+      </c>
+      <c r="G220" t="s">
+        <v>80</v>
+      </c>
+      <c r="H220" t="s">
+        <v>77</v>
+      </c>
+      <c r="I220">
+        <v>0</v>
+      </c>
+      <c r="J220">
+        <v>0</v>
+      </c>
+      <c r="K220">
+        <v>0</v>
+      </c>
+      <c r="L220">
+        <v>0</v>
+      </c>
+      <c r="M220">
+        <v>1</v>
+      </c>
+      <c r="N220">
+        <v>1</v>
+      </c>
+      <c r="O220" t="s">
+        <v>90</v>
+      </c>
+      <c r="P220" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q220">
+        <v>2.2</v>
+      </c>
+      <c r="R220">
+        <v>2.22</v>
+      </c>
+      <c r="S220">
+        <v>5.6</v>
+      </c>
+      <c r="T220">
+        <v>1.42</v>
+      </c>
+      <c r="U220">
+        <v>2.7</v>
+      </c>
+      <c r="V220">
+        <v>2.8</v>
+      </c>
+      <c r="W220">
+        <v>1.38</v>
+      </c>
+      <c r="X220">
+        <v>7.7</v>
+      </c>
+      <c r="Y220">
+        <v>1.02</v>
+      </c>
+      <c r="Z220">
+        <v>1.67</v>
+      </c>
+      <c r="AA220">
+        <v>3.65</v>
+      </c>
+      <c r="AB220">
+        <v>5</v>
+      </c>
+      <c r="AC220">
+        <v>1.06</v>
+      </c>
+      <c r="AD220">
+        <v>8.5</v>
+      </c>
+      <c r="AE220">
+        <v>1.33</v>
+      </c>
+      <c r="AF220">
+        <v>3.05</v>
+      </c>
+      <c r="AG220">
+        <v>1.98</v>
+      </c>
+      <c r="AH220">
+        <v>1.77</v>
+      </c>
+      <c r="AI220">
+        <v>1.97</v>
+      </c>
+      <c r="AJ220">
+        <v>1.75</v>
+      </c>
+      <c r="AK220">
+        <v>1.16</v>
+      </c>
+      <c r="AL220">
+        <v>1.24</v>
+      </c>
+      <c r="AM220">
+        <v>2.13</v>
+      </c>
+      <c r="AN220">
+        <v>1.64</v>
+      </c>
+      <c r="AO220">
+        <v>1.27</v>
+      </c>
+      <c r="AP220">
+        <v>1.5</v>
+      </c>
+      <c r="AQ220">
+        <v>1.42</v>
+      </c>
+      <c r="AR220">
+        <v>1.27</v>
+      </c>
+      <c r="AS220">
+        <v>1.1</v>
+      </c>
+      <c r="AT220">
+        <v>2.37</v>
+      </c>
+      <c r="AU220">
+        <v>4</v>
+      </c>
+      <c r="AV220">
+        <v>2</v>
+      </c>
+      <c r="AW220">
+        <v>8</v>
+      </c>
+      <c r="AX220">
+        <v>6</v>
+      </c>
+      <c r="AY220">
+        <v>14</v>
+      </c>
+      <c r="AZ220">
+        <v>8</v>
+      </c>
+      <c r="BA220">
+        <v>4</v>
+      </c>
+      <c r="BB220">
+        <v>4</v>
+      </c>
+      <c r="BC220">
+        <v>8</v>
+      </c>
+      <c r="BD220">
+        <v>1.47</v>
+      </c>
+      <c r="BE220">
+        <v>6.75</v>
+      </c>
+      <c r="BF220">
+        <v>3.05</v>
+      </c>
+      <c r="BG220">
+        <v>1.45</v>
+      </c>
+      <c r="BH220">
+        <v>2.55</v>
+      </c>
+      <c r="BI220">
+        <v>1.75</v>
+      </c>
+      <c r="BJ220">
+        <v>1.95</v>
+      </c>
+      <c r="BK220">
+        <v>2.17</v>
+      </c>
+      <c r="BL220">
+        <v>1.58</v>
+      </c>
+      <c r="BM220">
+        <v>2.8</v>
+      </c>
+      <c r="BN220">
+        <v>1.36</v>
+      </c>
+      <c r="BO220">
+        <v>3.7</v>
+      </c>
+      <c r="BP220">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="221" spans="1:68">
+      <c r="A221" s="1">
+        <v>220</v>
+      </c>
+      <c r="B221">
+        <v>7469088</v>
+      </c>
+      <c r="C221" t="s">
+        <v>68</v>
+      </c>
+      <c r="D221" t="s">
+        <v>69</v>
+      </c>
+      <c r="E221" s="2">
+        <v>45716.66666666666</v>
+      </c>
+      <c r="F221">
+        <v>25</v>
+      </c>
+      <c r="G221" t="s">
+        <v>79</v>
+      </c>
+      <c r="H221" t="s">
+        <v>83</v>
+      </c>
+      <c r="I221">
+        <v>1</v>
+      </c>
+      <c r="J221">
+        <v>0</v>
+      </c>
+      <c r="K221">
+        <v>1</v>
+      </c>
+      <c r="L221">
+        <v>2</v>
+      </c>
+      <c r="M221">
+        <v>0</v>
+      </c>
+      <c r="N221">
+        <v>2</v>
+      </c>
+      <c r="O221" t="s">
+        <v>230</v>
+      </c>
+      <c r="P221" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q221">
+        <v>3.7</v>
+      </c>
+      <c r="R221">
+        <v>1.92</v>
+      </c>
+      <c r="S221">
+        <v>3.5</v>
+      </c>
+      <c r="T221">
+        <v>1.59</v>
+      </c>
+      <c r="U221">
+        <v>2.24</v>
+      </c>
+      <c r="V221">
+        <v>3.6</v>
+      </c>
+      <c r="W221">
+        <v>1.25</v>
+      </c>
+      <c r="X221">
+        <v>8.4</v>
+      </c>
+      <c r="Y221">
+        <v>1.01</v>
+      </c>
+      <c r="Z221">
+        <v>2.83</v>
+      </c>
+      <c r="AA221">
+        <v>2.95</v>
+      </c>
+      <c r="AB221">
+        <v>2.65</v>
+      </c>
+      <c r="AC221">
+        <v>1.11</v>
+      </c>
+      <c r="AD221">
+        <v>6.4</v>
+      </c>
+      <c r="AE221">
+        <v>1.5</v>
+      </c>
+      <c r="AF221">
+        <v>2.4</v>
+      </c>
+      <c r="AG221">
+        <v>2.37</v>
+      </c>
+      <c r="AH221">
+        <v>1.48</v>
+      </c>
+      <c r="AI221">
+        <v>2.09</v>
+      </c>
+      <c r="AJ221">
+        <v>1.67</v>
+      </c>
+      <c r="AK221">
+        <v>1.45</v>
+      </c>
+      <c r="AL221">
+        <v>1.36</v>
+      </c>
+      <c r="AM221">
+        <v>1.4</v>
+      </c>
+      <c r="AN221">
+        <v>1.27</v>
+      </c>
+      <c r="AO221">
+        <v>1</v>
+      </c>
+      <c r="AP221">
+        <v>1.42</v>
+      </c>
+      <c r="AQ221">
+        <v>0.92</v>
+      </c>
+      <c r="AR221">
+        <v>1.73</v>
+      </c>
+      <c r="AS221">
+        <v>1.42</v>
+      </c>
+      <c r="AT221">
+        <v>3.15</v>
+      </c>
+      <c r="AU221">
+        <v>6</v>
+      </c>
+      <c r="AV221">
+        <v>5</v>
+      </c>
+      <c r="AW221">
+        <v>8</v>
+      </c>
+      <c r="AX221">
+        <v>6</v>
+      </c>
+      <c r="AY221">
+        <v>14</v>
+      </c>
+      <c r="AZ221">
+        <v>11</v>
+      </c>
+      <c r="BA221">
+        <v>4</v>
+      </c>
+      <c r="BB221">
+        <v>6</v>
+      </c>
+      <c r="BC221">
+        <v>10</v>
+      </c>
+      <c r="BD221">
+        <v>1.98</v>
+      </c>
+      <c r="BE221">
+        <v>6.25</v>
+      </c>
+      <c r="BF221">
+        <v>2</v>
+      </c>
+      <c r="BG221">
+        <v>1.5</v>
+      </c>
+      <c r="BH221">
+        <v>2.4</v>
+      </c>
+      <c r="BI221">
+        <v>1.84</v>
+      </c>
+      <c r="BJ221">
+        <v>1.84</v>
+      </c>
+      <c r="BK221">
+        <v>2.33</v>
+      </c>
+      <c r="BL221">
+        <v>1.5</v>
+      </c>
+      <c r="BM221">
+        <v>3.05</v>
+      </c>
+      <c r="BN221">
+        <v>1.3</v>
+      </c>
+      <c r="BO221">
+        <v>4.1</v>
+      </c>
+      <c r="BP221">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="222" spans="1:68">
+      <c r="A222" s="1">
+        <v>221</v>
+      </c>
+      <c r="B222">
+        <v>7469090</v>
+      </c>
+      <c r="C222" t="s">
+        <v>68</v>
+      </c>
+      <c r="D222" t="s">
+        <v>69</v>
+      </c>
+      <c r="E222" s="2">
+        <v>45716.66666666666</v>
+      </c>
+      <c r="F222">
+        <v>25</v>
+      </c>
+      <c r="G222" t="s">
+        <v>70</v>
+      </c>
+      <c r="H222" t="s">
+        <v>76</v>
+      </c>
+      <c r="I222">
+        <v>0</v>
+      </c>
+      <c r="J222">
+        <v>0</v>
+      </c>
+      <c r="K222">
+        <v>0</v>
+      </c>
+      <c r="L222">
+        <v>0</v>
+      </c>
+      <c r="M222">
+        <v>1</v>
+      </c>
+      <c r="N222">
+        <v>1</v>
+      </c>
+      <c r="O222" t="s">
+        <v>90</v>
+      </c>
+      <c r="P222" t="s">
+        <v>301</v>
+      </c>
+      <c r="Q222">
+        <v>2.7</v>
+      </c>
+      <c r="R222">
+        <v>2.12</v>
+      </c>
+      <c r="S222">
+        <v>4.1</v>
+      </c>
+      <c r="T222">
+        <v>1.43</v>
+      </c>
+      <c r="U222">
+        <v>2.65</v>
+      </c>
+      <c r="V222">
+        <v>2.9</v>
+      </c>
+      <c r="W222">
+        <v>1.37</v>
+      </c>
+      <c r="X222">
+        <v>8.1</v>
+      </c>
+      <c r="Y222">
+        <v>1.02</v>
+      </c>
+      <c r="Z222">
+        <v>2.21</v>
+      </c>
+      <c r="AA222">
+        <v>3.21</v>
+      </c>
+      <c r="AB222">
+        <v>3.27</v>
+      </c>
+      <c r="AC222">
+        <v>1.07</v>
+      </c>
+      <c r="AD222">
+        <v>8</v>
+      </c>
+      <c r="AE222">
+        <v>1.33</v>
+      </c>
+      <c r="AF222">
+        <v>3</v>
+      </c>
+      <c r="AG222">
+        <v>2</v>
+      </c>
+      <c r="AH222">
+        <v>1.67</v>
+      </c>
+      <c r="AI222">
+        <v>1.81</v>
+      </c>
+      <c r="AJ222">
+        <v>1.9</v>
+      </c>
+      <c r="AK222">
+        <v>1.29</v>
+      </c>
+      <c r="AL222">
+        <v>1.3</v>
+      </c>
+      <c r="AM222">
+        <v>1.69</v>
+      </c>
+      <c r="AN222">
+        <v>1</v>
+      </c>
+      <c r="AO222">
+        <v>0.36</v>
+      </c>
+      <c r="AP222">
+        <v>0.92</v>
+      </c>
+      <c r="AQ222">
+        <v>0.58</v>
+      </c>
+      <c r="AR222">
+        <v>1.41</v>
+      </c>
+      <c r="AS222">
+        <v>1.26</v>
+      </c>
+      <c r="AT222">
+        <v>2.67</v>
+      </c>
+      <c r="AU222">
+        <v>3</v>
+      </c>
+      <c r="AV222">
+        <v>8</v>
+      </c>
+      <c r="AW222">
+        <v>3</v>
+      </c>
+      <c r="AX222">
+        <v>9</v>
+      </c>
+      <c r="AY222">
+        <v>6</v>
+      </c>
+      <c r="AZ222">
+        <v>17</v>
+      </c>
+      <c r="BA222">
+        <v>4</v>
+      </c>
+      <c r="BB222">
+        <v>5</v>
+      </c>
+      <c r="BC222">
+        <v>9</v>
+      </c>
+      <c r="BD222">
+        <v>1.71</v>
+      </c>
+      <c r="BE222">
+        <v>6.4</v>
+      </c>
+      <c r="BF222">
+        <v>2.4</v>
+      </c>
+      <c r="BG222">
+        <v>1.36</v>
+      </c>
+      <c r="BH222">
+        <v>2.8</v>
+      </c>
+      <c r="BI222">
+        <v>1.61</v>
+      </c>
+      <c r="BJ222">
+        <v>2.15</v>
+      </c>
+      <c r="BK222">
+        <v>1.98</v>
+      </c>
+      <c r="BL222">
+        <v>1.73</v>
+      </c>
+      <c r="BM222">
+        <v>2.55</v>
+      </c>
+      <c r="BN222">
+        <v>1.45</v>
+      </c>
+      <c r="BO222">
+        <v>3.3</v>
+      </c>
+      <c r="BP222">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1394" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1412" uniqueCount="319">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -709,6 +709,15 @@
     <t>['12', '53']</t>
   </si>
   <si>
+    <t>['42', '88', '90+3']</t>
+  </si>
+  <si>
+    <t>['45']</t>
+  </si>
+  <si>
+    <t>['45+2']</t>
+  </si>
+  <si>
     <t>['16', '45+2']</t>
   </si>
   <si>
@@ -956,6 +965,12 @@
   </si>
   <si>
     <t>['10', '57', '62']</t>
+  </si>
+  <si>
+    <t>['16']</t>
+  </si>
+  <si>
+    <t>['70', '89']</t>
   </si>
 </sst>
 </file>
@@ -1317,7 +1332,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP222"/>
+  <dimension ref="A1:BP225"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1573,7 +1588,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q2">
         <v>2.4</v>
@@ -1985,7 +2000,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q4">
         <v>3.6</v>
@@ -2269,7 +2284,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ5">
         <v>0.92</v>
@@ -2809,7 +2824,7 @@
         <v>90</v>
       </c>
       <c r="P8" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q8">
         <v>3.1</v>
@@ -3221,7 +3236,7 @@
         <v>94</v>
       </c>
       <c r="P10" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q10">
         <v>2.6</v>
@@ -3714,7 +3729,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ12">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3839,7 +3854,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q13">
         <v>3.1</v>
@@ -3920,7 +3935,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ13">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4457,7 +4472,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q16">
         <v>2.63</v>
@@ -4663,7 +4678,7 @@
         <v>99</v>
       </c>
       <c r="P17" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -4947,7 +4962,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="AQ18">
         <v>0.83</v>
@@ -5153,7 +5168,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ19">
         <v>0.83</v>
@@ -5693,7 +5708,7 @@
         <v>103</v>
       </c>
       <c r="P22" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -6105,7 +6120,7 @@
         <v>105</v>
       </c>
       <c r="P24" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q24">
         <v>2.62</v>
@@ -6801,7 +6816,7 @@
         <v>3</v>
       </c>
       <c r="AP27">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ27">
         <v>1.5</v>
@@ -6929,7 +6944,7 @@
         <v>108</v>
       </c>
       <c r="P28" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q28">
         <v>2.6</v>
@@ -7419,7 +7434,7 @@
         <v>1.5</v>
       </c>
       <c r="AP30">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="AQ30">
         <v>0.92</v>
@@ -8371,7 +8386,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q35">
         <v>3.3</v>
@@ -8452,7 +8467,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ35">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR35">
         <v>1.69</v>
@@ -8577,7 +8592,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q36">
         <v>3.1</v>
@@ -8658,7 +8673,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ36">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR36">
         <v>1.66</v>
@@ -8783,7 +8798,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q37">
         <v>3.4</v>
@@ -8989,7 +9004,7 @@
         <v>90</v>
       </c>
       <c r="P38" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q38">
         <v>3.2</v>
@@ -9195,7 +9210,7 @@
         <v>90</v>
       </c>
       <c r="P39" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q39">
         <v>3.4</v>
@@ -9607,7 +9622,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q41">
         <v>2.5</v>
@@ -9813,7 +9828,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q42">
         <v>3.25</v>
@@ -10019,7 +10034,7 @@
         <v>90</v>
       </c>
       <c r="P43" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q43">
         <v>2.75</v>
@@ -10097,7 +10112,7 @@
         <v>0.5</v>
       </c>
       <c r="AP43">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ43">
         <v>1.46</v>
@@ -10509,7 +10524,7 @@
         <v>3</v>
       </c>
       <c r="AP45">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ45">
         <v>1.08</v>
@@ -11542,7 +11557,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ50">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR50">
         <v>1.61</v>
@@ -12079,7 +12094,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -12285,7 +12300,7 @@
         <v>129</v>
       </c>
       <c r="P54" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q54">
         <v>2.55</v>
@@ -12491,7 +12506,7 @@
         <v>130</v>
       </c>
       <c r="P55" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q55">
         <v>2.55</v>
@@ -12775,7 +12790,7 @@
         <v>0.33</v>
       </c>
       <c r="AP56">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="AQ56">
         <v>0.83</v>
@@ -12903,7 +12918,7 @@
         <v>132</v>
       </c>
       <c r="P57" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -13315,7 +13330,7 @@
         <v>134</v>
       </c>
       <c r="P59" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q59">
         <v>2.62</v>
@@ -13521,7 +13536,7 @@
         <v>135</v>
       </c>
       <c r="P60" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q60">
         <v>2.88</v>
@@ -13599,7 +13614,7 @@
         <v>1</v>
       </c>
       <c r="AP60">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ60">
         <v>1.08</v>
@@ -13933,7 +13948,7 @@
         <v>137</v>
       </c>
       <c r="P62" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q62">
         <v>3.6</v>
@@ -14011,7 +14026,7 @@
         <v>2</v>
       </c>
       <c r="AP62">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ62">
         <v>1.77</v>
@@ -14139,7 +14154,7 @@
         <v>138</v>
       </c>
       <c r="P63" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q63">
         <v>3.75</v>
@@ -14220,7 +14235,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ63">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR63">
         <v>1.33</v>
@@ -15169,7 +15184,7 @@
         <v>143</v>
       </c>
       <c r="P68" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15375,7 +15390,7 @@
         <v>144</v>
       </c>
       <c r="P69" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15581,7 +15596,7 @@
         <v>145</v>
       </c>
       <c r="P70" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q70">
         <v>3.75</v>
@@ -15868,7 +15883,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ71">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR71">
         <v>1.24</v>
@@ -15993,7 +16008,7 @@
         <v>147</v>
       </c>
       <c r="P72" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16199,7 +16214,7 @@
         <v>90</v>
       </c>
       <c r="P73" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q73">
         <v>4.33</v>
@@ -16405,7 +16420,7 @@
         <v>90</v>
       </c>
       <c r="P74" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q74">
         <v>2.4</v>
@@ -16611,7 +16626,7 @@
         <v>148</v>
       </c>
       <c r="P75" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q75">
         <v>3.5</v>
@@ -16689,7 +16704,7 @@
         <v>0</v>
       </c>
       <c r="AP75">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ75">
         <v>0.58</v>
@@ -16817,7 +16832,7 @@
         <v>149</v>
       </c>
       <c r="P76" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q76">
         <v>2.88</v>
@@ -17104,7 +17119,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ77">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR77">
         <v>1.29</v>
@@ -17435,7 +17450,7 @@
         <v>151</v>
       </c>
       <c r="P79" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17513,7 +17528,7 @@
         <v>0.25</v>
       </c>
       <c r="AP79">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ79">
         <v>0.83</v>
@@ -17641,7 +17656,7 @@
         <v>152</v>
       </c>
       <c r="P80" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q80">
         <v>2.05</v>
@@ -17719,7 +17734,7 @@
         <v>1.5</v>
       </c>
       <c r="AP80">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="AQ80">
         <v>1.31</v>
@@ -17847,7 +17862,7 @@
         <v>90</v>
       </c>
       <c r="P81" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q81">
         <v>4.33</v>
@@ -18671,7 +18686,7 @@
         <v>90</v>
       </c>
       <c r="P85" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q85">
         <v>3.1</v>
@@ -18877,7 +18892,7 @@
         <v>156</v>
       </c>
       <c r="P86" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -19370,7 +19385,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ88">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR88">
         <v>1.77</v>
@@ -19701,7 +19716,7 @@
         <v>90</v>
       </c>
       <c r="P90" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q90">
         <v>2.38</v>
@@ -20113,7 +20128,7 @@
         <v>160</v>
       </c>
       <c r="P92" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20397,10 +20412,10 @@
         <v>1.5</v>
       </c>
       <c r="AP93">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ93">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR93">
         <v>1.43</v>
@@ -20731,7 +20746,7 @@
         <v>162</v>
       </c>
       <c r="P95" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q95">
         <v>1.9</v>
@@ -20809,7 +20824,7 @@
         <v>1</v>
       </c>
       <c r="AP95">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="AQ95">
         <v>1.36</v>
@@ -20937,7 +20952,7 @@
         <v>163</v>
       </c>
       <c r="P96" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q96">
         <v>2.75</v>
@@ -21221,7 +21236,7 @@
         <v>2.4</v>
       </c>
       <c r="AP97">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ97">
         <v>1.77</v>
@@ -21349,7 +21364,7 @@
         <v>90</v>
       </c>
       <c r="P98" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q98">
         <v>4.75</v>
@@ -22585,7 +22600,7 @@
         <v>167</v>
       </c>
       <c r="P104" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q104">
         <v>2.25</v>
@@ -23409,7 +23424,7 @@
         <v>90</v>
       </c>
       <c r="P108" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q108">
         <v>4.5</v>
@@ -23490,7 +23505,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ108">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR108">
         <v>1.07</v>
@@ -23693,7 +23708,7 @@
         <v>1.4</v>
       </c>
       <c r="AP109">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ109">
         <v>1.42</v>
@@ -24233,7 +24248,7 @@
         <v>173</v>
       </c>
       <c r="P112" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q112">
         <v>3.5</v>
@@ -24645,7 +24660,7 @@
         <v>90</v>
       </c>
       <c r="P114" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q114">
         <v>2.85</v>
@@ -24723,7 +24738,7 @@
         <v>0.67</v>
       </c>
       <c r="AP114">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ114">
         <v>1</v>
@@ -25057,7 +25072,7 @@
         <v>175</v>
       </c>
       <c r="P116" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q116">
         <v>2.4</v>
@@ -25135,10 +25150,10 @@
         <v>1.2</v>
       </c>
       <c r="AP116">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="AQ116">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR116">
         <v>1.94</v>
@@ -25469,7 +25484,7 @@
         <v>90</v>
       </c>
       <c r="P118" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q118">
         <v>4</v>
@@ -25962,7 +25977,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ120">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR120">
         <v>1.24</v>
@@ -26087,7 +26102,7 @@
         <v>178</v>
       </c>
       <c r="P121" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q121">
         <v>2.88</v>
@@ -27607,7 +27622,7 @@
         <v>1</v>
       </c>
       <c r="AP128">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="AQ128">
         <v>1</v>
@@ -27816,7 +27831,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ129">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR129">
         <v>0.99</v>
@@ -28431,7 +28446,7 @@
         <v>1</v>
       </c>
       <c r="AP132">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ132">
         <v>0.92</v>
@@ -28765,7 +28780,7 @@
         <v>90</v>
       </c>
       <c r="P134" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q134">
         <v>3.2</v>
@@ -28971,7 +28986,7 @@
         <v>90</v>
       </c>
       <c r="P135" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q135">
         <v>5</v>
@@ -29464,7 +29479,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ137">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR137">
         <v>1.66</v>
@@ -30001,7 +30016,7 @@
         <v>188</v>
       </c>
       <c r="P140" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q140">
         <v>2.95</v>
@@ -30207,7 +30222,7 @@
         <v>189</v>
       </c>
       <c r="P141" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q141">
         <v>2.8</v>
@@ -30285,7 +30300,7 @@
         <v>1.38</v>
       </c>
       <c r="AP141">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ141">
         <v>1.46</v>
@@ -30491,7 +30506,7 @@
         <v>2.13</v>
       </c>
       <c r="AP142">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="AQ142">
         <v>1.77</v>
@@ -30697,7 +30712,7 @@
         <v>0.57</v>
       </c>
       <c r="AP143">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ143">
         <v>0.83</v>
@@ -30906,7 +30921,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ144">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR144">
         <v>1.43</v>
@@ -31031,7 +31046,7 @@
         <v>192</v>
       </c>
       <c r="P145" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q145">
         <v>2.75</v>
@@ -31237,7 +31252,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q146">
         <v>3.75</v>
@@ -31443,7 +31458,7 @@
         <v>129</v>
       </c>
       <c r="P147" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q147">
         <v>3.75</v>
@@ -31649,7 +31664,7 @@
         <v>90</v>
       </c>
       <c r="P148" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q148">
         <v>2.4</v>
@@ -31855,7 +31870,7 @@
         <v>90</v>
       </c>
       <c r="P149" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q149">
         <v>3.1</v>
@@ -31933,7 +31948,7 @@
         <v>0.88</v>
       </c>
       <c r="AP149">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ149">
         <v>1</v>
@@ -32267,7 +32282,7 @@
         <v>194</v>
       </c>
       <c r="P151" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q151">
         <v>1.62</v>
@@ -32679,7 +32694,7 @@
         <v>95</v>
       </c>
       <c r="P153" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q153">
         <v>2.63</v>
@@ -33503,7 +33518,7 @@
         <v>197</v>
       </c>
       <c r="P157" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q157">
         <v>2.7</v>
@@ -33709,7 +33724,7 @@
         <v>96</v>
       </c>
       <c r="P158" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q158">
         <v>2.55</v>
@@ -33915,7 +33930,7 @@
         <v>198</v>
       </c>
       <c r="P159" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q159">
         <v>3.3</v>
@@ -33996,7 +34011,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ159">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR159">
         <v>1.45</v>
@@ -34121,7 +34136,7 @@
         <v>90</v>
       </c>
       <c r="P160" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q160">
         <v>2.75</v>
@@ -34817,10 +34832,10 @@
         <v>1.38</v>
       </c>
       <c r="AP163">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="AQ163">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR163">
         <v>1.75</v>
@@ -35435,7 +35450,7 @@
         <v>0.89</v>
       </c>
       <c r="AP166">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ166">
         <v>0.92</v>
@@ -35563,7 +35578,7 @@
         <v>109</v>
       </c>
       <c r="P167" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q167">
         <v>3.35</v>
@@ -35641,7 +35656,7 @@
         <v>0.67</v>
       </c>
       <c r="AP167">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ167">
         <v>0.85</v>
@@ -35975,7 +35990,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q169">
         <v>2.8</v>
@@ -36181,7 +36196,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q170">
         <v>3</v>
@@ -36593,7 +36608,7 @@
         <v>90</v>
       </c>
       <c r="P172" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q172">
         <v>2.63</v>
@@ -36799,7 +36814,7 @@
         <v>207</v>
       </c>
       <c r="P173" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q173">
         <v>2.3</v>
@@ -37829,7 +37844,7 @@
         <v>90</v>
       </c>
       <c r="P178" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q178">
         <v>3.25</v>
@@ -37910,7 +37925,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ178">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR178">
         <v>1.34</v>
@@ -38241,7 +38256,7 @@
         <v>212</v>
       </c>
       <c r="P180" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q180">
         <v>2.2</v>
@@ -38319,7 +38334,7 @@
         <v>1.44</v>
       </c>
       <c r="AP180">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="AQ180">
         <v>1.08</v>
@@ -38447,7 +38462,7 @@
         <v>90</v>
       </c>
       <c r="P181" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q181">
         <v>3.25</v>
@@ -39143,7 +39158,7 @@
         <v>1.4</v>
       </c>
       <c r="AP184">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ184">
         <v>1.31</v>
@@ -39558,7 +39573,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ186">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR186">
         <v>1.69</v>
@@ -39683,7 +39698,7 @@
         <v>90</v>
       </c>
       <c r="P187" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q187">
         <v>2.55</v>
@@ -39889,7 +39904,7 @@
         <v>215</v>
       </c>
       <c r="P188" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q188">
         <v>4.5</v>
@@ -39967,7 +39982,7 @@
         <v>1.2</v>
       </c>
       <c r="AP188">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ188">
         <v>1.5</v>
@@ -40301,7 +40316,7 @@
         <v>90</v>
       </c>
       <c r="P190" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q190">
         <v>3.3</v>
@@ -40507,7 +40522,7 @@
         <v>90</v>
       </c>
       <c r="P191" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q191">
         <v>2.75</v>
@@ -40713,7 +40728,7 @@
         <v>90</v>
       </c>
       <c r="P192" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q192">
         <v>3.25</v>
@@ -41331,7 +41346,7 @@
         <v>214</v>
       </c>
       <c r="P195" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q195">
         <v>4.75</v>
@@ -41537,7 +41552,7 @@
         <v>90</v>
       </c>
       <c r="P196" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q196">
         <v>3.65</v>
@@ -41618,7 +41633,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ196">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR196">
         <v>1.27</v>
@@ -41743,7 +41758,7 @@
         <v>218</v>
       </c>
       <c r="P197" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q197">
         <v>1.94</v>
@@ -41821,7 +41836,7 @@
         <v>0.6</v>
       </c>
       <c r="AP197">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="AQ197">
         <v>0.58</v>
@@ -42155,7 +42170,7 @@
         <v>90</v>
       </c>
       <c r="P199" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q199">
         <v>3.75</v>
@@ -42851,7 +42866,7 @@
         <v>1.4</v>
       </c>
       <c r="AP202">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ202">
         <v>1.42</v>
@@ -43185,7 +43200,7 @@
         <v>160</v>
       </c>
       <c r="P204" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q204">
         <v>3</v>
@@ -43263,7 +43278,7 @@
         <v>0.7</v>
       </c>
       <c r="AP204">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ204">
         <v>0.83</v>
@@ -43391,7 +43406,7 @@
         <v>90</v>
       </c>
       <c r="P205" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q205">
         <v>2.75</v>
@@ -43803,7 +43818,7 @@
         <v>90</v>
       </c>
       <c r="P207" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q207">
         <v>3.8</v>
@@ -43884,7 +43899,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ207">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR207">
         <v>1.58</v>
@@ -45039,7 +45054,7 @@
         <v>226</v>
       </c>
       <c r="P213" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q213">
         <v>3.75</v>
@@ -45120,7 +45135,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ213">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR213">
         <v>1.24</v>
@@ -45451,7 +45466,7 @@
         <v>228</v>
       </c>
       <c r="P215" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q215">
         <v>2.95</v>
@@ -45657,7 +45672,7 @@
         <v>90</v>
       </c>
       <c r="P216" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q216">
         <v>1.96</v>
@@ -45735,7 +45750,7 @@
         <v>1.33</v>
       </c>
       <c r="AP216">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="AQ216">
         <v>1.46</v>
@@ -46275,7 +46290,7 @@
         <v>229</v>
       </c>
       <c r="P219" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q219">
         <v>4.3</v>
@@ -46893,7 +46908,7 @@
         <v>90</v>
       </c>
       <c r="P222" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q222">
         <v>2.7</v>
@@ -47050,6 +47065,624 @@
       </c>
       <c r="BP222">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="223" spans="1:68">
+      <c r="A223" s="1">
+        <v>222</v>
+      </c>
+      <c r="B223">
+        <v>7469086</v>
+      </c>
+      <c r="C223" t="s">
+        <v>68</v>
+      </c>
+      <c r="D223" t="s">
+        <v>69</v>
+      </c>
+      <c r="E223" s="2">
+        <v>45717.41666666666</v>
+      </c>
+      <c r="F223">
+        <v>25</v>
+      </c>
+      <c r="G223" t="s">
+        <v>87</v>
+      </c>
+      <c r="H223" t="s">
+        <v>75</v>
+      </c>
+      <c r="I223">
+        <v>1</v>
+      </c>
+      <c r="J223">
+        <v>1</v>
+      </c>
+      <c r="K223">
+        <v>2</v>
+      </c>
+      <c r="L223">
+        <v>3</v>
+      </c>
+      <c r="M223">
+        <v>1</v>
+      </c>
+      <c r="N223">
+        <v>4</v>
+      </c>
+      <c r="O223" t="s">
+        <v>231</v>
+      </c>
+      <c r="P223" t="s">
+        <v>317</v>
+      </c>
+      <c r="Q223">
+        <v>3.65</v>
+      </c>
+      <c r="R223">
+        <v>2.13</v>
+      </c>
+      <c r="S223">
+        <v>2.95</v>
+      </c>
+      <c r="T223">
+        <v>1.43</v>
+      </c>
+      <c r="U223">
+        <v>2.65</v>
+      </c>
+      <c r="V223">
+        <v>2.85</v>
+      </c>
+      <c r="W223">
+        <v>1.38</v>
+      </c>
+      <c r="X223">
+        <v>6.85</v>
+      </c>
+      <c r="Y223">
+        <v>1.04</v>
+      </c>
+      <c r="Z223">
+        <v>3.04</v>
+      </c>
+      <c r="AA223">
+        <v>3.37</v>
+      </c>
+      <c r="AB223">
+        <v>2.25</v>
+      </c>
+      <c r="AC223">
+        <v>1.06</v>
+      </c>
+      <c r="AD223">
+        <v>8.5</v>
+      </c>
+      <c r="AE223">
+        <v>1.32</v>
+      </c>
+      <c r="AF223">
+        <v>3.1</v>
+      </c>
+      <c r="AG223">
+        <v>1.98</v>
+      </c>
+      <c r="AH223">
+        <v>1.77</v>
+      </c>
+      <c r="AI223">
+        <v>1.76</v>
+      </c>
+      <c r="AJ223">
+        <v>1.96</v>
+      </c>
+      <c r="AK223">
+        <v>1.57</v>
+      </c>
+      <c r="AL223">
+        <v>1.3</v>
+      </c>
+      <c r="AM223">
+        <v>1.36</v>
+      </c>
+      <c r="AN223">
+        <v>1.27</v>
+      </c>
+      <c r="AO223">
+        <v>1.58</v>
+      </c>
+      <c r="AP223">
+        <v>1.42</v>
+      </c>
+      <c r="AQ223">
+        <v>1.46</v>
+      </c>
+      <c r="AR223">
+        <v>1.28</v>
+      </c>
+      <c r="AS223">
+        <v>1.49</v>
+      </c>
+      <c r="AT223">
+        <v>2.77</v>
+      </c>
+      <c r="AU223">
+        <v>8</v>
+      </c>
+      <c r="AV223">
+        <v>5</v>
+      </c>
+      <c r="AW223">
+        <v>1</v>
+      </c>
+      <c r="AX223">
+        <v>3</v>
+      </c>
+      <c r="AY223">
+        <v>9</v>
+      </c>
+      <c r="AZ223">
+        <v>8</v>
+      </c>
+      <c r="BA223">
+        <v>2</v>
+      </c>
+      <c r="BB223">
+        <v>5</v>
+      </c>
+      <c r="BC223">
+        <v>7</v>
+      </c>
+      <c r="BD223">
+        <v>2.23</v>
+      </c>
+      <c r="BE223">
+        <v>6.4</v>
+      </c>
+      <c r="BF223">
+        <v>1.79</v>
+      </c>
+      <c r="BG223">
+        <v>1.36</v>
+      </c>
+      <c r="BH223">
+        <v>2.8</v>
+      </c>
+      <c r="BI223">
+        <v>1.61</v>
+      </c>
+      <c r="BJ223">
+        <v>2.15</v>
+      </c>
+      <c r="BK223">
+        <v>1.98</v>
+      </c>
+      <c r="BL223">
+        <v>1.72</v>
+      </c>
+      <c r="BM223">
+        <v>2.55</v>
+      </c>
+      <c r="BN223">
+        <v>1.45</v>
+      </c>
+      <c r="BO223">
+        <v>3.3</v>
+      </c>
+      <c r="BP223">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="224" spans="1:68">
+      <c r="A224" s="1">
+        <v>223</v>
+      </c>
+      <c r="B224">
+        <v>7469089</v>
+      </c>
+      <c r="C224" t="s">
+        <v>68</v>
+      </c>
+      <c r="D224" t="s">
+        <v>69</v>
+      </c>
+      <c r="E224" s="2">
+        <v>45717.41666666666</v>
+      </c>
+      <c r="F224">
+        <v>25</v>
+      </c>
+      <c r="G224" t="s">
+        <v>73</v>
+      </c>
+      <c r="H224" t="s">
+        <v>78</v>
+      </c>
+      <c r="I224">
+        <v>1</v>
+      </c>
+      <c r="J224">
+        <v>0</v>
+      </c>
+      <c r="K224">
+        <v>1</v>
+      </c>
+      <c r="L224">
+        <v>1</v>
+      </c>
+      <c r="M224">
+        <v>2</v>
+      </c>
+      <c r="N224">
+        <v>3</v>
+      </c>
+      <c r="O224" t="s">
+        <v>232</v>
+      </c>
+      <c r="P224" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q224">
+        <v>5.2</v>
+      </c>
+      <c r="R224">
+        <v>2.19</v>
+      </c>
+      <c r="S224">
+        <v>2.29</v>
+      </c>
+      <c r="T224">
+        <v>1.42</v>
+      </c>
+      <c r="U224">
+        <v>2.7</v>
+      </c>
+      <c r="V224">
+        <v>2.85</v>
+      </c>
+      <c r="W224">
+        <v>1.38</v>
+      </c>
+      <c r="X224">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="Y224">
+        <v>1.01</v>
+      </c>
+      <c r="Z224">
+        <v>5.6</v>
+      </c>
+      <c r="AA224">
+        <v>3.74</v>
+      </c>
+      <c r="AB224">
+        <v>1.6</v>
+      </c>
+      <c r="AC224">
+        <v>1.06</v>
+      </c>
+      <c r="AD224">
+        <v>8.5</v>
+      </c>
+      <c r="AE224">
+        <v>1.33</v>
+      </c>
+      <c r="AF224">
+        <v>3.05</v>
+      </c>
+      <c r="AG224">
+        <v>1.95</v>
+      </c>
+      <c r="AH224">
+        <v>1.79</v>
+      </c>
+      <c r="AI224">
+        <v>1.92</v>
+      </c>
+      <c r="AJ224">
+        <v>1.8</v>
+      </c>
+      <c r="AK224">
+        <v>2.01</v>
+      </c>
+      <c r="AL224">
+        <v>1.26</v>
+      </c>
+      <c r="AM224">
+        <v>1.18</v>
+      </c>
+      <c r="AN224">
+        <v>1.92</v>
+      </c>
+      <c r="AO224">
+        <v>1.45</v>
+      </c>
+      <c r="AP224">
+        <v>1.77</v>
+      </c>
+      <c r="AQ224">
+        <v>1.58</v>
+      </c>
+      <c r="AR224">
+        <v>1.63</v>
+      </c>
+      <c r="AS224">
+        <v>1.27</v>
+      </c>
+      <c r="AT224">
+        <v>2.9</v>
+      </c>
+      <c r="AU224">
+        <v>8</v>
+      </c>
+      <c r="AV224">
+        <v>7</v>
+      </c>
+      <c r="AW224">
+        <v>6</v>
+      </c>
+      <c r="AX224">
+        <v>9</v>
+      </c>
+      <c r="AY224">
+        <v>14</v>
+      </c>
+      <c r="AZ224">
+        <v>16</v>
+      </c>
+      <c r="BA224">
+        <v>5</v>
+      </c>
+      <c r="BB224">
+        <v>8</v>
+      </c>
+      <c r="BC224">
+        <v>13</v>
+      </c>
+      <c r="BD224">
+        <v>2.7</v>
+      </c>
+      <c r="BE224">
+        <v>6.4</v>
+      </c>
+      <c r="BF224">
+        <v>1.55</v>
+      </c>
+      <c r="BG224">
+        <v>1.43</v>
+      </c>
+      <c r="BH224">
+        <v>2.63</v>
+      </c>
+      <c r="BI224">
+        <v>1.72</v>
+      </c>
+      <c r="BJ224">
+        <v>1.98</v>
+      </c>
+      <c r="BK224">
+        <v>2.15</v>
+      </c>
+      <c r="BL224">
+        <v>1.61</v>
+      </c>
+      <c r="BM224">
+        <v>2.75</v>
+      </c>
+      <c r="BN224">
+        <v>1.38</v>
+      </c>
+      <c r="BO224">
+        <v>3.65</v>
+      </c>
+      <c r="BP224">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="225" spans="1:68">
+      <c r="A225" s="1">
+        <v>224</v>
+      </c>
+      <c r="B225">
+        <v>7469082</v>
+      </c>
+      <c r="C225" t="s">
+        <v>68</v>
+      </c>
+      <c r="D225" t="s">
+        <v>69</v>
+      </c>
+      <c r="E225" s="2">
+        <v>45717.66666666666</v>
+      </c>
+      <c r="F225">
+        <v>25</v>
+      </c>
+      <c r="G225" t="s">
+        <v>86</v>
+      </c>
+      <c r="H225" t="s">
+        <v>81</v>
+      </c>
+      <c r="I225">
+        <v>1</v>
+      </c>
+      <c r="J225">
+        <v>1</v>
+      </c>
+      <c r="K225">
+        <v>2</v>
+      </c>
+      <c r="L225">
+        <v>1</v>
+      </c>
+      <c r="M225">
+        <v>1</v>
+      </c>
+      <c r="N225">
+        <v>2</v>
+      </c>
+      <c r="O225" t="s">
+        <v>233</v>
+      </c>
+      <c r="P225" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q225">
+        <v>2.15</v>
+      </c>
+      <c r="R225">
+        <v>2.4</v>
+      </c>
+      <c r="S225">
+        <v>4.9</v>
+      </c>
+      <c r="T225">
+        <v>1.31</v>
+      </c>
+      <c r="U225">
+        <v>3.2</v>
+      </c>
+      <c r="V225">
+        <v>2.4</v>
+      </c>
+      <c r="W225">
+        <v>1.52</v>
+      </c>
+      <c r="X225">
+        <v>5.35</v>
+      </c>
+      <c r="Y225">
+        <v>1.12</v>
+      </c>
+      <c r="Z225">
+        <v>1.68</v>
+      </c>
+      <c r="AA225">
+        <v>3.82</v>
+      </c>
+      <c r="AB225">
+        <v>4.7</v>
+      </c>
+      <c r="AC225">
+        <v>1.04</v>
+      </c>
+      <c r="AD225">
+        <v>10</v>
+      </c>
+      <c r="AE225">
+        <v>1.21</v>
+      </c>
+      <c r="AF225">
+        <v>4</v>
+      </c>
+      <c r="AG225">
+        <v>1.83</v>
+      </c>
+      <c r="AH225">
+        <v>1.91</v>
+      </c>
+      <c r="AI225">
+        <v>1.68</v>
+      </c>
+      <c r="AJ225">
+        <v>2.07</v>
+      </c>
+      <c r="AK225">
+        <v>1.19</v>
+      </c>
+      <c r="AL225">
+        <v>1.22</v>
+      </c>
+      <c r="AM225">
+        <v>2.11</v>
+      </c>
+      <c r="AN225">
+        <v>2.58</v>
+      </c>
+      <c r="AO225">
+        <v>1.08</v>
+      </c>
+      <c r="AP225">
+        <v>2.46</v>
+      </c>
+      <c r="AQ225">
+        <v>1.08</v>
+      </c>
+      <c r="AR225">
+        <v>1.82</v>
+      </c>
+      <c r="AS225">
+        <v>1.47</v>
+      </c>
+      <c r="AT225">
+        <v>3.29</v>
+      </c>
+      <c r="AU225">
+        <v>6</v>
+      </c>
+      <c r="AV225">
+        <v>4</v>
+      </c>
+      <c r="AW225">
+        <v>12</v>
+      </c>
+      <c r="AX225">
+        <v>3</v>
+      </c>
+      <c r="AY225">
+        <v>18</v>
+      </c>
+      <c r="AZ225">
+        <v>7</v>
+      </c>
+      <c r="BA225">
+        <v>10</v>
+      </c>
+      <c r="BB225">
+        <v>5</v>
+      </c>
+      <c r="BC225">
+        <v>15</v>
+      </c>
+      <c r="BD225">
+        <v>1.52</v>
+      </c>
+      <c r="BE225">
+        <v>6.75</v>
+      </c>
+      <c r="BF225">
+        <v>2.8</v>
+      </c>
+      <c r="BG225">
+        <v>1.3</v>
+      </c>
+      <c r="BH225">
+        <v>3.15</v>
+      </c>
+      <c r="BI225">
+        <v>1.52</v>
+      </c>
+      <c r="BJ225">
+        <v>2.33</v>
+      </c>
+      <c r="BK225">
+        <v>1.83</v>
+      </c>
+      <c r="BL225">
+        <v>1.85</v>
+      </c>
+      <c r="BM225">
+        <v>2.3</v>
+      </c>
+      <c r="BN225">
+        <v>1.53</v>
+      </c>
+      <c r="BO225">
+        <v>2.95</v>
+      </c>
+      <c r="BP225">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
@@ -715,7 +715,7 @@
     <t>['45']</t>
   </si>
   <si>
-    <t>['45+2']</t>
+    <t>['45+2', '73', '88']</t>
   </si>
   <si>
     <t>['16', '45+2']</t>
@@ -1875,7 +1875,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ3">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -4962,7 +4962,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="AQ18">
         <v>0.83</v>
@@ -5995,7 +5995,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ23">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR23">
         <v>2.13</v>
@@ -7434,7 +7434,7 @@
         <v>1.5</v>
       </c>
       <c r="AP30">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="AQ30">
         <v>0.92</v>
@@ -9085,7 +9085,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ38">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR38">
         <v>1.59</v>
@@ -12790,7 +12790,7 @@
         <v>0.33</v>
       </c>
       <c r="AP56">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="AQ56">
         <v>0.83</v>
@@ -13617,7 +13617,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ60">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR60">
         <v>1.51</v>
@@ -16295,7 +16295,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ73">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR73">
         <v>1</v>
@@ -17734,7 +17734,7 @@
         <v>1.5</v>
       </c>
       <c r="AP80">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="AQ80">
         <v>1.31</v>
@@ -20824,7 +20824,7 @@
         <v>1</v>
       </c>
       <c r="AP95">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="AQ95">
         <v>1.36</v>
@@ -21033,7 +21033,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ96">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR96">
         <v>1.65</v>
@@ -22681,7 +22681,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ104">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR104">
         <v>1.78</v>
@@ -25150,7 +25150,7 @@
         <v>1.2</v>
       </c>
       <c r="AP116">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="AQ116">
         <v>1.46</v>
@@ -26183,7 +26183,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ121">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR121">
         <v>1.35</v>
@@ -27622,7 +27622,7 @@
         <v>1</v>
       </c>
       <c r="AP128">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="AQ128">
         <v>1</v>
@@ -30097,7 +30097,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ140">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR140">
         <v>1.24</v>
@@ -30506,7 +30506,7 @@
         <v>2.13</v>
       </c>
       <c r="AP142">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="AQ142">
         <v>1.77</v>
@@ -34832,7 +34832,7 @@
         <v>1.38</v>
       </c>
       <c r="AP163">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="AQ163">
         <v>1.58</v>
@@ -35041,7 +35041,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ164">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR164">
         <v>1.64</v>
@@ -38334,7 +38334,7 @@
         <v>1.44</v>
       </c>
       <c r="AP180">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="AQ180">
         <v>1.08</v>
@@ -38955,7 +38955,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ183">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR183">
         <v>1.2</v>
@@ -41836,7 +41836,7 @@
         <v>0.6</v>
       </c>
       <c r="AP197">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="AQ197">
         <v>0.58</v>
@@ -43487,7 +43487,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ205">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR205">
         <v>1.62</v>
@@ -45750,7 +45750,7 @@
         <v>1.33</v>
       </c>
       <c r="AP216">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="AQ216">
         <v>1.46</v>
@@ -47514,13 +47514,13 @@
         <v>2</v>
       </c>
       <c r="L225">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M225">
         <v>1</v>
       </c>
       <c r="N225">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O225" t="s">
         <v>233</v>
@@ -47604,10 +47604,10 @@
         <v>1.08</v>
       </c>
       <c r="AP225">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="AQ225">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR225">
         <v>1.82</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1412" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1418" uniqueCount="320">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -972,6 +972,9 @@
   <si>
     <t>['70', '89']</t>
   </si>
+  <si>
+    <t>['16', '62']</t>
+  </si>
 </sst>
 </file>
 
@@ -1332,7 +1335,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP225"/>
+  <dimension ref="A1:BP226"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1872,7 +1875,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ3">
         <v>1</v>
@@ -4759,7 +4762,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ17">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5374,7 +5377,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ20">
         <v>1</v>
@@ -7643,7 +7646,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ31">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR31">
         <v>1.38</v>
@@ -11966,7 +11969,7 @@
         <v>1.5</v>
       </c>
       <c r="AP52">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ52">
         <v>0.83</v>
@@ -13205,7 +13208,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ58">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR58">
         <v>1</v>
@@ -15468,7 +15471,7 @@
         <v>1</v>
       </c>
       <c r="AP69">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ69">
         <v>1.42</v>
@@ -16913,7 +16916,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ76">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR76">
         <v>1.45</v>
@@ -20827,7 +20830,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ95">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR95">
         <v>2.11</v>
@@ -23502,7 +23505,7 @@
         <v>1.2</v>
       </c>
       <c r="AP108">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ108">
         <v>1.58</v>
@@ -24123,7 +24126,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ111">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR111">
         <v>1.14</v>
@@ -24532,7 +24535,7 @@
         <v>1.4</v>
       </c>
       <c r="AP113">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ113">
         <v>1.08</v>
@@ -27416,7 +27419,7 @@
         <v>1</v>
       </c>
       <c r="AP127">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ127">
         <v>0.92</v>
@@ -29064,7 +29067,7 @@
         <v>2</v>
       </c>
       <c r="AP135">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ135">
         <v>1.77</v>
@@ -29273,7 +29276,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ136">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR136">
         <v>1.62</v>
@@ -31536,7 +31539,7 @@
         <v>1</v>
       </c>
       <c r="AP147">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ147">
         <v>1.31</v>
@@ -32775,7 +32778,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ153">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR153">
         <v>1.78</v>
@@ -33393,7 +33396,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ156">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR156">
         <v>1.52</v>
@@ -35862,7 +35865,7 @@
         <v>0.5</v>
       </c>
       <c r="AP168">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ168">
         <v>0.58</v>
@@ -38543,7 +38546,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ181">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR181">
         <v>1.42</v>
@@ -41630,7 +41633,7 @@
         <v>1.5</v>
       </c>
       <c r="AP196">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ196">
         <v>1.46</v>
@@ -42251,7 +42254,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ199">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR199">
         <v>1.34</v>
@@ -43072,7 +43075,7 @@
         <v>1.45</v>
       </c>
       <c r="AP203">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ203">
         <v>1.46</v>
@@ -47683,6 +47686,212 @@
       </c>
       <c r="BP225">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="226" spans="1:68">
+      <c r="A226" s="1">
+        <v>225</v>
+      </c>
+      <c r="B226">
+        <v>7469085</v>
+      </c>
+      <c r="C226" t="s">
+        <v>68</v>
+      </c>
+      <c r="D226" t="s">
+        <v>69</v>
+      </c>
+      <c r="E226" s="2">
+        <v>45719.69791666666</v>
+      </c>
+      <c r="F226">
+        <v>25</v>
+      </c>
+      <c r="G226" t="s">
+        <v>71</v>
+      </c>
+      <c r="H226" t="s">
+        <v>72</v>
+      </c>
+      <c r="I226">
+        <v>0</v>
+      </c>
+      <c r="J226">
+        <v>1</v>
+      </c>
+      <c r="K226">
+        <v>1</v>
+      </c>
+      <c r="L226">
+        <v>1</v>
+      </c>
+      <c r="M226">
+        <v>2</v>
+      </c>
+      <c r="N226">
+        <v>3</v>
+      </c>
+      <c r="O226" t="s">
+        <v>221</v>
+      </c>
+      <c r="P226" t="s">
+        <v>319</v>
+      </c>
+      <c r="Q226">
+        <v>4.4</v>
+      </c>
+      <c r="R226">
+        <v>1.9</v>
+      </c>
+      <c r="S226">
+        <v>3.05</v>
+      </c>
+      <c r="T226">
+        <v>1.61</v>
+      </c>
+      <c r="U226">
+        <v>2.21</v>
+      </c>
+      <c r="V226">
+        <v>3.7</v>
+      </c>
+      <c r="W226">
+        <v>1.24</v>
+      </c>
+      <c r="X226">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Y226">
+        <v>1</v>
+      </c>
+      <c r="Z226">
+        <v>3.45</v>
+      </c>
+      <c r="AA226">
+        <v>2.88</v>
+      </c>
+      <c r="AB226">
+        <v>2.31</v>
+      </c>
+      <c r="AC226">
+        <v>1.11</v>
+      </c>
+      <c r="AD226">
+        <v>6</v>
+      </c>
+      <c r="AE226">
+        <v>1.5</v>
+      </c>
+      <c r="AF226">
+        <v>2.25</v>
+      </c>
+      <c r="AG226">
+        <v>2.65</v>
+      </c>
+      <c r="AH226">
+        <v>1.42</v>
+      </c>
+      <c r="AI226">
+        <v>2.17</v>
+      </c>
+      <c r="AJ226">
+        <v>1.62</v>
+      </c>
+      <c r="AK226">
+        <v>1.59</v>
+      </c>
+      <c r="AL226">
+        <v>1.36</v>
+      </c>
+      <c r="AM226">
+        <v>1.29</v>
+      </c>
+      <c r="AN226">
+        <v>1.67</v>
+      </c>
+      <c r="AO226">
+        <v>1.36</v>
+      </c>
+      <c r="AP226">
+        <v>1.54</v>
+      </c>
+      <c r="AQ226">
+        <v>1.5</v>
+      </c>
+      <c r="AR226">
+        <v>1.25</v>
+      </c>
+      <c r="AS226">
+        <v>1.4</v>
+      </c>
+      <c r="AT226">
+        <v>2.65</v>
+      </c>
+      <c r="AU226">
+        <v>4</v>
+      </c>
+      <c r="AV226">
+        <v>4</v>
+      </c>
+      <c r="AW226">
+        <v>9</v>
+      </c>
+      <c r="AX226">
+        <v>5</v>
+      </c>
+      <c r="AY226">
+        <v>13</v>
+      </c>
+      <c r="AZ226">
+        <v>9</v>
+      </c>
+      <c r="BA226">
+        <v>4</v>
+      </c>
+      <c r="BB226">
+        <v>3</v>
+      </c>
+      <c r="BC226">
+        <v>7</v>
+      </c>
+      <c r="BD226">
+        <v>2.32</v>
+      </c>
+      <c r="BE226">
+        <v>6.1</v>
+      </c>
+      <c r="BF226">
+        <v>1.76</v>
+      </c>
+      <c r="BG226">
+        <v>1.57</v>
+      </c>
+      <c r="BH226">
+        <v>2.23</v>
+      </c>
+      <c r="BI226">
+        <v>1.96</v>
+      </c>
+      <c r="BJ226">
+        <v>1.74</v>
+      </c>
+      <c r="BK226">
+        <v>2.5</v>
+      </c>
+      <c r="BL226">
+        <v>1.46</v>
+      </c>
+      <c r="BM226">
+        <v>3.4</v>
+      </c>
+      <c r="BN226">
+        <v>1.26</v>
+      </c>
+      <c r="BO226">
+        <v>4.75</v>
+      </c>
+      <c r="BP226">
+        <v>1.12</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1418" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1466" uniqueCount="329">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -718,6 +718,24 @@
     <t>['45+2', '73', '88']</t>
   </si>
   <si>
+    <t>['5', '82']</t>
+  </si>
+  <si>
+    <t>['45+3']</t>
+  </si>
+  <si>
+    <t>['22', '51']</t>
+  </si>
+  <si>
+    <t>['65', '88', '90+2']</t>
+  </si>
+  <si>
+    <t>['12', '35', '38']</t>
+  </si>
+  <si>
+    <t>['12', '29', '64', '86', '90+4']</t>
+  </si>
+  <si>
     <t>['16', '45+2']</t>
   </si>
   <si>
@@ -874,9 +892,6 @@
     <t>['55', '90+4']</t>
   </si>
   <si>
-    <t>['45+3']</t>
-  </si>
-  <si>
     <t>['6', '85', '89']</t>
   </si>
   <si>
@@ -974,6 +989,18 @@
   </si>
   <si>
     <t>['16', '62']</t>
+  </si>
+  <si>
+    <t>['16', '90+6']</t>
+  </si>
+  <si>
+    <t>['65', '69']</t>
+  </si>
+  <si>
+    <t>['25', '71']</t>
+  </si>
+  <si>
+    <t>['69']</t>
   </si>
 </sst>
 </file>
@@ -1335,7 +1362,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP226"/>
+  <dimension ref="A1:BP234"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1591,7 +1618,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="Q2">
         <v>2.4</v>
@@ -2003,7 +2030,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="Q4">
         <v>3.6</v>
@@ -2084,7 +2111,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ4">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2493,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AQ6">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2699,10 +2726,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ7">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2827,7 +2854,7 @@
         <v>90</v>
       </c>
       <c r="P8" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="Q8">
         <v>3.1</v>
@@ -2905,7 +2932,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ8">
         <v>1.77</v>
@@ -3114,7 +3141,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ9">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3239,7 +3266,7 @@
         <v>94</v>
       </c>
       <c r="P10" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="Q10">
         <v>2.6</v>
@@ -3317,7 +3344,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ10">
         <v>0.92</v>
@@ -3526,7 +3553,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ11">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3857,7 +3884,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="Q13">
         <v>3.1</v>
@@ -4141,7 +4168,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ14">
         <v>0.58</v>
@@ -4347,10 +4374,10 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ15">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4475,7 +4502,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="Q16">
         <v>2.63</v>
@@ -4556,7 +4583,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ16">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4681,7 +4708,7 @@
         <v>99</v>
       </c>
       <c r="P17" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -4759,7 +4786,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ17">
         <v>1.5</v>
@@ -5171,10 +5198,10 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ19">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5380,7 +5407,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ20">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR20">
         <v>0.67</v>
@@ -5711,7 +5738,7 @@
         <v>103</v>
       </c>
       <c r="P22" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -5789,7 +5816,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ22">
         <v>0.92</v>
@@ -6123,7 +6150,7 @@
         <v>105</v>
       </c>
       <c r="P24" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="Q24">
         <v>2.62</v>
@@ -6201,10 +6228,10 @@
         <v>3</v>
       </c>
       <c r="AP24">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ24">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR24">
         <v>1.39</v>
@@ -6613,7 +6640,7 @@
         <v>1</v>
       </c>
       <c r="AP26">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AQ26">
         <v>0.85</v>
@@ -6822,7 +6849,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ27">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR27">
         <v>1.55</v>
@@ -6947,7 +6974,7 @@
         <v>108</v>
       </c>
       <c r="P28" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="Q28">
         <v>2.6</v>
@@ -7025,10 +7052,10 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ28">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR28">
         <v>1.92</v>
@@ -7234,7 +7261,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ29">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR29">
         <v>1.48</v>
@@ -7849,10 +7876,10 @@
         <v>3</v>
       </c>
       <c r="AP32">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ32">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR32">
         <v>0.82</v>
@@ -8058,7 +8085,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ33">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR33">
         <v>2.15</v>
@@ -8261,10 +8288,10 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ34">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR34">
         <v>1.55</v>
@@ -8389,7 +8416,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="Q35">
         <v>3.3</v>
@@ -8595,7 +8622,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="Q36">
         <v>3.1</v>
@@ -8673,7 +8700,7 @@
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ36">
         <v>1.58</v>
@@ -8801,7 +8828,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="Q37">
         <v>3.4</v>
@@ -8879,7 +8906,7 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AQ37">
         <v>0.58</v>
@@ -9007,7 +9034,7 @@
         <v>90</v>
       </c>
       <c r="P38" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="Q38">
         <v>3.2</v>
@@ -9213,7 +9240,7 @@
         <v>90</v>
       </c>
       <c r="P39" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="Q39">
         <v>3.4</v>
@@ -9497,7 +9524,7 @@
         <v>3</v>
       </c>
       <c r="AP40">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ40">
         <v>1.77</v>
@@ -9625,7 +9652,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="Q41">
         <v>2.5</v>
@@ -9703,10 +9730,10 @@
         <v>2</v>
       </c>
       <c r="AP41">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ41">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR41">
         <v>1.73</v>
@@ -9831,7 +9858,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="Q42">
         <v>3.25</v>
@@ -10037,7 +10064,7 @@
         <v>90</v>
       </c>
       <c r="P43" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="Q43">
         <v>2.75</v>
@@ -10115,10 +10142,10 @@
         <v>0.5</v>
       </c>
       <c r="AP43">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ43">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR43">
         <v>0.8</v>
@@ -10321,10 +10348,10 @@
         <v>0.5</v>
       </c>
       <c r="AP44">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ44">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR44">
         <v>1.25</v>
@@ -10530,7 +10557,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ45">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR45">
         <v>1.53</v>
@@ -10733,10 +10760,10 @@
         <v>1.5</v>
       </c>
       <c r="AP46">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ46">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR46">
         <v>1.88</v>
@@ -10939,10 +10966,10 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ47">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR47">
         <v>1.49</v>
@@ -11148,7 +11175,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ48">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR48">
         <v>1.82</v>
@@ -11351,10 +11378,10 @@
         <v>1.5</v>
       </c>
       <c r="AP49">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ49">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR49">
         <v>1.53</v>
@@ -11557,7 +11584,7 @@
         <v>3</v>
       </c>
       <c r="AP50">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ50">
         <v>1.46</v>
@@ -11763,10 +11790,10 @@
         <v>1.33</v>
       </c>
       <c r="AP51">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ51">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR51">
         <v>1.48</v>
@@ -12097,7 +12124,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -12303,7 +12330,7 @@
         <v>129</v>
       </c>
       <c r="P54" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="Q54">
         <v>2.55</v>
@@ -12509,7 +12536,7 @@
         <v>130</v>
       </c>
       <c r="P55" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="Q55">
         <v>2.55</v>
@@ -12590,7 +12617,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ55">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR55">
         <v>1.98</v>
@@ -12796,7 +12823,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ56">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR56">
         <v>1.76</v>
@@ -12921,7 +12948,7 @@
         <v>132</v>
       </c>
       <c r="P57" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -13333,7 +13360,7 @@
         <v>134</v>
       </c>
       <c r="P59" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="Q59">
         <v>2.62</v>
@@ -13411,10 +13438,10 @@
         <v>1.67</v>
       </c>
       <c r="AP59">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ59">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR59">
         <v>1.53</v>
@@ -13539,7 +13566,7 @@
         <v>135</v>
       </c>
       <c r="P60" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="Q60">
         <v>2.88</v>
@@ -13823,10 +13850,10 @@
         <v>1.5</v>
       </c>
       <c r="AP61">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AQ61">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR61">
         <v>1.29</v>
@@ -13951,7 +13978,7 @@
         <v>137</v>
       </c>
       <c r="P62" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="Q62">
         <v>3.6</v>
@@ -14029,7 +14056,7 @@
         <v>2</v>
       </c>
       <c r="AP62">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ62">
         <v>1.77</v>
@@ -14157,7 +14184,7 @@
         <v>138</v>
       </c>
       <c r="P63" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="Q63">
         <v>3.75</v>
@@ -14441,7 +14468,7 @@
         <v>0</v>
       </c>
       <c r="AP64">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ64">
         <v>0.58</v>
@@ -14647,10 +14674,10 @@
         <v>1.75</v>
       </c>
       <c r="AP65">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ65">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR65">
         <v>1.6</v>
@@ -15062,7 +15089,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ67">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR67">
         <v>1.61</v>
@@ -15187,7 +15214,7 @@
         <v>143</v>
       </c>
       <c r="P68" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15393,7 +15420,7 @@
         <v>144</v>
       </c>
       <c r="P69" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15474,7 +15501,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ69">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR69">
         <v>1.23</v>
@@ -15599,7 +15626,7 @@
         <v>145</v>
       </c>
       <c r="P70" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="Q70">
         <v>3.75</v>
@@ -15677,10 +15704,10 @@
         <v>1</v>
       </c>
       <c r="AP70">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ70">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR70">
         <v>1.55</v>
@@ -16011,7 +16038,7 @@
         <v>147</v>
       </c>
       <c r="P72" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16089,10 +16116,10 @@
         <v>0</v>
       </c>
       <c r="AP72">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ72">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR72">
         <v>1.72</v>
@@ -16217,7 +16244,7 @@
         <v>90</v>
       </c>
       <c r="P73" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="Q73">
         <v>4.33</v>
@@ -16423,7 +16450,7 @@
         <v>90</v>
       </c>
       <c r="P74" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="Q74">
         <v>2.4</v>
@@ -16501,7 +16528,7 @@
         <v>0.5</v>
       </c>
       <c r="AP74">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ74">
         <v>0.85</v>
@@ -16629,7 +16656,7 @@
         <v>148</v>
       </c>
       <c r="P75" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="Q75">
         <v>3.5</v>
@@ -16707,7 +16734,7 @@
         <v>0</v>
       </c>
       <c r="AP75">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ75">
         <v>0.58</v>
@@ -16835,7 +16862,7 @@
         <v>149</v>
       </c>
       <c r="P76" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="Q76">
         <v>2.88</v>
@@ -17119,7 +17146,7 @@
         <v>2</v>
       </c>
       <c r="AP77">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AQ77">
         <v>1.58</v>
@@ -17325,10 +17352,10 @@
         <v>1</v>
       </c>
       <c r="AP78">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ78">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR78">
         <v>1.7</v>
@@ -17453,7 +17480,7 @@
         <v>151</v>
       </c>
       <c r="P79" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17534,7 +17561,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ79">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR79">
         <v>1.66</v>
@@ -17659,7 +17686,7 @@
         <v>152</v>
       </c>
       <c r="P80" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="Q80">
         <v>2.05</v>
@@ -17740,7 +17767,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ80">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR80">
         <v>2.09</v>
@@ -17865,7 +17892,7 @@
         <v>90</v>
       </c>
       <c r="P81" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="Q81">
         <v>4.33</v>
@@ -18149,7 +18176,7 @@
         <v>1.33</v>
       </c>
       <c r="AP82">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ82">
         <v>0.92</v>
@@ -18564,7 +18591,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ84">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR84">
         <v>1.51</v>
@@ -18689,7 +18716,7 @@
         <v>90</v>
       </c>
       <c r="P85" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="Q85">
         <v>3.1</v>
@@ -18767,10 +18794,10 @@
         <v>0</v>
       </c>
       <c r="AP85">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ85">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR85">
         <v>1.48</v>
@@ -18895,7 +18922,7 @@
         <v>156</v>
       </c>
       <c r="P86" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -18976,7 +19003,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ86">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR86">
         <v>1.88</v>
@@ -19182,7 +19209,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ87">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR87">
         <v>1.28</v>
@@ -19385,7 +19412,7 @@
         <v>1.5</v>
       </c>
       <c r="AP88">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ88">
         <v>1.46</v>
@@ -19591,7 +19618,7 @@
         <v>0.75</v>
       </c>
       <c r="AP89">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ89">
         <v>0.83</v>
@@ -19719,7 +19746,7 @@
         <v>90</v>
       </c>
       <c r="P90" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="Q90">
         <v>2.38</v>
@@ -19797,10 +19824,10 @@
         <v>0.2</v>
       </c>
       <c r="AP90">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ90">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR90">
         <v>1.42</v>
@@ -20131,7 +20158,7 @@
         <v>160</v>
       </c>
       <c r="P92" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20212,7 +20239,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ92">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR92">
         <v>1.2</v>
@@ -20415,7 +20442,7 @@
         <v>1.5</v>
       </c>
       <c r="AP93">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ93">
         <v>1.58</v>
@@ -20621,10 +20648,10 @@
         <v>1.2</v>
       </c>
       <c r="AP94">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AQ94">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR94">
         <v>1.21</v>
@@ -20749,7 +20776,7 @@
         <v>162</v>
       </c>
       <c r="P95" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="Q95">
         <v>1.9</v>
@@ -20955,7 +20982,7 @@
         <v>163</v>
       </c>
       <c r="P96" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="Q96">
         <v>2.75</v>
@@ -21033,7 +21060,7 @@
         <v>1.2</v>
       </c>
       <c r="AP96">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ96">
         <v>1</v>
@@ -21367,7 +21394,7 @@
         <v>90</v>
       </c>
       <c r="P98" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="Q98">
         <v>4.75</v>
@@ -21651,10 +21678,10 @@
         <v>0.2</v>
       </c>
       <c r="AP99">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ99">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR99">
         <v>1.8</v>
@@ -21860,7 +21887,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ100">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR100">
         <v>1.57</v>
@@ -22272,7 +22299,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ102">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR102">
         <v>1.45</v>
@@ -22478,7 +22505,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ103">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR103">
         <v>1.26</v>
@@ -22603,7 +22630,7 @@
         <v>167</v>
       </c>
       <c r="P104" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="Q104">
         <v>2.25</v>
@@ -22681,7 +22708,7 @@
         <v>1.17</v>
       </c>
       <c r="AP104">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ104">
         <v>1</v>
@@ -23093,7 +23120,7 @@
         <v>1.25</v>
       </c>
       <c r="AP106">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ106">
         <v>0.92</v>
@@ -23299,7 +23326,7 @@
         <v>0.6</v>
       </c>
       <c r="AP107">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ107">
         <v>0.83</v>
@@ -23427,7 +23454,7 @@
         <v>90</v>
       </c>
       <c r="P108" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="Q108">
         <v>4.5</v>
@@ -23714,7 +23741,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ109">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR109">
         <v>1.6</v>
@@ -23920,7 +23947,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ110">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR110">
         <v>1.85</v>
@@ -24123,7 +24150,7 @@
         <v>0.8</v>
       </c>
       <c r="AP111">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AQ111">
         <v>1.5</v>
@@ -24251,7 +24278,7 @@
         <v>173</v>
       </c>
       <c r="P112" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="Q112">
         <v>3.5</v>
@@ -24538,7 +24565,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ113">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR113">
         <v>1.1</v>
@@ -24663,7 +24690,7 @@
         <v>90</v>
       </c>
       <c r="P114" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="Q114">
         <v>2.85</v>
@@ -24741,10 +24768,10 @@
         <v>0.67</v>
       </c>
       <c r="AP114">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ114">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR114">
         <v>1.28</v>
@@ -24947,7 +24974,7 @@
         <v>2.17</v>
       </c>
       <c r="AP115">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ115">
         <v>1.77</v>
@@ -25075,7 +25102,7 @@
         <v>175</v>
       </c>
       <c r="P116" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="Q116">
         <v>2.4</v>
@@ -25359,7 +25386,7 @@
         <v>0.8</v>
       </c>
       <c r="AP117">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ117">
         <v>0.58</v>
@@ -25487,7 +25514,7 @@
         <v>90</v>
       </c>
       <c r="P118" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="Q118">
         <v>4</v>
@@ -25568,7 +25595,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ118">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR118">
         <v>0.99</v>
@@ -26105,7 +26132,7 @@
         <v>178</v>
       </c>
       <c r="P121" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="Q121">
         <v>2.88</v>
@@ -26183,7 +26210,7 @@
         <v>1.14</v>
       </c>
       <c r="AP121">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ121">
         <v>1</v>
@@ -26389,10 +26416,10 @@
         <v>0.5</v>
       </c>
       <c r="AP122">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ122">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR122">
         <v>1.78</v>
@@ -26595,7 +26622,7 @@
         <v>1</v>
       </c>
       <c r="AP123">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ123">
         <v>0.92</v>
@@ -26801,10 +26828,10 @@
         <v>1</v>
       </c>
       <c r="AP124">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ124">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR124">
         <v>1.79</v>
@@ -27007,10 +27034,10 @@
         <v>1.14</v>
       </c>
       <c r="AP125">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ125">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR125">
         <v>1.66</v>
@@ -27216,7 +27243,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ126">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR126">
         <v>1.58</v>
@@ -27628,7 +27655,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ128">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR128">
         <v>1.83</v>
@@ -28246,7 +28273,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ131">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR131">
         <v>1.33</v>
@@ -28449,7 +28476,7 @@
         <v>1</v>
       </c>
       <c r="AP132">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ132">
         <v>0.92</v>
@@ -28783,7 +28810,7 @@
         <v>90</v>
       </c>
       <c r="P134" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="Q134">
         <v>3.2</v>
@@ -28861,10 +28888,10 @@
         <v>0.43</v>
       </c>
       <c r="AP134">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AQ134">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR134">
         <v>1.08</v>
@@ -28989,7 +29016,7 @@
         <v>90</v>
       </c>
       <c r="P135" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="Q135">
         <v>5</v>
@@ -29273,7 +29300,7 @@
         <v>1.17</v>
       </c>
       <c r="AP136">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ136">
         <v>1.5</v>
@@ -29479,7 +29506,7 @@
         <v>1.29</v>
       </c>
       <c r="AP137">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ137">
         <v>1.46</v>
@@ -29685,10 +29712,10 @@
         <v>0.14</v>
       </c>
       <c r="AP138">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ138">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR138">
         <v>1.44</v>
@@ -29894,7 +29921,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ139">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR139">
         <v>1.46</v>
@@ -30019,7 +30046,7 @@
         <v>188</v>
       </c>
       <c r="P140" t="s">
-        <v>286</v>
+        <v>235</v>
       </c>
       <c r="Q140">
         <v>2.95</v>
@@ -30225,7 +30252,7 @@
         <v>189</v>
       </c>
       <c r="P141" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="Q141">
         <v>2.8</v>
@@ -30306,7 +30333,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ141">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR141">
         <v>1.72</v>
@@ -30715,7 +30742,7 @@
         <v>0.57</v>
       </c>
       <c r="AP143">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ143">
         <v>0.83</v>
@@ -31049,7 +31076,7 @@
         <v>192</v>
       </c>
       <c r="P145" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="Q145">
         <v>2.75</v>
@@ -31255,7 +31282,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="Q146">
         <v>3.75</v>
@@ -31333,7 +31360,7 @@
         <v>1</v>
       </c>
       <c r="AP146">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AQ146">
         <v>0.92</v>
@@ -31461,7 +31488,7 @@
         <v>129</v>
       </c>
       <c r="P147" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="Q147">
         <v>3.75</v>
@@ -31542,7 +31569,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ147">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR147">
         <v>1.16</v>
@@ -31667,7 +31694,7 @@
         <v>90</v>
       </c>
       <c r="P148" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="Q148">
         <v>2.4</v>
@@ -31873,7 +31900,7 @@
         <v>90</v>
       </c>
       <c r="P149" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="Q149">
         <v>3.1</v>
@@ -31954,7 +31981,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ149">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR149">
         <v>1.68</v>
@@ -32157,10 +32184,10 @@
         <v>1</v>
       </c>
       <c r="AP150">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ150">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR150">
         <v>1.35</v>
@@ -32285,7 +32312,7 @@
         <v>194</v>
       </c>
       <c r="P151" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="Q151">
         <v>1.62</v>
@@ -32363,10 +32390,10 @@
         <v>1.14</v>
       </c>
       <c r="AP151">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ151">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR151">
         <v>1.79</v>
@@ -32569,7 +32596,7 @@
         <v>0.63</v>
       </c>
       <c r="AP152">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ152">
         <v>0.85</v>
@@ -32697,7 +32724,7 @@
         <v>95</v>
       </c>
       <c r="P153" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="Q153">
         <v>2.63</v>
@@ -32775,7 +32802,7 @@
         <v>1</v>
       </c>
       <c r="AP153">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ153">
         <v>1.5</v>
@@ -32984,7 +33011,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ154">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR154">
         <v>1.27</v>
@@ -33190,7 +33217,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ155">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR155">
         <v>1</v>
@@ -33393,7 +33420,7 @@
         <v>1</v>
       </c>
       <c r="AP156">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ156">
         <v>1.5</v>
@@ -33521,7 +33548,7 @@
         <v>197</v>
       </c>
       <c r="P157" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="Q157">
         <v>2.7</v>
@@ -33602,7 +33629,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ157">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR157">
         <v>1.86</v>
@@ -33727,7 +33754,7 @@
         <v>96</v>
       </c>
       <c r="P158" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="Q158">
         <v>2.55</v>
@@ -33933,7 +33960,7 @@
         <v>198</v>
       </c>
       <c r="P159" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="Q159">
         <v>3.3</v>
@@ -34139,7 +34166,7 @@
         <v>90</v>
       </c>
       <c r="P160" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="Q160">
         <v>2.75</v>
@@ -34217,7 +34244,7 @@
         <v>0.5</v>
       </c>
       <c r="AP160">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ160">
         <v>0.83</v>
@@ -34423,10 +34450,10 @@
         <v>0.75</v>
       </c>
       <c r="AP161">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ161">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR161">
         <v>1.88</v>
@@ -34629,10 +34656,10 @@
         <v>0.13</v>
       </c>
       <c r="AP162">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ162">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR162">
         <v>1.68</v>
@@ -35041,7 +35068,7 @@
         <v>1.11</v>
       </c>
       <c r="AP164">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ164">
         <v>1</v>
@@ -35247,10 +35274,10 @@
         <v>1.38</v>
       </c>
       <c r="AP165">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AQ165">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR165">
         <v>1.13</v>
@@ -35581,7 +35608,7 @@
         <v>109</v>
       </c>
       <c r="P167" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="Q167">
         <v>3.35</v>
@@ -35659,7 +35686,7 @@
         <v>0.67</v>
       </c>
       <c r="AP167">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ167">
         <v>0.85</v>
@@ -35993,7 +36020,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="Q169">
         <v>2.8</v>
@@ -36074,7 +36101,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ169">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR169">
         <v>1.32</v>
@@ -36199,7 +36226,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="Q170">
         <v>3</v>
@@ -36277,7 +36304,7 @@
         <v>1.89</v>
       </c>
       <c r="AP170">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ170">
         <v>1.77</v>
@@ -36486,7 +36513,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ171">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR171">
         <v>1.68</v>
@@ -36611,7 +36638,7 @@
         <v>90</v>
       </c>
       <c r="P172" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="Q172">
         <v>2.63</v>
@@ -36692,7 +36719,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ172">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR172">
         <v>1.73</v>
@@ -36817,7 +36844,7 @@
         <v>207</v>
       </c>
       <c r="P173" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="Q173">
         <v>2.3</v>
@@ -36898,7 +36925,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ173">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR173">
         <v>1.78</v>
@@ -37101,7 +37128,7 @@
         <v>0.9</v>
       </c>
       <c r="AP174">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ174">
         <v>0.85</v>
@@ -37310,7 +37337,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ175">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR175">
         <v>0.95</v>
@@ -37516,7 +37543,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ176">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR176">
         <v>1.28</v>
@@ -37719,7 +37746,7 @@
         <v>0.78</v>
       </c>
       <c r="AP177">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ177">
         <v>0.83</v>
@@ -37847,7 +37874,7 @@
         <v>90</v>
       </c>
       <c r="P178" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="Q178">
         <v>3.25</v>
@@ -37925,7 +37952,7 @@
         <v>1.33</v>
       </c>
       <c r="AP178">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ178">
         <v>1.46</v>
@@ -38131,7 +38158,7 @@
         <v>1.1</v>
       </c>
       <c r="AP179">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ179">
         <v>0.92</v>
@@ -38259,7 +38286,7 @@
         <v>212</v>
       </c>
       <c r="P180" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="Q180">
         <v>2.2</v>
@@ -38340,7 +38367,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ180">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR180">
         <v>1.65</v>
@@ -38465,7 +38492,7 @@
         <v>90</v>
       </c>
       <c r="P181" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="Q181">
         <v>3.25</v>
@@ -38752,7 +38779,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ182">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR182">
         <v>1.62</v>
@@ -38955,7 +38982,7 @@
         <v>1</v>
       </c>
       <c r="AP183">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AQ183">
         <v>1</v>
@@ -39164,7 +39191,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ184">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR184">
         <v>1.62</v>
@@ -39367,10 +39394,10 @@
         <v>1.5</v>
       </c>
       <c r="AP185">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ185">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR185">
         <v>1.51</v>
@@ -39573,7 +39600,7 @@
         <v>1.33</v>
       </c>
       <c r="AP186">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ186">
         <v>1.58</v>
@@ -39701,7 +39728,7 @@
         <v>90</v>
       </c>
       <c r="P187" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="Q187">
         <v>2.55</v>
@@ -39782,7 +39809,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ187">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR187">
         <v>1.32</v>
@@ -39907,7 +39934,7 @@
         <v>215</v>
       </c>
       <c r="P188" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="Q188">
         <v>4.5</v>
@@ -39985,10 +40012,10 @@
         <v>1.2</v>
       </c>
       <c r="AP188">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ188">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR188">
         <v>1.26</v>
@@ -40319,7 +40346,7 @@
         <v>90</v>
       </c>
       <c r="P190" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="Q190">
         <v>3.3</v>
@@ -40397,7 +40424,7 @@
         <v>1.7</v>
       </c>
       <c r="AP190">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ190">
         <v>1.77</v>
@@ -40525,7 +40552,7 @@
         <v>90</v>
       </c>
       <c r="P191" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="Q191">
         <v>2.75</v>
@@ -40606,7 +40633,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ191">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR191">
         <v>1.28</v>
@@ -40731,7 +40758,7 @@
         <v>90</v>
       </c>
       <c r="P192" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="Q192">
         <v>3.25</v>
@@ -41015,7 +41042,7 @@
         <v>1</v>
       </c>
       <c r="AP193">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AQ193">
         <v>0.92</v>
@@ -41221,7 +41248,7 @@
         <v>0.91</v>
       </c>
       <c r="AP194">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ194">
         <v>0.85</v>
@@ -41349,7 +41376,7 @@
         <v>214</v>
       </c>
       <c r="P195" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="Q195">
         <v>4.75</v>
@@ -41430,7 +41457,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ195">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR195">
         <v>1.02</v>
@@ -41555,7 +41582,7 @@
         <v>90</v>
       </c>
       <c r="P196" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="Q196">
         <v>3.65</v>
@@ -41761,7 +41788,7 @@
         <v>218</v>
       </c>
       <c r="P197" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="Q197">
         <v>1.94</v>
@@ -41842,7 +41869,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ197">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR197">
         <v>1.67</v>
@@ -42045,10 +42072,10 @@
         <v>1.3</v>
       </c>
       <c r="AP198">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ198">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR198">
         <v>1.7</v>
@@ -42173,7 +42200,7 @@
         <v>90</v>
       </c>
       <c r="P199" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="Q199">
         <v>3.75</v>
@@ -42251,7 +42278,7 @@
         <v>1.2</v>
       </c>
       <c r="AP199">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ199">
         <v>1.5</v>
@@ -42666,7 +42693,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ201">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR201">
         <v>1.74</v>
@@ -42869,10 +42896,10 @@
         <v>1.4</v>
       </c>
       <c r="AP202">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ202">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR202">
         <v>1.2</v>
@@ -43078,7 +43105,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ203">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR203">
         <v>1.24</v>
@@ -43203,7 +43230,7 @@
         <v>160</v>
       </c>
       <c r="P204" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="Q204">
         <v>3</v>
@@ -43409,7 +43436,7 @@
         <v>90</v>
       </c>
       <c r="P205" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="Q205">
         <v>2.75</v>
@@ -43487,7 +43514,7 @@
         <v>0.91</v>
       </c>
       <c r="AP205">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ205">
         <v>1</v>
@@ -43821,7 +43848,7 @@
         <v>90</v>
       </c>
       <c r="P207" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="Q207">
         <v>3.8</v>
@@ -43899,7 +43926,7 @@
         <v>1.3</v>
       </c>
       <c r="AP207">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ207">
         <v>1.58</v>
@@ -44314,7 +44341,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ209">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR209">
         <v>1.77</v>
@@ -44517,7 +44544,7 @@
         <v>1</v>
       </c>
       <c r="AP210">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ210">
         <v>0.92</v>
@@ -44723,10 +44750,10 @@
         <v>1.08</v>
       </c>
       <c r="AP211">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ211">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR211">
         <v>1.79</v>
@@ -44932,7 +44959,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ212">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR212">
         <v>1.56</v>
@@ -45057,7 +45084,7 @@
         <v>226</v>
       </c>
       <c r="P213" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="Q213">
         <v>3.75</v>
@@ -45135,7 +45162,7 @@
         <v>1.64</v>
       </c>
       <c r="AP213">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AQ213">
         <v>1.46</v>
@@ -45344,7 +45371,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ214">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR214">
         <v>1.01</v>
@@ -45469,7 +45496,7 @@
         <v>228</v>
       </c>
       <c r="P215" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="Q215">
         <v>2.95</v>
@@ -45547,7 +45574,7 @@
         <v>0.83</v>
       </c>
       <c r="AP215">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ215">
         <v>0.85</v>
@@ -45675,7 +45702,7 @@
         <v>90</v>
       </c>
       <c r="P216" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="Q216">
         <v>1.96</v>
@@ -45756,7 +45783,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ216">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR216">
         <v>1.78</v>
@@ -45959,10 +45986,10 @@
         <v>0.64</v>
       </c>
       <c r="AP217">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ217">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR217">
         <v>1.74</v>
@@ -46165,7 +46192,7 @@
         <v>0.91</v>
       </c>
       <c r="AP218">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ218">
         <v>0.83</v>
@@ -46293,7 +46320,7 @@
         <v>229</v>
       </c>
       <c r="P219" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="Q219">
         <v>4.3</v>
@@ -46580,7 +46607,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ220">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR220">
         <v>1.27</v>
@@ -46911,7 +46938,7 @@
         <v>90</v>
       </c>
       <c r="P222" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="Q222">
         <v>2.7</v>
@@ -47117,7 +47144,7 @@
         <v>231</v>
       </c>
       <c r="P223" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="Q223">
         <v>3.65</v>
@@ -47195,7 +47222,7 @@
         <v>1.58</v>
       </c>
       <c r="AP223">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ223">
         <v>1.46</v>
@@ -47323,7 +47350,7 @@
         <v>232</v>
       </c>
       <c r="P224" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="Q224">
         <v>5.2</v>
@@ -47735,7 +47762,7 @@
         <v>221</v>
       </c>
       <c r="P226" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="Q226">
         <v>4.4</v>
@@ -47892,6 +47919,1654 @@
       </c>
       <c r="BP226">
         <v>1.12</v>
+      </c>
+    </row>
+    <row r="227" spans="1:68">
+      <c r="A227" s="1">
+        <v>226</v>
+      </c>
+      <c r="B227">
+        <v>7469096</v>
+      </c>
+      <c r="C227" t="s">
+        <v>68</v>
+      </c>
+      <c r="D227" t="s">
+        <v>69</v>
+      </c>
+      <c r="E227" s="2">
+        <v>45723.66666666666</v>
+      </c>
+      <c r="F227">
+        <v>26</v>
+      </c>
+      <c r="G227" t="s">
+        <v>74</v>
+      </c>
+      <c r="H227" t="s">
+        <v>71</v>
+      </c>
+      <c r="I227">
+        <v>1</v>
+      </c>
+      <c r="J227">
+        <v>1</v>
+      </c>
+      <c r="K227">
+        <v>2</v>
+      </c>
+      <c r="L227">
+        <v>2</v>
+      </c>
+      <c r="M227">
+        <v>2</v>
+      </c>
+      <c r="N227">
+        <v>4</v>
+      </c>
+      <c r="O227" t="s">
+        <v>234</v>
+      </c>
+      <c r="P227" t="s">
+        <v>325</v>
+      </c>
+      <c r="Q227">
+        <v>2.7</v>
+      </c>
+      <c r="R227">
+        <v>1.95</v>
+      </c>
+      <c r="S227">
+        <v>4.2</v>
+      </c>
+      <c r="T227">
+        <v>1.5</v>
+      </c>
+      <c r="U227">
+        <v>2.4</v>
+      </c>
+      <c r="V227">
+        <v>3.3</v>
+      </c>
+      <c r="W227">
+        <v>1.28</v>
+      </c>
+      <c r="X227">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y227">
+        <v>1</v>
+      </c>
+      <c r="Z227">
+        <v>2.24</v>
+      </c>
+      <c r="AA227">
+        <v>3.2</v>
+      </c>
+      <c r="AB227">
+        <v>3.21</v>
+      </c>
+      <c r="AC227">
+        <v>1.09</v>
+      </c>
+      <c r="AD227">
+        <v>7</v>
+      </c>
+      <c r="AE227">
+        <v>1.45</v>
+      </c>
+      <c r="AF227">
+        <v>2.7</v>
+      </c>
+      <c r="AG227">
+        <v>2.25</v>
+      </c>
+      <c r="AH227">
+        <v>1.53</v>
+      </c>
+      <c r="AI227">
+        <v>2</v>
+      </c>
+      <c r="AJ227">
+        <v>1.7</v>
+      </c>
+      <c r="AK227">
+        <v>1.25</v>
+      </c>
+      <c r="AL227">
+        <v>1.3</v>
+      </c>
+      <c r="AM227">
+        <v>1.7</v>
+      </c>
+      <c r="AN227">
+        <v>1.92</v>
+      </c>
+      <c r="AO227">
+        <v>0.83</v>
+      </c>
+      <c r="AP227">
+        <v>1.86</v>
+      </c>
+      <c r="AQ227">
+        <v>0.85</v>
+      </c>
+      <c r="AR227">
+        <v>1.25</v>
+      </c>
+      <c r="AS227">
+        <v>1</v>
+      </c>
+      <c r="AT227">
+        <v>2.25</v>
+      </c>
+      <c r="AU227">
+        <v>6</v>
+      </c>
+      <c r="AV227">
+        <v>4</v>
+      </c>
+      <c r="AW227">
+        <v>11</v>
+      </c>
+      <c r="AX227">
+        <v>6</v>
+      </c>
+      <c r="AY227">
+        <v>17</v>
+      </c>
+      <c r="AZ227">
+        <v>10</v>
+      </c>
+      <c r="BA227">
+        <v>10</v>
+      </c>
+      <c r="BB227">
+        <v>5</v>
+      </c>
+      <c r="BC227">
+        <v>15</v>
+      </c>
+      <c r="BD227">
+        <v>1.71</v>
+      </c>
+      <c r="BE227">
+        <v>6.4</v>
+      </c>
+      <c r="BF227">
+        <v>2.4</v>
+      </c>
+      <c r="BG227">
+        <v>1.52</v>
+      </c>
+      <c r="BH227">
+        <v>2.33</v>
+      </c>
+      <c r="BI227">
+        <v>1.88</v>
+      </c>
+      <c r="BJ227">
+        <v>1.81</v>
+      </c>
+      <c r="BK227">
+        <v>2.4</v>
+      </c>
+      <c r="BL227">
+        <v>1.49</v>
+      </c>
+      <c r="BM227">
+        <v>3.15</v>
+      </c>
+      <c r="BN227">
+        <v>1.3</v>
+      </c>
+      <c r="BO227">
+        <v>4.3</v>
+      </c>
+      <c r="BP227">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="228" spans="1:68">
+      <c r="A228" s="1">
+        <v>227</v>
+      </c>
+      <c r="B228">
+        <v>7469095</v>
+      </c>
+      <c r="C228" t="s">
+        <v>68</v>
+      </c>
+      <c r="D228" t="s">
+        <v>69</v>
+      </c>
+      <c r="E228" s="2">
+        <v>45723.66666666666</v>
+      </c>
+      <c r="F228">
+        <v>26</v>
+      </c>
+      <c r="G228" t="s">
+        <v>83</v>
+      </c>
+      <c r="H228" t="s">
+        <v>77</v>
+      </c>
+      <c r="I228">
+        <v>1</v>
+      </c>
+      <c r="J228">
+        <v>0</v>
+      </c>
+      <c r="K228">
+        <v>1</v>
+      </c>
+      <c r="L228">
+        <v>1</v>
+      </c>
+      <c r="M228">
+        <v>0</v>
+      </c>
+      <c r="N228">
+        <v>1</v>
+      </c>
+      <c r="O228" t="s">
+        <v>235</v>
+      </c>
+      <c r="P228" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q228">
+        <v>1.97</v>
+      </c>
+      <c r="R228">
+        <v>2.22</v>
+      </c>
+      <c r="S228">
+        <v>7.4</v>
+      </c>
+      <c r="T228">
+        <v>1.38</v>
+      </c>
+      <c r="U228">
+        <v>2.71</v>
+      </c>
+      <c r="V228">
+        <v>2.93</v>
+      </c>
+      <c r="W228">
+        <v>1.33</v>
+      </c>
+      <c r="X228">
+        <v>7.8</v>
+      </c>
+      <c r="Y228">
+        <v>1.02</v>
+      </c>
+      <c r="Z228">
+        <v>1.44</v>
+      </c>
+      <c r="AA228">
+        <v>3.96</v>
+      </c>
+      <c r="AB228">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC228">
+        <v>1</v>
+      </c>
+      <c r="AD228">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE228">
+        <v>1.3</v>
+      </c>
+      <c r="AF228">
+        <v>3.08</v>
+      </c>
+      <c r="AG228">
+        <v>1.98</v>
+      </c>
+      <c r="AH228">
+        <v>1.77</v>
+      </c>
+      <c r="AI228">
+        <v>2.25</v>
+      </c>
+      <c r="AJ228">
+        <v>1.57</v>
+      </c>
+      <c r="AK228">
+        <v>1.08</v>
+      </c>
+      <c r="AL228">
+        <v>1.22</v>
+      </c>
+      <c r="AM228">
+        <v>2.82</v>
+      </c>
+      <c r="AN228">
+        <v>1.83</v>
+      </c>
+      <c r="AO228">
+        <v>1.42</v>
+      </c>
+      <c r="AP228">
+        <v>1.92</v>
+      </c>
+      <c r="AQ228">
+        <v>1.31</v>
+      </c>
+      <c r="AR228">
+        <v>1.77</v>
+      </c>
+      <c r="AS228">
+        <v>1.09</v>
+      </c>
+      <c r="AT228">
+        <v>2.86</v>
+      </c>
+      <c r="AU228">
+        <v>9</v>
+      </c>
+      <c r="AV228">
+        <v>4</v>
+      </c>
+      <c r="AW228">
+        <v>10</v>
+      </c>
+      <c r="AX228">
+        <v>3</v>
+      </c>
+      <c r="AY228">
+        <v>19</v>
+      </c>
+      <c r="AZ228">
+        <v>7</v>
+      </c>
+      <c r="BA228">
+        <v>7</v>
+      </c>
+      <c r="BB228">
+        <v>1</v>
+      </c>
+      <c r="BC228">
+        <v>8</v>
+      </c>
+      <c r="BD228">
+        <v>1.27</v>
+      </c>
+      <c r="BE228">
+        <v>7.5</v>
+      </c>
+      <c r="BF228">
+        <v>4.1</v>
+      </c>
+      <c r="BG228">
+        <v>1.42</v>
+      </c>
+      <c r="BH228">
+        <v>2.63</v>
+      </c>
+      <c r="BI228">
+        <v>1.72</v>
+      </c>
+      <c r="BJ228">
+        <v>1.98</v>
+      </c>
+      <c r="BK228">
+        <v>2.15</v>
+      </c>
+      <c r="BL228">
+        <v>1.63</v>
+      </c>
+      <c r="BM228">
+        <v>2.7</v>
+      </c>
+      <c r="BN228">
+        <v>1.4</v>
+      </c>
+      <c r="BO228">
+        <v>3.55</v>
+      </c>
+      <c r="BP228">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="229" spans="1:68">
+      <c r="A229" s="1">
+        <v>228</v>
+      </c>
+      <c r="B229">
+        <v>7469099</v>
+      </c>
+      <c r="C229" t="s">
+        <v>68</v>
+      </c>
+      <c r="D229" t="s">
+        <v>69</v>
+      </c>
+      <c r="E229" s="2">
+        <v>45723.66666666666</v>
+      </c>
+      <c r="F229">
+        <v>26</v>
+      </c>
+      <c r="G229" t="s">
+        <v>87</v>
+      </c>
+      <c r="H229" t="s">
+        <v>73</v>
+      </c>
+      <c r="I229">
+        <v>1</v>
+      </c>
+      <c r="J229">
+        <v>0</v>
+      </c>
+      <c r="K229">
+        <v>1</v>
+      </c>
+      <c r="L229">
+        <v>2</v>
+      </c>
+      <c r="M229">
+        <v>0</v>
+      </c>
+      <c r="N229">
+        <v>2</v>
+      </c>
+      <c r="O229" t="s">
+        <v>236</v>
+      </c>
+      <c r="P229" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q229">
+        <v>2.45</v>
+      </c>
+      <c r="R229">
+        <v>2.1</v>
+      </c>
+      <c r="S229">
+        <v>4.2</v>
+      </c>
+      <c r="T229">
+        <v>1.38</v>
+      </c>
+      <c r="U229">
+        <v>2.8</v>
+      </c>
+      <c r="V229">
+        <v>2.75</v>
+      </c>
+      <c r="W229">
+        <v>1.4</v>
+      </c>
+      <c r="X229">
+        <v>7.5</v>
+      </c>
+      <c r="Y229">
+        <v>1.03</v>
+      </c>
+      <c r="Z229">
+        <v>2.07</v>
+      </c>
+      <c r="AA229">
+        <v>3.32</v>
+      </c>
+      <c r="AB229">
+        <v>3.5</v>
+      </c>
+      <c r="AC229">
+        <v>1.06</v>
+      </c>
+      <c r="AD229">
+        <v>8.5</v>
+      </c>
+      <c r="AE229">
+        <v>1.33</v>
+      </c>
+      <c r="AF229">
+        <v>3.25</v>
+      </c>
+      <c r="AG229">
+        <v>1.98</v>
+      </c>
+      <c r="AH229">
+        <v>1.77</v>
+      </c>
+      <c r="AI229">
+        <v>1.77</v>
+      </c>
+      <c r="AJ229">
+        <v>1.9</v>
+      </c>
+      <c r="AK229">
+        <v>1.22</v>
+      </c>
+      <c r="AL229">
+        <v>1.25</v>
+      </c>
+      <c r="AM229">
+        <v>1.85</v>
+      </c>
+      <c r="AN229">
+        <v>1.42</v>
+      </c>
+      <c r="AO229">
+        <v>0.58</v>
+      </c>
+      <c r="AP229">
+        <v>1.54</v>
+      </c>
+      <c r="AQ229">
+        <v>0.54</v>
+      </c>
+      <c r="AR229">
+        <v>1.3</v>
+      </c>
+      <c r="AS229">
+        <v>1.16</v>
+      </c>
+      <c r="AT229">
+        <v>2.46</v>
+      </c>
+      <c r="AU229">
+        <v>6</v>
+      </c>
+      <c r="AV229">
+        <v>3</v>
+      </c>
+      <c r="AW229">
+        <v>12</v>
+      </c>
+      <c r="AX229">
+        <v>5</v>
+      </c>
+      <c r="AY229">
+        <v>18</v>
+      </c>
+      <c r="AZ229">
+        <v>8</v>
+      </c>
+      <c r="BA229">
+        <v>4</v>
+      </c>
+      <c r="BB229">
+        <v>5</v>
+      </c>
+      <c r="BC229">
+        <v>9</v>
+      </c>
+      <c r="BD229">
+        <v>1.66</v>
+      </c>
+      <c r="BE229">
+        <v>6.4</v>
+      </c>
+      <c r="BF229">
+        <v>2.48</v>
+      </c>
+      <c r="BG229">
+        <v>1.35</v>
+      </c>
+      <c r="BH229">
+        <v>2.9</v>
+      </c>
+      <c r="BI229">
+        <v>1.58</v>
+      </c>
+      <c r="BJ229">
+        <v>2.18</v>
+      </c>
+      <c r="BK229">
+        <v>1.96</v>
+      </c>
+      <c r="BL229">
+        <v>1.74</v>
+      </c>
+      <c r="BM229">
+        <v>2.48</v>
+      </c>
+      <c r="BN229">
+        <v>1.47</v>
+      </c>
+      <c r="BO229">
+        <v>3.3</v>
+      </c>
+      <c r="BP229">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="230" spans="1:68">
+      <c r="A230" s="1">
+        <v>229</v>
+      </c>
+      <c r="B230">
+        <v>7469093</v>
+      </c>
+      <c r="C230" t="s">
+        <v>68</v>
+      </c>
+      <c r="D230" t="s">
+        <v>69</v>
+      </c>
+      <c r="E230" s="2">
+        <v>45723.66666666666</v>
+      </c>
+      <c r="F230">
+        <v>26</v>
+      </c>
+      <c r="G230" t="s">
+        <v>82</v>
+      </c>
+      <c r="H230" t="s">
+        <v>79</v>
+      </c>
+      <c r="I230">
+        <v>0</v>
+      </c>
+      <c r="J230">
+        <v>0</v>
+      </c>
+      <c r="K230">
+        <v>0</v>
+      </c>
+      <c r="L230">
+        <v>0</v>
+      </c>
+      <c r="M230">
+        <v>2</v>
+      </c>
+      <c r="N230">
+        <v>2</v>
+      </c>
+      <c r="O230" t="s">
+        <v>90</v>
+      </c>
+      <c r="P230" t="s">
+        <v>326</v>
+      </c>
+      <c r="Q230">
+        <v>3.04</v>
+      </c>
+      <c r="R230">
+        <v>2.08</v>
+      </c>
+      <c r="S230">
+        <v>3.54</v>
+      </c>
+      <c r="T230">
+        <v>1.36</v>
+      </c>
+      <c r="U230">
+        <v>2.78</v>
+      </c>
+      <c r="V230">
+        <v>2.91</v>
+      </c>
+      <c r="W230">
+        <v>1.33</v>
+      </c>
+      <c r="X230">
+        <v>8.1</v>
+      </c>
+      <c r="Y230">
+        <v>1.02</v>
+      </c>
+      <c r="Z230">
+        <v>2.45</v>
+      </c>
+      <c r="AA230">
+        <v>3.09</v>
+      </c>
+      <c r="AB230">
+        <v>2.96</v>
+      </c>
+      <c r="AC230">
+        <v>1.05</v>
+      </c>
+      <c r="AD230">
+        <v>8</v>
+      </c>
+      <c r="AE230">
+        <v>1.27</v>
+      </c>
+      <c r="AF230">
+        <v>3.25</v>
+      </c>
+      <c r="AG230">
+        <v>1.95</v>
+      </c>
+      <c r="AH230">
+        <v>1.79</v>
+      </c>
+      <c r="AI230">
+        <v>1.75</v>
+      </c>
+      <c r="AJ230">
+        <v>1.96</v>
+      </c>
+      <c r="AK230">
+        <v>1.41</v>
+      </c>
+      <c r="AL230">
+        <v>1.32</v>
+      </c>
+      <c r="AM230">
+        <v>1.57</v>
+      </c>
+      <c r="AN230">
+        <v>1.83</v>
+      </c>
+      <c r="AO230">
+        <v>1</v>
+      </c>
+      <c r="AP230">
+        <v>1.69</v>
+      </c>
+      <c r="AQ230">
+        <v>1.14</v>
+      </c>
+      <c r="AR230">
+        <v>1.69</v>
+      </c>
+      <c r="AS230">
+        <v>1.33</v>
+      </c>
+      <c r="AT230">
+        <v>3.02</v>
+      </c>
+      <c r="AU230">
+        <v>5</v>
+      </c>
+      <c r="AV230">
+        <v>9</v>
+      </c>
+      <c r="AW230">
+        <v>5</v>
+      </c>
+      <c r="AX230">
+        <v>7</v>
+      </c>
+      <c r="AY230">
+        <v>10</v>
+      </c>
+      <c r="AZ230">
+        <v>16</v>
+      </c>
+      <c r="BA230">
+        <v>1</v>
+      </c>
+      <c r="BB230">
+        <v>6</v>
+      </c>
+      <c r="BC230">
+        <v>7</v>
+      </c>
+      <c r="BD230">
+        <v>1.79</v>
+      </c>
+      <c r="BE230">
+        <v>6.4</v>
+      </c>
+      <c r="BF230">
+        <v>2.23</v>
+      </c>
+      <c r="BG230">
+        <v>1.38</v>
+      </c>
+      <c r="BH230">
+        <v>2.8</v>
+      </c>
+      <c r="BI230">
+        <v>1.64</v>
+      </c>
+      <c r="BJ230">
+        <v>2.12</v>
+      </c>
+      <c r="BK230">
+        <v>2</v>
+      </c>
+      <c r="BL230">
+        <v>1.71</v>
+      </c>
+      <c r="BM230">
+        <v>2.55</v>
+      </c>
+      <c r="BN230">
+        <v>1.44</v>
+      </c>
+      <c r="BO230">
+        <v>3.4</v>
+      </c>
+      <c r="BP230">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="231" spans="1:68">
+      <c r="A231" s="1">
+        <v>230</v>
+      </c>
+      <c r="B231">
+        <v>7469092</v>
+      </c>
+      <c r="C231" t="s">
+        <v>68</v>
+      </c>
+      <c r="D231" t="s">
+        <v>69</v>
+      </c>
+      <c r="E231" s="2">
+        <v>45723.66666666666</v>
+      </c>
+      <c r="F231">
+        <v>26</v>
+      </c>
+      <c r="G231" t="s">
+        <v>76</v>
+      </c>
+      <c r="H231" t="s">
+        <v>80</v>
+      </c>
+      <c r="I231">
+        <v>0</v>
+      </c>
+      <c r="J231">
+        <v>1</v>
+      </c>
+      <c r="K231">
+        <v>1</v>
+      </c>
+      <c r="L231">
+        <v>0</v>
+      </c>
+      <c r="M231">
+        <v>1</v>
+      </c>
+      <c r="N231">
+        <v>1</v>
+      </c>
+      <c r="O231" t="s">
+        <v>90</v>
+      </c>
+      <c r="P231" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q231">
+        <v>2.76</v>
+      </c>
+      <c r="R231">
+        <v>2.07</v>
+      </c>
+      <c r="S231">
+        <v>4.05</v>
+      </c>
+      <c r="T231">
+        <v>1.41</v>
+      </c>
+      <c r="U231">
+        <v>2.6</v>
+      </c>
+      <c r="V231">
+        <v>2.93</v>
+      </c>
+      <c r="W231">
+        <v>1.33</v>
+      </c>
+      <c r="X231">
+        <v>7.2</v>
+      </c>
+      <c r="Y231">
+        <v>1.03</v>
+      </c>
+      <c r="Z231">
+        <v>2.28</v>
+      </c>
+      <c r="AA231">
+        <v>3.31</v>
+      </c>
+      <c r="AB231">
+        <v>3.04</v>
+      </c>
+      <c r="AC231">
+        <v>1.02</v>
+      </c>
+      <c r="AD231">
+        <v>7.9</v>
+      </c>
+      <c r="AE231">
+        <v>1.32</v>
+      </c>
+      <c r="AF231">
+        <v>2.97</v>
+      </c>
+      <c r="AG231">
+        <v>2</v>
+      </c>
+      <c r="AH231">
+        <v>1.67</v>
+      </c>
+      <c r="AI231">
+        <v>1.83</v>
+      </c>
+      <c r="AJ231">
+        <v>1.87</v>
+      </c>
+      <c r="AK231">
+        <v>1.33</v>
+      </c>
+      <c r="AL231">
+        <v>1.32</v>
+      </c>
+      <c r="AM231">
+        <v>1.69</v>
+      </c>
+      <c r="AN231">
+        <v>0.92</v>
+      </c>
+      <c r="AO231">
+        <v>1.46</v>
+      </c>
+      <c r="AP231">
+        <v>0.86</v>
+      </c>
+      <c r="AQ231">
+        <v>1.57</v>
+      </c>
+      <c r="AR231">
+        <v>1.26</v>
+      </c>
+      <c r="AS231">
+        <v>1.11</v>
+      </c>
+      <c r="AT231">
+        <v>2.37</v>
+      </c>
+      <c r="AU231">
+        <v>5</v>
+      </c>
+      <c r="AV231">
+        <v>2</v>
+      </c>
+      <c r="AW231">
+        <v>10</v>
+      </c>
+      <c r="AX231">
+        <v>9</v>
+      </c>
+      <c r="AY231">
+        <v>15</v>
+      </c>
+      <c r="AZ231">
+        <v>11</v>
+      </c>
+      <c r="BA231">
+        <v>0</v>
+      </c>
+      <c r="BB231">
+        <v>1</v>
+      </c>
+      <c r="BC231">
+        <v>1</v>
+      </c>
+      <c r="BD231">
+        <v>1.73</v>
+      </c>
+      <c r="BE231">
+        <v>6.4</v>
+      </c>
+      <c r="BF231">
+        <v>2.33</v>
+      </c>
+      <c r="BG231">
+        <v>1.38</v>
+      </c>
+      <c r="BH231">
+        <v>2.75</v>
+      </c>
+      <c r="BI231">
+        <v>1.65</v>
+      </c>
+      <c r="BJ231">
+        <v>2.08</v>
+      </c>
+      <c r="BK231">
+        <v>2.05</v>
+      </c>
+      <c r="BL231">
+        <v>1.68</v>
+      </c>
+      <c r="BM231">
+        <v>2.63</v>
+      </c>
+      <c r="BN231">
+        <v>1.43</v>
+      </c>
+      <c r="BO231">
+        <v>3.4</v>
+      </c>
+      <c r="BP231">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="232" spans="1:68">
+      <c r="A232" s="1">
+        <v>231</v>
+      </c>
+      <c r="B232">
+        <v>7469091</v>
+      </c>
+      <c r="C232" t="s">
+        <v>68</v>
+      </c>
+      <c r="D232" t="s">
+        <v>69</v>
+      </c>
+      <c r="E232" s="2">
+        <v>45723.66666666666</v>
+      </c>
+      <c r="F232">
+        <v>26</v>
+      </c>
+      <c r="G232" t="s">
+        <v>75</v>
+      </c>
+      <c r="H232" t="s">
+        <v>70</v>
+      </c>
+      <c r="I232">
+        <v>0</v>
+      </c>
+      <c r="J232">
+        <v>1</v>
+      </c>
+      <c r="K232">
+        <v>1</v>
+      </c>
+      <c r="L232">
+        <v>3</v>
+      </c>
+      <c r="M232">
+        <v>1</v>
+      </c>
+      <c r="N232">
+        <v>4</v>
+      </c>
+      <c r="O232" t="s">
+        <v>237</v>
+      </c>
+      <c r="P232" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q232">
+        <v>2.4</v>
+      </c>
+      <c r="R232">
+        <v>2.1</v>
+      </c>
+      <c r="S232">
+        <v>4.33</v>
+      </c>
+      <c r="T232">
+        <v>1.4</v>
+      </c>
+      <c r="U232">
+        <v>2.7</v>
+      </c>
+      <c r="V232">
+        <v>2.88</v>
+      </c>
+      <c r="W232">
+        <v>1.36</v>
+      </c>
+      <c r="X232">
+        <v>7.3</v>
+      </c>
+      <c r="Y232">
+        <v>1.03</v>
+      </c>
+      <c r="Z232">
+        <v>1.95</v>
+      </c>
+      <c r="AA232">
+        <v>3.36</v>
+      </c>
+      <c r="AB232">
+        <v>3.83</v>
+      </c>
+      <c r="AC232">
+        <v>1.06</v>
+      </c>
+      <c r="AD232">
+        <v>8.5</v>
+      </c>
+      <c r="AE232">
+        <v>1.33</v>
+      </c>
+      <c r="AF232">
+        <v>3.2</v>
+      </c>
+      <c r="AG232">
+        <v>1.98</v>
+      </c>
+      <c r="AH232">
+        <v>1.76</v>
+      </c>
+      <c r="AI232">
+        <v>1.85</v>
+      </c>
+      <c r="AJ232">
+        <v>1.83</v>
+      </c>
+      <c r="AK232">
+        <v>1.22</v>
+      </c>
+      <c r="AL232">
+        <v>1.25</v>
+      </c>
+      <c r="AM232">
+        <v>1.91</v>
+      </c>
+      <c r="AN232">
+        <v>1.67</v>
+      </c>
+      <c r="AO232">
+        <v>1.08</v>
+      </c>
+      <c r="AP232">
+        <v>1.77</v>
+      </c>
+      <c r="AQ232">
+        <v>1</v>
+      </c>
+      <c r="AR232">
+        <v>1.59</v>
+      </c>
+      <c r="AS232">
+        <v>1.34</v>
+      </c>
+      <c r="AT232">
+        <v>2.93</v>
+      </c>
+      <c r="AU232">
+        <v>11</v>
+      </c>
+      <c r="AV232">
+        <v>3</v>
+      </c>
+      <c r="AW232">
+        <v>8</v>
+      </c>
+      <c r="AX232">
+        <v>2</v>
+      </c>
+      <c r="AY232">
+        <v>19</v>
+      </c>
+      <c r="AZ232">
+        <v>5</v>
+      </c>
+      <c r="BA232">
+        <v>10</v>
+      </c>
+      <c r="BB232">
+        <v>0</v>
+      </c>
+      <c r="BC232">
+        <v>10</v>
+      </c>
+      <c r="BD232">
+        <v>1.58</v>
+      </c>
+      <c r="BE232">
+        <v>6.75</v>
+      </c>
+      <c r="BF232">
+        <v>2.6</v>
+      </c>
+      <c r="BG232">
+        <v>1.38</v>
+      </c>
+      <c r="BH232">
+        <v>2.8</v>
+      </c>
+      <c r="BI232">
+        <v>1.64</v>
+      </c>
+      <c r="BJ232">
+        <v>2.12</v>
+      </c>
+      <c r="BK232">
+        <v>2</v>
+      </c>
+      <c r="BL232">
+        <v>1.7</v>
+      </c>
+      <c r="BM232">
+        <v>2.55</v>
+      </c>
+      <c r="BN232">
+        <v>1.44</v>
+      </c>
+      <c r="BO232">
+        <v>3.3</v>
+      </c>
+      <c r="BP232">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="233" spans="1:68">
+      <c r="A233" s="1">
+        <v>232</v>
+      </c>
+      <c r="B233">
+        <v>7469094</v>
+      </c>
+      <c r="C233" t="s">
+        <v>68</v>
+      </c>
+      <c r="D233" t="s">
+        <v>69</v>
+      </c>
+      <c r="E233" s="2">
+        <v>45724.41666666666</v>
+      </c>
+      <c r="F233">
+        <v>26</v>
+      </c>
+      <c r="G233" t="s">
+        <v>85</v>
+      </c>
+      <c r="H233" t="s">
+        <v>86</v>
+      </c>
+      <c r="I233">
+        <v>3</v>
+      </c>
+      <c r="J233">
+        <v>1</v>
+      </c>
+      <c r="K233">
+        <v>4</v>
+      </c>
+      <c r="L233">
+        <v>3</v>
+      </c>
+      <c r="M233">
+        <v>2</v>
+      </c>
+      <c r="N233">
+        <v>5</v>
+      </c>
+      <c r="O233" t="s">
+        <v>238</v>
+      </c>
+      <c r="P233" t="s">
+        <v>327</v>
+      </c>
+      <c r="Q233">
+        <v>3.1</v>
+      </c>
+      <c r="R233">
+        <v>2</v>
+      </c>
+      <c r="S233">
+        <v>3.35</v>
+      </c>
+      <c r="T233">
+        <v>1.42</v>
+      </c>
+      <c r="U233">
+        <v>2.62</v>
+      </c>
+      <c r="V233">
+        <v>2.9</v>
+      </c>
+      <c r="W233">
+        <v>1.36</v>
+      </c>
+      <c r="X233">
+        <v>7.9</v>
+      </c>
+      <c r="Y233">
+        <v>1.02</v>
+      </c>
+      <c r="Z233">
+        <v>2.72</v>
+      </c>
+      <c r="AA233">
+        <v>2.77</v>
+      </c>
+      <c r="AB233">
+        <v>2.92</v>
+      </c>
+      <c r="AC233">
+        <v>1.08</v>
+      </c>
+      <c r="AD233">
+        <v>7.5</v>
+      </c>
+      <c r="AE233">
+        <v>1.38</v>
+      </c>
+      <c r="AF233">
+        <v>2.95</v>
+      </c>
+      <c r="AG233">
+        <v>2.05</v>
+      </c>
+      <c r="AH233">
+        <v>1.65</v>
+      </c>
+      <c r="AI233">
+        <v>1.8</v>
+      </c>
+      <c r="AJ233">
+        <v>1.85</v>
+      </c>
+      <c r="AK233">
+        <v>1.4</v>
+      </c>
+      <c r="AL233">
+        <v>1.33</v>
+      </c>
+      <c r="AM233">
+        <v>1.48</v>
+      </c>
+      <c r="AN233">
+        <v>2.17</v>
+      </c>
+      <c r="AO233">
+        <v>1.5</v>
+      </c>
+      <c r="AP233">
+        <v>2.23</v>
+      </c>
+      <c r="AQ233">
+        <v>1.38</v>
+      </c>
+      <c r="AR233">
+        <v>1.74</v>
+      </c>
+      <c r="AS233">
+        <v>1.53</v>
+      </c>
+      <c r="AT233">
+        <v>3.27</v>
+      </c>
+      <c r="AU233">
+        <v>6</v>
+      </c>
+      <c r="AV233">
+        <v>8</v>
+      </c>
+      <c r="AW233">
+        <v>5</v>
+      </c>
+      <c r="AX233">
+        <v>10</v>
+      </c>
+      <c r="AY233">
+        <v>11</v>
+      </c>
+      <c r="AZ233">
+        <v>18</v>
+      </c>
+      <c r="BA233">
+        <v>1</v>
+      </c>
+      <c r="BB233">
+        <v>7</v>
+      </c>
+      <c r="BC233">
+        <v>8</v>
+      </c>
+      <c r="BD233">
+        <v>1.95</v>
+      </c>
+      <c r="BE233">
+        <v>6.4</v>
+      </c>
+      <c r="BF233">
+        <v>2.05</v>
+      </c>
+      <c r="BG233">
+        <v>1.38</v>
+      </c>
+      <c r="BH233">
+        <v>2.8</v>
+      </c>
+      <c r="BI233">
+        <v>1.64</v>
+      </c>
+      <c r="BJ233">
+        <v>2.1</v>
+      </c>
+      <c r="BK233">
+        <v>2.02</v>
+      </c>
+      <c r="BL233">
+        <v>1.68</v>
+      </c>
+      <c r="BM233">
+        <v>2.55</v>
+      </c>
+      <c r="BN233">
+        <v>1.43</v>
+      </c>
+      <c r="BO233">
+        <v>3.4</v>
+      </c>
+      <c r="BP233">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="234" spans="1:68">
+      <c r="A234" s="1">
+        <v>233</v>
+      </c>
+      <c r="B234">
+        <v>7469097</v>
+      </c>
+      <c r="C234" t="s">
+        <v>68</v>
+      </c>
+      <c r="D234" t="s">
+        <v>69</v>
+      </c>
+      <c r="E234" s="2">
+        <v>45724.66666666666</v>
+      </c>
+      <c r="F234">
+        <v>26</v>
+      </c>
+      <c r="G234" t="s">
+        <v>78</v>
+      </c>
+      <c r="H234" t="s">
+        <v>84</v>
+      </c>
+      <c r="I234">
+        <v>2</v>
+      </c>
+      <c r="J234">
+        <v>0</v>
+      </c>
+      <c r="K234">
+        <v>2</v>
+      </c>
+      <c r="L234">
+        <v>5</v>
+      </c>
+      <c r="M234">
+        <v>1</v>
+      </c>
+      <c r="N234">
+        <v>6</v>
+      </c>
+      <c r="O234" t="s">
+        <v>239</v>
+      </c>
+      <c r="P234" t="s">
+        <v>328</v>
+      </c>
+      <c r="Q234">
+        <v>1.85</v>
+      </c>
+      <c r="R234">
+        <v>2.38</v>
+      </c>
+      <c r="S234">
+        <v>6.25</v>
+      </c>
+      <c r="T234">
+        <v>1.33</v>
+      </c>
+      <c r="U234">
+        <v>3</v>
+      </c>
+      <c r="V234">
+        <v>2.6</v>
+      </c>
+      <c r="W234">
+        <v>1.44</v>
+      </c>
+      <c r="X234">
+        <v>7.2</v>
+      </c>
+      <c r="Y234">
+        <v>1.03</v>
+      </c>
+      <c r="Z234">
+        <v>1.42</v>
+      </c>
+      <c r="AA234">
+        <v>4.4</v>
+      </c>
+      <c r="AB234">
+        <v>7.2</v>
+      </c>
+      <c r="AC234">
+        <v>1.04</v>
+      </c>
+      <c r="AD234">
+        <v>10</v>
+      </c>
+      <c r="AE234">
+        <v>1.28</v>
+      </c>
+      <c r="AF234">
+        <v>3.65</v>
+      </c>
+      <c r="AG234">
+        <v>1.85</v>
+      </c>
+      <c r="AH234">
+        <v>1.89</v>
+      </c>
+      <c r="AI234">
+        <v>2.05</v>
+      </c>
+      <c r="AJ234">
+        <v>1.67</v>
+      </c>
+      <c r="AK234">
+        <v>1.09</v>
+      </c>
+      <c r="AL234">
+        <v>1.15</v>
+      </c>
+      <c r="AM234">
+        <v>2.75</v>
+      </c>
+      <c r="AN234">
+        <v>2.15</v>
+      </c>
+      <c r="AO234">
+        <v>1.31</v>
+      </c>
+      <c r="AP234">
+        <v>2.21</v>
+      </c>
+      <c r="AQ234">
+        <v>1.21</v>
+      </c>
+      <c r="AR234">
+        <v>1.75</v>
+      </c>
+      <c r="AS234">
+        <v>1.31</v>
+      </c>
+      <c r="AT234">
+        <v>3.06</v>
+      </c>
+      <c r="AU234">
+        <v>6</v>
+      </c>
+      <c r="AV234">
+        <v>3</v>
+      </c>
+      <c r="AW234">
+        <v>4</v>
+      </c>
+      <c r="AX234">
+        <v>6</v>
+      </c>
+      <c r="AY234">
+        <v>10</v>
+      </c>
+      <c r="AZ234">
+        <v>9</v>
+      </c>
+      <c r="BA234">
+        <v>4</v>
+      </c>
+      <c r="BB234">
+        <v>3</v>
+      </c>
+      <c r="BC234">
+        <v>7</v>
+      </c>
+      <c r="BD234">
+        <v>1.4</v>
+      </c>
+      <c r="BE234">
+        <v>6.75</v>
+      </c>
+      <c r="BF234">
+        <v>3.3</v>
+      </c>
+      <c r="BG234">
+        <v>1.43</v>
+      </c>
+      <c r="BH234">
+        <v>2.63</v>
+      </c>
+      <c r="BI234">
+        <v>1.71</v>
+      </c>
+      <c r="BJ234">
+        <v>2</v>
+      </c>
+      <c r="BK234">
+        <v>2.12</v>
+      </c>
+      <c r="BL234">
+        <v>1.63</v>
+      </c>
+      <c r="BM234">
+        <v>2.7</v>
+      </c>
+      <c r="BN234">
+        <v>1.38</v>
+      </c>
+      <c r="BO234">
+        <v>3.65</v>
+      </c>
+      <c r="BP234">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
@@ -48491,13 +48491,13 @@
         <v>8</v>
       </c>
       <c r="BA229">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB229">
         <v>5</v>
       </c>
       <c r="BC229">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD229">
         <v>1.66</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1466" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1472" uniqueCount="330">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -736,6 +736,9 @@
     <t>['12', '29', '64', '86', '90+4']</t>
   </si>
   <si>
+    <t>['52', '54', '57', '80', '90']</t>
+  </si>
+  <si>
     <t>['16', '45+2']</t>
   </si>
   <si>
@@ -1362,7 +1365,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP234"/>
+  <dimension ref="A1:BP235"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1618,7 +1621,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q2">
         <v>2.4</v>
@@ -2030,7 +2033,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q4">
         <v>3.6</v>
@@ -2854,7 +2857,7 @@
         <v>90</v>
       </c>
       <c r="P8" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q8">
         <v>3.1</v>
@@ -3266,7 +3269,7 @@
         <v>94</v>
       </c>
       <c r="P10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q10">
         <v>2.6</v>
@@ -3884,7 +3887,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q13">
         <v>3.1</v>
@@ -3962,7 +3965,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ13">
         <v>1.58</v>
@@ -4502,7 +4505,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q16">
         <v>2.63</v>
@@ -4708,7 +4711,7 @@
         <v>99</v>
       </c>
       <c r="P17" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -4789,7 +4792,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ17">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5738,7 +5741,7 @@
         <v>103</v>
       </c>
       <c r="P22" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -6150,7 +6153,7 @@
         <v>105</v>
       </c>
       <c r="P24" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q24">
         <v>2.62</v>
@@ -6974,7 +6977,7 @@
         <v>108</v>
       </c>
       <c r="P28" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q28">
         <v>2.6</v>
@@ -7673,7 +7676,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ31">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR31">
         <v>1.38</v>
@@ -8416,7 +8419,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q35">
         <v>3.3</v>
@@ -8494,7 +8497,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ35">
         <v>1.46</v>
@@ -8622,7 +8625,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q36">
         <v>3.1</v>
@@ -8828,7 +8831,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q37">
         <v>3.4</v>
@@ -9034,7 +9037,7 @@
         <v>90</v>
       </c>
       <c r="P38" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q38">
         <v>3.2</v>
@@ -9240,7 +9243,7 @@
         <v>90</v>
       </c>
       <c r="P39" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q39">
         <v>3.4</v>
@@ -9652,7 +9655,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q41">
         <v>2.5</v>
@@ -9858,7 +9861,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q42">
         <v>3.25</v>
@@ -10064,7 +10067,7 @@
         <v>90</v>
       </c>
       <c r="P43" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q43">
         <v>2.75</v>
@@ -12124,7 +12127,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -12330,7 +12333,7 @@
         <v>129</v>
       </c>
       <c r="P54" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q54">
         <v>2.55</v>
@@ -12536,7 +12539,7 @@
         <v>130</v>
       </c>
       <c r="P55" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q55">
         <v>2.55</v>
@@ -12614,7 +12617,7 @@
         <v>1.33</v>
       </c>
       <c r="AP55">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ55">
         <v>1.57</v>
@@ -12948,7 +12951,7 @@
         <v>132</v>
       </c>
       <c r="P57" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -13235,7 +13238,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ58">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR58">
         <v>1</v>
@@ -13360,7 +13363,7 @@
         <v>134</v>
       </c>
       <c r="P59" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q59">
         <v>2.62</v>
@@ -13566,7 +13569,7 @@
         <v>135</v>
       </c>
       <c r="P60" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q60">
         <v>2.88</v>
@@ -13978,7 +13981,7 @@
         <v>137</v>
       </c>
       <c r="P62" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q62">
         <v>3.6</v>
@@ -14184,7 +14187,7 @@
         <v>138</v>
       </c>
       <c r="P63" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q63">
         <v>3.75</v>
@@ -15214,7 +15217,7 @@
         <v>143</v>
       </c>
       <c r="P68" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15292,7 +15295,7 @@
         <v>1</v>
       </c>
       <c r="AP68">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ68">
         <v>0.83</v>
@@ -15420,7 +15423,7 @@
         <v>144</v>
       </c>
       <c r="P69" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15626,7 +15629,7 @@
         <v>145</v>
       </c>
       <c r="P70" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q70">
         <v>3.75</v>
@@ -16038,7 +16041,7 @@
         <v>147</v>
       </c>
       <c r="P72" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16244,7 +16247,7 @@
         <v>90</v>
       </c>
       <c r="P73" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q73">
         <v>4.33</v>
@@ -16450,7 +16453,7 @@
         <v>90</v>
       </c>
       <c r="P74" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q74">
         <v>2.4</v>
@@ -16656,7 +16659,7 @@
         <v>148</v>
       </c>
       <c r="P75" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q75">
         <v>3.5</v>
@@ -16862,7 +16865,7 @@
         <v>149</v>
       </c>
       <c r="P76" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q76">
         <v>2.88</v>
@@ -16943,7 +16946,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ76">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR76">
         <v>1.45</v>
@@ -17480,7 +17483,7 @@
         <v>151</v>
       </c>
       <c r="P79" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17686,7 +17689,7 @@
         <v>152</v>
       </c>
       <c r="P80" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q80">
         <v>2.05</v>
@@ -17892,7 +17895,7 @@
         <v>90</v>
       </c>
       <c r="P81" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q81">
         <v>4.33</v>
@@ -18716,7 +18719,7 @@
         <v>90</v>
       </c>
       <c r="P85" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q85">
         <v>3.1</v>
@@ -18922,7 +18925,7 @@
         <v>156</v>
       </c>
       <c r="P86" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -19000,7 +19003,7 @@
         <v>1.4</v>
       </c>
       <c r="AP86">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ86">
         <v>1.38</v>
@@ -19746,7 +19749,7 @@
         <v>90</v>
       </c>
       <c r="P90" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q90">
         <v>2.38</v>
@@ -20158,7 +20161,7 @@
         <v>160</v>
       </c>
       <c r="P92" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20776,7 +20779,7 @@
         <v>162</v>
       </c>
       <c r="P95" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q95">
         <v>1.9</v>
@@ -20857,7 +20860,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ95">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR95">
         <v>2.11</v>
@@ -20982,7 +20985,7 @@
         <v>163</v>
       </c>
       <c r="P96" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q96">
         <v>2.75</v>
@@ -21394,7 +21397,7 @@
         <v>90</v>
       </c>
       <c r="P98" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q98">
         <v>4.75</v>
@@ -22630,7 +22633,7 @@
         <v>167</v>
       </c>
       <c r="P104" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q104">
         <v>2.25</v>
@@ -23454,7 +23457,7 @@
         <v>90</v>
       </c>
       <c r="P108" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q108">
         <v>4.5</v>
@@ -23944,7 +23947,7 @@
         <v>1.17</v>
       </c>
       <c r="AP110">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ110">
         <v>1.21</v>
@@ -24153,7 +24156,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ111">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR111">
         <v>1.14</v>
@@ -24278,7 +24281,7 @@
         <v>173</v>
       </c>
       <c r="P112" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q112">
         <v>3.5</v>
@@ -24690,7 +24693,7 @@
         <v>90</v>
       </c>
       <c r="P114" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q114">
         <v>2.85</v>
@@ -25102,7 +25105,7 @@
         <v>175</v>
       </c>
       <c r="P116" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q116">
         <v>2.4</v>
@@ -25514,7 +25517,7 @@
         <v>90</v>
       </c>
       <c r="P118" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q118">
         <v>4</v>
@@ -26132,7 +26135,7 @@
         <v>178</v>
       </c>
       <c r="P121" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q121">
         <v>2.88</v>
@@ -28064,7 +28067,7 @@
         <v>0.71</v>
       </c>
       <c r="AP130">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ130">
         <v>0.85</v>
@@ -28810,7 +28813,7 @@
         <v>90</v>
       </c>
       <c r="P134" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q134">
         <v>3.2</v>
@@ -29016,7 +29019,7 @@
         <v>90</v>
       </c>
       <c r="P135" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q135">
         <v>5</v>
@@ -29303,7 +29306,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ136">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR136">
         <v>1.62</v>
@@ -30252,7 +30255,7 @@
         <v>189</v>
       </c>
       <c r="P141" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q141">
         <v>2.8</v>
@@ -31076,7 +31079,7 @@
         <v>192</v>
       </c>
       <c r="P145" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q145">
         <v>2.75</v>
@@ -31282,7 +31285,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q146">
         <v>3.75</v>
@@ -31488,7 +31491,7 @@
         <v>129</v>
       </c>
       <c r="P147" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q147">
         <v>3.75</v>
@@ -31694,7 +31697,7 @@
         <v>90</v>
       </c>
       <c r="P148" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q148">
         <v>2.4</v>
@@ -31772,7 +31775,7 @@
         <v>0.88</v>
       </c>
       <c r="AP148">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ148">
         <v>0.92</v>
@@ -31900,7 +31903,7 @@
         <v>90</v>
       </c>
       <c r="P149" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q149">
         <v>3.1</v>
@@ -32312,7 +32315,7 @@
         <v>194</v>
       </c>
       <c r="P151" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q151">
         <v>1.62</v>
@@ -32724,7 +32727,7 @@
         <v>95</v>
       </c>
       <c r="P153" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q153">
         <v>2.63</v>
@@ -32805,7 +32808,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ153">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR153">
         <v>1.78</v>
@@ -33423,7 +33426,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ156">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR156">
         <v>1.52</v>
@@ -33548,7 +33551,7 @@
         <v>197</v>
       </c>
       <c r="P157" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q157">
         <v>2.7</v>
@@ -33626,7 +33629,7 @@
         <v>1.11</v>
       </c>
       <c r="AP157">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ157">
         <v>1.14</v>
@@ -33754,7 +33757,7 @@
         <v>96</v>
       </c>
       <c r="P158" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q158">
         <v>2.55</v>
@@ -33960,7 +33963,7 @@
         <v>198</v>
       </c>
       <c r="P159" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q159">
         <v>3.3</v>
@@ -34166,7 +34169,7 @@
         <v>90</v>
       </c>
       <c r="P160" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q160">
         <v>2.75</v>
@@ -35608,7 +35611,7 @@
         <v>109</v>
       </c>
       <c r="P167" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q167">
         <v>3.35</v>
@@ -36020,7 +36023,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q169">
         <v>2.8</v>
@@ -36226,7 +36229,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q170">
         <v>3</v>
@@ -36638,7 +36641,7 @@
         <v>90</v>
       </c>
       <c r="P172" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q172">
         <v>2.63</v>
@@ -36844,7 +36847,7 @@
         <v>207</v>
       </c>
       <c r="P173" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q173">
         <v>2.3</v>
@@ -36922,7 +36925,7 @@
         <v>0.11</v>
       </c>
       <c r="AP173">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ173">
         <v>0.85</v>
@@ -37874,7 +37877,7 @@
         <v>90</v>
       </c>
       <c r="P178" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q178">
         <v>3.25</v>
@@ -38286,7 +38289,7 @@
         <v>212</v>
       </c>
       <c r="P180" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q180">
         <v>2.2</v>
@@ -38492,7 +38495,7 @@
         <v>90</v>
       </c>
       <c r="P181" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q181">
         <v>3.25</v>
@@ -38573,7 +38576,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ181">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR181">
         <v>1.42</v>
@@ -39728,7 +39731,7 @@
         <v>90</v>
       </c>
       <c r="P187" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q187">
         <v>2.55</v>
@@ -39934,7 +39937,7 @@
         <v>215</v>
       </c>
       <c r="P188" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q188">
         <v>4.5</v>
@@ -40346,7 +40349,7 @@
         <v>90</v>
       </c>
       <c r="P190" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q190">
         <v>3.3</v>
@@ -40552,7 +40555,7 @@
         <v>90</v>
       </c>
       <c r="P191" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q191">
         <v>2.75</v>
@@ -40758,7 +40761,7 @@
         <v>90</v>
       </c>
       <c r="P192" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q192">
         <v>3.25</v>
@@ -40836,7 +40839,7 @@
         <v>0.8</v>
       </c>
       <c r="AP192">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ192">
         <v>0.92</v>
@@ -41376,7 +41379,7 @@
         <v>214</v>
       </c>
       <c r="P195" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q195">
         <v>4.75</v>
@@ -41582,7 +41585,7 @@
         <v>90</v>
       </c>
       <c r="P196" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q196">
         <v>3.65</v>
@@ -41788,7 +41791,7 @@
         <v>218</v>
       </c>
       <c r="P197" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q197">
         <v>1.94</v>
@@ -42200,7 +42203,7 @@
         <v>90</v>
       </c>
       <c r="P199" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q199">
         <v>3.75</v>
@@ -42281,7 +42284,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ199">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR199">
         <v>1.34</v>
@@ -43230,7 +43233,7 @@
         <v>160</v>
       </c>
       <c r="P204" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q204">
         <v>3</v>
@@ -43436,7 +43439,7 @@
         <v>90</v>
       </c>
       <c r="P205" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q205">
         <v>2.75</v>
@@ -43848,7 +43851,7 @@
         <v>90</v>
       </c>
       <c r="P207" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q207">
         <v>3.8</v>
@@ -44338,7 +44341,7 @@
         <v>0.55</v>
       </c>
       <c r="AP209">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ209">
         <v>0.54</v>
@@ -45084,7 +45087,7 @@
         <v>226</v>
       </c>
       <c r="P213" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q213">
         <v>3.75</v>
@@ -45496,7 +45499,7 @@
         <v>228</v>
       </c>
       <c r="P215" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q215">
         <v>2.95</v>
@@ -45702,7 +45705,7 @@
         <v>90</v>
       </c>
       <c r="P216" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q216">
         <v>1.96</v>
@@ -46320,7 +46323,7 @@
         <v>229</v>
       </c>
       <c r="P219" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q219">
         <v>4.3</v>
@@ -46938,7 +46941,7 @@
         <v>90</v>
       </c>
       <c r="P222" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q222">
         <v>2.7</v>
@@ -47144,7 +47147,7 @@
         <v>231</v>
       </c>
       <c r="P223" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q223">
         <v>3.65</v>
@@ -47350,7 +47353,7 @@
         <v>232</v>
       </c>
       <c r="P224" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q224">
         <v>5.2</v>
@@ -47762,7 +47765,7 @@
         <v>221</v>
       </c>
       <c r="P226" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q226">
         <v>4.4</v>
@@ -47843,7 +47846,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ226">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR226">
         <v>1.25</v>
@@ -47968,7 +47971,7 @@
         <v>234</v>
       </c>
       <c r="P227" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q227">
         <v>2.7</v>
@@ -48586,7 +48589,7 @@
         <v>90</v>
       </c>
       <c r="P230" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q230">
         <v>3.04</v>
@@ -49204,7 +49207,7 @@
         <v>238</v>
       </c>
       <c r="P233" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q233">
         <v>3.1</v>
@@ -49410,7 +49413,7 @@
         <v>239</v>
       </c>
       <c r="P234" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q234">
         <v>1.85</v>
@@ -49567,6 +49570,212 @@
       </c>
       <c r="BP234">
         <v>1.24</v>
+      </c>
+    </row>
+    <row r="235" spans="1:68">
+      <c r="A235" s="1">
+        <v>234</v>
+      </c>
+      <c r="B235">
+        <v>7469098</v>
+      </c>
+      <c r="C235" t="s">
+        <v>68</v>
+      </c>
+      <c r="D235" t="s">
+        <v>69</v>
+      </c>
+      <c r="E235" s="2">
+        <v>45726.69791666666</v>
+      </c>
+      <c r="F235">
+        <v>26</v>
+      </c>
+      <c r="G235" t="s">
+        <v>81</v>
+      </c>
+      <c r="H235" t="s">
+        <v>72</v>
+      </c>
+      <c r="I235">
+        <v>0</v>
+      </c>
+      <c r="J235">
+        <v>1</v>
+      </c>
+      <c r="K235">
+        <v>1</v>
+      </c>
+      <c r="L235">
+        <v>5</v>
+      </c>
+      <c r="M235">
+        <v>1</v>
+      </c>
+      <c r="N235">
+        <v>6</v>
+      </c>
+      <c r="O235" t="s">
+        <v>240</v>
+      </c>
+      <c r="P235" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q235">
+        <v>3</v>
+      </c>
+      <c r="R235">
+        <v>2.05</v>
+      </c>
+      <c r="S235">
+        <v>3.35</v>
+      </c>
+      <c r="T235">
+        <v>1.4</v>
+      </c>
+      <c r="U235">
+        <v>2.75</v>
+      </c>
+      <c r="V235">
+        <v>2.8</v>
+      </c>
+      <c r="W235">
+        <v>1.38</v>
+      </c>
+      <c r="X235">
+        <v>6.75</v>
+      </c>
+      <c r="Y235">
+        <v>1.06</v>
+      </c>
+      <c r="Z235">
+        <v>2.38</v>
+      </c>
+      <c r="AA235">
+        <v>3.27</v>
+      </c>
+      <c r="AB235">
+        <v>2.91</v>
+      </c>
+      <c r="AC235">
+        <v>1.06</v>
+      </c>
+      <c r="AD235">
+        <v>8.5</v>
+      </c>
+      <c r="AE235">
+        <v>1.33</v>
+      </c>
+      <c r="AF235">
+        <v>3.3</v>
+      </c>
+      <c r="AG235">
+        <v>1.89</v>
+      </c>
+      <c r="AH235">
+        <v>1.85</v>
+      </c>
+      <c r="AI235">
+        <v>1.7</v>
+      </c>
+      <c r="AJ235">
+        <v>2</v>
+      </c>
+      <c r="AK235">
+        <v>1.4</v>
+      </c>
+      <c r="AL235">
+        <v>1.25</v>
+      </c>
+      <c r="AM235">
+        <v>1.55</v>
+      </c>
+      <c r="AN235">
+        <v>1.17</v>
+      </c>
+      <c r="AO235">
+        <v>1.5</v>
+      </c>
+      <c r="AP235">
+        <v>1.31</v>
+      </c>
+      <c r="AQ235">
+        <v>1.38</v>
+      </c>
+      <c r="AR235">
+        <v>1.76</v>
+      </c>
+      <c r="AS235">
+        <v>1.38</v>
+      </c>
+      <c r="AT235">
+        <v>3.14</v>
+      </c>
+      <c r="AU235">
+        <v>10</v>
+      </c>
+      <c r="AV235">
+        <v>2</v>
+      </c>
+      <c r="AW235">
+        <v>7</v>
+      </c>
+      <c r="AX235">
+        <v>9</v>
+      </c>
+      <c r="AY235">
+        <v>17</v>
+      </c>
+      <c r="AZ235">
+        <v>11</v>
+      </c>
+      <c r="BA235">
+        <v>4</v>
+      </c>
+      <c r="BB235">
+        <v>3</v>
+      </c>
+      <c r="BC235">
+        <v>7</v>
+      </c>
+      <c r="BD235">
+        <v>1.81</v>
+      </c>
+      <c r="BE235">
+        <v>6.4</v>
+      </c>
+      <c r="BF235">
+        <v>2.18</v>
+      </c>
+      <c r="BG235">
+        <v>1.38</v>
+      </c>
+      <c r="BH235">
+        <v>2.7</v>
+      </c>
+      <c r="BI235">
+        <v>1.66</v>
+      </c>
+      <c r="BJ235">
+        <v>2.08</v>
+      </c>
+      <c r="BK235">
+        <v>2.07</v>
+      </c>
+      <c r="BL235">
+        <v>1.67</v>
+      </c>
+      <c r="BM235">
+        <v>2.65</v>
+      </c>
+      <c r="BN235">
+        <v>1.42</v>
+      </c>
+      <c r="BO235">
+        <v>3.4</v>
+      </c>
+      <c r="BP235">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1472" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1508" uniqueCount="336">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -739,6 +739,18 @@
     <t>['52', '54', '57', '80', '90']</t>
   </si>
   <si>
+    <t>['8', '85']</t>
+  </si>
+  <si>
+    <t>['54']</t>
+  </si>
+  <si>
+    <t>['57', '81']</t>
+  </si>
+  <si>
+    <t>['58', '73']</t>
+  </si>
+  <si>
     <t>['16', '45+2']</t>
   </si>
   <si>
@@ -1004,6 +1016,12 @@
   </si>
   <si>
     <t>['69']</t>
+  </si>
+  <si>
+    <t>['50', '54']</t>
+  </si>
+  <si>
+    <t>['21']</t>
   </si>
 </sst>
 </file>
@@ -1365,7 +1383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP235"/>
+  <dimension ref="A1:BP241"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1621,7 +1639,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="Q2">
         <v>2.4</v>
@@ -1699,10 +1717,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ2">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1905,7 +1923,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ3">
         <v>1</v>
@@ -2033,7 +2051,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="Q4">
         <v>3.6</v>
@@ -2317,10 +2335,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ5">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2857,7 +2875,7 @@
         <v>90</v>
       </c>
       <c r="P8" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="Q8">
         <v>3.1</v>
@@ -3141,7 +3159,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AQ9">
         <v>1.38</v>
@@ -3269,7 +3287,7 @@
         <v>94</v>
       </c>
       <c r="P10" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="Q10">
         <v>2.6</v>
@@ -3553,7 +3571,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ11">
         <v>1</v>
@@ -3762,7 +3780,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ12">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3887,7 +3905,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="Q13">
         <v>3.1</v>
@@ -4174,7 +4192,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ14">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4505,7 +4523,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="Q16">
         <v>2.63</v>
@@ -4583,7 +4601,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ16">
         <v>1.31</v>
@@ -4711,7 +4729,7 @@
         <v>99</v>
       </c>
       <c r="P17" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -4998,7 +5016,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ18">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5407,7 +5425,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ20">
         <v>1.14</v>
@@ -5613,7 +5631,7 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ21">
         <v>1.77</v>
@@ -5741,7 +5759,7 @@
         <v>103</v>
       </c>
       <c r="P22" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -5822,7 +5840,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ22">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR22">
         <v>1.64</v>
@@ -6153,7 +6171,7 @@
         <v>105</v>
       </c>
       <c r="P24" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="Q24">
         <v>2.62</v>
@@ -6437,7 +6455,7 @@
         <v>1</v>
       </c>
       <c r="AP25">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AQ25">
         <v>0.92</v>
@@ -6646,7 +6664,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ26">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AR26">
         <v>1.19</v>
@@ -6849,7 +6867,7 @@
         <v>3</v>
       </c>
       <c r="AP27">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ27">
         <v>1.38</v>
@@ -6977,7 +6995,7 @@
         <v>108</v>
       </c>
       <c r="P28" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="Q28">
         <v>2.6</v>
@@ -7470,7 +7488,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ30">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR30">
         <v>1.49</v>
@@ -7673,7 +7691,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ31">
         <v>1.38</v>
@@ -8085,7 +8103,7 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ33">
         <v>0.54</v>
@@ -8419,7 +8437,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="Q35">
         <v>3.3</v>
@@ -8500,7 +8518,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ35">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR35">
         <v>1.69</v>
@@ -8625,7 +8643,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="Q36">
         <v>3.1</v>
@@ -8831,7 +8849,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="Q37">
         <v>3.4</v>
@@ -8912,7 +8930,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ37">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR37">
         <v>1.13</v>
@@ -9037,7 +9055,7 @@
         <v>90</v>
       </c>
       <c r="P38" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="Q38">
         <v>3.2</v>
@@ -9115,7 +9133,7 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ38">
         <v>1</v>
@@ -9243,7 +9261,7 @@
         <v>90</v>
       </c>
       <c r="P39" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="Q39">
         <v>3.4</v>
@@ -9321,10 +9339,10 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AQ39">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR39">
         <v>0.8</v>
@@ -9655,7 +9673,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="Q41">
         <v>2.5</v>
@@ -9861,7 +9879,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Q42">
         <v>3.25</v>
@@ -9942,7 +9960,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ42">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AR42">
         <v>1.75</v>
@@ -10067,7 +10085,7 @@
         <v>90</v>
       </c>
       <c r="P43" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="Q43">
         <v>2.75</v>
@@ -10557,7 +10575,7 @@
         <v>3</v>
       </c>
       <c r="AP45">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ45">
         <v>1</v>
@@ -11175,7 +11193,7 @@
         <v>0.33</v>
       </c>
       <c r="AP48">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ48">
         <v>1.14</v>
@@ -11590,7 +11608,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ50">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR50">
         <v>1.61</v>
@@ -11999,10 +12017,10 @@
         <v>1.5</v>
       </c>
       <c r="AP52">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ52">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR52">
         <v>1.34</v>
@@ -12127,7 +12145,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -12333,7 +12351,7 @@
         <v>129</v>
       </c>
       <c r="P54" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="Q54">
         <v>2.55</v>
@@ -12411,10 +12429,10 @@
         <v>1</v>
       </c>
       <c r="AP54">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ54">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR54">
         <v>1.19</v>
@@ -12539,7 +12557,7 @@
         <v>130</v>
       </c>
       <c r="P55" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="Q55">
         <v>2.55</v>
@@ -12951,7 +12969,7 @@
         <v>132</v>
       </c>
       <c r="P57" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -13032,7 +13050,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ57">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AR57">
         <v>1.54</v>
@@ -13235,7 +13253,7 @@
         <v>1.5</v>
       </c>
       <c r="AP58">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AQ58">
         <v>1.38</v>
@@ -13363,7 +13381,7 @@
         <v>134</v>
       </c>
       <c r="P59" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="Q59">
         <v>2.62</v>
@@ -13569,7 +13587,7 @@
         <v>135</v>
       </c>
       <c r="P60" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="Q60">
         <v>2.88</v>
@@ -13647,7 +13665,7 @@
         <v>1</v>
       </c>
       <c r="AP60">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ60">
         <v>1</v>
@@ -13981,7 +13999,7 @@
         <v>137</v>
       </c>
       <c r="P62" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="Q62">
         <v>3.6</v>
@@ -14187,7 +14205,7 @@
         <v>138</v>
       </c>
       <c r="P63" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="Q63">
         <v>3.75</v>
@@ -14265,7 +14283,7 @@
         <v>3</v>
       </c>
       <c r="AP63">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ63">
         <v>1.58</v>
@@ -14474,7 +14492,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ64">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR64">
         <v>1.73</v>
@@ -14883,10 +14901,10 @@
         <v>1</v>
       </c>
       <c r="AP66">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ66">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR66">
         <v>1.59</v>
@@ -15217,7 +15235,7 @@
         <v>143</v>
       </c>
       <c r="P68" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15298,7 +15316,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ68">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR68">
         <v>1.95</v>
@@ -15423,7 +15441,7 @@
         <v>144</v>
       </c>
       <c r="P69" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15501,7 +15519,7 @@
         <v>1</v>
       </c>
       <c r="AP69">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ69">
         <v>1.31</v>
@@ -15629,7 +15647,7 @@
         <v>145</v>
       </c>
       <c r="P70" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="Q70">
         <v>3.75</v>
@@ -15913,10 +15931,10 @@
         <v>2</v>
       </c>
       <c r="AP71">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ71">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR71">
         <v>1.24</v>
@@ -16041,7 +16059,7 @@
         <v>147</v>
       </c>
       <c r="P72" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16247,7 +16265,7 @@
         <v>90</v>
       </c>
       <c r="P73" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="Q73">
         <v>4.33</v>
@@ -16325,7 +16343,7 @@
         <v>0.75</v>
       </c>
       <c r="AP73">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AQ73">
         <v>1</v>
@@ -16453,7 +16471,7 @@
         <v>90</v>
       </c>
       <c r="P74" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="Q74">
         <v>2.4</v>
@@ -16534,7 +16552,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ74">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AR74">
         <v>1.85</v>
@@ -16659,7 +16677,7 @@
         <v>148</v>
       </c>
       <c r="P75" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="Q75">
         <v>3.5</v>
@@ -16740,7 +16758,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ75">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR75">
         <v>1.25</v>
@@ -16865,7 +16883,7 @@
         <v>149</v>
       </c>
       <c r="P76" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="Q76">
         <v>2.88</v>
@@ -17483,7 +17501,7 @@
         <v>151</v>
       </c>
       <c r="P79" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17561,7 +17579,7 @@
         <v>0.25</v>
       </c>
       <c r="AP79">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ79">
         <v>0.85</v>
@@ -17689,7 +17707,7 @@
         <v>152</v>
       </c>
       <c r="P80" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="Q80">
         <v>2.05</v>
@@ -17895,7 +17913,7 @@
         <v>90</v>
       </c>
       <c r="P81" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="Q81">
         <v>4.33</v>
@@ -17973,7 +17991,7 @@
         <v>2.25</v>
       </c>
       <c r="AP81">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ81">
         <v>1.77</v>
@@ -18388,7 +18406,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ83">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR83">
         <v>1.6</v>
@@ -18591,7 +18609,7 @@
         <v>1.4</v>
       </c>
       <c r="AP84">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ84">
         <v>1.57</v>
@@ -18719,7 +18737,7 @@
         <v>90</v>
       </c>
       <c r="P85" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="Q85">
         <v>3.1</v>
@@ -18925,7 +18943,7 @@
         <v>156</v>
       </c>
       <c r="P86" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -19209,7 +19227,7 @@
         <v>1</v>
       </c>
       <c r="AP87">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ87">
         <v>1.31</v>
@@ -19418,7 +19436,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ88">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR88">
         <v>1.77</v>
@@ -19624,7 +19642,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ89">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR89">
         <v>1.72</v>
@@ -19749,7 +19767,7 @@
         <v>90</v>
       </c>
       <c r="P90" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="Q90">
         <v>2.38</v>
@@ -20033,10 +20051,10 @@
         <v>1</v>
       </c>
       <c r="AP91">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ91">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AR91">
         <v>1.25</v>
@@ -20161,7 +20179,7 @@
         <v>160</v>
       </c>
       <c r="P92" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20779,7 +20797,7 @@
         <v>162</v>
       </c>
       <c r="P95" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="Q95">
         <v>1.9</v>
@@ -20985,7 +21003,7 @@
         <v>163</v>
       </c>
       <c r="P96" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="Q96">
         <v>2.75</v>
@@ -21269,7 +21287,7 @@
         <v>2.4</v>
       </c>
       <c r="AP97">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ97">
         <v>1.77</v>
@@ -21397,7 +21415,7 @@
         <v>90</v>
       </c>
       <c r="P98" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="Q98">
         <v>4.75</v>
@@ -21475,10 +21493,10 @@
         <v>0.25</v>
       </c>
       <c r="AP98">
+        <v>0.57</v>
+      </c>
+      <c r="AQ98">
         <v>0.54</v>
-      </c>
-      <c r="AQ98">
-        <v>0.58</v>
       </c>
       <c r="AR98">
         <v>1.06</v>
@@ -22093,10 +22111,10 @@
         <v>0.67</v>
       </c>
       <c r="AP101">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AQ101">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR101">
         <v>1.04</v>
@@ -22299,7 +22317,7 @@
         <v>1.17</v>
       </c>
       <c r="AP102">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ102">
         <v>1.57</v>
@@ -22505,7 +22523,7 @@
         <v>1.33</v>
       </c>
       <c r="AP103">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ103">
         <v>1.38</v>
@@ -22633,7 +22651,7 @@
         <v>167</v>
       </c>
       <c r="P104" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="Q104">
         <v>2.25</v>
@@ -22917,10 +22935,10 @@
         <v>0.83</v>
       </c>
       <c r="AP105">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ105">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AR105">
         <v>1.41</v>
@@ -23332,7 +23350,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ107">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR107">
         <v>1.74</v>
@@ -23457,7 +23475,7 @@
         <v>90</v>
       </c>
       <c r="P108" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="Q108">
         <v>4.5</v>
@@ -23535,7 +23553,7 @@
         <v>1.2</v>
       </c>
       <c r="AP108">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ108">
         <v>1.58</v>
@@ -23741,7 +23759,7 @@
         <v>1.4</v>
       </c>
       <c r="AP109">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ109">
         <v>1.31</v>
@@ -24281,7 +24299,7 @@
         <v>173</v>
       </c>
       <c r="P112" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="Q112">
         <v>3.5</v>
@@ -24565,7 +24583,7 @@
         <v>1.4</v>
       </c>
       <c r="AP113">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ113">
         <v>1</v>
@@ -24693,7 +24711,7 @@
         <v>90</v>
       </c>
       <c r="P114" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="Q114">
         <v>2.85</v>
@@ -25105,7 +25123,7 @@
         <v>175</v>
       </c>
       <c r="P116" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="Q116">
         <v>2.4</v>
@@ -25186,7 +25204,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ116">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR116">
         <v>1.94</v>
@@ -25392,7 +25410,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ117">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR117">
         <v>1.7</v>
@@ -25517,7 +25535,7 @@
         <v>90</v>
       </c>
       <c r="P118" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="Q118">
         <v>4</v>
@@ -25595,7 +25613,7 @@
         <v>1.14</v>
       </c>
       <c r="AP118">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AQ118">
         <v>1.57</v>
@@ -25801,10 +25819,10 @@
         <v>0.5</v>
       </c>
       <c r="AP119">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ119">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR119">
         <v>1.46</v>
@@ -26007,7 +26025,7 @@
         <v>1.5</v>
       </c>
       <c r="AP120">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ120">
         <v>1.58</v>
@@ -26135,7 +26153,7 @@
         <v>178</v>
       </c>
       <c r="P121" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="Q121">
         <v>2.88</v>
@@ -26628,7 +26646,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ123">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR123">
         <v>1.44</v>
@@ -27449,7 +27467,7 @@
         <v>1</v>
       </c>
       <c r="AP127">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ127">
         <v>0.92</v>
@@ -27861,10 +27879,10 @@
         <v>1</v>
       </c>
       <c r="AP129">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AQ129">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR129">
         <v>0.99</v>
@@ -28070,7 +28088,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ130">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AR130">
         <v>1.89</v>
@@ -28273,7 +28291,7 @@
         <v>1.17</v>
       </c>
       <c r="AP131">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ131">
         <v>1</v>
@@ -28688,7 +28706,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ133">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR133">
         <v>1.34</v>
@@ -28813,7 +28831,7 @@
         <v>90</v>
       </c>
       <c r="P134" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="Q134">
         <v>3.2</v>
@@ -29019,7 +29037,7 @@
         <v>90</v>
       </c>
       <c r="P135" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="Q135">
         <v>5</v>
@@ -29097,7 +29115,7 @@
         <v>2</v>
       </c>
       <c r="AP135">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ135">
         <v>1.77</v>
@@ -29512,7 +29530,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ137">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR137">
         <v>1.66</v>
@@ -29921,7 +29939,7 @@
         <v>1.33</v>
       </c>
       <c r="AP139">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ139">
         <v>1.31</v>
@@ -30127,7 +30145,7 @@
         <v>1.13</v>
       </c>
       <c r="AP140">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ140">
         <v>1</v>
@@ -30255,7 +30273,7 @@
         <v>189</v>
       </c>
       <c r="P141" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="Q141">
         <v>2.8</v>
@@ -30333,7 +30351,7 @@
         <v>1.38</v>
       </c>
       <c r="AP141">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ141">
         <v>1.57</v>
@@ -30748,7 +30766,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ143">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR143">
         <v>1.16</v>
@@ -30951,7 +30969,7 @@
         <v>1.43</v>
       </c>
       <c r="AP144">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ144">
         <v>1.58</v>
@@ -31079,7 +31097,7 @@
         <v>192</v>
       </c>
       <c r="P145" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="Q145">
         <v>2.75</v>
@@ -31160,7 +31178,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ145">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR145">
         <v>1.62</v>
@@ -31285,7 +31303,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="Q146">
         <v>3.75</v>
@@ -31491,7 +31509,7 @@
         <v>129</v>
       </c>
       <c r="P147" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="Q147">
         <v>3.75</v>
@@ -31569,7 +31587,7 @@
         <v>1</v>
       </c>
       <c r="AP147">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ147">
         <v>1.21</v>
@@ -31697,7 +31715,7 @@
         <v>90</v>
       </c>
       <c r="P148" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="Q148">
         <v>2.4</v>
@@ -31778,7 +31796,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ148">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR148">
         <v>1.89</v>
@@ -31903,7 +31921,7 @@
         <v>90</v>
       </c>
       <c r="P149" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="Q149">
         <v>3.1</v>
@@ -31981,7 +31999,7 @@
         <v>0.88</v>
       </c>
       <c r="AP149">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ149">
         <v>1.14</v>
@@ -32315,7 +32333,7 @@
         <v>194</v>
       </c>
       <c r="P151" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="Q151">
         <v>1.62</v>
@@ -32602,7 +32620,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ152">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AR152">
         <v>1.6</v>
@@ -32727,7 +32745,7 @@
         <v>95</v>
       </c>
       <c r="P153" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="Q153">
         <v>2.63</v>
@@ -33217,7 +33235,7 @@
         <v>1.25</v>
       </c>
       <c r="AP155">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AQ155">
         <v>1</v>
@@ -33551,7 +33569,7 @@
         <v>197</v>
       </c>
       <c r="P157" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="Q157">
         <v>2.7</v>
@@ -33757,7 +33775,7 @@
         <v>96</v>
       </c>
       <c r="P158" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="Q158">
         <v>2.55</v>
@@ -33838,7 +33856,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ158">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR158">
         <v>1.25</v>
@@ -33963,7 +33981,7 @@
         <v>198</v>
       </c>
       <c r="P159" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="Q159">
         <v>3.3</v>
@@ -34041,10 +34059,10 @@
         <v>1.13</v>
       </c>
       <c r="AP159">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ159">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR159">
         <v>1.45</v>
@@ -34169,7 +34187,7 @@
         <v>90</v>
       </c>
       <c r="P160" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q160">
         <v>2.75</v>
@@ -34250,7 +34268,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ160">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR160">
         <v>1.38</v>
@@ -35483,7 +35501,7 @@
         <v>0.89</v>
       </c>
       <c r="AP166">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ166">
         <v>0.92</v>
@@ -35611,7 +35629,7 @@
         <v>109</v>
       </c>
       <c r="P167" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="Q167">
         <v>3.35</v>
@@ -35692,7 +35710,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ167">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AR167">
         <v>1.14</v>
@@ -35895,10 +35913,10 @@
         <v>0.5</v>
       </c>
       <c r="AP168">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ168">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR168">
         <v>1.22</v>
@@ -36023,7 +36041,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="Q169">
         <v>2.8</v>
@@ -36101,7 +36119,7 @@
         <v>1.56</v>
       </c>
       <c r="AP169">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ169">
         <v>1.57</v>
@@ -36229,7 +36247,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="Q170">
         <v>3</v>
@@ -36641,7 +36659,7 @@
         <v>90</v>
       </c>
       <c r="P172" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="Q172">
         <v>2.63</v>
@@ -36719,7 +36737,7 @@
         <v>1.22</v>
       </c>
       <c r="AP172">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ172">
         <v>1.21</v>
@@ -36847,7 +36865,7 @@
         <v>207</v>
       </c>
       <c r="P173" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="Q173">
         <v>2.3</v>
@@ -37134,7 +37152,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ174">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AR174">
         <v>1.67</v>
@@ -37337,7 +37355,7 @@
         <v>0.67</v>
       </c>
       <c r="AP175">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AQ175">
         <v>0.54</v>
@@ -37752,7 +37770,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ177">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR177">
         <v>1.6</v>
@@ -37877,7 +37895,7 @@
         <v>90</v>
       </c>
       <c r="P178" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="Q178">
         <v>3.25</v>
@@ -37958,7 +37976,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ178">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR178">
         <v>1.34</v>
@@ -38164,7 +38182,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ179">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR179">
         <v>1.86</v>
@@ -38289,7 +38307,7 @@
         <v>212</v>
       </c>
       <c r="P180" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="Q180">
         <v>2.2</v>
@@ -38495,7 +38513,7 @@
         <v>90</v>
       </c>
       <c r="P181" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="Q181">
         <v>3.25</v>
@@ -38573,7 +38591,7 @@
         <v>1</v>
       </c>
       <c r="AP181">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ181">
         <v>1.38</v>
@@ -39191,7 +39209,7 @@
         <v>1.4</v>
       </c>
       <c r="AP184">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ184">
         <v>1.21</v>
@@ -39731,7 +39749,7 @@
         <v>90</v>
       </c>
       <c r="P187" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="Q187">
         <v>2.55</v>
@@ -39809,7 +39827,7 @@
         <v>0.4</v>
       </c>
       <c r="AP187">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ187">
         <v>0.85</v>
@@ -39937,7 +39955,7 @@
         <v>215</v>
       </c>
       <c r="P188" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="Q188">
         <v>4.5</v>
@@ -40221,10 +40239,10 @@
         <v>0.44</v>
       </c>
       <c r="AP189">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ189">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR189">
         <v>1.73</v>
@@ -40349,7 +40367,7 @@
         <v>90</v>
       </c>
       <c r="P190" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="Q190">
         <v>3.3</v>
@@ -40555,7 +40573,7 @@
         <v>90</v>
       </c>
       <c r="P191" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="Q191">
         <v>2.75</v>
@@ -40761,7 +40779,7 @@
         <v>90</v>
       </c>
       <c r="P192" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="Q192">
         <v>3.25</v>
@@ -41048,7 +41066,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ193">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR193">
         <v>1.24</v>
@@ -41254,7 +41272,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ194">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AR194">
         <v>1.83</v>
@@ -41379,7 +41397,7 @@
         <v>214</v>
       </c>
       <c r="P195" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="Q195">
         <v>4.75</v>
@@ -41457,7 +41475,7 @@
         <v>0.91</v>
       </c>
       <c r="AP195">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AQ195">
         <v>1.14</v>
@@ -41585,7 +41603,7 @@
         <v>90</v>
       </c>
       <c r="P196" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="Q196">
         <v>3.65</v>
@@ -41663,10 +41681,10 @@
         <v>1.5</v>
       </c>
       <c r="AP196">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ196">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR196">
         <v>1.27</v>
@@ -41791,7 +41809,7 @@
         <v>218</v>
       </c>
       <c r="P197" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="Q197">
         <v>1.94</v>
@@ -42203,7 +42221,7 @@
         <v>90</v>
       </c>
       <c r="P199" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="Q199">
         <v>3.75</v>
@@ -42487,7 +42505,7 @@
         <v>1</v>
       </c>
       <c r="AP200">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ200">
         <v>0.92</v>
@@ -42693,7 +42711,7 @@
         <v>1.36</v>
       </c>
       <c r="AP201">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ201">
         <v>1.38</v>
@@ -43105,7 +43123,7 @@
         <v>1.45</v>
       </c>
       <c r="AP203">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ203">
         <v>1.57</v>
@@ -43233,7 +43251,7 @@
         <v>160</v>
       </c>
       <c r="P204" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="Q204">
         <v>3</v>
@@ -43311,10 +43329,10 @@
         <v>0.7</v>
       </c>
       <c r="AP204">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ204">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR204">
         <v>1.59</v>
@@ -43439,7 +43457,7 @@
         <v>90</v>
       </c>
       <c r="P205" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="Q205">
         <v>2.75</v>
@@ -43851,7 +43869,7 @@
         <v>90</v>
       </c>
       <c r="P207" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="Q207">
         <v>3.8</v>
@@ -44135,10 +44153,10 @@
         <v>0.4</v>
       </c>
       <c r="AP208">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ208">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR208">
         <v>1.37</v>
@@ -44550,7 +44568,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ210">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR210">
         <v>1.74</v>
@@ -45087,7 +45105,7 @@
         <v>226</v>
       </c>
       <c r="P213" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="Q213">
         <v>3.75</v>
@@ -45168,7 +45186,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ213">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR213">
         <v>1.24</v>
@@ -45371,7 +45389,7 @@
         <v>1.42</v>
       </c>
       <c r="AP214">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AQ214">
         <v>1.21</v>
@@ -45499,7 +45517,7 @@
         <v>228</v>
       </c>
       <c r="P215" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="Q215">
         <v>2.95</v>
@@ -45580,7 +45598,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ215">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AR215">
         <v>1.26</v>
@@ -45705,7 +45723,7 @@
         <v>90</v>
       </c>
       <c r="P216" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="Q216">
         <v>1.96</v>
@@ -46198,7 +46216,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ218">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR218">
         <v>1.63</v>
@@ -46323,7 +46341,7 @@
         <v>229</v>
       </c>
       <c r="P219" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="Q219">
         <v>4.3</v>
@@ -46401,7 +46419,7 @@
         <v>1.67</v>
       </c>
       <c r="AP219">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ219">
         <v>1.77</v>
@@ -46813,7 +46831,7 @@
         <v>1</v>
       </c>
       <c r="AP221">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ221">
         <v>0.92</v>
@@ -46941,7 +46959,7 @@
         <v>90</v>
       </c>
       <c r="P222" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="Q222">
         <v>2.7</v>
@@ -47019,10 +47037,10 @@
         <v>0.36</v>
       </c>
       <c r="AP222">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ222">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR222">
         <v>1.41</v>
@@ -47147,7 +47165,7 @@
         <v>231</v>
       </c>
       <c r="P223" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="Q223">
         <v>3.65</v>
@@ -47228,7 +47246,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ223">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR223">
         <v>1.28</v>
@@ -47353,7 +47371,7 @@
         <v>232</v>
       </c>
       <c r="P224" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="Q224">
         <v>5.2</v>
@@ -47431,7 +47449,7 @@
         <v>1.45</v>
       </c>
       <c r="AP224">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ224">
         <v>1.58</v>
@@ -47765,7 +47783,7 @@
         <v>221</v>
       </c>
       <c r="P226" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="Q226">
         <v>4.4</v>
@@ -47843,7 +47861,7 @@
         <v>1.36</v>
       </c>
       <c r="AP226">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ226">
         <v>1.38</v>
@@ -47971,7 +47989,7 @@
         <v>234</v>
       </c>
       <c r="P227" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="Q227">
         <v>2.7</v>
@@ -48589,7 +48607,7 @@
         <v>90</v>
       </c>
       <c r="P230" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="Q230">
         <v>3.04</v>
@@ -49207,7 +49225,7 @@
         <v>238</v>
       </c>
       <c r="P233" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="Q233">
         <v>3.1</v>
@@ -49413,7 +49431,7 @@
         <v>239</v>
       </c>
       <c r="P234" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="Q234">
         <v>1.85</v>
@@ -49776,6 +49794,1242 @@
       </c>
       <c r="BP235">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="236" spans="1:68">
+      <c r="A236" s="1">
+        <v>235</v>
+      </c>
+      <c r="B236">
+        <v>7469100</v>
+      </c>
+      <c r="C236" t="s">
+        <v>68</v>
+      </c>
+      <c r="D236" t="s">
+        <v>69</v>
+      </c>
+      <c r="E236" s="2">
+        <v>45730.66666666666</v>
+      </c>
+      <c r="F236">
+        <v>27</v>
+      </c>
+      <c r="G236" t="s">
+        <v>77</v>
+      </c>
+      <c r="H236" t="s">
+        <v>82</v>
+      </c>
+      <c r="I236">
+        <v>1</v>
+      </c>
+      <c r="J236">
+        <v>0</v>
+      </c>
+      <c r="K236">
+        <v>1</v>
+      </c>
+      <c r="L236">
+        <v>2</v>
+      </c>
+      <c r="M236">
+        <v>2</v>
+      </c>
+      <c r="N236">
+        <v>4</v>
+      </c>
+      <c r="O236" t="s">
+        <v>241</v>
+      </c>
+      <c r="P236" t="s">
+        <v>334</v>
+      </c>
+      <c r="Q236">
+        <v>3.7</v>
+      </c>
+      <c r="R236">
+        <v>2.1</v>
+      </c>
+      <c r="S236">
+        <v>2.65</v>
+      </c>
+      <c r="T236">
+        <v>1.37</v>
+      </c>
+      <c r="U236">
+        <v>2.85</v>
+      </c>
+      <c r="V236">
+        <v>2.65</v>
+      </c>
+      <c r="W236">
+        <v>1.41</v>
+      </c>
+      <c r="X236">
+        <v>6.75</v>
+      </c>
+      <c r="Y236">
+        <v>1.09</v>
+      </c>
+      <c r="Z236">
+        <v>3.79</v>
+      </c>
+      <c r="AA236">
+        <v>3.33</v>
+      </c>
+      <c r="AB236">
+        <v>1.98</v>
+      </c>
+      <c r="AC236">
+        <v>1.06</v>
+      </c>
+      <c r="AD236">
+        <v>8.5</v>
+      </c>
+      <c r="AE236">
+        <v>1.3</v>
+      </c>
+      <c r="AF236">
+        <v>3.45</v>
+      </c>
+      <c r="AG236">
+        <v>1.87</v>
+      </c>
+      <c r="AH236">
+        <v>1.87</v>
+      </c>
+      <c r="AI236">
+        <v>1.73</v>
+      </c>
+      <c r="AJ236">
+        <v>1.95</v>
+      </c>
+      <c r="AK236">
+        <v>1.7</v>
+      </c>
+      <c r="AL236">
+        <v>1.29</v>
+      </c>
+      <c r="AM236">
+        <v>1.32</v>
+      </c>
+      <c r="AN236">
+        <v>0.54</v>
+      </c>
+      <c r="AO236">
+        <v>0.85</v>
+      </c>
+      <c r="AP236">
+        <v>0.57</v>
+      </c>
+      <c r="AQ236">
+        <v>0.86</v>
+      </c>
+      <c r="AR236">
+        <v>1.04</v>
+      </c>
+      <c r="AS236">
+        <v>1.41</v>
+      </c>
+      <c r="AT236">
+        <v>2.45</v>
+      </c>
+      <c r="AU236">
+        <v>5</v>
+      </c>
+      <c r="AV236">
+        <v>8</v>
+      </c>
+      <c r="AW236">
+        <v>6</v>
+      </c>
+      <c r="AX236">
+        <v>8</v>
+      </c>
+      <c r="AY236">
+        <v>11</v>
+      </c>
+      <c r="AZ236">
+        <v>16</v>
+      </c>
+      <c r="BA236">
+        <v>4</v>
+      </c>
+      <c r="BB236">
+        <v>3</v>
+      </c>
+      <c r="BC236">
+        <v>7</v>
+      </c>
+      <c r="BD236">
+        <v>2.55</v>
+      </c>
+      <c r="BE236">
+        <v>6.4</v>
+      </c>
+      <c r="BF236">
+        <v>1.64</v>
+      </c>
+      <c r="BG236">
+        <v>1.42</v>
+      </c>
+      <c r="BH236">
+        <v>2.65</v>
+      </c>
+      <c r="BI236">
+        <v>1.71</v>
+      </c>
+      <c r="BJ236">
+        <v>2</v>
+      </c>
+      <c r="BK236">
+        <v>2.12</v>
+      </c>
+      <c r="BL236">
+        <v>1.63</v>
+      </c>
+      <c r="BM236">
+        <v>2.75</v>
+      </c>
+      <c r="BN236">
+        <v>1.38</v>
+      </c>
+      <c r="BO236">
+        <v>3.55</v>
+      </c>
+      <c r="BP236">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="237" spans="1:68">
+      <c r="A237" s="1">
+        <v>236</v>
+      </c>
+      <c r="B237">
+        <v>7469101</v>
+      </c>
+      <c r="C237" t="s">
+        <v>68</v>
+      </c>
+      <c r="D237" t="s">
+        <v>69</v>
+      </c>
+      <c r="E237" s="2">
+        <v>45730.66666666666</v>
+      </c>
+      <c r="F237">
+        <v>27</v>
+      </c>
+      <c r="G237" t="s">
+        <v>70</v>
+      </c>
+      <c r="H237" t="s">
+        <v>74</v>
+      </c>
+      <c r="I237">
+        <v>0</v>
+      </c>
+      <c r="J237">
+        <v>0</v>
+      </c>
+      <c r="K237">
+        <v>0</v>
+      </c>
+      <c r="L237">
+        <v>0</v>
+      </c>
+      <c r="M237">
+        <v>0</v>
+      </c>
+      <c r="N237">
+        <v>0</v>
+      </c>
+      <c r="O237" t="s">
+        <v>90</v>
+      </c>
+      <c r="P237" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q237">
+        <v>2.8</v>
+      </c>
+      <c r="R237">
+        <v>2</v>
+      </c>
+      <c r="S237">
+        <v>3.7</v>
+      </c>
+      <c r="T237">
+        <v>1.43</v>
+      </c>
+      <c r="U237">
+        <v>2.6</v>
+      </c>
+      <c r="V237">
+        <v>3</v>
+      </c>
+      <c r="W237">
+        <v>1.34</v>
+      </c>
+      <c r="X237">
+        <v>8</v>
+      </c>
+      <c r="Y237">
+        <v>1.07</v>
+      </c>
+      <c r="Z237">
+        <v>2.17</v>
+      </c>
+      <c r="AA237">
+        <v>3.18</v>
+      </c>
+      <c r="AB237">
+        <v>3.4</v>
+      </c>
+      <c r="AC237">
+        <v>1.07</v>
+      </c>
+      <c r="AD237">
+        <v>8</v>
+      </c>
+      <c r="AE237">
+        <v>1.36</v>
+      </c>
+      <c r="AF237">
+        <v>3.1</v>
+      </c>
+      <c r="AG237">
+        <v>2.1</v>
+      </c>
+      <c r="AH237">
+        <v>1.61</v>
+      </c>
+      <c r="AI237">
+        <v>1.85</v>
+      </c>
+      <c r="AJ237">
+        <v>1.82</v>
+      </c>
+      <c r="AK237">
+        <v>1.33</v>
+      </c>
+      <c r="AL237">
+        <v>1.31</v>
+      </c>
+      <c r="AM237">
+        <v>1.65</v>
+      </c>
+      <c r="AN237">
+        <v>0.92</v>
+      </c>
+      <c r="AO237">
+        <v>0.83</v>
+      </c>
+      <c r="AP237">
+        <v>0.93</v>
+      </c>
+      <c r="AQ237">
+        <v>0.85</v>
+      </c>
+      <c r="AR237">
+        <v>1.37</v>
+      </c>
+      <c r="AS237">
+        <v>1.36</v>
+      </c>
+      <c r="AT237">
+        <v>2.73</v>
+      </c>
+      <c r="AU237">
+        <v>5</v>
+      </c>
+      <c r="AV237">
+        <v>6</v>
+      </c>
+      <c r="AW237">
+        <v>15</v>
+      </c>
+      <c r="AX237">
+        <v>9</v>
+      </c>
+      <c r="AY237">
+        <v>20</v>
+      </c>
+      <c r="AZ237">
+        <v>15</v>
+      </c>
+      <c r="BA237">
+        <v>1</v>
+      </c>
+      <c r="BB237">
+        <v>2</v>
+      </c>
+      <c r="BC237">
+        <v>3</v>
+      </c>
+      <c r="BD237">
+        <v>1.79</v>
+      </c>
+      <c r="BE237">
+        <v>6.4</v>
+      </c>
+      <c r="BF237">
+        <v>2.23</v>
+      </c>
+      <c r="BG237">
+        <v>1.33</v>
+      </c>
+      <c r="BH237">
+        <v>2.95</v>
+      </c>
+      <c r="BI237">
+        <v>1.56</v>
+      </c>
+      <c r="BJ237">
+        <v>2.23</v>
+      </c>
+      <c r="BK237">
+        <v>1.92</v>
+      </c>
+      <c r="BL237">
+        <v>1.77</v>
+      </c>
+      <c r="BM237">
+        <v>2.4</v>
+      </c>
+      <c r="BN237">
+        <v>1.49</v>
+      </c>
+      <c r="BO237">
+        <v>3.15</v>
+      </c>
+      <c r="BP237">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="238" spans="1:68">
+      <c r="A238" s="1">
+        <v>237</v>
+      </c>
+      <c r="B238">
+        <v>7469102</v>
+      </c>
+      <c r="C238" t="s">
+        <v>68</v>
+      </c>
+      <c r="D238" t="s">
+        <v>69</v>
+      </c>
+      <c r="E238" s="2">
+        <v>45730.66666666666</v>
+      </c>
+      <c r="F238">
+        <v>27</v>
+      </c>
+      <c r="G238" t="s">
+        <v>84</v>
+      </c>
+      <c r="H238" t="s">
+        <v>81</v>
+      </c>
+      <c r="I238">
+        <v>0</v>
+      </c>
+      <c r="J238">
+        <v>0</v>
+      </c>
+      <c r="K238">
+        <v>0</v>
+      </c>
+      <c r="L238">
+        <v>1</v>
+      </c>
+      <c r="M238">
+        <v>1</v>
+      </c>
+      <c r="N238">
+        <v>2</v>
+      </c>
+      <c r="O238" t="s">
+        <v>242</v>
+      </c>
+      <c r="P238" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q238">
+        <v>3.2</v>
+      </c>
+      <c r="R238">
+        <v>2.2</v>
+      </c>
+      <c r="S238">
+        <v>3.2</v>
+      </c>
+      <c r="T238">
+        <v>1.36</v>
+      </c>
+      <c r="U238">
+        <v>3</v>
+      </c>
+      <c r="V238">
+        <v>2.75</v>
+      </c>
+      <c r="W238">
+        <v>1.4</v>
+      </c>
+      <c r="X238">
+        <v>7</v>
+      </c>
+      <c r="Y238">
+        <v>1.1</v>
+      </c>
+      <c r="Z238">
+        <v>2.55</v>
+      </c>
+      <c r="AA238">
+        <v>3.5</v>
+      </c>
+      <c r="AB238">
+        <v>2.55</v>
+      </c>
+      <c r="AC238">
+        <v>1.05</v>
+      </c>
+      <c r="AD238">
+        <v>9.5</v>
+      </c>
+      <c r="AE238">
+        <v>1.25</v>
+      </c>
+      <c r="AF238">
+        <v>3.7</v>
+      </c>
+      <c r="AG238">
+        <v>1.82</v>
+      </c>
+      <c r="AH238">
+        <v>1.92</v>
+      </c>
+      <c r="AI238">
+        <v>1.67</v>
+      </c>
+      <c r="AJ238">
+        <v>2.1</v>
+      </c>
+      <c r="AK238">
+        <v>1.5</v>
+      </c>
+      <c r="AL238">
+        <v>1.29</v>
+      </c>
+      <c r="AM238">
+        <v>1.47</v>
+      </c>
+      <c r="AN238">
+        <v>1.83</v>
+      </c>
+      <c r="AO238">
+        <v>1</v>
+      </c>
+      <c r="AP238">
+        <v>1.77</v>
+      </c>
+      <c r="AQ238">
+        <v>1</v>
+      </c>
+      <c r="AR238">
+        <v>1.36</v>
+      </c>
+      <c r="AS238">
+        <v>1.42</v>
+      </c>
+      <c r="AT238">
+        <v>2.78</v>
+      </c>
+      <c r="AU238">
+        <v>4</v>
+      </c>
+      <c r="AV238">
+        <v>5</v>
+      </c>
+      <c r="AW238">
+        <v>7</v>
+      </c>
+      <c r="AX238">
+        <v>5</v>
+      </c>
+      <c r="AY238">
+        <v>11</v>
+      </c>
+      <c r="AZ238">
+        <v>10</v>
+      </c>
+      <c r="BA238">
+        <v>3</v>
+      </c>
+      <c r="BB238">
+        <v>2</v>
+      </c>
+      <c r="BC238">
+        <v>5</v>
+      </c>
+      <c r="BD238">
+        <v>2.08</v>
+      </c>
+      <c r="BE238">
+        <v>6.4</v>
+      </c>
+      <c r="BF238">
+        <v>1.9</v>
+      </c>
+      <c r="BG238">
+        <v>1.3</v>
+      </c>
+      <c r="BH238">
+        <v>3.05</v>
+      </c>
+      <c r="BI238">
+        <v>1.55</v>
+      </c>
+      <c r="BJ238">
+        <v>2.25</v>
+      </c>
+      <c r="BK238">
+        <v>1.89</v>
+      </c>
+      <c r="BL238">
+        <v>1.8</v>
+      </c>
+      <c r="BM238">
+        <v>2.4</v>
+      </c>
+      <c r="BN238">
+        <v>1.5</v>
+      </c>
+      <c r="BO238">
+        <v>3.05</v>
+      </c>
+      <c r="BP238">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="239" spans="1:68">
+      <c r="A239" s="1">
+        <v>238</v>
+      </c>
+      <c r="B239">
+        <v>7469104</v>
+      </c>
+      <c r="C239" t="s">
+        <v>68</v>
+      </c>
+      <c r="D239" t="s">
+        <v>69</v>
+      </c>
+      <c r="E239" s="2">
+        <v>45730.66666666666</v>
+      </c>
+      <c r="F239">
+        <v>27</v>
+      </c>
+      <c r="G239" t="s">
+        <v>71</v>
+      </c>
+      <c r="H239" t="s">
+        <v>87</v>
+      </c>
+      <c r="I239">
+        <v>0</v>
+      </c>
+      <c r="J239">
+        <v>1</v>
+      </c>
+      <c r="K239">
+        <v>1</v>
+      </c>
+      <c r="L239">
+        <v>2</v>
+      </c>
+      <c r="M239">
+        <v>1</v>
+      </c>
+      <c r="N239">
+        <v>3</v>
+      </c>
+      <c r="O239" t="s">
+        <v>243</v>
+      </c>
+      <c r="P239" t="s">
+        <v>335</v>
+      </c>
+      <c r="Q239">
+        <v>3.1</v>
+      </c>
+      <c r="R239">
+        <v>1.93</v>
+      </c>
+      <c r="S239">
+        <v>3.5</v>
+      </c>
+      <c r="T239">
+        <v>1.51</v>
+      </c>
+      <c r="U239">
+        <v>2.37</v>
+      </c>
+      <c r="V239">
+        <v>3.4</v>
+      </c>
+      <c r="W239">
+        <v>1.27</v>
+      </c>
+      <c r="X239">
+        <v>9.75</v>
+      </c>
+      <c r="Y239">
+        <v>1.04</v>
+      </c>
+      <c r="Z239">
+        <v>2.25</v>
+      </c>
+      <c r="AA239">
+        <v>2.92</v>
+      </c>
+      <c r="AB239">
+        <v>3.53</v>
+      </c>
+      <c r="AC239">
+        <v>1.1</v>
+      </c>
+      <c r="AD239">
+        <v>6.5</v>
+      </c>
+      <c r="AE239">
+        <v>1.5</v>
+      </c>
+      <c r="AF239">
+        <v>2.4</v>
+      </c>
+      <c r="AG239">
+        <v>2.3</v>
+      </c>
+      <c r="AH239">
+        <v>1.5</v>
+      </c>
+      <c r="AI239">
+        <v>2.05</v>
+      </c>
+      <c r="AJ239">
+        <v>1.68</v>
+      </c>
+      <c r="AK239">
+        <v>1.39</v>
+      </c>
+      <c r="AL239">
+        <v>1.34</v>
+      </c>
+      <c r="AM239">
+        <v>1.52</v>
+      </c>
+      <c r="AN239">
+        <v>1.54</v>
+      </c>
+      <c r="AO239">
+        <v>0.92</v>
+      </c>
+      <c r="AP239">
+        <v>1.64</v>
+      </c>
+      <c r="AQ239">
+        <v>0.86</v>
+      </c>
+      <c r="AR239">
+        <v>1.25</v>
+      </c>
+      <c r="AS239">
+        <v>1.18</v>
+      </c>
+      <c r="AT239">
+        <v>2.43</v>
+      </c>
+      <c r="AU239">
+        <v>6</v>
+      </c>
+      <c r="AV239">
+        <v>5</v>
+      </c>
+      <c r="AW239">
+        <v>9</v>
+      </c>
+      <c r="AX239">
+        <v>5</v>
+      </c>
+      <c r="AY239">
+        <v>15</v>
+      </c>
+      <c r="AZ239">
+        <v>10</v>
+      </c>
+      <c r="BA239">
+        <v>6</v>
+      </c>
+      <c r="BB239">
+        <v>7</v>
+      </c>
+      <c r="BC239">
+        <v>13</v>
+      </c>
+      <c r="BD239">
+        <v>1.84</v>
+      </c>
+      <c r="BE239">
+        <v>6.25</v>
+      </c>
+      <c r="BF239">
+        <v>2.18</v>
+      </c>
+      <c r="BG239">
+        <v>1.47</v>
+      </c>
+      <c r="BH239">
+        <v>2.48</v>
+      </c>
+      <c r="BI239">
+        <v>1.78</v>
+      </c>
+      <c r="BJ239">
+        <v>1.92</v>
+      </c>
+      <c r="BK239">
+        <v>2.23</v>
+      </c>
+      <c r="BL239">
+        <v>1.56</v>
+      </c>
+      <c r="BM239">
+        <v>2.9</v>
+      </c>
+      <c r="BN239">
+        <v>1.34</v>
+      </c>
+      <c r="BO239">
+        <v>3.9</v>
+      </c>
+      <c r="BP239">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="240" spans="1:68">
+      <c r="A240" s="1">
+        <v>239</v>
+      </c>
+      <c r="B240">
+        <v>7469107</v>
+      </c>
+      <c r="C240" t="s">
+        <v>68</v>
+      </c>
+      <c r="D240" t="s">
+        <v>69</v>
+      </c>
+      <c r="E240" s="2">
+        <v>45730.66666666666</v>
+      </c>
+      <c r="F240">
+        <v>27</v>
+      </c>
+      <c r="G240" t="s">
+        <v>73</v>
+      </c>
+      <c r="H240" t="s">
+        <v>76</v>
+      </c>
+      <c r="I240">
+        <v>0</v>
+      </c>
+      <c r="J240">
+        <v>0</v>
+      </c>
+      <c r="K240">
+        <v>0</v>
+      </c>
+      <c r="L240">
+        <v>2</v>
+      </c>
+      <c r="M240">
+        <v>1</v>
+      </c>
+      <c r="N240">
+        <v>3</v>
+      </c>
+      <c r="O240" t="s">
+        <v>244</v>
+      </c>
+      <c r="P240" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q240">
+        <v>3.4</v>
+      </c>
+      <c r="R240">
+        <v>2.05</v>
+      </c>
+      <c r="S240">
+        <v>2.95</v>
+      </c>
+      <c r="T240">
+        <v>1.42</v>
+      </c>
+      <c r="U240">
+        <v>2.65</v>
+      </c>
+      <c r="V240">
+        <v>2.95</v>
+      </c>
+      <c r="W240">
+        <v>1.34</v>
+      </c>
+      <c r="X240">
+        <v>8</v>
+      </c>
+      <c r="Y240">
+        <v>1.07</v>
+      </c>
+      <c r="Z240">
+        <v>2.93</v>
+      </c>
+      <c r="AA240">
+        <v>3.17</v>
+      </c>
+      <c r="AB240">
+        <v>2.42</v>
+      </c>
+      <c r="AC240">
+        <v>1.07</v>
+      </c>
+      <c r="AD240">
+        <v>8</v>
+      </c>
+      <c r="AE240">
+        <v>1.36</v>
+      </c>
+      <c r="AF240">
+        <v>3.1</v>
+      </c>
+      <c r="AG240">
+        <v>2</v>
+      </c>
+      <c r="AH240">
+        <v>1.75</v>
+      </c>
+      <c r="AI240">
+        <v>1.85</v>
+      </c>
+      <c r="AJ240">
+        <v>1.83</v>
+      </c>
+      <c r="AK240">
+        <v>1.55</v>
+      </c>
+      <c r="AL240">
+        <v>1.3</v>
+      </c>
+      <c r="AM240">
+        <v>1.4</v>
+      </c>
+      <c r="AN240">
+        <v>1.77</v>
+      </c>
+      <c r="AO240">
+        <v>0.58</v>
+      </c>
+      <c r="AP240">
+        <v>1.86</v>
+      </c>
+      <c r="AQ240">
+        <v>0.54</v>
+      </c>
+      <c r="AR240">
+        <v>1.63</v>
+      </c>
+      <c r="AS240">
+        <v>1.32</v>
+      </c>
+      <c r="AT240">
+        <v>2.95</v>
+      </c>
+      <c r="AU240">
+        <v>4</v>
+      </c>
+      <c r="AV240">
+        <v>6</v>
+      </c>
+      <c r="AW240">
+        <v>7</v>
+      </c>
+      <c r="AX240">
+        <v>6</v>
+      </c>
+      <c r="AY240">
+        <v>11</v>
+      </c>
+      <c r="AZ240">
+        <v>12</v>
+      </c>
+      <c r="BA240">
+        <v>2</v>
+      </c>
+      <c r="BB240">
+        <v>4</v>
+      </c>
+      <c r="BC240">
+        <v>6</v>
+      </c>
+      <c r="BD240">
+        <v>2.2</v>
+      </c>
+      <c r="BE240">
+        <v>6.25</v>
+      </c>
+      <c r="BF240">
+        <v>1.82</v>
+      </c>
+      <c r="BG240">
+        <v>1.46</v>
+      </c>
+      <c r="BH240">
+        <v>2.5</v>
+      </c>
+      <c r="BI240">
+        <v>1.75</v>
+      </c>
+      <c r="BJ240">
+        <v>1.95</v>
+      </c>
+      <c r="BK240">
+        <v>2.2</v>
+      </c>
+      <c r="BL240">
+        <v>1.58</v>
+      </c>
+      <c r="BM240">
+        <v>2.9</v>
+      </c>
+      <c r="BN240">
+        <v>1.35</v>
+      </c>
+      <c r="BO240">
+        <v>3.9</v>
+      </c>
+      <c r="BP240">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="241" spans="1:68">
+      <c r="A241" s="1">
+        <v>240</v>
+      </c>
+      <c r="B241">
+        <v>7469106</v>
+      </c>
+      <c r="C241" t="s">
+        <v>68</v>
+      </c>
+      <c r="D241" t="s">
+        <v>69</v>
+      </c>
+      <c r="E241" s="2">
+        <v>45730.66666666666</v>
+      </c>
+      <c r="F241">
+        <v>27</v>
+      </c>
+      <c r="G241" t="s">
+        <v>79</v>
+      </c>
+      <c r="H241" t="s">
+        <v>75</v>
+      </c>
+      <c r="I241">
+        <v>0</v>
+      </c>
+      <c r="J241">
+        <v>0</v>
+      </c>
+      <c r="K241">
+        <v>0</v>
+      </c>
+      <c r="L241">
+        <v>0</v>
+      </c>
+      <c r="M241">
+        <v>1</v>
+      </c>
+      <c r="N241">
+        <v>1</v>
+      </c>
+      <c r="O241" t="s">
+        <v>90</v>
+      </c>
+      <c r="P241" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q241">
+        <v>2.9</v>
+      </c>
+      <c r="R241">
+        <v>1.98</v>
+      </c>
+      <c r="S241">
+        <v>3.7</v>
+      </c>
+      <c r="T241">
+        <v>1.47</v>
+      </c>
+      <c r="U241">
+        <v>2.45</v>
+      </c>
+      <c r="V241">
+        <v>3.2</v>
+      </c>
+      <c r="W241">
+        <v>1.3</v>
+      </c>
+      <c r="X241">
+        <v>9</v>
+      </c>
+      <c r="Y241">
+        <v>1.06</v>
+      </c>
+      <c r="Z241">
+        <v>2.26</v>
+      </c>
+      <c r="AA241">
+        <v>3.09</v>
+      </c>
+      <c r="AB241">
+        <v>3.3</v>
+      </c>
+      <c r="AC241">
+        <v>1.09</v>
+      </c>
+      <c r="AD241">
+        <v>7</v>
+      </c>
+      <c r="AE241">
+        <v>1.45</v>
+      </c>
+      <c r="AF241">
+        <v>2.7</v>
+      </c>
+      <c r="AG241">
+        <v>2.15</v>
+      </c>
+      <c r="AH241">
+        <v>1.57</v>
+      </c>
+      <c r="AI241">
+        <v>2</v>
+      </c>
+      <c r="AJ241">
+        <v>1.71</v>
+      </c>
+      <c r="AK241">
+        <v>1.34</v>
+      </c>
+      <c r="AL241">
+        <v>1.33</v>
+      </c>
+      <c r="AM241">
+        <v>1.58</v>
+      </c>
+      <c r="AN241">
+        <v>1.42</v>
+      </c>
+      <c r="AO241">
+        <v>1.46</v>
+      </c>
+      <c r="AP241">
+        <v>1.31</v>
+      </c>
+      <c r="AQ241">
+        <v>1.57</v>
+      </c>
+      <c r="AR241">
+        <v>1.72</v>
+      </c>
+      <c r="AS241">
+        <v>1.47</v>
+      </c>
+      <c r="AT241">
+        <v>3.19</v>
+      </c>
+      <c r="AU241">
+        <v>4</v>
+      </c>
+      <c r="AV241">
+        <v>5</v>
+      </c>
+      <c r="AW241">
+        <v>12</v>
+      </c>
+      <c r="AX241">
+        <v>2</v>
+      </c>
+      <c r="AY241">
+        <v>16</v>
+      </c>
+      <c r="AZ241">
+        <v>7</v>
+      </c>
+      <c r="BA241">
+        <v>5</v>
+      </c>
+      <c r="BB241">
+        <v>3</v>
+      </c>
+      <c r="BC241">
+        <v>8</v>
+      </c>
+      <c r="BD241">
+        <v>1.81</v>
+      </c>
+      <c r="BE241">
+        <v>6.25</v>
+      </c>
+      <c r="BF241">
+        <v>2.23</v>
+      </c>
+      <c r="BG241">
+        <v>1.46</v>
+      </c>
+      <c r="BH241">
+        <v>2.48</v>
+      </c>
+      <c r="BI241">
+        <v>1.76</v>
+      </c>
+      <c r="BJ241">
+        <v>1.94</v>
+      </c>
+      <c r="BK241">
+        <v>2.23</v>
+      </c>
+      <c r="BL241">
+        <v>1.57</v>
+      </c>
+      <c r="BM241">
+        <v>2.9</v>
+      </c>
+      <c r="BN241">
+        <v>1.35</v>
+      </c>
+      <c r="BO241">
+        <v>3.9</v>
+      </c>
+      <c r="BP241">
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1508" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1526" uniqueCount="340">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -751,6 +751,15 @@
     <t>['58', '73']</t>
   </si>
   <si>
+    <t>['54', '90+4']</t>
+  </si>
+  <si>
+    <t>['18', '53', '55']</t>
+  </si>
+  <si>
+    <t>['8', '42', '70', '88']</t>
+  </si>
+  <si>
     <t>['16', '45+2']</t>
   </si>
   <si>
@@ -1022,6 +1031,9 @@
   </si>
   <si>
     <t>['21']</t>
+  </si>
+  <si>
+    <t>['30', '72', '90+11']</t>
   </si>
 </sst>
 </file>
@@ -1383,7 +1395,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP241"/>
+  <dimension ref="A1:BP244"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1639,7 +1651,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q2">
         <v>2.4</v>
@@ -2051,7 +2063,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q4">
         <v>3.6</v>
@@ -2129,7 +2141,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AQ4">
         <v>1.21</v>
@@ -2875,7 +2887,7 @@
         <v>90</v>
       </c>
       <c r="P8" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q8">
         <v>3.1</v>
@@ -2956,7 +2968,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ8">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3287,7 +3299,7 @@
         <v>94</v>
       </c>
       <c r="P10" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q10">
         <v>2.6</v>
@@ -3368,7 +3380,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ10">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3777,7 +3789,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ12">
         <v>1.57</v>
@@ -3905,7 +3917,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q13">
         <v>3.1</v>
@@ -3986,7 +3998,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ13">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4523,7 +4535,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q16">
         <v>2.63</v>
@@ -4729,7 +4741,7 @@
         <v>99</v>
       </c>
       <c r="P17" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -5013,7 +5025,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ18">
         <v>0.85</v>
@@ -5634,7 +5646,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ21">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR21">
         <v>1.81</v>
@@ -5759,7 +5771,7 @@
         <v>103</v>
       </c>
       <c r="P22" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -6043,7 +6055,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AQ23">
         <v>1</v>
@@ -6171,7 +6183,7 @@
         <v>105</v>
       </c>
       <c r="P24" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q24">
         <v>2.62</v>
@@ -6458,7 +6470,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ25">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR25">
         <v>0.67</v>
@@ -6995,7 +7007,7 @@
         <v>108</v>
       </c>
       <c r="P28" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q28">
         <v>2.6</v>
@@ -7279,7 +7291,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ29">
         <v>0.85</v>
@@ -7485,7 +7497,7 @@
         <v>1.5</v>
       </c>
       <c r="AP30">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ30">
         <v>0.86</v>
@@ -8437,7 +8449,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q35">
         <v>3.3</v>
@@ -8643,7 +8655,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q36">
         <v>3.1</v>
@@ -8724,7 +8736,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ36">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR36">
         <v>1.66</v>
@@ -8849,7 +8861,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q37">
         <v>3.4</v>
@@ -9055,7 +9067,7 @@
         <v>90</v>
       </c>
       <c r="P38" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q38">
         <v>3.2</v>
@@ -9261,7 +9273,7 @@
         <v>90</v>
       </c>
       <c r="P39" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q39">
         <v>3.4</v>
@@ -9548,7 +9560,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ40">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR40">
         <v>1.41</v>
@@ -9673,7 +9685,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q41">
         <v>2.5</v>
@@ -9879,7 +9891,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q42">
         <v>3.25</v>
@@ -9957,7 +9969,7 @@
         <v>1</v>
       </c>
       <c r="AP42">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AQ42">
         <v>0.86</v>
@@ -10085,7 +10097,7 @@
         <v>90</v>
       </c>
       <c r="P43" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q43">
         <v>2.75</v>
@@ -12145,7 +12157,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -12223,10 +12235,10 @@
         <v>2</v>
       </c>
       <c r="AP53">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AQ53">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR53">
         <v>1.76</v>
@@ -12351,7 +12363,7 @@
         <v>129</v>
       </c>
       <c r="P54" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q54">
         <v>2.55</v>
@@ -12557,7 +12569,7 @@
         <v>130</v>
       </c>
       <c r="P55" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q55">
         <v>2.55</v>
@@ -12841,7 +12853,7 @@
         <v>0.33</v>
       </c>
       <c r="AP56">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ56">
         <v>0.85</v>
@@ -12969,7 +12981,7 @@
         <v>132</v>
       </c>
       <c r="P57" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -13047,7 +13059,7 @@
         <v>0.67</v>
       </c>
       <c r="AP57">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ57">
         <v>0.86</v>
@@ -13381,7 +13393,7 @@
         <v>134</v>
       </c>
       <c r="P59" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q59">
         <v>2.62</v>
@@ -13587,7 +13599,7 @@
         <v>135</v>
       </c>
       <c r="P60" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q60">
         <v>2.88</v>
@@ -13999,7 +14011,7 @@
         <v>137</v>
       </c>
       <c r="P62" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q62">
         <v>3.6</v>
@@ -14080,7 +14092,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ62">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR62">
         <v>1.16</v>
@@ -14205,7 +14217,7 @@
         <v>138</v>
       </c>
       <c r="P63" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q63">
         <v>3.75</v>
@@ -14286,7 +14298,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ63">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR63">
         <v>1.33</v>
@@ -15107,7 +15119,7 @@
         <v>0.25</v>
       </c>
       <c r="AP67">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AQ67">
         <v>1.14</v>
@@ -15235,7 +15247,7 @@
         <v>143</v>
       </c>
       <c r="P68" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15441,7 +15453,7 @@
         <v>144</v>
       </c>
       <c r="P69" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15647,7 +15659,7 @@
         <v>145</v>
       </c>
       <c r="P70" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q70">
         <v>3.75</v>
@@ -16059,7 +16071,7 @@
         <v>147</v>
       </c>
       <c r="P72" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16265,7 +16277,7 @@
         <v>90</v>
       </c>
       <c r="P73" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q73">
         <v>4.33</v>
@@ -16471,7 +16483,7 @@
         <v>90</v>
       </c>
       <c r="P74" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q74">
         <v>2.4</v>
@@ -16677,7 +16689,7 @@
         <v>148</v>
       </c>
       <c r="P75" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q75">
         <v>3.5</v>
@@ -16883,7 +16895,7 @@
         <v>149</v>
       </c>
       <c r="P76" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q76">
         <v>2.88</v>
@@ -16961,7 +16973,7 @@
         <v>1.33</v>
       </c>
       <c r="AP76">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ76">
         <v>1.38</v>
@@ -17170,7 +17182,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ77">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR77">
         <v>1.29</v>
@@ -17501,7 +17513,7 @@
         <v>151</v>
       </c>
       <c r="P79" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17707,7 +17719,7 @@
         <v>152</v>
       </c>
       <c r="P80" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q80">
         <v>2.05</v>
@@ -17785,7 +17797,7 @@
         <v>1.5</v>
       </c>
       <c r="AP80">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ80">
         <v>1.21</v>
@@ -17913,7 +17925,7 @@
         <v>90</v>
       </c>
       <c r="P81" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q81">
         <v>4.33</v>
@@ -17994,7 +18006,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ81">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR81">
         <v>1.22</v>
@@ -18200,7 +18212,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ82">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR82">
         <v>1.57</v>
@@ -18403,7 +18415,7 @@
         <v>0.8</v>
       </c>
       <c r="AP83">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AQ83">
         <v>0.86</v>
@@ -18737,7 +18749,7 @@
         <v>90</v>
       </c>
       <c r="P85" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q85">
         <v>3.1</v>
@@ -18943,7 +18955,7 @@
         <v>156</v>
       </c>
       <c r="P86" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -19767,7 +19779,7 @@
         <v>90</v>
       </c>
       <c r="P90" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q90">
         <v>2.38</v>
@@ -20179,7 +20191,7 @@
         <v>160</v>
       </c>
       <c r="P92" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20257,7 +20269,7 @@
         <v>1</v>
       </c>
       <c r="AP92">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ92">
         <v>1</v>
@@ -20466,7 +20478,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ93">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR93">
         <v>1.43</v>
@@ -20797,7 +20809,7 @@
         <v>162</v>
       </c>
       <c r="P95" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q95">
         <v>1.9</v>
@@ -20875,7 +20887,7 @@
         <v>1</v>
       </c>
       <c r="AP95">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ95">
         <v>1.38</v>
@@ -21003,7 +21015,7 @@
         <v>163</v>
       </c>
       <c r="P96" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q96">
         <v>2.75</v>
@@ -21290,7 +21302,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ97">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR97">
         <v>1.69</v>
@@ -21415,7 +21427,7 @@
         <v>90</v>
       </c>
       <c r="P98" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q98">
         <v>4.75</v>
@@ -21905,7 +21917,7 @@
         <v>0.6</v>
       </c>
       <c r="AP100">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AQ100">
         <v>0.54</v>
@@ -22651,7 +22663,7 @@
         <v>167</v>
       </c>
       <c r="P104" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q104">
         <v>2.25</v>
@@ -23144,7 +23156,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ106">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR106">
         <v>1.41</v>
@@ -23475,7 +23487,7 @@
         <v>90</v>
       </c>
       <c r="P108" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q108">
         <v>4.5</v>
@@ -23556,7 +23568,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ108">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR108">
         <v>1.07</v>
@@ -24299,7 +24311,7 @@
         <v>173</v>
       </c>
       <c r="P112" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q112">
         <v>3.5</v>
@@ -24377,10 +24389,10 @@
         <v>1</v>
       </c>
       <c r="AP112">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ112">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR112">
         <v>1.26</v>
@@ -24711,7 +24723,7 @@
         <v>90</v>
       </c>
       <c r="P114" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q114">
         <v>2.85</v>
@@ -24998,7 +25010,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ115">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR115">
         <v>1.51</v>
@@ -25123,7 +25135,7 @@
         <v>175</v>
       </c>
       <c r="P116" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q116">
         <v>2.4</v>
@@ -25201,7 +25213,7 @@
         <v>1.2</v>
       </c>
       <c r="AP116">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ116">
         <v>1.57</v>
@@ -25535,7 +25547,7 @@
         <v>90</v>
       </c>
       <c r="P118" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q118">
         <v>4</v>
@@ -26028,7 +26040,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ120">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR120">
         <v>1.24</v>
@@ -26153,7 +26165,7 @@
         <v>178</v>
       </c>
       <c r="P121" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q121">
         <v>2.88</v>
@@ -27261,7 +27273,7 @@
         <v>0.17</v>
       </c>
       <c r="AP126">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AQ126">
         <v>0.85</v>
@@ -27470,7 +27482,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ127">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR127">
         <v>1.21</v>
@@ -27673,7 +27685,7 @@
         <v>1</v>
       </c>
       <c r="AP128">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ128">
         <v>1.14</v>
@@ -28500,7 +28512,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ132">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR132">
         <v>1.26</v>
@@ -28703,7 +28715,7 @@
         <v>0.67</v>
       </c>
       <c r="AP133">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ133">
         <v>0.54</v>
@@ -28831,7 +28843,7 @@
         <v>90</v>
       </c>
       <c r="P134" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q134">
         <v>3.2</v>
@@ -29037,7 +29049,7 @@
         <v>90</v>
       </c>
       <c r="P135" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q135">
         <v>5</v>
@@ -29118,7 +29130,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ135">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR135">
         <v>1.14</v>
@@ -30273,7 +30285,7 @@
         <v>189</v>
       </c>
       <c r="P141" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q141">
         <v>2.8</v>
@@ -30557,10 +30569,10 @@
         <v>2.13</v>
       </c>
       <c r="AP142">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ142">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR142">
         <v>1.78</v>
@@ -30972,7 +30984,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ144">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR144">
         <v>1.43</v>
@@ -31097,7 +31109,7 @@
         <v>192</v>
       </c>
       <c r="P145" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q145">
         <v>2.75</v>
@@ -31175,7 +31187,7 @@
         <v>0.57</v>
       </c>
       <c r="AP145">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AQ145">
         <v>0.54</v>
@@ -31303,7 +31315,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q146">
         <v>3.75</v>
@@ -31384,7 +31396,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ146">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR146">
         <v>1.08</v>
@@ -31509,7 +31521,7 @@
         <v>129</v>
       </c>
       <c r="P147" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q147">
         <v>3.75</v>
@@ -31715,7 +31727,7 @@
         <v>90</v>
       </c>
       <c r="P148" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q148">
         <v>2.4</v>
@@ -31921,7 +31933,7 @@
         <v>90</v>
       </c>
       <c r="P149" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q149">
         <v>3.1</v>
@@ -32333,7 +32345,7 @@
         <v>194</v>
       </c>
       <c r="P151" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q151">
         <v>1.62</v>
@@ -32745,7 +32757,7 @@
         <v>95</v>
       </c>
       <c r="P153" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q153">
         <v>2.63</v>
@@ -33029,7 +33041,7 @@
         <v>1.13</v>
       </c>
       <c r="AP154">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ154">
         <v>1.38</v>
@@ -33569,7 +33581,7 @@
         <v>197</v>
       </c>
       <c r="P157" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q157">
         <v>2.7</v>
@@ -33775,7 +33787,7 @@
         <v>96</v>
       </c>
       <c r="P158" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q158">
         <v>2.55</v>
@@ -33853,7 +33865,7 @@
         <v>1.11</v>
       </c>
       <c r="AP158">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ158">
         <v>0.86</v>
@@ -33981,7 +33993,7 @@
         <v>198</v>
       </c>
       <c r="P159" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q159">
         <v>3.3</v>
@@ -34187,7 +34199,7 @@
         <v>90</v>
       </c>
       <c r="P160" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q160">
         <v>2.75</v>
@@ -34883,10 +34895,10 @@
         <v>1.38</v>
       </c>
       <c r="AP163">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ163">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR163">
         <v>1.75</v>
@@ -35504,7 +35516,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ166">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR166">
         <v>1.68</v>
@@ -35629,7 +35641,7 @@
         <v>109</v>
       </c>
       <c r="P167" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q167">
         <v>3.35</v>
@@ -36041,7 +36053,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q169">
         <v>2.8</v>
@@ -36247,7 +36259,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q170">
         <v>3</v>
@@ -36328,7 +36340,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ170">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR170">
         <v>1.64</v>
@@ -36531,7 +36543,7 @@
         <v>1</v>
       </c>
       <c r="AP171">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AQ171">
         <v>1.38</v>
@@ -36659,7 +36671,7 @@
         <v>90</v>
       </c>
       <c r="P172" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q172">
         <v>2.63</v>
@@ -36865,7 +36877,7 @@
         <v>207</v>
       </c>
       <c r="P173" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q173">
         <v>2.3</v>
@@ -37561,7 +37573,7 @@
         <v>1</v>
       </c>
       <c r="AP176">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ176">
         <v>1.14</v>
@@ -37895,7 +37907,7 @@
         <v>90</v>
       </c>
       <c r="P178" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q178">
         <v>3.25</v>
@@ -38307,7 +38319,7 @@
         <v>212</v>
       </c>
       <c r="P180" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q180">
         <v>2.2</v>
@@ -38385,7 +38397,7 @@
         <v>1.44</v>
       </c>
       <c r="AP180">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ180">
         <v>1</v>
@@ -38513,7 +38525,7 @@
         <v>90</v>
       </c>
       <c r="P181" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q181">
         <v>3.25</v>
@@ -38797,7 +38809,7 @@
         <v>1.22</v>
       </c>
       <c r="AP182">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AQ182">
         <v>1.31</v>
@@ -39624,7 +39636,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ186">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR186">
         <v>1.69</v>
@@ -39749,7 +39761,7 @@
         <v>90</v>
       </c>
       <c r="P187" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q187">
         <v>2.55</v>
@@ -39955,7 +39967,7 @@
         <v>215</v>
       </c>
       <c r="P188" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q188">
         <v>4.5</v>
@@ -40367,7 +40379,7 @@
         <v>90</v>
       </c>
       <c r="P190" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q190">
         <v>3.3</v>
@@ -40448,7 +40460,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ190">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR190">
         <v>1.63</v>
@@ -40573,7 +40585,7 @@
         <v>90</v>
       </c>
       <c r="P191" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q191">
         <v>2.75</v>
@@ -40651,7 +40663,7 @@
         <v>1.27</v>
       </c>
       <c r="AP191">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ191">
         <v>1.21</v>
@@ -40779,7 +40791,7 @@
         <v>90</v>
       </c>
       <c r="P192" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q192">
         <v>3.25</v>
@@ -40860,7 +40872,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ192">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR192">
         <v>1.84</v>
@@ -41397,7 +41409,7 @@
         <v>214</v>
       </c>
       <c r="P195" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q195">
         <v>4.75</v>
@@ -41603,7 +41615,7 @@
         <v>90</v>
       </c>
       <c r="P196" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q196">
         <v>3.65</v>
@@ -41809,7 +41821,7 @@
         <v>218</v>
       </c>
       <c r="P197" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q197">
         <v>1.94</v>
@@ -41887,7 +41899,7 @@
         <v>0.6</v>
       </c>
       <c r="AP197">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ197">
         <v>0.54</v>
@@ -42221,7 +42233,7 @@
         <v>90</v>
       </c>
       <c r="P199" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q199">
         <v>3.75</v>
@@ -42508,7 +42520,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ200">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR200">
         <v>1.39</v>
@@ -43251,7 +43263,7 @@
         <v>160</v>
       </c>
       <c r="P204" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q204">
         <v>3</v>
@@ -43457,7 +43469,7 @@
         <v>90</v>
       </c>
       <c r="P205" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q205">
         <v>2.75</v>
@@ -43741,10 +43753,10 @@
         <v>1.82</v>
       </c>
       <c r="AP206">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AQ206">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR206">
         <v>1.62</v>
@@ -43869,7 +43881,7 @@
         <v>90</v>
       </c>
       <c r="P207" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q207">
         <v>3.8</v>
@@ -43950,7 +43962,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ207">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR207">
         <v>1.58</v>
@@ -44977,7 +44989,7 @@
         <v>1.18</v>
       </c>
       <c r="AP212">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AQ212">
         <v>1</v>
@@ -45105,7 +45117,7 @@
         <v>226</v>
       </c>
       <c r="P213" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q213">
         <v>3.75</v>
@@ -45517,7 +45529,7 @@
         <v>228</v>
       </c>
       <c r="P215" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q215">
         <v>2.95</v>
@@ -45723,7 +45735,7 @@
         <v>90</v>
       </c>
       <c r="P216" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q216">
         <v>1.96</v>
@@ -45801,7 +45813,7 @@
         <v>1.33</v>
       </c>
       <c r="AP216">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ216">
         <v>1.57</v>
@@ -46341,7 +46353,7 @@
         <v>229</v>
       </c>
       <c r="P219" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q219">
         <v>4.3</v>
@@ -46422,7 +46434,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ219">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR219">
         <v>1.4</v>
@@ -46625,7 +46637,7 @@
         <v>1.27</v>
       </c>
       <c r="AP220">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ220">
         <v>1.31</v>
@@ -46834,7 +46846,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ221">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR221">
         <v>1.73</v>
@@ -46959,7 +46971,7 @@
         <v>90</v>
       </c>
       <c r="P222" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q222">
         <v>2.7</v>
@@ -47165,7 +47177,7 @@
         <v>231</v>
       </c>
       <c r="P223" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q223">
         <v>3.65</v>
@@ -47371,7 +47383,7 @@
         <v>232</v>
       </c>
       <c r="P224" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q224">
         <v>5.2</v>
@@ -47452,7 +47464,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ224">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR224">
         <v>1.63</v>
@@ -47655,7 +47667,7 @@
         <v>1.08</v>
       </c>
       <c r="AP225">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ225">
         <v>1</v>
@@ -47783,7 +47795,7 @@
         <v>221</v>
       </c>
       <c r="P226" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q226">
         <v>4.4</v>
@@ -47989,7 +48001,7 @@
         <v>234</v>
       </c>
       <c r="P227" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q227">
         <v>2.7</v>
@@ -48607,7 +48619,7 @@
         <v>90</v>
       </c>
       <c r="P230" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q230">
         <v>3.04</v>
@@ -49225,7 +49237,7 @@
         <v>238</v>
       </c>
       <c r="P233" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q233">
         <v>3.1</v>
@@ -49431,7 +49443,7 @@
         <v>239</v>
       </c>
       <c r="P234" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q234">
         <v>1.85</v>
@@ -49843,7 +49855,7 @@
         <v>241</v>
       </c>
       <c r="P236" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="Q236">
         <v>3.7</v>
@@ -50461,7 +50473,7 @@
         <v>243</v>
       </c>
       <c r="P239" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="Q239">
         <v>3.1</v>
@@ -51029,6 +51041,624 @@
         <v>3.9</v>
       </c>
       <c r="BP241">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="242" spans="1:68">
+      <c r="A242" s="1">
+        <v>241</v>
+      </c>
+      <c r="B242">
+        <v>7469103</v>
+      </c>
+      <c r="C242" t="s">
+        <v>68</v>
+      </c>
+      <c r="D242" t="s">
+        <v>69</v>
+      </c>
+      <c r="E242" s="2">
+        <v>45731.41666666666</v>
+      </c>
+      <c r="F242">
+        <v>27</v>
+      </c>
+      <c r="G242" t="s">
+        <v>72</v>
+      </c>
+      <c r="H242" t="s">
+        <v>78</v>
+      </c>
+      <c r="I242">
+        <v>0</v>
+      </c>
+      <c r="J242">
+        <v>1</v>
+      </c>
+      <c r="K242">
+        <v>1</v>
+      </c>
+      <c r="L242">
+        <v>2</v>
+      </c>
+      <c r="M242">
+        <v>3</v>
+      </c>
+      <c r="N242">
+        <v>5</v>
+      </c>
+      <c r="O242" t="s">
+        <v>245</v>
+      </c>
+      <c r="P242" t="s">
+        <v>339</v>
+      </c>
+      <c r="Q242">
+        <v>3.6</v>
+      </c>
+      <c r="R242">
+        <v>2.05</v>
+      </c>
+      <c r="S242">
+        <v>3.1</v>
+      </c>
+      <c r="T242">
+        <v>1.44</v>
+      </c>
+      <c r="U242">
+        <v>2.63</v>
+      </c>
+      <c r="V242">
+        <v>3.25</v>
+      </c>
+      <c r="W242">
+        <v>1.33</v>
+      </c>
+      <c r="X242">
+        <v>10</v>
+      </c>
+      <c r="Y242">
+        <v>1.06</v>
+      </c>
+      <c r="Z242">
+        <v>2.55</v>
+      </c>
+      <c r="AA242">
+        <v>3.28</v>
+      </c>
+      <c r="AB242">
+        <v>2.68</v>
+      </c>
+      <c r="AC242">
+        <v>1.07</v>
+      </c>
+      <c r="AD242">
+        <v>8</v>
+      </c>
+      <c r="AE242">
+        <v>1.35</v>
+      </c>
+      <c r="AF242">
+        <v>3.1</v>
+      </c>
+      <c r="AG242">
+        <v>1.95</v>
+      </c>
+      <c r="AH242">
+        <v>1.73</v>
+      </c>
+      <c r="AI242">
+        <v>1.83</v>
+      </c>
+      <c r="AJ242">
+        <v>1.83</v>
+      </c>
+      <c r="AK242">
+        <v>1.53</v>
+      </c>
+      <c r="AL242">
+        <v>1.32</v>
+      </c>
+      <c r="AM242">
+        <v>1.4</v>
+      </c>
+      <c r="AN242">
+        <v>2.31</v>
+      </c>
+      <c r="AO242">
+        <v>1.58</v>
+      </c>
+      <c r="AP242">
+        <v>2.14</v>
+      </c>
+      <c r="AQ242">
+        <v>1.69</v>
+      </c>
+      <c r="AR242">
+        <v>1.6</v>
+      </c>
+      <c r="AS242">
+        <v>1.34</v>
+      </c>
+      <c r="AT242">
+        <v>2.94</v>
+      </c>
+      <c r="AU242">
+        <v>6</v>
+      </c>
+      <c r="AV242">
+        <v>7</v>
+      </c>
+      <c r="AW242">
+        <v>6</v>
+      </c>
+      <c r="AX242">
+        <v>4</v>
+      </c>
+      <c r="AY242">
+        <v>12</v>
+      </c>
+      <c r="AZ242">
+        <v>11</v>
+      </c>
+      <c r="BA242">
+        <v>8</v>
+      </c>
+      <c r="BB242">
+        <v>6</v>
+      </c>
+      <c r="BC242">
+        <v>14</v>
+      </c>
+      <c r="BD242">
+        <v>1.95</v>
+      </c>
+      <c r="BE242">
+        <v>8</v>
+      </c>
+      <c r="BF242">
+        <v>2.05</v>
+      </c>
+      <c r="BG242">
+        <v>1.39</v>
+      </c>
+      <c r="BH242">
+        <v>2.67</v>
+      </c>
+      <c r="BI242">
+        <v>1.73</v>
+      </c>
+      <c r="BJ242">
+        <v>1.99</v>
+      </c>
+      <c r="BK242">
+        <v>2.21</v>
+      </c>
+      <c r="BL242">
+        <v>1.56</v>
+      </c>
+      <c r="BM242">
+        <v>2.92</v>
+      </c>
+      <c r="BN242">
+        <v>1.31</v>
+      </c>
+      <c r="BO242">
+        <v>4.2</v>
+      </c>
+      <c r="BP242">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="243" spans="1:68">
+      <c r="A243" s="1">
+        <v>242</v>
+      </c>
+      <c r="B243">
+        <v>7469105</v>
+      </c>
+      <c r="C243" t="s">
+        <v>68</v>
+      </c>
+      <c r="D243" t="s">
+        <v>69</v>
+      </c>
+      <c r="E243" s="2">
+        <v>45731.41666666666</v>
+      </c>
+      <c r="F243">
+        <v>27</v>
+      </c>
+      <c r="G243" t="s">
+        <v>80</v>
+      </c>
+      <c r="H243" t="s">
+        <v>85</v>
+      </c>
+      <c r="I243">
+        <v>1</v>
+      </c>
+      <c r="J243">
+        <v>0</v>
+      </c>
+      <c r="K243">
+        <v>1</v>
+      </c>
+      <c r="L243">
+        <v>3</v>
+      </c>
+      <c r="M243">
+        <v>0</v>
+      </c>
+      <c r="N243">
+        <v>3</v>
+      </c>
+      <c r="O243" t="s">
+        <v>246</v>
+      </c>
+      <c r="P243" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q243">
+        <v>4.5</v>
+      </c>
+      <c r="R243">
+        <v>2.05</v>
+      </c>
+      <c r="S243">
+        <v>2.75</v>
+      </c>
+      <c r="T243">
+        <v>1.44</v>
+      </c>
+      <c r="U243">
+        <v>2.63</v>
+      </c>
+      <c r="V243">
+        <v>3.25</v>
+      </c>
+      <c r="W243">
+        <v>1.33</v>
+      </c>
+      <c r="X243">
+        <v>10</v>
+      </c>
+      <c r="Y243">
+        <v>1.06</v>
+      </c>
+      <c r="Z243">
+        <v>3.61</v>
+      </c>
+      <c r="AA243">
+        <v>3.41</v>
+      </c>
+      <c r="AB243">
+        <v>2</v>
+      </c>
+      <c r="AC243">
+        <v>1.07</v>
+      </c>
+      <c r="AD243">
+        <v>8</v>
+      </c>
+      <c r="AE243">
+        <v>1.38</v>
+      </c>
+      <c r="AF243">
+        <v>3</v>
+      </c>
+      <c r="AG243">
+        <v>2.1</v>
+      </c>
+      <c r="AH243">
+        <v>1.6</v>
+      </c>
+      <c r="AI243">
+        <v>1.91</v>
+      </c>
+      <c r="AJ243">
+        <v>1.8</v>
+      </c>
+      <c r="AK243">
+        <v>1.77</v>
+      </c>
+      <c r="AL243">
+        <v>1.25</v>
+      </c>
+      <c r="AM243">
+        <v>1.25</v>
+      </c>
+      <c r="AN243">
+        <v>1.5</v>
+      </c>
+      <c r="AO243">
+        <v>1.77</v>
+      </c>
+      <c r="AP243">
+        <v>1.62</v>
+      </c>
+      <c r="AQ243">
+        <v>1.64</v>
+      </c>
+      <c r="AR243">
+        <v>1.29</v>
+      </c>
+      <c r="AS243">
+        <v>1.42</v>
+      </c>
+      <c r="AT243">
+        <v>2.71</v>
+      </c>
+      <c r="AU243">
+        <v>5</v>
+      </c>
+      <c r="AV243">
+        <v>4</v>
+      </c>
+      <c r="AW243">
+        <v>2</v>
+      </c>
+      <c r="AX243">
+        <v>6</v>
+      </c>
+      <c r="AY243">
+        <v>7</v>
+      </c>
+      <c r="AZ243">
+        <v>10</v>
+      </c>
+      <c r="BA243">
+        <v>5</v>
+      </c>
+      <c r="BB243">
+        <v>8</v>
+      </c>
+      <c r="BC243">
+        <v>13</v>
+      </c>
+      <c r="BD243">
+        <v>2.25</v>
+      </c>
+      <c r="BE243">
+        <v>8</v>
+      </c>
+      <c r="BF243">
+        <v>1.8</v>
+      </c>
+      <c r="BG243">
+        <v>1.31</v>
+      </c>
+      <c r="BH243">
+        <v>2.92</v>
+      </c>
+      <c r="BI243">
+        <v>1.59</v>
+      </c>
+      <c r="BJ243">
+        <v>2.16</v>
+      </c>
+      <c r="BK243">
+        <v>2.03</v>
+      </c>
+      <c r="BL243">
+        <v>1.7</v>
+      </c>
+      <c r="BM243">
+        <v>2.67</v>
+      </c>
+      <c r="BN243">
+        <v>1.39</v>
+      </c>
+      <c r="BO243">
+        <v>3.68</v>
+      </c>
+      <c r="BP243">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="244" spans="1:68">
+      <c r="A244" s="1">
+        <v>243</v>
+      </c>
+      <c r="B244">
+        <v>7469108</v>
+      </c>
+      <c r="C244" t="s">
+        <v>68</v>
+      </c>
+      <c r="D244" t="s">
+        <v>69</v>
+      </c>
+      <c r="E244" s="2">
+        <v>45731.66666666666</v>
+      </c>
+      <c r="F244">
+        <v>27</v>
+      </c>
+      <c r="G244" t="s">
+        <v>86</v>
+      </c>
+      <c r="H244" t="s">
+        <v>83</v>
+      </c>
+      <c r="I244">
+        <v>2</v>
+      </c>
+      <c r="J244">
+        <v>0</v>
+      </c>
+      <c r="K244">
+        <v>2</v>
+      </c>
+      <c r="L244">
+        <v>4</v>
+      </c>
+      <c r="M244">
+        <v>0</v>
+      </c>
+      <c r="N244">
+        <v>4</v>
+      </c>
+      <c r="O244" t="s">
+        <v>247</v>
+      </c>
+      <c r="P244" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q244">
+        <v>2.38</v>
+      </c>
+      <c r="R244">
+        <v>2.05</v>
+      </c>
+      <c r="S244">
+        <v>5.5</v>
+      </c>
+      <c r="T244">
+        <v>1.5</v>
+      </c>
+      <c r="U244">
+        <v>2.5</v>
+      </c>
+      <c r="V244">
+        <v>3.4</v>
+      </c>
+      <c r="W244">
+        <v>1.3</v>
+      </c>
+      <c r="X244">
+        <v>10</v>
+      </c>
+      <c r="Y244">
+        <v>1.06</v>
+      </c>
+      <c r="Z244">
+        <v>1.79</v>
+      </c>
+      <c r="AA244">
+        <v>3.37</v>
+      </c>
+      <c r="AB244">
+        <v>4.7</v>
+      </c>
+      <c r="AC244">
+        <v>1.08</v>
+      </c>
+      <c r="AD244">
+        <v>7.5</v>
+      </c>
+      <c r="AE244">
+        <v>1.42</v>
+      </c>
+      <c r="AF244">
+        <v>2.8</v>
+      </c>
+      <c r="AG244">
+        <v>2.2</v>
+      </c>
+      <c r="AH244">
+        <v>1.55</v>
+      </c>
+      <c r="AI244">
+        <v>2.2</v>
+      </c>
+      <c r="AJ244">
+        <v>1.62</v>
+      </c>
+      <c r="AK244">
+        <v>1.15</v>
+      </c>
+      <c r="AL244">
+        <v>1.3</v>
+      </c>
+      <c r="AM244">
+        <v>2.1</v>
+      </c>
+      <c r="AN244">
+        <v>2.62</v>
+      </c>
+      <c r="AO244">
+        <v>0.92</v>
+      </c>
+      <c r="AP244">
+        <v>2.64</v>
+      </c>
+      <c r="AQ244">
+        <v>0.86</v>
+      </c>
+      <c r="AR244">
+        <v>1.82</v>
+      </c>
+      <c r="AS244">
+        <v>1.42</v>
+      </c>
+      <c r="AT244">
+        <v>3.24</v>
+      </c>
+      <c r="AU244">
+        <v>7</v>
+      </c>
+      <c r="AV244">
+        <v>6</v>
+      </c>
+      <c r="AW244">
+        <v>0</v>
+      </c>
+      <c r="AX244">
+        <v>3</v>
+      </c>
+      <c r="AY244">
+        <v>7</v>
+      </c>
+      <c r="AZ244">
+        <v>9</v>
+      </c>
+      <c r="BA244">
+        <v>2</v>
+      </c>
+      <c r="BB244">
+        <v>1</v>
+      </c>
+      <c r="BC244">
+        <v>3</v>
+      </c>
+      <c r="BD244">
+        <v>1.36</v>
+      </c>
+      <c r="BE244">
+        <v>9.5</v>
+      </c>
+      <c r="BF244">
+        <v>3.4</v>
+      </c>
+      <c r="BG244">
+        <v>1.31</v>
+      </c>
+      <c r="BH244">
+        <v>2.92</v>
+      </c>
+      <c r="BI244">
+        <v>1.59</v>
+      </c>
+      <c r="BJ244">
+        <v>2.16</v>
+      </c>
+      <c r="BK244">
+        <v>2.03</v>
+      </c>
+      <c r="BL244">
+        <v>1.7</v>
+      </c>
+      <c r="BM244">
+        <v>2.67</v>
+      </c>
+      <c r="BN244">
+        <v>1.39</v>
+      </c>
+      <c r="BO244">
+        <v>3.58</v>
+      </c>
+      <c r="BP244">
         <v>1.21</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1526" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1562" uniqueCount="343">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -760,6 +760,15 @@
     <t>['8', '42', '70', '88']</t>
   </si>
   <si>
+    <t>['22', '38']</t>
+  </si>
+  <si>
+    <t>['2', '70']</t>
+  </si>
+  <si>
+    <t>['42', '82']</t>
+  </si>
+  <si>
     <t>['16', '45+2']</t>
   </si>
   <si>
@@ -1395,7 +1404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP244"/>
+  <dimension ref="A1:BP250"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1651,7 +1660,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q2">
         <v>2.4</v>
@@ -2063,7 +2072,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q4">
         <v>3.6</v>
@@ -2144,7 +2153,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ4">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2762,7 +2771,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ7">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2887,7 +2896,7 @@
         <v>90</v>
       </c>
       <c r="P8" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q8">
         <v>3.1</v>
@@ -3171,7 +3180,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="AQ9">
         <v>1.38</v>
@@ -3299,7 +3308,7 @@
         <v>94</v>
       </c>
       <c r="P10" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q10">
         <v>2.6</v>
@@ -3377,7 +3386,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ10">
         <v>0.86</v>
@@ -3917,7 +3926,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q13">
         <v>3.1</v>
@@ -4201,7 +4210,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ14">
         <v>0.54</v>
@@ -4407,10 +4416,10 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ15">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4535,7 +4544,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q16">
         <v>2.63</v>
@@ -4741,7 +4750,7 @@
         <v>99</v>
       </c>
       <c r="P17" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -4822,7 +4831,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ17">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5231,10 +5240,10 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ19">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5440,7 +5449,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ20">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR20">
         <v>0.67</v>
@@ -5771,7 +5780,7 @@
         <v>103</v>
       </c>
       <c r="P22" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -6183,7 +6192,7 @@
         <v>105</v>
       </c>
       <c r="P24" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q24">
         <v>2.62</v>
@@ -6264,7 +6273,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ24">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR24">
         <v>1.39</v>
@@ -6467,7 +6476,7 @@
         <v>1</v>
       </c>
       <c r="AP25">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="AQ25">
         <v>0.86</v>
@@ -7007,7 +7016,7 @@
         <v>108</v>
       </c>
       <c r="P28" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q28">
         <v>2.6</v>
@@ -7085,7 +7094,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ28">
         <v>1.57</v>
@@ -7294,7 +7303,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ29">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR29">
         <v>1.48</v>
@@ -7706,7 +7715,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ31">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR31">
         <v>1.38</v>
@@ -7909,7 +7918,7 @@
         <v>3</v>
       </c>
       <c r="AP32">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ32">
         <v>1.31</v>
@@ -8118,7 +8127,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ33">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AR33">
         <v>2.15</v>
@@ -8321,10 +8330,10 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ34">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR34">
         <v>1.55</v>
@@ -8449,7 +8458,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q35">
         <v>3.3</v>
@@ -8655,7 +8664,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q36">
         <v>3.1</v>
@@ -8861,7 +8870,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q37">
         <v>3.4</v>
@@ -9067,7 +9076,7 @@
         <v>90</v>
       </c>
       <c r="P38" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q38">
         <v>3.2</v>
@@ -9273,7 +9282,7 @@
         <v>90</v>
       </c>
       <c r="P39" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q39">
         <v>3.4</v>
@@ -9351,7 +9360,7 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="AQ39">
         <v>0.85</v>
@@ -9557,7 +9566,7 @@
         <v>3</v>
       </c>
       <c r="AP40">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ40">
         <v>1.64</v>
@@ -9685,7 +9694,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q41">
         <v>2.5</v>
@@ -9766,7 +9775,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ41">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR41">
         <v>1.73</v>
@@ -9891,7 +9900,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q42">
         <v>3.25</v>
@@ -10097,7 +10106,7 @@
         <v>90</v>
       </c>
       <c r="P43" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q43">
         <v>2.75</v>
@@ -10175,7 +10184,7 @@
         <v>0.5</v>
       </c>
       <c r="AP43">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ43">
         <v>1.57</v>
@@ -10384,7 +10393,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ44">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR44">
         <v>1.25</v>
@@ -10793,7 +10802,7 @@
         <v>1.5</v>
       </c>
       <c r="AP46">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ46">
         <v>1.38</v>
@@ -11002,7 +11011,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ47">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AR47">
         <v>1.49</v>
@@ -11208,7 +11217,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ48">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR48">
         <v>1.82</v>
@@ -11411,7 +11420,7 @@
         <v>1.5</v>
       </c>
       <c r="AP49">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ49">
         <v>1.31</v>
@@ -11823,7 +11832,7 @@
         <v>1.33</v>
       </c>
       <c r="AP51">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ51">
         <v>1.38</v>
@@ -12157,7 +12166,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -12363,7 +12372,7 @@
         <v>129</v>
       </c>
       <c r="P54" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q54">
         <v>2.55</v>
@@ -12569,7 +12578,7 @@
         <v>130</v>
       </c>
       <c r="P55" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q55">
         <v>2.55</v>
@@ -12856,7 +12865,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ56">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR56">
         <v>1.76</v>
@@ -12981,7 +12990,7 @@
         <v>132</v>
       </c>
       <c r="P57" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -13265,10 +13274,10 @@
         <v>1.5</v>
       </c>
       <c r="AP58">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="AQ58">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR58">
         <v>1</v>
@@ -13393,7 +13402,7 @@
         <v>134</v>
       </c>
       <c r="P59" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q59">
         <v>2.62</v>
@@ -13471,10 +13480,10 @@
         <v>1.67</v>
       </c>
       <c r="AP59">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ59">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR59">
         <v>1.53</v>
@@ -13599,7 +13608,7 @@
         <v>135</v>
       </c>
       <c r="P60" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q60">
         <v>2.88</v>
@@ -14011,7 +14020,7 @@
         <v>137</v>
       </c>
       <c r="P62" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q62">
         <v>3.6</v>
@@ -14089,7 +14098,7 @@
         <v>2</v>
       </c>
       <c r="AP62">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ62">
         <v>1.64</v>
@@ -14217,7 +14226,7 @@
         <v>138</v>
       </c>
       <c r="P63" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q63">
         <v>3.75</v>
@@ -15122,7 +15131,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ67">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR67">
         <v>1.61</v>
@@ -15247,7 +15256,7 @@
         <v>143</v>
       </c>
       <c r="P68" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15453,7 +15462,7 @@
         <v>144</v>
       </c>
       <c r="P69" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15659,7 +15668,7 @@
         <v>145</v>
       </c>
       <c r="P70" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q70">
         <v>3.75</v>
@@ -16071,7 +16080,7 @@
         <v>147</v>
       </c>
       <c r="P72" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16149,10 +16158,10 @@
         <v>0</v>
       </c>
       <c r="AP72">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ72">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AR72">
         <v>1.72</v>
@@ -16277,7 +16286,7 @@
         <v>90</v>
       </c>
       <c r="P73" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q73">
         <v>4.33</v>
@@ -16355,7 +16364,7 @@
         <v>0.75</v>
       </c>
       <c r="AP73">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="AQ73">
         <v>1</v>
@@ -16483,7 +16492,7 @@
         <v>90</v>
       </c>
       <c r="P74" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q74">
         <v>2.4</v>
@@ -16689,7 +16698,7 @@
         <v>148</v>
       </c>
       <c r="P75" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q75">
         <v>3.5</v>
@@ -16767,7 +16776,7 @@
         <v>0</v>
       </c>
       <c r="AP75">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ75">
         <v>0.54</v>
@@ -16895,7 +16904,7 @@
         <v>149</v>
       </c>
       <c r="P76" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q76">
         <v>2.88</v>
@@ -16976,7 +16985,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ76">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR76">
         <v>1.45</v>
@@ -17385,7 +17394,7 @@
         <v>1</v>
       </c>
       <c r="AP78">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ78">
         <v>1</v>
@@ -17513,7 +17522,7 @@
         <v>151</v>
       </c>
       <c r="P79" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17594,7 +17603,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ79">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR79">
         <v>1.66</v>
@@ -17719,7 +17728,7 @@
         <v>152</v>
       </c>
       <c r="P80" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q80">
         <v>2.05</v>
@@ -17800,7 +17809,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ80">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR80">
         <v>2.09</v>
@@ -17925,7 +17934,7 @@
         <v>90</v>
       </c>
       <c r="P81" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q81">
         <v>4.33</v>
@@ -18209,7 +18218,7 @@
         <v>1.33</v>
       </c>
       <c r="AP82">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ82">
         <v>0.86</v>
@@ -18749,7 +18758,7 @@
         <v>90</v>
       </c>
       <c r="P85" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q85">
         <v>3.1</v>
@@ -18827,10 +18836,10 @@
         <v>0</v>
       </c>
       <c r="AP85">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ85">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AR85">
         <v>1.48</v>
@@ -18955,7 +18964,7 @@
         <v>156</v>
       </c>
       <c r="P86" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -19445,7 +19454,7 @@
         <v>1.5</v>
       </c>
       <c r="AP88">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ88">
         <v>1.57</v>
@@ -19779,7 +19788,7 @@
         <v>90</v>
       </c>
       <c r="P90" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q90">
         <v>2.38</v>
@@ -19860,7 +19869,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ90">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR90">
         <v>1.42</v>
@@ -20191,7 +20200,7 @@
         <v>160</v>
       </c>
       <c r="P92" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20475,7 +20484,7 @@
         <v>1.5</v>
       </c>
       <c r="AP93">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ93">
         <v>1.69</v>
@@ -20684,7 +20693,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ94">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR94">
         <v>1.21</v>
@@ -20809,7 +20818,7 @@
         <v>162</v>
       </c>
       <c r="P95" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q95">
         <v>1.9</v>
@@ -20890,7 +20899,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ95">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR95">
         <v>2.11</v>
@@ -21015,7 +21024,7 @@
         <v>163</v>
       </c>
       <c r="P96" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q96">
         <v>2.75</v>
@@ -21093,7 +21102,7 @@
         <v>1.2</v>
       </c>
       <c r="AP96">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ96">
         <v>1</v>
@@ -21427,7 +21436,7 @@
         <v>90</v>
       </c>
       <c r="P98" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q98">
         <v>4.75</v>
@@ -21505,7 +21514,7 @@
         <v>0.25</v>
       </c>
       <c r="AP98">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="AQ98">
         <v>0.54</v>
@@ -21714,7 +21723,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ99">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR99">
         <v>1.8</v>
@@ -21920,7 +21929,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ100">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AR100">
         <v>1.57</v>
@@ -22123,7 +22132,7 @@
         <v>0.67</v>
       </c>
       <c r="AP101">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="AQ101">
         <v>0.86</v>
@@ -22663,7 +22672,7 @@
         <v>167</v>
       </c>
       <c r="P104" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q104">
         <v>2.25</v>
@@ -23487,7 +23496,7 @@
         <v>90</v>
       </c>
       <c r="P108" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q108">
         <v>4.5</v>
@@ -23980,7 +23989,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ110">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR110">
         <v>1.85</v>
@@ -24186,7 +24195,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ111">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR111">
         <v>1.14</v>
@@ -24311,7 +24320,7 @@
         <v>173</v>
       </c>
       <c r="P112" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q112">
         <v>3.5</v>
@@ -24723,7 +24732,7 @@
         <v>90</v>
       </c>
       <c r="P114" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q114">
         <v>2.85</v>
@@ -24801,10 +24810,10 @@
         <v>0.67</v>
       </c>
       <c r="AP114">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ114">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR114">
         <v>1.28</v>
@@ -25007,7 +25016,7 @@
         <v>2.17</v>
       </c>
       <c r="AP115">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ115">
         <v>1.64</v>
@@ -25135,7 +25144,7 @@
         <v>175</v>
       </c>
       <c r="P116" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q116">
         <v>2.4</v>
@@ -25419,7 +25428,7 @@
         <v>0.8</v>
       </c>
       <c r="AP117">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ117">
         <v>0.54</v>
@@ -25547,7 +25556,7 @@
         <v>90</v>
       </c>
       <c r="P118" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q118">
         <v>4</v>
@@ -25625,7 +25634,7 @@
         <v>1.14</v>
       </c>
       <c r="AP118">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="AQ118">
         <v>1.57</v>
@@ -26165,7 +26174,7 @@
         <v>178</v>
       </c>
       <c r="P121" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q121">
         <v>2.88</v>
@@ -26452,7 +26461,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ122">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AR122">
         <v>1.78</v>
@@ -26655,7 +26664,7 @@
         <v>1</v>
       </c>
       <c r="AP123">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ123">
         <v>0.86</v>
@@ -26864,7 +26873,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ124">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR124">
         <v>1.79</v>
@@ -27067,7 +27076,7 @@
         <v>1.14</v>
       </c>
       <c r="AP125">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ125">
         <v>1.38</v>
@@ -27276,7 +27285,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ126">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR126">
         <v>1.58</v>
@@ -27688,7 +27697,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ128">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR128">
         <v>1.83</v>
@@ -27891,7 +27900,7 @@
         <v>1</v>
       </c>
       <c r="AP129">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="AQ129">
         <v>1.57</v>
@@ -28509,7 +28518,7 @@
         <v>1</v>
       </c>
       <c r="AP132">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ132">
         <v>0.86</v>
@@ -28843,7 +28852,7 @@
         <v>90</v>
       </c>
       <c r="P134" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q134">
         <v>3.2</v>
@@ -28924,7 +28933,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ134">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AR134">
         <v>1.08</v>
@@ -29049,7 +29058,7 @@
         <v>90</v>
       </c>
       <c r="P135" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q135">
         <v>5</v>
@@ -29333,10 +29342,10 @@
         <v>1.17</v>
       </c>
       <c r="AP136">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ136">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR136">
         <v>1.62</v>
@@ -29539,7 +29548,7 @@
         <v>1.29</v>
       </c>
       <c r="AP137">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ137">
         <v>1.57</v>
@@ -29745,10 +29754,10 @@
         <v>0.14</v>
       </c>
       <c r="AP138">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ138">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR138">
         <v>1.44</v>
@@ -30285,7 +30294,7 @@
         <v>189</v>
       </c>
       <c r="P141" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q141">
         <v>2.8</v>
@@ -30775,7 +30784,7 @@
         <v>0.57</v>
       </c>
       <c r="AP143">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ143">
         <v>0.85</v>
@@ -31109,7 +31118,7 @@
         <v>192</v>
       </c>
       <c r="P145" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q145">
         <v>2.75</v>
@@ -31315,7 +31324,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q146">
         <v>3.75</v>
@@ -31521,7 +31530,7 @@
         <v>129</v>
       </c>
       <c r="P147" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q147">
         <v>3.75</v>
@@ -31602,7 +31611,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ147">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR147">
         <v>1.16</v>
@@ -31727,7 +31736,7 @@
         <v>90</v>
       </c>
       <c r="P148" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q148">
         <v>2.4</v>
@@ -31933,7 +31942,7 @@
         <v>90</v>
       </c>
       <c r="P149" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q149">
         <v>3.1</v>
@@ -32014,7 +32023,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ149">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR149">
         <v>1.68</v>
@@ -32345,7 +32354,7 @@
         <v>194</v>
       </c>
       <c r="P151" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q151">
         <v>1.62</v>
@@ -32629,7 +32638,7 @@
         <v>0.63</v>
       </c>
       <c r="AP152">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ152">
         <v>0.86</v>
@@ -32757,7 +32766,7 @@
         <v>95</v>
       </c>
       <c r="P153" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q153">
         <v>2.63</v>
@@ -32838,7 +32847,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ153">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR153">
         <v>1.78</v>
@@ -33247,7 +33256,7 @@
         <v>1.25</v>
       </c>
       <c r="AP155">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="AQ155">
         <v>1</v>
@@ -33453,10 +33462,10 @@
         <v>1</v>
       </c>
       <c r="AP156">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ156">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR156">
         <v>1.52</v>
@@ -33581,7 +33590,7 @@
         <v>197</v>
       </c>
       <c r="P157" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q157">
         <v>2.7</v>
@@ -33662,7 +33671,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ157">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR157">
         <v>1.86</v>
@@ -33787,7 +33796,7 @@
         <v>96</v>
       </c>
       <c r="P158" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q158">
         <v>2.55</v>
@@ -33993,7 +34002,7 @@
         <v>198</v>
       </c>
       <c r="P159" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q159">
         <v>3.3</v>
@@ -34199,7 +34208,7 @@
         <v>90</v>
       </c>
       <c r="P160" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q160">
         <v>2.75</v>
@@ -34486,7 +34495,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ161">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AR161">
         <v>1.88</v>
@@ -34689,10 +34698,10 @@
         <v>0.13</v>
       </c>
       <c r="AP162">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ162">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR162">
         <v>1.68</v>
@@ -35641,7 +35650,7 @@
         <v>109</v>
       </c>
       <c r="P167" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q167">
         <v>3.35</v>
@@ -35719,7 +35728,7 @@
         <v>0.67</v>
       </c>
       <c r="AP167">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ167">
         <v>0.86</v>
@@ -36053,7 +36062,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q169">
         <v>2.8</v>
@@ -36259,7 +36268,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q170">
         <v>3</v>
@@ -36337,7 +36346,7 @@
         <v>1.89</v>
       </c>
       <c r="AP170">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ170">
         <v>1.64</v>
@@ -36671,7 +36680,7 @@
         <v>90</v>
       </c>
       <c r="P172" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q172">
         <v>2.63</v>
@@ -36752,7 +36761,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ172">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR172">
         <v>1.73</v>
@@ -36877,7 +36886,7 @@
         <v>207</v>
       </c>
       <c r="P173" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q173">
         <v>2.3</v>
@@ -36958,7 +36967,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ173">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR173">
         <v>1.78</v>
@@ -37161,7 +37170,7 @@
         <v>0.9</v>
       </c>
       <c r="AP174">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ174">
         <v>0.86</v>
@@ -37367,10 +37376,10 @@
         <v>0.67</v>
       </c>
       <c r="AP175">
+        <v>0.73</v>
+      </c>
+      <c r="AQ175">
         <v>0.57</v>
-      </c>
-      <c r="AQ175">
-        <v>0.54</v>
       </c>
       <c r="AR175">
         <v>0.95</v>
@@ -37576,7 +37585,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ176">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR176">
         <v>1.28</v>
@@ -37779,7 +37788,7 @@
         <v>0.78</v>
       </c>
       <c r="AP177">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ177">
         <v>0.85</v>
@@ -37907,7 +37916,7 @@
         <v>90</v>
       </c>
       <c r="P178" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q178">
         <v>3.25</v>
@@ -38319,7 +38328,7 @@
         <v>212</v>
       </c>
       <c r="P180" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q180">
         <v>2.2</v>
@@ -38525,7 +38534,7 @@
         <v>90</v>
       </c>
       <c r="P181" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q181">
         <v>3.25</v>
@@ -38606,7 +38615,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ181">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR181">
         <v>1.42</v>
@@ -39224,7 +39233,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ184">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR184">
         <v>1.62</v>
@@ -39427,7 +39436,7 @@
         <v>1.5</v>
       </c>
       <c r="AP185">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ185">
         <v>1.57</v>
@@ -39633,7 +39642,7 @@
         <v>1.33</v>
       </c>
       <c r="AP186">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ186">
         <v>1.69</v>
@@ -39761,7 +39770,7 @@
         <v>90</v>
       </c>
       <c r="P187" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q187">
         <v>2.55</v>
@@ -39842,7 +39851,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ187">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR187">
         <v>1.32</v>
@@ -39967,7 +39976,7 @@
         <v>215</v>
       </c>
       <c r="P188" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q188">
         <v>4.5</v>
@@ -40045,7 +40054,7 @@
         <v>1.2</v>
       </c>
       <c r="AP188">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ188">
         <v>1.38</v>
@@ -40379,7 +40388,7 @@
         <v>90</v>
       </c>
       <c r="P190" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q190">
         <v>3.3</v>
@@ -40585,7 +40594,7 @@
         <v>90</v>
       </c>
       <c r="P191" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q191">
         <v>2.75</v>
@@ -40666,7 +40675,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ191">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR191">
         <v>1.28</v>
@@ -40791,7 +40800,7 @@
         <v>90</v>
       </c>
       <c r="P192" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q192">
         <v>3.25</v>
@@ -41409,7 +41418,7 @@
         <v>214</v>
       </c>
       <c r="P195" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q195">
         <v>4.75</v>
@@ -41487,10 +41496,10 @@
         <v>0.91</v>
       </c>
       <c r="AP195">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="AQ195">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR195">
         <v>1.02</v>
@@ -41615,7 +41624,7 @@
         <v>90</v>
       </c>
       <c r="P196" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q196">
         <v>3.65</v>
@@ -41821,7 +41830,7 @@
         <v>218</v>
       </c>
       <c r="P197" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q197">
         <v>1.94</v>
@@ -41902,7 +41911,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ197">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AR197">
         <v>1.67</v>
@@ -42105,7 +42114,7 @@
         <v>1.3</v>
       </c>
       <c r="AP198">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ198">
         <v>1</v>
@@ -42233,7 +42242,7 @@
         <v>90</v>
       </c>
       <c r="P199" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q199">
         <v>3.75</v>
@@ -42314,7 +42323,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ199">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR199">
         <v>1.34</v>
@@ -42929,7 +42938,7 @@
         <v>1.4</v>
       </c>
       <c r="AP202">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ202">
         <v>1.31</v>
@@ -43263,7 +43272,7 @@
         <v>160</v>
       </c>
       <c r="P204" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q204">
         <v>3</v>
@@ -43469,7 +43478,7 @@
         <v>90</v>
       </c>
       <c r="P205" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q205">
         <v>2.75</v>
@@ -43547,7 +43556,7 @@
         <v>0.91</v>
       </c>
       <c r="AP205">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ205">
         <v>1</v>
@@ -43881,7 +43890,7 @@
         <v>90</v>
       </c>
       <c r="P207" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q207">
         <v>3.8</v>
@@ -44374,7 +44383,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ209">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AR209">
         <v>1.77</v>
@@ -44577,7 +44586,7 @@
         <v>1</v>
       </c>
       <c r="AP210">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ210">
         <v>0.86</v>
@@ -44786,7 +44795,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ211">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR211">
         <v>1.79</v>
@@ -45117,7 +45126,7 @@
         <v>226</v>
       </c>
       <c r="P213" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q213">
         <v>3.75</v>
@@ -45401,10 +45410,10 @@
         <v>1.42</v>
       </c>
       <c r="AP214">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="AQ214">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR214">
         <v>1.01</v>
@@ -45529,7 +45538,7 @@
         <v>228</v>
       </c>
       <c r="P215" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q215">
         <v>2.95</v>
@@ -45735,7 +45744,7 @@
         <v>90</v>
       </c>
       <c r="P216" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q216">
         <v>1.96</v>
@@ -46019,10 +46028,10 @@
         <v>0.64</v>
       </c>
       <c r="AP217">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ217">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR217">
         <v>1.74</v>
@@ -46225,7 +46234,7 @@
         <v>0.91</v>
       </c>
       <c r="AP218">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ218">
         <v>0.85</v>
@@ -46353,7 +46362,7 @@
         <v>229</v>
       </c>
       <c r="P219" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q219">
         <v>4.3</v>
@@ -46971,7 +46980,7 @@
         <v>90</v>
       </c>
       <c r="P222" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q222">
         <v>2.7</v>
@@ -47177,7 +47186,7 @@
         <v>231</v>
       </c>
       <c r="P223" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q223">
         <v>3.65</v>
@@ -47255,7 +47264,7 @@
         <v>1.58</v>
       </c>
       <c r="AP223">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ223">
         <v>1.57</v>
@@ -47383,7 +47392,7 @@
         <v>232</v>
       </c>
       <c r="P224" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q224">
         <v>5.2</v>
@@ -47795,7 +47804,7 @@
         <v>221</v>
       </c>
       <c r="P226" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q226">
         <v>4.4</v>
@@ -47876,7 +47885,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ226">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR226">
         <v>1.25</v>
@@ -48001,7 +48010,7 @@
         <v>234</v>
       </c>
       <c r="P227" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q227">
         <v>2.7</v>
@@ -48082,7 +48091,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ227">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR227">
         <v>1.25</v>
@@ -48285,7 +48294,7 @@
         <v>1.42</v>
       </c>
       <c r="AP228">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ228">
         <v>1.31</v>
@@ -48491,10 +48500,10 @@
         <v>0.58</v>
       </c>
       <c r="AP229">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ229">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AR229">
         <v>1.3</v>
@@ -48619,7 +48628,7 @@
         <v>90</v>
       </c>
       <c r="P230" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="Q230">
         <v>3.04</v>
@@ -48697,10 +48706,10 @@
         <v>1</v>
       </c>
       <c r="AP230">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ230">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR230">
         <v>1.69</v>
@@ -49237,7 +49246,7 @@
         <v>238</v>
       </c>
       <c r="P233" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="Q233">
         <v>3.1</v>
@@ -49443,7 +49452,7 @@
         <v>239</v>
       </c>
       <c r="P234" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q234">
         <v>1.85</v>
@@ -49521,10 +49530,10 @@
         <v>1.31</v>
       </c>
       <c r="AP234">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ234">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR234">
         <v>1.75</v>
@@ -49730,7 +49739,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ235">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR235">
         <v>1.76</v>
@@ -49855,7 +49864,7 @@
         <v>241</v>
       </c>
       <c r="P236" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="Q236">
         <v>3.7</v>
@@ -49933,7 +49942,7 @@
         <v>0.85</v>
       </c>
       <c r="AP236">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="AQ236">
         <v>0.86</v>
@@ -50473,7 +50482,7 @@
         <v>243</v>
       </c>
       <c r="P239" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="Q239">
         <v>3.1</v>
@@ -51091,7 +51100,7 @@
         <v>245</v>
       </c>
       <c r="P242" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="Q242">
         <v>3.6</v>
@@ -51660,6 +51669,1242 @@
       </c>
       <c r="BP244">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="245" spans="1:68">
+      <c r="A245" s="1">
+        <v>244</v>
+      </c>
+      <c r="B245">
+        <v>7469114</v>
+      </c>
+      <c r="C245" t="s">
+        <v>68</v>
+      </c>
+      <c r="D245" t="s">
+        <v>69</v>
+      </c>
+      <c r="E245" s="2">
+        <v>45744.66666666666</v>
+      </c>
+      <c r="F245">
+        <v>28</v>
+      </c>
+      <c r="G245" t="s">
+        <v>82</v>
+      </c>
+      <c r="H245" t="s">
+        <v>84</v>
+      </c>
+      <c r="I245">
+        <v>0</v>
+      </c>
+      <c r="J245">
+        <v>0</v>
+      </c>
+      <c r="K245">
+        <v>0</v>
+      </c>
+      <c r="L245">
+        <v>1</v>
+      </c>
+      <c r="M245">
+        <v>0</v>
+      </c>
+      <c r="N245">
+        <v>1</v>
+      </c>
+      <c r="O245" t="s">
+        <v>188</v>
+      </c>
+      <c r="P245" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q245">
+        <v>2.88</v>
+      </c>
+      <c r="R245">
+        <v>2.05</v>
+      </c>
+      <c r="S245">
+        <v>4</v>
+      </c>
+      <c r="T245">
+        <v>1.44</v>
+      </c>
+      <c r="U245">
+        <v>2.63</v>
+      </c>
+      <c r="V245">
+        <v>3.25</v>
+      </c>
+      <c r="W245">
+        <v>1.33</v>
+      </c>
+      <c r="X245">
+        <v>10</v>
+      </c>
+      <c r="Y245">
+        <v>1.06</v>
+      </c>
+      <c r="Z245">
+        <v>2.12</v>
+      </c>
+      <c r="AA245">
+        <v>3.23</v>
+      </c>
+      <c r="AB245">
+        <v>3.47</v>
+      </c>
+      <c r="AC245">
+        <v>1.07</v>
+      </c>
+      <c r="AD245">
+        <v>8</v>
+      </c>
+      <c r="AE245">
+        <v>1.36</v>
+      </c>
+      <c r="AF245">
+        <v>3.1</v>
+      </c>
+      <c r="AG245">
+        <v>2</v>
+      </c>
+      <c r="AH245">
+        <v>1.67</v>
+      </c>
+      <c r="AI245">
+        <v>1.83</v>
+      </c>
+      <c r="AJ245">
+        <v>1.83</v>
+      </c>
+      <c r="AK245">
+        <v>1.31</v>
+      </c>
+      <c r="AL245">
+        <v>1.31</v>
+      </c>
+      <c r="AM245">
+        <v>1.68</v>
+      </c>
+      <c r="AN245">
+        <v>1.69</v>
+      </c>
+      <c r="AO245">
+        <v>1.21</v>
+      </c>
+      <c r="AP245">
+        <v>1.79</v>
+      </c>
+      <c r="AQ245">
+        <v>1.13</v>
+      </c>
+      <c r="AR245">
+        <v>1.66</v>
+      </c>
+      <c r="AS245">
+        <v>1.28</v>
+      </c>
+      <c r="AT245">
+        <v>2.94</v>
+      </c>
+      <c r="AU245">
+        <v>5</v>
+      </c>
+      <c r="AV245">
+        <v>3</v>
+      </c>
+      <c r="AW245">
+        <v>2</v>
+      </c>
+      <c r="AX245">
+        <v>5</v>
+      </c>
+      <c r="AY245">
+        <v>7</v>
+      </c>
+      <c r="AZ245">
+        <v>8</v>
+      </c>
+      <c r="BA245">
+        <v>2</v>
+      </c>
+      <c r="BB245">
+        <v>6</v>
+      </c>
+      <c r="BC245">
+        <v>8</v>
+      </c>
+      <c r="BD245">
+        <v>1.51</v>
+      </c>
+      <c r="BE245">
+        <v>8.5</v>
+      </c>
+      <c r="BF245">
+        <v>3.16</v>
+      </c>
+      <c r="BG245">
+        <v>1.39</v>
+      </c>
+      <c r="BH245">
+        <v>2.77</v>
+      </c>
+      <c r="BI245">
+        <v>1.68</v>
+      </c>
+      <c r="BJ245">
+        <v>2.12</v>
+      </c>
+      <c r="BK245">
+        <v>2.11</v>
+      </c>
+      <c r="BL245">
+        <v>1.68</v>
+      </c>
+      <c r="BM245">
+        <v>2.7</v>
+      </c>
+      <c r="BN245">
+        <v>1.41</v>
+      </c>
+      <c r="BO245">
+        <v>3.65</v>
+      </c>
+      <c r="BP245">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="246" spans="1:68">
+      <c r="A246" s="1">
+        <v>245</v>
+      </c>
+      <c r="B246">
+        <v>7469116</v>
+      </c>
+      <c r="C246" t="s">
+        <v>68</v>
+      </c>
+      <c r="D246" t="s">
+        <v>69</v>
+      </c>
+      <c r="E246" s="2">
+        <v>45744.66666666666</v>
+      </c>
+      <c r="F246">
+        <v>28</v>
+      </c>
+      <c r="G246" t="s">
+        <v>87</v>
+      </c>
+      <c r="H246" t="s">
+        <v>81</v>
+      </c>
+      <c r="I246">
+        <v>1</v>
+      </c>
+      <c r="J246">
+        <v>1</v>
+      </c>
+      <c r="K246">
+        <v>2</v>
+      </c>
+      <c r="L246">
+        <v>1</v>
+      </c>
+      <c r="M246">
+        <v>1</v>
+      </c>
+      <c r="N246">
+        <v>2</v>
+      </c>
+      <c r="O246" t="s">
+        <v>114</v>
+      </c>
+      <c r="P246" t="s">
+        <v>278</v>
+      </c>
+      <c r="Q246">
+        <v>3.6</v>
+      </c>
+      <c r="R246">
+        <v>2.2</v>
+      </c>
+      <c r="S246">
+        <v>2.88</v>
+      </c>
+      <c r="T246">
+        <v>1.4</v>
+      </c>
+      <c r="U246">
+        <v>2.75</v>
+      </c>
+      <c r="V246">
+        <v>2.75</v>
+      </c>
+      <c r="W246">
+        <v>1.4</v>
+      </c>
+      <c r="X246">
+        <v>8</v>
+      </c>
+      <c r="Y246">
+        <v>1.08</v>
+      </c>
+      <c r="Z246">
+        <v>3.04</v>
+      </c>
+      <c r="AA246">
+        <v>3.41</v>
+      </c>
+      <c r="AB246">
+        <v>2.23</v>
+      </c>
+      <c r="AC246">
+        <v>1.06</v>
+      </c>
+      <c r="AD246">
+        <v>8.5</v>
+      </c>
+      <c r="AE246">
+        <v>1.28</v>
+      </c>
+      <c r="AF246">
+        <v>3.5</v>
+      </c>
+      <c r="AG246">
+        <v>1.87</v>
+      </c>
+      <c r="AH246">
+        <v>1.87</v>
+      </c>
+      <c r="AI246">
+        <v>1.67</v>
+      </c>
+      <c r="AJ246">
+        <v>2.1</v>
+      </c>
+      <c r="AK246">
+        <v>1.6</v>
+      </c>
+      <c r="AL246">
+        <v>1.3</v>
+      </c>
+      <c r="AM246">
+        <v>1.36</v>
+      </c>
+      <c r="AN246">
+        <v>1.54</v>
+      </c>
+      <c r="AO246">
+        <v>1</v>
+      </c>
+      <c r="AP246">
+        <v>1.5</v>
+      </c>
+      <c r="AQ246">
+        <v>1</v>
+      </c>
+      <c r="AR246">
+        <v>1.33</v>
+      </c>
+      <c r="AS246">
+        <v>1.41</v>
+      </c>
+      <c r="AT246">
+        <v>2.74</v>
+      </c>
+      <c r="AU246">
+        <v>4</v>
+      </c>
+      <c r="AV246">
+        <v>3</v>
+      </c>
+      <c r="AW246">
+        <v>7</v>
+      </c>
+      <c r="AX246">
+        <v>9</v>
+      </c>
+      <c r="AY246">
+        <v>11</v>
+      </c>
+      <c r="AZ246">
+        <v>12</v>
+      </c>
+      <c r="BA246">
+        <v>2</v>
+      </c>
+      <c r="BB246">
+        <v>8</v>
+      </c>
+      <c r="BC246">
+        <v>10</v>
+      </c>
+      <c r="BD246">
+        <v>2.66</v>
+      </c>
+      <c r="BE246">
+        <v>8.5</v>
+      </c>
+      <c r="BF246">
+        <v>1.64</v>
+      </c>
+      <c r="BG246">
+        <v>1.23</v>
+      </c>
+      <c r="BH246">
+        <v>3.6</v>
+      </c>
+      <c r="BI246">
+        <v>1.44</v>
+      </c>
+      <c r="BJ246">
+        <v>2.58</v>
+      </c>
+      <c r="BK246">
+        <v>1.74</v>
+      </c>
+      <c r="BL246">
+        <v>2.02</v>
+      </c>
+      <c r="BM246">
+        <v>2.19</v>
+      </c>
+      <c r="BN246">
+        <v>1.63</v>
+      </c>
+      <c r="BO246">
+        <v>2.77</v>
+      </c>
+      <c r="BP246">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="247" spans="1:68">
+      <c r="A247" s="1">
+        <v>246</v>
+      </c>
+      <c r="B247">
+        <v>7469113</v>
+      </c>
+      <c r="C247" t="s">
+        <v>68</v>
+      </c>
+      <c r="D247" t="s">
+        <v>69</v>
+      </c>
+      <c r="E247" s="2">
+        <v>45744.66666666666</v>
+      </c>
+      <c r="F247">
+        <v>28</v>
+      </c>
+      <c r="G247" t="s">
+        <v>77</v>
+      </c>
+      <c r="H247" t="s">
+        <v>71</v>
+      </c>
+      <c r="I247">
+        <v>2</v>
+      </c>
+      <c r="J247">
+        <v>0</v>
+      </c>
+      <c r="K247">
+        <v>2</v>
+      </c>
+      <c r="L247">
+        <v>2</v>
+      </c>
+      <c r="M247">
+        <v>0</v>
+      </c>
+      <c r="N247">
+        <v>2</v>
+      </c>
+      <c r="O247" t="s">
+        <v>248</v>
+      </c>
+      <c r="P247" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q247">
+        <v>4</v>
+      </c>
+      <c r="R247">
+        <v>1.95</v>
+      </c>
+      <c r="S247">
+        <v>3.2</v>
+      </c>
+      <c r="T247">
+        <v>1.53</v>
+      </c>
+      <c r="U247">
+        <v>2.38</v>
+      </c>
+      <c r="V247">
+        <v>3.75</v>
+      </c>
+      <c r="W247">
+        <v>1.25</v>
+      </c>
+      <c r="X247">
+        <v>11</v>
+      </c>
+      <c r="Y247">
+        <v>1.05</v>
+      </c>
+      <c r="Z247">
+        <v>3.03</v>
+      </c>
+      <c r="AA247">
+        <v>3.17</v>
+      </c>
+      <c r="AB247">
+        <v>2.36</v>
+      </c>
+      <c r="AC247">
+        <v>1.09</v>
+      </c>
+      <c r="AD247">
+        <v>7</v>
+      </c>
+      <c r="AE247">
+        <v>1.48</v>
+      </c>
+      <c r="AF247">
+        <v>2.6</v>
+      </c>
+      <c r="AG247">
+        <v>2.3</v>
+      </c>
+      <c r="AH247">
+        <v>1.5</v>
+      </c>
+      <c r="AI247">
+        <v>2.1</v>
+      </c>
+      <c r="AJ247">
+        <v>1.67</v>
+      </c>
+      <c r="AK247">
+        <v>1.55</v>
+      </c>
+      <c r="AL247">
+        <v>1.34</v>
+      </c>
+      <c r="AM247">
+        <v>1.36</v>
+      </c>
+      <c r="AN247">
+        <v>0.57</v>
+      </c>
+      <c r="AO247">
+        <v>0.85</v>
+      </c>
+      <c r="AP247">
+        <v>0.73</v>
+      </c>
+      <c r="AQ247">
+        <v>0.79</v>
+      </c>
+      <c r="AR247">
+        <v>1.07</v>
+      </c>
+      <c r="AS247">
+        <v>1.01</v>
+      </c>
+      <c r="AT247">
+        <v>2.08</v>
+      </c>
+      <c r="AU247">
+        <v>4</v>
+      </c>
+      <c r="AV247">
+        <v>5</v>
+      </c>
+      <c r="AW247">
+        <v>6</v>
+      </c>
+      <c r="AX247">
+        <v>14</v>
+      </c>
+      <c r="AY247">
+        <v>11</v>
+      </c>
+      <c r="AZ247">
+        <v>20</v>
+      </c>
+      <c r="BA247">
+        <v>0</v>
+      </c>
+      <c r="BB247">
+        <v>10</v>
+      </c>
+      <c r="BC247">
+        <v>10</v>
+      </c>
+      <c r="BD247">
+        <v>2.1</v>
+      </c>
+      <c r="BE247">
+        <v>7.5</v>
+      </c>
+      <c r="BF247">
+        <v>2</v>
+      </c>
+      <c r="BG247">
+        <v>1.39</v>
+      </c>
+      <c r="BH247">
+        <v>2.77</v>
+      </c>
+      <c r="BI247">
+        <v>1.68</v>
+      </c>
+      <c r="BJ247">
+        <v>2.12</v>
+      </c>
+      <c r="BK247">
+        <v>2.11</v>
+      </c>
+      <c r="BL247">
+        <v>1.68</v>
+      </c>
+      <c r="BM247">
+        <v>2.7</v>
+      </c>
+      <c r="BN247">
+        <v>1.41</v>
+      </c>
+      <c r="BO247">
+        <v>3.65</v>
+      </c>
+      <c r="BP247">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="248" spans="1:68">
+      <c r="A248" s="1">
+        <v>247</v>
+      </c>
+      <c r="B248">
+        <v>7469115</v>
+      </c>
+      <c r="C248" t="s">
+        <v>68</v>
+      </c>
+      <c r="D248" t="s">
+        <v>69</v>
+      </c>
+      <c r="E248" s="2">
+        <v>45744.66666666666</v>
+      </c>
+      <c r="F248">
+        <v>28</v>
+      </c>
+      <c r="G248" t="s">
+        <v>83</v>
+      </c>
+      <c r="H248" t="s">
+        <v>72</v>
+      </c>
+      <c r="I248">
+        <v>1</v>
+      </c>
+      <c r="J248">
+        <v>0</v>
+      </c>
+      <c r="K248">
+        <v>1</v>
+      </c>
+      <c r="L248">
+        <v>2</v>
+      </c>
+      <c r="M248">
+        <v>0</v>
+      </c>
+      <c r="N248">
+        <v>2</v>
+      </c>
+      <c r="O248" t="s">
+        <v>249</v>
+      </c>
+      <c r="P248" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q248">
+        <v>3</v>
+      </c>
+      <c r="R248">
+        <v>1.95</v>
+      </c>
+      <c r="S248">
+        <v>4.33</v>
+      </c>
+      <c r="T248">
+        <v>1.57</v>
+      </c>
+      <c r="U248">
+        <v>2.25</v>
+      </c>
+      <c r="V248">
+        <v>3.75</v>
+      </c>
+      <c r="W248">
+        <v>1.25</v>
+      </c>
+      <c r="X248">
+        <v>11</v>
+      </c>
+      <c r="Y248">
+        <v>1.05</v>
+      </c>
+      <c r="Z248">
+        <v>2.19</v>
+      </c>
+      <c r="AA248">
+        <v>3.02</v>
+      </c>
+      <c r="AB248">
+        <v>3.56</v>
+      </c>
+      <c r="AC248">
+        <v>1.1</v>
+      </c>
+      <c r="AD248">
+        <v>6.5</v>
+      </c>
+      <c r="AE248">
+        <v>1.48</v>
+      </c>
+      <c r="AF248">
+        <v>2.6</v>
+      </c>
+      <c r="AG248">
+        <v>2.37</v>
+      </c>
+      <c r="AH248">
+        <v>1.48</v>
+      </c>
+      <c r="AI248">
+        <v>2.1</v>
+      </c>
+      <c r="AJ248">
+        <v>1.67</v>
+      </c>
+      <c r="AK248">
+        <v>1.29</v>
+      </c>
+      <c r="AL248">
+        <v>1.35</v>
+      </c>
+      <c r="AM248">
+        <v>1.65</v>
+      </c>
+      <c r="AN248">
+        <v>1.92</v>
+      </c>
+      <c r="AO248">
+        <v>1.38</v>
+      </c>
+      <c r="AP248">
+        <v>2</v>
+      </c>
+      <c r="AQ248">
+        <v>1.29</v>
+      </c>
+      <c r="AR248">
+        <v>1.81</v>
+      </c>
+      <c r="AS248">
+        <v>1.36</v>
+      </c>
+      <c r="AT248">
+        <v>3.17</v>
+      </c>
+      <c r="AU248">
+        <v>9</v>
+      </c>
+      <c r="AV248">
+        <v>2</v>
+      </c>
+      <c r="AW248">
+        <v>7</v>
+      </c>
+      <c r="AX248">
+        <v>11</v>
+      </c>
+      <c r="AY248">
+        <v>16</v>
+      </c>
+      <c r="AZ248">
+        <v>13</v>
+      </c>
+      <c r="BA248">
+        <v>3</v>
+      </c>
+      <c r="BB248">
+        <v>4</v>
+      </c>
+      <c r="BC248">
+        <v>7</v>
+      </c>
+      <c r="BD248">
+        <v>1.64</v>
+      </c>
+      <c r="BE248">
+        <v>8</v>
+      </c>
+      <c r="BF248">
+        <v>2.67</v>
+      </c>
+      <c r="BG248">
+        <v>1.39</v>
+      </c>
+      <c r="BH248">
+        <v>2.77</v>
+      </c>
+      <c r="BI248">
+        <v>1.68</v>
+      </c>
+      <c r="BJ248">
+        <v>2.12</v>
+      </c>
+      <c r="BK248">
+        <v>2.11</v>
+      </c>
+      <c r="BL248">
+        <v>1.68</v>
+      </c>
+      <c r="BM248">
+        <v>2.7</v>
+      </c>
+      <c r="BN248">
+        <v>1.41</v>
+      </c>
+      <c r="BO248">
+        <v>3.65</v>
+      </c>
+      <c r="BP248">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="249" spans="1:68">
+      <c r="A249" s="1">
+        <v>248</v>
+      </c>
+      <c r="B249">
+        <v>7469111</v>
+      </c>
+      <c r="C249" t="s">
+        <v>68</v>
+      </c>
+      <c r="D249" t="s">
+        <v>69</v>
+      </c>
+      <c r="E249" s="2">
+        <v>45744.66666666666</v>
+      </c>
+      <c r="F249">
+        <v>28</v>
+      </c>
+      <c r="G249" t="s">
+        <v>70</v>
+      </c>
+      <c r="H249" t="s">
+        <v>73</v>
+      </c>
+      <c r="I249">
+        <v>1</v>
+      </c>
+      <c r="J249">
+        <v>0</v>
+      </c>
+      <c r="K249">
+        <v>1</v>
+      </c>
+      <c r="L249">
+        <v>1</v>
+      </c>
+      <c r="M249">
+        <v>1</v>
+      </c>
+      <c r="N249">
+        <v>2</v>
+      </c>
+      <c r="O249" t="s">
+        <v>176</v>
+      </c>
+      <c r="P249" t="s">
+        <v>198</v>
+      </c>
+      <c r="Q249">
+        <v>2.75</v>
+      </c>
+      <c r="R249">
+        <v>2.1</v>
+      </c>
+      <c r="S249">
+        <v>4.33</v>
+      </c>
+      <c r="T249">
+        <v>1.44</v>
+      </c>
+      <c r="U249">
+        <v>2.63</v>
+      </c>
+      <c r="V249">
+        <v>3.25</v>
+      </c>
+      <c r="W249">
+        <v>1.33</v>
+      </c>
+      <c r="X249">
+        <v>9</v>
+      </c>
+      <c r="Y249">
+        <v>1.07</v>
+      </c>
+      <c r="Z249">
+        <v>2.04</v>
+      </c>
+      <c r="AA249">
+        <v>3.28</v>
+      </c>
+      <c r="AB249">
+        <v>3.64</v>
+      </c>
+      <c r="AC249">
+        <v>1.07</v>
+      </c>
+      <c r="AD249">
+        <v>8</v>
+      </c>
+      <c r="AE249">
+        <v>1.36</v>
+      </c>
+      <c r="AF249">
+        <v>3.1</v>
+      </c>
+      <c r="AG249">
+        <v>1.94</v>
+      </c>
+      <c r="AH249">
+        <v>1.8</v>
+      </c>
+      <c r="AI249">
+        <v>1.83</v>
+      </c>
+      <c r="AJ249">
+        <v>1.83</v>
+      </c>
+      <c r="AK249">
+        <v>1.28</v>
+      </c>
+      <c r="AL249">
+        <v>1.31</v>
+      </c>
+      <c r="AM249">
+        <v>1.72</v>
+      </c>
+      <c r="AN249">
+        <v>0.93</v>
+      </c>
+      <c r="AO249">
+        <v>0.54</v>
+      </c>
+      <c r="AP249">
+        <v>0.93</v>
+      </c>
+      <c r="AQ249">
+        <v>0.57</v>
+      </c>
+      <c r="AR249">
+        <v>1.42</v>
+      </c>
+      <c r="AS249">
+        <v>1.16</v>
+      </c>
+      <c r="AT249">
+        <v>2.58</v>
+      </c>
+      <c r="AU249">
+        <v>3</v>
+      </c>
+      <c r="AV249">
+        <v>9</v>
+      </c>
+      <c r="AW249">
+        <v>9</v>
+      </c>
+      <c r="AX249">
+        <v>8</v>
+      </c>
+      <c r="AY249">
+        <v>12</v>
+      </c>
+      <c r="AZ249">
+        <v>17</v>
+      </c>
+      <c r="BA249">
+        <v>5</v>
+      </c>
+      <c r="BB249">
+        <v>9</v>
+      </c>
+      <c r="BC249">
+        <v>14</v>
+      </c>
+      <c r="BD249">
+        <v>1.59</v>
+      </c>
+      <c r="BE249">
+        <v>8</v>
+      </c>
+      <c r="BF249">
+        <v>2.9</v>
+      </c>
+      <c r="BG249">
+        <v>1.28</v>
+      </c>
+      <c r="BH249">
+        <v>3.25</v>
+      </c>
+      <c r="BI249">
+        <v>1.52</v>
+      </c>
+      <c r="BJ249">
+        <v>2.37</v>
+      </c>
+      <c r="BK249">
+        <v>1.87</v>
+      </c>
+      <c r="BL249">
+        <v>1.87</v>
+      </c>
+      <c r="BM249">
+        <v>2.38</v>
+      </c>
+      <c r="BN249">
+        <v>1.54</v>
+      </c>
+      <c r="BO249">
+        <v>3.12</v>
+      </c>
+      <c r="BP249">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="250" spans="1:68">
+      <c r="A250" s="1">
+        <v>249</v>
+      </c>
+      <c r="B250">
+        <v>7469112</v>
+      </c>
+      <c r="C250" t="s">
+        <v>68</v>
+      </c>
+      <c r="D250" t="s">
+        <v>69</v>
+      </c>
+      <c r="E250" s="2">
+        <v>45744.66666666666</v>
+      </c>
+      <c r="F250">
+        <v>28</v>
+      </c>
+      <c r="G250" t="s">
+        <v>78</v>
+      </c>
+      <c r="H250" t="s">
+        <v>79</v>
+      </c>
+      <c r="I250">
+        <v>1</v>
+      </c>
+      <c r="J250">
+        <v>0</v>
+      </c>
+      <c r="K250">
+        <v>1</v>
+      </c>
+      <c r="L250">
+        <v>2</v>
+      </c>
+      <c r="M250">
+        <v>1</v>
+      </c>
+      <c r="N250">
+        <v>3</v>
+      </c>
+      <c r="O250" t="s">
+        <v>250</v>
+      </c>
+      <c r="P250" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q250">
+        <v>2.3</v>
+      </c>
+      <c r="R250">
+        <v>2.1</v>
+      </c>
+      <c r="S250">
+        <v>5.5</v>
+      </c>
+      <c r="T250">
+        <v>1.44</v>
+      </c>
+      <c r="U250">
+        <v>2.63</v>
+      </c>
+      <c r="V250">
+        <v>3.25</v>
+      </c>
+      <c r="W250">
+        <v>1.33</v>
+      </c>
+      <c r="X250">
+        <v>9</v>
+      </c>
+      <c r="Y250">
+        <v>1.07</v>
+      </c>
+      <c r="Z250">
+        <v>1.66</v>
+      </c>
+      <c r="AA250">
+        <v>3.51</v>
+      </c>
+      <c r="AB250">
+        <v>5.4</v>
+      </c>
+      <c r="AC250">
+        <v>1.07</v>
+      </c>
+      <c r="AD250">
+        <v>8</v>
+      </c>
+      <c r="AE250">
+        <v>1.38</v>
+      </c>
+      <c r="AF250">
+        <v>3</v>
+      </c>
+      <c r="AG250">
+        <v>2</v>
+      </c>
+      <c r="AH250">
+        <v>1.67</v>
+      </c>
+      <c r="AI250">
+        <v>2</v>
+      </c>
+      <c r="AJ250">
+        <v>1.73</v>
+      </c>
+      <c r="AK250">
+        <v>1.16</v>
+      </c>
+      <c r="AL250">
+        <v>1.27</v>
+      </c>
+      <c r="AM250">
+        <v>2.1</v>
+      </c>
+      <c r="AN250">
+        <v>2.21</v>
+      </c>
+      <c r="AO250">
+        <v>1.14</v>
+      </c>
+      <c r="AP250">
+        <v>2.27</v>
+      </c>
+      <c r="AQ250">
+        <v>1.07</v>
+      </c>
+      <c r="AR250">
+        <v>1.74</v>
+      </c>
+      <c r="AS250">
+        <v>1.38</v>
+      </c>
+      <c r="AT250">
+        <v>3.12</v>
+      </c>
+      <c r="AU250">
+        <v>4</v>
+      </c>
+      <c r="AV250">
+        <v>5</v>
+      </c>
+      <c r="AW250">
+        <v>6</v>
+      </c>
+      <c r="AX250">
+        <v>6</v>
+      </c>
+      <c r="AY250">
+        <v>10</v>
+      </c>
+      <c r="AZ250">
+        <v>11</v>
+      </c>
+      <c r="BA250">
+        <v>5</v>
+      </c>
+      <c r="BB250">
+        <v>1</v>
+      </c>
+      <c r="BC250">
+        <v>6</v>
+      </c>
+      <c r="BD250">
+        <v>1.64</v>
+      </c>
+      <c r="BE250">
+        <v>8</v>
+      </c>
+      <c r="BF250">
+        <v>2.77</v>
+      </c>
+      <c r="BG250">
+        <v>1.39</v>
+      </c>
+      <c r="BH250">
+        <v>2.77</v>
+      </c>
+      <c r="BI250">
+        <v>1.68</v>
+      </c>
+      <c r="BJ250">
+        <v>2.12</v>
+      </c>
+      <c r="BK250">
+        <v>2.11</v>
+      </c>
+      <c r="BL250">
+        <v>1.68</v>
+      </c>
+      <c r="BM250">
+        <v>2.7</v>
+      </c>
+      <c r="BN250">
+        <v>1.41</v>
+      </c>
+      <c r="BO250">
+        <v>3.65</v>
+      </c>
+      <c r="BP250">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1562" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1574" uniqueCount="345">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -769,6 +769,12 @@
     <t>['42', '82']</t>
   </si>
   <si>
+    <t>['36']</t>
+  </si>
+  <si>
+    <t>['13', '30']</t>
+  </si>
+  <si>
     <t>['16', '45+2']</t>
   </si>
   <si>
@@ -821,9 +827,6 @@
   </si>
   <si>
     <t>['15', '37', '69']</t>
-  </si>
-  <si>
-    <t>['36']</t>
   </si>
   <si>
     <t>['65']</t>
@@ -1043,6 +1046,9 @@
   </si>
   <si>
     <t>['30', '72', '90+11']</t>
+  </si>
+  <si>
+    <t>['8', '17']</t>
   </si>
 </sst>
 </file>
@@ -1404,7 +1410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP250"/>
+  <dimension ref="A1:BP252"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1660,7 +1666,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q2">
         <v>2.4</v>
@@ -2072,7 +2078,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q4">
         <v>3.6</v>
@@ -2562,10 +2568,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ6">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2768,7 +2774,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ7">
         <v>1.07</v>
@@ -2896,7 +2902,7 @@
         <v>90</v>
       </c>
       <c r="P8" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q8">
         <v>3.1</v>
@@ -3183,7 +3189,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ9">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3308,7 +3314,7 @@
         <v>94</v>
       </c>
       <c r="P10" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q10">
         <v>2.6</v>
@@ -3926,7 +3932,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q13">
         <v>3.1</v>
@@ -4544,7 +4550,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q16">
         <v>2.63</v>
@@ -4750,7 +4756,7 @@
         <v>99</v>
       </c>
       <c r="P17" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -5780,7 +5786,7 @@
         <v>103</v>
       </c>
       <c r="P22" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -5858,7 +5864,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ22">
         <v>0.86</v>
@@ -6192,7 +6198,7 @@
         <v>105</v>
       </c>
       <c r="P24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q24">
         <v>2.62</v>
@@ -6682,7 +6688,7 @@
         <v>1</v>
       </c>
       <c r="AP26">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ26">
         <v>0.86</v>
@@ -6891,7 +6897,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ27">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR27">
         <v>1.55</v>
@@ -7016,7 +7022,7 @@
         <v>108</v>
       </c>
       <c r="P28" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q28">
         <v>2.6</v>
@@ -7097,7 +7103,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ28">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR28">
         <v>1.92</v>
@@ -8458,7 +8464,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q35">
         <v>3.3</v>
@@ -8664,7 +8670,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q36">
         <v>3.1</v>
@@ -8870,7 +8876,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q37">
         <v>3.4</v>
@@ -8948,7 +8954,7 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ37">
         <v>0.54</v>
@@ -9076,7 +9082,7 @@
         <v>90</v>
       </c>
       <c r="P38" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q38">
         <v>3.2</v>
@@ -9282,7 +9288,7 @@
         <v>90</v>
       </c>
       <c r="P39" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q39">
         <v>3.4</v>
@@ -9694,7 +9700,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q41">
         <v>2.5</v>
@@ -9772,7 +9778,7 @@
         <v>2</v>
       </c>
       <c r="AP41">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ41">
         <v>1.13</v>
@@ -9900,7 +9906,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q42">
         <v>3.25</v>
@@ -10106,7 +10112,7 @@
         <v>90</v>
       </c>
       <c r="P43" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q43">
         <v>2.75</v>
@@ -10187,7 +10193,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ43">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR43">
         <v>0.8</v>
@@ -10805,7 +10811,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ46">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR46">
         <v>1.88</v>
@@ -11835,7 +11841,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ51">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR51">
         <v>1.48</v>
@@ -12166,7 +12172,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>269</v>
+        <v>251</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -12372,7 +12378,7 @@
         <v>129</v>
       </c>
       <c r="P54" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q54">
         <v>2.55</v>
@@ -12578,7 +12584,7 @@
         <v>130</v>
       </c>
       <c r="P55" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q55">
         <v>2.55</v>
@@ -12659,7 +12665,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ55">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR55">
         <v>1.98</v>
@@ -12990,7 +12996,7 @@
         <v>132</v>
       </c>
       <c r="P57" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -13402,7 +13408,7 @@
         <v>134</v>
       </c>
       <c r="P59" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q59">
         <v>2.62</v>
@@ -13608,7 +13614,7 @@
         <v>135</v>
       </c>
       <c r="P60" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q60">
         <v>2.88</v>
@@ -13892,7 +13898,7 @@
         <v>1.5</v>
       </c>
       <c r="AP61">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ61">
         <v>1</v>
@@ -14020,7 +14026,7 @@
         <v>137</v>
       </c>
       <c r="P62" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q62">
         <v>3.6</v>
@@ -14226,7 +14232,7 @@
         <v>138</v>
       </c>
       <c r="P63" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q63">
         <v>3.75</v>
@@ -14510,7 +14516,7 @@
         <v>0</v>
       </c>
       <c r="AP64">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ64">
         <v>0.54</v>
@@ -14719,7 +14725,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ65">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR65">
         <v>1.6</v>
@@ -15256,7 +15262,7 @@
         <v>143</v>
       </c>
       <c r="P68" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15462,7 +15468,7 @@
         <v>144</v>
       </c>
       <c r="P69" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15668,7 +15674,7 @@
         <v>145</v>
       </c>
       <c r="P70" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q70">
         <v>3.75</v>
@@ -15749,7 +15755,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ70">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR70">
         <v>1.55</v>
@@ -16080,7 +16086,7 @@
         <v>147</v>
       </c>
       <c r="P72" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16286,7 +16292,7 @@
         <v>90</v>
       </c>
       <c r="P73" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q73">
         <v>4.33</v>
@@ -16492,7 +16498,7 @@
         <v>90</v>
       </c>
       <c r="P74" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q74">
         <v>2.4</v>
@@ -16570,7 +16576,7 @@
         <v>0.5</v>
       </c>
       <c r="AP74">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ74">
         <v>0.86</v>
@@ -16698,7 +16704,7 @@
         <v>148</v>
       </c>
       <c r="P75" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q75">
         <v>3.5</v>
@@ -16904,7 +16910,7 @@
         <v>149</v>
       </c>
       <c r="P76" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q76">
         <v>2.88</v>
@@ -17188,7 +17194,7 @@
         <v>2</v>
       </c>
       <c r="AP77">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ77">
         <v>1.69</v>
@@ -17522,7 +17528,7 @@
         <v>151</v>
       </c>
       <c r="P79" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17728,7 +17734,7 @@
         <v>152</v>
       </c>
       <c r="P80" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q80">
         <v>2.05</v>
@@ -17934,7 +17940,7 @@
         <v>90</v>
       </c>
       <c r="P81" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q81">
         <v>4.33</v>
@@ -18633,7 +18639,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ84">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR84">
         <v>1.51</v>
@@ -18758,7 +18764,7 @@
         <v>90</v>
       </c>
       <c r="P85" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q85">
         <v>3.1</v>
@@ -18964,7 +18970,7 @@
         <v>156</v>
       </c>
       <c r="P86" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -19045,7 +19051,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ86">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR86">
         <v>1.88</v>
@@ -19788,7 +19794,7 @@
         <v>90</v>
       </c>
       <c r="P90" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q90">
         <v>2.38</v>
@@ -20200,7 +20206,7 @@
         <v>160</v>
       </c>
       <c r="P92" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20690,7 +20696,7 @@
         <v>1.2</v>
       </c>
       <c r="AP94">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ94">
         <v>1.13</v>
@@ -20818,7 +20824,7 @@
         <v>162</v>
       </c>
       <c r="P95" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q95">
         <v>1.9</v>
@@ -21024,7 +21030,7 @@
         <v>163</v>
       </c>
       <c r="P96" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q96">
         <v>2.75</v>
@@ -21436,7 +21442,7 @@
         <v>90</v>
       </c>
       <c r="P98" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q98">
         <v>4.75</v>
@@ -21720,7 +21726,7 @@
         <v>0.2</v>
       </c>
       <c r="AP99">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ99">
         <v>0.79</v>
@@ -22341,7 +22347,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ102">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR102">
         <v>1.45</v>
@@ -22547,7 +22553,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ103">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR103">
         <v>1.26</v>
@@ -22672,7 +22678,7 @@
         <v>167</v>
       </c>
       <c r="P104" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q104">
         <v>2.25</v>
@@ -23368,7 +23374,7 @@
         <v>0.6</v>
       </c>
       <c r="AP107">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ107">
         <v>0.85</v>
@@ -23496,7 +23502,7 @@
         <v>90</v>
       </c>
       <c r="P108" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q108">
         <v>4.5</v>
@@ -24192,7 +24198,7 @@
         <v>0.8</v>
       </c>
       <c r="AP111">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ111">
         <v>1.29</v>
@@ -24320,7 +24326,7 @@
         <v>173</v>
       </c>
       <c r="P112" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q112">
         <v>3.5</v>
@@ -24732,7 +24738,7 @@
         <v>90</v>
       </c>
       <c r="P114" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q114">
         <v>2.85</v>
@@ -25144,7 +25150,7 @@
         <v>175</v>
       </c>
       <c r="P116" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q116">
         <v>2.4</v>
@@ -25556,7 +25562,7 @@
         <v>90</v>
       </c>
       <c r="P118" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q118">
         <v>4</v>
@@ -25637,7 +25643,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ118">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR118">
         <v>0.99</v>
@@ -26174,7 +26180,7 @@
         <v>178</v>
       </c>
       <c r="P121" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q121">
         <v>2.88</v>
@@ -26458,7 +26464,7 @@
         <v>0.5</v>
       </c>
       <c r="AP122">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ122">
         <v>0.57</v>
@@ -27079,7 +27085,7 @@
         <v>2</v>
       </c>
       <c r="AQ125">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR125">
         <v>1.66</v>
@@ -28852,7 +28858,7 @@
         <v>90</v>
       </c>
       <c r="P134" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q134">
         <v>3.2</v>
@@ -28930,7 +28936,7 @@
         <v>0.43</v>
       </c>
       <c r="AP134">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ134">
         <v>0.57</v>
@@ -29058,7 +29064,7 @@
         <v>90</v>
       </c>
       <c r="P135" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q135">
         <v>5</v>
@@ -30294,7 +30300,7 @@
         <v>189</v>
       </c>
       <c r="P141" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q141">
         <v>2.8</v>
@@ -30375,7 +30381,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ141">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR141">
         <v>1.72</v>
@@ -31118,7 +31124,7 @@
         <v>192</v>
       </c>
       <c r="P145" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q145">
         <v>2.75</v>
@@ -31324,7 +31330,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q146">
         <v>3.75</v>
@@ -31402,7 +31408,7 @@
         <v>1</v>
       </c>
       <c r="AP146">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ146">
         <v>0.86</v>
@@ -31530,7 +31536,7 @@
         <v>129</v>
       </c>
       <c r="P147" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q147">
         <v>3.75</v>
@@ -31736,7 +31742,7 @@
         <v>90</v>
       </c>
       <c r="P148" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q148">
         <v>2.4</v>
@@ -31942,7 +31948,7 @@
         <v>90</v>
       </c>
       <c r="P149" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q149">
         <v>3.1</v>
@@ -32354,7 +32360,7 @@
         <v>194</v>
       </c>
       <c r="P151" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q151">
         <v>1.62</v>
@@ -32766,7 +32772,7 @@
         <v>95</v>
       </c>
       <c r="P153" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q153">
         <v>2.63</v>
@@ -32844,7 +32850,7 @@
         <v>1</v>
       </c>
       <c r="AP153">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ153">
         <v>1.29</v>
@@ -33053,7 +33059,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ154">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR154">
         <v>1.27</v>
@@ -33590,7 +33596,7 @@
         <v>197</v>
       </c>
       <c r="P157" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q157">
         <v>2.7</v>
@@ -33796,7 +33802,7 @@
         <v>96</v>
       </c>
       <c r="P158" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q158">
         <v>2.55</v>
@@ -34002,7 +34008,7 @@
         <v>198</v>
       </c>
       <c r="P159" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q159">
         <v>3.3</v>
@@ -34208,7 +34214,7 @@
         <v>90</v>
       </c>
       <c r="P160" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q160">
         <v>2.75</v>
@@ -35110,7 +35116,7 @@
         <v>1.11</v>
       </c>
       <c r="AP164">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ164">
         <v>1</v>
@@ -35316,7 +35322,7 @@
         <v>1.38</v>
       </c>
       <c r="AP165">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ165">
         <v>1.31</v>
@@ -35650,7 +35656,7 @@
         <v>109</v>
       </c>
       <c r="P167" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q167">
         <v>3.35</v>
@@ -36062,7 +36068,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q169">
         <v>2.8</v>
@@ -36143,7 +36149,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ169">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR169">
         <v>1.32</v>
@@ -36268,7 +36274,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q170">
         <v>3</v>
@@ -36555,7 +36561,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ171">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR171">
         <v>1.68</v>
@@ -36680,7 +36686,7 @@
         <v>90</v>
       </c>
       <c r="P172" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q172">
         <v>2.63</v>
@@ -36886,7 +36892,7 @@
         <v>207</v>
       </c>
       <c r="P173" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q173">
         <v>2.3</v>
@@ -37916,7 +37922,7 @@
         <v>90</v>
       </c>
       <c r="P178" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q178">
         <v>3.25</v>
@@ -38328,7 +38334,7 @@
         <v>212</v>
       </c>
       <c r="P180" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q180">
         <v>2.2</v>
@@ -38534,7 +38540,7 @@
         <v>90</v>
       </c>
       <c r="P181" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q181">
         <v>3.25</v>
@@ -39024,7 +39030,7 @@
         <v>1</v>
       </c>
       <c r="AP183">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ183">
         <v>1</v>
@@ -39439,7 +39445,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ185">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR185">
         <v>1.51</v>
@@ -39770,7 +39776,7 @@
         <v>90</v>
       </c>
       <c r="P187" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q187">
         <v>2.55</v>
@@ -39976,7 +39982,7 @@
         <v>215</v>
       </c>
       <c r="P188" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q188">
         <v>4.5</v>
@@ -40057,7 +40063,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ188">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR188">
         <v>1.26</v>
@@ -40388,7 +40394,7 @@
         <v>90</v>
       </c>
       <c r="P190" t="s">
-        <v>269</v>
+        <v>251</v>
       </c>
       <c r="Q190">
         <v>3.3</v>
@@ -40466,7 +40472,7 @@
         <v>1.7</v>
       </c>
       <c r="AP190">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ190">
         <v>1.64</v>
@@ -40594,7 +40600,7 @@
         <v>90</v>
       </c>
       <c r="P191" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q191">
         <v>2.75</v>
@@ -40800,7 +40806,7 @@
         <v>90</v>
       </c>
       <c r="P192" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q192">
         <v>3.25</v>
@@ -41084,7 +41090,7 @@
         <v>1</v>
       </c>
       <c r="AP193">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ193">
         <v>0.86</v>
@@ -41418,7 +41424,7 @@
         <v>214</v>
       </c>
       <c r="P195" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q195">
         <v>4.75</v>
@@ -41624,7 +41630,7 @@
         <v>90</v>
       </c>
       <c r="P196" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q196">
         <v>3.65</v>
@@ -41830,7 +41836,7 @@
         <v>218</v>
       </c>
       <c r="P197" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q197">
         <v>1.94</v>
@@ -42242,7 +42248,7 @@
         <v>90</v>
       </c>
       <c r="P199" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q199">
         <v>3.75</v>
@@ -42735,7 +42741,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ201">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR201">
         <v>1.74</v>
@@ -43147,7 +43153,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ203">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR203">
         <v>1.24</v>
@@ -43272,7 +43278,7 @@
         <v>160</v>
       </c>
       <c r="P204" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q204">
         <v>3</v>
@@ -43478,7 +43484,7 @@
         <v>90</v>
       </c>
       <c r="P205" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q205">
         <v>2.75</v>
@@ -43890,7 +43896,7 @@
         <v>90</v>
       </c>
       <c r="P207" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q207">
         <v>3.8</v>
@@ -43968,7 +43974,7 @@
         <v>1.3</v>
       </c>
       <c r="AP207">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ207">
         <v>1.69</v>
@@ -45126,7 +45132,7 @@
         <v>226</v>
       </c>
       <c r="P213" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q213">
         <v>3.75</v>
@@ -45204,7 +45210,7 @@
         <v>1.64</v>
       </c>
       <c r="AP213">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ213">
         <v>1.57</v>
@@ -45538,7 +45544,7 @@
         <v>228</v>
       </c>
       <c r="P215" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q215">
         <v>2.95</v>
@@ -45744,7 +45750,7 @@
         <v>90</v>
       </c>
       <c r="P216" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q216">
         <v>1.96</v>
@@ -45825,7 +45831,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ216">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR216">
         <v>1.78</v>
@@ -46362,7 +46368,7 @@
         <v>229</v>
       </c>
       <c r="P219" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q219">
         <v>4.3</v>
@@ -46980,7 +46986,7 @@
         <v>90</v>
       </c>
       <c r="P222" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q222">
         <v>2.7</v>
@@ -47186,7 +47192,7 @@
         <v>231</v>
       </c>
       <c r="P223" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q223">
         <v>3.65</v>
@@ -47392,7 +47398,7 @@
         <v>232</v>
       </c>
       <c r="P224" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q224">
         <v>5.2</v>
@@ -47804,7 +47810,7 @@
         <v>221</v>
       </c>
       <c r="P226" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q226">
         <v>4.4</v>
@@ -48010,7 +48016,7 @@
         <v>234</v>
       </c>
       <c r="P227" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q227">
         <v>2.7</v>
@@ -48088,7 +48094,7 @@
         <v>0.83</v>
       </c>
       <c r="AP227">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ227">
         <v>0.79</v>
@@ -48628,7 +48634,7 @@
         <v>90</v>
       </c>
       <c r="P230" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q230">
         <v>3.04</v>
@@ -48915,7 +48921,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ231">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR231">
         <v>1.26</v>
@@ -49118,7 +49124,7 @@
         <v>1.08</v>
       </c>
       <c r="AP232">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ232">
         <v>1</v>
@@ -49246,7 +49252,7 @@
         <v>238</v>
       </c>
       <c r="P233" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q233">
         <v>3.1</v>
@@ -49327,7 +49333,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ233">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR233">
         <v>1.74</v>
@@ -49452,7 +49458,7 @@
         <v>239</v>
       </c>
       <c r="P234" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q234">
         <v>1.85</v>
@@ -49864,7 +49870,7 @@
         <v>241</v>
       </c>
       <c r="P236" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q236">
         <v>3.7</v>
@@ -50482,7 +50488,7 @@
         <v>243</v>
       </c>
       <c r="P239" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q239">
         <v>3.1</v>
@@ -51100,7 +51106,7 @@
         <v>245</v>
       </c>
       <c r="P242" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q242">
         <v>3.6</v>
@@ -51924,7 +51930,7 @@
         <v>114</v>
       </c>
       <c r="P246" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q246">
         <v>3.6</v>
@@ -52905,6 +52911,418 @@
       </c>
       <c r="BP250">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="251" spans="1:68">
+      <c r="A251" s="1">
+        <v>250</v>
+      </c>
+      <c r="B251">
+        <v>7469109</v>
+      </c>
+      <c r="C251" t="s">
+        <v>68</v>
+      </c>
+      <c r="D251" t="s">
+        <v>69</v>
+      </c>
+      <c r="E251" s="2">
+        <v>45745.41666666666</v>
+      </c>
+      <c r="F251">
+        <v>28</v>
+      </c>
+      <c r="G251" t="s">
+        <v>74</v>
+      </c>
+      <c r="H251" t="s">
+        <v>86</v>
+      </c>
+      <c r="I251">
+        <v>1</v>
+      </c>
+      <c r="J251">
+        <v>2</v>
+      </c>
+      <c r="K251">
+        <v>3</v>
+      </c>
+      <c r="L251">
+        <v>1</v>
+      </c>
+      <c r="M251">
+        <v>2</v>
+      </c>
+      <c r="N251">
+        <v>3</v>
+      </c>
+      <c r="O251" t="s">
+        <v>251</v>
+      </c>
+      <c r="P251" t="s">
+        <v>344</v>
+      </c>
+      <c r="Q251">
+        <v>4.75</v>
+      </c>
+      <c r="R251">
+        <v>2.1</v>
+      </c>
+      <c r="S251">
+        <v>2.5</v>
+      </c>
+      <c r="T251">
+        <v>1.44</v>
+      </c>
+      <c r="U251">
+        <v>2.63</v>
+      </c>
+      <c r="V251">
+        <v>3</v>
+      </c>
+      <c r="W251">
+        <v>1.36</v>
+      </c>
+      <c r="X251">
+        <v>9</v>
+      </c>
+      <c r="Y251">
+        <v>1.07</v>
+      </c>
+      <c r="Z251">
+        <v>4.2</v>
+      </c>
+      <c r="AA251">
+        <v>3.61</v>
+      </c>
+      <c r="AB251">
+        <v>1.81</v>
+      </c>
+      <c r="AC251">
+        <v>1.06</v>
+      </c>
+      <c r="AD251">
+        <v>8.5</v>
+      </c>
+      <c r="AE251">
+        <v>1.33</v>
+      </c>
+      <c r="AF251">
+        <v>3.25</v>
+      </c>
+      <c r="AG251">
+        <v>1.94</v>
+      </c>
+      <c r="AH251">
+        <v>1.8</v>
+      </c>
+      <c r="AI251">
+        <v>1.83</v>
+      </c>
+      <c r="AJ251">
+        <v>1.83</v>
+      </c>
+      <c r="AK251">
+        <v>1.85</v>
+      </c>
+      <c r="AL251">
+        <v>1.25</v>
+      </c>
+      <c r="AM251">
+        <v>1.22</v>
+      </c>
+      <c r="AN251">
+        <v>1.86</v>
+      </c>
+      <c r="AO251">
+        <v>1.38</v>
+      </c>
+      <c r="AP251">
+        <v>1.73</v>
+      </c>
+      <c r="AQ251">
+        <v>1.5</v>
+      </c>
+      <c r="AR251">
+        <v>1.3</v>
+      </c>
+      <c r="AS251">
+        <v>1.57</v>
+      </c>
+      <c r="AT251">
+        <v>2.87</v>
+      </c>
+      <c r="AU251">
+        <v>2</v>
+      </c>
+      <c r="AV251">
+        <v>6</v>
+      </c>
+      <c r="AW251">
+        <v>2</v>
+      </c>
+      <c r="AX251">
+        <v>15</v>
+      </c>
+      <c r="AY251">
+        <v>4</v>
+      </c>
+      <c r="AZ251">
+        <v>21</v>
+      </c>
+      <c r="BA251">
+        <v>2</v>
+      </c>
+      <c r="BB251">
+        <v>5</v>
+      </c>
+      <c r="BC251">
+        <v>7</v>
+      </c>
+      <c r="BD251">
+        <v>3.16</v>
+      </c>
+      <c r="BE251">
+        <v>8.5</v>
+      </c>
+      <c r="BF251">
+        <v>1.51</v>
+      </c>
+      <c r="BG251">
+        <v>1.31</v>
+      </c>
+      <c r="BH251">
+        <v>3.15</v>
+      </c>
+      <c r="BI251">
+        <v>1.56</v>
+      </c>
+      <c r="BJ251">
+        <v>2.33</v>
+      </c>
+      <c r="BK251">
+        <v>1.93</v>
+      </c>
+      <c r="BL251">
+        <v>1.82</v>
+      </c>
+      <c r="BM251">
+        <v>2.43</v>
+      </c>
+      <c r="BN251">
+        <v>1.49</v>
+      </c>
+      <c r="BO251">
+        <v>3.22</v>
+      </c>
+      <c r="BP251">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="252" spans="1:68">
+      <c r="A252" s="1">
+        <v>251</v>
+      </c>
+      <c r="B252">
+        <v>7469117</v>
+      </c>
+      <c r="C252" t="s">
+        <v>68</v>
+      </c>
+      <c r="D252" t="s">
+        <v>69</v>
+      </c>
+      <c r="E252" s="2">
+        <v>45745.66666666666</v>
+      </c>
+      <c r="F252">
+        <v>28</v>
+      </c>
+      <c r="G252" t="s">
+        <v>75</v>
+      </c>
+      <c r="H252" t="s">
+        <v>80</v>
+      </c>
+      <c r="I252">
+        <v>2</v>
+      </c>
+      <c r="J252">
+        <v>0</v>
+      </c>
+      <c r="K252">
+        <v>2</v>
+      </c>
+      <c r="L252">
+        <v>2</v>
+      </c>
+      <c r="M252">
+        <v>0</v>
+      </c>
+      <c r="N252">
+        <v>2</v>
+      </c>
+      <c r="O252" t="s">
+        <v>252</v>
+      </c>
+      <c r="P252" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q252">
+        <v>2.4</v>
+      </c>
+      <c r="R252">
+        <v>2.1</v>
+      </c>
+      <c r="S252">
+        <v>5.5</v>
+      </c>
+      <c r="T252">
+        <v>1.44</v>
+      </c>
+      <c r="U252">
+        <v>2.63</v>
+      </c>
+      <c r="V252">
+        <v>3.25</v>
+      </c>
+      <c r="W252">
+        <v>1.33</v>
+      </c>
+      <c r="X252">
+        <v>10</v>
+      </c>
+      <c r="Y252">
+        <v>1.06</v>
+      </c>
+      <c r="Z252">
+        <v>1.73</v>
+      </c>
+      <c r="AA252">
+        <v>3.53</v>
+      </c>
+      <c r="AB252">
+        <v>4.8</v>
+      </c>
+      <c r="AC252">
+        <v>1.07</v>
+      </c>
+      <c r="AD252">
+        <v>8</v>
+      </c>
+      <c r="AE252">
+        <v>1.38</v>
+      </c>
+      <c r="AF252">
+        <v>3</v>
+      </c>
+      <c r="AG252">
+        <v>2.05</v>
+      </c>
+      <c r="AH252">
+        <v>1.65</v>
+      </c>
+      <c r="AI252">
+        <v>2</v>
+      </c>
+      <c r="AJ252">
+        <v>1.73</v>
+      </c>
+      <c r="AK252">
+        <v>1.2</v>
+      </c>
+      <c r="AL252">
+        <v>1.25</v>
+      </c>
+      <c r="AM252">
+        <v>1.95</v>
+      </c>
+      <c r="AN252">
+        <v>1.77</v>
+      </c>
+      <c r="AO252">
+        <v>1.57</v>
+      </c>
+      <c r="AP252">
+        <v>1.86</v>
+      </c>
+      <c r="AQ252">
+        <v>1.47</v>
+      </c>
+      <c r="AR252">
+        <v>1.66</v>
+      </c>
+      <c r="AS252">
+        <v>1.1</v>
+      </c>
+      <c r="AT252">
+        <v>2.76</v>
+      </c>
+      <c r="AU252">
+        <v>8</v>
+      </c>
+      <c r="AV252">
+        <v>4</v>
+      </c>
+      <c r="AW252">
+        <v>9</v>
+      </c>
+      <c r="AX252">
+        <v>3</v>
+      </c>
+      <c r="AY252">
+        <v>17</v>
+      </c>
+      <c r="AZ252">
+        <v>7</v>
+      </c>
+      <c r="BA252">
+        <v>8</v>
+      </c>
+      <c r="BB252">
+        <v>3</v>
+      </c>
+      <c r="BC252">
+        <v>11</v>
+      </c>
+      <c r="BD252">
+        <v>1.55</v>
+      </c>
+      <c r="BE252">
+        <v>8.5</v>
+      </c>
+      <c r="BF252">
+        <v>3.01</v>
+      </c>
+      <c r="BG252">
+        <v>1.28</v>
+      </c>
+      <c r="BH252">
+        <v>3.25</v>
+      </c>
+      <c r="BI252">
+        <v>1.52</v>
+      </c>
+      <c r="BJ252">
+        <v>2.37</v>
+      </c>
+      <c r="BK252">
+        <v>1.87</v>
+      </c>
+      <c r="BL252">
+        <v>1.87</v>
+      </c>
+      <c r="BM252">
+        <v>2.38</v>
+      </c>
+      <c r="BN252">
+        <v>1.54</v>
+      </c>
+      <c r="BO252">
+        <v>3.12</v>
+      </c>
+      <c r="BP252">
+        <v>1.31</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1574" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1580" uniqueCount="347">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -775,6 +775,9 @@
     <t>['13', '30']</t>
   </si>
   <si>
+    <t>['13', '32', '44', '60']</t>
+  </si>
+  <si>
     <t>['16', '45+2']</t>
   </si>
   <si>
@@ -1049,6 +1052,9 @@
   </si>
   <si>
     <t>['8', '17']</t>
+  </si>
+  <si>
+    <t>['82', '90+1']</t>
   </si>
 </sst>
 </file>
@@ -1410,7 +1416,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP252"/>
+  <dimension ref="A1:BP253"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1666,7 +1672,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q2">
         <v>2.4</v>
@@ -2078,7 +2084,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q4">
         <v>3.6</v>
@@ -2902,7 +2908,7 @@
         <v>90</v>
       </c>
       <c r="P8" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q8">
         <v>3.1</v>
@@ -3314,7 +3320,7 @@
         <v>94</v>
       </c>
       <c r="P10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q10">
         <v>2.6</v>
@@ -3932,7 +3938,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q13">
         <v>3.1</v>
@@ -4219,7 +4225,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ14">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4550,7 +4556,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q16">
         <v>2.63</v>
@@ -4756,7 +4762,7 @@
         <v>99</v>
       </c>
       <c r="P17" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -4834,7 +4840,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ17">
         <v>1.29</v>
@@ -5786,7 +5792,7 @@
         <v>103</v>
       </c>
       <c r="P22" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -6198,7 +6204,7 @@
         <v>105</v>
       </c>
       <c r="P24" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q24">
         <v>2.62</v>
@@ -7022,7 +7028,7 @@
         <v>108</v>
       </c>
       <c r="P28" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q28">
         <v>2.6</v>
@@ -8464,7 +8470,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q35">
         <v>3.3</v>
@@ -8670,7 +8676,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q36">
         <v>3.1</v>
@@ -8748,7 +8754,7 @@
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ36">
         <v>1.69</v>
@@ -8876,7 +8882,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q37">
         <v>3.4</v>
@@ -8957,7 +8963,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ37">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR37">
         <v>1.13</v>
@@ -9082,7 +9088,7 @@
         <v>90</v>
       </c>
       <c r="P38" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q38">
         <v>3.2</v>
@@ -9288,7 +9294,7 @@
         <v>90</v>
       </c>
       <c r="P39" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q39">
         <v>3.4</v>
@@ -9700,7 +9706,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q41">
         <v>2.5</v>
@@ -9906,7 +9912,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q42">
         <v>3.25</v>
@@ -10112,7 +10118,7 @@
         <v>90</v>
       </c>
       <c r="P43" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q43">
         <v>2.75</v>
@@ -11632,7 +11638,7 @@
         <v>3</v>
       </c>
       <c r="AP50">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ50">
         <v>1.57</v>
@@ -12378,7 +12384,7 @@
         <v>129</v>
       </c>
       <c r="P54" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q54">
         <v>2.55</v>
@@ -12584,7 +12590,7 @@
         <v>130</v>
       </c>
       <c r="P55" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q55">
         <v>2.55</v>
@@ -12996,7 +13002,7 @@
         <v>132</v>
       </c>
       <c r="P57" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -13408,7 +13414,7 @@
         <v>134</v>
       </c>
       <c r="P59" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q59">
         <v>2.62</v>
@@ -13614,7 +13620,7 @@
         <v>135</v>
       </c>
       <c r="P60" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q60">
         <v>2.88</v>
@@ -14026,7 +14032,7 @@
         <v>137</v>
       </c>
       <c r="P62" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q62">
         <v>3.6</v>
@@ -14232,7 +14238,7 @@
         <v>138</v>
       </c>
       <c r="P63" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q63">
         <v>3.75</v>
@@ -14519,7 +14525,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ64">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR64">
         <v>1.73</v>
@@ -14722,7 +14728,7 @@
         <v>1.75</v>
       </c>
       <c r="AP65">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ65">
         <v>1.47</v>
@@ -15262,7 +15268,7 @@
         <v>143</v>
       </c>
       <c r="P68" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15468,7 +15474,7 @@
         <v>144</v>
       </c>
       <c r="P69" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15674,7 +15680,7 @@
         <v>145</v>
       </c>
       <c r="P70" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q70">
         <v>3.75</v>
@@ -16086,7 +16092,7 @@
         <v>147</v>
       </c>
       <c r="P72" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16292,7 +16298,7 @@
         <v>90</v>
       </c>
       <c r="P73" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q73">
         <v>4.33</v>
@@ -16498,7 +16504,7 @@
         <v>90</v>
       </c>
       <c r="P74" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q74">
         <v>2.4</v>
@@ -16704,7 +16710,7 @@
         <v>148</v>
       </c>
       <c r="P75" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q75">
         <v>3.5</v>
@@ -16785,7 +16791,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ75">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR75">
         <v>1.25</v>
@@ -16910,7 +16916,7 @@
         <v>149</v>
       </c>
       <c r="P76" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q76">
         <v>2.88</v>
@@ -17528,7 +17534,7 @@
         <v>151</v>
       </c>
       <c r="P79" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17734,7 +17740,7 @@
         <v>152</v>
       </c>
       <c r="P80" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q80">
         <v>2.05</v>
@@ -17940,7 +17946,7 @@
         <v>90</v>
       </c>
       <c r="P81" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q81">
         <v>4.33</v>
@@ -18764,7 +18770,7 @@
         <v>90</v>
       </c>
       <c r="P85" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q85">
         <v>3.1</v>
@@ -18970,7 +18976,7 @@
         <v>156</v>
       </c>
       <c r="P86" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -19666,7 +19672,7 @@
         <v>0.75</v>
       </c>
       <c r="AP89">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ89">
         <v>0.85</v>
@@ -19794,7 +19800,7 @@
         <v>90</v>
       </c>
       <c r="P90" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q90">
         <v>2.38</v>
@@ -20206,7 +20212,7 @@
         <v>160</v>
       </c>
       <c r="P92" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20824,7 +20830,7 @@
         <v>162</v>
       </c>
       <c r="P95" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q95">
         <v>1.9</v>
@@ -21030,7 +21036,7 @@
         <v>163</v>
       </c>
       <c r="P96" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q96">
         <v>2.75</v>
@@ -21442,7 +21448,7 @@
         <v>90</v>
       </c>
       <c r="P98" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q98">
         <v>4.75</v>
@@ -21523,7 +21529,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ98">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR98">
         <v>1.06</v>
@@ -22678,7 +22684,7 @@
         <v>167</v>
       </c>
       <c r="P104" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q104">
         <v>2.25</v>
@@ -22756,7 +22762,7 @@
         <v>1.17</v>
       </c>
       <c r="AP104">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ104">
         <v>1</v>
@@ -23502,7 +23508,7 @@
         <v>90</v>
       </c>
       <c r="P108" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q108">
         <v>4.5</v>
@@ -24326,7 +24332,7 @@
         <v>173</v>
       </c>
       <c r="P112" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q112">
         <v>3.5</v>
@@ -24738,7 +24744,7 @@
         <v>90</v>
       </c>
       <c r="P114" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q114">
         <v>2.85</v>
@@ -25150,7 +25156,7 @@
         <v>175</v>
       </c>
       <c r="P116" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q116">
         <v>2.4</v>
@@ -25437,7 +25443,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ117">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR117">
         <v>1.7</v>
@@ -25562,7 +25568,7 @@
         <v>90</v>
       </c>
       <c r="P118" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q118">
         <v>4</v>
@@ -26180,7 +26186,7 @@
         <v>178</v>
       </c>
       <c r="P121" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q121">
         <v>2.88</v>
@@ -26876,7 +26882,7 @@
         <v>1</v>
       </c>
       <c r="AP124">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ124">
         <v>1.13</v>
@@ -28733,7 +28739,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ133">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR133">
         <v>1.34</v>
@@ -28858,7 +28864,7 @@
         <v>90</v>
       </c>
       <c r="P134" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q134">
         <v>3.2</v>
@@ -29064,7 +29070,7 @@
         <v>90</v>
       </c>
       <c r="P135" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q135">
         <v>5</v>
@@ -30300,7 +30306,7 @@
         <v>189</v>
       </c>
       <c r="P141" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q141">
         <v>2.8</v>
@@ -31124,7 +31130,7 @@
         <v>192</v>
       </c>
       <c r="P145" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q145">
         <v>2.75</v>
@@ -31205,7 +31211,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ145">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR145">
         <v>1.62</v>
@@ -31330,7 +31336,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q146">
         <v>3.75</v>
@@ -31536,7 +31542,7 @@
         <v>129</v>
       </c>
       <c r="P147" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q147">
         <v>3.75</v>
@@ -31742,7 +31748,7 @@
         <v>90</v>
       </c>
       <c r="P148" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q148">
         <v>2.4</v>
@@ -31948,7 +31954,7 @@
         <v>90</v>
       </c>
       <c r="P149" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q149">
         <v>3.1</v>
@@ -32360,7 +32366,7 @@
         <v>194</v>
       </c>
       <c r="P151" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q151">
         <v>1.62</v>
@@ -32438,7 +32444,7 @@
         <v>1.14</v>
       </c>
       <c r="AP151">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ151">
         <v>1.31</v>
@@ -32772,7 +32778,7 @@
         <v>95</v>
       </c>
       <c r="P153" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q153">
         <v>2.63</v>
@@ -33596,7 +33602,7 @@
         <v>197</v>
       </c>
       <c r="P157" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q157">
         <v>2.7</v>
@@ -33802,7 +33808,7 @@
         <v>96</v>
       </c>
       <c r="P158" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q158">
         <v>2.55</v>
@@ -34008,7 +34014,7 @@
         <v>198</v>
       </c>
       <c r="P159" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q159">
         <v>3.3</v>
@@ -34214,7 +34220,7 @@
         <v>90</v>
       </c>
       <c r="P160" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q160">
         <v>2.75</v>
@@ -34498,7 +34504,7 @@
         <v>0.75</v>
       </c>
       <c r="AP161">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ161">
         <v>0.57</v>
@@ -35656,7 +35662,7 @@
         <v>109</v>
       </c>
       <c r="P167" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q167">
         <v>3.35</v>
@@ -35943,7 +35949,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ168">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR168">
         <v>1.22</v>
@@ -36068,7 +36074,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q169">
         <v>2.8</v>
@@ -36274,7 +36280,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q170">
         <v>3</v>
@@ -36686,7 +36692,7 @@
         <v>90</v>
       </c>
       <c r="P172" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q172">
         <v>2.63</v>
@@ -36892,7 +36898,7 @@
         <v>207</v>
       </c>
       <c r="P173" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q173">
         <v>2.3</v>
@@ -37922,7 +37928,7 @@
         <v>90</v>
       </c>
       <c r="P178" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q178">
         <v>3.25</v>
@@ -38206,7 +38212,7 @@
         <v>1.1</v>
       </c>
       <c r="AP179">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ179">
         <v>0.86</v>
@@ -38334,7 +38340,7 @@
         <v>212</v>
       </c>
       <c r="P180" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q180">
         <v>2.2</v>
@@ -38540,7 +38546,7 @@
         <v>90</v>
       </c>
       <c r="P181" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q181">
         <v>3.25</v>
@@ -39776,7 +39782,7 @@
         <v>90</v>
       </c>
       <c r="P187" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q187">
         <v>2.55</v>
@@ -39982,7 +39988,7 @@
         <v>215</v>
       </c>
       <c r="P188" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q188">
         <v>4.5</v>
@@ -40269,7 +40275,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ189">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR189">
         <v>1.73</v>
@@ -40600,7 +40606,7 @@
         <v>90</v>
       </c>
       <c r="P191" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q191">
         <v>2.75</v>
@@ -40806,7 +40812,7 @@
         <v>90</v>
       </c>
       <c r="P192" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q192">
         <v>3.25</v>
@@ -41296,7 +41302,7 @@
         <v>0.91</v>
       </c>
       <c r="AP194">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ194">
         <v>0.86</v>
@@ -41424,7 +41430,7 @@
         <v>214</v>
       </c>
       <c r="P195" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q195">
         <v>4.75</v>
@@ -41630,7 +41636,7 @@
         <v>90</v>
       </c>
       <c r="P196" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q196">
         <v>3.65</v>
@@ -41836,7 +41842,7 @@
         <v>218</v>
       </c>
       <c r="P197" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q197">
         <v>1.94</v>
@@ -42248,7 +42254,7 @@
         <v>90</v>
       </c>
       <c r="P199" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q199">
         <v>3.75</v>
@@ -43278,7 +43284,7 @@
         <v>160</v>
       </c>
       <c r="P204" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q204">
         <v>3</v>
@@ -43484,7 +43490,7 @@
         <v>90</v>
       </c>
       <c r="P205" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q205">
         <v>2.75</v>
@@ -43896,7 +43902,7 @@
         <v>90</v>
       </c>
       <c r="P207" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q207">
         <v>3.8</v>
@@ -44183,7 +44189,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ208">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR208">
         <v>1.37</v>
@@ -44798,7 +44804,7 @@
         <v>1.08</v>
       </c>
       <c r="AP211">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ211">
         <v>1.07</v>
@@ -45132,7 +45138,7 @@
         <v>226</v>
       </c>
       <c r="P213" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q213">
         <v>3.75</v>
@@ -45544,7 +45550,7 @@
         <v>228</v>
       </c>
       <c r="P215" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q215">
         <v>2.95</v>
@@ -45750,7 +45756,7 @@
         <v>90</v>
       </c>
       <c r="P216" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q216">
         <v>1.96</v>
@@ -46368,7 +46374,7 @@
         <v>229</v>
       </c>
       <c r="P219" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q219">
         <v>4.3</v>
@@ -46986,7 +46992,7 @@
         <v>90</v>
       </c>
       <c r="P222" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q222">
         <v>2.7</v>
@@ -47067,7 +47073,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ222">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR222">
         <v>1.41</v>
@@ -47192,7 +47198,7 @@
         <v>231</v>
       </c>
       <c r="P223" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q223">
         <v>3.65</v>
@@ -47398,7 +47404,7 @@
         <v>232</v>
       </c>
       <c r="P224" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q224">
         <v>5.2</v>
@@ -47810,7 +47816,7 @@
         <v>221</v>
       </c>
       <c r="P226" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q226">
         <v>4.4</v>
@@ -48016,7 +48022,7 @@
         <v>234</v>
       </c>
       <c r="P227" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q227">
         <v>2.7</v>
@@ -48634,7 +48640,7 @@
         <v>90</v>
       </c>
       <c r="P230" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q230">
         <v>3.04</v>
@@ -49252,7 +49258,7 @@
         <v>238</v>
       </c>
       <c r="P233" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q233">
         <v>3.1</v>
@@ -49330,7 +49336,7 @@
         <v>1.5</v>
       </c>
       <c r="AP233">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ233">
         <v>1.5</v>
@@ -49458,7 +49464,7 @@
         <v>239</v>
       </c>
       <c r="P234" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q234">
         <v>1.85</v>
@@ -49870,7 +49876,7 @@
         <v>241</v>
       </c>
       <c r="P236" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q236">
         <v>3.7</v>
@@ -50488,7 +50494,7 @@
         <v>243</v>
       </c>
       <c r="P239" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q239">
         <v>3.1</v>
@@ -50775,7 +50781,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ240">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR240">
         <v>1.63</v>
@@ -51106,7 +51112,7 @@
         <v>245</v>
       </c>
       <c r="P242" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q242">
         <v>3.6</v>
@@ -51930,7 +51936,7 @@
         <v>114</v>
       </c>
       <c r="P246" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q246">
         <v>3.6</v>
@@ -52960,7 +52966,7 @@
         <v>251</v>
       </c>
       <c r="P251" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q251">
         <v>4.75</v>
@@ -53323,6 +53329,212 @@
       </c>
       <c r="BP252">
         <v>1.31</v>
+      </c>
+    </row>
+    <row r="253" spans="1:68">
+      <c r="A253" s="1">
+        <v>252</v>
+      </c>
+      <c r="B253">
+        <v>7469110</v>
+      </c>
+      <c r="C253" t="s">
+        <v>68</v>
+      </c>
+      <c r="D253" t="s">
+        <v>69</v>
+      </c>
+      <c r="E253" s="2">
+        <v>45747.65625</v>
+      </c>
+      <c r="F253">
+        <v>28</v>
+      </c>
+      <c r="G253" t="s">
+        <v>85</v>
+      </c>
+      <c r="H253" t="s">
+        <v>76</v>
+      </c>
+      <c r="I253">
+        <v>3</v>
+      </c>
+      <c r="J253">
+        <v>0</v>
+      </c>
+      <c r="K253">
+        <v>3</v>
+      </c>
+      <c r="L253">
+        <v>4</v>
+      </c>
+      <c r="M253">
+        <v>2</v>
+      </c>
+      <c r="N253">
+        <v>6</v>
+      </c>
+      <c r="O253" t="s">
+        <v>253</v>
+      </c>
+      <c r="P253" t="s">
+        <v>346</v>
+      </c>
+      <c r="Q253">
+        <v>2.2</v>
+      </c>
+      <c r="R253">
+        <v>2.25</v>
+      </c>
+      <c r="S253">
+        <v>5.5</v>
+      </c>
+      <c r="T253">
+        <v>1.4</v>
+      </c>
+      <c r="U253">
+        <v>2.75</v>
+      </c>
+      <c r="V253">
+        <v>2.75</v>
+      </c>
+      <c r="W253">
+        <v>1.4</v>
+      </c>
+      <c r="X253">
+        <v>8</v>
+      </c>
+      <c r="Y253">
+        <v>1.08</v>
+      </c>
+      <c r="Z253">
+        <v>1.67</v>
+      </c>
+      <c r="AA253">
+        <v>3.77</v>
+      </c>
+      <c r="AB253">
+        <v>4.8</v>
+      </c>
+      <c r="AC253">
+        <v>1.05</v>
+      </c>
+      <c r="AD253">
+        <v>9.5</v>
+      </c>
+      <c r="AE253">
+        <v>1.28</v>
+      </c>
+      <c r="AF253">
+        <v>3.55</v>
+      </c>
+      <c r="AG253">
+        <v>1.87</v>
+      </c>
+      <c r="AH253">
+        <v>1.87</v>
+      </c>
+      <c r="AI253">
+        <v>1.83</v>
+      </c>
+      <c r="AJ253">
+        <v>1.83</v>
+      </c>
+      <c r="AK253">
+        <v>1.15</v>
+      </c>
+      <c r="AL253">
+        <v>1.2</v>
+      </c>
+      <c r="AM253">
+        <v>2.25</v>
+      </c>
+      <c r="AN253">
+        <v>2.23</v>
+      </c>
+      <c r="AO253">
+        <v>0.54</v>
+      </c>
+      <c r="AP253">
+        <v>2.29</v>
+      </c>
+      <c r="AQ253">
+        <v>0.5</v>
+      </c>
+      <c r="AR253">
+        <v>1.71</v>
+      </c>
+      <c r="AS253">
+        <v>1.33</v>
+      </c>
+      <c r="AT253">
+        <v>3.04</v>
+      </c>
+      <c r="AU253">
+        <v>7</v>
+      </c>
+      <c r="AV253">
+        <v>6</v>
+      </c>
+      <c r="AW253">
+        <v>10</v>
+      </c>
+      <c r="AX253">
+        <v>12</v>
+      </c>
+      <c r="AY253">
+        <v>17</v>
+      </c>
+      <c r="AZ253">
+        <v>18</v>
+      </c>
+      <c r="BA253">
+        <v>2</v>
+      </c>
+      <c r="BB253">
+        <v>3</v>
+      </c>
+      <c r="BC253">
+        <v>5</v>
+      </c>
+      <c r="BD253">
+        <v>1.46</v>
+      </c>
+      <c r="BE253">
+        <v>6.75</v>
+      </c>
+      <c r="BF253">
+        <v>3.05</v>
+      </c>
+      <c r="BG253">
+        <v>1.36</v>
+      </c>
+      <c r="BH253">
+        <v>2.8</v>
+      </c>
+      <c r="BI253">
+        <v>1.61</v>
+      </c>
+      <c r="BJ253">
+        <v>2.15</v>
+      </c>
+      <c r="BK253">
+        <v>1.98</v>
+      </c>
+      <c r="BL253">
+        <v>1.72</v>
+      </c>
+      <c r="BM253">
+        <v>2.55</v>
+      </c>
+      <c r="BN253">
+        <v>1.45</v>
+      </c>
+      <c r="BO253">
+        <v>3.3</v>
+      </c>
+      <c r="BP253">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1580" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1610" uniqueCount="350">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -778,6 +778,12 @@
     <t>['13', '32', '44', '60']</t>
   </si>
   <si>
+    <t>['23', '78']</t>
+  </si>
+  <si>
+    <t>['8', '51']</t>
+  </si>
+  <si>
     <t>['16', '45+2']</t>
   </si>
   <si>
@@ -1055,6 +1061,9 @@
   </si>
   <si>
     <t>['82', '90+1']</t>
+  </si>
+  <si>
+    <t>['40', '45+1']</t>
   </si>
 </sst>
 </file>
@@ -1416,7 +1425,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP253"/>
+  <dimension ref="A1:BP258"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1672,7 +1681,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q2">
         <v>2.4</v>
@@ -1956,7 +1965,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ3">
         <v>1</v>
@@ -2084,7 +2093,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q4">
         <v>3.6</v>
@@ -2908,7 +2917,7 @@
         <v>90</v>
       </c>
       <c r="P8" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q8">
         <v>3.1</v>
@@ -3320,7 +3329,7 @@
         <v>94</v>
       </c>
       <c r="P10" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q10">
         <v>2.6</v>
@@ -3401,7 +3410,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ10">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3607,7 +3616,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ11">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3810,7 +3819,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ12">
         <v>1.57</v>
@@ -3938,7 +3947,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q13">
         <v>3.1</v>
@@ -4016,7 +4025,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ13">
         <v>1.69</v>
@@ -4431,7 +4440,7 @@
         <v>2</v>
       </c>
       <c r="AQ15">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4556,7 +4565,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q16">
         <v>2.63</v>
@@ -4634,10 +4643,10 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ16">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4762,7 +4771,7 @@
         <v>99</v>
       </c>
       <c r="P17" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -4840,7 +4849,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ17">
         <v>1.29</v>
@@ -5049,7 +5058,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ18">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5458,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ20">
         <v>1.07</v>
@@ -5792,7 +5801,7 @@
         <v>103</v>
       </c>
       <c r="P22" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -6204,7 +6213,7 @@
         <v>105</v>
       </c>
       <c r="P24" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q24">
         <v>2.62</v>
@@ -6491,7 +6500,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ25">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR25">
         <v>0.67</v>
@@ -7028,7 +7037,7 @@
         <v>108</v>
       </c>
       <c r="P28" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q28">
         <v>2.6</v>
@@ -7312,7 +7321,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ29">
         <v>0.79</v>
@@ -7933,7 +7942,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ32">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR32">
         <v>0.82</v>
@@ -8136,10 +8145,10 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ33">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR33">
         <v>2.15</v>
@@ -8470,7 +8479,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q35">
         <v>3.3</v>
@@ -8548,7 +8557,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ35">
         <v>1.57</v>
@@ -8676,7 +8685,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q36">
         <v>3.1</v>
@@ -8754,7 +8763,7 @@
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ36">
         <v>1.69</v>
@@ -8882,7 +8891,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q37">
         <v>3.4</v>
@@ -9088,7 +9097,7 @@
         <v>90</v>
       </c>
       <c r="P38" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q38">
         <v>3.2</v>
@@ -9294,7 +9303,7 @@
         <v>90</v>
       </c>
       <c r="P39" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q39">
         <v>3.4</v>
@@ -9375,7 +9384,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ39">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR39">
         <v>0.8</v>
@@ -9706,7 +9715,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q41">
         <v>2.5</v>
@@ -9912,7 +9921,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q42">
         <v>3.25</v>
@@ -10118,7 +10127,7 @@
         <v>90</v>
       </c>
       <c r="P43" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q43">
         <v>2.75</v>
@@ -10611,7 +10620,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ45">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR45">
         <v>1.53</v>
@@ -11023,7 +11032,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ47">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR47">
         <v>1.49</v>
@@ -11226,7 +11235,7 @@
         <v>0.33</v>
       </c>
       <c r="AP48">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ48">
         <v>1.07</v>
@@ -11435,7 +11444,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ49">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR49">
         <v>1.53</v>
@@ -11638,7 +11647,7 @@
         <v>3</v>
       </c>
       <c r="AP50">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ50">
         <v>1.57</v>
@@ -12050,10 +12059,10 @@
         <v>1.5</v>
       </c>
       <c r="AP52">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ52">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR52">
         <v>1.34</v>
@@ -12259,7 +12268,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ53">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR53">
         <v>1.76</v>
@@ -12384,7 +12393,7 @@
         <v>129</v>
       </c>
       <c r="P54" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q54">
         <v>2.55</v>
@@ -12590,7 +12599,7 @@
         <v>130</v>
       </c>
       <c r="P55" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q55">
         <v>2.55</v>
@@ -12668,7 +12677,7 @@
         <v>1.33</v>
       </c>
       <c r="AP55">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ55">
         <v>1.47</v>
@@ -13002,7 +13011,7 @@
         <v>132</v>
       </c>
       <c r="P57" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -13080,7 +13089,7 @@
         <v>0.67</v>
       </c>
       <c r="AP57">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ57">
         <v>0.86</v>
@@ -13414,7 +13423,7 @@
         <v>134</v>
       </c>
       <c r="P59" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q59">
         <v>2.62</v>
@@ -13620,7 +13629,7 @@
         <v>135</v>
       </c>
       <c r="P60" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q60">
         <v>2.88</v>
@@ -13907,7 +13916,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ61">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR61">
         <v>1.29</v>
@@ -14032,7 +14041,7 @@
         <v>137</v>
       </c>
       <c r="P62" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q62">
         <v>3.6</v>
@@ -14238,7 +14247,7 @@
         <v>138</v>
       </c>
       <c r="P63" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q63">
         <v>3.75</v>
@@ -14728,7 +14737,7 @@
         <v>1.75</v>
       </c>
       <c r="AP65">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ65">
         <v>1.47</v>
@@ -14934,7 +14943,7 @@
         <v>1</v>
       </c>
       <c r="AP66">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ66">
         <v>0.86</v>
@@ -15268,7 +15277,7 @@
         <v>143</v>
       </c>
       <c r="P68" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15346,10 +15355,10 @@
         <v>1</v>
       </c>
       <c r="AP68">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ68">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR68">
         <v>1.95</v>
@@ -15474,7 +15483,7 @@
         <v>144</v>
       </c>
       <c r="P69" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15552,10 +15561,10 @@
         <v>1</v>
       </c>
       <c r="AP69">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ69">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR69">
         <v>1.23</v>
@@ -15680,7 +15689,7 @@
         <v>145</v>
       </c>
       <c r="P70" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q70">
         <v>3.75</v>
@@ -16092,7 +16101,7 @@
         <v>147</v>
       </c>
       <c r="P72" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16173,7 +16182,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ72">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR72">
         <v>1.72</v>
@@ -16298,7 +16307,7 @@
         <v>90</v>
       </c>
       <c r="P73" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q73">
         <v>4.33</v>
@@ -16504,7 +16513,7 @@
         <v>90</v>
       </c>
       <c r="P74" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q74">
         <v>2.4</v>
@@ -16710,7 +16719,7 @@
         <v>148</v>
       </c>
       <c r="P75" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q75">
         <v>3.5</v>
@@ -16916,7 +16925,7 @@
         <v>149</v>
       </c>
       <c r="P76" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q76">
         <v>2.88</v>
@@ -16994,7 +17003,7 @@
         <v>1.33</v>
       </c>
       <c r="AP76">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ76">
         <v>1.29</v>
@@ -17409,7 +17418,7 @@
         <v>2</v>
       </c>
       <c r="AQ78">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR78">
         <v>1.7</v>
@@ -17534,7 +17543,7 @@
         <v>151</v>
       </c>
       <c r="P79" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17740,7 +17749,7 @@
         <v>152</v>
       </c>
       <c r="P80" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q80">
         <v>2.05</v>
@@ -17946,7 +17955,7 @@
         <v>90</v>
       </c>
       <c r="P81" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q81">
         <v>4.33</v>
@@ -18233,7 +18242,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ82">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR82">
         <v>1.57</v>
@@ -18642,7 +18651,7 @@
         <v>1.4</v>
       </c>
       <c r="AP84">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ84">
         <v>1.47</v>
@@ -18770,7 +18779,7 @@
         <v>90</v>
       </c>
       <c r="P85" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q85">
         <v>3.1</v>
@@ -18851,7 +18860,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ85">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR85">
         <v>1.48</v>
@@ -18976,7 +18985,7 @@
         <v>156</v>
       </c>
       <c r="P86" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -19054,7 +19063,7 @@
         <v>1.4</v>
       </c>
       <c r="AP86">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ86">
         <v>1.5</v>
@@ -19263,7 +19272,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ87">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR87">
         <v>1.28</v>
@@ -19672,10 +19681,10 @@
         <v>0.75</v>
       </c>
       <c r="AP89">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ89">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR89">
         <v>1.72</v>
@@ -19800,7 +19809,7 @@
         <v>90</v>
       </c>
       <c r="P90" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q90">
         <v>2.38</v>
@@ -20212,7 +20221,7 @@
         <v>160</v>
       </c>
       <c r="P92" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20290,10 +20299,10 @@
         <v>1</v>
       </c>
       <c r="AP92">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ92">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR92">
         <v>1.2</v>
@@ -20830,7 +20839,7 @@
         <v>162</v>
       </c>
       <c r="P95" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q95">
         <v>1.9</v>
@@ -21036,7 +21045,7 @@
         <v>163</v>
       </c>
       <c r="P96" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q96">
         <v>2.75</v>
@@ -21448,7 +21457,7 @@
         <v>90</v>
       </c>
       <c r="P98" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q98">
         <v>4.75</v>
@@ -21941,7 +21950,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ100">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR100">
         <v>1.57</v>
@@ -22684,7 +22693,7 @@
         <v>167</v>
       </c>
       <c r="P104" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q104">
         <v>2.25</v>
@@ -22762,7 +22771,7 @@
         <v>1.17</v>
       </c>
       <c r="AP104">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ104">
         <v>1</v>
@@ -22968,7 +22977,7 @@
         <v>0.83</v>
       </c>
       <c r="AP105">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ105">
         <v>0.86</v>
@@ -23177,7 +23186,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ106">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR106">
         <v>1.41</v>
@@ -23383,7 +23392,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ107">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR107">
         <v>1.74</v>
@@ -23508,7 +23517,7 @@
         <v>90</v>
       </c>
       <c r="P108" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q108">
         <v>4.5</v>
@@ -23586,7 +23595,7 @@
         <v>1.2</v>
       </c>
       <c r="AP108">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ108">
         <v>1.69</v>
@@ -23795,7 +23804,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ109">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR109">
         <v>1.6</v>
@@ -23998,7 +24007,7 @@
         <v>1.17</v>
       </c>
       <c r="AP110">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ110">
         <v>1.13</v>
@@ -24332,7 +24341,7 @@
         <v>173</v>
       </c>
       <c r="P112" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q112">
         <v>3.5</v>
@@ -24410,10 +24419,10 @@
         <v>1</v>
       </c>
       <c r="AP112">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ112">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR112">
         <v>1.26</v>
@@ -24616,10 +24625,10 @@
         <v>1.4</v>
       </c>
       <c r="AP113">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ113">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR113">
         <v>1.1</v>
@@ -24744,7 +24753,7 @@
         <v>90</v>
       </c>
       <c r="P114" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q114">
         <v>2.85</v>
@@ -25156,7 +25165,7 @@
         <v>175</v>
       </c>
       <c r="P116" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q116">
         <v>2.4</v>
@@ -25568,7 +25577,7 @@
         <v>90</v>
       </c>
       <c r="P118" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q118">
         <v>4</v>
@@ -25855,7 +25864,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ119">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR119">
         <v>1.46</v>
@@ -26186,7 +26195,7 @@
         <v>178</v>
       </c>
       <c r="P121" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q121">
         <v>2.88</v>
@@ -26473,7 +26482,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ122">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR122">
         <v>1.78</v>
@@ -26882,7 +26891,7 @@
         <v>1</v>
       </c>
       <c r="AP124">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ124">
         <v>1.13</v>
@@ -27500,10 +27509,10 @@
         <v>1</v>
       </c>
       <c r="AP127">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ127">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR127">
         <v>1.21</v>
@@ -28118,7 +28127,7 @@
         <v>0.71</v>
       </c>
       <c r="AP130">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ130">
         <v>0.86</v>
@@ -28324,10 +28333,10 @@
         <v>1.17</v>
       </c>
       <c r="AP131">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ131">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR131">
         <v>1.33</v>
@@ -28533,7 +28542,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ132">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR132">
         <v>1.26</v>
@@ -28736,7 +28745,7 @@
         <v>0.67</v>
       </c>
       <c r="AP133">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ133">
         <v>0.5</v>
@@ -28864,7 +28873,7 @@
         <v>90</v>
       </c>
       <c r="P134" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q134">
         <v>3.2</v>
@@ -28945,7 +28954,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ134">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR134">
         <v>1.08</v>
@@ -29070,7 +29079,7 @@
         <v>90</v>
       </c>
       <c r="P135" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q135">
         <v>5</v>
@@ -29148,7 +29157,7 @@
         <v>2</v>
       </c>
       <c r="AP135">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ135">
         <v>1.64</v>
@@ -29975,7 +29984,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ139">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR139">
         <v>1.46</v>
@@ -30306,7 +30315,7 @@
         <v>189</v>
       </c>
       <c r="P141" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q141">
         <v>2.8</v>
@@ -30799,7 +30808,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ143">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR143">
         <v>1.16</v>
@@ -31002,7 +31011,7 @@
         <v>1.43</v>
       </c>
       <c r="AP144">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ144">
         <v>1.69</v>
@@ -31130,7 +31139,7 @@
         <v>192</v>
       </c>
       <c r="P145" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q145">
         <v>2.75</v>
@@ -31336,7 +31345,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q146">
         <v>3.75</v>
@@ -31417,7 +31426,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ146">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR146">
         <v>1.08</v>
@@ -31542,7 +31551,7 @@
         <v>129</v>
       </c>
       <c r="P147" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q147">
         <v>3.75</v>
@@ -31620,7 +31629,7 @@
         <v>1</v>
       </c>
       <c r="AP147">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ147">
         <v>1.13</v>
@@ -31748,7 +31757,7 @@
         <v>90</v>
       </c>
       <c r="P148" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q148">
         <v>2.4</v>
@@ -31826,7 +31835,7 @@
         <v>0.88</v>
       </c>
       <c r="AP148">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ148">
         <v>0.86</v>
@@ -31954,7 +31963,7 @@
         <v>90</v>
       </c>
       <c r="P149" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q149">
         <v>3.1</v>
@@ -32241,7 +32250,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ150">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR150">
         <v>1.35</v>
@@ -32366,7 +32375,7 @@
         <v>194</v>
       </c>
       <c r="P151" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q151">
         <v>1.62</v>
@@ -32444,10 +32453,10 @@
         <v>1.14</v>
       </c>
       <c r="AP151">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ151">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR151">
         <v>1.79</v>
@@ -32778,7 +32787,7 @@
         <v>95</v>
       </c>
       <c r="P153" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q153">
         <v>2.63</v>
@@ -33062,7 +33071,7 @@
         <v>1.13</v>
       </c>
       <c r="AP154">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ154">
         <v>1.5</v>
@@ -33271,7 +33280,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ155">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR155">
         <v>1</v>
@@ -33602,7 +33611,7 @@
         <v>197</v>
       </c>
       <c r="P157" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q157">
         <v>2.7</v>
@@ -33680,7 +33689,7 @@
         <v>1.11</v>
       </c>
       <c r="AP157">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ157">
         <v>1.07</v>
@@ -33808,7 +33817,7 @@
         <v>96</v>
       </c>
       <c r="P158" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q158">
         <v>2.55</v>
@@ -33886,7 +33895,7 @@
         <v>1.11</v>
       </c>
       <c r="AP158">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ158">
         <v>0.86</v>
@@ -34014,7 +34023,7 @@
         <v>198</v>
       </c>
       <c r="P159" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q159">
         <v>3.3</v>
@@ -34092,7 +34101,7 @@
         <v>1.13</v>
       </c>
       <c r="AP159">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ159">
         <v>1.57</v>
@@ -34220,7 +34229,7 @@
         <v>90</v>
       </c>
       <c r="P160" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q160">
         <v>2.75</v>
@@ -34301,7 +34310,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ160">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR160">
         <v>1.38</v>
@@ -34504,10 +34513,10 @@
         <v>0.75</v>
       </c>
       <c r="AP161">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ161">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR161">
         <v>1.88</v>
@@ -35331,7 +35340,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ165">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR165">
         <v>1.13</v>
@@ -35537,7 +35546,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ166">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR166">
         <v>1.68</v>
@@ -35662,7 +35671,7 @@
         <v>109</v>
       </c>
       <c r="P167" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q167">
         <v>3.35</v>
@@ -35946,7 +35955,7 @@
         <v>0.5</v>
       </c>
       <c r="AP168">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ168">
         <v>0.5</v>
@@ -36074,7 +36083,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q169">
         <v>2.8</v>
@@ -36280,7 +36289,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q170">
         <v>3</v>
@@ -36692,7 +36701,7 @@
         <v>90</v>
       </c>
       <c r="P172" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q172">
         <v>2.63</v>
@@ -36898,7 +36907,7 @@
         <v>207</v>
       </c>
       <c r="P173" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q173">
         <v>2.3</v>
@@ -36976,7 +36985,7 @@
         <v>0.11</v>
       </c>
       <c r="AP173">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ173">
         <v>0.79</v>
@@ -37391,7 +37400,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ175">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR175">
         <v>0.95</v>
@@ -37594,7 +37603,7 @@
         <v>1</v>
       </c>
       <c r="AP176">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ176">
         <v>1.07</v>
@@ -37803,7 +37812,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ177">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR177">
         <v>1.6</v>
@@ -37928,7 +37937,7 @@
         <v>90</v>
       </c>
       <c r="P178" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q178">
         <v>3.25</v>
@@ -38212,7 +38221,7 @@
         <v>1.1</v>
       </c>
       <c r="AP179">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ179">
         <v>0.86</v>
@@ -38340,7 +38349,7 @@
         <v>212</v>
       </c>
       <c r="P180" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q180">
         <v>2.2</v>
@@ -38421,7 +38430,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ180">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR180">
         <v>1.65</v>
@@ -38546,7 +38555,7 @@
         <v>90</v>
       </c>
       <c r="P181" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q181">
         <v>3.25</v>
@@ -38624,7 +38633,7 @@
         <v>1</v>
       </c>
       <c r="AP181">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ181">
         <v>1.29</v>
@@ -38833,7 +38842,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ182">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR182">
         <v>1.62</v>
@@ -39782,7 +39791,7 @@
         <v>90</v>
       </c>
       <c r="P187" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q187">
         <v>2.55</v>
@@ -39988,7 +39997,7 @@
         <v>215</v>
       </c>
       <c r="P188" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q188">
         <v>4.5</v>
@@ -40606,7 +40615,7 @@
         <v>90</v>
       </c>
       <c r="P191" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q191">
         <v>2.75</v>
@@ -40684,7 +40693,7 @@
         <v>1.27</v>
       </c>
       <c r="AP191">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ191">
         <v>1.13</v>
@@ -40812,7 +40821,7 @@
         <v>90</v>
       </c>
       <c r="P192" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q192">
         <v>3.25</v>
@@ -40890,10 +40899,10 @@
         <v>0.8</v>
       </c>
       <c r="AP192">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ192">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR192">
         <v>1.84</v>
@@ -41302,7 +41311,7 @@
         <v>0.91</v>
       </c>
       <c r="AP194">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ194">
         <v>0.86</v>
@@ -41430,7 +41439,7 @@
         <v>214</v>
       </c>
       <c r="P195" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q195">
         <v>4.75</v>
@@ -41636,7 +41645,7 @@
         <v>90</v>
       </c>
       <c r="P196" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q196">
         <v>3.65</v>
@@ -41714,7 +41723,7 @@
         <v>1.5</v>
       </c>
       <c r="AP196">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ196">
         <v>1.57</v>
@@ -41842,7 +41851,7 @@
         <v>218</v>
       </c>
       <c r="P197" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q197">
         <v>1.94</v>
@@ -41923,7 +41932,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ197">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR197">
         <v>1.67</v>
@@ -42129,7 +42138,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ198">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR198">
         <v>1.7</v>
@@ -42254,7 +42263,7 @@
         <v>90</v>
       </c>
       <c r="P199" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q199">
         <v>3.75</v>
@@ -42541,7 +42550,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ200">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR200">
         <v>1.39</v>
@@ -42953,7 +42962,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ202">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR202">
         <v>1.2</v>
@@ -43156,7 +43165,7 @@
         <v>1.45</v>
       </c>
       <c r="AP203">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ203">
         <v>1.47</v>
@@ -43284,7 +43293,7 @@
         <v>160</v>
       </c>
       <c r="P204" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q204">
         <v>3</v>
@@ -43365,7 +43374,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ204">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR204">
         <v>1.59</v>
@@ -43490,7 +43499,7 @@
         <v>90</v>
       </c>
       <c r="P205" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q205">
         <v>2.75</v>
@@ -43902,7 +43911,7 @@
         <v>90</v>
       </c>
       <c r="P207" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q207">
         <v>3.8</v>
@@ -44186,7 +44195,7 @@
         <v>0.4</v>
       </c>
       <c r="AP208">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ208">
         <v>0.5</v>
@@ -44392,10 +44401,10 @@
         <v>0.55</v>
       </c>
       <c r="AP209">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ209">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR209">
         <v>1.77</v>
@@ -44804,7 +44813,7 @@
         <v>1.08</v>
       </c>
       <c r="AP211">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ211">
         <v>1.07</v>
@@ -45013,7 +45022,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ212">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR212">
         <v>1.56</v>
@@ -45138,7 +45147,7 @@
         <v>226</v>
       </c>
       <c r="P213" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q213">
         <v>3.75</v>
@@ -45550,7 +45559,7 @@
         <v>228</v>
       </c>
       <c r="P215" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q215">
         <v>2.95</v>
@@ -45756,7 +45765,7 @@
         <v>90</v>
       </c>
       <c r="P216" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q216">
         <v>1.96</v>
@@ -46249,7 +46258,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ218">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR218">
         <v>1.63</v>
@@ -46374,7 +46383,7 @@
         <v>229</v>
       </c>
       <c r="P219" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q219">
         <v>4.3</v>
@@ -46452,7 +46461,7 @@
         <v>1.67</v>
       </c>
       <c r="AP219">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ219">
         <v>1.64</v>
@@ -46658,10 +46667,10 @@
         <v>1.27</v>
       </c>
       <c r="AP220">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ220">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR220">
         <v>1.27</v>
@@ -46867,7 +46876,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ221">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR221">
         <v>1.73</v>
@@ -46992,7 +47001,7 @@
         <v>90</v>
       </c>
       <c r="P222" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q222">
         <v>2.7</v>
@@ -47198,7 +47207,7 @@
         <v>231</v>
       </c>
       <c r="P223" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q223">
         <v>3.65</v>
@@ -47404,7 +47413,7 @@
         <v>232</v>
       </c>
       <c r="P224" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q224">
         <v>5.2</v>
@@ -47816,7 +47825,7 @@
         <v>221</v>
       </c>
       <c r="P226" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q226">
         <v>4.4</v>
@@ -47894,7 +47903,7 @@
         <v>1.36</v>
       </c>
       <c r="AP226">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ226">
         <v>1.29</v>
@@ -48022,7 +48031,7 @@
         <v>234</v>
       </c>
       <c r="P227" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q227">
         <v>2.7</v>
@@ -48309,7 +48318,7 @@
         <v>2</v>
       </c>
       <c r="AQ228">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR228">
         <v>1.77</v>
@@ -48515,7 +48524,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ229">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR229">
         <v>1.3</v>
@@ -48640,7 +48649,7 @@
         <v>90</v>
       </c>
       <c r="P230" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q230">
         <v>3.04</v>
@@ -49133,7 +49142,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ232">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR232">
         <v>1.59</v>
@@ -49258,7 +49267,7 @@
         <v>238</v>
       </c>
       <c r="P233" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q233">
         <v>3.1</v>
@@ -49336,7 +49345,7 @@
         <v>1.5</v>
       </c>
       <c r="AP233">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ233">
         <v>1.5</v>
@@ -49464,7 +49473,7 @@
         <v>239</v>
       </c>
       <c r="P234" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q234">
         <v>1.85</v>
@@ -49748,7 +49757,7 @@
         <v>1.5</v>
       </c>
       <c r="AP235">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ235">
         <v>1.29</v>
@@ -49876,7 +49885,7 @@
         <v>241</v>
       </c>
       <c r="P236" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q236">
         <v>3.7</v>
@@ -50163,7 +50172,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ237">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR237">
         <v>1.37</v>
@@ -50366,7 +50375,7 @@
         <v>1</v>
       </c>
       <c r="AP238">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ238">
         <v>1</v>
@@ -50494,7 +50503,7 @@
         <v>243</v>
       </c>
       <c r="P239" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q239">
         <v>3.1</v>
@@ -50572,7 +50581,7 @@
         <v>0.92</v>
       </c>
       <c r="AP239">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ239">
         <v>0.86</v>
@@ -51112,7 +51121,7 @@
         <v>245</v>
       </c>
       <c r="P242" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q242">
         <v>3.6</v>
@@ -51396,7 +51405,7 @@
         <v>1.77</v>
       </c>
       <c r="AP243">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ243">
         <v>1.64</v>
@@ -51605,7 +51614,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ244">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR244">
         <v>1.82</v>
@@ -51936,7 +51945,7 @@
         <v>114</v>
       </c>
       <c r="P246" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q246">
         <v>3.6</v>
@@ -52635,7 +52644,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ249">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR249">
         <v>1.42</v>
@@ -52966,7 +52975,7 @@
         <v>251</v>
       </c>
       <c r="P251" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q251">
         <v>4.75</v>
@@ -53378,7 +53387,7 @@
         <v>253</v>
       </c>
       <c r="P253" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q253">
         <v>2.2</v>
@@ -53456,7 +53465,7 @@
         <v>0.54</v>
       </c>
       <c r="AP253">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ253">
         <v>0.5</v>
@@ -53535,6 +53544,1036 @@
       </c>
       <c r="BP253">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="254" spans="1:68">
+      <c r="A254" s="1">
+        <v>253</v>
+      </c>
+      <c r="B254">
+        <v>7469118</v>
+      </c>
+      <c r="C254" t="s">
+        <v>68</v>
+      </c>
+      <c r="D254" t="s">
+        <v>69</v>
+      </c>
+      <c r="E254" s="2">
+        <v>45751.625</v>
+      </c>
+      <c r="F254">
+        <v>29</v>
+      </c>
+      <c r="G254" t="s">
+        <v>81</v>
+      </c>
+      <c r="H254" t="s">
+        <v>77</v>
+      </c>
+      <c r="I254">
+        <v>0</v>
+      </c>
+      <c r="J254">
+        <v>0</v>
+      </c>
+      <c r="K254">
+        <v>0</v>
+      </c>
+      <c r="L254">
+        <v>1</v>
+      </c>
+      <c r="M254">
+        <v>0</v>
+      </c>
+      <c r="N254">
+        <v>1</v>
+      </c>
+      <c r="O254" t="s">
+        <v>207</v>
+      </c>
+      <c r="P254" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q254">
+        <v>1.83</v>
+      </c>
+      <c r="R254">
+        <v>2.5</v>
+      </c>
+      <c r="S254">
+        <v>5.75</v>
+      </c>
+      <c r="T254">
+        <v>1.26</v>
+      </c>
+      <c r="U254">
+        <v>3.5</v>
+      </c>
+      <c r="V254">
+        <v>2.2</v>
+      </c>
+      <c r="W254">
+        <v>1.57</v>
+      </c>
+      <c r="X254">
+        <v>5</v>
+      </c>
+      <c r="Y254">
+        <v>1.14</v>
+      </c>
+      <c r="Z254">
+        <v>1.41</v>
+      </c>
+      <c r="AA254">
+        <v>4.75</v>
+      </c>
+      <c r="AB254">
+        <v>6.7</v>
+      </c>
+      <c r="AC254">
+        <v>1.03</v>
+      </c>
+      <c r="AD254">
+        <v>11</v>
+      </c>
+      <c r="AE254">
+        <v>1.17</v>
+      </c>
+      <c r="AF254">
+        <v>5</v>
+      </c>
+      <c r="AG254">
+        <v>1.57</v>
+      </c>
+      <c r="AH254">
+        <v>2.15</v>
+      </c>
+      <c r="AI254">
+        <v>1.77</v>
+      </c>
+      <c r="AJ254">
+        <v>1.9</v>
+      </c>
+      <c r="AK254">
+        <v>1.11</v>
+      </c>
+      <c r="AL254">
+        <v>1.17</v>
+      </c>
+      <c r="AM254">
+        <v>2.85</v>
+      </c>
+      <c r="AN254">
+        <v>1.31</v>
+      </c>
+      <c r="AO254">
+        <v>1.31</v>
+      </c>
+      <c r="AP254">
+        <v>1.43</v>
+      </c>
+      <c r="AQ254">
+        <v>1.21</v>
+      </c>
+      <c r="AR254">
+        <v>1.79</v>
+      </c>
+      <c r="AS254">
+        <v>1.07</v>
+      </c>
+      <c r="AT254">
+        <v>2.86</v>
+      </c>
+      <c r="AU254">
+        <v>-1</v>
+      </c>
+      <c r="AV254">
+        <v>-1</v>
+      </c>
+      <c r="AW254">
+        <v>-1</v>
+      </c>
+      <c r="AX254">
+        <v>-1</v>
+      </c>
+      <c r="AY254">
+        <v>-1</v>
+      </c>
+      <c r="AZ254">
+        <v>-1</v>
+      </c>
+      <c r="BA254">
+        <v>-1</v>
+      </c>
+      <c r="BB254">
+        <v>-1</v>
+      </c>
+      <c r="BC254">
+        <v>-1</v>
+      </c>
+      <c r="BD254">
+        <v>1.3</v>
+      </c>
+      <c r="BE254">
+        <v>7.5</v>
+      </c>
+      <c r="BF254">
+        <v>3.8</v>
+      </c>
+      <c r="BG254">
+        <v>1.28</v>
+      </c>
+      <c r="BH254">
+        <v>3.3</v>
+      </c>
+      <c r="BI254">
+        <v>1.49</v>
+      </c>
+      <c r="BJ254">
+        <v>2.43</v>
+      </c>
+      <c r="BK254">
+        <v>1.79</v>
+      </c>
+      <c r="BL254">
+        <v>1.91</v>
+      </c>
+      <c r="BM254">
+        <v>2.2</v>
+      </c>
+      <c r="BN254">
+        <v>1.58</v>
+      </c>
+      <c r="BO254">
+        <v>2.8</v>
+      </c>
+      <c r="BP254">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="255" spans="1:68">
+      <c r="A255" s="1">
+        <v>254</v>
+      </c>
+      <c r="B255">
+        <v>7469120</v>
+      </c>
+      <c r="C255" t="s">
+        <v>68</v>
+      </c>
+      <c r="D255" t="s">
+        <v>69</v>
+      </c>
+      <c r="E255" s="2">
+        <v>45751.625</v>
+      </c>
+      <c r="F255">
+        <v>29</v>
+      </c>
+      <c r="G255" t="s">
+        <v>71</v>
+      </c>
+      <c r="H255" t="s">
+        <v>73</v>
+      </c>
+      <c r="I255">
+        <v>1</v>
+      </c>
+      <c r="J255">
+        <v>1</v>
+      </c>
+      <c r="K255">
+        <v>2</v>
+      </c>
+      <c r="L255">
+        <v>2</v>
+      </c>
+      <c r="M255">
+        <v>1</v>
+      </c>
+      <c r="N255">
+        <v>3</v>
+      </c>
+      <c r="O255" t="s">
+        <v>254</v>
+      </c>
+      <c r="P255" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q255">
+        <v>2.8</v>
+      </c>
+      <c r="R255">
+        <v>1.93</v>
+      </c>
+      <c r="S255">
+        <v>4.1</v>
+      </c>
+      <c r="T255">
+        <v>1.51</v>
+      </c>
+      <c r="U255">
+        <v>2.35</v>
+      </c>
+      <c r="V255">
+        <v>3.4</v>
+      </c>
+      <c r="W255">
+        <v>1.28</v>
+      </c>
+      <c r="X255">
+        <v>9.5</v>
+      </c>
+      <c r="Y255">
+        <v>1.04</v>
+      </c>
+      <c r="Z255">
+        <v>2.02</v>
+      </c>
+      <c r="AA255">
+        <v>3.13</v>
+      </c>
+      <c r="AB255">
+        <v>3.91</v>
+      </c>
+      <c r="AC255">
+        <v>1.11</v>
+      </c>
+      <c r="AD255">
+        <v>6.25</v>
+      </c>
+      <c r="AE255">
+        <v>1.5</v>
+      </c>
+      <c r="AF255">
+        <v>2.4</v>
+      </c>
+      <c r="AG255">
+        <v>2.3</v>
+      </c>
+      <c r="AH255">
+        <v>1.5</v>
+      </c>
+      <c r="AI255">
+        <v>2.1</v>
+      </c>
+      <c r="AJ255">
+        <v>1.65</v>
+      </c>
+      <c r="AK255">
+        <v>1.28</v>
+      </c>
+      <c r="AL255">
+        <v>1.34</v>
+      </c>
+      <c r="AM255">
+        <v>1.66</v>
+      </c>
+      <c r="AN255">
+        <v>1.64</v>
+      </c>
+      <c r="AO255">
+        <v>0.57</v>
+      </c>
+      <c r="AP255">
+        <v>1.73</v>
+      </c>
+      <c r="AQ255">
+        <v>0.53</v>
+      </c>
+      <c r="AR255">
+        <v>1.28</v>
+      </c>
+      <c r="AS255">
+        <v>1.23</v>
+      </c>
+      <c r="AT255">
+        <v>2.51</v>
+      </c>
+      <c r="AU255">
+        <v>-1</v>
+      </c>
+      <c r="AV255">
+        <v>-1</v>
+      </c>
+      <c r="AW255">
+        <v>-1</v>
+      </c>
+      <c r="AX255">
+        <v>-1</v>
+      </c>
+      <c r="AY255">
+        <v>-1</v>
+      </c>
+      <c r="AZ255">
+        <v>-1</v>
+      </c>
+      <c r="BA255">
+        <v>-1</v>
+      </c>
+      <c r="BB255">
+        <v>-1</v>
+      </c>
+      <c r="BC255">
+        <v>-1</v>
+      </c>
+      <c r="BD255">
+        <v>1.78</v>
+      </c>
+      <c r="BE255">
+        <v>6.25</v>
+      </c>
+      <c r="BF255">
+        <v>2.28</v>
+      </c>
+      <c r="BG255">
+        <v>1.49</v>
+      </c>
+      <c r="BH255">
+        <v>2.4</v>
+      </c>
+      <c r="BI255">
+        <v>1.84</v>
+      </c>
+      <c r="BJ255">
+        <v>1.84</v>
+      </c>
+      <c r="BK255">
+        <v>2.33</v>
+      </c>
+      <c r="BL255">
+        <v>1.5</v>
+      </c>
+      <c r="BM255">
+        <v>3.05</v>
+      </c>
+      <c r="BN255">
+        <v>1.3</v>
+      </c>
+      <c r="BO255">
+        <v>4.1</v>
+      </c>
+      <c r="BP255">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="256" spans="1:68">
+      <c r="A256" s="1">
+        <v>255</v>
+      </c>
+      <c r="B256">
+        <v>7469121</v>
+      </c>
+      <c r="C256" t="s">
+        <v>68</v>
+      </c>
+      <c r="D256" t="s">
+        <v>69</v>
+      </c>
+      <c r="E256" s="2">
+        <v>45751.625</v>
+      </c>
+      <c r="F256">
+        <v>29</v>
+      </c>
+      <c r="G256" t="s">
+        <v>84</v>
+      </c>
+      <c r="H256" t="s">
+        <v>83</v>
+      </c>
+      <c r="I256">
+        <v>1</v>
+      </c>
+      <c r="J256">
+        <v>0</v>
+      </c>
+      <c r="K256">
+        <v>1</v>
+      </c>
+      <c r="L256">
+        <v>1</v>
+      </c>
+      <c r="M256">
+        <v>1</v>
+      </c>
+      <c r="N256">
+        <v>2</v>
+      </c>
+      <c r="O256" t="s">
+        <v>184</v>
+      </c>
+      <c r="P256" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q256">
+        <v>3.9</v>
+      </c>
+      <c r="R256">
+        <v>1.9</v>
+      </c>
+      <c r="S256">
+        <v>2.9</v>
+      </c>
+      <c r="T256">
+        <v>1.53</v>
+      </c>
+      <c r="U256">
+        <v>2.3</v>
+      </c>
+      <c r="V256">
+        <v>3.4</v>
+      </c>
+      <c r="W256">
+        <v>1.27</v>
+      </c>
+      <c r="X256">
+        <v>10</v>
+      </c>
+      <c r="Y256">
+        <v>1.04</v>
+      </c>
+      <c r="Z256">
+        <v>3.38</v>
+      </c>
+      <c r="AA256">
+        <v>3.01</v>
+      </c>
+      <c r="AB256">
+        <v>2.26</v>
+      </c>
+      <c r="AC256">
+        <v>1.1</v>
+      </c>
+      <c r="AD256">
+        <v>6.5</v>
+      </c>
+      <c r="AE256">
+        <v>1.5</v>
+      </c>
+      <c r="AF256">
+        <v>2.4</v>
+      </c>
+      <c r="AG256">
+        <v>2.37</v>
+      </c>
+      <c r="AH256">
+        <v>1.48</v>
+      </c>
+      <c r="AI256">
+        <v>2.1</v>
+      </c>
+      <c r="AJ256">
+        <v>1.65</v>
+      </c>
+      <c r="AK256">
+        <v>1.61</v>
+      </c>
+      <c r="AL256">
+        <v>1.35</v>
+      </c>
+      <c r="AM256">
+        <v>1.31</v>
+      </c>
+      <c r="AN256">
+        <v>1.77</v>
+      </c>
+      <c r="AO256">
+        <v>0.86</v>
+      </c>
+      <c r="AP256">
+        <v>1.71</v>
+      </c>
+      <c r="AQ256">
+        <v>0.87</v>
+      </c>
+      <c r="AR256">
+        <v>1.35</v>
+      </c>
+      <c r="AS256">
+        <v>1.42</v>
+      </c>
+      <c r="AT256">
+        <v>2.77</v>
+      </c>
+      <c r="AU256">
+        <v>-1</v>
+      </c>
+      <c r="AV256">
+        <v>-1</v>
+      </c>
+      <c r="AW256">
+        <v>-1</v>
+      </c>
+      <c r="AX256">
+        <v>-1</v>
+      </c>
+      <c r="AY256">
+        <v>-1</v>
+      </c>
+      <c r="AZ256">
+        <v>-1</v>
+      </c>
+      <c r="BA256">
+        <v>-1</v>
+      </c>
+      <c r="BB256">
+        <v>-1</v>
+      </c>
+      <c r="BC256">
+        <v>-1</v>
+      </c>
+      <c r="BD256">
+        <v>2.15</v>
+      </c>
+      <c r="BE256">
+        <v>6.25</v>
+      </c>
+      <c r="BF256">
+        <v>1.88</v>
+      </c>
+      <c r="BG256">
+        <v>1.55</v>
+      </c>
+      <c r="BH256">
+        <v>2.25</v>
+      </c>
+      <c r="BI256">
+        <v>1.93</v>
+      </c>
+      <c r="BJ256">
+        <v>1.77</v>
+      </c>
+      <c r="BK256">
+        <v>2.48</v>
+      </c>
+      <c r="BL256">
+        <v>1.47</v>
+      </c>
+      <c r="BM256">
+        <v>3.3</v>
+      </c>
+      <c r="BN256">
+        <v>1.28</v>
+      </c>
+      <c r="BO256">
+        <v>4.4</v>
+      </c>
+      <c r="BP256">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="257" spans="1:68">
+      <c r="A257" s="1">
+        <v>256</v>
+      </c>
+      <c r="B257">
+        <v>7469123</v>
+      </c>
+      <c r="C257" t="s">
+        <v>68</v>
+      </c>
+      <c r="D257" t="s">
+        <v>69</v>
+      </c>
+      <c r="E257" s="2">
+        <v>45751.625</v>
+      </c>
+      <c r="F257">
+        <v>29</v>
+      </c>
+      <c r="G257" t="s">
+        <v>80</v>
+      </c>
+      <c r="H257" t="s">
+        <v>74</v>
+      </c>
+      <c r="I257">
+        <v>1</v>
+      </c>
+      <c r="J257">
+        <v>2</v>
+      </c>
+      <c r="K257">
+        <v>3</v>
+      </c>
+      <c r="L257">
+        <v>1</v>
+      </c>
+      <c r="M257">
+        <v>2</v>
+      </c>
+      <c r="N257">
+        <v>3</v>
+      </c>
+      <c r="O257" t="s">
+        <v>133</v>
+      </c>
+      <c r="P257" t="s">
+        <v>349</v>
+      </c>
+      <c r="Q257">
+        <v>2.65</v>
+      </c>
+      <c r="R257">
+        <v>2</v>
+      </c>
+      <c r="S257">
+        <v>4.1</v>
+      </c>
+      <c r="T257">
+        <v>1.44</v>
+      </c>
+      <c r="U257">
+        <v>2.55</v>
+      </c>
+      <c r="V257">
+        <v>3</v>
+      </c>
+      <c r="W257">
+        <v>1.34</v>
+      </c>
+      <c r="X257">
+        <v>8</v>
+      </c>
+      <c r="Y257">
+        <v>1.07</v>
+      </c>
+      <c r="Z257">
+        <v>2.19</v>
+      </c>
+      <c r="AA257">
+        <v>3.19</v>
+      </c>
+      <c r="AB257">
+        <v>3.34</v>
+      </c>
+      <c r="AC257">
+        <v>1.08</v>
+      </c>
+      <c r="AD257">
+        <v>7.5</v>
+      </c>
+      <c r="AE257">
+        <v>1.4</v>
+      </c>
+      <c r="AF257">
+        <v>2.9</v>
+      </c>
+      <c r="AG257">
+        <v>2.05</v>
+      </c>
+      <c r="AH257">
+        <v>1.61</v>
+      </c>
+      <c r="AI257">
+        <v>1.9</v>
+      </c>
+      <c r="AJ257">
+        <v>1.78</v>
+      </c>
+      <c r="AK257">
+        <v>1.27</v>
+      </c>
+      <c r="AL257">
+        <v>1.32</v>
+      </c>
+      <c r="AM257">
+        <v>1.72</v>
+      </c>
+      <c r="AN257">
+        <v>1.62</v>
+      </c>
+      <c r="AO257">
+        <v>0.85</v>
+      </c>
+      <c r="AP257">
+        <v>1.5</v>
+      </c>
+      <c r="AQ257">
+        <v>1</v>
+      </c>
+      <c r="AR257">
+        <v>1.28</v>
+      </c>
+      <c r="AS257">
+        <v>1.39</v>
+      </c>
+      <c r="AT257">
+        <v>2.67</v>
+      </c>
+      <c r="AU257">
+        <v>-1</v>
+      </c>
+      <c r="AV257">
+        <v>-1</v>
+      </c>
+      <c r="AW257">
+        <v>-1</v>
+      </c>
+      <c r="AX257">
+        <v>-1</v>
+      </c>
+      <c r="AY257">
+        <v>-1</v>
+      </c>
+      <c r="AZ257">
+        <v>-1</v>
+      </c>
+      <c r="BA257">
+        <v>-1</v>
+      </c>
+      <c r="BB257">
+        <v>-1</v>
+      </c>
+      <c r="BC257">
+        <v>-1</v>
+      </c>
+      <c r="BD257">
+        <v>1.58</v>
+      </c>
+      <c r="BE257">
+        <v>6.5</v>
+      </c>
+      <c r="BF257">
+        <v>2.65</v>
+      </c>
+      <c r="BG257">
+        <v>1.35</v>
+      </c>
+      <c r="BH257">
+        <v>2.9</v>
+      </c>
+      <c r="BI257">
+        <v>1.58</v>
+      </c>
+      <c r="BJ257">
+        <v>2.18</v>
+      </c>
+      <c r="BK257">
+        <v>1.96</v>
+      </c>
+      <c r="BL257">
+        <v>1.74</v>
+      </c>
+      <c r="BM257">
+        <v>2.5</v>
+      </c>
+      <c r="BN257">
+        <v>1.46</v>
+      </c>
+      <c r="BO257">
+        <v>3.3</v>
+      </c>
+      <c r="BP257">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="258" spans="1:68">
+      <c r="A258" s="1">
+        <v>257</v>
+      </c>
+      <c r="B258">
+        <v>7469125</v>
+      </c>
+      <c r="C258" t="s">
+        <v>68</v>
+      </c>
+      <c r="D258" t="s">
+        <v>69</v>
+      </c>
+      <c r="E258" s="2">
+        <v>45751.625</v>
+      </c>
+      <c r="F258">
+        <v>29</v>
+      </c>
+      <c r="G258" t="s">
+        <v>85</v>
+      </c>
+      <c r="H258" t="s">
+        <v>70</v>
+      </c>
+      <c r="I258">
+        <v>1</v>
+      </c>
+      <c r="J258">
+        <v>0</v>
+      </c>
+      <c r="K258">
+        <v>1</v>
+      </c>
+      <c r="L258">
+        <v>2</v>
+      </c>
+      <c r="M258">
+        <v>0</v>
+      </c>
+      <c r="N258">
+        <v>2</v>
+      </c>
+      <c r="O258" t="s">
+        <v>255</v>
+      </c>
+      <c r="P258" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q258">
+        <v>2</v>
+      </c>
+      <c r="R258">
+        <v>2.4</v>
+      </c>
+      <c r="S258">
+        <v>6</v>
+      </c>
+      <c r="T258">
+        <v>1.33</v>
+      </c>
+      <c r="U258">
+        <v>3.25</v>
+      </c>
+      <c r="V258">
+        <v>2.5</v>
+      </c>
+      <c r="W258">
+        <v>1.5</v>
+      </c>
+      <c r="X258">
+        <v>6.5</v>
+      </c>
+      <c r="Y258">
+        <v>1.11</v>
+      </c>
+      <c r="Z258">
+        <v>1.56</v>
+      </c>
+      <c r="AA258">
+        <v>3.55</v>
+      </c>
+      <c r="AB258">
+        <v>6.9</v>
+      </c>
+      <c r="AC258">
+        <v>1.01</v>
+      </c>
+      <c r="AD258">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AE258">
+        <v>1.22</v>
+      </c>
+      <c r="AF258">
+        <v>3.64</v>
+      </c>
+      <c r="AG258">
+        <v>1.91</v>
+      </c>
+      <c r="AH258">
+        <v>1.83</v>
+      </c>
+      <c r="AI258">
+        <v>1.83</v>
+      </c>
+      <c r="AJ258">
+        <v>1.83</v>
+      </c>
+      <c r="AK258">
+        <v>1.11</v>
+      </c>
+      <c r="AL258">
+        <v>1.21</v>
+      </c>
+      <c r="AM258">
+        <v>2.55</v>
+      </c>
+      <c r="AN258">
+        <v>2.29</v>
+      </c>
+      <c r="AO258">
+        <v>1</v>
+      </c>
+      <c r="AP258">
+        <v>2.33</v>
+      </c>
+      <c r="AQ258">
+        <v>0.93</v>
+      </c>
+      <c r="AR258">
+        <v>1.72</v>
+      </c>
+      <c r="AS258">
+        <v>1.29</v>
+      </c>
+      <c r="AT258">
+        <v>3.01</v>
+      </c>
+      <c r="AU258">
+        <v>-1</v>
+      </c>
+      <c r="AV258">
+        <v>-1</v>
+      </c>
+      <c r="AW258">
+        <v>-1</v>
+      </c>
+      <c r="AX258">
+        <v>-1</v>
+      </c>
+      <c r="AY258">
+        <v>-1</v>
+      </c>
+      <c r="AZ258">
+        <v>-1</v>
+      </c>
+      <c r="BA258">
+        <v>-1</v>
+      </c>
+      <c r="BB258">
+        <v>-1</v>
+      </c>
+      <c r="BC258">
+        <v>-1</v>
+      </c>
+      <c r="BD258">
+        <v>1.41</v>
+      </c>
+      <c r="BE258">
+        <v>7</v>
+      </c>
+      <c r="BF258">
+        <v>3.3</v>
+      </c>
+      <c r="BG258">
+        <v>1.34</v>
+      </c>
+      <c r="BH258">
+        <v>2.9</v>
+      </c>
+      <c r="BI258">
+        <v>1.58</v>
+      </c>
+      <c r="BJ258">
+        <v>2.2</v>
+      </c>
+      <c r="BK258">
+        <v>1.94</v>
+      </c>
+      <c r="BL258">
+        <v>1.76</v>
+      </c>
+      <c r="BM258">
+        <v>2.43</v>
+      </c>
+      <c r="BN258">
+        <v>1.48</v>
+      </c>
+      <c r="BO258">
+        <v>3.15</v>
+      </c>
+      <c r="BP258">
+        <v>1.29</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1610" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1628" uniqueCount="355">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -784,6 +784,15 @@
     <t>['8', '51']</t>
   </si>
   <si>
+    <t>['47', '68']</t>
+  </si>
+  <si>
+    <t>['11', '55', '75', '80', '90+5']</t>
+  </si>
+  <si>
+    <t>['12', '40']</t>
+  </si>
+  <si>
     <t>['16', '45+2']</t>
   </si>
   <si>
@@ -1064,6 +1073,12 @@
   </si>
   <si>
     <t>['40', '45+1']</t>
+  </si>
+  <si>
+    <t>['42', '61']</t>
+  </si>
+  <si>
+    <t>['28', '34']</t>
   </si>
 </sst>
 </file>
@@ -1425,7 +1440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP258"/>
+  <dimension ref="A1:BP261"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1681,7 +1696,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q2">
         <v>2.4</v>
@@ -1762,7 +1777,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ2">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2093,7 +2108,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q4">
         <v>3.6</v>
@@ -2380,7 +2395,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ5">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2917,7 +2932,7 @@
         <v>90</v>
       </c>
       <c r="P8" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q8">
         <v>3.1</v>
@@ -2995,7 +3010,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AQ8">
         <v>1.64</v>
@@ -3329,7 +3344,7 @@
         <v>94</v>
       </c>
       <c r="P10" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q10">
         <v>2.6</v>
@@ -3613,7 +3628,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ11">
         <v>0.93</v>
@@ -3947,7 +3962,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q13">
         <v>3.1</v>
@@ -4028,7 +4043,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ13">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4565,7 +4580,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q16">
         <v>2.63</v>
@@ -4771,7 +4786,7 @@
         <v>99</v>
       </c>
       <c r="P17" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -5055,7 +5070,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AQ18">
         <v>1</v>
@@ -5801,7 +5816,7 @@
         <v>103</v>
       </c>
       <c r="P22" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -5882,7 +5897,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ22">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR22">
         <v>1.64</v>
@@ -6213,7 +6228,7 @@
         <v>105</v>
       </c>
       <c r="P24" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q24">
         <v>2.62</v>
@@ -6291,7 +6306,7 @@
         <v>3</v>
       </c>
       <c r="AP24">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AQ24">
         <v>1.13</v>
@@ -6706,7 +6721,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ26">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR26">
         <v>1.19</v>
@@ -7037,7 +7052,7 @@
         <v>108</v>
       </c>
       <c r="P28" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q28">
         <v>2.6</v>
@@ -7527,10 +7542,10 @@
         <v>1.5</v>
       </c>
       <c r="AP30">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AQ30">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR30">
         <v>1.49</v>
@@ -8479,7 +8494,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q35">
         <v>3.3</v>
@@ -8685,7 +8700,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q36">
         <v>3.1</v>
@@ -8766,7 +8781,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ36">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR36">
         <v>1.66</v>
@@ -8891,7 +8906,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q37">
         <v>3.4</v>
@@ -9097,7 +9112,7 @@
         <v>90</v>
       </c>
       <c r="P38" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q38">
         <v>3.2</v>
@@ -9175,7 +9190,7 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ38">
         <v>1</v>
@@ -9303,7 +9318,7 @@
         <v>90</v>
       </c>
       <c r="P39" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q39">
         <v>3.4</v>
@@ -9715,7 +9730,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q41">
         <v>2.5</v>
@@ -9921,7 +9936,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q42">
         <v>3.25</v>
@@ -10002,7 +10017,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ42">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR42">
         <v>1.75</v>
@@ -10127,7 +10142,7 @@
         <v>90</v>
       </c>
       <c r="P43" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q43">
         <v>2.75</v>
@@ -10411,7 +10426,7 @@
         <v>0.5</v>
       </c>
       <c r="AP44">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AQ44">
         <v>0.79</v>
@@ -11029,7 +11044,7 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AQ47">
         <v>0.53</v>
@@ -12393,7 +12408,7 @@
         <v>129</v>
       </c>
       <c r="P54" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q54">
         <v>2.55</v>
@@ -12474,7 +12489,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ54">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR54">
         <v>1.19</v>
@@ -12599,7 +12614,7 @@
         <v>130</v>
       </c>
       <c r="P55" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q55">
         <v>2.55</v>
@@ -12883,7 +12898,7 @@
         <v>0.33</v>
       </c>
       <c r="AP56">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AQ56">
         <v>0.79</v>
@@ -13011,7 +13026,7 @@
         <v>132</v>
       </c>
       <c r="P57" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -13092,7 +13107,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ57">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR57">
         <v>1.54</v>
@@ -13423,7 +13438,7 @@
         <v>134</v>
       </c>
       <c r="P59" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q59">
         <v>2.62</v>
@@ -13629,7 +13644,7 @@
         <v>135</v>
       </c>
       <c r="P60" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q60">
         <v>2.88</v>
@@ -14041,7 +14056,7 @@
         <v>137</v>
       </c>
       <c r="P62" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q62">
         <v>3.6</v>
@@ -14247,7 +14262,7 @@
         <v>138</v>
       </c>
       <c r="P63" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q63">
         <v>3.75</v>
@@ -14325,10 +14340,10 @@
         <v>3</v>
       </c>
       <c r="AP63">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ63">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR63">
         <v>1.33</v>
@@ -14946,7 +14961,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ66">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR66">
         <v>1.59</v>
@@ -15277,7 +15292,7 @@
         <v>143</v>
       </c>
       <c r="P68" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15483,7 +15498,7 @@
         <v>144</v>
       </c>
       <c r="P69" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15689,7 +15704,7 @@
         <v>145</v>
       </c>
       <c r="P70" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q70">
         <v>3.75</v>
@@ -15767,7 +15782,7 @@
         <v>1</v>
       </c>
       <c r="AP70">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AQ70">
         <v>1.5</v>
@@ -16101,7 +16116,7 @@
         <v>147</v>
       </c>
       <c r="P72" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16307,7 +16322,7 @@
         <v>90</v>
       </c>
       <c r="P73" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q73">
         <v>4.33</v>
@@ -16513,7 +16528,7 @@
         <v>90</v>
       </c>
       <c r="P74" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q74">
         <v>2.4</v>
@@ -16594,7 +16609,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ74">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR74">
         <v>1.85</v>
@@ -16719,7 +16734,7 @@
         <v>148</v>
       </c>
       <c r="P75" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q75">
         <v>3.5</v>
@@ -16925,7 +16940,7 @@
         <v>149</v>
       </c>
       <c r="P76" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q76">
         <v>2.88</v>
@@ -17212,7 +17227,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ77">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR77">
         <v>1.29</v>
@@ -17543,7 +17558,7 @@
         <v>151</v>
       </c>
       <c r="P79" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17749,7 +17764,7 @@
         <v>152</v>
       </c>
       <c r="P80" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q80">
         <v>2.05</v>
@@ -17827,7 +17842,7 @@
         <v>1.5</v>
       </c>
       <c r="AP80">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AQ80">
         <v>1.13</v>
@@ -17955,7 +17970,7 @@
         <v>90</v>
       </c>
       <c r="P81" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q81">
         <v>4.33</v>
@@ -18033,7 +18048,7 @@
         <v>2.25</v>
       </c>
       <c r="AP81">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ81">
         <v>1.64</v>
@@ -18448,7 +18463,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ83">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR83">
         <v>1.6</v>
@@ -18779,7 +18794,7 @@
         <v>90</v>
       </c>
       <c r="P85" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q85">
         <v>3.1</v>
@@ -18985,7 +19000,7 @@
         <v>156</v>
       </c>
       <c r="P86" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -19809,7 +19824,7 @@
         <v>90</v>
       </c>
       <c r="P90" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q90">
         <v>2.38</v>
@@ -19887,7 +19902,7 @@
         <v>0.2</v>
       </c>
       <c r="AP90">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AQ90">
         <v>1.07</v>
@@ -20093,10 +20108,10 @@
         <v>1</v>
       </c>
       <c r="AP91">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ91">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR91">
         <v>1.25</v>
@@ -20221,7 +20236,7 @@
         <v>160</v>
       </c>
       <c r="P92" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20508,7 +20523,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ93">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR93">
         <v>1.43</v>
@@ -20839,7 +20854,7 @@
         <v>162</v>
       </c>
       <c r="P95" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q95">
         <v>1.9</v>
@@ -20917,7 +20932,7 @@
         <v>1</v>
       </c>
       <c r="AP95">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AQ95">
         <v>1.29</v>
@@ -21045,7 +21060,7 @@
         <v>163</v>
       </c>
       <c r="P96" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q96">
         <v>2.75</v>
@@ -21457,7 +21472,7 @@
         <v>90</v>
       </c>
       <c r="P98" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q98">
         <v>4.75</v>
@@ -22156,7 +22171,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ101">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR101">
         <v>1.04</v>
@@ -22359,7 +22374,7 @@
         <v>1.17</v>
       </c>
       <c r="AP102">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ102">
         <v>1.47</v>
@@ -22693,7 +22708,7 @@
         <v>167</v>
       </c>
       <c r="P104" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q104">
         <v>2.25</v>
@@ -22980,7 +22995,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ105">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR105">
         <v>1.41</v>
@@ -23183,7 +23198,7 @@
         <v>1.25</v>
       </c>
       <c r="AP106">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AQ106">
         <v>0.87</v>
@@ -23517,7 +23532,7 @@
         <v>90</v>
       </c>
       <c r="P108" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q108">
         <v>4.5</v>
@@ -23598,7 +23613,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ108">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR108">
         <v>1.07</v>
@@ -24341,7 +24356,7 @@
         <v>173</v>
       </c>
       <c r="P112" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q112">
         <v>3.5</v>
@@ -24753,7 +24768,7 @@
         <v>90</v>
       </c>
       <c r="P114" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q114">
         <v>2.85</v>
@@ -25165,7 +25180,7 @@
         <v>175</v>
       </c>
       <c r="P116" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q116">
         <v>2.4</v>
@@ -25243,7 +25258,7 @@
         <v>1.2</v>
       </c>
       <c r="AP116">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AQ116">
         <v>1.57</v>
@@ -25577,7 +25592,7 @@
         <v>90</v>
       </c>
       <c r="P118" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q118">
         <v>4</v>
@@ -25861,7 +25876,7 @@
         <v>0.5</v>
       </c>
       <c r="AP119">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ119">
         <v>1</v>
@@ -26070,7 +26085,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ120">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR120">
         <v>1.24</v>
@@ -26195,7 +26210,7 @@
         <v>178</v>
       </c>
       <c r="P121" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q121">
         <v>2.88</v>
@@ -26273,7 +26288,7 @@
         <v>1.14</v>
       </c>
       <c r="AP121">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AQ121">
         <v>1</v>
@@ -26688,7 +26703,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ123">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR123">
         <v>1.44</v>
@@ -27715,7 +27730,7 @@
         <v>1</v>
       </c>
       <c r="AP128">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AQ128">
         <v>1.07</v>
@@ -28130,7 +28145,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ130">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR130">
         <v>1.89</v>
@@ -28873,7 +28888,7 @@
         <v>90</v>
       </c>
       <c r="P134" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q134">
         <v>3.2</v>
@@ -29079,7 +29094,7 @@
         <v>90</v>
       </c>
       <c r="P135" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q135">
         <v>5</v>
@@ -29981,7 +29996,7 @@
         <v>1.33</v>
       </c>
       <c r="AP139">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ139">
         <v>1.21</v>
@@ -30315,7 +30330,7 @@
         <v>189</v>
       </c>
       <c r="P141" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q141">
         <v>2.8</v>
@@ -30599,7 +30614,7 @@
         <v>2.13</v>
       </c>
       <c r="AP142">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AQ142">
         <v>1.64</v>
@@ -31014,7 +31029,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ144">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR144">
         <v>1.43</v>
@@ -31139,7 +31154,7 @@
         <v>192</v>
       </c>
       <c r="P145" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q145">
         <v>2.75</v>
@@ -31345,7 +31360,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q146">
         <v>3.75</v>
@@ -31551,7 +31566,7 @@
         <v>129</v>
       </c>
       <c r="P147" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q147">
         <v>3.75</v>
@@ -31757,7 +31772,7 @@
         <v>90</v>
       </c>
       <c r="P148" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q148">
         <v>2.4</v>
@@ -31838,7 +31853,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ148">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR148">
         <v>1.89</v>
@@ -31963,7 +31978,7 @@
         <v>90</v>
       </c>
       <c r="P149" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q149">
         <v>3.1</v>
@@ -32247,7 +32262,7 @@
         <v>1</v>
       </c>
       <c r="AP150">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AQ150">
         <v>0.93</v>
@@ -32375,7 +32390,7 @@
         <v>194</v>
       </c>
       <c r="P151" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q151">
         <v>1.62</v>
@@ -32662,7 +32677,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ152">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR152">
         <v>1.6</v>
@@ -32787,7 +32802,7 @@
         <v>95</v>
       </c>
       <c r="P153" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q153">
         <v>2.63</v>
@@ -33611,7 +33626,7 @@
         <v>197</v>
       </c>
       <c r="P157" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q157">
         <v>2.7</v>
@@ -33817,7 +33832,7 @@
         <v>96</v>
       </c>
       <c r="P158" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q158">
         <v>2.55</v>
@@ -33898,7 +33913,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ158">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR158">
         <v>1.25</v>
@@ -34023,7 +34038,7 @@
         <v>198</v>
       </c>
       <c r="P159" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q159">
         <v>3.3</v>
@@ -34229,7 +34244,7 @@
         <v>90</v>
       </c>
       <c r="P160" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q160">
         <v>2.75</v>
@@ -34307,7 +34322,7 @@
         <v>0.5</v>
       </c>
       <c r="AP160">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AQ160">
         <v>1</v>
@@ -34925,10 +34940,10 @@
         <v>1.38</v>
       </c>
       <c r="AP163">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AQ163">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR163">
         <v>1.75</v>
@@ -35671,7 +35686,7 @@
         <v>109</v>
       </c>
       <c r="P167" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q167">
         <v>3.35</v>
@@ -35752,7 +35767,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ167">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR167">
         <v>1.14</v>
@@ -36083,7 +36098,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q169">
         <v>2.8</v>
@@ -36289,7 +36304,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q170">
         <v>3</v>
@@ -36701,7 +36716,7 @@
         <v>90</v>
       </c>
       <c r="P172" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q172">
         <v>2.63</v>
@@ -36779,7 +36794,7 @@
         <v>1.22</v>
       </c>
       <c r="AP172">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ172">
         <v>1.13</v>
@@ -36907,7 +36922,7 @@
         <v>207</v>
       </c>
       <c r="P173" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q173">
         <v>2.3</v>
@@ -37194,7 +37209,7 @@
         <v>2</v>
       </c>
       <c r="AQ174">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR174">
         <v>1.67</v>
@@ -37937,7 +37952,7 @@
         <v>90</v>
       </c>
       <c r="P178" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q178">
         <v>3.25</v>
@@ -38015,7 +38030,7 @@
         <v>1.33</v>
       </c>
       <c r="AP178">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AQ178">
         <v>1.57</v>
@@ -38224,7 +38239,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ179">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR179">
         <v>1.86</v>
@@ -38349,7 +38364,7 @@
         <v>212</v>
       </c>
       <c r="P180" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q180">
         <v>2.2</v>
@@ -38427,7 +38442,7 @@
         <v>1.44</v>
       </c>
       <c r="AP180">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AQ180">
         <v>0.93</v>
@@ -38555,7 +38570,7 @@
         <v>90</v>
       </c>
       <c r="P181" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q181">
         <v>3.25</v>
@@ -39666,7 +39681,7 @@
         <v>2</v>
       </c>
       <c r="AQ186">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR186">
         <v>1.69</v>
@@ -39791,7 +39806,7 @@
         <v>90</v>
       </c>
       <c r="P187" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q187">
         <v>2.55</v>
@@ -39997,7 +40012,7 @@
         <v>215</v>
       </c>
       <c r="P188" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q188">
         <v>4.5</v>
@@ -40281,7 +40296,7 @@
         <v>0.44</v>
       </c>
       <c r="AP189">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ189">
         <v>0.5</v>
@@ -40615,7 +40630,7 @@
         <v>90</v>
       </c>
       <c r="P191" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q191">
         <v>2.75</v>
@@ -40821,7 +40836,7 @@
         <v>90</v>
       </c>
       <c r="P192" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q192">
         <v>3.25</v>
@@ -41108,7 +41123,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ193">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR193">
         <v>1.24</v>
@@ -41314,7 +41329,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ194">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR194">
         <v>1.83</v>
@@ -41439,7 +41454,7 @@
         <v>214</v>
       </c>
       <c r="P195" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q195">
         <v>4.75</v>
@@ -41645,7 +41660,7 @@
         <v>90</v>
       </c>
       <c r="P196" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q196">
         <v>3.65</v>
@@ -41851,7 +41866,7 @@
         <v>218</v>
       </c>
       <c r="P197" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q197">
         <v>1.94</v>
@@ -41929,7 +41944,7 @@
         <v>0.6</v>
       </c>
       <c r="AP197">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AQ197">
         <v>0.53</v>
@@ -42263,7 +42278,7 @@
         <v>90</v>
       </c>
       <c r="P199" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q199">
         <v>3.75</v>
@@ -42341,7 +42356,7 @@
         <v>1.2</v>
       </c>
       <c r="AP199">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AQ199">
         <v>1.29</v>
@@ -42753,7 +42768,7 @@
         <v>1.36</v>
       </c>
       <c r="AP201">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ201">
         <v>1.5</v>
@@ -43293,7 +43308,7 @@
         <v>160</v>
       </c>
       <c r="P204" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q204">
         <v>3</v>
@@ -43499,7 +43514,7 @@
         <v>90</v>
       </c>
       <c r="P205" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q205">
         <v>2.75</v>
@@ -43911,7 +43926,7 @@
         <v>90</v>
       </c>
       <c r="P207" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q207">
         <v>3.8</v>
@@ -43992,7 +44007,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ207">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR207">
         <v>1.58</v>
@@ -44610,7 +44625,7 @@
         <v>2</v>
       </c>
       <c r="AQ210">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR210">
         <v>1.74</v>
@@ -45147,7 +45162,7 @@
         <v>226</v>
       </c>
       <c r="P213" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q213">
         <v>3.75</v>
@@ -45559,7 +45574,7 @@
         <v>228</v>
       </c>
       <c r="P215" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="Q215">
         <v>2.95</v>
@@ -45637,10 +45652,10 @@
         <v>0.83</v>
       </c>
       <c r="AP215">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AQ215">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR215">
         <v>1.26</v>
@@ -45765,7 +45780,7 @@
         <v>90</v>
       </c>
       <c r="P216" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="Q216">
         <v>1.96</v>
@@ -45843,7 +45858,7 @@
         <v>1.33</v>
       </c>
       <c r="AP216">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AQ216">
         <v>1.47</v>
@@ -46383,7 +46398,7 @@
         <v>229</v>
       </c>
       <c r="P219" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q219">
         <v>4.3</v>
@@ -46873,7 +46888,7 @@
         <v>1</v>
       </c>
       <c r="AP221">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ221">
         <v>0.87</v>
@@ -47001,7 +47016,7 @@
         <v>90</v>
       </c>
       <c r="P222" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q222">
         <v>2.7</v>
@@ -47207,7 +47222,7 @@
         <v>231</v>
       </c>
       <c r="P223" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="Q223">
         <v>3.65</v>
@@ -47413,7 +47428,7 @@
         <v>232</v>
       </c>
       <c r="P224" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="Q224">
         <v>5.2</v>
@@ -47494,7 +47509,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ224">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR224">
         <v>1.63</v>
@@ -47697,7 +47712,7 @@
         <v>1.08</v>
       </c>
       <c r="AP225">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AQ225">
         <v>1</v>
@@ -47825,7 +47840,7 @@
         <v>221</v>
       </c>
       <c r="P226" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="Q226">
         <v>4.4</v>
@@ -48031,7 +48046,7 @@
         <v>234</v>
       </c>
       <c r="P227" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="Q227">
         <v>2.7</v>
@@ -48649,7 +48664,7 @@
         <v>90</v>
       </c>
       <c r="P230" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="Q230">
         <v>3.04</v>
@@ -48933,7 +48948,7 @@
         <v>1.46</v>
       </c>
       <c r="AP231">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AQ231">
         <v>1.47</v>
@@ -49267,7 +49282,7 @@
         <v>238</v>
       </c>
       <c r="P233" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="Q233">
         <v>3.1</v>
@@ -49473,7 +49488,7 @@
         <v>239</v>
       </c>
       <c r="P234" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="Q234">
         <v>1.85</v>
@@ -49885,7 +49900,7 @@
         <v>241</v>
       </c>
       <c r="P236" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="Q236">
         <v>3.7</v>
@@ -49966,7 +49981,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ236">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR236">
         <v>1.04</v>
@@ -50503,7 +50518,7 @@
         <v>243</v>
       </c>
       <c r="P239" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="Q239">
         <v>3.1</v>
@@ -50584,7 +50599,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ239">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR239">
         <v>1.25</v>
@@ -50993,7 +51008,7 @@
         <v>1.46</v>
       </c>
       <c r="AP241">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ241">
         <v>1.57</v>
@@ -51121,7 +51136,7 @@
         <v>245</v>
       </c>
       <c r="P242" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="Q242">
         <v>3.6</v>
@@ -51202,7 +51217,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ242">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR242">
         <v>1.6</v>
@@ -51611,7 +51626,7 @@
         <v>0.92</v>
       </c>
       <c r="AP244">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AQ244">
         <v>0.87</v>
@@ -51945,7 +51960,7 @@
         <v>114</v>
       </c>
       <c r="P246" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q246">
         <v>3.6</v>
@@ -52975,7 +52990,7 @@
         <v>251</v>
       </c>
       <c r="P251" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="Q251">
         <v>4.75</v>
@@ -53387,7 +53402,7 @@
         <v>253</v>
       </c>
       <c r="P253" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="Q253">
         <v>2.2</v>
@@ -53686,31 +53701,31 @@
         <v>2.86</v>
       </c>
       <c r="AU254">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AV254">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AW254">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AX254">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AY254">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AZ254">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="BA254">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BB254">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BC254">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="BD254">
         <v>1.3</v>
@@ -53892,31 +53907,31 @@
         <v>2.51</v>
       </c>
       <c r="AU255">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AV255">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AW255">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AX255">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AY255">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AZ255">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="BA255">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="BB255">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BC255">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="BD255">
         <v>1.78</v>
@@ -54002,10 +54017,10 @@
         <v>2</v>
       </c>
       <c r="O256" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="P256" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q256">
         <v>3.9</v>
@@ -54098,31 +54113,31 @@
         <v>2.77</v>
       </c>
       <c r="AU256">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AV256">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AW256">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AX256">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AY256">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AZ256">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="BA256">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BB256">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="BC256">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="BD256">
         <v>2.15</v>
@@ -54211,7 +54226,7 @@
         <v>133</v>
       </c>
       <c r="P257" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="Q257">
         <v>2.65</v>
@@ -54304,31 +54319,31 @@
         <v>2.67</v>
       </c>
       <c r="AU257">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AV257">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AW257">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AX257">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AY257">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AZ257">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="BA257">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BB257">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BC257">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="BD257">
         <v>1.58</v>
@@ -54510,31 +54525,31 @@
         <v>3.01</v>
       </c>
       <c r="AU258">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AV258">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AW258">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AX258">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AY258">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AZ258">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BA258">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="BB258">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BC258">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="BD258">
         <v>1.41</v>
@@ -54574,6 +54589,624 @@
       </c>
       <c r="BP258">
         <v>1.29</v>
+      </c>
+    </row>
+    <row r="259" spans="1:68">
+      <c r="A259" s="1">
+        <v>258</v>
+      </c>
+      <c r="B259">
+        <v>7469124</v>
+      </c>
+      <c r="C259" t="s">
+        <v>68</v>
+      </c>
+      <c r="D259" t="s">
+        <v>69</v>
+      </c>
+      <c r="E259" s="2">
+        <v>45752.375</v>
+      </c>
+      <c r="F259">
+        <v>29</v>
+      </c>
+      <c r="G259" t="s">
+        <v>76</v>
+      </c>
+      <c r="H259" t="s">
+        <v>78</v>
+      </c>
+      <c r="I259">
+        <v>0</v>
+      </c>
+      <c r="J259">
+        <v>1</v>
+      </c>
+      <c r="K259">
+        <v>1</v>
+      </c>
+      <c r="L259">
+        <v>2</v>
+      </c>
+      <c r="M259">
+        <v>2</v>
+      </c>
+      <c r="N259">
+        <v>4</v>
+      </c>
+      <c r="O259" t="s">
+        <v>256</v>
+      </c>
+      <c r="P259" t="s">
+        <v>353</v>
+      </c>
+      <c r="Q259">
+        <v>4.75</v>
+      </c>
+      <c r="R259">
+        <v>2.2</v>
+      </c>
+      <c r="S259">
+        <v>2.4</v>
+      </c>
+      <c r="T259">
+        <v>1.4</v>
+      </c>
+      <c r="U259">
+        <v>2.75</v>
+      </c>
+      <c r="V259">
+        <v>3</v>
+      </c>
+      <c r="W259">
+        <v>1.36</v>
+      </c>
+      <c r="X259">
+        <v>8</v>
+      </c>
+      <c r="Y259">
+        <v>1.08</v>
+      </c>
+      <c r="Z259">
+        <v>4.6</v>
+      </c>
+      <c r="AA259">
+        <v>3.64</v>
+      </c>
+      <c r="AB259">
+        <v>1.74</v>
+      </c>
+      <c r="AC259">
+        <v>1.06</v>
+      </c>
+      <c r="AD259">
+        <v>8.5</v>
+      </c>
+      <c r="AE259">
+        <v>1.33</v>
+      </c>
+      <c r="AF259">
+        <v>3.25</v>
+      </c>
+      <c r="AG259">
+        <v>1.98</v>
+      </c>
+      <c r="AH259">
+        <v>1.77</v>
+      </c>
+      <c r="AI259">
+        <v>1.83</v>
+      </c>
+      <c r="AJ259">
+        <v>1.83</v>
+      </c>
+      <c r="AK259">
+        <v>1.87</v>
+      </c>
+      <c r="AL259">
+        <v>1.29</v>
+      </c>
+      <c r="AM259">
+        <v>1.23</v>
+      </c>
+      <c r="AN259">
+        <v>0.86</v>
+      </c>
+      <c r="AO259">
+        <v>1.69</v>
+      </c>
+      <c r="AP259">
+        <v>0.87</v>
+      </c>
+      <c r="AQ259">
+        <v>1.64</v>
+      </c>
+      <c r="AR259">
+        <v>1.3</v>
+      </c>
+      <c r="AS259">
+        <v>1.36</v>
+      </c>
+      <c r="AT259">
+        <v>2.66</v>
+      </c>
+      <c r="AU259">
+        <v>7</v>
+      </c>
+      <c r="AV259">
+        <v>6</v>
+      </c>
+      <c r="AW259">
+        <v>5</v>
+      </c>
+      <c r="AX259">
+        <v>10</v>
+      </c>
+      <c r="AY259">
+        <v>12</v>
+      </c>
+      <c r="AZ259">
+        <v>16</v>
+      </c>
+      <c r="BA259">
+        <v>6</v>
+      </c>
+      <c r="BB259">
+        <v>8</v>
+      </c>
+      <c r="BC259">
+        <v>14</v>
+      </c>
+      <c r="BD259">
+        <v>2.4</v>
+      </c>
+      <c r="BE259">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="BF259">
+        <v>1.8</v>
+      </c>
+      <c r="BG259">
+        <v>1.3</v>
+      </c>
+      <c r="BH259">
+        <v>3.1</v>
+      </c>
+      <c r="BI259">
+        <v>1.57</v>
+      </c>
+      <c r="BJ259">
+        <v>2.15</v>
+      </c>
+      <c r="BK259">
+        <v>2</v>
+      </c>
+      <c r="BL259">
+        <v>1.68</v>
+      </c>
+      <c r="BM259">
+        <v>2.7</v>
+      </c>
+      <c r="BN259">
+        <v>1.38</v>
+      </c>
+      <c r="BO259">
+        <v>3.8</v>
+      </c>
+      <c r="BP259">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="260" spans="1:68">
+      <c r="A260" s="1">
+        <v>259</v>
+      </c>
+      <c r="B260">
+        <v>7469119</v>
+      </c>
+      <c r="C260" t="s">
+        <v>68</v>
+      </c>
+      <c r="D260" t="s">
+        <v>69</v>
+      </c>
+      <c r="E260" s="2">
+        <v>45752.625</v>
+      </c>
+      <c r="F260">
+        <v>29</v>
+      </c>
+      <c r="G260" t="s">
+        <v>86</v>
+      </c>
+      <c r="H260" t="s">
+        <v>82</v>
+      </c>
+      <c r="I260">
+        <v>1</v>
+      </c>
+      <c r="J260">
+        <v>0</v>
+      </c>
+      <c r="K260">
+        <v>1</v>
+      </c>
+      <c r="L260">
+        <v>5</v>
+      </c>
+      <c r="M260">
+        <v>0</v>
+      </c>
+      <c r="N260">
+        <v>5</v>
+      </c>
+      <c r="O260" t="s">
+        <v>257</v>
+      </c>
+      <c r="P260" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q260">
+        <v>1.91</v>
+      </c>
+      <c r="R260">
+        <v>2.5</v>
+      </c>
+      <c r="S260">
+        <v>6.5</v>
+      </c>
+      <c r="T260">
+        <v>1.3</v>
+      </c>
+      <c r="U260">
+        <v>3.4</v>
+      </c>
+      <c r="V260">
+        <v>2.5</v>
+      </c>
+      <c r="W260">
+        <v>1.5</v>
+      </c>
+      <c r="X260">
+        <v>6</v>
+      </c>
+      <c r="Y260">
+        <v>1.13</v>
+      </c>
+      <c r="Z260">
+        <v>1.47</v>
+      </c>
+      <c r="AA260">
+        <v>4.4</v>
+      </c>
+      <c r="AB260">
+        <v>6.2</v>
+      </c>
+      <c r="AC260">
+        <v>1.03</v>
+      </c>
+      <c r="AD260">
+        <v>11</v>
+      </c>
+      <c r="AE260">
+        <v>1.2</v>
+      </c>
+      <c r="AF260">
+        <v>4.33</v>
+      </c>
+      <c r="AG260">
+        <v>1.65</v>
+      </c>
+      <c r="AH260">
+        <v>2.05</v>
+      </c>
+      <c r="AI260">
+        <v>1.83</v>
+      </c>
+      <c r="AJ260">
+        <v>1.83</v>
+      </c>
+      <c r="AK260">
+        <v>1.11</v>
+      </c>
+      <c r="AL260">
+        <v>1.19</v>
+      </c>
+      <c r="AM260">
+        <v>2.7</v>
+      </c>
+      <c r="AN260">
+        <v>2.64</v>
+      </c>
+      <c r="AO260">
+        <v>0.86</v>
+      </c>
+      <c r="AP260">
+        <v>2.67</v>
+      </c>
+      <c r="AQ260">
+        <v>0.8</v>
+      </c>
+      <c r="AR260">
+        <v>1.78</v>
+      </c>
+      <c r="AS260">
+        <v>1.45</v>
+      </c>
+      <c r="AT260">
+        <v>3.23</v>
+      </c>
+      <c r="AU260">
+        <v>-1</v>
+      </c>
+      <c r="AV260">
+        <v>-1</v>
+      </c>
+      <c r="AW260">
+        <v>-1</v>
+      </c>
+      <c r="AX260">
+        <v>-1</v>
+      </c>
+      <c r="AY260">
+        <v>-1</v>
+      </c>
+      <c r="AZ260">
+        <v>-1</v>
+      </c>
+      <c r="BA260">
+        <v>-1</v>
+      </c>
+      <c r="BB260">
+        <v>-1</v>
+      </c>
+      <c r="BC260">
+        <v>-1</v>
+      </c>
+      <c r="BD260">
+        <v>1.3</v>
+      </c>
+      <c r="BE260">
+        <v>10</v>
+      </c>
+      <c r="BF260">
+        <v>4.45</v>
+      </c>
+      <c r="BG260">
+        <v>1.24</v>
+      </c>
+      <c r="BH260">
+        <v>3.5</v>
+      </c>
+      <c r="BI260">
+        <v>1.46</v>
+      </c>
+      <c r="BJ260">
+        <v>2.45</v>
+      </c>
+      <c r="BK260">
+        <v>1.8</v>
+      </c>
+      <c r="BL260">
+        <v>1.83</v>
+      </c>
+      <c r="BM260">
+        <v>2.37</v>
+      </c>
+      <c r="BN260">
+        <v>1.49</v>
+      </c>
+      <c r="BO260">
+        <v>3.25</v>
+      </c>
+      <c r="BP260">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="261" spans="1:68">
+      <c r="A261" s="1">
+        <v>260</v>
+      </c>
+      <c r="B261">
+        <v>7469126</v>
+      </c>
+      <c r="C261" t="s">
+        <v>68</v>
+      </c>
+      <c r="D261" t="s">
+        <v>69</v>
+      </c>
+      <c r="E261" s="2">
+        <v>45752.625</v>
+      </c>
+      <c r="F261">
+        <v>29</v>
+      </c>
+      <c r="G261" t="s">
+        <v>79</v>
+      </c>
+      <c r="H261" t="s">
+        <v>87</v>
+      </c>
+      <c r="I261">
+        <v>2</v>
+      </c>
+      <c r="J261">
+        <v>2</v>
+      </c>
+      <c r="K261">
+        <v>4</v>
+      </c>
+      <c r="L261">
+        <v>2</v>
+      </c>
+      <c r="M261">
+        <v>2</v>
+      </c>
+      <c r="N261">
+        <v>4</v>
+      </c>
+      <c r="O261" t="s">
+        <v>258</v>
+      </c>
+      <c r="P261" t="s">
+        <v>354</v>
+      </c>
+      <c r="Q261">
+        <v>2.63</v>
+      </c>
+      <c r="R261">
+        <v>2.05</v>
+      </c>
+      <c r="S261">
+        <v>4.75</v>
+      </c>
+      <c r="T261">
+        <v>1.5</v>
+      </c>
+      <c r="U261">
+        <v>2.5</v>
+      </c>
+      <c r="V261">
+        <v>3.4</v>
+      </c>
+      <c r="W261">
+        <v>1.3</v>
+      </c>
+      <c r="X261">
+        <v>10</v>
+      </c>
+      <c r="Y261">
+        <v>1.06</v>
+      </c>
+      <c r="Z261">
+        <v>1.83</v>
+      </c>
+      <c r="AA261">
+        <v>3.39</v>
+      </c>
+      <c r="AB261">
+        <v>4.4</v>
+      </c>
+      <c r="AC261">
+        <v>1.08</v>
+      </c>
+      <c r="AD261">
+        <v>7.5</v>
+      </c>
+      <c r="AE261">
+        <v>1.4</v>
+      </c>
+      <c r="AF261">
+        <v>2.88</v>
+      </c>
+      <c r="AG261">
+        <v>2.1</v>
+      </c>
+      <c r="AH261">
+        <v>1.6</v>
+      </c>
+      <c r="AI261">
+        <v>2</v>
+      </c>
+      <c r="AJ261">
+        <v>1.73</v>
+      </c>
+      <c r="AK261">
+        <v>1.23</v>
+      </c>
+      <c r="AL261">
+        <v>1.31</v>
+      </c>
+      <c r="AM261">
+        <v>1.82</v>
+      </c>
+      <c r="AN261">
+        <v>1.31</v>
+      </c>
+      <c r="AO261">
+        <v>0.86</v>
+      </c>
+      <c r="AP261">
+        <v>1.29</v>
+      </c>
+      <c r="AQ261">
+        <v>0.87</v>
+      </c>
+      <c r="AR261">
+        <v>1.71</v>
+      </c>
+      <c r="AS261">
+        <v>1.18</v>
+      </c>
+      <c r="AT261">
+        <v>2.89</v>
+      </c>
+      <c r="AU261">
+        <v>-1</v>
+      </c>
+      <c r="AV261">
+        <v>-1</v>
+      </c>
+      <c r="AW261">
+        <v>-1</v>
+      </c>
+      <c r="AX261">
+        <v>-1</v>
+      </c>
+      <c r="AY261">
+        <v>-1</v>
+      </c>
+      <c r="AZ261">
+        <v>-1</v>
+      </c>
+      <c r="BA261">
+        <v>-1</v>
+      </c>
+      <c r="BB261">
+        <v>-1</v>
+      </c>
+      <c r="BC261">
+        <v>-1</v>
+      </c>
+      <c r="BD261">
+        <v>1.47</v>
+      </c>
+      <c r="BE261">
+        <v>8.9</v>
+      </c>
+      <c r="BF261">
+        <v>3.32</v>
+      </c>
+      <c r="BG261">
+        <v>1.27</v>
+      </c>
+      <c r="BH261">
+        <v>3.25</v>
+      </c>
+      <c r="BI261">
+        <v>1.51</v>
+      </c>
+      <c r="BJ261">
+        <v>2.3</v>
+      </c>
+      <c r="BK261">
+        <v>1.9</v>
+      </c>
+      <c r="BL261">
+        <v>1.75</v>
+      </c>
+      <c r="BM261">
+        <v>2.55</v>
+      </c>
+      <c r="BN261">
+        <v>1.43</v>
+      </c>
+      <c r="BO261">
+        <v>3.6</v>
+      </c>
+      <c r="BP261">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
@@ -54937,31 +54937,31 @@
         <v>3.23</v>
       </c>
       <c r="AU260">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AV260">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AW260">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AX260">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AY260">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AZ260">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA260">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BB260">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BC260">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BD260">
         <v>1.3</v>
@@ -55143,31 +55143,31 @@
         <v>2.89</v>
       </c>
       <c r="AU261">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AV261">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AW261">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AX261">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AY261">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AZ261">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="BA261">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BB261">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BC261">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="BD261">
         <v>1.47</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1628" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1634" uniqueCount="357">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -793,6 +793,9 @@
     <t>['12', '40']</t>
   </si>
   <si>
+    <t>['69', '82', '90+7']</t>
+  </si>
+  <si>
     <t>['16', '45+2']</t>
   </si>
   <si>
@@ -1079,6 +1082,9 @@
   </si>
   <si>
     <t>['28', '34']</t>
+  </si>
+  <si>
+    <t>['90+6']</t>
   </si>
 </sst>
 </file>
@@ -1440,7 +1446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP261"/>
+  <dimension ref="A1:BP262"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1696,7 +1702,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q2">
         <v>2.4</v>
@@ -2108,7 +2114,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q4">
         <v>3.6</v>
@@ -2186,7 +2192,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ4">
         <v>1.13</v>
@@ -2932,7 +2938,7 @@
         <v>90</v>
       </c>
       <c r="P8" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q8">
         <v>3.1</v>
@@ -3344,7 +3350,7 @@
         <v>94</v>
       </c>
       <c r="P10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q10">
         <v>2.6</v>
@@ -3837,7 +3843,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ12">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3962,7 +3968,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q13">
         <v>3.1</v>
@@ -4580,7 +4586,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q16">
         <v>2.63</v>
@@ -4786,7 +4792,7 @@
         <v>99</v>
       </c>
       <c r="P17" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -5816,7 +5822,7 @@
         <v>103</v>
       </c>
       <c r="P22" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -6100,7 +6106,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ23">
         <v>1</v>
@@ -6228,7 +6234,7 @@
         <v>105</v>
       </c>
       <c r="P24" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q24">
         <v>2.62</v>
@@ -7052,7 +7058,7 @@
         <v>108</v>
       </c>
       <c r="P28" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q28">
         <v>2.6</v>
@@ -8494,7 +8500,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q35">
         <v>3.3</v>
@@ -8575,7 +8581,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ35">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR35">
         <v>1.69</v>
@@ -8700,7 +8706,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q36">
         <v>3.1</v>
@@ -8906,7 +8912,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q37">
         <v>3.4</v>
@@ -9112,7 +9118,7 @@
         <v>90</v>
       </c>
       <c r="P38" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q38">
         <v>3.2</v>
@@ -9318,7 +9324,7 @@
         <v>90</v>
       </c>
       <c r="P39" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q39">
         <v>3.4</v>
@@ -9730,7 +9736,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q41">
         <v>2.5</v>
@@ -9936,7 +9942,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q42">
         <v>3.25</v>
@@ -10014,7 +10020,7 @@
         <v>1</v>
       </c>
       <c r="AP42">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ42">
         <v>0.8</v>
@@ -10142,7 +10148,7 @@
         <v>90</v>
       </c>
       <c r="P43" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q43">
         <v>2.75</v>
@@ -11665,7 +11671,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ50">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR50">
         <v>1.61</v>
@@ -12280,7 +12286,7 @@
         <v>2</v>
       </c>
       <c r="AP53">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ53">
         <v>0.87</v>
@@ -12408,7 +12414,7 @@
         <v>129</v>
       </c>
       <c r="P54" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q54">
         <v>2.55</v>
@@ -12614,7 +12620,7 @@
         <v>130</v>
       </c>
       <c r="P55" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q55">
         <v>2.55</v>
@@ -13026,7 +13032,7 @@
         <v>132</v>
       </c>
       <c r="P57" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -13438,7 +13444,7 @@
         <v>134</v>
       </c>
       <c r="P59" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q59">
         <v>2.62</v>
@@ -13644,7 +13650,7 @@
         <v>135</v>
       </c>
       <c r="P60" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q60">
         <v>2.88</v>
@@ -14056,7 +14062,7 @@
         <v>137</v>
       </c>
       <c r="P62" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q62">
         <v>3.6</v>
@@ -14262,7 +14268,7 @@
         <v>138</v>
       </c>
       <c r="P63" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q63">
         <v>3.75</v>
@@ -15164,7 +15170,7 @@
         <v>0.25</v>
       </c>
       <c r="AP67">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ67">
         <v>1.07</v>
@@ -15292,7 +15298,7 @@
         <v>143</v>
       </c>
       <c r="P68" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15498,7 +15504,7 @@
         <v>144</v>
       </c>
       <c r="P69" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15704,7 +15710,7 @@
         <v>145</v>
       </c>
       <c r="P70" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q70">
         <v>3.75</v>
@@ -15991,7 +15997,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ71">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR71">
         <v>1.24</v>
@@ -16116,7 +16122,7 @@
         <v>147</v>
       </c>
       <c r="P72" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16322,7 +16328,7 @@
         <v>90</v>
       </c>
       <c r="P73" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q73">
         <v>4.33</v>
@@ -16528,7 +16534,7 @@
         <v>90</v>
       </c>
       <c r="P74" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q74">
         <v>2.4</v>
@@ -16734,7 +16740,7 @@
         <v>148</v>
       </c>
       <c r="P75" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q75">
         <v>3.5</v>
@@ -16940,7 +16946,7 @@
         <v>149</v>
       </c>
       <c r="P76" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q76">
         <v>2.88</v>
@@ -17558,7 +17564,7 @@
         <v>151</v>
       </c>
       <c r="P79" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17764,7 +17770,7 @@
         <v>152</v>
       </c>
       <c r="P80" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q80">
         <v>2.05</v>
@@ -17970,7 +17976,7 @@
         <v>90</v>
       </c>
       <c r="P81" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q81">
         <v>4.33</v>
@@ -18460,7 +18466,7 @@
         <v>0.8</v>
       </c>
       <c r="AP83">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ83">
         <v>0.87</v>
@@ -18794,7 +18800,7 @@
         <v>90</v>
       </c>
       <c r="P85" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q85">
         <v>3.1</v>
@@ -19000,7 +19006,7 @@
         <v>156</v>
       </c>
       <c r="P86" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -19493,7 +19499,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ88">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR88">
         <v>1.77</v>
@@ -19824,7 +19830,7 @@
         <v>90</v>
       </c>
       <c r="P90" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q90">
         <v>2.38</v>
@@ -20236,7 +20242,7 @@
         <v>160</v>
       </c>
       <c r="P92" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20854,7 +20860,7 @@
         <v>162</v>
       </c>
       <c r="P95" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q95">
         <v>1.9</v>
@@ -21060,7 +21066,7 @@
         <v>163</v>
       </c>
       <c r="P96" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q96">
         <v>2.75</v>
@@ -21472,7 +21478,7 @@
         <v>90</v>
       </c>
       <c r="P98" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q98">
         <v>4.75</v>
@@ -21962,7 +21968,7 @@
         <v>0.6</v>
       </c>
       <c r="AP100">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ100">
         <v>0.53</v>
@@ -22708,7 +22714,7 @@
         <v>167</v>
       </c>
       <c r="P104" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q104">
         <v>2.25</v>
@@ -23532,7 +23538,7 @@
         <v>90</v>
       </c>
       <c r="P108" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q108">
         <v>4.5</v>
@@ -24356,7 +24362,7 @@
         <v>173</v>
       </c>
       <c r="P112" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q112">
         <v>3.5</v>
@@ -24768,7 +24774,7 @@
         <v>90</v>
       </c>
       <c r="P114" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q114">
         <v>2.85</v>
@@ -25180,7 +25186,7 @@
         <v>175</v>
       </c>
       <c r="P116" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q116">
         <v>2.4</v>
@@ -25261,7 +25267,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ116">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR116">
         <v>1.94</v>
@@ -25592,7 +25598,7 @@
         <v>90</v>
       </c>
       <c r="P118" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q118">
         <v>4</v>
@@ -26210,7 +26216,7 @@
         <v>178</v>
       </c>
       <c r="P121" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q121">
         <v>2.88</v>
@@ -27318,7 +27324,7 @@
         <v>0.17</v>
       </c>
       <c r="AP126">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ126">
         <v>0.79</v>
@@ -27939,7 +27945,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ129">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR129">
         <v>0.99</v>
@@ -28888,7 +28894,7 @@
         <v>90</v>
       </c>
       <c r="P134" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q134">
         <v>3.2</v>
@@ -29094,7 +29100,7 @@
         <v>90</v>
       </c>
       <c r="P135" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q135">
         <v>5</v>
@@ -29587,7 +29593,7 @@
         <v>2</v>
       </c>
       <c r="AQ137">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR137">
         <v>1.66</v>
@@ -30330,7 +30336,7 @@
         <v>189</v>
       </c>
       <c r="P141" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q141">
         <v>2.8</v>
@@ -31154,7 +31160,7 @@
         <v>192</v>
       </c>
       <c r="P145" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q145">
         <v>2.75</v>
@@ -31232,7 +31238,7 @@
         <v>0.57</v>
       </c>
       <c r="AP145">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ145">
         <v>0.5</v>
@@ -31360,7 +31366,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q146">
         <v>3.75</v>
@@ -31566,7 +31572,7 @@
         <v>129</v>
       </c>
       <c r="P147" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q147">
         <v>3.75</v>
@@ -31772,7 +31778,7 @@
         <v>90</v>
       </c>
       <c r="P148" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q148">
         <v>2.4</v>
@@ -31978,7 +31984,7 @@
         <v>90</v>
       </c>
       <c r="P149" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q149">
         <v>3.1</v>
@@ -32390,7 +32396,7 @@
         <v>194</v>
       </c>
       <c r="P151" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q151">
         <v>1.62</v>
@@ -32802,7 +32808,7 @@
         <v>95</v>
       </c>
       <c r="P153" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q153">
         <v>2.63</v>
@@ -33626,7 +33632,7 @@
         <v>197</v>
       </c>
       <c r="P157" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q157">
         <v>2.7</v>
@@ -33832,7 +33838,7 @@
         <v>96</v>
       </c>
       <c r="P158" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q158">
         <v>2.55</v>
@@ -34038,7 +34044,7 @@
         <v>198</v>
       </c>
       <c r="P159" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q159">
         <v>3.3</v>
@@ -34119,7 +34125,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ159">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR159">
         <v>1.45</v>
@@ -34244,7 +34250,7 @@
         <v>90</v>
       </c>
       <c r="P160" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q160">
         <v>2.75</v>
@@ -35686,7 +35692,7 @@
         <v>109</v>
       </c>
       <c r="P167" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q167">
         <v>3.35</v>
@@ -36098,7 +36104,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q169">
         <v>2.8</v>
@@ -36304,7 +36310,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q170">
         <v>3</v>
@@ -36588,7 +36594,7 @@
         <v>1</v>
       </c>
       <c r="AP171">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ171">
         <v>1.5</v>
@@ -36716,7 +36722,7 @@
         <v>90</v>
       </c>
       <c r="P172" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q172">
         <v>2.63</v>
@@ -36922,7 +36928,7 @@
         <v>207</v>
       </c>
       <c r="P173" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q173">
         <v>2.3</v>
@@ -37952,7 +37958,7 @@
         <v>90</v>
       </c>
       <c r="P178" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q178">
         <v>3.25</v>
@@ -38033,7 +38039,7 @@
         <v>0.87</v>
       </c>
       <c r="AQ178">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR178">
         <v>1.34</v>
@@ -38364,7 +38370,7 @@
         <v>212</v>
       </c>
       <c r="P180" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q180">
         <v>2.2</v>
@@ -38570,7 +38576,7 @@
         <v>90</v>
       </c>
       <c r="P181" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q181">
         <v>3.25</v>
@@ -38854,7 +38860,7 @@
         <v>1.22</v>
       </c>
       <c r="AP182">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ182">
         <v>1.21</v>
@@ -39806,7 +39812,7 @@
         <v>90</v>
       </c>
       <c r="P187" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q187">
         <v>2.55</v>
@@ -40012,7 +40018,7 @@
         <v>215</v>
       </c>
       <c r="P188" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q188">
         <v>4.5</v>
@@ -40630,7 +40636,7 @@
         <v>90</v>
       </c>
       <c r="P191" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q191">
         <v>2.75</v>
@@ -40836,7 +40842,7 @@
         <v>90</v>
       </c>
       <c r="P192" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q192">
         <v>3.25</v>
@@ -41454,7 +41460,7 @@
         <v>214</v>
       </c>
       <c r="P195" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q195">
         <v>4.75</v>
@@ -41660,7 +41666,7 @@
         <v>90</v>
       </c>
       <c r="P196" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q196">
         <v>3.65</v>
@@ -41741,7 +41747,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ196">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR196">
         <v>1.27</v>
@@ -41866,7 +41872,7 @@
         <v>218</v>
       </c>
       <c r="P197" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q197">
         <v>1.94</v>
@@ -42278,7 +42284,7 @@
         <v>90</v>
       </c>
       <c r="P199" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q199">
         <v>3.75</v>
@@ -43308,7 +43314,7 @@
         <v>160</v>
       </c>
       <c r="P204" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q204">
         <v>3</v>
@@ -43514,7 +43520,7 @@
         <v>90</v>
       </c>
       <c r="P205" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q205">
         <v>2.75</v>
@@ -43798,7 +43804,7 @@
         <v>1.82</v>
       </c>
       <c r="AP206">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ206">
         <v>1.64</v>
@@ -43926,7 +43932,7 @@
         <v>90</v>
       </c>
       <c r="P207" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q207">
         <v>3.8</v>
@@ -45034,7 +45040,7 @@
         <v>1.18</v>
       </c>
       <c r="AP212">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ212">
         <v>0.93</v>
@@ -45162,7 +45168,7 @@
         <v>226</v>
       </c>
       <c r="P213" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q213">
         <v>3.75</v>
@@ -45243,7 +45249,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ213">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR213">
         <v>1.24</v>
@@ -45574,7 +45580,7 @@
         <v>228</v>
       </c>
       <c r="P215" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q215">
         <v>2.95</v>
@@ -45780,7 +45786,7 @@
         <v>90</v>
       </c>
       <c r="P216" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q216">
         <v>1.96</v>
@@ -46398,7 +46404,7 @@
         <v>229</v>
       </c>
       <c r="P219" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q219">
         <v>4.3</v>
@@ -47016,7 +47022,7 @@
         <v>90</v>
       </c>
       <c r="P222" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q222">
         <v>2.7</v>
@@ -47222,7 +47228,7 @@
         <v>231</v>
       </c>
       <c r="P223" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q223">
         <v>3.65</v>
@@ -47303,7 +47309,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ223">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR223">
         <v>1.28</v>
@@ -47428,7 +47434,7 @@
         <v>232</v>
       </c>
       <c r="P224" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q224">
         <v>5.2</v>
@@ -47840,7 +47846,7 @@
         <v>221</v>
       </c>
       <c r="P226" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q226">
         <v>4.4</v>
@@ -48046,7 +48052,7 @@
         <v>234</v>
       </c>
       <c r="P227" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q227">
         <v>2.7</v>
@@ -48664,7 +48670,7 @@
         <v>90</v>
       </c>
       <c r="P230" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q230">
         <v>3.04</v>
@@ -49282,7 +49288,7 @@
         <v>238</v>
       </c>
       <c r="P233" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q233">
         <v>3.1</v>
@@ -49488,7 +49494,7 @@
         <v>239</v>
       </c>
       <c r="P234" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q234">
         <v>1.85</v>
@@ -49900,7 +49906,7 @@
         <v>241</v>
       </c>
       <c r="P236" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q236">
         <v>3.7</v>
@@ -50518,7 +50524,7 @@
         <v>243</v>
       </c>
       <c r="P239" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q239">
         <v>3.1</v>
@@ -51011,7 +51017,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ241">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR241">
         <v>1.72</v>
@@ -51136,7 +51142,7 @@
         <v>245</v>
       </c>
       <c r="P242" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q242">
         <v>3.6</v>
@@ -51214,7 +51220,7 @@
         <v>1.58</v>
       </c>
       <c r="AP242">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ242">
         <v>1.64</v>
@@ -51960,7 +51966,7 @@
         <v>114</v>
       </c>
       <c r="P246" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q246">
         <v>3.6</v>
@@ -52990,7 +52996,7 @@
         <v>251</v>
       </c>
       <c r="P251" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q251">
         <v>4.75</v>
@@ -53402,7 +53408,7 @@
         <v>253</v>
       </c>
       <c r="P253" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q253">
         <v>2.2</v>
@@ -54020,7 +54026,7 @@
         <v>194</v>
       </c>
       <c r="P256" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q256">
         <v>3.9</v>
@@ -54226,7 +54232,7 @@
         <v>133</v>
       </c>
       <c r="P257" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q257">
         <v>2.65</v>
@@ -54638,7 +54644,7 @@
         <v>256</v>
       </c>
       <c r="P259" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q259">
         <v>4.75</v>
@@ -55050,7 +55056,7 @@
         <v>258</v>
       </c>
       <c r="P261" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q261">
         <v>2.63</v>
@@ -55207,6 +55213,212 @@
       </c>
       <c r="BP261">
         <v>1.24</v>
+      </c>
+    </row>
+    <row r="262" spans="1:68">
+      <c r="A262" s="1">
+        <v>261</v>
+      </c>
+      <c r="B262">
+        <v>7469122</v>
+      </c>
+      <c r="C262" t="s">
+        <v>68</v>
+      </c>
+      <c r="D262" t="s">
+        <v>69</v>
+      </c>
+      <c r="E262" s="2">
+        <v>45754.65625</v>
+      </c>
+      <c r="F262">
+        <v>29</v>
+      </c>
+      <c r="G262" t="s">
+        <v>72</v>
+      </c>
+      <c r="H262" t="s">
+        <v>75</v>
+      </c>
+      <c r="I262">
+        <v>0</v>
+      </c>
+      <c r="J262">
+        <v>0</v>
+      </c>
+      <c r="K262">
+        <v>0</v>
+      </c>
+      <c r="L262">
+        <v>3</v>
+      </c>
+      <c r="M262">
+        <v>1</v>
+      </c>
+      <c r="N262">
+        <v>4</v>
+      </c>
+      <c r="O262" t="s">
+        <v>259</v>
+      </c>
+      <c r="P262" t="s">
+        <v>356</v>
+      </c>
+      <c r="Q262">
+        <v>3.1</v>
+      </c>
+      <c r="R262">
+        <v>2.1</v>
+      </c>
+      <c r="S262">
+        <v>3.6</v>
+      </c>
+      <c r="T262">
+        <v>1.4</v>
+      </c>
+      <c r="U262">
+        <v>2.75</v>
+      </c>
+      <c r="V262">
+        <v>3</v>
+      </c>
+      <c r="W262">
+        <v>1.36</v>
+      </c>
+      <c r="X262">
+        <v>9</v>
+      </c>
+      <c r="Y262">
+        <v>1.07</v>
+      </c>
+      <c r="Z262">
+        <v>2.25</v>
+      </c>
+      <c r="AA262">
+        <v>3.3</v>
+      </c>
+      <c r="AB262">
+        <v>3.11</v>
+      </c>
+      <c r="AC262">
+        <v>1.07</v>
+      </c>
+      <c r="AD262">
+        <v>8</v>
+      </c>
+      <c r="AE262">
+        <v>1.33</v>
+      </c>
+      <c r="AF262">
+        <v>3.2</v>
+      </c>
+      <c r="AG262">
+        <v>1.92</v>
+      </c>
+      <c r="AH262">
+        <v>1.82</v>
+      </c>
+      <c r="AI262">
+        <v>1.73</v>
+      </c>
+      <c r="AJ262">
+        <v>2</v>
+      </c>
+      <c r="AK262">
+        <v>1.36</v>
+      </c>
+      <c r="AL262">
+        <v>1.28</v>
+      </c>
+      <c r="AM262">
+        <v>1.55</v>
+      </c>
+      <c r="AN262">
+        <v>2.14</v>
+      </c>
+      <c r="AO262">
+        <v>1.57</v>
+      </c>
+      <c r="AP262">
+        <v>2.2</v>
+      </c>
+      <c r="AQ262">
+        <v>1.47</v>
+      </c>
+      <c r="AR262">
+        <v>1.6</v>
+      </c>
+      <c r="AS262">
+        <v>1.44</v>
+      </c>
+      <c r="AT262">
+        <v>3.04</v>
+      </c>
+      <c r="AU262">
+        <v>8</v>
+      </c>
+      <c r="AV262">
+        <v>4</v>
+      </c>
+      <c r="AW262">
+        <v>8</v>
+      </c>
+      <c r="AX262">
+        <v>4</v>
+      </c>
+      <c r="AY262">
+        <v>16</v>
+      </c>
+      <c r="AZ262">
+        <v>8</v>
+      </c>
+      <c r="BA262">
+        <v>2</v>
+      </c>
+      <c r="BB262">
+        <v>4</v>
+      </c>
+      <c r="BC262">
+        <v>6</v>
+      </c>
+      <c r="BD262">
+        <v>1.84</v>
+      </c>
+      <c r="BE262">
+        <v>6.4</v>
+      </c>
+      <c r="BF262">
+        <v>2.18</v>
+      </c>
+      <c r="BG262">
+        <v>1.45</v>
+      </c>
+      <c r="BH262">
+        <v>2.55</v>
+      </c>
+      <c r="BI262">
+        <v>1.74</v>
+      </c>
+      <c r="BJ262">
+        <v>1.95</v>
+      </c>
+      <c r="BK262">
+        <v>2.2</v>
+      </c>
+      <c r="BL262">
+        <v>1.58</v>
+      </c>
+      <c r="BM262">
+        <v>2.88</v>
+      </c>
+      <c r="BN262">
+        <v>1.35</v>
+      </c>
+      <c r="BO262">
+        <v>3.8</v>
+      </c>
+      <c r="BP262">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
@@ -787,7 +787,7 @@
     <t>['47', '68']</t>
   </si>
   <si>
-    <t>['11', '55', '75', '80', '90+5']</t>
+    <t>['11', '54', '74', '79', '90+6']</t>
   </si>
   <si>
     <t>['12', '40']</t>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/France Ligue 2_20242025.xlsx
@@ -1939,10 +1939,10 @@
         <v>4</v>
       </c>
       <c r="AY2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA2">
         <v>4</v>
@@ -2557,10 +2557,10 @@
         <v>7</v>
       </c>
       <c r="AY5">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AZ5">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA5">
         <v>6</v>
@@ -2969,10 +2969,10 @@
         <v>5</v>
       </c>
       <c r="AY7">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AZ7">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA7">
         <v>3</v>
@@ -3175,10 +3175,10 @@
         <v>6</v>
       </c>
       <c r="AY8">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AZ8">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA8">
         <v>9</v>
@@ -3384,7 +3384,7 @@
         <v>3</v>
       </c>
       <c r="AZ9">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="BA9">
         <v>1</v>
@@ -3587,10 +3587,10 @@
         <v>0</v>
       </c>
       <c r="AY10">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="AZ10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BA10">
         <v>9</v>
@@ -3793,10 +3793,10 @@
         <v>3</v>
       </c>
       <c r="AY11">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AZ11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA11">
         <v>15</v>
@@ -3999,10 +3999,10 @@
         <v>8</v>
       </c>
       <c r="AY12">
+        <v>12</v>
+      </c>
+      <c r="AZ12">
         <v>13</v>
-      </c>
-      <c r="AZ12">
-        <v>15</v>
       </c>
       <c r="BA12">
         <v>8</v>
@@ -4205,10 +4205,10 @@
         <v>5</v>
       </c>
       <c r="AY13">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ13">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BA13">
         <v>7</v>
@@ -4411,10 +4411,10 @@
         <v>11</v>
       </c>
       <c r="AY14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AZ14">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="BA14">
         <v>0</v>
@@ -4617,10 +4617,10 @@
         <v>5</v>
       </c>
       <c r="AY15">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AZ15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA15">
         <v>6</v>
@@ -4823,10 +4823,10 @@
         <v>2</v>
       </c>
       <c r="AY16">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="AZ16">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA16">
         <v>19</v>
@@ -5029,10 +5029,10 @@
         <v>1</v>
       </c>
       <c r="AY17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ17">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BA17">
         <v>7</v>
@@ -5235,10 +5235,10 @@
         <v>3</v>
       </c>
       <c r="AY18">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ18">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="BA18">
         <v>9</v>
@@ -5441,10 +5441,10 @@
         <v>9</v>
       </c>
       <c r="AY19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ19">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="BA19">
         <v>2</v>
@@ -5647,10 +5647,10 @@
         <v>1</v>
       </c>
       <c r="AY20">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="AZ20">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BA20">
         <v>7</v>
@@ -5853,10 +5853,10 @@
         <v>2</v>
       </c>
       <c r="AY21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA21">
         <v>4</v>
@@ -6059,10 +6059,10 @@
         <v>5</v>
       </c>
       <c r="AY22">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AZ22">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BA22">
         <v>8</v>
@@ -6265,7 +6265,7 @@
         <v>5</v>
       </c>
       <c r="AY23">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AZ23">
         <v>10</v>
@@ -6471,10 +6471,10 @@
         <v>3</v>
       </c>
       <c r="AY24">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA24">
         <v>6</v>
@@ -6883,10 +6883,10 @@
         <v>5</v>
       </c>
       <c r="AY26">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ26">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="BA26">
         <v>3</v>
@@ -7089,10 +7089,10 @@
         <v>6</v>
       </c>
       <c r="AY27">
+        <v>11</v>
+      </c>
+      <c r="AZ27">
         <v>15</v>
-      </c>
-      <c r="AZ27">
-        <v>20</v>
       </c>
       <c r="BA27">
         <v>9</v>
@@ -7295,10 +7295,10 @@
         <v>0</v>
       </c>
       <c r="AY28">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AZ28">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BA28">
         <v>4</v>
@@ -7504,7 +7504,7 @@
         <v>10</v>
       </c>
       <c r="AZ29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA29">
         <v>6</v>
@@ -7707,10 +7707,10 @@
         <v>2</v>
       </c>
       <c r="AY30">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AZ30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA30">
         <v>13</v>
@@ -7913,10 +7913,10 @@
         <v>2</v>
       </c>
       <c r="AY31">
+        <v>4</v>
+      </c>
+      <c r="AZ31">
         <v>7</v>
-      </c>
-      <c r="AZ31">
-        <v>9</v>
       </c>
       <c r="BA31">
         <v>3</v>
@@ -8122,7 +8122,7 @@
         <v>10</v>
       </c>
       <c r="AZ32">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA32">
         <v>6</v>
@@ -8325,10 +8325,10 @@
         <v>3</v>
       </c>
       <c r="AY33">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AZ33">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="BA33">
         <v>5</v>
@@ -8531,10 +8531,10 @@
         <v>1</v>
       </c>
       <c r="AY34">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AZ34">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="BA34">
         <v>5</v>
@@ -8737,7 +8737,7 @@
         <v>5</v>
       </c>
       <c r="AY35">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AZ35">
         <v>9</v>
@@ -8943,10 +8943,10 @@
         <v>1</v>
       </c>
       <c r="AY36">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ36">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA36">
         <v>5</v>
@@ -9149,10 +9149,10 @@
         <v>4</v>
       </c>
       <c r="AY37">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ37">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA37">
         <v>9</v>
@@ -9355,10 +9355,10 @@
         <v>9</v>
       </c>
       <c r="AY38">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AZ38">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BA38">
         <v>4</v>
@@ -9561,10 +9561,10 @@
         <v>0</v>
       </c>
       <c r="AY39">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AZ39">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA39">
         <v>10</v>
@@ -9767,10 +9767,10 @@
         <v>10</v>
       </c>
       <c r="AY40">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AZ40">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BA40">
         <v>5</v>
@@ -9973,10 +9973,10 @@
         <v>4</v>
       </c>
       <c r="AY41">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AZ41">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BA41">
         <v>2</v>
@@ -10179,10 +10179,10 @@
         <v>6</v>
       </c>
       <c r="AY42">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AZ42">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="BA42">
         <v>2</v>
@@ -10385,10 +10385,10 @@
         <v>1</v>
       </c>
       <c r="AY43">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ43">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BA43">
         <v>6</v>
@@ -10594,7 +10594,7 @@
         <v>15</v>
       </c>
       <c r="AZ44">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="BA44">
         <v>3</v>
@@ -10797,10 +10797,10 @@
         <v>8</v>
       </c>
       <c r="AY45">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AZ45">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA45">
         <v>5</v>
@@ -11003,10 +11003,10 @@
         <v>7</v>
       </c>
       <c r="AY46">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AZ46">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="BA46">
         <v>1</v>
@@ -11209,7 +11209,7 @@
         <v>3</v>
       </c>
       <c r="AY47">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AZ47">
         <v>8</v>
@@ -11415,10 +11415,10 @@
         <v>9</v>
       </c>
       <c r="AY48">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ48">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="BA48">
         <v>2</v>
@@ -11621,10 +11621,10 @@
         <v>4</v>
       </c>
       <c r="AY49">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ49">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA49">
         <v>5</v>
@@ -11827,10 +11827,10 @@
         <v>3</v>
       </c>
       <c r="AY50">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ50">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA50">
         <v>2</v>
@@ -12033,10 +12033,10 @@
         <v>3</v>
       </c>
       <c r="AY51">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AZ51">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA51">
         <v>7</v>
@@ -12239,10 +12239,10 @@
         <v>5</v>
       </c>
       <c r="AY52">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AZ52">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA52">
         <v>6</v>
@@ -12445,10 +12445,10 @@
         <v>6</v>
       </c>
       <c r="AY53">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AZ53">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA53">
         <v>5</v>
@@ -12651,7 +12651,7 @@
         <v>3</v>
       </c>
       <c r="AY54">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AZ54">
         <v>8</v>
@@ -12857,10 +12857,10 @@
         <v>0</v>
       </c>
       <c r="AY55">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AZ55">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="BA55">
         <v>3</v>
@@ -13063,10 +13063,10 @@
         <v>2</v>
       </c>
       <c r="AY56">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="AZ56">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA56">
         <v>8</v>
@@ -13269,10 +13269,10 @@
         <v>3</v>
       </c>
       <c r="AY57">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ57">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BA57">
         <v>3</v>
@@ -13475,10 +13475,10 @@
         <v>7</v>
       </c>
       <c r="AY58">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ58">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="BA58">
         <v>7</v>
@@ -13681,10 +13681,10 @@
         <v>6</v>
       </c>
       <c r="AY59">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="AZ59">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA59">
         <v>5</v>
@@ -13887,7 +13887,7 @@
         <v>4</v>
       </c>
       <c r="AY60">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ60">
         <v>8</v>
@@ -14093,10 +14093,10 @@
         <v>4</v>
       </c>
       <c r="AY61">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AZ61">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BA61">
         <v>3</v>
@@ -14299,10 +14299,10 @@
         <v>3</v>
       </c>
       <c r="AY62">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ62">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA62">
         <v>6</v>
@@ -14508,7 +14508,7 @@
         <v>7</v>
       </c>
       <c r="AZ63">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA63">
         <v>1</v>
@@ -14711,10 +14711,10 @@
         <v>3</v>
       </c>
       <c r="AY64">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ64">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BA64">
         <v>7</v>
@@ -14917,10 +14917,10 @@
         <v>2</v>
       </c>
       <c r="AY65">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AZ65">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="BA65">
         <v>11</v>
@@ -15123,10 +15123,10 @@
         <v>4</v>
       </c>
       <c r="AY66">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ66">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="BA66">
         <v>5</v>
@@ -15329,7 +15329,7 @@
         <v>2</v>
       </c>
       <c r="AY67">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ67">
         <v>5</v>
@@ -15535,10 +15535,10 @@
         <v>4</v>
       </c>
       <c r="AY68">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ68">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="BA68">
         <v>3</v>
@@ -15744,7 +15744,7 @@
         <v>10</v>
       </c>
       <c r="AZ69">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="BA69">
         <v>3</v>
@@ -15950,7 +15950,7 @@
         <v>5</v>
       </c>
       <c r="AZ70">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="BA70">
         <v>0</v>
@@ -16359,10 +16359,10 @@
         <v>1</v>
       </c>
       <c r="AY72">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ72">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA72">
         <v>2</v>
@@ -17801,10 +17801,10 @@
         <v>7</v>
       </c>
       <c r="AY79">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ79">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA79">
         <v>4</v>
@@ -18007,7 +18007,7 @@
         <v>5</v>
       </c>
       <c r="AY80">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AZ80">
         <v>10</v>
@@ -18213,10 +18213,10 @@
         <v>3</v>
       </c>
       <c r="AY81">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ81">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA81">
         <v>6</v>
@@ -18419,10 +18419,10 @@
         <v>4</v>
       </c>
       <c r="AY82">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AZ82">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA82">
         <v>6</v>
@@ -19661,13 +19661,13 @@
         <v>-1</v>
       </c>
       <c r="BA88">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="BB88">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="BC88">
-        <v>11</v>
+        <v>-1</v>
       </c>
       <c r="BD88">
         <v>2.8</v>
@@ -19861,10 +19861,10 @@
         <v>3</v>
       </c>
       <c r="AY89">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AZ89">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA89">
         <v>5</v>
@@ -20067,10 +20067,10 @@
         <v>1</v>
       </c>
       <c r="AY90">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AZ90">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="BA90">
         <v>6</v>
@@ -20273,10 +20273,10 @@
         <v>9</v>
       </c>
       <c r="AY91">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AZ91">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="BA91">
         <v>0</v>
@@ -20479,10 +20479,10 @@
         <v>4</v>
       </c>
       <c r="AY92">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ92">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BA92">
         <v>2</v>
@@ -20685,10 +20685,10 @@
         <v>2</v>
       </c>
       <c r="AY93">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AZ93">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BA93">
         <v>3</v>
@@ -20891,10 +20891,10 @@
         <v>2</v>
       </c>
       <c r="AY94">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AZ94">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BA94">
         <v>4</v>
@@ -21097,10 +21097,10 @@
         <v>6</v>
       </c>
       <c r="AY95">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AZ95">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="BA95">
         <v>2</v>
@@ -21303,10 +21303,10 @@
         <v>1</v>
       </c>
       <c r="AY96">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ96">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA96">
         <v>2</v>
@@ -21509,10 +21509,10 @@
         <v>4</v>
       </c>
       <c r="AY97">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AZ97">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="BA97">
         <v>4</v>
@@ -21715,10 +21715,10 @@
         <v>8</v>
       </c>
       <c r="AY98">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AZ98">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA98">
         <v>6</v>
@@ -21921,10 +21921,10 @@
         <v>6</v>
       </c>
       <c r="AY99">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AZ99">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BA99">
         <v>7</v>
@@ -22127,10 +22127,10 @@
         <v>9</v>
       </c>
       <c r="AY100">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AZ100">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BA100">
         <v>5</v>
@@ -22333,10 +22333,10 @@
         <v>2</v>
       </c>
       <c r="AY101">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ101">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="BA101">
         <v>5</v>
@@ -22539,10 +22539,10 @@
         <v>4</v>
       </c>
       <c r="AY102">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AZ102">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BA102">
         <v>2</v>
@@ -22745,10 +22745,10 @@
         <v>4</v>
       </c>
       <c r="AY103">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AZ103">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA103">
         <v>7</v>
@@ -22951,10 +22951,10 @@
         <v>4</v>
       </c>
       <c r="AY104">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AZ104">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA104">
         <v>3</v>
@@ -23157,10 +23157,10 @@
         <v>8</v>
       </c>
       <c r="AY105">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AZ105">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BA105">
         <v>2</v>
@@ -23363,10 +23363,10 @@
         <v>9</v>
       </c>
       <c r="AY106">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ106">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="BA106">
         <v>1</v>
@@ -23569,10 +23569,10 @@
         <v>8</v>
       </c>
       <c r="AY107">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AZ107">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BA107">
         <v>4</v>
@@ -23775,10 +23775,10 @@
         <v>3</v>
       </c>
       <c r="AY108">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AZ108">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA108">
         <v>6</v>
@@ -23981,10 +23981,10 @@
         <v>3</v>
       </c>
       <c r="AY109">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ109">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA109">
         <v>5</v>
@@ -24187,10 +24187,10 @@
         <v>3</v>
       </c>
       <c r="AY110">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="AZ110">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA110">
         <v>10</v>
@@ -24393,10 +24393,10 @@
         <v>3</v>
       </c>
       <c r="AY111">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ111">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA111">
         <v>3</v>
@@ -24599,10 +24599,10 @@
         <v>2</v>
       </c>
       <c r="AY112">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AZ112">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BA112">
         <v>2</v>
@@ -24805,10 +24805,10 @@
         <v>6</v>
       </c>
       <c r="AY113">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ113">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA113">
         <v>7</v>
@@ -25011,10 +25011,10 @@
         <v>4</v>
       </c>
       <c r="AY114">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ114">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="BA114">
         <v>3</v>
@@ -25217,10 +25217,10 @@
         <v>3</v>
       </c>
       <c r="AY115">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AZ115">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BA115">
         <v>6</v>
@@ -25423,10 +25423,10 @@
         <v>4</v>
       </c>
       <c r="AY116">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AZ116">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="BA116">
         <v>3</v>
@@ -25629,10 +25629,10 @@
         <v>8</v>
       </c>
       <c r="AY117">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="AZ117">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA117">
         <v>5</v>
@@ -26253,13 +26253,13 @@
         <v>-1</v>
       </c>
       <c r="BA120">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="BB120">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="BC120">
-        <v>18</v>
+        <v>-1</v>
       </c>
       <c r="BD120">
         <v>1.82</v>
@@ -27283,13 +27283,13 @@
         <v>-1</v>
       </c>
       <c r="BA125">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="BB125">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="BC125">
-        <v>12</v>
+        <v>-1</v>
       </c>
       <c r="BD125">
         <v>2.54</v>
@@ -27483,7 +27483,7 @@
         <v>1</v>
       </c>
       <c r="AY126">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AZ126">
         <v>3</v>
@@ -27692,7 +27692,7 @@
         <v>6</v>
       </c>
       <c r="AZ127">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BA127">
         <v>2</v>
@@ -27895,10 +27895,10 @@
         <v>4</v>
       </c>
       <c r="AY128">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AZ128">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA128">
         <v>4</v>
@@ -28101,10 +28101,10 @@
         <v>4</v>
       </c>
       <c r="AY129">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ129">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA129">
         <v>2</v>
@@ -28307,10 +28307,10 @@
         <v>3</v>
       </c>
       <c r="AY130">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ130">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="BA130">
         <v>2</v>
@@ -28513,10 +28513,10 @@
         <v>7</v>
       </c>
       <c r="AY131">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AZ131">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BA131">
         <v>8</v>
@@ -28719,10 +28719,10 @@
         <v>6</v>
       </c>
       <c r="AY132">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="AZ132">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BA132">
         <v>12</v>
@@ -28925,10 +28925,10 @@
         <v>8</v>
       </c>
       <c r="AY133">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AZ133">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BA133">
         <v>4</v>
@@ -29131,10 +29131,10 @@
         <v>8</v>
       </c>
       <c r="AY134">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ134">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="BA134">
         <v>2</v>
@@ -29337,10 +29337,10 @@
         <v>4</v>
       </c>
       <c r="AY135">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AZ135">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BA135">
         <v>3</v>
@@ -29543,10 +29543,10 @@
         <v>5</v>
       </c>
       <c r="AY136">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ136">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="BA136">
         <v>5</v>
@@ -29749,10 +29749,10 @@
         <v>3</v>
       </c>
       <c r="AY137">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AZ137">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA137">
         <v>3</v>
@@ -29955,10 +29955,10 @@
         <v>5</v>
       </c>
       <c r="AY138">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="AZ138">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA138">
         <v>4</v>
@@ -30161,10 +30161,10 @@
         <v>5</v>
       </c>
       <c r="AY139">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AZ139">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA139">
         <v>5</v>
@@ -30367,10 +30367,10 @@
         <v>3</v>
       </c>
       <c r="AY140">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AZ140">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BA140">
         <v>4</v>
@@ -30573,10 +30573,10 @@
         <v>2</v>
       </c>
       <c r="AY141">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AZ141">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA141">
         <v>8</v>
@@ -30779,10 +30779,10 @@
         <v>9</v>
       </c>
       <c r="AY142">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="AZ142">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="BA142">
         <v>4</v>
@@ -30985,10 +30985,10 @@
         <v>5</v>
       </c>
       <c r="AY143">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AZ143">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA143">
         <v>8</v>
@@ -31603,10 +31603,10 @@
         <v>4</v>
       </c>
       <c r="AY146">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ146">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA146">
         <v>4</v>
@@ -31809,10 +31809,10 @@
         <v>4</v>
       </c>
       <c r="AY147">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ147">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA147">
         <v>4</v>
@@ -32015,10 +32015,10 @@
         <v>7</v>
       </c>
       <c r="AY148">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ148">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA148">
         <v>5</v>
@@ -32221,10 +32221,10 @@
         <v>1</v>
       </c>
       <c r="AY149">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AZ149">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA149">
         <v>4</v>
@@ -32427,10 +32427,10 @@
         <v>4</v>
       </c>
       <c r="AY150">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ150">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA150">
         <v>4</v>
@@ -32633,10 +32633,10 @@
         <v>4</v>
       </c>
       <c r="AY151">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="AZ151">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA151">
         <v>5</v>
@@ -32839,10 +32839,10 @@
         <v>8</v>
       </c>
       <c r="AY152">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="AZ152">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BA152">
         <v>6</v>
@@ -33045,10 +33045,10 @@
         <v>3</v>
       </c>
       <c r="AY153">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AZ153">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA153">
         <v>3</v>
@@ -33254,7 +33254,7 @@
         <v>9</v>
       </c>
       <c r="AZ154">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BA154">
         <v>6</v>
@@ -33457,10 +33457,10 @@
         <v>8</v>
       </c>
       <c r="AY155">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AZ155">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA155">
         <v>4</v>
@@ -33663,10 +33663,10 @@
         <v>3</v>
       </c>
       <c r="AY156">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ156">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA156">
         <v>9</v>
@@ -33869,10 +33869,10 @@
         <v>4</v>
       </c>
       <c r="AY157">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AZ157">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BA157">
         <v>4</v>
@@ -34075,10 +34075,10 @@
         <v>5</v>
       </c>
       <c r="AY158">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AZ158">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="BA158">
         <v>3</v>
@@ -34281,10 +34281,10 @@
         <v>4</v>
       </c>
       <c r="AY159">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AZ159">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA159">
         <v>4</v>
@@ -34487,10 +34487,10 @@
         <v>2</v>
       </c>
       <c r="AY160">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ160">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA160">
         <v>2</v>
@@ -34693,10 +34693,10 @@
         <v>8</v>
       </c>
       <c r="AY161">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AZ161">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BA161">
         <v>8</v>
@@ -34899,10 +34899,10 @@
         <v>2</v>
       </c>
       <c r="AY162">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="AZ162">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="BA162">
         <v>13</v>
@@ -36959,10 +36959,10 @@
         <v>1</v>
       </c>
       <c r="AY172">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="AZ172">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA172">
         <v>10</v>
@@ -38813,7 +38813,7 @@
         <v>8</v>
       </c>
       <c r="AY181">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ181">
         <v>15</v>
@@ -44581,7 +44581,7 @@
         <v>2</v>
       </c>
       <c r="AY209">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ209">
         <v>5</v>
@@ -46847,7 +46847,7 @@
         <v>6</v>
       </c>
       <c r="AY220">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ220">
         <v>8</v>
@@ -53027,10 +53027,10 @@
         <v>14</v>
       </c>
       <c r="AY250">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ250">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA250">
         <v>0</v>
@@ -56941,10 +56941,10 @@
         <v>4</v>
       </c>
       <c r="AY269">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AZ269">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA269">
         <v>7</v>
@@ -63121,19 +63121,19 @@
         <v>9</v>
       </c>
       <c r="AY299">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="AZ299">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="BA299">
+        <v>9</v>
+      </c>
+      <c r="BB299">
+        <v>2</v>
+      </c>
+      <c r="BC299">
         <v>11</v>
-      </c>
-      <c r="BB299">
-        <v>2</v>
-      </c>
-      <c r="BC299">
-        <v>13</v>
       </c>
       <c r="BD299">
         <v>1.41</v>
@@ -63533,19 +63533,19 @@
         <v>1</v>
       </c>
       <c r="AY301">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="AZ301">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="BA301">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB301">
         <v>2</v>
       </c>
       <c r="BC301">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD301">
         <v>1.68</v>
@@ -64366,10 +64366,10 @@
         <v>3</v>
       </c>
       <c r="BB305">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC305">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD305">
         <v>1.29</v>
@@ -64975,7 +64975,7 @@
         <v>5</v>
       </c>
       <c r="AY308">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ308">
         <v>9</v>
@@ -65181,10 +65181,10 @@
         <v>5</v>
       </c>
       <c r="AY309">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ309">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA309">
         <v>1</v>
